--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -532,14 +532,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>対象期間：2026-01-05 23:21:47 ～ 2026-07-28 23:51:39</t>
+          <t>対象期間：2026-01-05 14:21:47 ～ 2026-07-28 14:51:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-07-29 18:18:33</t>
+          <t>出力日時：2026-07-29 17:34:37</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1.249649122807017</v>
+        <v>1.249649122807018</v>
       </c>
     </row>
     <row r="30">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>2.045228070175439</v>
+        <v>2.045228070175438</v>
       </c>
     </row>
   </sheetData>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.249649122807017</v>
+        <v>1.249649122807018</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>63.44210526315789</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>2.045228070175439</v>
+        <v>2.045228070175438</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.933833333333333</v>
+        <v>4.933833333333332</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>31.96666666666667</v>
@@ -1133,7 +1133,7 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1239,7 +1239,7 @@
         <v>52.89225589225589</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>1.716734006734007</v>
+        <v>1.716734006734006</v>
       </c>
     </row>
     <row r="3">
@@ -1281,7 +1281,7 @@
         <v>69.22857142857143</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.189</v>
+        <v>2.189000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.801860465116279</v>
+        <v>1.80186046511628</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>68.76744186046511</v>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5.148285714285715</v>
+        <v>5.148285714285714</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>34.6</v>
@@ -1758,7 +1758,7 @@
         <v>25.625</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.85625</v>
+        <v>0.8562500000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>21.83333333333333</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.8633333333333333</v>
+        <v>0.8633333333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5.050000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>16.25</v>
@@ -3366,7 +3366,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 23:51:39</t>
+          <t>2026-07-28 14:51:39</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 23:05:20</t>
+          <t>2026-07-28 14:05:20</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27 01:21:51</t>
+          <t>2026-07-26 16:21:51</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27 00:43:02</t>
+          <t>2026-07-26 15:43:02</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 23:12:09</t>
+          <t>2026-07-25 14:12:09</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 22:30:57</t>
+          <t>2026-07-25 13:30:57</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 00:11:55</t>
+          <t>2026-07-24 15:11:55</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24 23:25:38</t>
+          <t>2026-07-24 14:25:38</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22 00:17:56</t>
+          <t>2026-07-21 15:17:56</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22 00:04:35</t>
+          <t>2026-07-21 15:04:35</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -4166,7 +4166,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 23:25:56</t>
+          <t>2026-07-21 14:25:56</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 22:44:36</t>
+          <t>2026-07-21 13:44:36</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -4326,7 +4326,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 22:18:59</t>
+          <t>2026-07-21 13:18:59</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20 03:20:20</t>
+          <t>2026-07-19 18:20:20</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -4486,7 +4486,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20 02:39:51</t>
+          <t>2026-07-19 17:39:51</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -4566,7 +4566,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:59:14</t>
+          <t>2026-07-18 09:59:14</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -4646,7 +4646,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:21:14</t>
+          <t>2026-07-18 09:21:14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 23:06:28</t>
+          <t>2026-07-16 14:06:28</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 22:32:42</t>
+          <t>2026-07-16 13:32:42</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -4886,7 +4886,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 00:40:48</t>
+          <t>2026-07-15 15:40:48</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -4966,7 +4966,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 23:41:56</t>
+          <t>2026-07-15 14:41:56</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 22:58:44</t>
+          <t>2026-07-15 13:58:44</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -5126,7 +5126,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 22:34:16</t>
+          <t>2026-07-15 13:34:16</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 23:36:35</t>
+          <t>2026-07-14 14:36:35</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -5286,7 +5286,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 22:49:50</t>
+          <t>2026-07-14 13:49:50</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -5366,7 +5366,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 01:02:29</t>
+          <t>2026-07-13 16:02:29</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 00:22:46</t>
+          <t>2026-07-13 15:22:46</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -5526,7 +5526,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 23:51:38</t>
+          <t>2026-07-13 14:51:38</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -5606,7 +5606,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 02:05:19</t>
+          <t>2026-07-12 17:05:19</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 01:29:17</t>
+          <t>2026-07-12 16:29:17</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -5766,7 +5766,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 03:11:38</t>
+          <t>2026-07-11 18:11:38</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -5846,7 +5846,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 02:46:15</t>
+          <t>2026-07-11 17:46:15</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -5926,7 +5926,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 03:42:29</t>
+          <t>2026-07-10 18:42:29</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -6006,7 +6006,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 03:06:21</t>
+          <t>2026-07-10 18:06:21</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:55:25</t>
+          <t>2026-07-08 17:55:25</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:17:09</t>
+          <t>2026-07-08 17:17:09</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 02:03:51</t>
+          <t>2026-07-05 17:03:51</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -6326,7 +6326,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 01:07:17</t>
+          <t>2026-07-05 16:07:17</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -6406,7 +6406,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 00:23:00</t>
+          <t>2026-07-05 15:23:00</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -6486,7 +6486,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05 03:21:23</t>
+          <t>2026-07-04 18:21:23</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -6566,7 +6566,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-07-04 03:01:40</t>
+          <t>2026-07-03 18:01:40</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -6646,7 +6646,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03 01:48:19</t>
+          <t>2026-07-02 16:48:19</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -6726,7 +6726,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01 00:21:19</t>
+          <t>2026-06-30 15:21:19</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -6806,7 +6806,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 23:38:16</t>
+          <t>2026-06-30 14:38:16</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -6886,7 +6886,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 01:16:28</t>
+          <t>2026-06-29 16:16:28</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -6966,7 +6966,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 00:34:32</t>
+          <t>2026-06-29 15:34:32</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26 00:50:56</t>
+          <t>2026-06-25 15:50:56</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -7126,7 +7126,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26 00:06:40</t>
+          <t>2026-06-25 15:06:40</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07:56</t>
+          <t>2026-06-24 17:07:56</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -7286,7 +7286,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 01:33:19</t>
+          <t>2026-06-24 16:33:19</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -7366,7 +7366,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:47:59</t>
+          <t>2026-06-24 15:47:59</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -7446,7 +7446,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:08:31</t>
+          <t>2026-06-24 15:08:31</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -7526,7 +7526,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 23:33:15</t>
+          <t>2026-06-24 14:33:15</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 22:39:11</t>
+          <t>2026-06-24 13:39:11</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -7686,7 +7686,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 01:16:06</t>
+          <t>2026-06-22 16:16:06</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -7766,7 +7766,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 00:38:08</t>
+          <t>2026-06-22 15:38:08</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -7846,7 +7846,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 00:29:33</t>
+          <t>2026-06-22 15:29:33</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -7926,7 +7926,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 01:54:04</t>
+          <t>2026-06-18 16:54:04</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -8006,7 +8006,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 01:14:50</t>
+          <t>2026-06-18 16:14:50</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -8086,7 +8086,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 00:35:17</t>
+          <t>2026-06-18 15:35:17</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 23:55:50</t>
+          <t>2026-06-18 14:55:50</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -8246,7 +8246,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 00:44:42</t>
+          <t>2026-06-17 15:44:42</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -8326,7 +8326,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 23:57:38</t>
+          <t>2026-06-17 14:57:38</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -8406,7 +8406,7 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 01:58:55</t>
+          <t>2026-06-16 16:58:55</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -8486,7 +8486,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 01:30:07</t>
+          <t>2026-06-16 16:30:07</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -8566,7 +8566,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 03:10:28</t>
+          <t>2026-06-14 18:10:28</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 02:27:52</t>
+          <t>2026-06-14 17:27:52</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 01:57:23</t>
+          <t>2026-06-14 16:57:23</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -8806,7 +8806,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 01:27:22</t>
+          <t>2026-06-14 16:27:22</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -8886,7 +8886,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 00:24:35</t>
+          <t>2026-06-14 15:24:35</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -8966,7 +8966,7 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 23:46:55</t>
+          <t>2026-06-14 14:46:55</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -9046,7 +9046,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 01:41:53</t>
+          <t>2026-06-13 16:41:53</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -9126,7 +9126,7 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 00:52:58</t>
+          <t>2026-06-13 15:52:58</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -9206,7 +9206,7 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 00:14:23</t>
+          <t>2026-06-13 15:14:23</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
@@ -9286,7 +9286,7 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 23:45:21</t>
+          <t>2026-06-13 14:45:21</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -9366,7 +9366,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 23:05:32</t>
+          <t>2026-06-13 14:05:32</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -9446,7 +9446,7 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 01:08:14</t>
+          <t>2026-06-10 16:08:14</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -9526,7 +9526,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:34:35</t>
+          <t>2026-06-10 15:34:35</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -9606,7 +9606,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:09:17</t>
+          <t>2026-06-10 15:09:17</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -9686,7 +9686,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 23:27:53</t>
+          <t>2026-06-10 14:27:53</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -9766,7 +9766,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 00:49:00</t>
+          <t>2026-06-09 15:49:00</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -9846,7 +9846,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06 02:58:51</t>
+          <t>2026-06-05 17:58:51</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -9926,7 +9926,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06 02:15:04</t>
+          <t>2026-06-05 17:15:04</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -10006,7 +10006,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 23:49:14</t>
+          <t>2026-06-04 14:49:14</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -10086,7 +10086,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 21:40:04</t>
+          <t>2026-06-04 12:40:04</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -10166,7 +10166,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 21:17:24</t>
+          <t>2026-06-04 12:17:24</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 01:06:27</t>
+          <t>2026-06-03 16:06:27</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -10326,7 +10326,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 00:31:09</t>
+          <t>2026-06-03 15:31:09</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 23:53:57</t>
+          <t>2026-06-03 14:53:57</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -10486,7 +10486,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 22:44:02</t>
+          <t>2026-06-03 13:44:02</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -10566,7 +10566,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02 22:49:11</t>
+          <t>2026-06-02 13:49:11</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -10646,7 +10646,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:56:06</t>
+          <t>2026-06-01 14:56:06</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -10726,7 +10726,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:20:26</t>
+          <t>2026-06-01 14:20:26</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -10806,7 +10806,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:01:06</t>
+          <t>2026-06-01 14:01:06</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -10886,7 +10886,7 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31 03:01:04</t>
+          <t>2026-05-30 18:01:04</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -10966,7 +10966,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31 02:13:41</t>
+          <t>2026-05-30 17:13:41</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -11046,7 +11046,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 23:00:40</t>
+          <t>2026-05-25 14:00:40</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -11126,7 +11126,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 01:55:47</t>
+          <t>2026-05-24 16:55:47</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 01:24:22</t>
+          <t>2026-05-24 16:24:22</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -11286,7 +11286,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 23:49:25</t>
+          <t>2026-05-24 14:49:25</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -11366,7 +11366,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 03:13:39</t>
+          <t>2026-05-23 18:13:39</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -11446,7 +11446,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 02:41:52</t>
+          <t>2026-05-23 17:41:52</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -11526,7 +11526,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 23:19:04</t>
+          <t>2026-05-23 14:19:04</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 22:43:20</t>
+          <t>2026-05-23 13:43:20</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -11686,7 +11686,7 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 15:54:19</t>
+          <t>2026-05-23 06:54:19</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -11766,7 +11766,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 02:25:24</t>
+          <t>2026-05-22 17:25:24</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -11846,7 +11846,7 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 01:29:23</t>
+          <t>2026-05-21 16:29:23</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -11926,7 +11926,7 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 00:48:49</t>
+          <t>2026-05-21 15:48:49</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -12006,7 +12006,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:45</t>
+          <t>2026-05-21 15:00:45</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 23:22:44</t>
+          <t>2026-05-21 14:22:44</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -12166,7 +12166,7 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 00:05:15</t>
+          <t>2026-05-20 15:05:15</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -12246,7 +12246,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 23:43:50</t>
+          <t>2026-05-20 14:43:50</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -12326,7 +12326,7 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 22:57:45</t>
+          <t>2026-05-20 13:57:45</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -12406,7 +12406,7 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 01:25:45</t>
+          <t>2026-05-19 16:25:45</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -12486,7 +12486,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 00:46:42</t>
+          <t>2026-05-19 15:46:42</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -12566,7 +12566,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>2026-05-18 22:56:39</t>
+          <t>2026-05-18 13:56:39</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -12646,7 +12646,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 01:35:56</t>
+          <t>2026-05-14 16:35:56</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -12726,7 +12726,7 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 01:17:05</t>
+          <t>2026-05-14 16:17:05</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -12806,7 +12806,7 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 00:05:48</t>
+          <t>2026-05-14 15:05:48</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -12886,7 +12886,7 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14 01:25:38</t>
+          <t>2026-05-13 16:25:38</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -12966,7 +12966,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>2026-05-12 00:19:57</t>
+          <t>2026-05-11 15:19:57</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -13046,7 +13046,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 23:54:15</t>
+          <t>2026-05-11 14:54:15</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -13126,7 +13126,7 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 23:14:30</t>
+          <t>2026-05-11 14:14:30</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -13206,7 +13206,7 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 22:37:05</t>
+          <t>2026-05-11 13:37:05</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -13286,7 +13286,7 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 21:53:13</t>
+          <t>2026-05-11 12:53:13</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -13366,7 +13366,7 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 00:04:01</t>
+          <t>2026-05-10 15:04:01</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -13446,7 +13446,7 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:54:24</t>
+          <t>2026-05-09 16:54:24</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -13526,7 +13526,7 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:22:50</t>
+          <t>2026-05-09 16:22:50</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -13606,7 +13606,7 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 00:26:16</t>
+          <t>2026-05-09 15:26:16</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -13686,7 +13686,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 23:38:30</t>
+          <t>2026-05-09 14:38:30</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 22:50:20</t>
+          <t>2026-05-09 13:50:20</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -13846,7 +13846,7 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 22:13:25</t>
+          <t>2026-05-09 13:13:25</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -13926,7 +13926,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 20:00:11</t>
+          <t>2026-05-09 11:00:11</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -14006,7 +14006,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 19:10:28</t>
+          <t>2026-05-09 10:10:28</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -14086,7 +14086,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 02:17:27</t>
+          <t>2026-05-08 17:17:27</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -14166,7 +14166,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 01:38:25</t>
+          <t>2026-05-08 16:38:25</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -14246,7 +14246,7 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 00:58:58</t>
+          <t>2026-05-08 15:58:58</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -14326,7 +14326,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 00:37:55</t>
+          <t>2026-05-08 15:37:55</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -14406,7 +14406,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 01:48:31</t>
+          <t>2026-05-07 16:48:31</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -14486,7 +14486,7 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 01:02:52</t>
+          <t>2026-05-07 16:02:52</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -14566,7 +14566,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 00:23:29</t>
+          <t>2026-05-07 15:23:29</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -14646,7 +14646,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 01:30:56</t>
+          <t>2026-05-06 16:30:56</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -14726,7 +14726,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 00:42:16</t>
+          <t>2026-05-06 15:42:16</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -14806,7 +14806,7 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 23:44:04</t>
+          <t>2026-05-06 14:44:04</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -14886,7 +14886,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:13:52</t>
+          <t>2026-05-06 09:13:52</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -14966,7 +14966,7 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:05:08</t>
+          <t>2026-05-06 09:05:08</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -15046,7 +15046,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 17:22:30</t>
+          <t>2026-05-06 08:22:30</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -15126,7 +15126,7 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 16:28:42</t>
+          <t>2026-05-06 07:28:42</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -15206,7 +15206,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 03:16:57</t>
+          <t>2026-05-05 18:16:57</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -15286,7 +15286,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:32:40</t>
+          <t>2026-05-05 17:32:40</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -15366,7 +15366,7 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:23:28</t>
+          <t>2026-05-05 17:23:28</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 01:48:28</t>
+          <t>2026-05-05 16:48:28</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -15526,7 +15526,7 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 00:52:33</t>
+          <t>2026-05-05 15:52:33</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -15606,7 +15606,7 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 17:43:06</t>
+          <t>2026-05-05 08:43:06</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -15686,7 +15686,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>2026-05-03 00:36:42</t>
+          <t>2026-05-02 15:36:42</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -15766,7 +15766,7 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 23:51:09</t>
+          <t>2026-05-02 14:51:09</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -15846,7 +15846,7 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 22:15:10</t>
+          <t>2026-05-02 13:15:10</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -15926,7 +15926,7 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 21:29:49</t>
+          <t>2026-05-02 12:29:49</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 01:39:42</t>
+          <t>2026-04-30 16:39:42</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -16086,7 +16086,7 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 01:01:34</t>
+          <t>2026-04-30 16:01:34</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -16166,7 +16166,7 @@
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 00:24:48</t>
+          <t>2026-04-30 15:24:48</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -16246,7 +16246,7 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 23:37:10</t>
+          <t>2026-04-30 14:37:10</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -16326,7 +16326,7 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 22:58:06</t>
+          <t>2026-04-30 13:58:06</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -16406,7 +16406,7 @@
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 03:29:33</t>
+          <t>2026-04-29 18:29:33</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -16486,7 +16486,7 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 02:54:07</t>
+          <t>2026-04-29 17:54:07</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -16566,7 +16566,7 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 02:20:58</t>
+          <t>2026-04-29 17:20:58</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -16646,7 +16646,7 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 01:42:01</t>
+          <t>2026-04-29 16:42:01</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -16726,7 +16726,7 @@
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 01:03:17</t>
+          <t>2026-04-29 16:03:17</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -16806,7 +16806,7 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 00:19:47</t>
+          <t>2026-04-29 15:19:47</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -16886,7 +16886,7 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 23:29:53</t>
+          <t>2026-04-29 14:29:53</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
@@ -16966,7 +16966,7 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:59:49</t>
+          <t>2026-04-29 13:59:49</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -17046,7 +17046,7 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:38:22</t>
+          <t>2026-04-29 13:38:22</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:44</t>
+          <t>2026-04-29 13:17:44</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
@@ -17206,7 +17206,7 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 03:28:56</t>
+          <t>2026-04-28 18:28:56</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -17286,7 +17286,7 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:58:50</t>
+          <t>2026-04-28 17:58:50</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
@@ -17366,7 +17366,7 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:29:43</t>
+          <t>2026-04-28 17:29:43</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -17446,7 +17446,7 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 01:38:43</t>
+          <t>2026-04-28 16:38:43</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -17526,7 +17526,7 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:54</t>
+          <t>2026-04-28 15:58:54</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
@@ -17606,7 +17606,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:31:32</t>
+          <t>2026-04-28 15:31:32</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -17686,7 +17686,7 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:04:20</t>
+          <t>2026-04-28 15:04:20</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
@@ -17766,7 +17766,7 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 23:37:27</t>
+          <t>2026-04-28 14:37:27</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
@@ -17846,7 +17846,7 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 23:09:10</t>
+          <t>2026-04-28 14:09:10</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
@@ -17926,7 +17926,7 @@
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:59:25</t>
+          <t>2026-04-27 14:59:25</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
@@ -18006,7 +18006,7 @@
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:49:35</t>
+          <t>2026-04-27 14:49:35</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
@@ -18086,7 +18086,7 @@
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 22:55:34</t>
+          <t>2026-04-27 13:55:34</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
@@ -18166,7 +18166,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 22:04:13</t>
+          <t>2026-04-27 13:04:13</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
@@ -18246,7 +18246,7 @@
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 02:49:02</t>
+          <t>2026-04-24 17:49:02</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
@@ -18326,7 +18326,7 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 02:03:56</t>
+          <t>2026-04-24 17:03:56</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
@@ -18406,7 +18406,7 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 01:37:00</t>
+          <t>2026-04-24 16:37:00</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
@@ -18486,7 +18486,7 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:33:59</t>
+          <t>2026-04-23 15:33:59</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
@@ -18566,7 +18566,7 @@
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:22:46</t>
+          <t>2026-04-23 15:22:46</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -18646,7 +18646,7 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:12:54</t>
+          <t>2026-04-23 15:12:54</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
@@ -18726,7 +18726,7 @@
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 22:36:03</t>
+          <t>2026-04-23 13:36:03</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:58:57</t>
+          <t>2026-04-13 15:58:57</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
@@ -18886,7 +18886,7 @@
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:09:08</t>
+          <t>2026-04-13 15:09:08</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -18966,7 +18966,7 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 01:48:02</t>
+          <t>2026-04-12 16:48:02</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
@@ -19046,7 +19046,7 @@
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 01:17:58</t>
+          <t>2026-04-12 16:17:58</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -19126,7 +19126,7 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 00:41:20</t>
+          <t>2026-04-12 15:41:20</t>
         </is>
       </c>
       <c r="B199" s="7" t="inlineStr">
@@ -19206,7 +19206,7 @@
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 23:18:06</t>
+          <t>2026-04-09 14:18:06</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -19286,7 +19286,7 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 22:52:44</t>
+          <t>2026-04-09 13:52:44</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
@@ -19366,7 +19366,7 @@
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 22:27:45</t>
+          <t>2026-04-09 13:27:45</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -19446,7 +19446,7 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>2026-04-08 01:10:31</t>
+          <t>2026-04-07 16:10:31</t>
         </is>
       </c>
       <c r="B203" s="7" t="inlineStr">
@@ -19526,7 +19526,7 @@
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>2026-04-08 00:29:19</t>
+          <t>2026-04-07 15:29:19</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
@@ -19606,7 +19606,7 @@
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>2026-04-04 04:36:31</t>
+          <t>2026-04-03 19:36:31</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
@@ -19686,7 +19686,7 @@
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>2026-04-04 04:16:32</t>
+          <t>2026-04-03 19:16:32</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
@@ -19766,7 +19766,7 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 04:24:43</t>
+          <t>2026-03-27 19:24:43</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
@@ -19846,7 +19846,7 @@
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 03:38:31</t>
+          <t>2026-03-27 18:38:31</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -19926,7 +19926,7 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 03:17:50</t>
+          <t>2026-03-27 18:17:50</t>
         </is>
       </c>
       <c r="B209" s="7" t="inlineStr">
@@ -20006,7 +20006,7 @@
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 02:43:19</t>
+          <t>2026-03-27 17:43:19</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -20086,7 +20086,7 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 02:15:18</t>
+          <t>2026-03-27 17:15:18</t>
         </is>
       </c>
       <c r="B211" s="7" t="inlineStr">
@@ -20166,7 +20166,7 @@
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 23:18:12</t>
+          <t>2026-03-25 14:18:12</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
@@ -20246,7 +20246,7 @@
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 00:01:49</t>
+          <t>2026-03-24 15:01:49</t>
         </is>
       </c>
       <c r="B213" s="7" t="inlineStr">
@@ -20326,7 +20326,7 @@
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 23:25:16</t>
+          <t>2026-03-24 14:25:16</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
@@ -20406,7 +20406,7 @@
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 23:02:52</t>
+          <t>2026-03-24 14:02:52</t>
         </is>
       </c>
       <c r="B215" s="7" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 22:26:26</t>
+          <t>2026-03-24 13:26:26</t>
         </is>
       </c>
       <c r="B216" s="7" t="inlineStr">
@@ -20566,7 +20566,7 @@
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 00:56:18</t>
+          <t>2026-03-23 15:56:18</t>
         </is>
       </c>
       <c r="B217" s="7" t="inlineStr">
@@ -20646,7 +20646,7 @@
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 00:29:29</t>
+          <t>2026-03-23 15:29:29</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
@@ -20726,7 +20726,7 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 23:51:11</t>
+          <t>2026-03-22 14:51:11</t>
         </is>
       </c>
       <c r="B219" s="7" t="inlineStr">
@@ -20806,7 +20806,7 @@
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 01:04:36</t>
+          <t>2026-03-21 16:04:36</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
@@ -20886,7 +20886,7 @@
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>2026-03-21 02:55:49</t>
+          <t>2026-03-20 17:55:49</t>
         </is>
       </c>
       <c r="B221" s="7" t="inlineStr">
@@ -20966,7 +20966,7 @@
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>2026-03-18 00:07:07</t>
+          <t>2026-03-17 15:07:07</t>
         </is>
       </c>
       <c r="B222" s="7" t="inlineStr">
@@ -21046,7 +21046,7 @@
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 23:24:05</t>
+          <t>2026-03-17 14:24:05</t>
         </is>
       </c>
       <c r="B223" s="7" t="inlineStr">
@@ -21126,7 +21126,7 @@
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 02:00:50</t>
+          <t>2026-03-16 17:00:50</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -21206,7 +21206,7 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 01:33:08</t>
+          <t>2026-03-16 16:33:08</t>
         </is>
       </c>
       <c r="B225" s="7" t="inlineStr">
@@ -21286,7 +21286,7 @@
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 23:28:09</t>
+          <t>2026-03-16 14:28:09</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
@@ -21366,7 +21366,7 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 01:32:22</t>
+          <t>2026-03-15 16:32:22</t>
         </is>
       </c>
       <c r="B227" s="7" t="inlineStr">
@@ -21446,7 +21446,7 @@
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14 01:43:49</t>
+          <t>2026-03-13 16:43:49</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
@@ -21526,7 +21526,7 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14 01:19:35</t>
+          <t>2026-03-13 16:19:35</t>
         </is>
       </c>
       <c r="B229" s="7" t="inlineStr">
@@ -21606,7 +21606,7 @@
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 23:45:27</t>
+          <t>2026-03-12 14:45:27</t>
         </is>
       </c>
       <c r="B230" s="7" t="inlineStr">
@@ -21686,7 +21686,7 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 23:02:09</t>
+          <t>2026-03-12 14:02:09</t>
         </is>
       </c>
       <c r="B231" s="7" t="inlineStr">
@@ -21766,7 +21766,7 @@
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 22:42:59</t>
+          <t>2026-03-12 13:42:59</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
@@ -21846,7 +21846,7 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 01:39:10</t>
+          <t>2026-03-11 16:39:10</t>
         </is>
       </c>
       <c r="B233" s="7" t="inlineStr">
@@ -21926,7 +21926,7 @@
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:43:21</t>
+          <t>2026-03-11 15:43:21</t>
         </is>
       </c>
       <c r="B234" s="7" t="inlineStr">
@@ -22006,7 +22006,7 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:04:25</t>
+          <t>2026-03-11 15:04:25</t>
         </is>
       </c>
       <c r="B235" s="7" t="inlineStr">
@@ -22086,7 +22086,7 @@
     <row r="236">
       <c r="A236" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 22:54:02</t>
+          <t>2026-03-11 13:54:02</t>
         </is>
       </c>
       <c r="B236" s="7" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>2026-03-08 02:01:53</t>
+          <t>2026-03-07 17:01:53</t>
         </is>
       </c>
       <c r="B237" s="7" t="inlineStr">
@@ -22246,7 +22246,7 @@
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>2026-03-02 02:18:59</t>
+          <t>2026-03-01 17:18:59</t>
         </is>
       </c>
       <c r="B238" s="7" t="inlineStr">
@@ -22326,7 +22326,7 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>2026-02-24 01:40:38</t>
+          <t>2026-02-23 16:40:38</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
@@ -22406,7 +22406,7 @@
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>2026-02-24 00:10:31</t>
+          <t>2026-02-23 15:10:31</t>
         </is>
       </c>
       <c r="B240" s="7" t="inlineStr">
@@ -22486,7 +22486,7 @@
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 23:33:47</t>
+          <t>2026-02-23 14:33:47</t>
         </is>
       </c>
       <c r="B241" s="7" t="inlineStr">
@@ -22566,7 +22566,7 @@
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 22:40:54</t>
+          <t>2026-02-23 13:40:54</t>
         </is>
       </c>
       <c r="B242" s="7" t="inlineStr">
@@ -22646,7 +22646,7 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 21:58:56</t>
+          <t>2026-02-23 12:58:56</t>
         </is>
       </c>
       <c r="B243" s="7" t="inlineStr">
@@ -22726,7 +22726,7 @@
     <row r="244">
       <c r="A244" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 19:21:48</t>
+          <t>2026-02-23 10:21:48</t>
         </is>
       </c>
       <c r="B244" s="7" t="inlineStr">
@@ -22806,7 +22806,7 @@
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 17:17:13</t>
+          <t>2026-02-23 08:17:13</t>
         </is>
       </c>
       <c r="B245" s="7" t="inlineStr">
@@ -22886,7 +22886,7 @@
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 04:22:01</t>
+          <t>2026-02-22 19:22:01</t>
         </is>
       </c>
       <c r="B246" s="7" t="inlineStr">
@@ -22966,7 +22966,7 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 03:23:51</t>
+          <t>2026-02-22 18:23:51</t>
         </is>
       </c>
       <c r="B247" s="7" t="inlineStr">
@@ -23046,7 +23046,7 @@
     <row r="248">
       <c r="A248" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 02:58:18</t>
+          <t>2026-02-22 17:58:18</t>
         </is>
       </c>
       <c r="B248" s="7" t="inlineStr">
@@ -23126,7 +23126,7 @@
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 02:29:21</t>
+          <t>2026-02-22 17:29:21</t>
         </is>
       </c>
       <c r="B249" s="7" t="inlineStr">
@@ -23206,7 +23206,7 @@
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 01:59:09</t>
+          <t>2026-02-22 16:59:09</t>
         </is>
       </c>
       <c r="B250" s="7" t="inlineStr">
@@ -23286,7 +23286,7 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 01:32:08</t>
+          <t>2026-02-22 16:32:08</t>
         </is>
       </c>
       <c r="B251" s="7" t="inlineStr">
@@ -23366,7 +23366,7 @@
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 03:34:36</t>
+          <t>2026-02-20 18:34:36</t>
         </is>
       </c>
       <c r="B252" s="7" t="inlineStr">
@@ -23446,7 +23446,7 @@
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 02:57:13</t>
+          <t>2026-02-20 17:57:13</t>
         </is>
       </c>
       <c r="B253" s="7" t="inlineStr">
@@ -23526,7 +23526,7 @@
     <row r="254">
       <c r="A254" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 02:19:01</t>
+          <t>2026-02-20 17:19:01</t>
         </is>
       </c>
       <c r="B254" s="7" t="inlineStr">
@@ -23606,7 +23606,7 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 01:41:10</t>
+          <t>2026-02-20 16:41:10</t>
         </is>
       </c>
       <c r="B255" s="7" t="inlineStr">
@@ -23686,7 +23686,7 @@
     <row r="256">
       <c r="A256" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:57:47</t>
+          <t>2026-02-20 15:57:47</t>
         </is>
       </c>
       <c r="B256" s="7" t="inlineStr">
@@ -23766,7 +23766,7 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:39:52</t>
+          <t>2026-02-20 15:39:52</t>
         </is>
       </c>
       <c r="B257" s="7" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="258">
       <c r="A258" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 01:21:13</t>
+          <t>2026-02-19 16:21:13</t>
         </is>
       </c>
       <c r="B258" s="7" t="inlineStr">
@@ -23926,7 +23926,7 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 00:33:10</t>
+          <t>2026-02-19 15:33:10</t>
         </is>
       </c>
       <c r="B259" s="7" t="inlineStr">
@@ -24006,7 +24006,7 @@
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>2026-02-18 00:37:38</t>
+          <t>2026-02-17 15:37:38</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
@@ -24086,7 +24086,7 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>2026-02-17 23:58:39</t>
+          <t>2026-02-17 14:58:39</t>
         </is>
       </c>
       <c r="B261" s="7" t="inlineStr">
@@ -24166,7 +24166,7 @@
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 02:24:16</t>
+          <t>2026-02-15 17:24:16</t>
         </is>
       </c>
       <c r="B262" s="7" t="inlineStr">
@@ -24246,7 +24246,7 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 01:47:19</t>
+          <t>2026-02-15 16:47:19</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
@@ -24326,7 +24326,7 @@
     <row r="264">
       <c r="A264" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 00:56:43</t>
+          <t>2026-02-15 15:56:43</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -24406,7 +24406,7 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 00:26:20</t>
+          <t>2026-02-15 15:26:20</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
@@ -24486,7 +24486,7 @@
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 23:48:44</t>
+          <t>2026-02-15 14:48:44</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -24566,7 +24566,7 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 04:17:17</t>
+          <t>2026-02-14 19:17:17</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -24646,7 +24646,7 @@
     <row r="268">
       <c r="A268" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 03:53:01</t>
+          <t>2026-02-14 18:53:01</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
@@ -24726,7 +24726,7 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:59:46</t>
+          <t>2026-02-14 17:59:46</t>
         </is>
       </c>
       <c r="B269" s="7" t="inlineStr">
@@ -24806,7 +24806,7 @@
     <row r="270">
       <c r="A270" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:26:42</t>
+          <t>2026-02-14 17:26:42</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
@@ -24886,7 +24886,7 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:00:09</t>
+          <t>2026-02-14 17:00:09</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
@@ -24966,7 +24966,7 @@
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 01:39:16</t>
+          <t>2026-02-14 16:39:16</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -25046,7 +25046,7 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 00:56:51</t>
+          <t>2026-02-14 15:56:51</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
@@ -25126,7 +25126,7 @@
     <row r="274">
       <c r="A274" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 23:52:26</t>
+          <t>2026-02-14 14:52:26</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -25206,7 +25206,7 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 23:14:55</t>
+          <t>2026-02-14 14:14:55</t>
         </is>
       </c>
       <c r="B275" s="7" t="inlineStr">
@@ -25286,7 +25286,7 @@
     <row r="276">
       <c r="A276" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 04:19:58</t>
+          <t>2026-02-13 19:19:58</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
@@ -25366,7 +25366,7 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 03:37:53</t>
+          <t>2026-02-13 18:37:53</t>
         </is>
       </c>
       <c r="B277" s="7" t="inlineStr">
@@ -25446,7 +25446,7 @@
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 03:03:31</t>
+          <t>2026-02-13 18:03:31</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 02:08:36</t>
+          <t>2026-02-13 17:08:36</t>
         </is>
       </c>
       <c r="B279" s="7" t="inlineStr">
@@ -25606,7 +25606,7 @@
     <row r="280">
       <c r="A280" s="7" t="inlineStr">
         <is>
-          <t>2026-02-12 00:20:03</t>
+          <t>2026-02-11 15:20:03</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -25686,7 +25686,7 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 03:05:03</t>
+          <t>2026-02-10 18:05:03</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
@@ -25766,7 +25766,7 @@
     <row r="282">
       <c r="A282" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 02:14:02</t>
+          <t>2026-02-10 17:14:02</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -25846,7 +25846,7 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 01:33:21</t>
+          <t>2026-02-10 16:33:21</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
@@ -25926,7 +25926,7 @@
     <row r="284">
       <c r="A284" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 01:01:41</t>
+          <t>2026-02-10 16:01:41</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -26006,7 +26006,7 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 01:49:32</t>
+          <t>2026-02-09 16:49:32</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
@@ -26086,7 +26086,7 @@
     <row r="286">
       <c r="A286" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 01:42:29</t>
+          <t>2026-02-09 16:42:29</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -26166,7 +26166,7 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 23:44:10</t>
+          <t>2026-02-09 14:44:10</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -26246,7 +26246,7 @@
     <row r="288">
       <c r="A288" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 23:00:28</t>
+          <t>2026-02-09 14:00:28</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -26326,7 +26326,7 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 00:27:49</t>
+          <t>2026-02-08 15:27:49</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -26406,7 +26406,7 @@
     <row r="290">
       <c r="A290" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 00:16:42</t>
+          <t>2026-02-08 15:16:42</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -26486,7 +26486,7 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08 04:04:43</t>
+          <t>2026-02-07 19:04:43</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
@@ -26566,7 +26566,7 @@
     <row r="292">
       <c r="A292" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 03:13:11</t>
+          <t>2026-02-06 18:13:11</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -26646,7 +26646,7 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 02:19:42</t>
+          <t>2026-02-06 17:19:42</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
@@ -26726,7 +26726,7 @@
     <row r="294">
       <c r="A294" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 01:37:36</t>
+          <t>2026-02-06 16:37:36</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -26806,7 +26806,7 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>2026-02-03 23:04:49</t>
+          <t>2026-02-03 14:04:49</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
@@ -26886,7 +26886,7 @@
     <row r="296">
       <c r="A296" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 23:21:38</t>
+          <t>2026-02-02 14:21:38</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -26966,7 +26966,7 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 03:08:17</t>
+          <t>2026-02-01 18:08:17</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -27046,7 +27046,7 @@
     <row r="298">
       <c r="A298" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 02:41:55</t>
+          <t>2026-02-01 17:41:55</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -27126,7 +27126,7 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 02:09:57</t>
+          <t>2026-02-01 17:09:57</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="300">
       <c r="A300" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 01:41:49</t>
+          <t>2026-02-01 16:41:49</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
@@ -27286,7 +27286,7 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 02:22:13</t>
+          <t>2026-01-31 17:22:13</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -27366,7 +27366,7 @@
     <row r="302">
       <c r="A302" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 01:20:54</t>
+          <t>2026-01-31 16:20:54</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
@@ -27446,7 +27446,7 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 01:09:32</t>
+          <t>2026-01-31 16:09:32</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
@@ -27526,7 +27526,7 @@
     <row r="304">
       <c r="A304" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 00:29:37</t>
+          <t>2026-01-31 15:29:37</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -27606,7 +27606,7 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 00:03:50</t>
+          <t>2026-01-31 15:03:50</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -27686,7 +27686,7 @@
     <row r="306">
       <c r="A306" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 23:15:28</t>
+          <t>2026-01-31 14:15:28</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -27766,7 +27766,7 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>2026-01-29 00:36:39</t>
+          <t>2026-01-28 15:36:39</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
@@ -27846,7 +27846,7 @@
     <row r="308">
       <c r="A308" s="7" t="inlineStr">
         <is>
-          <t>2026-01-29 00:02:45</t>
+          <t>2026-01-28 15:02:45</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
@@ -27926,7 +27926,7 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 23:26:47</t>
+          <t>2026-01-28 14:26:47</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
@@ -28006,7 +28006,7 @@
     <row r="310">
       <c r="A310" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 23:04:33</t>
+          <t>2026-01-28 14:04:33</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -28086,7 +28086,7 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 00:33:31</t>
+          <t>2026-01-27 15:33:31</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -28166,7 +28166,7 @@
     <row r="312">
       <c r="A312" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 23:59:21</t>
+          <t>2026-01-27 14:59:21</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -28246,7 +28246,7 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 23:08:33</t>
+          <t>2026-01-27 14:08:33</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -28326,7 +28326,7 @@
     <row r="314">
       <c r="A314" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 23:28:17</t>
+          <t>2026-01-25 14:28:17</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -28406,7 +28406,7 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 22:56:22</t>
+          <t>2026-01-25 13:56:22</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -28486,7 +28486,7 @@
     <row r="316">
       <c r="A316" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 22:28:25</t>
+          <t>2026-01-25 13:28:25</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -28566,7 +28566,7 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 21:42:03</t>
+          <t>2026-01-25 12:42:03</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -28646,7 +28646,7 @@
     <row r="318">
       <c r="A318" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 19:38:23</t>
+          <t>2026-01-25 10:38:23</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -28726,7 +28726,7 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 18:56:35</t>
+          <t>2026-01-25 09:56:35</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -28806,7 +28806,7 @@
     <row r="320">
       <c r="A320" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 18:29:19</t>
+          <t>2026-01-25 09:29:19</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 17:14:05</t>
+          <t>2026-01-25 08:14:05</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -28966,7 +28966,7 @@
     <row r="322">
       <c r="A322" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 02:47:24</t>
+          <t>2026-01-23 17:47:24</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -29046,7 +29046,7 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 02:12:26</t>
+          <t>2026-01-23 17:12:26</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -29126,7 +29126,7 @@
     <row r="324">
       <c r="A324" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 01:33:34</t>
+          <t>2026-01-23 16:33:34</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -29206,7 +29206,7 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 01:00:39</t>
+          <t>2026-01-23 16:00:39</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -29286,7 +29286,7 @@
     <row r="326">
       <c r="A326" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 00:19:07</t>
+          <t>2026-01-23 15:19:07</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -29366,7 +29366,7 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 23:52:33</t>
+          <t>2026-01-23 14:52:33</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -29446,7 +29446,7 @@
     <row r="328">
       <c r="A328" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 23:19:19</t>
+          <t>2026-01-23 14:19:19</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -29526,7 +29526,7 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36:59</t>
+          <t>2026-01-23 13:36:59</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -29606,7 +29606,7 @@
     <row r="330">
       <c r="A330" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 03:01:58</t>
+          <t>2026-01-22 18:01:58</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -29686,7 +29686,7 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 02:25:41</t>
+          <t>2026-01-22 17:25:41</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -29766,7 +29766,7 @@
     <row r="332">
       <c r="A332" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 00:32:45</t>
+          <t>2026-01-22 15:32:45</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -29846,7 +29846,7 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 23:54:46</t>
+          <t>2026-01-22 14:54:46</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -29926,7 +29926,7 @@
     <row r="334">
       <c r="A334" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 23:17:42</t>
+          <t>2026-01-22 14:17:42</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -30006,7 +30006,7 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 01:10:08</t>
+          <t>2026-01-21 16:10:08</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -30086,7 +30086,7 @@
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
         <is>
-          <t>2026-01-21 00:27:51</t>
+          <t>2026-01-20 15:27:51</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -30166,7 +30166,7 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 23:25:34</t>
+          <t>2026-01-20 14:25:34</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -30246,7 +30246,7 @@
     <row r="338">
       <c r="A338" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 22:56:13</t>
+          <t>2026-01-20 13:56:13</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -30326,7 +30326,7 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>2026-01-19 01:59:11</t>
+          <t>2026-01-18 16:59:11</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -30406,7 +30406,7 @@
     <row r="340">
       <c r="A340" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 03:05:32</t>
+          <t>2026-01-17 18:05:32</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -30486,7 +30486,7 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 02:19:17</t>
+          <t>2026-01-17 17:19:17</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="342">
       <c r="A342" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 01:58:17</t>
+          <t>2026-01-17 16:58:17</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -30646,7 +30646,7 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 01:18:29</t>
+          <t>2026-01-17 16:18:29</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -30726,7 +30726,7 @@
     <row r="344">
       <c r="A344" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 00:38:58</t>
+          <t>2026-01-17 15:38:58</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -30806,7 +30806,7 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 18:46:30</t>
+          <t>2026-01-17 09:46:30</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -30886,7 +30886,7 @@
     <row r="346">
       <c r="A346" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 02:21:36</t>
+          <t>2026-01-16 17:21:36</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -30966,7 +30966,7 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 01:51:05</t>
+          <t>2026-01-16 16:51:05</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -31046,7 +31046,7 @@
     <row r="348">
       <c r="A348" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 01:18:22</t>
+          <t>2026-01-16 16:18:22</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -31126,7 +31126,7 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 01:41:15</t>
+          <t>2026-01-15 16:41:15</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -31206,7 +31206,7 @@
     <row r="350">
       <c r="A350" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 01:05:38</t>
+          <t>2026-01-15 16:05:38</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -31286,7 +31286,7 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14 00:57:21</t>
+          <t>2026-01-13 15:57:21</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -31366,7 +31366,7 @@
     <row r="352">
       <c r="A352" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14 00:19:49</t>
+          <t>2026-01-13 15:19:49</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -31446,7 +31446,7 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 23:53:29</t>
+          <t>2026-01-13 14:53:29</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -31526,7 +31526,7 @@
     <row r="354">
       <c r="A354" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 02:23:29</t>
+          <t>2026-01-12 17:23:29</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -31606,7 +31606,7 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 01:42:12</t>
+          <t>2026-01-12 16:42:12</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -31686,7 +31686,7 @@
     <row r="356">
       <c r="A356" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 01:17:01</t>
+          <t>2026-01-12 16:17:01</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -31766,7 +31766,7 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 00:43:11</t>
+          <t>2026-01-12 15:43:11</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -31846,7 +31846,7 @@
     <row r="358">
       <c r="A358" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 17:24:44</t>
+          <t>2026-01-12 08:24:44</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -31926,7 +31926,7 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 03:12:16</t>
+          <t>2026-01-11 18:12:16</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -32006,7 +32006,7 @@
     <row r="360">
       <c r="A360" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 02:54:03</t>
+          <t>2026-01-10 17:54:03</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -32086,7 +32086,7 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 02:14:56</t>
+          <t>2026-01-10 17:14:56</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -32166,7 +32166,7 @@
     <row r="362">
       <c r="A362" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 01:17:21</t>
+          <t>2026-01-10 16:17:21</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 00:22:11</t>
+          <t>2026-01-10 15:22:11</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -32326,7 +32326,7 @@
     <row r="364">
       <c r="A364" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 23:38:24</t>
+          <t>2026-01-10 14:38:24</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -32406,7 +32406,7 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 02:54:19</t>
+          <t>2026-01-09 17:54:19</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -32486,7 +32486,7 @@
     <row r="366">
       <c r="A366" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 02:00:16</t>
+          <t>2026-01-09 17:00:16</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -32566,7 +32566,7 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>2026-01-09 23:36:27</t>
+          <t>2026-01-09 14:36:27</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -32646,7 +32646,7 @@
     <row r="368">
       <c r="A368" s="7" t="inlineStr">
         <is>
-          <t>2026-01-05 23:21:47</t>
+          <t>2026-01-05 14:21:47</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -32841,7 +32841,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 23:51:39</t>
+          <t>2026-07-28 14:51:39</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
@@ -32903,7 +32903,7 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 23:05:20</t>
+          <t>2026-07-28 14:05:20</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
@@ -32965,7 +32965,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>2026-07-27 01:21:51</t>
+          <t>2026-07-26 16:21:51</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -33027,7 +33027,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>2026-07-27 00:43:02</t>
+          <t>2026-07-26 15:43:02</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -33089,7 +33089,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 23:12:09</t>
+          <t>2026-07-25 14:12:09</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -33151,7 +33151,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 22:30:57</t>
+          <t>2026-07-25 13:30:57</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -33213,7 +33213,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 00:11:55</t>
+          <t>2026-07-24 15:11:55</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -33275,7 +33275,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>2026-07-24 23:25:38</t>
+          <t>2026-07-24 14:25:38</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -33337,7 +33337,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>2026-07-22 00:17:56</t>
+          <t>2026-07-21 15:17:56</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -33399,7 +33399,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>2026-07-22 00:04:35</t>
+          <t>2026-07-21 15:04:35</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -33461,7 +33461,7 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 23:25:56</t>
+          <t>2026-07-21 14:25:56</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -33523,7 +33523,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 22:44:36</t>
+          <t>2026-07-21 13:44:36</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -33585,7 +33585,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 22:18:59</t>
+          <t>2026-07-21 13:18:59</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
@@ -33647,7 +33647,7 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>2026-07-20 03:20:20</t>
+          <t>2026-07-19 18:20:20</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -33709,7 +33709,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>2026-07-20 02:39:51</t>
+          <t>2026-07-19 17:39:51</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -33771,7 +33771,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:59:14</t>
+          <t>2026-07-18 09:59:14</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -33833,7 +33833,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:21:14</t>
+          <t>2026-07-18 09:21:14</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -33895,7 +33895,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 23:06:28</t>
+          <t>2026-07-16 14:06:28</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -33957,7 +33957,7 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 22:32:42</t>
+          <t>2026-07-16 13:32:42</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -34019,7 +34019,7 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 00:40:48</t>
+          <t>2026-07-15 15:40:48</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -34081,7 +34081,7 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 23:41:56</t>
+          <t>2026-07-15 14:41:56</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -34143,7 +34143,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 22:58:44</t>
+          <t>2026-07-15 13:58:44</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -34205,7 +34205,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 22:34:16</t>
+          <t>2026-07-15 13:34:16</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -34267,7 +34267,7 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 23:36:35</t>
+          <t>2026-07-14 14:36:35</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -34329,7 +34329,7 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 22:49:50</t>
+          <t>2026-07-14 13:49:50</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
@@ -34391,7 +34391,7 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 01:02:29</t>
+          <t>2026-07-13 16:02:29</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -34453,7 +34453,7 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 00:22:46</t>
+          <t>2026-07-13 15:22:46</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
@@ -34515,7 +34515,7 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 23:51:38</t>
+          <t>2026-07-13 14:51:38</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -34577,7 +34577,7 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 02:05:19</t>
+          <t>2026-07-12 17:05:19</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
@@ -34639,7 +34639,7 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 01:29:17</t>
+          <t>2026-07-12 16:29:17</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
@@ -34701,7 +34701,7 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 03:11:38</t>
+          <t>2026-07-11 18:11:38</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
@@ -34763,7 +34763,7 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 02:46:15</t>
+          <t>2026-07-11 17:46:15</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -34825,7 +34825,7 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 03:42:29</t>
+          <t>2026-07-10 18:42:29</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
@@ -34887,7 +34887,7 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 03:06:21</t>
+          <t>2026-07-10 18:06:21</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
@@ -34949,7 +34949,7 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:55:25</t>
+          <t>2026-07-08 17:55:25</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
@@ -35011,7 +35011,7 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:17:09</t>
+          <t>2026-07-08 17:17:09</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -35073,7 +35073,7 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 02:03:51</t>
+          <t>2026-07-05 17:03:51</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
@@ -35135,7 +35135,7 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 01:07:17</t>
+          <t>2026-07-05 16:07:17</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -35197,7 +35197,7 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 00:23:00</t>
+          <t>2026-07-05 15:23:00</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
@@ -35259,7 +35259,7 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>2026-07-05 03:21:23</t>
+          <t>2026-07-04 18:21:23</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
@@ -35321,7 +35321,7 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>2026-07-04 03:01:40</t>
+          <t>2026-07-03 18:01:40</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
@@ -35383,7 +35383,7 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>2026-07-03 01:48:19</t>
+          <t>2026-07-02 16:48:19</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
@@ -35445,7 +35445,7 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>2026-07-01 00:21:19</t>
+          <t>2026-06-30 15:21:19</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
@@ -35507,7 +35507,7 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 23:38:16</t>
+          <t>2026-06-30 14:38:16</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
@@ -35569,7 +35569,7 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 01:16:28</t>
+          <t>2026-06-29 16:16:28</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
@@ -35631,7 +35631,7 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 00:34:32</t>
+          <t>2026-06-29 15:34:32</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
@@ -35693,7 +35693,7 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>2026-06-26 00:50:56</t>
+          <t>2026-06-25 15:50:56</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
@@ -35755,7 +35755,7 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>2026-06-26 00:06:40</t>
+          <t>2026-06-25 15:06:40</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
@@ -35817,7 +35817,7 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07:56</t>
+          <t>2026-06-24 17:07:56</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
@@ -35879,7 +35879,7 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 01:33:19</t>
+          <t>2026-06-24 16:33:19</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
@@ -35941,7 +35941,7 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:47:59</t>
+          <t>2026-06-24 15:47:59</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
@@ -36003,7 +36003,7 @@
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:08:31</t>
+          <t>2026-06-24 15:08:31</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
@@ -36065,7 +36065,7 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 23:33:15</t>
+          <t>2026-06-24 14:33:15</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
@@ -36127,7 +36127,7 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 22:39:11</t>
+          <t>2026-06-24 13:39:11</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
@@ -36189,7 +36189,7 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 01:16:06</t>
+          <t>2026-06-22 16:16:06</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
@@ -36251,7 +36251,7 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 00:38:08</t>
+          <t>2026-06-22 15:38:08</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
@@ -36313,7 +36313,7 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 00:29:33</t>
+          <t>2026-06-22 15:29:33</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
@@ -36375,7 +36375,7 @@
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 01:54:04</t>
+          <t>2026-06-18 16:54:04</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
@@ -36437,7 +36437,7 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 01:14:50</t>
+          <t>2026-06-18 16:14:50</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
@@ -36499,7 +36499,7 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 00:35:17</t>
+          <t>2026-06-18 15:35:17</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
@@ -36561,7 +36561,7 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 23:55:50</t>
+          <t>2026-06-18 14:55:50</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
@@ -36623,7 +36623,7 @@
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 00:44:42</t>
+          <t>2026-06-17 15:44:42</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
@@ -36685,7 +36685,7 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 23:57:38</t>
+          <t>2026-06-17 14:57:38</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
@@ -36747,7 +36747,7 @@
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 01:58:55</t>
+          <t>2026-06-16 16:58:55</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
@@ -36809,7 +36809,7 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 01:30:07</t>
+          <t>2026-06-16 16:30:07</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
@@ -36871,7 +36871,7 @@
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 03:10:28</t>
+          <t>2026-06-14 18:10:28</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
@@ -36933,7 +36933,7 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 02:27:52</t>
+          <t>2026-06-14 17:27:52</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
@@ -36995,7 +36995,7 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 01:57:23</t>
+          <t>2026-06-14 16:57:23</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
@@ -37057,7 +37057,7 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 01:27:22</t>
+          <t>2026-06-14 16:27:22</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
@@ -37119,7 +37119,7 @@
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 00:24:35</t>
+          <t>2026-06-14 15:24:35</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
@@ -37181,7 +37181,7 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 23:46:55</t>
+          <t>2026-06-14 14:46:55</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
@@ -37243,7 +37243,7 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 01:41:53</t>
+          <t>2026-06-13 16:41:53</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
@@ -37305,7 +37305,7 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 00:52:58</t>
+          <t>2026-06-13 15:52:58</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
@@ -37367,7 +37367,7 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 00:14:23</t>
+          <t>2026-06-13 15:14:23</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
@@ -37429,7 +37429,7 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 23:45:21</t>
+          <t>2026-06-13 14:45:21</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
@@ -37491,7 +37491,7 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 23:05:32</t>
+          <t>2026-06-13 14:05:32</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
@@ -37553,7 +37553,7 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 01:08:14</t>
+          <t>2026-06-10 16:08:14</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
@@ -37615,7 +37615,7 @@
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:34:35</t>
+          <t>2026-06-10 15:34:35</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
@@ -37677,7 +37677,7 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:09:17</t>
+          <t>2026-06-10 15:09:17</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
@@ -37739,7 +37739,7 @@
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 23:27:53</t>
+          <t>2026-06-10 14:27:53</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
@@ -37801,7 +37801,7 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 00:49:00</t>
+          <t>2026-06-09 15:49:00</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
@@ -37863,7 +37863,7 @@
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>2026-06-06 02:58:51</t>
+          <t>2026-06-05 17:58:51</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
@@ -37925,7 +37925,7 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>2026-06-06 02:15:04</t>
+          <t>2026-06-05 17:15:04</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
@@ -37987,7 +37987,7 @@
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 23:49:14</t>
+          <t>2026-06-04 14:49:14</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
@@ -38049,7 +38049,7 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 21:40:04</t>
+          <t>2026-06-04 12:40:04</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
@@ -38111,7 +38111,7 @@
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 21:17:24</t>
+          <t>2026-06-04 12:17:24</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
@@ -38173,7 +38173,7 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 01:06:27</t>
+          <t>2026-06-03 16:06:27</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
@@ -38235,7 +38235,7 @@
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 00:31:09</t>
+          <t>2026-06-03 15:31:09</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
@@ -38297,7 +38297,7 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 23:53:57</t>
+          <t>2026-06-03 14:53:57</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
@@ -38359,7 +38359,7 @@
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 22:44:02</t>
+          <t>2026-06-03 13:44:02</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
@@ -38421,7 +38421,7 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>2026-06-02 22:49:11</t>
+          <t>2026-06-02 13:49:11</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
@@ -38483,7 +38483,7 @@
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:56:06</t>
+          <t>2026-06-01 14:56:06</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
@@ -38545,7 +38545,7 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:20:26</t>
+          <t>2026-06-01 14:20:26</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
@@ -38607,7 +38607,7 @@
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:01:06</t>
+          <t>2026-06-01 14:01:06</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
@@ -38669,7 +38669,7 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>2026-05-31 03:01:04</t>
+          <t>2026-05-30 18:01:04</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
@@ -38731,7 +38731,7 @@
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>2026-05-31 02:13:41</t>
+          <t>2026-05-30 17:13:41</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
@@ -38793,7 +38793,7 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 23:00:40</t>
+          <t>2026-05-25 14:00:40</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
@@ -38855,7 +38855,7 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 01:55:47</t>
+          <t>2026-05-24 16:55:47</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
@@ -38917,7 +38917,7 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 01:24:22</t>
+          <t>2026-05-24 16:24:22</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
@@ -38979,7 +38979,7 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 23:49:25</t>
+          <t>2026-05-24 14:49:25</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
@@ -39041,7 +39041,7 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 03:13:39</t>
+          <t>2026-05-23 18:13:39</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
@@ -39103,7 +39103,7 @@
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 02:41:52</t>
+          <t>2026-05-23 17:41:52</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
@@ -39165,7 +39165,7 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 23:19:04</t>
+          <t>2026-05-23 14:19:04</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
@@ -39227,7 +39227,7 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 22:43:20</t>
+          <t>2026-05-23 13:43:20</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
@@ -39289,7 +39289,7 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 15:54:19</t>
+          <t>2026-05-23 06:54:19</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
@@ -39351,7 +39351,7 @@
     <row r="107">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 02:25:24</t>
+          <t>2026-05-22 17:25:24</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
@@ -39413,7 +39413,7 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 01:29:23</t>
+          <t>2026-05-21 16:29:23</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
@@ -39475,7 +39475,7 @@
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 00:48:49</t>
+          <t>2026-05-21 15:48:49</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
@@ -39537,7 +39537,7 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:45</t>
+          <t>2026-05-21 15:00:45</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
@@ -39599,7 +39599,7 @@
     <row r="111">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 23:22:44</t>
+          <t>2026-05-21 14:22:44</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
@@ -39661,7 +39661,7 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 00:05:15</t>
+          <t>2026-05-20 15:05:15</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
@@ -39723,7 +39723,7 @@
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 23:43:50</t>
+          <t>2026-05-20 14:43:50</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
@@ -39785,7 +39785,7 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 22:57:45</t>
+          <t>2026-05-20 13:57:45</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
@@ -39847,7 +39847,7 @@
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 01:25:45</t>
+          <t>2026-05-19 16:25:45</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
@@ -39909,7 +39909,7 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 00:46:42</t>
+          <t>2026-05-19 15:46:42</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
@@ -39971,7 +39971,7 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>2026-05-18 22:56:39</t>
+          <t>2026-05-18 13:56:39</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
@@ -40033,7 +40033,7 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 01:35:56</t>
+          <t>2026-05-14 16:35:56</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
@@ -40095,7 +40095,7 @@
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 01:17:05</t>
+          <t>2026-05-14 16:17:05</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
@@ -40157,7 +40157,7 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 00:05:48</t>
+          <t>2026-05-14 15:05:48</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
@@ -40219,7 +40219,7 @@
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>2026-05-14 01:25:38</t>
+          <t>2026-05-13 16:25:38</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
@@ -40281,7 +40281,7 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>2026-05-12 00:19:57</t>
+          <t>2026-05-11 15:19:57</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
@@ -40343,7 +40343,7 @@
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 23:54:15</t>
+          <t>2026-05-11 14:54:15</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
@@ -40405,7 +40405,7 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 23:14:30</t>
+          <t>2026-05-11 14:14:30</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
@@ -40467,7 +40467,7 @@
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 22:37:05</t>
+          <t>2026-05-11 13:37:05</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
@@ -40529,7 +40529,7 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 21:53:13</t>
+          <t>2026-05-11 12:53:13</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
@@ -40591,7 +40591,7 @@
     <row r="127">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 00:04:01</t>
+          <t>2026-05-10 15:04:01</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
@@ -40653,7 +40653,7 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:54:24</t>
+          <t>2026-05-09 16:54:24</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
@@ -40715,7 +40715,7 @@
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:22:50</t>
+          <t>2026-05-09 16:22:50</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
@@ -40777,7 +40777,7 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 00:26:16</t>
+          <t>2026-05-09 15:26:16</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
@@ -40839,7 +40839,7 @@
     <row r="131">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 23:38:30</t>
+          <t>2026-05-09 14:38:30</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
@@ -40901,7 +40901,7 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 22:50:20</t>
+          <t>2026-05-09 13:50:20</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
@@ -40963,7 +40963,7 @@
     <row r="133">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 22:13:25</t>
+          <t>2026-05-09 13:13:25</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
@@ -41025,7 +41025,7 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 20:00:11</t>
+          <t>2026-05-09 11:00:11</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
@@ -41087,7 +41087,7 @@
     <row r="135">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 19:10:28</t>
+          <t>2026-05-09 10:10:28</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
@@ -41149,7 +41149,7 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 02:17:27</t>
+          <t>2026-05-08 17:17:27</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
@@ -41211,7 +41211,7 @@
     <row r="137">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 01:38:25</t>
+          <t>2026-05-08 16:38:25</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
@@ -41273,7 +41273,7 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 00:58:58</t>
+          <t>2026-05-08 15:58:58</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
@@ -41335,7 +41335,7 @@
     <row r="139">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 00:37:55</t>
+          <t>2026-05-08 15:37:55</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
@@ -41397,7 +41397,7 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 01:48:31</t>
+          <t>2026-05-07 16:48:31</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
@@ -41459,7 +41459,7 @@
     <row r="141">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 01:02:52</t>
+          <t>2026-05-07 16:02:52</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
@@ -41521,7 +41521,7 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 00:23:29</t>
+          <t>2026-05-07 15:23:29</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
@@ -41583,7 +41583,7 @@
     <row r="143">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 01:30:56</t>
+          <t>2026-05-06 16:30:56</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
@@ -41645,7 +41645,7 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 00:42:16</t>
+          <t>2026-05-06 15:42:16</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
@@ -41707,7 +41707,7 @@
     <row r="145">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 23:44:04</t>
+          <t>2026-05-06 14:44:04</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
@@ -41769,7 +41769,7 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:13:52</t>
+          <t>2026-05-06 09:13:52</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
@@ -41831,7 +41831,7 @@
     <row r="147">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:05:08</t>
+          <t>2026-05-06 09:05:08</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
@@ -41893,7 +41893,7 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 17:22:30</t>
+          <t>2026-05-06 08:22:30</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
@@ -41955,7 +41955,7 @@
     <row r="149">
       <c r="A149" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 16:28:42</t>
+          <t>2026-05-06 07:28:42</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
@@ -42017,7 +42017,7 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 03:16:57</t>
+          <t>2026-05-05 18:16:57</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
@@ -42079,7 +42079,7 @@
     <row r="151">
       <c r="A151" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:32:40</t>
+          <t>2026-05-05 17:32:40</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
@@ -42141,7 +42141,7 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:23:28</t>
+          <t>2026-05-05 17:23:28</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
@@ -42203,7 +42203,7 @@
     <row r="153">
       <c r="A153" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 01:48:28</t>
+          <t>2026-05-05 16:48:28</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
@@ -42265,7 +42265,7 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 00:52:33</t>
+          <t>2026-05-05 15:52:33</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
@@ -42327,7 +42327,7 @@
     <row r="155">
       <c r="A155" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 17:43:06</t>
+          <t>2026-05-05 08:43:06</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
@@ -42389,7 +42389,7 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>2026-05-03 00:36:42</t>
+          <t>2026-05-02 15:36:42</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
@@ -42451,7 +42451,7 @@
     <row r="157">
       <c r="A157" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 23:51:09</t>
+          <t>2026-05-02 14:51:09</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
@@ -42513,7 +42513,7 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 22:15:10</t>
+          <t>2026-05-02 13:15:10</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
@@ -42575,7 +42575,7 @@
     <row r="159">
       <c r="A159" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 21:29:49</t>
+          <t>2026-05-02 12:29:49</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
@@ -42637,7 +42637,7 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 01:39:42</t>
+          <t>2026-04-30 16:39:42</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
@@ -42699,7 +42699,7 @@
     <row r="161">
       <c r="A161" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 01:01:34</t>
+          <t>2026-04-30 16:01:34</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
@@ -42761,7 +42761,7 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 00:24:48</t>
+          <t>2026-04-30 15:24:48</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
@@ -42823,7 +42823,7 @@
     <row r="163">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 23:37:10</t>
+          <t>2026-04-30 14:37:10</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
@@ -42885,7 +42885,7 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 22:58:06</t>
+          <t>2026-04-30 13:58:06</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
@@ -42947,7 +42947,7 @@
     <row r="165">
       <c r="A165" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 03:29:33</t>
+          <t>2026-04-29 18:29:33</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
@@ -43009,7 +43009,7 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 02:54:07</t>
+          <t>2026-04-29 17:54:07</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
@@ -43071,7 +43071,7 @@
     <row r="167">
       <c r="A167" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 02:20:58</t>
+          <t>2026-04-29 17:20:58</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
@@ -43133,7 +43133,7 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 01:42:01</t>
+          <t>2026-04-29 16:42:01</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
@@ -43195,7 +43195,7 @@
     <row r="169">
       <c r="A169" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 01:03:17</t>
+          <t>2026-04-29 16:03:17</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
@@ -43257,7 +43257,7 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 00:19:47</t>
+          <t>2026-04-29 15:19:47</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
@@ -43319,7 +43319,7 @@
     <row r="171">
       <c r="A171" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 23:29:53</t>
+          <t>2026-04-29 14:29:53</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
@@ -43381,7 +43381,7 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:59:49</t>
+          <t>2026-04-29 13:59:49</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
@@ -43443,7 +43443,7 @@
     <row r="173">
       <c r="A173" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:38:22</t>
+          <t>2026-04-29 13:38:22</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
@@ -43505,7 +43505,7 @@
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:44</t>
+          <t>2026-04-29 13:17:44</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
@@ -43567,7 +43567,7 @@
     <row r="175">
       <c r="A175" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 03:28:56</t>
+          <t>2026-04-28 18:28:56</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
@@ -43629,7 +43629,7 @@
     <row r="176">
       <c r="A176" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:58:50</t>
+          <t>2026-04-28 17:58:50</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
@@ -43691,7 +43691,7 @@
     <row r="177">
       <c r="A177" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:29:43</t>
+          <t>2026-04-28 17:29:43</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
@@ -43753,7 +43753,7 @@
     <row r="178">
       <c r="A178" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 01:38:43</t>
+          <t>2026-04-28 16:38:43</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
@@ -43815,7 +43815,7 @@
     <row r="179">
       <c r="A179" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:54</t>
+          <t>2026-04-28 15:58:54</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
@@ -43877,7 +43877,7 @@
     <row r="180">
       <c r="A180" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:31:32</t>
+          <t>2026-04-28 15:31:32</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
@@ -43939,7 +43939,7 @@
     <row r="181">
       <c r="A181" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:04:20</t>
+          <t>2026-04-28 15:04:20</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
@@ -44001,7 +44001,7 @@
     <row r="182">
       <c r="A182" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 23:37:27</t>
+          <t>2026-04-28 14:37:27</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
@@ -44063,7 +44063,7 @@
     <row r="183">
       <c r="A183" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 23:09:10</t>
+          <t>2026-04-28 14:09:10</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
@@ -44125,7 +44125,7 @@
     <row r="184">
       <c r="A184" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:59:25</t>
+          <t>2026-04-27 14:59:25</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
@@ -44187,7 +44187,7 @@
     <row r="185">
       <c r="A185" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:49:35</t>
+          <t>2026-04-27 14:49:35</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
@@ -44249,7 +44249,7 @@
     <row r="186">
       <c r="A186" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 22:55:34</t>
+          <t>2026-04-27 13:55:34</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
@@ -44311,7 +44311,7 @@
     <row r="187">
       <c r="A187" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 22:04:13</t>
+          <t>2026-04-27 13:04:13</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
@@ -44373,7 +44373,7 @@
     <row r="188">
       <c r="A188" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 02:49:02</t>
+          <t>2026-04-24 17:49:02</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
@@ -44435,7 +44435,7 @@
     <row r="189">
       <c r="A189" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 02:03:56</t>
+          <t>2026-04-24 17:03:56</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
@@ -44497,7 +44497,7 @@
     <row r="190">
       <c r="A190" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 01:37:00</t>
+          <t>2026-04-24 16:37:00</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
@@ -44559,7 +44559,7 @@
     <row r="191">
       <c r="A191" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:33:59</t>
+          <t>2026-04-23 15:33:59</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
@@ -44621,7 +44621,7 @@
     <row r="192">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:22:46</t>
+          <t>2026-04-23 15:22:46</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
@@ -44683,7 +44683,7 @@
     <row r="193">
       <c r="A193" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:12:54</t>
+          <t>2026-04-23 15:12:54</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
@@ -44745,7 +44745,7 @@
     <row r="194">
       <c r="A194" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 22:36:03</t>
+          <t>2026-04-23 13:36:03</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
@@ -44807,7 +44807,7 @@
     <row r="195">
       <c r="A195" s="13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:58:57</t>
+          <t>2026-04-13 15:58:57</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
@@ -44869,7 +44869,7 @@
     <row r="196">
       <c r="A196" s="13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:09:08</t>
+          <t>2026-04-13 15:09:08</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
@@ -44931,7 +44931,7 @@
     <row r="197">
       <c r="A197" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 01:48:02</t>
+          <t>2026-04-12 16:48:02</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
@@ -44993,7 +44993,7 @@
     <row r="198">
       <c r="A198" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 01:17:58</t>
+          <t>2026-04-12 16:17:58</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
@@ -45055,7 +45055,7 @@
     <row r="199">
       <c r="A199" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 00:41:20</t>
+          <t>2026-04-12 15:41:20</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
@@ -45117,7 +45117,7 @@
     <row r="200">
       <c r="A200" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 23:18:06</t>
+          <t>2026-04-09 14:18:06</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
@@ -45179,7 +45179,7 @@
     <row r="201">
       <c r="A201" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 22:52:44</t>
+          <t>2026-04-09 13:52:44</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
@@ -45241,7 +45241,7 @@
     <row r="202">
       <c r="A202" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 22:27:45</t>
+          <t>2026-04-09 13:27:45</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
@@ -45303,7 +45303,7 @@
     <row r="203">
       <c r="A203" s="13" t="inlineStr">
         <is>
-          <t>2026-04-08 01:10:31</t>
+          <t>2026-04-07 16:10:31</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
@@ -45365,7 +45365,7 @@
     <row r="204">
       <c r="A204" s="13" t="inlineStr">
         <is>
-          <t>2026-04-08 00:29:19</t>
+          <t>2026-04-07 15:29:19</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
@@ -45427,7 +45427,7 @@
     <row r="205">
       <c r="A205" s="13" t="inlineStr">
         <is>
-          <t>2026-04-04 04:36:31</t>
+          <t>2026-04-03 19:36:31</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
@@ -45489,7 +45489,7 @@
     <row r="206">
       <c r="A206" s="13" t="inlineStr">
         <is>
-          <t>2026-04-04 04:16:32</t>
+          <t>2026-04-03 19:16:32</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
@@ -45551,7 +45551,7 @@
     <row r="207">
       <c r="A207" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 04:24:43</t>
+          <t>2026-03-27 19:24:43</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
@@ -45613,7 +45613,7 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:38:31</t>
+          <t>2026-03-27 18:38:31</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
@@ -45675,7 +45675,7 @@
     <row r="209">
       <c r="A209" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:17:50</t>
+          <t>2026-03-27 18:17:50</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
@@ -45737,7 +45737,7 @@
     <row r="210">
       <c r="A210" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 02:43:19</t>
+          <t>2026-03-27 17:43:19</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
@@ -45799,7 +45799,7 @@
     <row r="211">
       <c r="A211" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 02:15:18</t>
+          <t>2026-03-27 17:15:18</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
@@ -45861,7 +45861,7 @@
     <row r="212">
       <c r="A212" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 23:18:12</t>
+          <t>2026-03-25 14:18:12</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
@@ -45923,7 +45923,7 @@
     <row r="213">
       <c r="A213" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 00:01:49</t>
+          <t>2026-03-24 15:01:49</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
@@ -45985,7 +45985,7 @@
     <row r="214">
       <c r="A214" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 23:25:16</t>
+          <t>2026-03-24 14:25:16</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
@@ -46047,7 +46047,7 @@
     <row r="215">
       <c r="A215" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 23:02:52</t>
+          <t>2026-03-24 14:02:52</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
@@ -46109,7 +46109,7 @@
     <row r="216">
       <c r="A216" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 22:26:26</t>
+          <t>2026-03-24 13:26:26</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
@@ -46171,7 +46171,7 @@
     <row r="217">
       <c r="A217" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 00:56:18</t>
+          <t>2026-03-23 15:56:18</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
@@ -46233,7 +46233,7 @@
     <row r="218">
       <c r="A218" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 00:29:29</t>
+          <t>2026-03-23 15:29:29</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
@@ -46295,7 +46295,7 @@
     <row r="219">
       <c r="A219" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 23:51:11</t>
+          <t>2026-03-22 14:51:11</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
@@ -46357,7 +46357,7 @@
     <row r="220">
       <c r="A220" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 01:04:36</t>
+          <t>2026-03-21 16:04:36</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
@@ -46419,7 +46419,7 @@
     <row r="221">
       <c r="A221" s="13" t="inlineStr">
         <is>
-          <t>2026-03-21 02:55:49</t>
+          <t>2026-03-20 17:55:49</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
@@ -46481,7 +46481,7 @@
     <row r="222">
       <c r="A222" s="13" t="inlineStr">
         <is>
-          <t>2026-03-18 00:07:07</t>
+          <t>2026-03-17 15:07:07</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
@@ -46543,7 +46543,7 @@
     <row r="223">
       <c r="A223" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 23:24:05</t>
+          <t>2026-03-17 14:24:05</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
@@ -46605,7 +46605,7 @@
     <row r="224">
       <c r="A224" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 02:00:50</t>
+          <t>2026-03-16 17:00:50</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
@@ -46667,7 +46667,7 @@
     <row r="225">
       <c r="A225" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 01:33:08</t>
+          <t>2026-03-16 16:33:08</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
@@ -46729,7 +46729,7 @@
     <row r="226">
       <c r="A226" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 23:28:09</t>
+          <t>2026-03-16 14:28:09</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
@@ -46791,7 +46791,7 @@
     <row r="227">
       <c r="A227" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 01:32:22</t>
+          <t>2026-03-15 16:32:22</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
@@ -46853,7 +46853,7 @@
     <row r="228">
       <c r="A228" s="13" t="inlineStr">
         <is>
-          <t>2026-03-14 01:43:49</t>
+          <t>2026-03-13 16:43:49</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
@@ -46915,7 +46915,7 @@
     <row r="229">
       <c r="A229" s="13" t="inlineStr">
         <is>
-          <t>2026-03-14 01:19:35</t>
+          <t>2026-03-13 16:19:35</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
@@ -46977,7 +46977,7 @@
     <row r="230">
       <c r="A230" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 23:45:27</t>
+          <t>2026-03-12 14:45:27</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
@@ -47039,7 +47039,7 @@
     <row r="231">
       <c r="A231" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 23:02:09</t>
+          <t>2026-03-12 14:02:09</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
@@ -47101,7 +47101,7 @@
     <row r="232">
       <c r="A232" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 22:42:59</t>
+          <t>2026-03-12 13:42:59</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
@@ -47163,7 +47163,7 @@
     <row r="233">
       <c r="A233" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 01:39:10</t>
+          <t>2026-03-11 16:39:10</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
@@ -47225,7 +47225,7 @@
     <row r="234">
       <c r="A234" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:43:21</t>
+          <t>2026-03-11 15:43:21</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
@@ -47287,7 +47287,7 @@
     <row r="235">
       <c r="A235" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:04:25</t>
+          <t>2026-03-11 15:04:25</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
@@ -47349,7 +47349,7 @@
     <row r="236">
       <c r="A236" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 22:54:02</t>
+          <t>2026-03-11 13:54:02</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
@@ -47411,7 +47411,7 @@
     <row r="237">
       <c r="A237" s="13" t="inlineStr">
         <is>
-          <t>2026-03-08 02:01:53</t>
+          <t>2026-03-07 17:01:53</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
@@ -47473,7 +47473,7 @@
     <row r="238">
       <c r="A238" s="13" t="inlineStr">
         <is>
-          <t>2026-03-02 02:18:59</t>
+          <t>2026-03-01 17:18:59</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
@@ -47535,7 +47535,7 @@
     <row r="239">
       <c r="A239" s="13" t="inlineStr">
         <is>
-          <t>2026-02-24 01:40:38</t>
+          <t>2026-02-23 16:40:38</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
@@ -47597,7 +47597,7 @@
     <row r="240">
       <c r="A240" s="13" t="inlineStr">
         <is>
-          <t>2026-02-24 00:10:31</t>
+          <t>2026-02-23 15:10:31</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
@@ -47659,7 +47659,7 @@
     <row r="241">
       <c r="A241" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 23:33:47</t>
+          <t>2026-02-23 14:33:47</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
@@ -47721,7 +47721,7 @@
     <row r="242">
       <c r="A242" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 22:40:54</t>
+          <t>2026-02-23 13:40:54</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
@@ -47783,7 +47783,7 @@
     <row r="243">
       <c r="A243" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 21:58:56</t>
+          <t>2026-02-23 12:58:56</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
@@ -47845,7 +47845,7 @@
     <row r="244">
       <c r="A244" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 19:21:48</t>
+          <t>2026-02-23 10:21:48</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
@@ -47907,7 +47907,7 @@
     <row r="245">
       <c r="A245" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 17:17:13</t>
+          <t>2026-02-23 08:17:13</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
@@ -47969,7 +47969,7 @@
     <row r="246">
       <c r="A246" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 04:22:01</t>
+          <t>2026-02-22 19:22:01</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
@@ -48031,7 +48031,7 @@
     <row r="247">
       <c r="A247" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 03:23:51</t>
+          <t>2026-02-22 18:23:51</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
@@ -48093,7 +48093,7 @@
     <row r="248">
       <c r="A248" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 02:58:18</t>
+          <t>2026-02-22 17:58:18</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
@@ -48155,7 +48155,7 @@
     <row r="249">
       <c r="A249" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 02:29:21</t>
+          <t>2026-02-22 17:29:21</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
@@ -48217,7 +48217,7 @@
     <row r="250">
       <c r="A250" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 01:59:09</t>
+          <t>2026-02-22 16:59:09</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
@@ -48279,7 +48279,7 @@
     <row r="251">
       <c r="A251" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 01:32:08</t>
+          <t>2026-02-22 16:32:08</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
@@ -48341,7 +48341,7 @@
     <row r="252">
       <c r="A252" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 03:34:36</t>
+          <t>2026-02-20 18:34:36</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
@@ -48403,7 +48403,7 @@
     <row r="253">
       <c r="A253" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 02:57:13</t>
+          <t>2026-02-20 17:57:13</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
@@ -48465,7 +48465,7 @@
     <row r="254">
       <c r="A254" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 02:19:01</t>
+          <t>2026-02-20 17:19:01</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
@@ -48527,7 +48527,7 @@
     <row r="255">
       <c r="A255" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 01:41:10</t>
+          <t>2026-02-20 16:41:10</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
@@ -48589,7 +48589,7 @@
     <row r="256">
       <c r="A256" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 00:57:47</t>
+          <t>2026-02-20 15:57:47</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
@@ -48651,7 +48651,7 @@
     <row r="257">
       <c r="A257" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 00:39:52</t>
+          <t>2026-02-20 15:39:52</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
@@ -48713,7 +48713,7 @@
     <row r="258">
       <c r="A258" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 01:21:13</t>
+          <t>2026-02-19 16:21:13</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
@@ -48775,7 +48775,7 @@
     <row r="259">
       <c r="A259" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 00:33:10</t>
+          <t>2026-02-19 15:33:10</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
@@ -48837,7 +48837,7 @@
     <row r="260">
       <c r="A260" s="13" t="inlineStr">
         <is>
-          <t>2026-02-18 00:37:38</t>
+          <t>2026-02-17 15:37:38</t>
         </is>
       </c>
       <c r="B260" s="13" t="inlineStr">
@@ -48899,7 +48899,7 @@
     <row r="261">
       <c r="A261" s="13" t="inlineStr">
         <is>
-          <t>2026-02-17 23:58:39</t>
+          <t>2026-02-17 14:58:39</t>
         </is>
       </c>
       <c r="B261" s="13" t="inlineStr">
@@ -48961,7 +48961,7 @@
     <row r="262">
       <c r="A262" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 02:24:16</t>
+          <t>2026-02-15 17:24:16</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
@@ -49023,7 +49023,7 @@
     <row r="263">
       <c r="A263" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 01:47:19</t>
+          <t>2026-02-15 16:47:19</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
@@ -49085,7 +49085,7 @@
     <row r="264">
       <c r="A264" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 00:56:43</t>
+          <t>2026-02-15 15:56:43</t>
         </is>
       </c>
       <c r="B264" s="13" t="inlineStr">
@@ -49147,7 +49147,7 @@
     <row r="265">
       <c r="A265" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 00:26:20</t>
+          <t>2026-02-15 15:26:20</t>
         </is>
       </c>
       <c r="B265" s="13" t="inlineStr">
@@ -49209,7 +49209,7 @@
     <row r="266">
       <c r="A266" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 23:48:44</t>
+          <t>2026-02-15 14:48:44</t>
         </is>
       </c>
       <c r="B266" s="13" t="inlineStr">
@@ -49271,7 +49271,7 @@
     <row r="267">
       <c r="A267" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 04:17:17</t>
+          <t>2026-02-14 19:17:17</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
@@ -49333,7 +49333,7 @@
     <row r="268">
       <c r="A268" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 03:53:01</t>
+          <t>2026-02-14 18:53:01</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
@@ -49395,7 +49395,7 @@
     <row r="269">
       <c r="A269" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:59:46</t>
+          <t>2026-02-14 17:59:46</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
@@ -49457,7 +49457,7 @@
     <row r="270">
       <c r="A270" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:26:42</t>
+          <t>2026-02-14 17:26:42</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
@@ -49519,7 +49519,7 @@
     <row r="271">
       <c r="A271" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:00:09</t>
+          <t>2026-02-14 17:00:09</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
@@ -49581,7 +49581,7 @@
     <row r="272">
       <c r="A272" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 01:39:16</t>
+          <t>2026-02-14 16:39:16</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
@@ -49643,7 +49643,7 @@
     <row r="273">
       <c r="A273" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 00:56:51</t>
+          <t>2026-02-14 15:56:51</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
@@ -49705,7 +49705,7 @@
     <row r="274">
       <c r="A274" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 23:52:26</t>
+          <t>2026-02-14 14:52:26</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
@@ -49767,7 +49767,7 @@
     <row r="275">
       <c r="A275" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 23:14:55</t>
+          <t>2026-02-14 14:14:55</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
@@ -49829,7 +49829,7 @@
     <row r="276">
       <c r="A276" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 04:19:58</t>
+          <t>2026-02-13 19:19:58</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
@@ -49891,7 +49891,7 @@
     <row r="277">
       <c r="A277" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 03:37:53</t>
+          <t>2026-02-13 18:37:53</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
@@ -49953,7 +49953,7 @@
     <row r="278">
       <c r="A278" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 03:03:31</t>
+          <t>2026-02-13 18:03:31</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
@@ -50015,7 +50015,7 @@
     <row r="279">
       <c r="A279" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 02:08:36</t>
+          <t>2026-02-13 17:08:36</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
@@ -50077,7 +50077,7 @@
     <row r="280">
       <c r="A280" s="13" t="inlineStr">
         <is>
-          <t>2026-02-12 00:20:03</t>
+          <t>2026-02-11 15:20:03</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
@@ -50139,7 +50139,7 @@
     <row r="281">
       <c r="A281" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 03:05:03</t>
+          <t>2026-02-10 18:05:03</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
@@ -50201,7 +50201,7 @@
     <row r="282">
       <c r="A282" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 02:14:02</t>
+          <t>2026-02-10 17:14:02</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
@@ -50263,7 +50263,7 @@
     <row r="283">
       <c r="A283" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 01:33:21</t>
+          <t>2026-02-10 16:33:21</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
@@ -50325,7 +50325,7 @@
     <row r="284">
       <c r="A284" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 01:01:41</t>
+          <t>2026-02-10 16:01:41</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
@@ -50387,7 +50387,7 @@
     <row r="285">
       <c r="A285" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 01:49:32</t>
+          <t>2026-02-09 16:49:32</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
@@ -50449,7 +50449,7 @@
     <row r="286">
       <c r="A286" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 01:42:29</t>
+          <t>2026-02-09 16:42:29</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
@@ -50511,7 +50511,7 @@
     <row r="287">
       <c r="A287" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 23:44:10</t>
+          <t>2026-02-09 14:44:10</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
@@ -50573,7 +50573,7 @@
     <row r="288">
       <c r="A288" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 23:00:28</t>
+          <t>2026-02-09 14:00:28</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
@@ -50635,7 +50635,7 @@
     <row r="289">
       <c r="A289" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 00:27:49</t>
+          <t>2026-02-08 15:27:49</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
@@ -50697,7 +50697,7 @@
     <row r="290">
       <c r="A290" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 00:16:42</t>
+          <t>2026-02-08 15:16:42</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
@@ -50759,7 +50759,7 @@
     <row r="291">
       <c r="A291" s="13" t="inlineStr">
         <is>
-          <t>2026-02-08 04:04:43</t>
+          <t>2026-02-07 19:04:43</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
@@ -50821,7 +50821,7 @@
     <row r="292">
       <c r="A292" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 03:13:11</t>
+          <t>2026-02-06 18:13:11</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
@@ -50883,7 +50883,7 @@
     <row r="293">
       <c r="A293" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 02:19:42</t>
+          <t>2026-02-06 17:19:42</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
@@ -50945,7 +50945,7 @@
     <row r="294">
       <c r="A294" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 01:37:36</t>
+          <t>2026-02-06 16:37:36</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
@@ -51007,7 +51007,7 @@
     <row r="295">
       <c r="A295" s="13" t="inlineStr">
         <is>
-          <t>2026-02-03 23:04:49</t>
+          <t>2026-02-03 14:04:49</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
@@ -51069,7 +51069,7 @@
     <row r="296">
       <c r="A296" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 23:21:38</t>
+          <t>2026-02-02 14:21:38</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
@@ -51131,7 +51131,7 @@
     <row r="297">
       <c r="A297" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 03:08:17</t>
+          <t>2026-02-01 18:08:17</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
@@ -51193,7 +51193,7 @@
     <row r="298">
       <c r="A298" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 02:41:55</t>
+          <t>2026-02-01 17:41:55</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
@@ -51255,7 +51255,7 @@
     <row r="299">
       <c r="A299" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 02:09:57</t>
+          <t>2026-02-01 17:09:57</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
@@ -51317,7 +51317,7 @@
     <row r="300">
       <c r="A300" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 01:41:49</t>
+          <t>2026-02-01 16:41:49</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
@@ -51379,7 +51379,7 @@
     <row r="301">
       <c r="A301" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 02:22:13</t>
+          <t>2026-01-31 17:22:13</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
@@ -51441,7 +51441,7 @@
     <row r="302">
       <c r="A302" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 01:20:54</t>
+          <t>2026-01-31 16:20:54</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
@@ -51503,7 +51503,7 @@
     <row r="303">
       <c r="A303" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 01:09:32</t>
+          <t>2026-01-31 16:09:32</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
@@ -51565,7 +51565,7 @@
     <row r="304">
       <c r="A304" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 00:29:37</t>
+          <t>2026-01-31 15:29:37</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
@@ -51627,7 +51627,7 @@
     <row r="305">
       <c r="A305" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 00:03:50</t>
+          <t>2026-01-31 15:03:50</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
@@ -51689,7 +51689,7 @@
     <row r="306">
       <c r="A306" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 23:15:28</t>
+          <t>2026-01-31 14:15:28</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
@@ -51751,7 +51751,7 @@
     <row r="307">
       <c r="A307" s="13" t="inlineStr">
         <is>
-          <t>2026-01-29 00:36:39</t>
+          <t>2026-01-28 15:36:39</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
@@ -51813,7 +51813,7 @@
     <row r="308">
       <c r="A308" s="13" t="inlineStr">
         <is>
-          <t>2026-01-29 00:02:45</t>
+          <t>2026-01-28 15:02:45</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
@@ -51875,7 +51875,7 @@
     <row r="309">
       <c r="A309" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 23:26:47</t>
+          <t>2026-01-28 14:26:47</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
@@ -51937,7 +51937,7 @@
     <row r="310">
       <c r="A310" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 23:04:33</t>
+          <t>2026-01-28 14:04:33</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
@@ -51999,7 +51999,7 @@
     <row r="311">
       <c r="A311" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 00:33:31</t>
+          <t>2026-01-27 15:33:31</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
@@ -52061,7 +52061,7 @@
     <row r="312">
       <c r="A312" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 23:59:21</t>
+          <t>2026-01-27 14:59:21</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
@@ -52123,7 +52123,7 @@
     <row r="313">
       <c r="A313" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 23:08:33</t>
+          <t>2026-01-27 14:08:33</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
@@ -52185,7 +52185,7 @@
     <row r="314">
       <c r="A314" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 23:28:17</t>
+          <t>2026-01-25 14:28:17</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
@@ -52247,7 +52247,7 @@
     <row r="315">
       <c r="A315" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 22:56:22</t>
+          <t>2026-01-25 13:56:22</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
@@ -52309,7 +52309,7 @@
     <row r="316">
       <c r="A316" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 22:28:25</t>
+          <t>2026-01-25 13:28:25</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
@@ -52371,7 +52371,7 @@
     <row r="317">
       <c r="A317" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 21:42:03</t>
+          <t>2026-01-25 12:42:03</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
@@ -52433,7 +52433,7 @@
     <row r="318">
       <c r="A318" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 19:38:23</t>
+          <t>2026-01-25 10:38:23</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
@@ -52495,7 +52495,7 @@
     <row r="319">
       <c r="A319" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 18:56:35</t>
+          <t>2026-01-25 09:56:35</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
@@ -52557,7 +52557,7 @@
     <row r="320">
       <c r="A320" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 18:29:19</t>
+          <t>2026-01-25 09:29:19</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
@@ -52619,7 +52619,7 @@
     <row r="321">
       <c r="A321" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 17:14:05</t>
+          <t>2026-01-25 08:14:05</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
@@ -52681,7 +52681,7 @@
     <row r="322">
       <c r="A322" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 02:47:24</t>
+          <t>2026-01-23 17:47:24</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
@@ -52743,7 +52743,7 @@
     <row r="323">
       <c r="A323" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 02:12:26</t>
+          <t>2026-01-23 17:12:26</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
@@ -52805,7 +52805,7 @@
     <row r="324">
       <c r="A324" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 01:33:34</t>
+          <t>2026-01-23 16:33:34</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
@@ -52867,7 +52867,7 @@
     <row r="325">
       <c r="A325" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 01:00:39</t>
+          <t>2026-01-23 16:00:39</t>
         </is>
       </c>
       <c r="B325" s="13" t="inlineStr">
@@ -52929,7 +52929,7 @@
     <row r="326">
       <c r="A326" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 00:19:07</t>
+          <t>2026-01-23 15:19:07</t>
         </is>
       </c>
       <c r="B326" s="13" t="inlineStr">
@@ -52991,7 +52991,7 @@
     <row r="327">
       <c r="A327" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 23:52:33</t>
+          <t>2026-01-23 14:52:33</t>
         </is>
       </c>
       <c r="B327" s="13" t="inlineStr">
@@ -53053,7 +53053,7 @@
     <row r="328">
       <c r="A328" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 23:19:19</t>
+          <t>2026-01-23 14:19:19</t>
         </is>
       </c>
       <c r="B328" s="13" t="inlineStr">
@@ -53115,7 +53115,7 @@
     <row r="329">
       <c r="A329" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36:59</t>
+          <t>2026-01-23 13:36:59</t>
         </is>
       </c>
       <c r="B329" s="13" t="inlineStr">
@@ -53177,7 +53177,7 @@
     <row r="330">
       <c r="A330" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 03:01:58</t>
+          <t>2026-01-22 18:01:58</t>
         </is>
       </c>
       <c r="B330" s="13" t="inlineStr">
@@ -53239,7 +53239,7 @@
     <row r="331">
       <c r="A331" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 02:25:41</t>
+          <t>2026-01-22 17:25:41</t>
         </is>
       </c>
       <c r="B331" s="13" t="inlineStr">
@@ -53301,7 +53301,7 @@
     <row r="332">
       <c r="A332" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 00:32:45</t>
+          <t>2026-01-22 15:32:45</t>
         </is>
       </c>
       <c r="B332" s="13" t="inlineStr">
@@ -53363,7 +53363,7 @@
     <row r="333">
       <c r="A333" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 23:54:46</t>
+          <t>2026-01-22 14:54:46</t>
         </is>
       </c>
       <c r="B333" s="13" t="inlineStr">
@@ -53425,7 +53425,7 @@
     <row r="334">
       <c r="A334" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 23:17:42</t>
+          <t>2026-01-22 14:17:42</t>
         </is>
       </c>
       <c r="B334" s="13" t="inlineStr">
@@ -53487,7 +53487,7 @@
     <row r="335">
       <c r="A335" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 01:10:08</t>
+          <t>2026-01-21 16:10:08</t>
         </is>
       </c>
       <c r="B335" s="13" t="inlineStr">
@@ -53549,7 +53549,7 @@
     <row r="336">
       <c r="A336" s="13" t="inlineStr">
         <is>
-          <t>2026-01-21 00:27:51</t>
+          <t>2026-01-20 15:27:51</t>
         </is>
       </c>
       <c r="B336" s="13" t="inlineStr">
@@ -53611,7 +53611,7 @@
     <row r="337">
       <c r="A337" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 23:25:34</t>
+          <t>2026-01-20 14:25:34</t>
         </is>
       </c>
       <c r="B337" s="13" t="inlineStr">
@@ -53673,7 +53673,7 @@
     <row r="338">
       <c r="A338" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 22:56:13</t>
+          <t>2026-01-20 13:56:13</t>
         </is>
       </c>
       <c r="B338" s="13" t="inlineStr">
@@ -53735,7 +53735,7 @@
     <row r="339">
       <c r="A339" s="13" t="inlineStr">
         <is>
-          <t>2026-01-19 01:59:11</t>
+          <t>2026-01-18 16:59:11</t>
         </is>
       </c>
       <c r="B339" s="13" t="inlineStr">
@@ -53797,7 +53797,7 @@
     <row r="340">
       <c r="A340" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 03:05:32</t>
+          <t>2026-01-17 18:05:32</t>
         </is>
       </c>
       <c r="B340" s="13" t="inlineStr">
@@ -53859,7 +53859,7 @@
     <row r="341">
       <c r="A341" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 02:19:17</t>
+          <t>2026-01-17 17:19:17</t>
         </is>
       </c>
       <c r="B341" s="13" t="inlineStr">
@@ -53921,7 +53921,7 @@
     <row r="342">
       <c r="A342" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 01:58:17</t>
+          <t>2026-01-17 16:58:17</t>
         </is>
       </c>
       <c r="B342" s="13" t="inlineStr">
@@ -53983,7 +53983,7 @@
     <row r="343">
       <c r="A343" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 01:18:29</t>
+          <t>2026-01-17 16:18:29</t>
         </is>
       </c>
       <c r="B343" s="13" t="inlineStr">
@@ -54045,7 +54045,7 @@
     <row r="344">
       <c r="A344" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 00:38:58</t>
+          <t>2026-01-17 15:38:58</t>
         </is>
       </c>
       <c r="B344" s="13" t="inlineStr">
@@ -54107,7 +54107,7 @@
     <row r="345">
       <c r="A345" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 18:46:30</t>
+          <t>2026-01-17 09:46:30</t>
         </is>
       </c>
       <c r="B345" s="13" t="inlineStr">
@@ -54169,7 +54169,7 @@
     <row r="346">
       <c r="A346" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 02:21:36</t>
+          <t>2026-01-16 17:21:36</t>
         </is>
       </c>
       <c r="B346" s="13" t="inlineStr">
@@ -54231,7 +54231,7 @@
     <row r="347">
       <c r="A347" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 01:51:05</t>
+          <t>2026-01-16 16:51:05</t>
         </is>
       </c>
       <c r="B347" s="13" t="inlineStr">
@@ -54293,7 +54293,7 @@
     <row r="348">
       <c r="A348" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 01:18:22</t>
+          <t>2026-01-16 16:18:22</t>
         </is>
       </c>
       <c r="B348" s="13" t="inlineStr">
@@ -54355,7 +54355,7 @@
     <row r="349">
       <c r="A349" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 01:41:15</t>
+          <t>2026-01-15 16:41:15</t>
         </is>
       </c>
       <c r="B349" s="13" t="inlineStr">
@@ -54417,7 +54417,7 @@
     <row r="350">
       <c r="A350" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 01:05:38</t>
+          <t>2026-01-15 16:05:38</t>
         </is>
       </c>
       <c r="B350" s="13" t="inlineStr">
@@ -54479,7 +54479,7 @@
     <row r="351">
       <c r="A351" s="13" t="inlineStr">
         <is>
-          <t>2026-01-14 00:57:21</t>
+          <t>2026-01-13 15:57:21</t>
         </is>
       </c>
       <c r="B351" s="13" t="inlineStr">
@@ -54541,7 +54541,7 @@
     <row r="352">
       <c r="A352" s="13" t="inlineStr">
         <is>
-          <t>2026-01-14 00:19:49</t>
+          <t>2026-01-13 15:19:49</t>
         </is>
       </c>
       <c r="B352" s="13" t="inlineStr">
@@ -54603,7 +54603,7 @@
     <row r="353">
       <c r="A353" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 23:53:29</t>
+          <t>2026-01-13 14:53:29</t>
         </is>
       </c>
       <c r="B353" s="13" t="inlineStr">
@@ -54665,7 +54665,7 @@
     <row r="354">
       <c r="A354" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 02:23:29</t>
+          <t>2026-01-12 17:23:29</t>
         </is>
       </c>
       <c r="B354" s="13" t="inlineStr">
@@ -54727,7 +54727,7 @@
     <row r="355">
       <c r="A355" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 01:42:12</t>
+          <t>2026-01-12 16:42:12</t>
         </is>
       </c>
       <c r="B355" s="13" t="inlineStr">
@@ -54789,7 +54789,7 @@
     <row r="356">
       <c r="A356" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 01:17:01</t>
+          <t>2026-01-12 16:17:01</t>
         </is>
       </c>
       <c r="B356" s="13" t="inlineStr">
@@ -54851,7 +54851,7 @@
     <row r="357">
       <c r="A357" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 00:43:11</t>
+          <t>2026-01-12 15:43:11</t>
         </is>
       </c>
       <c r="B357" s="13" t="inlineStr">
@@ -54913,7 +54913,7 @@
     <row r="358">
       <c r="A358" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 17:24:44</t>
+          <t>2026-01-12 08:24:44</t>
         </is>
       </c>
       <c r="B358" s="13" t="inlineStr">
@@ -54975,7 +54975,7 @@
     <row r="359">
       <c r="A359" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 03:12:16</t>
+          <t>2026-01-11 18:12:16</t>
         </is>
       </c>
       <c r="B359" s="13" t="inlineStr">
@@ -55037,7 +55037,7 @@
     <row r="360">
       <c r="A360" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 02:54:03</t>
+          <t>2026-01-10 17:54:03</t>
         </is>
       </c>
       <c r="B360" s="13" t="inlineStr">
@@ -55099,7 +55099,7 @@
     <row r="361">
       <c r="A361" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 02:14:56</t>
+          <t>2026-01-10 17:14:56</t>
         </is>
       </c>
       <c r="B361" s="13" t="inlineStr">
@@ -55161,7 +55161,7 @@
     <row r="362">
       <c r="A362" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 01:17:21</t>
+          <t>2026-01-10 16:17:21</t>
         </is>
       </c>
       <c r="B362" s="13" t="inlineStr">
@@ -55223,7 +55223,7 @@
     <row r="363">
       <c r="A363" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 00:22:11</t>
+          <t>2026-01-10 15:22:11</t>
         </is>
       </c>
       <c r="B363" s="13" t="inlineStr">
@@ -55285,7 +55285,7 @@
     <row r="364">
       <c r="A364" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 23:38:24</t>
+          <t>2026-01-10 14:38:24</t>
         </is>
       </c>
       <c r="B364" s="13" t="inlineStr">
@@ -55347,7 +55347,7 @@
     <row r="365">
       <c r="A365" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 02:54:19</t>
+          <t>2026-01-09 17:54:19</t>
         </is>
       </c>
       <c r="B365" s="13" t="inlineStr">
@@ -55409,7 +55409,7 @@
     <row r="366">
       <c r="A366" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 02:00:16</t>
+          <t>2026-01-09 17:00:16</t>
         </is>
       </c>
       <c r="B366" s="13" t="inlineStr">
@@ -55471,7 +55471,7 @@
     <row r="367">
       <c r="A367" s="13" t="inlineStr">
         <is>
-          <t>2026-01-09 23:36:27</t>
+          <t>2026-01-09 14:36:27</t>
         </is>
       </c>
       <c r="B367" s="13" t="inlineStr">
@@ -55533,7 +55533,7 @@
     <row r="368">
       <c r="A368" s="13" t="inlineStr">
         <is>
-          <t>2026-01-05 23:21:47</t>
+          <t>2026-01-05 14:21:47</t>
         </is>
       </c>
       <c r="B368" s="13" t="inlineStr">

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-07-29 17:34:37</t>
+          <t>出力日時：2026-07-29 17:51:53</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'キュー別'!$A$1:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'チャンピオン別'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SUPチャンピオン別'!$A$1:$L$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$368</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$368</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$367</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$367</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,14 +532,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>対象期間：2026-01-05 14:21:47 ～ 2026-07-28 14:51:39</t>
+          <t>対象期間：2026-01-09 23:36:27 ～ 2026-07-28 23:51:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-07-29 17:51:53</t>
+          <t>出力日時：2026-07-30 03:15:04</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.4741144414168937</v>
+        <v>0.4754098360655737</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.670299727520436</v>
+        <v>1.674863387978142</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5.318801089918257</v>
+        <v>5.319672131147541</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>8.861035422343324</v>
+        <v>8.860655737704919</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>60.65395095367847</v>
+        <v>60.724043715847</v>
       </c>
     </row>
     <row r="15">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2.069427792915532</v>
+        <v>2.071912568306011</v>
       </c>
     </row>
     <row r="16">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>56.00817438692098</v>
+        <v>56.03825136612022</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1.806811989100817</v>
+        <v>1.807650273224044</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.5052631578947369</v>
+        <v>0.5070422535211268</v>
       </c>
     </row>
     <row r="24">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>1.43859649122807</v>
+        <v>1.443661971830986</v>
       </c>
     </row>
     <row r="25">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.140350877192983</v>
+        <v>5.140845070422535</v>
       </c>
     </row>
     <row r="26">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>9.768421052631579</v>
+        <v>9.77112676056338</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>36.13333333333333</v>
+        <v>36.13732394366197</v>
       </c>
     </row>
     <row r="29">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1.249649122807018</v>
+        <v>1.249964788732394</v>
       </c>
     </row>
     <row r="30">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>63.44210526315789</v>
+        <v>63.50704225352113</v>
       </c>
     </row>
     <row r="31">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>2.045228070175438</v>
+        <v>2.047147887323943</v>
       </c>
     </row>
   </sheetData>
@@ -820,7 +820,7 @@
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>144</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.5052631578947369</v>
+        <v>0.5070422535211268</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.43859649122807</v>
+        <v>1.443661971830986</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5.140350877192983</v>
+        <v>5.140845070422535</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9.768421052631579</v>
+        <v>9.77112676056338</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.249649122807018</v>
+        <v>1.249964788732394</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>63.44210526315789</v>
+        <v>63.50704225352113</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>2.045228070175438</v>
+        <v>2.047147887323943</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.933833333333332</v>
+        <v>4.933833333333333</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>31.96666666666667</v>
@@ -1133,7 +1133,7 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1239,7 +1239,7 @@
         <v>52.89225589225589</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>1.716734006734006</v>
+        <v>1.716734006734007</v>
       </c>
     </row>
     <row r="3">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>30</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.114285714285714</v>
+        <v>1.130434782608696</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>5.771428571428571</v>
+        <v>5.782608695652174</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>9.9</v>
+        <v>9.913043478260869</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.241142857142857</v>
+        <v>1.24231884057971</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>69.22857142857143</v>
+        <v>69.57971014492753</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.189000000000001</v>
+        <v>2.198985507246377</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.80186046511628</v>
+        <v>1.801860465116279</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>68.76744186046511</v>
@@ -1516,25 +1516,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.775</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.15</v>
+        <v>5.153846153846154</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.225</v>
+        <v>7.17948717948718</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.231</v>
+        <v>1.232820512820513</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.75</v>
+        <v>53.97435897435897</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.86175</v>
+        <v>1.871025641025641</v>
       </c>
     </row>
     <row r="6">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5.148285714285714</v>
+        <v>5.148285714285715</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>34.6</v>
@@ -1758,7 +1758,7 @@
         <v>25.625</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.8562500000000001</v>
+        <v>0.85625</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>21.83333333333333</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.8633333333333334</v>
+        <v>0.8633333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5.05</v>
+        <v>5.050000000000001</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>16.25</v>
@@ -2833,25 +2833,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.775</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.15</v>
+        <v>5.153846153846154</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.225</v>
+        <v>7.17948717948718</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.231</v>
+        <v>1.232820512820513</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.75</v>
+        <v>53.97435897435897</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.86175</v>
+        <v>1.871025641025641</v>
       </c>
     </row>
     <row r="6">
@@ -3224,7 +3224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V368"/>
+  <dimension ref="A1:V367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3366,7 +3366,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 14:51:39</t>
+          <t>2026-07-28 23:51:39</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 14:05:20</t>
+          <t>2026-07-28 23:05:20</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 16:21:51</t>
+          <t>2026-07-27 01:21:51</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 15:43:02</t>
+          <t>2026-07-27 00:43:02</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 14:12:09</t>
+          <t>2026-07-25 23:12:09</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 13:30:57</t>
+          <t>2026-07-25 22:30:57</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24 15:11:55</t>
+          <t>2026-07-25 00:11:55</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24 14:25:38</t>
+          <t>2026-07-24 23:25:38</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 15:17:56</t>
+          <t>2026-07-22 00:17:56</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 15:04:35</t>
+          <t>2026-07-22 00:04:35</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -4166,7 +4166,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 14:25:56</t>
+          <t>2026-07-21 23:25:56</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 13:44:36</t>
+          <t>2026-07-21 22:44:36</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -4326,7 +4326,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 13:18:59</t>
+          <t>2026-07-21 22:18:59</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-19 18:20:20</t>
+          <t>2026-07-20 03:20:20</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -4486,7 +4486,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-19 17:39:51</t>
+          <t>2026-07-20 02:39:51</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -4566,7 +4566,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 09:59:14</t>
+          <t>2026-07-18 18:59:14</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -4646,7 +4646,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 09:21:14</t>
+          <t>2026-07-18 18:21:14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 14:06:28</t>
+          <t>2026-07-16 23:06:28</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 13:32:42</t>
+          <t>2026-07-16 22:32:42</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -4886,7 +4886,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 15:40:48</t>
+          <t>2026-07-16 00:40:48</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -4966,7 +4966,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 14:41:56</t>
+          <t>2026-07-15 23:41:56</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 13:58:44</t>
+          <t>2026-07-15 22:58:44</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -5126,7 +5126,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 13:34:16</t>
+          <t>2026-07-15 22:34:16</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 14:36:35</t>
+          <t>2026-07-14 23:36:35</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -5286,7 +5286,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 13:49:50</t>
+          <t>2026-07-14 22:49:50</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -5366,7 +5366,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 16:02:29</t>
+          <t>2026-07-14 01:02:29</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 15:22:46</t>
+          <t>2026-07-14 00:22:46</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -5526,7 +5526,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 14:51:38</t>
+          <t>2026-07-13 23:51:38</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -5606,7 +5606,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 17:05:19</t>
+          <t>2026-07-13 02:05:19</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 16:29:17</t>
+          <t>2026-07-13 01:29:17</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -5766,7 +5766,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 18:11:38</t>
+          <t>2026-07-12 03:11:38</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -5846,7 +5846,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 17:46:15</t>
+          <t>2026-07-12 02:46:15</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -5926,7 +5926,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10 18:42:29</t>
+          <t>2026-07-11 03:42:29</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -6006,7 +6006,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10 18:06:21</t>
+          <t>2026-07-11 03:06:21</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08 17:55:25</t>
+          <t>2026-07-09 02:55:25</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08 17:17:09</t>
+          <t>2026-07-09 02:17:09</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05 17:03:51</t>
+          <t>2026-07-06 02:03:51</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -6326,7 +6326,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05 16:07:17</t>
+          <t>2026-07-06 01:07:17</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -6406,7 +6406,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05 15:23:00</t>
+          <t>2026-07-06 00:23:00</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -6486,7 +6486,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-04 18:21:23</t>
+          <t>2026-07-05 03:21:23</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -6566,7 +6566,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03 18:01:40</t>
+          <t>2026-07-04 03:01:40</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -6646,7 +6646,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02 16:48:19</t>
+          <t>2026-07-03 01:48:19</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -6726,7 +6726,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 15:21:19</t>
+          <t>2026-07-01 00:21:19</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -6806,7 +6806,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 14:38:16</t>
+          <t>2026-06-30 23:38:16</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -6886,7 +6886,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-06-29 16:16:28</t>
+          <t>2026-06-30 01:16:28</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -6966,7 +6966,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-29 15:34:32</t>
+          <t>2026-06-30 00:34:32</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 15:50:56</t>
+          <t>2026-06-26 00:50:56</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -7126,7 +7126,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 15:06:40</t>
+          <t>2026-06-26 00:06:40</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 17:07:56</t>
+          <t>2026-06-25 02:07:56</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -7286,7 +7286,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 16:33:19</t>
+          <t>2026-06-25 01:33:19</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -7366,7 +7366,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 15:47:59</t>
+          <t>2026-06-25 00:47:59</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -7446,7 +7446,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 15:08:31</t>
+          <t>2026-06-25 00:08:31</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -7526,7 +7526,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 14:33:15</t>
+          <t>2026-06-24 23:33:15</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 13:39:11</t>
+          <t>2026-06-24 22:39:11</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -7686,7 +7686,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22 16:16:06</t>
+          <t>2026-06-23 01:16:06</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -7766,7 +7766,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22 15:38:08</t>
+          <t>2026-06-23 00:38:08</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -7846,7 +7846,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22 15:29:33</t>
+          <t>2026-06-23 00:29:33</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -7926,7 +7926,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 16:54:04</t>
+          <t>2026-06-19 01:54:04</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -8006,7 +8006,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 16:14:50</t>
+          <t>2026-06-19 01:14:50</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -8086,7 +8086,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 15:35:17</t>
+          <t>2026-06-19 00:35:17</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 14:55:50</t>
+          <t>2026-06-18 23:55:50</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -8246,7 +8246,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 15:44:42</t>
+          <t>2026-06-18 00:44:42</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -8326,7 +8326,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 14:57:38</t>
+          <t>2026-06-17 23:57:38</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -8406,7 +8406,7 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16 16:58:55</t>
+          <t>2026-06-17 01:58:55</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -8486,7 +8486,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16 16:30:07</t>
+          <t>2026-06-17 01:30:07</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -8566,7 +8566,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 18:10:28</t>
+          <t>2026-06-15 03:10:28</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 17:27:52</t>
+          <t>2026-06-15 02:27:52</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 16:57:23</t>
+          <t>2026-06-15 01:57:23</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -8806,7 +8806,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 16:27:22</t>
+          <t>2026-06-15 01:27:22</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -8886,7 +8886,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 15:24:35</t>
+          <t>2026-06-15 00:24:35</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -8966,7 +8966,7 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 14:46:55</t>
+          <t>2026-06-14 23:46:55</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -9046,7 +9046,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 16:41:53</t>
+          <t>2026-06-14 01:41:53</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -9126,7 +9126,7 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 15:52:58</t>
+          <t>2026-06-14 00:52:58</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -9206,7 +9206,7 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 15:14:23</t>
+          <t>2026-06-14 00:14:23</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
@@ -9286,7 +9286,7 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 14:45:21</t>
+          <t>2026-06-13 23:45:21</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -9366,7 +9366,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 14:05:32</t>
+          <t>2026-06-13 23:05:32</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -9446,7 +9446,7 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 16:08:14</t>
+          <t>2026-06-11 01:08:14</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -9526,7 +9526,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 15:34:35</t>
+          <t>2026-06-11 00:34:35</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -9606,7 +9606,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 15:09:17</t>
+          <t>2026-06-11 00:09:17</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -9686,7 +9686,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 14:27:53</t>
+          <t>2026-06-10 23:27:53</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -9766,7 +9766,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09 15:49:00</t>
+          <t>2026-06-10 00:49:00</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -9846,7 +9846,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05 17:58:51</t>
+          <t>2026-06-06 02:58:51</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -9926,7 +9926,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05 17:15:04</t>
+          <t>2026-06-06 02:15:04</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -10006,7 +10006,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 14:49:14</t>
+          <t>2026-06-04 23:49:14</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -10086,7 +10086,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 12:40:04</t>
+          <t>2026-06-04 21:40:04</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -10166,7 +10166,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 12:17:24</t>
+          <t>2026-06-04 21:17:24</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 16:06:27</t>
+          <t>2026-06-04 01:06:27</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -10326,7 +10326,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 15:31:09</t>
+          <t>2026-06-04 00:31:09</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 14:53:57</t>
+          <t>2026-06-03 23:53:57</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -10486,7 +10486,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 13:44:02</t>
+          <t>2026-06-03 22:44:02</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -10566,7 +10566,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02 13:49:11</t>
+          <t>2026-06-02 22:49:11</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -10646,7 +10646,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 14:56:06</t>
+          <t>2026-06-01 23:56:06</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -10726,7 +10726,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 14:20:26</t>
+          <t>2026-06-01 23:20:26</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -10806,7 +10806,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 14:01:06</t>
+          <t>2026-06-01 23:01:06</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -10886,7 +10886,7 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>2026-05-30 18:01:04</t>
+          <t>2026-05-31 03:01:04</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -10966,7 +10966,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>2026-05-30 17:13:41</t>
+          <t>2026-05-31 02:13:41</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -11046,7 +11046,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:00:40</t>
+          <t>2026-05-25 23:00:40</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -11126,7 +11126,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 16:55:47</t>
+          <t>2026-05-25 01:55:47</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 16:24:22</t>
+          <t>2026-05-25 01:24:22</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -11286,7 +11286,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 14:49:25</t>
+          <t>2026-05-24 23:49:25</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -11366,7 +11366,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 18:13:39</t>
+          <t>2026-05-24 03:13:39</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -11446,7 +11446,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 17:41:52</t>
+          <t>2026-05-24 02:41:52</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -11526,7 +11526,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 14:19:04</t>
+          <t>2026-05-23 23:19:04</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 13:43:20</t>
+          <t>2026-05-23 22:43:20</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -11686,7 +11686,7 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 06:54:19</t>
+          <t>2026-05-23 15:54:19</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -11766,7 +11766,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 17:25:24</t>
+          <t>2026-05-23 02:25:24</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -11846,7 +11846,7 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 16:29:23</t>
+          <t>2026-05-22 01:29:23</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -11926,7 +11926,7 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 15:48:49</t>
+          <t>2026-05-22 00:48:49</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -12006,7 +12006,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 15:00:45</t>
+          <t>2026-05-22 00:00:45</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 14:22:44</t>
+          <t>2026-05-21 23:22:44</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -12166,7 +12166,7 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 15:05:15</t>
+          <t>2026-05-21 00:05:15</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -12246,7 +12246,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 14:43:50</t>
+          <t>2026-05-20 23:43:50</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -12326,7 +12326,7 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 13:57:45</t>
+          <t>2026-05-20 22:57:45</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -12406,7 +12406,7 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>2026-05-19 16:25:45</t>
+          <t>2026-05-20 01:25:45</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -12486,7 +12486,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>2026-05-19 15:46:42</t>
+          <t>2026-05-20 00:46:42</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -12566,7 +12566,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>2026-05-18 13:56:39</t>
+          <t>2026-05-18 22:56:39</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -12646,7 +12646,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14 16:35:56</t>
+          <t>2026-05-15 01:35:56</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -12726,7 +12726,7 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14 16:17:05</t>
+          <t>2026-05-15 01:17:05</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -12806,7 +12806,7 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14 15:05:48</t>
+          <t>2026-05-15 00:05:48</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -12886,7 +12886,7 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>2026-05-13 16:25:38</t>
+          <t>2026-05-14 01:25:38</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -12966,7 +12966,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 15:19:57</t>
+          <t>2026-05-12 00:19:57</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -13046,7 +13046,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 14:54:15</t>
+          <t>2026-05-11 23:54:15</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -13126,7 +13126,7 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 14:14:30</t>
+          <t>2026-05-11 23:14:30</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -13206,7 +13206,7 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 13:37:05</t>
+          <t>2026-05-11 22:37:05</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -13286,7 +13286,7 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 12:53:13</t>
+          <t>2026-05-11 21:53:13</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -13366,7 +13366,7 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 15:04:01</t>
+          <t>2026-05-11 00:04:01</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -13446,7 +13446,7 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 16:54:24</t>
+          <t>2026-05-10 01:54:24</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -13526,7 +13526,7 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 16:22:50</t>
+          <t>2026-05-10 01:22:50</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -13606,7 +13606,7 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 15:26:16</t>
+          <t>2026-05-10 00:26:16</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -13686,7 +13686,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 14:38:30</t>
+          <t>2026-05-09 23:38:30</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 13:50:20</t>
+          <t>2026-05-09 22:50:20</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -13846,7 +13846,7 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 13:13:25</t>
+          <t>2026-05-09 22:13:25</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -13926,7 +13926,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 11:00:11</t>
+          <t>2026-05-09 20:00:11</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -14006,7 +14006,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 10:10:28</t>
+          <t>2026-05-09 19:10:28</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -14086,7 +14086,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 17:17:27</t>
+          <t>2026-05-09 02:17:27</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -14166,7 +14166,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 16:38:25</t>
+          <t>2026-05-09 01:38:25</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -14246,7 +14246,7 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 15:58:58</t>
+          <t>2026-05-09 00:58:58</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -14326,7 +14326,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 15:37:55</t>
+          <t>2026-05-09 00:37:55</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -14406,7 +14406,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 16:48:31</t>
+          <t>2026-05-08 01:48:31</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -14486,7 +14486,7 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 16:02:52</t>
+          <t>2026-05-08 01:02:52</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -14566,7 +14566,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 15:23:29</t>
+          <t>2026-05-08 00:23:29</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -14646,7 +14646,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 16:30:56</t>
+          <t>2026-05-07 01:30:56</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -14726,7 +14726,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 15:42:16</t>
+          <t>2026-05-07 00:42:16</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -14806,7 +14806,7 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 14:44:04</t>
+          <t>2026-05-06 23:44:04</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -14886,7 +14886,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 09:13:52</t>
+          <t>2026-05-06 18:13:52</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -14966,7 +14966,7 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 09:05:08</t>
+          <t>2026-05-06 18:05:08</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -15046,7 +15046,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 08:22:30</t>
+          <t>2026-05-06 17:22:30</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -15126,7 +15126,7 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 07:28:42</t>
+          <t>2026-05-06 16:28:42</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -15206,7 +15206,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 18:16:57</t>
+          <t>2026-05-06 03:16:57</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -15286,7 +15286,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 17:32:40</t>
+          <t>2026-05-06 02:32:40</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -15366,7 +15366,7 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 17:23:28</t>
+          <t>2026-05-06 02:23:28</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 16:48:28</t>
+          <t>2026-05-06 01:48:28</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -15526,7 +15526,7 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 15:52:33</t>
+          <t>2026-05-06 00:52:33</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -15606,7 +15606,7 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 08:43:06</t>
+          <t>2026-05-05 17:43:06</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -15686,7 +15686,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 15:36:42</t>
+          <t>2026-05-03 00:36:42</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -15766,7 +15766,7 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 14:51:09</t>
+          <t>2026-05-02 23:51:09</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -15846,7 +15846,7 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 13:15:10</t>
+          <t>2026-05-02 22:15:10</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -15926,7 +15926,7 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 12:29:49</t>
+          <t>2026-05-02 21:29:49</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 16:39:42</t>
+          <t>2026-05-01 01:39:42</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -16086,7 +16086,7 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 16:01:34</t>
+          <t>2026-05-01 01:01:34</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -16166,7 +16166,7 @@
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 15:24:48</t>
+          <t>2026-05-01 00:24:48</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -16246,7 +16246,7 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 14:37:10</t>
+          <t>2026-04-30 23:37:10</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -16326,7 +16326,7 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 13:58:06</t>
+          <t>2026-04-30 22:58:06</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -16406,7 +16406,7 @@
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 18:29:33</t>
+          <t>2026-04-30 03:29:33</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -16486,7 +16486,7 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 17:54:07</t>
+          <t>2026-04-30 02:54:07</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -16566,7 +16566,7 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 17:20:58</t>
+          <t>2026-04-30 02:20:58</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -16646,7 +16646,7 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 16:42:01</t>
+          <t>2026-04-30 01:42:01</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -16726,7 +16726,7 @@
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 16:03:17</t>
+          <t>2026-04-30 01:03:17</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -16806,7 +16806,7 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 15:19:47</t>
+          <t>2026-04-30 00:19:47</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -16886,7 +16886,7 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 14:29:53</t>
+          <t>2026-04-29 23:29:53</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
@@ -16966,7 +16966,7 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 13:59:49</t>
+          <t>2026-04-29 22:59:49</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -17046,7 +17046,7 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 13:38:22</t>
+          <t>2026-04-29 22:38:22</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 13:17:44</t>
+          <t>2026-04-29 22:17:44</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
@@ -17206,7 +17206,7 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 18:28:56</t>
+          <t>2026-04-29 03:28:56</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -17286,7 +17286,7 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 17:58:50</t>
+          <t>2026-04-29 02:58:50</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
@@ -17366,7 +17366,7 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 17:29:43</t>
+          <t>2026-04-29 02:29:43</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -17446,7 +17446,7 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 16:38:43</t>
+          <t>2026-04-29 01:38:43</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -17526,7 +17526,7 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 15:58:54</t>
+          <t>2026-04-29 00:58:54</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
@@ -17606,7 +17606,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 15:31:32</t>
+          <t>2026-04-29 00:31:32</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -17686,7 +17686,7 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 15:04:20</t>
+          <t>2026-04-29 00:04:20</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
@@ -17766,7 +17766,7 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 14:37:27</t>
+          <t>2026-04-28 23:37:27</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
@@ -17846,7 +17846,7 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 14:09:10</t>
+          <t>2026-04-28 23:09:10</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
@@ -17926,7 +17926,7 @@
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 14:59:25</t>
+          <t>2026-04-27 23:59:25</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
@@ -18006,7 +18006,7 @@
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 14:49:35</t>
+          <t>2026-04-27 23:49:35</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
@@ -18086,7 +18086,7 @@
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 13:55:34</t>
+          <t>2026-04-27 22:55:34</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
@@ -18166,7 +18166,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 13:04:13</t>
+          <t>2026-04-27 22:04:13</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
@@ -18246,7 +18246,7 @@
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 17:49:02</t>
+          <t>2026-04-25 02:49:02</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
@@ -18326,7 +18326,7 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 17:03:56</t>
+          <t>2026-04-25 02:03:56</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
@@ -18406,7 +18406,7 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 16:37:00</t>
+          <t>2026-04-25 01:37:00</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
@@ -18486,7 +18486,7 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 15:33:59</t>
+          <t>2026-04-24 00:33:59</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
@@ -18566,7 +18566,7 @@
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 15:22:46</t>
+          <t>2026-04-24 00:22:46</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -18646,7 +18646,7 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 15:12:54</t>
+          <t>2026-04-24 00:12:54</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
@@ -18726,7 +18726,7 @@
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 13:36:03</t>
+          <t>2026-04-23 22:36:03</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 15:58:57</t>
+          <t>2026-04-14 00:58:57</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
@@ -18886,7 +18886,7 @@
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 15:09:08</t>
+          <t>2026-04-14 00:09:08</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -18966,7 +18966,7 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>2026-04-12 16:48:02</t>
+          <t>2026-04-13 01:48:02</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
@@ -19046,7 +19046,7 @@
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>2026-04-12 16:17:58</t>
+          <t>2026-04-13 01:17:58</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -19126,7 +19126,7 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>2026-04-12 15:41:20</t>
+          <t>2026-04-13 00:41:20</t>
         </is>
       </c>
       <c r="B199" s="7" t="inlineStr">
@@ -19206,7 +19206,7 @@
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 14:18:06</t>
+          <t>2026-04-09 23:18:06</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -19286,7 +19286,7 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 13:52:44</t>
+          <t>2026-04-09 22:52:44</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
@@ -19366,7 +19366,7 @@
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 13:27:45</t>
+          <t>2026-04-09 22:27:45</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -19446,7 +19446,7 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>2026-04-07 16:10:31</t>
+          <t>2026-04-08 01:10:31</t>
         </is>
       </c>
       <c r="B203" s="7" t="inlineStr">
@@ -19526,7 +19526,7 @@
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>2026-04-07 15:29:19</t>
+          <t>2026-04-08 00:29:19</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
@@ -19606,7 +19606,7 @@
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>2026-04-03 19:36:31</t>
+          <t>2026-04-04 04:36:31</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
@@ -19686,7 +19686,7 @@
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>2026-04-03 19:16:32</t>
+          <t>2026-04-04 04:16:32</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
@@ -19766,7 +19766,7 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>2026-03-27 19:24:43</t>
+          <t>2026-03-28 04:24:43</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
@@ -19846,7 +19846,7 @@
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>2026-03-27 18:38:31</t>
+          <t>2026-03-28 03:38:31</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -19926,7 +19926,7 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>2026-03-27 18:17:50</t>
+          <t>2026-03-28 03:17:50</t>
         </is>
       </c>
       <c r="B209" s="7" t="inlineStr">
@@ -20006,7 +20006,7 @@
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>2026-03-27 17:43:19</t>
+          <t>2026-03-28 02:43:19</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -20086,7 +20086,7 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>2026-03-27 17:15:18</t>
+          <t>2026-03-28 02:15:18</t>
         </is>
       </c>
       <c r="B211" s="7" t="inlineStr">
@@ -20166,7 +20166,7 @@
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 14:18:12</t>
+          <t>2026-03-25 23:18:12</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
@@ -20246,7 +20246,7 @@
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 15:01:49</t>
+          <t>2026-03-25 00:01:49</t>
         </is>
       </c>
       <c r="B213" s="7" t="inlineStr">
@@ -20326,7 +20326,7 @@
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 14:25:16</t>
+          <t>2026-03-24 23:25:16</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
@@ -20406,7 +20406,7 @@
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 14:02:52</t>
+          <t>2026-03-24 23:02:52</t>
         </is>
       </c>
       <c r="B215" s="7" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 13:26:26</t>
+          <t>2026-03-24 22:26:26</t>
         </is>
       </c>
       <c r="B216" s="7" t="inlineStr">
@@ -20566,7 +20566,7 @@
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>2026-03-23 15:56:18</t>
+          <t>2026-03-24 00:56:18</t>
         </is>
       </c>
       <c r="B217" s="7" t="inlineStr">
@@ -20646,7 +20646,7 @@
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>2026-03-23 15:29:29</t>
+          <t>2026-03-24 00:29:29</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
@@ -20726,7 +20726,7 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 14:51:11</t>
+          <t>2026-03-22 23:51:11</t>
         </is>
       </c>
       <c r="B219" s="7" t="inlineStr">
@@ -20806,7 +20806,7 @@
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>2026-03-21 16:04:36</t>
+          <t>2026-03-22 01:04:36</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
@@ -20886,7 +20886,7 @@
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>2026-03-20 17:55:49</t>
+          <t>2026-03-21 02:55:49</t>
         </is>
       </c>
       <c r="B221" s="7" t="inlineStr">
@@ -20966,7 +20966,7 @@
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 15:07:07</t>
+          <t>2026-03-18 00:07:07</t>
         </is>
       </c>
       <c r="B222" s="7" t="inlineStr">
@@ -21046,7 +21046,7 @@
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 14:24:05</t>
+          <t>2026-03-17 23:24:05</t>
         </is>
       </c>
       <c r="B223" s="7" t="inlineStr">
@@ -21126,7 +21126,7 @@
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 17:00:50</t>
+          <t>2026-03-17 02:00:50</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -21206,7 +21206,7 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 16:33:08</t>
+          <t>2026-03-17 01:33:08</t>
         </is>
       </c>
       <c r="B225" s="7" t="inlineStr">
@@ -21286,7 +21286,7 @@
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 14:28:09</t>
+          <t>2026-03-16 23:28:09</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
@@ -21366,7 +21366,7 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>2026-03-15 16:32:22</t>
+          <t>2026-03-16 01:32:22</t>
         </is>
       </c>
       <c r="B227" s="7" t="inlineStr">
@@ -21446,7 +21446,7 @@
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
-          <t>2026-03-13 16:43:49</t>
+          <t>2026-03-14 01:43:49</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
@@ -21526,7 +21526,7 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>2026-03-13 16:19:35</t>
+          <t>2026-03-14 01:19:35</t>
         </is>
       </c>
       <c r="B229" s="7" t="inlineStr">
@@ -21606,7 +21606,7 @@
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 14:45:27</t>
+          <t>2026-03-12 23:45:27</t>
         </is>
       </c>
       <c r="B230" s="7" t="inlineStr">
@@ -21686,7 +21686,7 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 14:02:09</t>
+          <t>2026-03-12 23:02:09</t>
         </is>
       </c>
       <c r="B231" s="7" t="inlineStr">
@@ -21766,7 +21766,7 @@
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 13:42:59</t>
+          <t>2026-03-12 22:42:59</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
@@ -21846,7 +21846,7 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 16:39:10</t>
+          <t>2026-03-12 01:39:10</t>
         </is>
       </c>
       <c r="B233" s="7" t="inlineStr">
@@ -21926,7 +21926,7 @@
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 15:43:21</t>
+          <t>2026-03-12 00:43:21</t>
         </is>
       </c>
       <c r="B234" s="7" t="inlineStr">
@@ -22006,7 +22006,7 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:25</t>
+          <t>2026-03-12 00:04:25</t>
         </is>
       </c>
       <c r="B235" s="7" t="inlineStr">
@@ -22086,7 +22086,7 @@
     <row r="236">
       <c r="A236" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 13:54:02</t>
+          <t>2026-03-11 22:54:02</t>
         </is>
       </c>
       <c r="B236" s="7" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>2026-03-07 17:01:53</t>
+          <t>2026-03-08 02:01:53</t>
         </is>
       </c>
       <c r="B237" s="7" t="inlineStr">
@@ -22246,7 +22246,7 @@
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>2026-03-01 17:18:59</t>
+          <t>2026-03-02 02:18:59</t>
         </is>
       </c>
       <c r="B238" s="7" t="inlineStr">
@@ -22326,7 +22326,7 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 16:40:38</t>
+          <t>2026-02-24 01:40:38</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
@@ -22406,7 +22406,7 @@
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 15:10:31</t>
+          <t>2026-02-24 00:10:31</t>
         </is>
       </c>
       <c r="B240" s="7" t="inlineStr">
@@ -22486,7 +22486,7 @@
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 14:33:47</t>
+          <t>2026-02-23 23:33:47</t>
         </is>
       </c>
       <c r="B241" s="7" t="inlineStr">
@@ -22566,7 +22566,7 @@
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 13:40:54</t>
+          <t>2026-02-23 22:40:54</t>
         </is>
       </c>
       <c r="B242" s="7" t="inlineStr">
@@ -22646,7 +22646,7 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 12:58:56</t>
+          <t>2026-02-23 21:58:56</t>
         </is>
       </c>
       <c r="B243" s="7" t="inlineStr">
@@ -22726,7 +22726,7 @@
     <row r="244">
       <c r="A244" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 10:21:48</t>
+          <t>2026-02-23 19:21:48</t>
         </is>
       </c>
       <c r="B244" s="7" t="inlineStr">
@@ -22806,7 +22806,7 @@
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 08:17:13</t>
+          <t>2026-02-23 17:17:13</t>
         </is>
       </c>
       <c r="B245" s="7" t="inlineStr">
@@ -22886,7 +22886,7 @@
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22 19:22:01</t>
+          <t>2026-02-23 04:22:01</t>
         </is>
       </c>
       <c r="B246" s="7" t="inlineStr">
@@ -22966,7 +22966,7 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22 18:23:51</t>
+          <t>2026-02-23 03:23:51</t>
         </is>
       </c>
       <c r="B247" s="7" t="inlineStr">
@@ -23046,7 +23046,7 @@
     <row r="248">
       <c r="A248" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22 17:58:18</t>
+          <t>2026-02-23 02:58:18</t>
         </is>
       </c>
       <c r="B248" s="7" t="inlineStr">
@@ -23126,7 +23126,7 @@
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22 17:29:21</t>
+          <t>2026-02-23 02:29:21</t>
         </is>
       </c>
       <c r="B249" s="7" t="inlineStr">
@@ -23206,7 +23206,7 @@
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22 16:59:09</t>
+          <t>2026-02-23 01:59:09</t>
         </is>
       </c>
       <c r="B250" s="7" t="inlineStr">
@@ -23286,7 +23286,7 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22 16:32:08</t>
+          <t>2026-02-23 01:32:08</t>
         </is>
       </c>
       <c r="B251" s="7" t="inlineStr">
@@ -23366,7 +23366,7 @@
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 18:34:36</t>
+          <t>2026-02-21 03:34:36</t>
         </is>
       </c>
       <c r="B252" s="7" t="inlineStr">
@@ -23446,7 +23446,7 @@
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 17:57:13</t>
+          <t>2026-02-21 02:57:13</t>
         </is>
       </c>
       <c r="B253" s="7" t="inlineStr">
@@ -23526,7 +23526,7 @@
     <row r="254">
       <c r="A254" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 17:19:01</t>
+          <t>2026-02-21 02:19:01</t>
         </is>
       </c>
       <c r="B254" s="7" t="inlineStr">
@@ -23606,7 +23606,7 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 16:41:10</t>
+          <t>2026-02-21 01:41:10</t>
         </is>
       </c>
       <c r="B255" s="7" t="inlineStr">
@@ -23686,7 +23686,7 @@
     <row r="256">
       <c r="A256" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 15:57:47</t>
+          <t>2026-02-21 00:57:47</t>
         </is>
       </c>
       <c r="B256" s="7" t="inlineStr">
@@ -23766,7 +23766,7 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 15:39:52</t>
+          <t>2026-02-21 00:39:52</t>
         </is>
       </c>
       <c r="B257" s="7" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="258">
       <c r="A258" s="7" t="inlineStr">
         <is>
-          <t>2026-02-19 16:21:13</t>
+          <t>2026-02-20 01:21:13</t>
         </is>
       </c>
       <c r="B258" s="7" t="inlineStr">
@@ -23926,7 +23926,7 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>2026-02-19 15:33:10</t>
+          <t>2026-02-20 00:33:10</t>
         </is>
       </c>
       <c r="B259" s="7" t="inlineStr">
@@ -24006,7 +24006,7 @@
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>2026-02-17 15:37:38</t>
+          <t>2026-02-18 00:37:38</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
@@ -24086,7 +24086,7 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>2026-02-17 14:58:39</t>
+          <t>2026-02-17 23:58:39</t>
         </is>
       </c>
       <c r="B261" s="7" t="inlineStr">
@@ -24166,7 +24166,7 @@
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 17:24:16</t>
+          <t>2026-02-16 02:24:16</t>
         </is>
       </c>
       <c r="B262" s="7" t="inlineStr">
@@ -24246,7 +24246,7 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 16:47:19</t>
+          <t>2026-02-16 01:47:19</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
@@ -24326,7 +24326,7 @@
     <row r="264">
       <c r="A264" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 15:56:43</t>
+          <t>2026-02-16 00:56:43</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -24406,7 +24406,7 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 15:26:20</t>
+          <t>2026-02-16 00:26:20</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
@@ -24486,7 +24486,7 @@
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 14:48:44</t>
+          <t>2026-02-15 23:48:44</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -24566,7 +24566,7 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 19:17:17</t>
+          <t>2026-02-15 04:17:17</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -24646,7 +24646,7 @@
     <row r="268">
       <c r="A268" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 18:53:01</t>
+          <t>2026-02-15 03:53:01</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
@@ -24726,7 +24726,7 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 17:59:46</t>
+          <t>2026-02-15 02:59:46</t>
         </is>
       </c>
       <c r="B269" s="7" t="inlineStr">
@@ -24806,7 +24806,7 @@
     <row r="270">
       <c r="A270" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 17:26:42</t>
+          <t>2026-02-15 02:26:42</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
@@ -24886,7 +24886,7 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 17:00:09</t>
+          <t>2026-02-15 02:00:09</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
@@ -24966,7 +24966,7 @@
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 16:39:16</t>
+          <t>2026-02-15 01:39:16</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -25046,7 +25046,7 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 15:56:51</t>
+          <t>2026-02-15 00:56:51</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
@@ -25126,7 +25126,7 @@
     <row r="274">
       <c r="A274" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 14:52:26</t>
+          <t>2026-02-14 23:52:26</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -25206,7 +25206,7 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 14:14:55</t>
+          <t>2026-02-14 23:14:55</t>
         </is>
       </c>
       <c r="B275" s="7" t="inlineStr">
@@ -25286,7 +25286,7 @@
     <row r="276">
       <c r="A276" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13 19:19:58</t>
+          <t>2026-02-14 04:19:58</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
@@ -25366,7 +25366,7 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13 18:37:53</t>
+          <t>2026-02-14 03:37:53</t>
         </is>
       </c>
       <c r="B277" s="7" t="inlineStr">
@@ -25446,7 +25446,7 @@
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13 18:03:31</t>
+          <t>2026-02-14 03:03:31</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13 17:08:36</t>
+          <t>2026-02-14 02:08:36</t>
         </is>
       </c>
       <c r="B279" s="7" t="inlineStr">
@@ -25606,7 +25606,7 @@
     <row r="280">
       <c r="A280" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 15:20:03</t>
+          <t>2026-02-12 00:20:03</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -25686,7 +25686,7 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 18:05:03</t>
+          <t>2026-02-11 03:05:03</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
@@ -25766,7 +25766,7 @@
     <row r="282">
       <c r="A282" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 17:14:02</t>
+          <t>2026-02-11 02:14:02</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -25846,7 +25846,7 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 16:33:21</t>
+          <t>2026-02-11 01:33:21</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
@@ -25926,7 +25926,7 @@
     <row r="284">
       <c r="A284" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 16:01:41</t>
+          <t>2026-02-11 01:01:41</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -26006,7 +26006,7 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 16:49:32</t>
+          <t>2026-02-10 01:49:32</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
@@ -26086,7 +26086,7 @@
     <row r="286">
       <c r="A286" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 16:42:29</t>
+          <t>2026-02-10 01:42:29</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -26166,7 +26166,7 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 14:44:10</t>
+          <t>2026-02-09 23:44:10</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -26246,7 +26246,7 @@
     <row r="288">
       <c r="A288" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 14:00:28</t>
+          <t>2026-02-09 23:00:28</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -26326,7 +26326,7 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08 15:27:49</t>
+          <t>2026-02-09 00:27:49</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -26406,7 +26406,7 @@
     <row r="290">
       <c r="A290" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08 15:16:42</t>
+          <t>2026-02-09 00:16:42</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -26486,7 +26486,7 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 19:04:43</t>
+          <t>2026-02-08 04:04:43</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
@@ -26566,7 +26566,7 @@
     <row r="292">
       <c r="A292" s="7" t="inlineStr">
         <is>
-          <t>2026-02-06 18:13:11</t>
+          <t>2026-02-07 03:13:11</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -26646,7 +26646,7 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>2026-02-06 17:19:42</t>
+          <t>2026-02-07 02:19:42</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
@@ -26726,7 +26726,7 @@
     <row r="294">
       <c r="A294" s="7" t="inlineStr">
         <is>
-          <t>2026-02-06 16:37:36</t>
+          <t>2026-02-07 01:37:36</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -26806,7 +26806,7 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>2026-02-03 14:04:49</t>
+          <t>2026-02-03 23:04:49</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
@@ -26886,7 +26886,7 @@
     <row r="296">
       <c r="A296" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 14:21:38</t>
+          <t>2026-02-02 23:21:38</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -26966,7 +26966,7 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 18:08:17</t>
+          <t>2026-02-02 03:08:17</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -27046,7 +27046,7 @@
     <row r="298">
       <c r="A298" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 17:41:55</t>
+          <t>2026-02-02 02:41:55</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -27126,7 +27126,7 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 17:09:57</t>
+          <t>2026-02-02 02:09:57</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="300">
       <c r="A300" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 16:41:49</t>
+          <t>2026-02-02 01:41:49</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
@@ -27286,7 +27286,7 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 17:22:13</t>
+          <t>2026-02-01 02:22:13</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -27366,7 +27366,7 @@
     <row r="302">
       <c r="A302" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 16:20:54</t>
+          <t>2026-02-01 01:20:54</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
@@ -27446,7 +27446,7 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 16:09:32</t>
+          <t>2026-02-01 01:09:32</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
@@ -27526,7 +27526,7 @@
     <row r="304">
       <c r="A304" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 15:29:37</t>
+          <t>2026-02-01 00:29:37</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -27606,7 +27606,7 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 15:03:50</t>
+          <t>2026-02-01 00:03:50</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -27686,7 +27686,7 @@
     <row r="306">
       <c r="A306" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 14:15:28</t>
+          <t>2026-01-31 23:15:28</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -27766,7 +27766,7 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 15:36:39</t>
+          <t>2026-01-29 00:36:39</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
@@ -27846,7 +27846,7 @@
     <row r="308">
       <c r="A308" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 15:02:45</t>
+          <t>2026-01-29 00:02:45</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
@@ -27926,7 +27926,7 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 14:26:47</t>
+          <t>2026-01-28 23:26:47</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
@@ -28006,7 +28006,7 @@
     <row r="310">
       <c r="A310" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 14:04:33</t>
+          <t>2026-01-28 23:04:33</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -28086,7 +28086,7 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 15:33:31</t>
+          <t>2026-01-28 00:33:31</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -28166,7 +28166,7 @@
     <row r="312">
       <c r="A312" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 14:59:21</t>
+          <t>2026-01-27 23:59:21</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -28246,7 +28246,7 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 14:08:33</t>
+          <t>2026-01-27 23:08:33</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -28326,7 +28326,7 @@
     <row r="314">
       <c r="A314" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 14:28:17</t>
+          <t>2026-01-25 23:28:17</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -28406,7 +28406,7 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 13:56:22</t>
+          <t>2026-01-25 22:56:22</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -28486,7 +28486,7 @@
     <row r="316">
       <c r="A316" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 13:28:25</t>
+          <t>2026-01-25 22:28:25</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -28566,7 +28566,7 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 12:42:03</t>
+          <t>2026-01-25 21:42:03</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -28646,7 +28646,7 @@
     <row r="318">
       <c r="A318" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 10:38:23</t>
+          <t>2026-01-25 19:38:23</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -28726,7 +28726,7 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 09:56:35</t>
+          <t>2026-01-25 18:56:35</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -28806,7 +28806,7 @@
     <row r="320">
       <c r="A320" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 09:29:19</t>
+          <t>2026-01-25 18:29:19</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 08:14:05</t>
+          <t>2026-01-25 17:14:05</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -28966,7 +28966,7 @@
     <row r="322">
       <c r="A322" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 17:47:24</t>
+          <t>2026-01-24 02:47:24</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -29046,7 +29046,7 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 17:12:26</t>
+          <t>2026-01-24 02:12:26</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -29126,7 +29126,7 @@
     <row r="324">
       <c r="A324" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 16:33:34</t>
+          <t>2026-01-24 01:33:34</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -29206,7 +29206,7 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 16:00:39</t>
+          <t>2026-01-24 01:00:39</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -29286,7 +29286,7 @@
     <row r="326">
       <c r="A326" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 15:19:07</t>
+          <t>2026-01-24 00:19:07</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -29366,7 +29366,7 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 14:52:33</t>
+          <t>2026-01-23 23:52:33</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -29446,7 +29446,7 @@
     <row r="328">
       <c r="A328" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 14:19:19</t>
+          <t>2026-01-23 23:19:19</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -29526,7 +29526,7 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 13:36:59</t>
+          <t>2026-01-23 22:36:59</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -29606,7 +29606,7 @@
     <row r="330">
       <c r="A330" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 18:01:58</t>
+          <t>2026-01-23 03:01:58</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -29686,7 +29686,7 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 17:25:41</t>
+          <t>2026-01-23 02:25:41</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -29766,7 +29766,7 @@
     <row r="332">
       <c r="A332" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 15:32:45</t>
+          <t>2026-01-23 00:32:45</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -29846,7 +29846,7 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 14:54:46</t>
+          <t>2026-01-22 23:54:46</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -29926,7 +29926,7 @@
     <row r="334">
       <c r="A334" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 14:17:42</t>
+          <t>2026-01-22 23:17:42</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -30006,7 +30006,7 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>2026-01-21 16:10:08</t>
+          <t>2026-01-22 01:10:08</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -30086,7 +30086,7 @@
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 15:27:51</t>
+          <t>2026-01-21 00:27:51</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -30166,7 +30166,7 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 14:25:34</t>
+          <t>2026-01-20 23:25:34</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -30246,7 +30246,7 @@
     <row r="338">
       <c r="A338" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 13:56:13</t>
+          <t>2026-01-20 22:56:13</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -30326,7 +30326,7 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 16:59:11</t>
+          <t>2026-01-19 01:59:11</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -30406,7 +30406,7 @@
     <row r="340">
       <c r="A340" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 18:05:32</t>
+          <t>2026-01-18 03:05:32</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -30486,7 +30486,7 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 17:19:17</t>
+          <t>2026-01-18 02:19:17</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="342">
       <c r="A342" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 16:58:17</t>
+          <t>2026-01-18 01:58:17</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -30646,7 +30646,7 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 16:18:29</t>
+          <t>2026-01-18 01:18:29</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -30726,7 +30726,7 @@
     <row r="344">
       <c r="A344" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 15:38:58</t>
+          <t>2026-01-18 00:38:58</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -30806,7 +30806,7 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 09:46:30</t>
+          <t>2026-01-17 18:46:30</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -30886,7 +30886,7 @@
     <row r="346">
       <c r="A346" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 17:21:36</t>
+          <t>2026-01-17 02:21:36</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -30966,7 +30966,7 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 16:51:05</t>
+          <t>2026-01-17 01:51:05</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -31046,7 +31046,7 @@
     <row r="348">
       <c r="A348" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 16:18:22</t>
+          <t>2026-01-17 01:18:22</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -31126,7 +31126,7 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>2026-01-15 16:41:15</t>
+          <t>2026-01-16 01:41:15</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -31206,7 +31206,7 @@
     <row r="350">
       <c r="A350" s="7" t="inlineStr">
         <is>
-          <t>2026-01-15 16:05:38</t>
+          <t>2026-01-16 01:05:38</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -31286,7 +31286,7 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 15:57:21</t>
+          <t>2026-01-14 00:57:21</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -31366,7 +31366,7 @@
     <row r="352">
       <c r="A352" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 15:19:49</t>
+          <t>2026-01-14 00:19:49</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -31446,7 +31446,7 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 14:53:29</t>
+          <t>2026-01-13 23:53:29</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -31526,7 +31526,7 @@
     <row r="354">
       <c r="A354" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 17:23:29</t>
+          <t>2026-01-13 02:23:29</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -31606,7 +31606,7 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 16:42:12</t>
+          <t>2026-01-13 01:42:12</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -31686,7 +31686,7 @@
     <row r="356">
       <c r="A356" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 16:17:01</t>
+          <t>2026-01-13 01:17:01</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -31766,7 +31766,7 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 15:43:11</t>
+          <t>2026-01-13 00:43:11</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -31846,7 +31846,7 @@
     <row r="358">
       <c r="A358" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 08:24:44</t>
+          <t>2026-01-12 17:24:44</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -31926,7 +31926,7 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 18:12:16</t>
+          <t>2026-01-12 03:12:16</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -32006,7 +32006,7 @@
     <row r="360">
       <c r="A360" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 17:54:03</t>
+          <t>2026-01-11 02:54:03</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -32086,7 +32086,7 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 17:14:56</t>
+          <t>2026-01-11 02:14:56</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -32166,7 +32166,7 @@
     <row r="362">
       <c r="A362" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 16:17:21</t>
+          <t>2026-01-11 01:17:21</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 15:22:11</t>
+          <t>2026-01-11 00:22:11</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -32326,7 +32326,7 @@
     <row r="364">
       <c r="A364" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 14:38:24</t>
+          <t>2026-01-10 23:38:24</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -32406,7 +32406,7 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>2026-01-09 17:54:19</t>
+          <t>2026-01-10 02:54:19</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -32486,7 +32486,7 @@
     <row r="366">
       <c r="A366" s="7" t="inlineStr">
         <is>
-          <t>2026-01-09 17:00:16</t>
+          <t>2026-01-10 02:00:16</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -32566,7 +32566,7 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>2026-01-09 14:36:27</t>
+          <t>2026-01-09 23:36:27</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -32643,88 +32643,8 @@
         </is>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" s="7" t="inlineStr">
-        <is>
-          <t>2026-01-05 14:21:47</t>
-        </is>
-      </c>
-      <c r="B368" s="7" t="inlineStr">
-        <is>
-          <t>ランク(ソロ/デュオ)</t>
-        </is>
-      </c>
-      <c r="C368" s="10" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D368" s="7" t="inlineStr">
-        <is>
-          <t>SUP</t>
-        </is>
-      </c>
-      <c r="E368" s="7" t="inlineStr">
-        <is>
-          <t>ジャンナ</t>
-        </is>
-      </c>
-      <c r="F368" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G368" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H368" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I368" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J368" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="K368" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="L368" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="M368" s="6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N368" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="O368" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P368" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q368" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R368" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S368" s="11" t="n">
-        <v>6751</v>
-      </c>
-      <c r="T368" s="11" t="n">
-        <v>2219</v>
-      </c>
-      <c r="U368" s="6" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="V368" s="7" t="inlineStr">
-        <is>
-          <t>JP1_556572228</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V368"/>
+  <autoFilter ref="A1:V367"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32735,7 +32655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P368"/>
+  <dimension ref="A1:P367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -32841,7 +32761,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 14:51:39</t>
+          <t>2026-07-28 23:51:39</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
@@ -32903,7 +32823,7 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 14:05:20</t>
+          <t>2026-07-28 23:05:20</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
@@ -32965,7 +32885,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>2026-07-26 16:21:51</t>
+          <t>2026-07-27 01:21:51</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -33027,7 +32947,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>2026-07-26 15:43:02</t>
+          <t>2026-07-27 00:43:02</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -33089,7 +33009,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 14:12:09</t>
+          <t>2026-07-25 23:12:09</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -33151,7 +33071,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 13:30:57</t>
+          <t>2026-07-25 22:30:57</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -33213,7 +33133,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>2026-07-24 15:11:55</t>
+          <t>2026-07-25 00:11:55</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -33275,7 +33195,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>2026-07-24 14:25:38</t>
+          <t>2026-07-24 23:25:38</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -33337,7 +33257,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 15:17:56</t>
+          <t>2026-07-22 00:17:56</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -33399,7 +33319,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 15:04:35</t>
+          <t>2026-07-22 00:04:35</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -33461,7 +33381,7 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 14:25:56</t>
+          <t>2026-07-21 23:25:56</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -33523,7 +33443,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 13:44:36</t>
+          <t>2026-07-21 22:44:36</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -33585,7 +33505,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 13:18:59</t>
+          <t>2026-07-21 22:18:59</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
@@ -33647,7 +33567,7 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>2026-07-19 18:20:20</t>
+          <t>2026-07-20 03:20:20</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -33709,7 +33629,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>2026-07-19 17:39:51</t>
+          <t>2026-07-20 02:39:51</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -33771,7 +33691,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 09:59:14</t>
+          <t>2026-07-18 18:59:14</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -33833,7 +33753,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 09:21:14</t>
+          <t>2026-07-18 18:21:14</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -33895,7 +33815,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 14:06:28</t>
+          <t>2026-07-16 23:06:28</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -33957,7 +33877,7 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 13:32:42</t>
+          <t>2026-07-16 22:32:42</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -34019,7 +33939,7 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 15:40:48</t>
+          <t>2026-07-16 00:40:48</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -34081,7 +34001,7 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 14:41:56</t>
+          <t>2026-07-15 23:41:56</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -34143,7 +34063,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 13:58:44</t>
+          <t>2026-07-15 22:58:44</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -34205,7 +34125,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 13:34:16</t>
+          <t>2026-07-15 22:34:16</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -34267,7 +34187,7 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 14:36:35</t>
+          <t>2026-07-14 23:36:35</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -34329,7 +34249,7 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 13:49:50</t>
+          <t>2026-07-14 22:49:50</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
@@ -34391,7 +34311,7 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 16:02:29</t>
+          <t>2026-07-14 01:02:29</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -34453,7 +34373,7 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 15:22:46</t>
+          <t>2026-07-14 00:22:46</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
@@ -34515,7 +34435,7 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 14:51:38</t>
+          <t>2026-07-13 23:51:38</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -34577,7 +34497,7 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 17:05:19</t>
+          <t>2026-07-13 02:05:19</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
@@ -34639,7 +34559,7 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 16:29:17</t>
+          <t>2026-07-13 01:29:17</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
@@ -34701,7 +34621,7 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 18:11:38</t>
+          <t>2026-07-12 03:11:38</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
@@ -34763,7 +34683,7 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 17:46:15</t>
+          <t>2026-07-12 02:46:15</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -34825,7 +34745,7 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>2026-07-10 18:42:29</t>
+          <t>2026-07-11 03:42:29</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
@@ -34887,7 +34807,7 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>2026-07-10 18:06:21</t>
+          <t>2026-07-11 03:06:21</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
@@ -34949,7 +34869,7 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>2026-07-08 17:55:25</t>
+          <t>2026-07-09 02:55:25</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
@@ -35011,7 +34931,7 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>2026-07-08 17:17:09</t>
+          <t>2026-07-09 02:17:09</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -35073,7 +34993,7 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>2026-07-05 17:03:51</t>
+          <t>2026-07-06 02:03:51</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
@@ -35135,7 +35055,7 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>2026-07-05 16:07:17</t>
+          <t>2026-07-06 01:07:17</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -35197,7 +35117,7 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>2026-07-05 15:23:00</t>
+          <t>2026-07-06 00:23:00</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
@@ -35259,7 +35179,7 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>2026-07-04 18:21:23</t>
+          <t>2026-07-05 03:21:23</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
@@ -35321,7 +35241,7 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>2026-07-03 18:01:40</t>
+          <t>2026-07-04 03:01:40</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
@@ -35383,7 +35303,7 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>2026-07-02 16:48:19</t>
+          <t>2026-07-03 01:48:19</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
@@ -35445,7 +35365,7 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 15:21:19</t>
+          <t>2026-07-01 00:21:19</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
@@ -35507,7 +35427,7 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 14:38:16</t>
+          <t>2026-06-30 23:38:16</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
@@ -35569,7 +35489,7 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>2026-06-29 16:16:28</t>
+          <t>2026-06-30 01:16:28</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
@@ -35631,7 +35551,7 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>2026-06-29 15:34:32</t>
+          <t>2026-06-30 00:34:32</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
@@ -35693,7 +35613,7 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 15:50:56</t>
+          <t>2026-06-26 00:50:56</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
@@ -35755,7 +35675,7 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 15:06:40</t>
+          <t>2026-06-26 00:06:40</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
@@ -35817,7 +35737,7 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 17:07:56</t>
+          <t>2026-06-25 02:07:56</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
@@ -35879,7 +35799,7 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 16:33:19</t>
+          <t>2026-06-25 01:33:19</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
@@ -35941,7 +35861,7 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 15:47:59</t>
+          <t>2026-06-25 00:47:59</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
@@ -36003,7 +35923,7 @@
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 15:08:31</t>
+          <t>2026-06-25 00:08:31</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
@@ -36065,7 +35985,7 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 14:33:15</t>
+          <t>2026-06-24 23:33:15</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
@@ -36127,7 +36047,7 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 13:39:11</t>
+          <t>2026-06-24 22:39:11</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
@@ -36189,7 +36109,7 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>2026-06-22 16:16:06</t>
+          <t>2026-06-23 01:16:06</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
@@ -36251,7 +36171,7 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>2026-06-22 15:38:08</t>
+          <t>2026-06-23 00:38:08</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
@@ -36313,7 +36233,7 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>2026-06-22 15:29:33</t>
+          <t>2026-06-23 00:29:33</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
@@ -36375,7 +36295,7 @@
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 16:54:04</t>
+          <t>2026-06-19 01:54:04</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
@@ -36437,7 +36357,7 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 16:14:50</t>
+          <t>2026-06-19 01:14:50</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
@@ -36499,7 +36419,7 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 15:35:17</t>
+          <t>2026-06-19 00:35:17</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
@@ -36561,7 +36481,7 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 14:55:50</t>
+          <t>2026-06-18 23:55:50</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
@@ -36623,7 +36543,7 @@
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 15:44:42</t>
+          <t>2026-06-18 00:44:42</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
@@ -36685,7 +36605,7 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 14:57:38</t>
+          <t>2026-06-17 23:57:38</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
@@ -36747,7 +36667,7 @@
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>2026-06-16 16:58:55</t>
+          <t>2026-06-17 01:58:55</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
@@ -36809,7 +36729,7 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>2026-06-16 16:30:07</t>
+          <t>2026-06-17 01:30:07</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
@@ -36871,7 +36791,7 @@
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 18:10:28</t>
+          <t>2026-06-15 03:10:28</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
@@ -36933,7 +36853,7 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 17:27:52</t>
+          <t>2026-06-15 02:27:52</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
@@ -36995,7 +36915,7 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 16:57:23</t>
+          <t>2026-06-15 01:57:23</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
@@ -37057,7 +36977,7 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 16:27:22</t>
+          <t>2026-06-15 01:27:22</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
@@ -37119,7 +37039,7 @@
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 15:24:35</t>
+          <t>2026-06-15 00:24:35</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
@@ -37181,7 +37101,7 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 14:46:55</t>
+          <t>2026-06-14 23:46:55</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
@@ -37243,7 +37163,7 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 16:41:53</t>
+          <t>2026-06-14 01:41:53</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
@@ -37305,7 +37225,7 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 15:52:58</t>
+          <t>2026-06-14 00:52:58</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
@@ -37367,7 +37287,7 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 15:14:23</t>
+          <t>2026-06-14 00:14:23</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
@@ -37429,7 +37349,7 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 14:45:21</t>
+          <t>2026-06-13 23:45:21</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
@@ -37491,7 +37411,7 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 14:05:32</t>
+          <t>2026-06-13 23:05:32</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
@@ -37553,7 +37473,7 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 16:08:14</t>
+          <t>2026-06-11 01:08:14</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
@@ -37615,7 +37535,7 @@
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 15:34:35</t>
+          <t>2026-06-11 00:34:35</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
@@ -37677,7 +37597,7 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 15:09:17</t>
+          <t>2026-06-11 00:09:17</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
@@ -37739,7 +37659,7 @@
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 14:27:53</t>
+          <t>2026-06-10 23:27:53</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
@@ -37801,7 +37721,7 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>2026-06-09 15:49:00</t>
+          <t>2026-06-10 00:49:00</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
@@ -37863,7 +37783,7 @@
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>2026-06-05 17:58:51</t>
+          <t>2026-06-06 02:58:51</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
@@ -37925,7 +37845,7 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>2026-06-05 17:15:04</t>
+          <t>2026-06-06 02:15:04</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
@@ -37987,7 +37907,7 @@
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 14:49:14</t>
+          <t>2026-06-04 23:49:14</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
@@ -38049,7 +37969,7 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 12:40:04</t>
+          <t>2026-06-04 21:40:04</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
@@ -38111,7 +38031,7 @@
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 12:17:24</t>
+          <t>2026-06-04 21:17:24</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
@@ -38173,7 +38093,7 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 16:06:27</t>
+          <t>2026-06-04 01:06:27</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
@@ -38235,7 +38155,7 @@
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 15:31:09</t>
+          <t>2026-06-04 00:31:09</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
@@ -38297,7 +38217,7 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 14:53:57</t>
+          <t>2026-06-03 23:53:57</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
@@ -38359,7 +38279,7 @@
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 13:44:02</t>
+          <t>2026-06-03 22:44:02</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
@@ -38421,7 +38341,7 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>2026-06-02 13:49:11</t>
+          <t>2026-06-02 22:49:11</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
@@ -38483,7 +38403,7 @@
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 14:56:06</t>
+          <t>2026-06-01 23:56:06</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
@@ -38545,7 +38465,7 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 14:20:26</t>
+          <t>2026-06-01 23:20:26</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
@@ -38607,7 +38527,7 @@
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 14:01:06</t>
+          <t>2026-06-01 23:01:06</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
@@ -38669,7 +38589,7 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>2026-05-30 18:01:04</t>
+          <t>2026-05-31 03:01:04</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
@@ -38731,7 +38651,7 @@
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>2026-05-30 17:13:41</t>
+          <t>2026-05-31 02:13:41</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
@@ -38793,7 +38713,7 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 14:00:40</t>
+          <t>2026-05-25 23:00:40</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
@@ -38855,7 +38775,7 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 16:55:47</t>
+          <t>2026-05-25 01:55:47</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
@@ -38917,7 +38837,7 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 16:24:22</t>
+          <t>2026-05-25 01:24:22</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
@@ -38979,7 +38899,7 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 14:49:25</t>
+          <t>2026-05-24 23:49:25</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
@@ -39041,7 +38961,7 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 18:13:39</t>
+          <t>2026-05-24 03:13:39</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
@@ -39103,7 +39023,7 @@
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 17:41:52</t>
+          <t>2026-05-24 02:41:52</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
@@ -39165,7 +39085,7 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 14:19:04</t>
+          <t>2026-05-23 23:19:04</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
@@ -39227,7 +39147,7 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 13:43:20</t>
+          <t>2026-05-23 22:43:20</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
@@ -39289,7 +39209,7 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 06:54:19</t>
+          <t>2026-05-23 15:54:19</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
@@ -39351,7 +39271,7 @@
     <row r="107">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 17:25:24</t>
+          <t>2026-05-23 02:25:24</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
@@ -39413,7 +39333,7 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 16:29:23</t>
+          <t>2026-05-22 01:29:23</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
@@ -39475,7 +39395,7 @@
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 15:48:49</t>
+          <t>2026-05-22 00:48:49</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
@@ -39537,7 +39457,7 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 15:00:45</t>
+          <t>2026-05-22 00:00:45</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
@@ -39599,7 +39519,7 @@
     <row r="111">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 14:22:44</t>
+          <t>2026-05-21 23:22:44</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
@@ -39661,7 +39581,7 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 15:05:15</t>
+          <t>2026-05-21 00:05:15</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
@@ -39723,7 +39643,7 @@
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 14:43:50</t>
+          <t>2026-05-20 23:43:50</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
@@ -39785,7 +39705,7 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 13:57:45</t>
+          <t>2026-05-20 22:57:45</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
@@ -39847,7 +39767,7 @@
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>2026-05-19 16:25:45</t>
+          <t>2026-05-20 01:25:45</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
@@ -39909,7 +39829,7 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>2026-05-19 15:46:42</t>
+          <t>2026-05-20 00:46:42</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
@@ -39971,7 +39891,7 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>2026-05-18 13:56:39</t>
+          <t>2026-05-18 22:56:39</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
@@ -40033,7 +39953,7 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>2026-05-14 16:35:56</t>
+          <t>2026-05-15 01:35:56</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
@@ -40095,7 +40015,7 @@
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>2026-05-14 16:17:05</t>
+          <t>2026-05-15 01:17:05</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
@@ -40157,7 +40077,7 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>2026-05-14 15:05:48</t>
+          <t>2026-05-15 00:05:48</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
@@ -40219,7 +40139,7 @@
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>2026-05-13 16:25:38</t>
+          <t>2026-05-14 01:25:38</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
@@ -40281,7 +40201,7 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 15:19:57</t>
+          <t>2026-05-12 00:19:57</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
@@ -40343,7 +40263,7 @@
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 14:54:15</t>
+          <t>2026-05-11 23:54:15</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
@@ -40405,7 +40325,7 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 14:14:30</t>
+          <t>2026-05-11 23:14:30</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
@@ -40467,7 +40387,7 @@
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 13:37:05</t>
+          <t>2026-05-11 22:37:05</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
@@ -40529,7 +40449,7 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 12:53:13</t>
+          <t>2026-05-11 21:53:13</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
@@ -40591,7 +40511,7 @@
     <row r="127">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 15:04:01</t>
+          <t>2026-05-11 00:04:01</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
@@ -40653,7 +40573,7 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 16:54:24</t>
+          <t>2026-05-10 01:54:24</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
@@ -40715,7 +40635,7 @@
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 16:22:50</t>
+          <t>2026-05-10 01:22:50</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
@@ -40777,7 +40697,7 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 15:26:16</t>
+          <t>2026-05-10 00:26:16</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
@@ -40839,7 +40759,7 @@
     <row r="131">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 14:38:30</t>
+          <t>2026-05-09 23:38:30</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
@@ -40901,7 +40821,7 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 13:50:20</t>
+          <t>2026-05-09 22:50:20</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
@@ -40963,7 +40883,7 @@
     <row r="133">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 13:13:25</t>
+          <t>2026-05-09 22:13:25</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
@@ -41025,7 +40945,7 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 11:00:11</t>
+          <t>2026-05-09 20:00:11</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
@@ -41087,7 +41007,7 @@
     <row r="135">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 10:10:28</t>
+          <t>2026-05-09 19:10:28</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
@@ -41149,7 +41069,7 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 17:17:27</t>
+          <t>2026-05-09 02:17:27</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
@@ -41211,7 +41131,7 @@
     <row r="137">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 16:38:25</t>
+          <t>2026-05-09 01:38:25</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
@@ -41273,7 +41193,7 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 15:58:58</t>
+          <t>2026-05-09 00:58:58</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
@@ -41335,7 +41255,7 @@
     <row r="139">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 15:37:55</t>
+          <t>2026-05-09 00:37:55</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
@@ -41397,7 +41317,7 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 16:48:31</t>
+          <t>2026-05-08 01:48:31</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
@@ -41459,7 +41379,7 @@
     <row r="141">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 16:02:52</t>
+          <t>2026-05-08 01:02:52</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
@@ -41521,7 +41441,7 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 15:23:29</t>
+          <t>2026-05-08 00:23:29</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
@@ -41583,7 +41503,7 @@
     <row r="143">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 16:30:56</t>
+          <t>2026-05-07 01:30:56</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
@@ -41645,7 +41565,7 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 15:42:16</t>
+          <t>2026-05-07 00:42:16</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
@@ -41707,7 +41627,7 @@
     <row r="145">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 14:44:04</t>
+          <t>2026-05-06 23:44:04</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
@@ -41769,7 +41689,7 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 09:13:52</t>
+          <t>2026-05-06 18:13:52</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
@@ -41831,7 +41751,7 @@
     <row r="147">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 09:05:08</t>
+          <t>2026-05-06 18:05:08</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
@@ -41893,7 +41813,7 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 08:22:30</t>
+          <t>2026-05-06 17:22:30</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
@@ -41955,7 +41875,7 @@
     <row r="149">
       <c r="A149" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 07:28:42</t>
+          <t>2026-05-06 16:28:42</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
@@ -42017,7 +41937,7 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 18:16:57</t>
+          <t>2026-05-06 03:16:57</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
@@ -42079,7 +41999,7 @@
     <row r="151">
       <c r="A151" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 17:32:40</t>
+          <t>2026-05-06 02:32:40</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
@@ -42141,7 +42061,7 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 17:23:28</t>
+          <t>2026-05-06 02:23:28</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
@@ -42203,7 +42123,7 @@
     <row r="153">
       <c r="A153" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 16:48:28</t>
+          <t>2026-05-06 01:48:28</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
@@ -42265,7 +42185,7 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 15:52:33</t>
+          <t>2026-05-06 00:52:33</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
@@ -42327,7 +42247,7 @@
     <row r="155">
       <c r="A155" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 08:43:06</t>
+          <t>2026-05-05 17:43:06</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
@@ -42389,7 +42309,7 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 15:36:42</t>
+          <t>2026-05-03 00:36:42</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
@@ -42451,7 +42371,7 @@
     <row r="157">
       <c r="A157" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 14:51:09</t>
+          <t>2026-05-02 23:51:09</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
@@ -42513,7 +42433,7 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 13:15:10</t>
+          <t>2026-05-02 22:15:10</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
@@ -42575,7 +42495,7 @@
     <row r="159">
       <c r="A159" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 12:29:49</t>
+          <t>2026-05-02 21:29:49</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
@@ -42637,7 +42557,7 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 16:39:42</t>
+          <t>2026-05-01 01:39:42</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
@@ -42699,7 +42619,7 @@
     <row r="161">
       <c r="A161" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 16:01:34</t>
+          <t>2026-05-01 01:01:34</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
@@ -42761,7 +42681,7 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 15:24:48</t>
+          <t>2026-05-01 00:24:48</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
@@ -42823,7 +42743,7 @@
     <row r="163">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 14:37:10</t>
+          <t>2026-04-30 23:37:10</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
@@ -42885,7 +42805,7 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 13:58:06</t>
+          <t>2026-04-30 22:58:06</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
@@ -42947,7 +42867,7 @@
     <row r="165">
       <c r="A165" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 18:29:33</t>
+          <t>2026-04-30 03:29:33</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
@@ -43009,7 +42929,7 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 17:54:07</t>
+          <t>2026-04-30 02:54:07</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
@@ -43071,7 +42991,7 @@
     <row r="167">
       <c r="A167" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 17:20:58</t>
+          <t>2026-04-30 02:20:58</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
@@ -43133,7 +43053,7 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 16:42:01</t>
+          <t>2026-04-30 01:42:01</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
@@ -43195,7 +43115,7 @@
     <row r="169">
       <c r="A169" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 16:03:17</t>
+          <t>2026-04-30 01:03:17</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
@@ -43257,7 +43177,7 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 15:19:47</t>
+          <t>2026-04-30 00:19:47</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
@@ -43319,7 +43239,7 @@
     <row r="171">
       <c r="A171" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 14:29:53</t>
+          <t>2026-04-29 23:29:53</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
@@ -43381,7 +43301,7 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 13:59:49</t>
+          <t>2026-04-29 22:59:49</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
@@ -43443,7 +43363,7 @@
     <row r="173">
       <c r="A173" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 13:38:22</t>
+          <t>2026-04-29 22:38:22</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
@@ -43505,7 +43425,7 @@
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 13:17:44</t>
+          <t>2026-04-29 22:17:44</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
@@ -43567,7 +43487,7 @@
     <row r="175">
       <c r="A175" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 18:28:56</t>
+          <t>2026-04-29 03:28:56</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
@@ -43629,7 +43549,7 @@
     <row r="176">
       <c r="A176" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 17:58:50</t>
+          <t>2026-04-29 02:58:50</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
@@ -43691,7 +43611,7 @@
     <row r="177">
       <c r="A177" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 17:29:43</t>
+          <t>2026-04-29 02:29:43</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
@@ -43753,7 +43673,7 @@
     <row r="178">
       <c r="A178" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 16:38:43</t>
+          <t>2026-04-29 01:38:43</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
@@ -43815,7 +43735,7 @@
     <row r="179">
       <c r="A179" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 15:58:54</t>
+          <t>2026-04-29 00:58:54</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
@@ -43877,7 +43797,7 @@
     <row r="180">
       <c r="A180" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 15:31:32</t>
+          <t>2026-04-29 00:31:32</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
@@ -43939,7 +43859,7 @@
     <row r="181">
       <c r="A181" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 15:04:20</t>
+          <t>2026-04-29 00:04:20</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
@@ -44001,7 +43921,7 @@
     <row r="182">
       <c r="A182" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 14:37:27</t>
+          <t>2026-04-28 23:37:27</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
@@ -44063,7 +43983,7 @@
     <row r="183">
       <c r="A183" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 14:09:10</t>
+          <t>2026-04-28 23:09:10</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
@@ -44125,7 +44045,7 @@
     <row r="184">
       <c r="A184" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 14:59:25</t>
+          <t>2026-04-27 23:59:25</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
@@ -44187,7 +44107,7 @@
     <row r="185">
       <c r="A185" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 14:49:35</t>
+          <t>2026-04-27 23:49:35</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
@@ -44249,7 +44169,7 @@
     <row r="186">
       <c r="A186" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 13:55:34</t>
+          <t>2026-04-27 22:55:34</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
@@ -44311,7 +44231,7 @@
     <row r="187">
       <c r="A187" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 13:04:13</t>
+          <t>2026-04-27 22:04:13</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
@@ -44373,7 +44293,7 @@
     <row r="188">
       <c r="A188" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 17:49:02</t>
+          <t>2026-04-25 02:49:02</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
@@ -44435,7 +44355,7 @@
     <row r="189">
       <c r="A189" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 17:03:56</t>
+          <t>2026-04-25 02:03:56</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
@@ -44497,7 +44417,7 @@
     <row r="190">
       <c r="A190" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 16:37:00</t>
+          <t>2026-04-25 01:37:00</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
@@ -44559,7 +44479,7 @@
     <row r="191">
       <c r="A191" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 15:33:59</t>
+          <t>2026-04-24 00:33:59</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
@@ -44621,7 +44541,7 @@
     <row r="192">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 15:22:46</t>
+          <t>2026-04-24 00:22:46</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
@@ -44683,7 +44603,7 @@
     <row r="193">
       <c r="A193" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 15:12:54</t>
+          <t>2026-04-24 00:12:54</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
@@ -44745,7 +44665,7 @@
     <row r="194">
       <c r="A194" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 13:36:03</t>
+          <t>2026-04-23 22:36:03</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
@@ -44807,7 +44727,7 @@
     <row r="195">
       <c r="A195" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 15:58:57</t>
+          <t>2026-04-14 00:58:57</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
@@ -44869,7 +44789,7 @@
     <row r="196">
       <c r="A196" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 15:09:08</t>
+          <t>2026-04-14 00:09:08</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
@@ -44931,7 +44851,7 @@
     <row r="197">
       <c r="A197" s="13" t="inlineStr">
         <is>
-          <t>2026-04-12 16:48:02</t>
+          <t>2026-04-13 01:48:02</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
@@ -44993,7 +44913,7 @@
     <row r="198">
       <c r="A198" s="13" t="inlineStr">
         <is>
-          <t>2026-04-12 16:17:58</t>
+          <t>2026-04-13 01:17:58</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
@@ -45055,7 +44975,7 @@
     <row r="199">
       <c r="A199" s="13" t="inlineStr">
         <is>
-          <t>2026-04-12 15:41:20</t>
+          <t>2026-04-13 00:41:20</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
@@ -45117,7 +45037,7 @@
     <row r="200">
       <c r="A200" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 14:18:06</t>
+          <t>2026-04-09 23:18:06</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
@@ -45179,7 +45099,7 @@
     <row r="201">
       <c r="A201" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 13:52:44</t>
+          <t>2026-04-09 22:52:44</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
@@ -45241,7 +45161,7 @@
     <row r="202">
       <c r="A202" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 13:27:45</t>
+          <t>2026-04-09 22:27:45</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
@@ -45303,7 +45223,7 @@
     <row r="203">
       <c r="A203" s="13" t="inlineStr">
         <is>
-          <t>2026-04-07 16:10:31</t>
+          <t>2026-04-08 01:10:31</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
@@ -45365,7 +45285,7 @@
     <row r="204">
       <c r="A204" s="13" t="inlineStr">
         <is>
-          <t>2026-04-07 15:29:19</t>
+          <t>2026-04-08 00:29:19</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
@@ -45427,7 +45347,7 @@
     <row r="205">
       <c r="A205" s="13" t="inlineStr">
         <is>
-          <t>2026-04-03 19:36:31</t>
+          <t>2026-04-04 04:36:31</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
@@ -45489,7 +45409,7 @@
     <row r="206">
       <c r="A206" s="13" t="inlineStr">
         <is>
-          <t>2026-04-03 19:16:32</t>
+          <t>2026-04-04 04:16:32</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
@@ -45551,7 +45471,7 @@
     <row r="207">
       <c r="A207" s="13" t="inlineStr">
         <is>
-          <t>2026-03-27 19:24:43</t>
+          <t>2026-03-28 04:24:43</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
@@ -45613,7 +45533,7 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>2026-03-27 18:38:31</t>
+          <t>2026-03-28 03:38:31</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
@@ -45675,7 +45595,7 @@
     <row r="209">
       <c r="A209" s="13" t="inlineStr">
         <is>
-          <t>2026-03-27 18:17:50</t>
+          <t>2026-03-28 03:17:50</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
@@ -45737,7 +45657,7 @@
     <row r="210">
       <c r="A210" s="13" t="inlineStr">
         <is>
-          <t>2026-03-27 17:43:19</t>
+          <t>2026-03-28 02:43:19</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
@@ -45799,7 +45719,7 @@
     <row r="211">
       <c r="A211" s="13" t="inlineStr">
         <is>
-          <t>2026-03-27 17:15:18</t>
+          <t>2026-03-28 02:15:18</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
@@ -45861,7 +45781,7 @@
     <row r="212">
       <c r="A212" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 14:18:12</t>
+          <t>2026-03-25 23:18:12</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
@@ -45923,7 +45843,7 @@
     <row r="213">
       <c r="A213" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 15:01:49</t>
+          <t>2026-03-25 00:01:49</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
@@ -45985,7 +45905,7 @@
     <row r="214">
       <c r="A214" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 14:25:16</t>
+          <t>2026-03-24 23:25:16</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
@@ -46047,7 +45967,7 @@
     <row r="215">
       <c r="A215" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 14:02:52</t>
+          <t>2026-03-24 23:02:52</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
@@ -46109,7 +46029,7 @@
     <row r="216">
       <c r="A216" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 13:26:26</t>
+          <t>2026-03-24 22:26:26</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
@@ -46171,7 +46091,7 @@
     <row r="217">
       <c r="A217" s="13" t="inlineStr">
         <is>
-          <t>2026-03-23 15:56:18</t>
+          <t>2026-03-24 00:56:18</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
@@ -46233,7 +46153,7 @@
     <row r="218">
       <c r="A218" s="13" t="inlineStr">
         <is>
-          <t>2026-03-23 15:29:29</t>
+          <t>2026-03-24 00:29:29</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
@@ -46295,7 +46215,7 @@
     <row r="219">
       <c r="A219" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 14:51:11</t>
+          <t>2026-03-22 23:51:11</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
@@ -46357,7 +46277,7 @@
     <row r="220">
       <c r="A220" s="13" t="inlineStr">
         <is>
-          <t>2026-03-21 16:04:36</t>
+          <t>2026-03-22 01:04:36</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
@@ -46419,7 +46339,7 @@
     <row r="221">
       <c r="A221" s="13" t="inlineStr">
         <is>
-          <t>2026-03-20 17:55:49</t>
+          <t>2026-03-21 02:55:49</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
@@ -46481,7 +46401,7 @@
     <row r="222">
       <c r="A222" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 15:07:07</t>
+          <t>2026-03-18 00:07:07</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
@@ -46543,7 +46463,7 @@
     <row r="223">
       <c r="A223" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 14:24:05</t>
+          <t>2026-03-17 23:24:05</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
@@ -46605,7 +46525,7 @@
     <row r="224">
       <c r="A224" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 17:00:50</t>
+          <t>2026-03-17 02:00:50</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
@@ -46667,7 +46587,7 @@
     <row r="225">
       <c r="A225" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 16:33:08</t>
+          <t>2026-03-17 01:33:08</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
@@ -46729,7 +46649,7 @@
     <row r="226">
       <c r="A226" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 14:28:09</t>
+          <t>2026-03-16 23:28:09</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
@@ -46791,7 +46711,7 @@
     <row r="227">
       <c r="A227" s="13" t="inlineStr">
         <is>
-          <t>2026-03-15 16:32:22</t>
+          <t>2026-03-16 01:32:22</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
@@ -46853,7 +46773,7 @@
     <row r="228">
       <c r="A228" s="13" t="inlineStr">
         <is>
-          <t>2026-03-13 16:43:49</t>
+          <t>2026-03-14 01:43:49</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
@@ -46915,7 +46835,7 @@
     <row r="229">
       <c r="A229" s="13" t="inlineStr">
         <is>
-          <t>2026-03-13 16:19:35</t>
+          <t>2026-03-14 01:19:35</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
@@ -46977,7 +46897,7 @@
     <row r="230">
       <c r="A230" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 14:45:27</t>
+          <t>2026-03-12 23:45:27</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
@@ -47039,7 +46959,7 @@
     <row r="231">
       <c r="A231" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 14:02:09</t>
+          <t>2026-03-12 23:02:09</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
@@ -47101,7 +47021,7 @@
     <row r="232">
       <c r="A232" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 13:42:59</t>
+          <t>2026-03-12 22:42:59</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
@@ -47163,7 +47083,7 @@
     <row r="233">
       <c r="A233" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 16:39:10</t>
+          <t>2026-03-12 01:39:10</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
@@ -47225,7 +47145,7 @@
     <row r="234">
       <c r="A234" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 15:43:21</t>
+          <t>2026-03-12 00:43:21</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
@@ -47287,7 +47207,7 @@
     <row r="235">
       <c r="A235" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:25</t>
+          <t>2026-03-12 00:04:25</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
@@ -47349,7 +47269,7 @@
     <row r="236">
       <c r="A236" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 13:54:02</t>
+          <t>2026-03-11 22:54:02</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
@@ -47411,7 +47331,7 @@
     <row r="237">
       <c r="A237" s="13" t="inlineStr">
         <is>
-          <t>2026-03-07 17:01:53</t>
+          <t>2026-03-08 02:01:53</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
@@ -47473,7 +47393,7 @@
     <row r="238">
       <c r="A238" s="13" t="inlineStr">
         <is>
-          <t>2026-03-01 17:18:59</t>
+          <t>2026-03-02 02:18:59</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
@@ -47535,7 +47455,7 @@
     <row r="239">
       <c r="A239" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 16:40:38</t>
+          <t>2026-02-24 01:40:38</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
@@ -47597,7 +47517,7 @@
     <row r="240">
       <c r="A240" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 15:10:31</t>
+          <t>2026-02-24 00:10:31</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
@@ -47659,7 +47579,7 @@
     <row r="241">
       <c r="A241" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 14:33:47</t>
+          <t>2026-02-23 23:33:47</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
@@ -47721,7 +47641,7 @@
     <row r="242">
       <c r="A242" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 13:40:54</t>
+          <t>2026-02-23 22:40:54</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
@@ -47783,7 +47703,7 @@
     <row r="243">
       <c r="A243" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 12:58:56</t>
+          <t>2026-02-23 21:58:56</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
@@ -47845,7 +47765,7 @@
     <row r="244">
       <c r="A244" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 10:21:48</t>
+          <t>2026-02-23 19:21:48</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
@@ -47907,7 +47827,7 @@
     <row r="245">
       <c r="A245" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 08:17:13</t>
+          <t>2026-02-23 17:17:13</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
@@ -47969,7 +47889,7 @@
     <row r="246">
       <c r="A246" s="13" t="inlineStr">
         <is>
-          <t>2026-02-22 19:22:01</t>
+          <t>2026-02-23 04:22:01</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
@@ -48031,7 +47951,7 @@
     <row r="247">
       <c r="A247" s="13" t="inlineStr">
         <is>
-          <t>2026-02-22 18:23:51</t>
+          <t>2026-02-23 03:23:51</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
@@ -48093,7 +48013,7 @@
     <row r="248">
       <c r="A248" s="13" t="inlineStr">
         <is>
-          <t>2026-02-22 17:58:18</t>
+          <t>2026-02-23 02:58:18</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
@@ -48155,7 +48075,7 @@
     <row r="249">
       <c r="A249" s="13" t="inlineStr">
         <is>
-          <t>2026-02-22 17:29:21</t>
+          <t>2026-02-23 02:29:21</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
@@ -48217,7 +48137,7 @@
     <row r="250">
       <c r="A250" s="13" t="inlineStr">
         <is>
-          <t>2026-02-22 16:59:09</t>
+          <t>2026-02-23 01:59:09</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
@@ -48279,7 +48199,7 @@
     <row r="251">
       <c r="A251" s="13" t="inlineStr">
         <is>
-          <t>2026-02-22 16:32:08</t>
+          <t>2026-02-23 01:32:08</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
@@ -48341,7 +48261,7 @@
     <row r="252">
       <c r="A252" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 18:34:36</t>
+          <t>2026-02-21 03:34:36</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
@@ -48403,7 +48323,7 @@
     <row r="253">
       <c r="A253" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 17:57:13</t>
+          <t>2026-02-21 02:57:13</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
@@ -48465,7 +48385,7 @@
     <row r="254">
       <c r="A254" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 17:19:01</t>
+          <t>2026-02-21 02:19:01</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
@@ -48527,7 +48447,7 @@
     <row r="255">
       <c r="A255" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 16:41:10</t>
+          <t>2026-02-21 01:41:10</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
@@ -48589,7 +48509,7 @@
     <row r="256">
       <c r="A256" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 15:57:47</t>
+          <t>2026-02-21 00:57:47</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
@@ -48651,7 +48571,7 @@
     <row r="257">
       <c r="A257" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 15:39:52</t>
+          <t>2026-02-21 00:39:52</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
@@ -48713,7 +48633,7 @@
     <row r="258">
       <c r="A258" s="13" t="inlineStr">
         <is>
-          <t>2026-02-19 16:21:13</t>
+          <t>2026-02-20 01:21:13</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
@@ -48775,7 +48695,7 @@
     <row r="259">
       <c r="A259" s="13" t="inlineStr">
         <is>
-          <t>2026-02-19 15:33:10</t>
+          <t>2026-02-20 00:33:10</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
@@ -48837,7 +48757,7 @@
     <row r="260">
       <c r="A260" s="13" t="inlineStr">
         <is>
-          <t>2026-02-17 15:37:38</t>
+          <t>2026-02-18 00:37:38</t>
         </is>
       </c>
       <c r="B260" s="13" t="inlineStr">
@@ -48899,7 +48819,7 @@
     <row r="261">
       <c r="A261" s="13" t="inlineStr">
         <is>
-          <t>2026-02-17 14:58:39</t>
+          <t>2026-02-17 23:58:39</t>
         </is>
       </c>
       <c r="B261" s="13" t="inlineStr">
@@ -48961,7 +48881,7 @@
     <row r="262">
       <c r="A262" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 17:24:16</t>
+          <t>2026-02-16 02:24:16</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
@@ -49023,7 +48943,7 @@
     <row r="263">
       <c r="A263" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 16:47:19</t>
+          <t>2026-02-16 01:47:19</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
@@ -49085,7 +49005,7 @@
     <row r="264">
       <c r="A264" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 15:56:43</t>
+          <t>2026-02-16 00:56:43</t>
         </is>
       </c>
       <c r="B264" s="13" t="inlineStr">
@@ -49147,7 +49067,7 @@
     <row r="265">
       <c r="A265" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 15:26:20</t>
+          <t>2026-02-16 00:26:20</t>
         </is>
       </c>
       <c r="B265" s="13" t="inlineStr">
@@ -49209,7 +49129,7 @@
     <row r="266">
       <c r="A266" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 14:48:44</t>
+          <t>2026-02-15 23:48:44</t>
         </is>
       </c>
       <c r="B266" s="13" t="inlineStr">
@@ -49271,7 +49191,7 @@
     <row r="267">
       <c r="A267" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 19:17:17</t>
+          <t>2026-02-15 04:17:17</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
@@ -49333,7 +49253,7 @@
     <row r="268">
       <c r="A268" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 18:53:01</t>
+          <t>2026-02-15 03:53:01</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
@@ -49395,7 +49315,7 @@
     <row r="269">
       <c r="A269" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 17:59:46</t>
+          <t>2026-02-15 02:59:46</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
@@ -49457,7 +49377,7 @@
     <row r="270">
       <c r="A270" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 17:26:42</t>
+          <t>2026-02-15 02:26:42</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
@@ -49519,7 +49439,7 @@
     <row r="271">
       <c r="A271" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 17:00:09</t>
+          <t>2026-02-15 02:00:09</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
@@ -49581,7 +49501,7 @@
     <row r="272">
       <c r="A272" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 16:39:16</t>
+          <t>2026-02-15 01:39:16</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
@@ -49643,7 +49563,7 @@
     <row r="273">
       <c r="A273" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 15:56:51</t>
+          <t>2026-02-15 00:56:51</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
@@ -49705,7 +49625,7 @@
     <row r="274">
       <c r="A274" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 14:52:26</t>
+          <t>2026-02-14 23:52:26</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
@@ -49767,7 +49687,7 @@
     <row r="275">
       <c r="A275" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 14:14:55</t>
+          <t>2026-02-14 23:14:55</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
@@ -49829,7 +49749,7 @@
     <row r="276">
       <c r="A276" s="13" t="inlineStr">
         <is>
-          <t>2026-02-13 19:19:58</t>
+          <t>2026-02-14 04:19:58</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
@@ -49891,7 +49811,7 @@
     <row r="277">
       <c r="A277" s="13" t="inlineStr">
         <is>
-          <t>2026-02-13 18:37:53</t>
+          <t>2026-02-14 03:37:53</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
@@ -49953,7 +49873,7 @@
     <row r="278">
       <c r="A278" s="13" t="inlineStr">
         <is>
-          <t>2026-02-13 18:03:31</t>
+          <t>2026-02-14 03:03:31</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
@@ -50015,7 +49935,7 @@
     <row r="279">
       <c r="A279" s="13" t="inlineStr">
         <is>
-          <t>2026-02-13 17:08:36</t>
+          <t>2026-02-14 02:08:36</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
@@ -50077,7 +49997,7 @@
     <row r="280">
       <c r="A280" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 15:20:03</t>
+          <t>2026-02-12 00:20:03</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
@@ -50139,7 +50059,7 @@
     <row r="281">
       <c r="A281" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 18:05:03</t>
+          <t>2026-02-11 03:05:03</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
@@ -50201,7 +50121,7 @@
     <row r="282">
       <c r="A282" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 17:14:02</t>
+          <t>2026-02-11 02:14:02</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
@@ -50263,7 +50183,7 @@
     <row r="283">
       <c r="A283" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 16:33:21</t>
+          <t>2026-02-11 01:33:21</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
@@ -50325,7 +50245,7 @@
     <row r="284">
       <c r="A284" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 16:01:41</t>
+          <t>2026-02-11 01:01:41</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
@@ -50387,7 +50307,7 @@
     <row r="285">
       <c r="A285" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 16:49:32</t>
+          <t>2026-02-10 01:49:32</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
@@ -50449,7 +50369,7 @@
     <row r="286">
       <c r="A286" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 16:42:29</t>
+          <t>2026-02-10 01:42:29</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
@@ -50511,7 +50431,7 @@
     <row r="287">
       <c r="A287" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 14:44:10</t>
+          <t>2026-02-09 23:44:10</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
@@ -50573,7 +50493,7 @@
     <row r="288">
       <c r="A288" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 14:00:28</t>
+          <t>2026-02-09 23:00:28</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
@@ -50635,7 +50555,7 @@
     <row r="289">
       <c r="A289" s="13" t="inlineStr">
         <is>
-          <t>2026-02-08 15:27:49</t>
+          <t>2026-02-09 00:27:49</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
@@ -50697,7 +50617,7 @@
     <row r="290">
       <c r="A290" s="13" t="inlineStr">
         <is>
-          <t>2026-02-08 15:16:42</t>
+          <t>2026-02-09 00:16:42</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
@@ -50759,7 +50679,7 @@
     <row r="291">
       <c r="A291" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 19:04:43</t>
+          <t>2026-02-08 04:04:43</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
@@ -50821,7 +50741,7 @@
     <row r="292">
       <c r="A292" s="13" t="inlineStr">
         <is>
-          <t>2026-02-06 18:13:11</t>
+          <t>2026-02-07 03:13:11</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
@@ -50883,7 +50803,7 @@
     <row r="293">
       <c r="A293" s="13" t="inlineStr">
         <is>
-          <t>2026-02-06 17:19:42</t>
+          <t>2026-02-07 02:19:42</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
@@ -50945,7 +50865,7 @@
     <row r="294">
       <c r="A294" s="13" t="inlineStr">
         <is>
-          <t>2026-02-06 16:37:36</t>
+          <t>2026-02-07 01:37:36</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
@@ -51007,7 +50927,7 @@
     <row r="295">
       <c r="A295" s="13" t="inlineStr">
         <is>
-          <t>2026-02-03 14:04:49</t>
+          <t>2026-02-03 23:04:49</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
@@ -51069,7 +50989,7 @@
     <row r="296">
       <c r="A296" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 14:21:38</t>
+          <t>2026-02-02 23:21:38</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
@@ -51131,7 +51051,7 @@
     <row r="297">
       <c r="A297" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 18:08:17</t>
+          <t>2026-02-02 03:08:17</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
@@ -51193,7 +51113,7 @@
     <row r="298">
       <c r="A298" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 17:41:55</t>
+          <t>2026-02-02 02:41:55</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
@@ -51255,7 +51175,7 @@
     <row r="299">
       <c r="A299" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 17:09:57</t>
+          <t>2026-02-02 02:09:57</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
@@ -51317,7 +51237,7 @@
     <row r="300">
       <c r="A300" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 16:41:49</t>
+          <t>2026-02-02 01:41:49</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
@@ -51379,7 +51299,7 @@
     <row r="301">
       <c r="A301" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 17:22:13</t>
+          <t>2026-02-01 02:22:13</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
@@ -51441,7 +51361,7 @@
     <row r="302">
       <c r="A302" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 16:20:54</t>
+          <t>2026-02-01 01:20:54</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
@@ -51503,7 +51423,7 @@
     <row r="303">
       <c r="A303" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 16:09:32</t>
+          <t>2026-02-01 01:09:32</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
@@ -51565,7 +51485,7 @@
     <row r="304">
       <c r="A304" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 15:29:37</t>
+          <t>2026-02-01 00:29:37</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
@@ -51627,7 +51547,7 @@
     <row r="305">
       <c r="A305" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 15:03:50</t>
+          <t>2026-02-01 00:03:50</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
@@ -51689,7 +51609,7 @@
     <row r="306">
       <c r="A306" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 14:15:28</t>
+          <t>2026-01-31 23:15:28</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
@@ -51751,7 +51671,7 @@
     <row r="307">
       <c r="A307" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 15:36:39</t>
+          <t>2026-01-29 00:36:39</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
@@ -51813,7 +51733,7 @@
     <row r="308">
       <c r="A308" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 15:02:45</t>
+          <t>2026-01-29 00:02:45</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
@@ -51875,7 +51795,7 @@
     <row r="309">
       <c r="A309" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 14:26:47</t>
+          <t>2026-01-28 23:26:47</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
@@ -51937,7 +51857,7 @@
     <row r="310">
       <c r="A310" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 14:04:33</t>
+          <t>2026-01-28 23:04:33</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
@@ -51999,7 +51919,7 @@
     <row r="311">
       <c r="A311" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 15:33:31</t>
+          <t>2026-01-28 00:33:31</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
@@ -52061,7 +51981,7 @@
     <row r="312">
       <c r="A312" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 14:59:21</t>
+          <t>2026-01-27 23:59:21</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
@@ -52123,7 +52043,7 @@
     <row r="313">
       <c r="A313" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 14:08:33</t>
+          <t>2026-01-27 23:08:33</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
@@ -52185,7 +52105,7 @@
     <row r="314">
       <c r="A314" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 14:28:17</t>
+          <t>2026-01-25 23:28:17</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
@@ -52247,7 +52167,7 @@
     <row r="315">
       <c r="A315" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 13:56:22</t>
+          <t>2026-01-25 22:56:22</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
@@ -52309,7 +52229,7 @@
     <row r="316">
       <c r="A316" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 13:28:25</t>
+          <t>2026-01-25 22:28:25</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
@@ -52371,7 +52291,7 @@
     <row r="317">
       <c r="A317" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 12:42:03</t>
+          <t>2026-01-25 21:42:03</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
@@ -52433,7 +52353,7 @@
     <row r="318">
       <c r="A318" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 10:38:23</t>
+          <t>2026-01-25 19:38:23</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
@@ -52495,7 +52415,7 @@
     <row r="319">
       <c r="A319" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 09:56:35</t>
+          <t>2026-01-25 18:56:35</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
@@ -52557,7 +52477,7 @@
     <row r="320">
       <c r="A320" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 09:29:19</t>
+          <t>2026-01-25 18:29:19</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
@@ -52619,7 +52539,7 @@
     <row r="321">
       <c r="A321" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 08:14:05</t>
+          <t>2026-01-25 17:14:05</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
@@ -52681,7 +52601,7 @@
     <row r="322">
       <c r="A322" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 17:47:24</t>
+          <t>2026-01-24 02:47:24</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
@@ -52743,7 +52663,7 @@
     <row r="323">
       <c r="A323" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 17:12:26</t>
+          <t>2026-01-24 02:12:26</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
@@ -52805,7 +52725,7 @@
     <row r="324">
       <c r="A324" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 16:33:34</t>
+          <t>2026-01-24 01:33:34</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
@@ -52867,7 +52787,7 @@
     <row r="325">
       <c r="A325" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 16:00:39</t>
+          <t>2026-01-24 01:00:39</t>
         </is>
       </c>
       <c r="B325" s="13" t="inlineStr">
@@ -52929,7 +52849,7 @@
     <row r="326">
       <c r="A326" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 15:19:07</t>
+          <t>2026-01-24 00:19:07</t>
         </is>
       </c>
       <c r="B326" s="13" t="inlineStr">
@@ -52991,7 +52911,7 @@
     <row r="327">
       <c r="A327" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 14:52:33</t>
+          <t>2026-01-23 23:52:33</t>
         </is>
       </c>
       <c r="B327" s="13" t="inlineStr">
@@ -53053,7 +52973,7 @@
     <row r="328">
       <c r="A328" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 14:19:19</t>
+          <t>2026-01-23 23:19:19</t>
         </is>
       </c>
       <c r="B328" s="13" t="inlineStr">
@@ -53115,7 +53035,7 @@
     <row r="329">
       <c r="A329" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 13:36:59</t>
+          <t>2026-01-23 22:36:59</t>
         </is>
       </c>
       <c r="B329" s="13" t="inlineStr">
@@ -53177,7 +53097,7 @@
     <row r="330">
       <c r="A330" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 18:01:58</t>
+          <t>2026-01-23 03:01:58</t>
         </is>
       </c>
       <c r="B330" s="13" t="inlineStr">
@@ -53239,7 +53159,7 @@
     <row r="331">
       <c r="A331" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 17:25:41</t>
+          <t>2026-01-23 02:25:41</t>
         </is>
       </c>
       <c r="B331" s="13" t="inlineStr">
@@ -53301,7 +53221,7 @@
     <row r="332">
       <c r="A332" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 15:32:45</t>
+          <t>2026-01-23 00:32:45</t>
         </is>
       </c>
       <c r="B332" s="13" t="inlineStr">
@@ -53363,7 +53283,7 @@
     <row r="333">
       <c r="A333" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 14:54:46</t>
+          <t>2026-01-22 23:54:46</t>
         </is>
       </c>
       <c r="B333" s="13" t="inlineStr">
@@ -53425,7 +53345,7 @@
     <row r="334">
       <c r="A334" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 14:17:42</t>
+          <t>2026-01-22 23:17:42</t>
         </is>
       </c>
       <c r="B334" s="13" t="inlineStr">
@@ -53487,7 +53407,7 @@
     <row r="335">
       <c r="A335" s="13" t="inlineStr">
         <is>
-          <t>2026-01-21 16:10:08</t>
+          <t>2026-01-22 01:10:08</t>
         </is>
       </c>
       <c r="B335" s="13" t="inlineStr">
@@ -53549,7 +53469,7 @@
     <row r="336">
       <c r="A336" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 15:27:51</t>
+          <t>2026-01-21 00:27:51</t>
         </is>
       </c>
       <c r="B336" s="13" t="inlineStr">
@@ -53611,7 +53531,7 @@
     <row r="337">
       <c r="A337" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 14:25:34</t>
+          <t>2026-01-20 23:25:34</t>
         </is>
       </c>
       <c r="B337" s="13" t="inlineStr">
@@ -53673,7 +53593,7 @@
     <row r="338">
       <c r="A338" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 13:56:13</t>
+          <t>2026-01-20 22:56:13</t>
         </is>
       </c>
       <c r="B338" s="13" t="inlineStr">
@@ -53735,7 +53655,7 @@
     <row r="339">
       <c r="A339" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 16:59:11</t>
+          <t>2026-01-19 01:59:11</t>
         </is>
       </c>
       <c r="B339" s="13" t="inlineStr">
@@ -53797,7 +53717,7 @@
     <row r="340">
       <c r="A340" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 18:05:32</t>
+          <t>2026-01-18 03:05:32</t>
         </is>
       </c>
       <c r="B340" s="13" t="inlineStr">
@@ -53859,7 +53779,7 @@
     <row r="341">
       <c r="A341" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 17:19:17</t>
+          <t>2026-01-18 02:19:17</t>
         </is>
       </c>
       <c r="B341" s="13" t="inlineStr">
@@ -53921,7 +53841,7 @@
     <row r="342">
       <c r="A342" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 16:58:17</t>
+          <t>2026-01-18 01:58:17</t>
         </is>
       </c>
       <c r="B342" s="13" t="inlineStr">
@@ -53983,7 +53903,7 @@
     <row r="343">
       <c r="A343" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 16:18:29</t>
+          <t>2026-01-18 01:18:29</t>
         </is>
       </c>
       <c r="B343" s="13" t="inlineStr">
@@ -54045,7 +53965,7 @@
     <row r="344">
       <c r="A344" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 15:38:58</t>
+          <t>2026-01-18 00:38:58</t>
         </is>
       </c>
       <c r="B344" s="13" t="inlineStr">
@@ -54107,7 +54027,7 @@
     <row r="345">
       <c r="A345" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 09:46:30</t>
+          <t>2026-01-17 18:46:30</t>
         </is>
       </c>
       <c r="B345" s="13" t="inlineStr">
@@ -54169,7 +54089,7 @@
     <row r="346">
       <c r="A346" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 17:21:36</t>
+          <t>2026-01-17 02:21:36</t>
         </is>
       </c>
       <c r="B346" s="13" t="inlineStr">
@@ -54231,7 +54151,7 @@
     <row r="347">
       <c r="A347" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 16:51:05</t>
+          <t>2026-01-17 01:51:05</t>
         </is>
       </c>
       <c r="B347" s="13" t="inlineStr">
@@ -54293,7 +54213,7 @@
     <row r="348">
       <c r="A348" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 16:18:22</t>
+          <t>2026-01-17 01:18:22</t>
         </is>
       </c>
       <c r="B348" s="13" t="inlineStr">
@@ -54355,7 +54275,7 @@
     <row r="349">
       <c r="A349" s="13" t="inlineStr">
         <is>
-          <t>2026-01-15 16:41:15</t>
+          <t>2026-01-16 01:41:15</t>
         </is>
       </c>
       <c r="B349" s="13" t="inlineStr">
@@ -54417,7 +54337,7 @@
     <row r="350">
       <c r="A350" s="13" t="inlineStr">
         <is>
-          <t>2026-01-15 16:05:38</t>
+          <t>2026-01-16 01:05:38</t>
         </is>
       </c>
       <c r="B350" s="13" t="inlineStr">
@@ -54479,7 +54399,7 @@
     <row r="351">
       <c r="A351" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 15:57:21</t>
+          <t>2026-01-14 00:57:21</t>
         </is>
       </c>
       <c r="B351" s="13" t="inlineStr">
@@ -54541,7 +54461,7 @@
     <row r="352">
       <c r="A352" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 15:19:49</t>
+          <t>2026-01-14 00:19:49</t>
         </is>
       </c>
       <c r="B352" s="13" t="inlineStr">
@@ -54603,7 +54523,7 @@
     <row r="353">
       <c r="A353" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 14:53:29</t>
+          <t>2026-01-13 23:53:29</t>
         </is>
       </c>
       <c r="B353" s="13" t="inlineStr">
@@ -54665,7 +54585,7 @@
     <row r="354">
       <c r="A354" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 17:23:29</t>
+          <t>2026-01-13 02:23:29</t>
         </is>
       </c>
       <c r="B354" s="13" t="inlineStr">
@@ -54727,7 +54647,7 @@
     <row r="355">
       <c r="A355" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 16:42:12</t>
+          <t>2026-01-13 01:42:12</t>
         </is>
       </c>
       <c r="B355" s="13" t="inlineStr">
@@ -54789,7 +54709,7 @@
     <row r="356">
       <c r="A356" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 16:17:01</t>
+          <t>2026-01-13 01:17:01</t>
         </is>
       </c>
       <c r="B356" s="13" t="inlineStr">
@@ -54851,7 +54771,7 @@
     <row r="357">
       <c r="A357" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 15:43:11</t>
+          <t>2026-01-13 00:43:11</t>
         </is>
       </c>
       <c r="B357" s="13" t="inlineStr">
@@ -54913,7 +54833,7 @@
     <row r="358">
       <c r="A358" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 08:24:44</t>
+          <t>2026-01-12 17:24:44</t>
         </is>
       </c>
       <c r="B358" s="13" t="inlineStr">
@@ -54975,7 +54895,7 @@
     <row r="359">
       <c r="A359" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 18:12:16</t>
+          <t>2026-01-12 03:12:16</t>
         </is>
       </c>
       <c r="B359" s="13" t="inlineStr">
@@ -55037,7 +54957,7 @@
     <row r="360">
       <c r="A360" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 17:54:03</t>
+          <t>2026-01-11 02:54:03</t>
         </is>
       </c>
       <c r="B360" s="13" t="inlineStr">
@@ -55099,7 +55019,7 @@
     <row r="361">
       <c r="A361" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 17:14:56</t>
+          <t>2026-01-11 02:14:56</t>
         </is>
       </c>
       <c r="B361" s="13" t="inlineStr">
@@ -55161,7 +55081,7 @@
     <row r="362">
       <c r="A362" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 16:17:21</t>
+          <t>2026-01-11 01:17:21</t>
         </is>
       </c>
       <c r="B362" s="13" t="inlineStr">
@@ -55223,7 +55143,7 @@
     <row r="363">
       <c r="A363" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 15:22:11</t>
+          <t>2026-01-11 00:22:11</t>
         </is>
       </c>
       <c r="B363" s="13" t="inlineStr">
@@ -55285,7 +55205,7 @@
     <row r="364">
       <c r="A364" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 14:38:24</t>
+          <t>2026-01-10 23:38:24</t>
         </is>
       </c>
       <c r="B364" s="13" t="inlineStr">
@@ -55347,7 +55267,7 @@
     <row r="365">
       <c r="A365" s="13" t="inlineStr">
         <is>
-          <t>2026-01-09 17:54:19</t>
+          <t>2026-01-10 02:54:19</t>
         </is>
       </c>
       <c r="B365" s="13" t="inlineStr">
@@ -55409,7 +55329,7 @@
     <row r="366">
       <c r="A366" s="13" t="inlineStr">
         <is>
-          <t>2026-01-09 17:00:16</t>
+          <t>2026-01-10 02:00:16</t>
         </is>
       </c>
       <c r="B366" s="13" t="inlineStr">
@@ -55471,7 +55391,7 @@
     <row r="367">
       <c r="A367" s="13" t="inlineStr">
         <is>
-          <t>2026-01-09 14:36:27</t>
+          <t>2026-01-09 23:36:27</t>
         </is>
       </c>
       <c r="B367" s="13" t="inlineStr">
@@ -55530,70 +55450,8 @@
         </is>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" s="13" t="inlineStr">
-        <is>
-          <t>2026-01-05 14:21:47</t>
-        </is>
-      </c>
-      <c r="B368" s="13" t="inlineStr">
-        <is>
-          <t>ランク</t>
-        </is>
-      </c>
-      <c r="C368" s="13" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D368" s="13" t="inlineStr">
-        <is>
-          <t>SUP</t>
-        </is>
-      </c>
-      <c r="E368" s="13" t="inlineStr">
-        <is>
-          <t>ジャンナ</t>
-        </is>
-      </c>
-      <c r="F368" s="13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G368" s="13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H368" s="13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I368" s="13" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J368" s="13" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K368" s="14" t="inlineStr"/>
-      <c r="L368" s="14" t="inlineStr"/>
-      <c r="M368" s="14" t="inlineStr"/>
-      <c r="N368" s="14" t="inlineStr"/>
-      <c r="O368" s="14" t="inlineStr"/>
-      <c r="P368" s="13" t="inlineStr">
-        <is>
-          <t>JP1_556572228</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P368"/>
+  <autoFilter ref="A1:P367"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-07-30 03:15:04</t>
+          <t>出力日時：2026-07-30 03:29:00</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'キュー別'!$A$1:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'チャンピオン別'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SUPチャンピオン別'!$A$1:$L$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$367</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$367</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$368</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$368</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,14 +532,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>対象期間：2026-01-09 23:36:27 ～ 2026-07-28 23:51:39</t>
+          <t>対象期間：2026-01-05 14:21:47 ～ 2026-07-28 14:51:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-07-30 03:29:00</t>
+          <t>出力日時：2026-07-30 10:04:01</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.4754098360655737</v>
+        <v>0.4741144414168937</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.674863387978142</v>
+        <v>1.670299727520436</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5.319672131147541</v>
+        <v>5.318801089918257</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>8.860655737704919</v>
+        <v>8.861035422343324</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>60.724043715847</v>
+        <v>60.65395095367847</v>
       </c>
     </row>
     <row r="15">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2.071912568306011</v>
+        <v>2.069427792915532</v>
       </c>
     </row>
     <row r="16">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>56.03825136612022</v>
+        <v>56.00817438692098</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1.807650273224044</v>
+        <v>1.806811989100817</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.5070422535211268</v>
+        <v>0.5052631578947369</v>
       </c>
     </row>
     <row r="24">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>1.443661971830986</v>
+        <v>1.43859649122807</v>
       </c>
     </row>
     <row r="25">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.140845070422535</v>
+        <v>5.140350877192983</v>
       </c>
     </row>
     <row r="26">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>9.77112676056338</v>
+        <v>9.768421052631579</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>36.13732394366197</v>
+        <v>36.13333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1.249964788732394</v>
+        <v>1.249649122807018</v>
       </c>
     </row>
     <row r="30">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>63.50704225352113</v>
+        <v>63.44210526315789</v>
       </c>
     </row>
     <row r="31">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>2.047147887323943</v>
+        <v>2.045228070175438</v>
       </c>
     </row>
   </sheetData>
@@ -820,7 +820,7 @@
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>144</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.5070422535211268</v>
+        <v>0.5052631578947369</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.443661971830986</v>
+        <v>1.43859649122807</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5.140845070422535</v>
+        <v>5.140350877192983</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9.77112676056338</v>
+        <v>9.768421052631579</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.249964788732394</v>
+        <v>1.249649122807018</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>63.50704225352113</v>
+        <v>63.44210526315789</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>2.047147887323943</v>
+        <v>2.045228070175438</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.933833333333333</v>
+        <v>4.933833333333332</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>31.96666666666667</v>
@@ -1133,7 +1133,7 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1239,7 +1239,7 @@
         <v>52.89225589225589</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>1.716734006734007</v>
+        <v>1.716734006734006</v>
       </c>
     </row>
     <row r="3">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>30</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.130434782608696</v>
+        <v>1.114285714285714</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>5.782608695652174</v>
+        <v>5.771428571428571</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>9.913043478260869</v>
+        <v>9.9</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.24231884057971</v>
+        <v>1.241142857142857</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>69.57971014492753</v>
+        <v>69.22857142857143</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.198985507246377</v>
+        <v>2.189000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.801860465116279</v>
+        <v>1.80186046511628</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>68.76744186046511</v>
@@ -1516,25 +1516,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.775</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.153846153846154</v>
+        <v>5.15</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.17948717948718</v>
+        <v>7.225</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.232820512820513</v>
+        <v>1.231</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.97435897435897</v>
+        <v>53.75</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.871025641025641</v>
+        <v>1.86175</v>
       </c>
     </row>
     <row r="6">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5.148285714285715</v>
+        <v>5.148285714285714</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>34.6</v>
@@ -1758,7 +1758,7 @@
         <v>25.625</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.85625</v>
+        <v>0.8562500000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>21.83333333333333</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.8633333333333333</v>
+        <v>0.8633333333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5.050000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>16.25</v>
@@ -2833,25 +2833,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.775</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.153846153846154</v>
+        <v>5.15</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.17948717948718</v>
+        <v>7.225</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.232820512820513</v>
+        <v>1.231</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.97435897435897</v>
+        <v>53.75</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.871025641025641</v>
+        <v>1.86175</v>
       </c>
     </row>
     <row r="6">
@@ -3224,7 +3224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V367"/>
+  <dimension ref="A1:V368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3366,7 +3366,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 23:51:39</t>
+          <t>2026-07-28 14:51:39</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 23:05:20</t>
+          <t>2026-07-28 14:05:20</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27 01:21:51</t>
+          <t>2026-07-26 16:21:51</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27 00:43:02</t>
+          <t>2026-07-26 15:43:02</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 23:12:09</t>
+          <t>2026-07-25 14:12:09</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 22:30:57</t>
+          <t>2026-07-25 13:30:57</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 00:11:55</t>
+          <t>2026-07-24 15:11:55</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24 23:25:38</t>
+          <t>2026-07-24 14:25:38</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22 00:17:56</t>
+          <t>2026-07-21 15:17:56</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22 00:04:35</t>
+          <t>2026-07-21 15:04:35</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -4166,7 +4166,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 23:25:56</t>
+          <t>2026-07-21 14:25:56</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 22:44:36</t>
+          <t>2026-07-21 13:44:36</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -4326,7 +4326,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 22:18:59</t>
+          <t>2026-07-21 13:18:59</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20 03:20:20</t>
+          <t>2026-07-19 18:20:20</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -4486,7 +4486,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20 02:39:51</t>
+          <t>2026-07-19 17:39:51</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -4566,7 +4566,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:59:14</t>
+          <t>2026-07-18 09:59:14</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -4646,7 +4646,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:21:14</t>
+          <t>2026-07-18 09:21:14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 23:06:28</t>
+          <t>2026-07-16 14:06:28</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 22:32:42</t>
+          <t>2026-07-16 13:32:42</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -4886,7 +4886,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 00:40:48</t>
+          <t>2026-07-15 15:40:48</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -4966,7 +4966,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 23:41:56</t>
+          <t>2026-07-15 14:41:56</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 22:58:44</t>
+          <t>2026-07-15 13:58:44</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -5126,7 +5126,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 22:34:16</t>
+          <t>2026-07-15 13:34:16</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 23:36:35</t>
+          <t>2026-07-14 14:36:35</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -5286,7 +5286,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 22:49:50</t>
+          <t>2026-07-14 13:49:50</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -5366,7 +5366,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 01:02:29</t>
+          <t>2026-07-13 16:02:29</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 00:22:46</t>
+          <t>2026-07-13 15:22:46</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -5526,7 +5526,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 23:51:38</t>
+          <t>2026-07-13 14:51:38</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -5606,7 +5606,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 02:05:19</t>
+          <t>2026-07-12 17:05:19</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 01:29:17</t>
+          <t>2026-07-12 16:29:17</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -5766,7 +5766,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 03:11:38</t>
+          <t>2026-07-11 18:11:38</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -5846,7 +5846,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 02:46:15</t>
+          <t>2026-07-11 17:46:15</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -5926,7 +5926,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 03:42:29</t>
+          <t>2026-07-10 18:42:29</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -6006,7 +6006,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 03:06:21</t>
+          <t>2026-07-10 18:06:21</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:55:25</t>
+          <t>2026-07-08 17:55:25</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:17:09</t>
+          <t>2026-07-08 17:17:09</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 02:03:51</t>
+          <t>2026-07-05 17:03:51</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -6326,7 +6326,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 01:07:17</t>
+          <t>2026-07-05 16:07:17</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -6406,7 +6406,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 00:23:00</t>
+          <t>2026-07-05 15:23:00</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -6486,7 +6486,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05 03:21:23</t>
+          <t>2026-07-04 18:21:23</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -6566,7 +6566,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-07-04 03:01:40</t>
+          <t>2026-07-03 18:01:40</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -6646,7 +6646,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03 01:48:19</t>
+          <t>2026-07-02 16:48:19</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -6726,7 +6726,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01 00:21:19</t>
+          <t>2026-06-30 15:21:19</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -6806,7 +6806,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 23:38:16</t>
+          <t>2026-06-30 14:38:16</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -6886,7 +6886,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 01:16:28</t>
+          <t>2026-06-29 16:16:28</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -6966,7 +6966,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 00:34:32</t>
+          <t>2026-06-29 15:34:32</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26 00:50:56</t>
+          <t>2026-06-25 15:50:56</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -7126,7 +7126,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26 00:06:40</t>
+          <t>2026-06-25 15:06:40</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07:56</t>
+          <t>2026-06-24 17:07:56</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -7286,7 +7286,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 01:33:19</t>
+          <t>2026-06-24 16:33:19</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -7366,7 +7366,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:47:59</t>
+          <t>2026-06-24 15:47:59</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -7446,7 +7446,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:08:31</t>
+          <t>2026-06-24 15:08:31</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -7526,7 +7526,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 23:33:15</t>
+          <t>2026-06-24 14:33:15</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 22:39:11</t>
+          <t>2026-06-24 13:39:11</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -7686,7 +7686,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 01:16:06</t>
+          <t>2026-06-22 16:16:06</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -7766,7 +7766,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 00:38:08</t>
+          <t>2026-06-22 15:38:08</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -7846,7 +7846,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 00:29:33</t>
+          <t>2026-06-22 15:29:33</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -7926,7 +7926,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 01:54:04</t>
+          <t>2026-06-18 16:54:04</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -8006,7 +8006,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 01:14:50</t>
+          <t>2026-06-18 16:14:50</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -8086,7 +8086,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 00:35:17</t>
+          <t>2026-06-18 15:35:17</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 23:55:50</t>
+          <t>2026-06-18 14:55:50</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -8246,7 +8246,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 00:44:42</t>
+          <t>2026-06-17 15:44:42</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -8326,7 +8326,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 23:57:38</t>
+          <t>2026-06-17 14:57:38</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -8406,7 +8406,7 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 01:58:55</t>
+          <t>2026-06-16 16:58:55</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -8486,7 +8486,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 01:30:07</t>
+          <t>2026-06-16 16:30:07</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -8566,7 +8566,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 03:10:28</t>
+          <t>2026-06-14 18:10:28</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 02:27:52</t>
+          <t>2026-06-14 17:27:52</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 01:57:23</t>
+          <t>2026-06-14 16:57:23</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -8806,7 +8806,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 01:27:22</t>
+          <t>2026-06-14 16:27:22</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -8886,7 +8886,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 00:24:35</t>
+          <t>2026-06-14 15:24:35</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -8966,7 +8966,7 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 23:46:55</t>
+          <t>2026-06-14 14:46:55</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -9046,7 +9046,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 01:41:53</t>
+          <t>2026-06-13 16:41:53</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -9126,7 +9126,7 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 00:52:58</t>
+          <t>2026-06-13 15:52:58</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -9206,7 +9206,7 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 00:14:23</t>
+          <t>2026-06-13 15:14:23</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
@@ -9286,7 +9286,7 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 23:45:21</t>
+          <t>2026-06-13 14:45:21</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -9366,7 +9366,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 23:05:32</t>
+          <t>2026-06-13 14:05:32</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -9446,7 +9446,7 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 01:08:14</t>
+          <t>2026-06-10 16:08:14</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -9526,7 +9526,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:34:35</t>
+          <t>2026-06-10 15:34:35</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -9606,7 +9606,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:09:17</t>
+          <t>2026-06-10 15:09:17</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -9686,7 +9686,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 23:27:53</t>
+          <t>2026-06-10 14:27:53</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -9766,7 +9766,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 00:49:00</t>
+          <t>2026-06-09 15:49:00</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -9846,7 +9846,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06 02:58:51</t>
+          <t>2026-06-05 17:58:51</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -9926,7 +9926,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06 02:15:04</t>
+          <t>2026-06-05 17:15:04</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -10006,7 +10006,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 23:49:14</t>
+          <t>2026-06-04 14:49:14</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -10086,7 +10086,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 21:40:04</t>
+          <t>2026-06-04 12:40:04</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -10166,7 +10166,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 21:17:24</t>
+          <t>2026-06-04 12:17:24</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 01:06:27</t>
+          <t>2026-06-03 16:06:27</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -10326,7 +10326,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 00:31:09</t>
+          <t>2026-06-03 15:31:09</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 23:53:57</t>
+          <t>2026-06-03 14:53:57</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -10486,7 +10486,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 22:44:02</t>
+          <t>2026-06-03 13:44:02</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -10566,7 +10566,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02 22:49:11</t>
+          <t>2026-06-02 13:49:11</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -10646,7 +10646,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:56:06</t>
+          <t>2026-06-01 14:56:06</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -10726,7 +10726,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:20:26</t>
+          <t>2026-06-01 14:20:26</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -10806,7 +10806,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:01:06</t>
+          <t>2026-06-01 14:01:06</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -10886,7 +10886,7 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31 03:01:04</t>
+          <t>2026-05-30 18:01:04</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -10966,7 +10966,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31 02:13:41</t>
+          <t>2026-05-30 17:13:41</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -11046,7 +11046,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 23:00:40</t>
+          <t>2026-05-25 14:00:40</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -11126,7 +11126,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 01:55:47</t>
+          <t>2026-05-24 16:55:47</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 01:24:22</t>
+          <t>2026-05-24 16:24:22</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -11286,7 +11286,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 23:49:25</t>
+          <t>2026-05-24 14:49:25</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -11366,7 +11366,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 03:13:39</t>
+          <t>2026-05-23 18:13:39</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -11446,7 +11446,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 02:41:52</t>
+          <t>2026-05-23 17:41:52</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -11526,7 +11526,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 23:19:04</t>
+          <t>2026-05-23 14:19:04</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 22:43:20</t>
+          <t>2026-05-23 13:43:20</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -11686,7 +11686,7 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 15:54:19</t>
+          <t>2026-05-23 06:54:19</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -11766,7 +11766,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 02:25:24</t>
+          <t>2026-05-22 17:25:24</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -11846,7 +11846,7 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 01:29:23</t>
+          <t>2026-05-21 16:29:23</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -11926,7 +11926,7 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 00:48:49</t>
+          <t>2026-05-21 15:48:49</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -12006,7 +12006,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:45</t>
+          <t>2026-05-21 15:00:45</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 23:22:44</t>
+          <t>2026-05-21 14:22:44</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -12166,7 +12166,7 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 00:05:15</t>
+          <t>2026-05-20 15:05:15</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -12246,7 +12246,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 23:43:50</t>
+          <t>2026-05-20 14:43:50</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -12326,7 +12326,7 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 22:57:45</t>
+          <t>2026-05-20 13:57:45</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -12406,7 +12406,7 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 01:25:45</t>
+          <t>2026-05-19 16:25:45</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -12486,7 +12486,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 00:46:42</t>
+          <t>2026-05-19 15:46:42</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -12566,7 +12566,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>2026-05-18 22:56:39</t>
+          <t>2026-05-18 13:56:39</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -12646,7 +12646,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 01:35:56</t>
+          <t>2026-05-14 16:35:56</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -12726,7 +12726,7 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 01:17:05</t>
+          <t>2026-05-14 16:17:05</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -12806,7 +12806,7 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 00:05:48</t>
+          <t>2026-05-14 15:05:48</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -12886,7 +12886,7 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14 01:25:38</t>
+          <t>2026-05-13 16:25:38</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -12966,7 +12966,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>2026-05-12 00:19:57</t>
+          <t>2026-05-11 15:19:57</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -13046,7 +13046,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 23:54:15</t>
+          <t>2026-05-11 14:54:15</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -13126,7 +13126,7 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 23:14:30</t>
+          <t>2026-05-11 14:14:30</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -13206,7 +13206,7 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 22:37:05</t>
+          <t>2026-05-11 13:37:05</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -13286,7 +13286,7 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 21:53:13</t>
+          <t>2026-05-11 12:53:13</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -13366,7 +13366,7 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 00:04:01</t>
+          <t>2026-05-10 15:04:01</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -13446,7 +13446,7 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:54:24</t>
+          <t>2026-05-09 16:54:24</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -13526,7 +13526,7 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:22:50</t>
+          <t>2026-05-09 16:22:50</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -13606,7 +13606,7 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 00:26:16</t>
+          <t>2026-05-09 15:26:16</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -13686,7 +13686,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 23:38:30</t>
+          <t>2026-05-09 14:38:30</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 22:50:20</t>
+          <t>2026-05-09 13:50:20</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -13846,7 +13846,7 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 22:13:25</t>
+          <t>2026-05-09 13:13:25</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -13926,7 +13926,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 20:00:11</t>
+          <t>2026-05-09 11:00:11</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -14006,7 +14006,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 19:10:28</t>
+          <t>2026-05-09 10:10:28</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -14086,7 +14086,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 02:17:27</t>
+          <t>2026-05-08 17:17:27</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -14166,7 +14166,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 01:38:25</t>
+          <t>2026-05-08 16:38:25</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -14246,7 +14246,7 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 00:58:58</t>
+          <t>2026-05-08 15:58:58</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -14326,7 +14326,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 00:37:55</t>
+          <t>2026-05-08 15:37:55</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -14406,7 +14406,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 01:48:31</t>
+          <t>2026-05-07 16:48:31</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -14486,7 +14486,7 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 01:02:52</t>
+          <t>2026-05-07 16:02:52</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -14566,7 +14566,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 00:23:29</t>
+          <t>2026-05-07 15:23:29</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -14646,7 +14646,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 01:30:56</t>
+          <t>2026-05-06 16:30:56</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -14726,7 +14726,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 00:42:16</t>
+          <t>2026-05-06 15:42:16</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -14806,7 +14806,7 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 23:44:04</t>
+          <t>2026-05-06 14:44:04</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -14886,7 +14886,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:13:52</t>
+          <t>2026-05-06 09:13:52</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -14966,7 +14966,7 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:05:08</t>
+          <t>2026-05-06 09:05:08</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -15046,7 +15046,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 17:22:30</t>
+          <t>2026-05-06 08:22:30</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -15126,7 +15126,7 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 16:28:42</t>
+          <t>2026-05-06 07:28:42</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -15206,7 +15206,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 03:16:57</t>
+          <t>2026-05-05 18:16:57</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -15286,7 +15286,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:32:40</t>
+          <t>2026-05-05 17:32:40</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -15366,7 +15366,7 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:23:28</t>
+          <t>2026-05-05 17:23:28</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 01:48:28</t>
+          <t>2026-05-05 16:48:28</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -15526,7 +15526,7 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 00:52:33</t>
+          <t>2026-05-05 15:52:33</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -15606,7 +15606,7 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 17:43:06</t>
+          <t>2026-05-05 08:43:06</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -15686,7 +15686,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>2026-05-03 00:36:42</t>
+          <t>2026-05-02 15:36:42</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -15766,7 +15766,7 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 23:51:09</t>
+          <t>2026-05-02 14:51:09</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -15846,7 +15846,7 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 22:15:10</t>
+          <t>2026-05-02 13:15:10</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -15926,7 +15926,7 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 21:29:49</t>
+          <t>2026-05-02 12:29:49</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 01:39:42</t>
+          <t>2026-04-30 16:39:42</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -16086,7 +16086,7 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 01:01:34</t>
+          <t>2026-04-30 16:01:34</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -16166,7 +16166,7 @@
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 00:24:48</t>
+          <t>2026-04-30 15:24:48</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -16246,7 +16246,7 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 23:37:10</t>
+          <t>2026-04-30 14:37:10</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -16326,7 +16326,7 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 22:58:06</t>
+          <t>2026-04-30 13:58:06</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -16406,7 +16406,7 @@
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 03:29:33</t>
+          <t>2026-04-29 18:29:33</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -16486,7 +16486,7 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 02:54:07</t>
+          <t>2026-04-29 17:54:07</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -16566,7 +16566,7 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 02:20:58</t>
+          <t>2026-04-29 17:20:58</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -16646,7 +16646,7 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 01:42:01</t>
+          <t>2026-04-29 16:42:01</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -16726,7 +16726,7 @@
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 01:03:17</t>
+          <t>2026-04-29 16:03:17</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -16806,7 +16806,7 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 00:19:47</t>
+          <t>2026-04-29 15:19:47</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -16886,7 +16886,7 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 23:29:53</t>
+          <t>2026-04-29 14:29:53</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
@@ -16966,7 +16966,7 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:59:49</t>
+          <t>2026-04-29 13:59:49</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -17046,7 +17046,7 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:38:22</t>
+          <t>2026-04-29 13:38:22</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:44</t>
+          <t>2026-04-29 13:17:44</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
@@ -17206,7 +17206,7 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 03:28:56</t>
+          <t>2026-04-28 18:28:56</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -17286,7 +17286,7 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:58:50</t>
+          <t>2026-04-28 17:58:50</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
@@ -17366,7 +17366,7 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:29:43</t>
+          <t>2026-04-28 17:29:43</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -17446,7 +17446,7 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 01:38:43</t>
+          <t>2026-04-28 16:38:43</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -17526,7 +17526,7 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:54</t>
+          <t>2026-04-28 15:58:54</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
@@ -17606,7 +17606,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:31:32</t>
+          <t>2026-04-28 15:31:32</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -17686,7 +17686,7 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:04:20</t>
+          <t>2026-04-28 15:04:20</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
@@ -17766,7 +17766,7 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 23:37:27</t>
+          <t>2026-04-28 14:37:27</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
@@ -17846,7 +17846,7 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 23:09:10</t>
+          <t>2026-04-28 14:09:10</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
@@ -17926,7 +17926,7 @@
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:59:25</t>
+          <t>2026-04-27 14:59:25</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
@@ -18006,7 +18006,7 @@
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:49:35</t>
+          <t>2026-04-27 14:49:35</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
@@ -18086,7 +18086,7 @@
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 22:55:34</t>
+          <t>2026-04-27 13:55:34</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
@@ -18166,7 +18166,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 22:04:13</t>
+          <t>2026-04-27 13:04:13</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
@@ -18246,7 +18246,7 @@
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 02:49:02</t>
+          <t>2026-04-24 17:49:02</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
@@ -18326,7 +18326,7 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 02:03:56</t>
+          <t>2026-04-24 17:03:56</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
@@ -18406,7 +18406,7 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 01:37:00</t>
+          <t>2026-04-24 16:37:00</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
@@ -18486,7 +18486,7 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:33:59</t>
+          <t>2026-04-23 15:33:59</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
@@ -18566,7 +18566,7 @@
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:22:46</t>
+          <t>2026-04-23 15:22:46</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -18646,7 +18646,7 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:12:54</t>
+          <t>2026-04-23 15:12:54</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
@@ -18726,7 +18726,7 @@
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 22:36:03</t>
+          <t>2026-04-23 13:36:03</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:58:57</t>
+          <t>2026-04-13 15:58:57</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
@@ -18886,7 +18886,7 @@
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:09:08</t>
+          <t>2026-04-13 15:09:08</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -18966,7 +18966,7 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 01:48:02</t>
+          <t>2026-04-12 16:48:02</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
@@ -19046,7 +19046,7 @@
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 01:17:58</t>
+          <t>2026-04-12 16:17:58</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -19126,7 +19126,7 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 00:41:20</t>
+          <t>2026-04-12 15:41:20</t>
         </is>
       </c>
       <c r="B199" s="7" t="inlineStr">
@@ -19206,7 +19206,7 @@
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 23:18:06</t>
+          <t>2026-04-09 14:18:06</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -19286,7 +19286,7 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 22:52:44</t>
+          <t>2026-04-09 13:52:44</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
@@ -19366,7 +19366,7 @@
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 22:27:45</t>
+          <t>2026-04-09 13:27:45</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -19446,7 +19446,7 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>2026-04-08 01:10:31</t>
+          <t>2026-04-07 16:10:31</t>
         </is>
       </c>
       <c r="B203" s="7" t="inlineStr">
@@ -19526,7 +19526,7 @@
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>2026-04-08 00:29:19</t>
+          <t>2026-04-07 15:29:19</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
@@ -19606,7 +19606,7 @@
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>2026-04-04 04:36:31</t>
+          <t>2026-04-03 19:36:31</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
@@ -19686,7 +19686,7 @@
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>2026-04-04 04:16:32</t>
+          <t>2026-04-03 19:16:32</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
@@ -19766,7 +19766,7 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 04:24:43</t>
+          <t>2026-03-27 19:24:43</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
@@ -19846,7 +19846,7 @@
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 03:38:31</t>
+          <t>2026-03-27 18:38:31</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -19926,7 +19926,7 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 03:17:50</t>
+          <t>2026-03-27 18:17:50</t>
         </is>
       </c>
       <c r="B209" s="7" t="inlineStr">
@@ -20006,7 +20006,7 @@
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 02:43:19</t>
+          <t>2026-03-27 17:43:19</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -20086,7 +20086,7 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 02:15:18</t>
+          <t>2026-03-27 17:15:18</t>
         </is>
       </c>
       <c r="B211" s="7" t="inlineStr">
@@ -20166,7 +20166,7 @@
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 23:18:12</t>
+          <t>2026-03-25 14:18:12</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
@@ -20246,7 +20246,7 @@
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 00:01:49</t>
+          <t>2026-03-24 15:01:49</t>
         </is>
       </c>
       <c r="B213" s="7" t="inlineStr">
@@ -20326,7 +20326,7 @@
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 23:25:16</t>
+          <t>2026-03-24 14:25:16</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
@@ -20406,7 +20406,7 @@
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 23:02:52</t>
+          <t>2026-03-24 14:02:52</t>
         </is>
       </c>
       <c r="B215" s="7" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 22:26:26</t>
+          <t>2026-03-24 13:26:26</t>
         </is>
       </c>
       <c r="B216" s="7" t="inlineStr">
@@ -20566,7 +20566,7 @@
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 00:56:18</t>
+          <t>2026-03-23 15:56:18</t>
         </is>
       </c>
       <c r="B217" s="7" t="inlineStr">
@@ -20646,7 +20646,7 @@
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 00:29:29</t>
+          <t>2026-03-23 15:29:29</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
@@ -20726,7 +20726,7 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 23:51:11</t>
+          <t>2026-03-22 14:51:11</t>
         </is>
       </c>
       <c r="B219" s="7" t="inlineStr">
@@ -20806,7 +20806,7 @@
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 01:04:36</t>
+          <t>2026-03-21 16:04:36</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
@@ -20886,7 +20886,7 @@
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>2026-03-21 02:55:49</t>
+          <t>2026-03-20 17:55:49</t>
         </is>
       </c>
       <c r="B221" s="7" t="inlineStr">
@@ -20966,7 +20966,7 @@
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>2026-03-18 00:07:07</t>
+          <t>2026-03-17 15:07:07</t>
         </is>
       </c>
       <c r="B222" s="7" t="inlineStr">
@@ -21046,7 +21046,7 @@
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 23:24:05</t>
+          <t>2026-03-17 14:24:05</t>
         </is>
       </c>
       <c r="B223" s="7" t="inlineStr">
@@ -21126,7 +21126,7 @@
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 02:00:50</t>
+          <t>2026-03-16 17:00:50</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -21206,7 +21206,7 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 01:33:08</t>
+          <t>2026-03-16 16:33:08</t>
         </is>
       </c>
       <c r="B225" s="7" t="inlineStr">
@@ -21286,7 +21286,7 @@
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 23:28:09</t>
+          <t>2026-03-16 14:28:09</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
@@ -21366,7 +21366,7 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 01:32:22</t>
+          <t>2026-03-15 16:32:22</t>
         </is>
       </c>
       <c r="B227" s="7" t="inlineStr">
@@ -21446,7 +21446,7 @@
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14 01:43:49</t>
+          <t>2026-03-13 16:43:49</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
@@ -21526,7 +21526,7 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14 01:19:35</t>
+          <t>2026-03-13 16:19:35</t>
         </is>
       </c>
       <c r="B229" s="7" t="inlineStr">
@@ -21606,7 +21606,7 @@
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 23:45:27</t>
+          <t>2026-03-12 14:45:27</t>
         </is>
       </c>
       <c r="B230" s="7" t="inlineStr">
@@ -21686,7 +21686,7 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 23:02:09</t>
+          <t>2026-03-12 14:02:09</t>
         </is>
       </c>
       <c r="B231" s="7" t="inlineStr">
@@ -21766,7 +21766,7 @@
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 22:42:59</t>
+          <t>2026-03-12 13:42:59</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
@@ -21846,7 +21846,7 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 01:39:10</t>
+          <t>2026-03-11 16:39:10</t>
         </is>
       </c>
       <c r="B233" s="7" t="inlineStr">
@@ -21926,7 +21926,7 @@
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:43:21</t>
+          <t>2026-03-11 15:43:21</t>
         </is>
       </c>
       <c r="B234" s="7" t="inlineStr">
@@ -22006,7 +22006,7 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:04:25</t>
+          <t>2026-03-11 15:04:25</t>
         </is>
       </c>
       <c r="B235" s="7" t="inlineStr">
@@ -22086,7 +22086,7 @@
     <row r="236">
       <c r="A236" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 22:54:02</t>
+          <t>2026-03-11 13:54:02</t>
         </is>
       </c>
       <c r="B236" s="7" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>2026-03-08 02:01:53</t>
+          <t>2026-03-07 17:01:53</t>
         </is>
       </c>
       <c r="B237" s="7" t="inlineStr">
@@ -22246,7 +22246,7 @@
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>2026-03-02 02:18:59</t>
+          <t>2026-03-01 17:18:59</t>
         </is>
       </c>
       <c r="B238" s="7" t="inlineStr">
@@ -22326,7 +22326,7 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>2026-02-24 01:40:38</t>
+          <t>2026-02-23 16:40:38</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
@@ -22406,7 +22406,7 @@
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>2026-02-24 00:10:31</t>
+          <t>2026-02-23 15:10:31</t>
         </is>
       </c>
       <c r="B240" s="7" t="inlineStr">
@@ -22486,7 +22486,7 @@
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 23:33:47</t>
+          <t>2026-02-23 14:33:47</t>
         </is>
       </c>
       <c r="B241" s="7" t="inlineStr">
@@ -22566,7 +22566,7 @@
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 22:40:54</t>
+          <t>2026-02-23 13:40:54</t>
         </is>
       </c>
       <c r="B242" s="7" t="inlineStr">
@@ -22646,7 +22646,7 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 21:58:56</t>
+          <t>2026-02-23 12:58:56</t>
         </is>
       </c>
       <c r="B243" s="7" t="inlineStr">
@@ -22726,7 +22726,7 @@
     <row r="244">
       <c r="A244" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 19:21:48</t>
+          <t>2026-02-23 10:21:48</t>
         </is>
       </c>
       <c r="B244" s="7" t="inlineStr">
@@ -22806,7 +22806,7 @@
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 17:17:13</t>
+          <t>2026-02-23 08:17:13</t>
         </is>
       </c>
       <c r="B245" s="7" t="inlineStr">
@@ -22886,7 +22886,7 @@
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 04:22:01</t>
+          <t>2026-02-22 19:22:01</t>
         </is>
       </c>
       <c r="B246" s="7" t="inlineStr">
@@ -22966,7 +22966,7 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 03:23:51</t>
+          <t>2026-02-22 18:23:51</t>
         </is>
       </c>
       <c r="B247" s="7" t="inlineStr">
@@ -23046,7 +23046,7 @@
     <row r="248">
       <c r="A248" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 02:58:18</t>
+          <t>2026-02-22 17:58:18</t>
         </is>
       </c>
       <c r="B248" s="7" t="inlineStr">
@@ -23126,7 +23126,7 @@
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 02:29:21</t>
+          <t>2026-02-22 17:29:21</t>
         </is>
       </c>
       <c r="B249" s="7" t="inlineStr">
@@ -23206,7 +23206,7 @@
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 01:59:09</t>
+          <t>2026-02-22 16:59:09</t>
         </is>
       </c>
       <c r="B250" s="7" t="inlineStr">
@@ -23286,7 +23286,7 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 01:32:08</t>
+          <t>2026-02-22 16:32:08</t>
         </is>
       </c>
       <c r="B251" s="7" t="inlineStr">
@@ -23366,7 +23366,7 @@
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 03:34:36</t>
+          <t>2026-02-20 18:34:36</t>
         </is>
       </c>
       <c r="B252" s="7" t="inlineStr">
@@ -23446,7 +23446,7 @@
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 02:57:13</t>
+          <t>2026-02-20 17:57:13</t>
         </is>
       </c>
       <c r="B253" s="7" t="inlineStr">
@@ -23526,7 +23526,7 @@
     <row r="254">
       <c r="A254" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 02:19:01</t>
+          <t>2026-02-20 17:19:01</t>
         </is>
       </c>
       <c r="B254" s="7" t="inlineStr">
@@ -23606,7 +23606,7 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 01:41:10</t>
+          <t>2026-02-20 16:41:10</t>
         </is>
       </c>
       <c r="B255" s="7" t="inlineStr">
@@ -23686,7 +23686,7 @@
     <row r="256">
       <c r="A256" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:57:47</t>
+          <t>2026-02-20 15:57:47</t>
         </is>
       </c>
       <c r="B256" s="7" t="inlineStr">
@@ -23766,7 +23766,7 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:39:52</t>
+          <t>2026-02-20 15:39:52</t>
         </is>
       </c>
       <c r="B257" s="7" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="258">
       <c r="A258" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 01:21:13</t>
+          <t>2026-02-19 16:21:13</t>
         </is>
       </c>
       <c r="B258" s="7" t="inlineStr">
@@ -23926,7 +23926,7 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 00:33:10</t>
+          <t>2026-02-19 15:33:10</t>
         </is>
       </c>
       <c r="B259" s="7" t="inlineStr">
@@ -24006,7 +24006,7 @@
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>2026-02-18 00:37:38</t>
+          <t>2026-02-17 15:37:38</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
@@ -24086,7 +24086,7 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>2026-02-17 23:58:39</t>
+          <t>2026-02-17 14:58:39</t>
         </is>
       </c>
       <c r="B261" s="7" t="inlineStr">
@@ -24166,7 +24166,7 @@
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 02:24:16</t>
+          <t>2026-02-15 17:24:16</t>
         </is>
       </c>
       <c r="B262" s="7" t="inlineStr">
@@ -24246,7 +24246,7 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 01:47:19</t>
+          <t>2026-02-15 16:47:19</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
@@ -24326,7 +24326,7 @@
     <row r="264">
       <c r="A264" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 00:56:43</t>
+          <t>2026-02-15 15:56:43</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -24406,7 +24406,7 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 00:26:20</t>
+          <t>2026-02-15 15:26:20</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
@@ -24486,7 +24486,7 @@
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 23:48:44</t>
+          <t>2026-02-15 14:48:44</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -24566,7 +24566,7 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 04:17:17</t>
+          <t>2026-02-14 19:17:17</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -24646,7 +24646,7 @@
     <row r="268">
       <c r="A268" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 03:53:01</t>
+          <t>2026-02-14 18:53:01</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
@@ -24726,7 +24726,7 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:59:46</t>
+          <t>2026-02-14 17:59:46</t>
         </is>
       </c>
       <c r="B269" s="7" t="inlineStr">
@@ -24806,7 +24806,7 @@
     <row r="270">
       <c r="A270" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:26:42</t>
+          <t>2026-02-14 17:26:42</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
@@ -24886,7 +24886,7 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:00:09</t>
+          <t>2026-02-14 17:00:09</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
@@ -24966,7 +24966,7 @@
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 01:39:16</t>
+          <t>2026-02-14 16:39:16</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -25046,7 +25046,7 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 00:56:51</t>
+          <t>2026-02-14 15:56:51</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
@@ -25126,7 +25126,7 @@
     <row r="274">
       <c r="A274" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 23:52:26</t>
+          <t>2026-02-14 14:52:26</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -25206,7 +25206,7 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 23:14:55</t>
+          <t>2026-02-14 14:14:55</t>
         </is>
       </c>
       <c r="B275" s="7" t="inlineStr">
@@ -25286,7 +25286,7 @@
     <row r="276">
       <c r="A276" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 04:19:58</t>
+          <t>2026-02-13 19:19:58</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
@@ -25366,7 +25366,7 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 03:37:53</t>
+          <t>2026-02-13 18:37:53</t>
         </is>
       </c>
       <c r="B277" s="7" t="inlineStr">
@@ -25446,7 +25446,7 @@
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 03:03:31</t>
+          <t>2026-02-13 18:03:31</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 02:08:36</t>
+          <t>2026-02-13 17:08:36</t>
         </is>
       </c>
       <c r="B279" s="7" t="inlineStr">
@@ -25606,7 +25606,7 @@
     <row r="280">
       <c r="A280" s="7" t="inlineStr">
         <is>
-          <t>2026-02-12 00:20:03</t>
+          <t>2026-02-11 15:20:03</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -25686,7 +25686,7 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 03:05:03</t>
+          <t>2026-02-10 18:05:03</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
@@ -25766,7 +25766,7 @@
     <row r="282">
       <c r="A282" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 02:14:02</t>
+          <t>2026-02-10 17:14:02</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -25846,7 +25846,7 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 01:33:21</t>
+          <t>2026-02-10 16:33:21</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
@@ -25926,7 +25926,7 @@
     <row r="284">
       <c r="A284" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 01:01:41</t>
+          <t>2026-02-10 16:01:41</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -26006,7 +26006,7 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 01:49:32</t>
+          <t>2026-02-09 16:49:32</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
@@ -26086,7 +26086,7 @@
     <row r="286">
       <c r="A286" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 01:42:29</t>
+          <t>2026-02-09 16:42:29</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -26166,7 +26166,7 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 23:44:10</t>
+          <t>2026-02-09 14:44:10</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -26246,7 +26246,7 @@
     <row r="288">
       <c r="A288" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 23:00:28</t>
+          <t>2026-02-09 14:00:28</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -26326,7 +26326,7 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 00:27:49</t>
+          <t>2026-02-08 15:27:49</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -26406,7 +26406,7 @@
     <row r="290">
       <c r="A290" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 00:16:42</t>
+          <t>2026-02-08 15:16:42</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -26486,7 +26486,7 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08 04:04:43</t>
+          <t>2026-02-07 19:04:43</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
@@ -26566,7 +26566,7 @@
     <row r="292">
       <c r="A292" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 03:13:11</t>
+          <t>2026-02-06 18:13:11</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -26646,7 +26646,7 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 02:19:42</t>
+          <t>2026-02-06 17:19:42</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
@@ -26726,7 +26726,7 @@
     <row r="294">
       <c r="A294" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 01:37:36</t>
+          <t>2026-02-06 16:37:36</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -26806,7 +26806,7 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>2026-02-03 23:04:49</t>
+          <t>2026-02-03 14:04:49</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
@@ -26886,7 +26886,7 @@
     <row r="296">
       <c r="A296" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 23:21:38</t>
+          <t>2026-02-02 14:21:38</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -26966,7 +26966,7 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 03:08:17</t>
+          <t>2026-02-01 18:08:17</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -27046,7 +27046,7 @@
     <row r="298">
       <c r="A298" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 02:41:55</t>
+          <t>2026-02-01 17:41:55</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -27126,7 +27126,7 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 02:09:57</t>
+          <t>2026-02-01 17:09:57</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="300">
       <c r="A300" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 01:41:49</t>
+          <t>2026-02-01 16:41:49</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
@@ -27286,7 +27286,7 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 02:22:13</t>
+          <t>2026-01-31 17:22:13</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -27366,7 +27366,7 @@
     <row r="302">
       <c r="A302" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 01:20:54</t>
+          <t>2026-01-31 16:20:54</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
@@ -27446,7 +27446,7 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 01:09:32</t>
+          <t>2026-01-31 16:09:32</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
@@ -27526,7 +27526,7 @@
     <row r="304">
       <c r="A304" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 00:29:37</t>
+          <t>2026-01-31 15:29:37</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -27606,7 +27606,7 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 00:03:50</t>
+          <t>2026-01-31 15:03:50</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -27686,7 +27686,7 @@
     <row r="306">
       <c r="A306" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 23:15:28</t>
+          <t>2026-01-31 14:15:28</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -27766,7 +27766,7 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>2026-01-29 00:36:39</t>
+          <t>2026-01-28 15:36:39</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
@@ -27846,7 +27846,7 @@
     <row r="308">
       <c r="A308" s="7" t="inlineStr">
         <is>
-          <t>2026-01-29 00:02:45</t>
+          <t>2026-01-28 15:02:45</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
@@ -27926,7 +27926,7 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 23:26:47</t>
+          <t>2026-01-28 14:26:47</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
@@ -28006,7 +28006,7 @@
     <row r="310">
       <c r="A310" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 23:04:33</t>
+          <t>2026-01-28 14:04:33</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -28086,7 +28086,7 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 00:33:31</t>
+          <t>2026-01-27 15:33:31</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -28166,7 +28166,7 @@
     <row r="312">
       <c r="A312" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 23:59:21</t>
+          <t>2026-01-27 14:59:21</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -28246,7 +28246,7 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 23:08:33</t>
+          <t>2026-01-27 14:08:33</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -28326,7 +28326,7 @@
     <row r="314">
       <c r="A314" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 23:28:17</t>
+          <t>2026-01-25 14:28:17</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -28406,7 +28406,7 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 22:56:22</t>
+          <t>2026-01-25 13:56:22</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -28486,7 +28486,7 @@
     <row r="316">
       <c r="A316" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 22:28:25</t>
+          <t>2026-01-25 13:28:25</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -28566,7 +28566,7 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 21:42:03</t>
+          <t>2026-01-25 12:42:03</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -28646,7 +28646,7 @@
     <row r="318">
       <c r="A318" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 19:38:23</t>
+          <t>2026-01-25 10:38:23</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -28726,7 +28726,7 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 18:56:35</t>
+          <t>2026-01-25 09:56:35</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -28806,7 +28806,7 @@
     <row r="320">
       <c r="A320" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 18:29:19</t>
+          <t>2026-01-25 09:29:19</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 17:14:05</t>
+          <t>2026-01-25 08:14:05</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -28966,7 +28966,7 @@
     <row r="322">
       <c r="A322" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 02:47:24</t>
+          <t>2026-01-23 17:47:24</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -29046,7 +29046,7 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 02:12:26</t>
+          <t>2026-01-23 17:12:26</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -29126,7 +29126,7 @@
     <row r="324">
       <c r="A324" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 01:33:34</t>
+          <t>2026-01-23 16:33:34</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -29206,7 +29206,7 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 01:00:39</t>
+          <t>2026-01-23 16:00:39</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -29286,7 +29286,7 @@
     <row r="326">
       <c r="A326" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 00:19:07</t>
+          <t>2026-01-23 15:19:07</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -29366,7 +29366,7 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 23:52:33</t>
+          <t>2026-01-23 14:52:33</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -29446,7 +29446,7 @@
     <row r="328">
       <c r="A328" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 23:19:19</t>
+          <t>2026-01-23 14:19:19</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -29526,7 +29526,7 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36:59</t>
+          <t>2026-01-23 13:36:59</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -29606,7 +29606,7 @@
     <row r="330">
       <c r="A330" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 03:01:58</t>
+          <t>2026-01-22 18:01:58</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -29686,7 +29686,7 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 02:25:41</t>
+          <t>2026-01-22 17:25:41</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -29766,7 +29766,7 @@
     <row r="332">
       <c r="A332" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 00:32:45</t>
+          <t>2026-01-22 15:32:45</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -29846,7 +29846,7 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 23:54:46</t>
+          <t>2026-01-22 14:54:46</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -29926,7 +29926,7 @@
     <row r="334">
       <c r="A334" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 23:17:42</t>
+          <t>2026-01-22 14:17:42</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -30006,7 +30006,7 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 01:10:08</t>
+          <t>2026-01-21 16:10:08</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -30086,7 +30086,7 @@
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
         <is>
-          <t>2026-01-21 00:27:51</t>
+          <t>2026-01-20 15:27:51</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -30166,7 +30166,7 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 23:25:34</t>
+          <t>2026-01-20 14:25:34</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -30246,7 +30246,7 @@
     <row r="338">
       <c r="A338" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 22:56:13</t>
+          <t>2026-01-20 13:56:13</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -30326,7 +30326,7 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>2026-01-19 01:59:11</t>
+          <t>2026-01-18 16:59:11</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -30406,7 +30406,7 @@
     <row r="340">
       <c r="A340" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 03:05:32</t>
+          <t>2026-01-17 18:05:32</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -30486,7 +30486,7 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 02:19:17</t>
+          <t>2026-01-17 17:19:17</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="342">
       <c r="A342" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 01:58:17</t>
+          <t>2026-01-17 16:58:17</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -30646,7 +30646,7 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 01:18:29</t>
+          <t>2026-01-17 16:18:29</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -30726,7 +30726,7 @@
     <row r="344">
       <c r="A344" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 00:38:58</t>
+          <t>2026-01-17 15:38:58</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -30806,7 +30806,7 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 18:46:30</t>
+          <t>2026-01-17 09:46:30</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -30886,7 +30886,7 @@
     <row r="346">
       <c r="A346" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 02:21:36</t>
+          <t>2026-01-16 17:21:36</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -30966,7 +30966,7 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 01:51:05</t>
+          <t>2026-01-16 16:51:05</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -31046,7 +31046,7 @@
     <row r="348">
       <c r="A348" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 01:18:22</t>
+          <t>2026-01-16 16:18:22</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -31126,7 +31126,7 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 01:41:15</t>
+          <t>2026-01-15 16:41:15</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -31206,7 +31206,7 @@
     <row r="350">
       <c r="A350" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 01:05:38</t>
+          <t>2026-01-15 16:05:38</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -31286,7 +31286,7 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14 00:57:21</t>
+          <t>2026-01-13 15:57:21</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -31366,7 +31366,7 @@
     <row r="352">
       <c r="A352" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14 00:19:49</t>
+          <t>2026-01-13 15:19:49</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -31446,7 +31446,7 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 23:53:29</t>
+          <t>2026-01-13 14:53:29</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -31526,7 +31526,7 @@
     <row r="354">
       <c r="A354" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 02:23:29</t>
+          <t>2026-01-12 17:23:29</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -31606,7 +31606,7 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 01:42:12</t>
+          <t>2026-01-12 16:42:12</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -31686,7 +31686,7 @@
     <row r="356">
       <c r="A356" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 01:17:01</t>
+          <t>2026-01-12 16:17:01</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -31766,7 +31766,7 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 00:43:11</t>
+          <t>2026-01-12 15:43:11</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -31846,7 +31846,7 @@
     <row r="358">
       <c r="A358" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 17:24:44</t>
+          <t>2026-01-12 08:24:44</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -31926,7 +31926,7 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 03:12:16</t>
+          <t>2026-01-11 18:12:16</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -32006,7 +32006,7 @@
     <row r="360">
       <c r="A360" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 02:54:03</t>
+          <t>2026-01-10 17:54:03</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -32086,7 +32086,7 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 02:14:56</t>
+          <t>2026-01-10 17:14:56</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -32166,7 +32166,7 @@
     <row r="362">
       <c r="A362" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 01:17:21</t>
+          <t>2026-01-10 16:17:21</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 00:22:11</t>
+          <t>2026-01-10 15:22:11</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -32326,7 +32326,7 @@
     <row r="364">
       <c r="A364" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 23:38:24</t>
+          <t>2026-01-10 14:38:24</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -32406,7 +32406,7 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 02:54:19</t>
+          <t>2026-01-09 17:54:19</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -32486,7 +32486,7 @@
     <row r="366">
       <c r="A366" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 02:00:16</t>
+          <t>2026-01-09 17:00:16</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -32566,7 +32566,7 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>2026-01-09 23:36:27</t>
+          <t>2026-01-09 14:36:27</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -32643,8 +32643,88 @@
         </is>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-05 14:21:47</t>
+        </is>
+      </c>
+      <c r="B368" s="7" t="inlineStr">
+        <is>
+          <t>ランク(ソロ/デュオ)</t>
+        </is>
+      </c>
+      <c r="C368" s="10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D368" s="7" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E368" s="7" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F368" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H368" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I368" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J368" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K368" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="L368" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M368" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N368" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="O368" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P368" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q368" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R368" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S368" s="11" t="n">
+        <v>6751</v>
+      </c>
+      <c r="T368" s="11" t="n">
+        <v>2219</v>
+      </c>
+      <c r="U368" s="6" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V368" s="7" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V367"/>
+  <autoFilter ref="A1:V368"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32655,7 +32735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P367"/>
+  <dimension ref="A1:P368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -32761,7 +32841,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 23:51:39</t>
+          <t>2026-07-28 14:51:39</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
@@ -32823,7 +32903,7 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 23:05:20</t>
+          <t>2026-07-28 14:05:20</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
@@ -32885,7 +32965,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>2026-07-27 01:21:51</t>
+          <t>2026-07-26 16:21:51</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -32947,7 +33027,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>2026-07-27 00:43:02</t>
+          <t>2026-07-26 15:43:02</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -33009,7 +33089,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 23:12:09</t>
+          <t>2026-07-25 14:12:09</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -33071,7 +33151,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 22:30:57</t>
+          <t>2026-07-25 13:30:57</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -33133,7 +33213,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 00:11:55</t>
+          <t>2026-07-24 15:11:55</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -33195,7 +33275,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>2026-07-24 23:25:38</t>
+          <t>2026-07-24 14:25:38</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -33257,7 +33337,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>2026-07-22 00:17:56</t>
+          <t>2026-07-21 15:17:56</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -33319,7 +33399,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>2026-07-22 00:04:35</t>
+          <t>2026-07-21 15:04:35</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -33381,7 +33461,7 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 23:25:56</t>
+          <t>2026-07-21 14:25:56</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -33443,7 +33523,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 22:44:36</t>
+          <t>2026-07-21 13:44:36</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -33505,7 +33585,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 22:18:59</t>
+          <t>2026-07-21 13:18:59</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
@@ -33567,7 +33647,7 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>2026-07-20 03:20:20</t>
+          <t>2026-07-19 18:20:20</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -33629,7 +33709,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>2026-07-20 02:39:51</t>
+          <t>2026-07-19 17:39:51</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -33691,7 +33771,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:59:14</t>
+          <t>2026-07-18 09:59:14</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -33753,7 +33833,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:21:14</t>
+          <t>2026-07-18 09:21:14</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -33815,7 +33895,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 23:06:28</t>
+          <t>2026-07-16 14:06:28</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -33877,7 +33957,7 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 22:32:42</t>
+          <t>2026-07-16 13:32:42</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -33939,7 +34019,7 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 00:40:48</t>
+          <t>2026-07-15 15:40:48</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -34001,7 +34081,7 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 23:41:56</t>
+          <t>2026-07-15 14:41:56</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -34063,7 +34143,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 22:58:44</t>
+          <t>2026-07-15 13:58:44</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -34125,7 +34205,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 22:34:16</t>
+          <t>2026-07-15 13:34:16</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -34187,7 +34267,7 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 23:36:35</t>
+          <t>2026-07-14 14:36:35</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -34249,7 +34329,7 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 22:49:50</t>
+          <t>2026-07-14 13:49:50</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
@@ -34311,7 +34391,7 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 01:02:29</t>
+          <t>2026-07-13 16:02:29</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -34373,7 +34453,7 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 00:22:46</t>
+          <t>2026-07-13 15:22:46</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
@@ -34435,7 +34515,7 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 23:51:38</t>
+          <t>2026-07-13 14:51:38</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -34497,7 +34577,7 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 02:05:19</t>
+          <t>2026-07-12 17:05:19</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
@@ -34559,7 +34639,7 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 01:29:17</t>
+          <t>2026-07-12 16:29:17</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
@@ -34621,7 +34701,7 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 03:11:38</t>
+          <t>2026-07-11 18:11:38</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
@@ -34683,7 +34763,7 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 02:46:15</t>
+          <t>2026-07-11 17:46:15</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -34745,7 +34825,7 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 03:42:29</t>
+          <t>2026-07-10 18:42:29</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
@@ -34807,7 +34887,7 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 03:06:21</t>
+          <t>2026-07-10 18:06:21</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
@@ -34869,7 +34949,7 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:55:25</t>
+          <t>2026-07-08 17:55:25</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
@@ -34931,7 +35011,7 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:17:09</t>
+          <t>2026-07-08 17:17:09</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -34993,7 +35073,7 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 02:03:51</t>
+          <t>2026-07-05 17:03:51</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
@@ -35055,7 +35135,7 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 01:07:17</t>
+          <t>2026-07-05 16:07:17</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -35117,7 +35197,7 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 00:23:00</t>
+          <t>2026-07-05 15:23:00</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
@@ -35179,7 +35259,7 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>2026-07-05 03:21:23</t>
+          <t>2026-07-04 18:21:23</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
@@ -35241,7 +35321,7 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>2026-07-04 03:01:40</t>
+          <t>2026-07-03 18:01:40</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
@@ -35303,7 +35383,7 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>2026-07-03 01:48:19</t>
+          <t>2026-07-02 16:48:19</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
@@ -35365,7 +35445,7 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>2026-07-01 00:21:19</t>
+          <t>2026-06-30 15:21:19</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
@@ -35427,7 +35507,7 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 23:38:16</t>
+          <t>2026-06-30 14:38:16</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
@@ -35489,7 +35569,7 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 01:16:28</t>
+          <t>2026-06-29 16:16:28</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
@@ -35551,7 +35631,7 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 00:34:32</t>
+          <t>2026-06-29 15:34:32</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
@@ -35613,7 +35693,7 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>2026-06-26 00:50:56</t>
+          <t>2026-06-25 15:50:56</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
@@ -35675,7 +35755,7 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>2026-06-26 00:06:40</t>
+          <t>2026-06-25 15:06:40</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
@@ -35737,7 +35817,7 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07:56</t>
+          <t>2026-06-24 17:07:56</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
@@ -35799,7 +35879,7 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 01:33:19</t>
+          <t>2026-06-24 16:33:19</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
@@ -35861,7 +35941,7 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:47:59</t>
+          <t>2026-06-24 15:47:59</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
@@ -35923,7 +36003,7 @@
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:08:31</t>
+          <t>2026-06-24 15:08:31</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
@@ -35985,7 +36065,7 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 23:33:15</t>
+          <t>2026-06-24 14:33:15</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
@@ -36047,7 +36127,7 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 22:39:11</t>
+          <t>2026-06-24 13:39:11</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
@@ -36109,7 +36189,7 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 01:16:06</t>
+          <t>2026-06-22 16:16:06</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
@@ -36171,7 +36251,7 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 00:38:08</t>
+          <t>2026-06-22 15:38:08</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
@@ -36233,7 +36313,7 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 00:29:33</t>
+          <t>2026-06-22 15:29:33</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
@@ -36295,7 +36375,7 @@
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 01:54:04</t>
+          <t>2026-06-18 16:54:04</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
@@ -36357,7 +36437,7 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 01:14:50</t>
+          <t>2026-06-18 16:14:50</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
@@ -36419,7 +36499,7 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 00:35:17</t>
+          <t>2026-06-18 15:35:17</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
@@ -36481,7 +36561,7 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 23:55:50</t>
+          <t>2026-06-18 14:55:50</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
@@ -36543,7 +36623,7 @@
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 00:44:42</t>
+          <t>2026-06-17 15:44:42</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
@@ -36605,7 +36685,7 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 23:57:38</t>
+          <t>2026-06-17 14:57:38</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
@@ -36667,7 +36747,7 @@
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 01:58:55</t>
+          <t>2026-06-16 16:58:55</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
@@ -36729,7 +36809,7 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 01:30:07</t>
+          <t>2026-06-16 16:30:07</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
@@ -36791,7 +36871,7 @@
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 03:10:28</t>
+          <t>2026-06-14 18:10:28</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
@@ -36853,7 +36933,7 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 02:27:52</t>
+          <t>2026-06-14 17:27:52</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
@@ -36915,7 +36995,7 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 01:57:23</t>
+          <t>2026-06-14 16:57:23</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
@@ -36977,7 +37057,7 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 01:27:22</t>
+          <t>2026-06-14 16:27:22</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
@@ -37039,7 +37119,7 @@
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 00:24:35</t>
+          <t>2026-06-14 15:24:35</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
@@ -37101,7 +37181,7 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 23:46:55</t>
+          <t>2026-06-14 14:46:55</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
@@ -37163,7 +37243,7 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 01:41:53</t>
+          <t>2026-06-13 16:41:53</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
@@ -37225,7 +37305,7 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 00:52:58</t>
+          <t>2026-06-13 15:52:58</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
@@ -37287,7 +37367,7 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 00:14:23</t>
+          <t>2026-06-13 15:14:23</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
@@ -37349,7 +37429,7 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 23:45:21</t>
+          <t>2026-06-13 14:45:21</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
@@ -37411,7 +37491,7 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 23:05:32</t>
+          <t>2026-06-13 14:05:32</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
@@ -37473,7 +37553,7 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 01:08:14</t>
+          <t>2026-06-10 16:08:14</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
@@ -37535,7 +37615,7 @@
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:34:35</t>
+          <t>2026-06-10 15:34:35</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
@@ -37597,7 +37677,7 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:09:17</t>
+          <t>2026-06-10 15:09:17</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
@@ -37659,7 +37739,7 @@
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 23:27:53</t>
+          <t>2026-06-10 14:27:53</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
@@ -37721,7 +37801,7 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 00:49:00</t>
+          <t>2026-06-09 15:49:00</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
@@ -37783,7 +37863,7 @@
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>2026-06-06 02:58:51</t>
+          <t>2026-06-05 17:58:51</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
@@ -37845,7 +37925,7 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>2026-06-06 02:15:04</t>
+          <t>2026-06-05 17:15:04</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
@@ -37907,7 +37987,7 @@
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 23:49:14</t>
+          <t>2026-06-04 14:49:14</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
@@ -37969,7 +38049,7 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 21:40:04</t>
+          <t>2026-06-04 12:40:04</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
@@ -38031,7 +38111,7 @@
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 21:17:24</t>
+          <t>2026-06-04 12:17:24</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
@@ -38093,7 +38173,7 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 01:06:27</t>
+          <t>2026-06-03 16:06:27</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
@@ -38155,7 +38235,7 @@
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 00:31:09</t>
+          <t>2026-06-03 15:31:09</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
@@ -38217,7 +38297,7 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 23:53:57</t>
+          <t>2026-06-03 14:53:57</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
@@ -38279,7 +38359,7 @@
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 22:44:02</t>
+          <t>2026-06-03 13:44:02</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
@@ -38341,7 +38421,7 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>2026-06-02 22:49:11</t>
+          <t>2026-06-02 13:49:11</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
@@ -38403,7 +38483,7 @@
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:56:06</t>
+          <t>2026-06-01 14:56:06</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
@@ -38465,7 +38545,7 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:20:26</t>
+          <t>2026-06-01 14:20:26</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
@@ -38527,7 +38607,7 @@
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:01:06</t>
+          <t>2026-06-01 14:01:06</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
@@ -38589,7 +38669,7 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>2026-05-31 03:01:04</t>
+          <t>2026-05-30 18:01:04</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
@@ -38651,7 +38731,7 @@
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>2026-05-31 02:13:41</t>
+          <t>2026-05-30 17:13:41</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
@@ -38713,7 +38793,7 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 23:00:40</t>
+          <t>2026-05-25 14:00:40</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
@@ -38775,7 +38855,7 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 01:55:47</t>
+          <t>2026-05-24 16:55:47</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
@@ -38837,7 +38917,7 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 01:24:22</t>
+          <t>2026-05-24 16:24:22</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
@@ -38899,7 +38979,7 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 23:49:25</t>
+          <t>2026-05-24 14:49:25</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
@@ -38961,7 +39041,7 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 03:13:39</t>
+          <t>2026-05-23 18:13:39</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
@@ -39023,7 +39103,7 @@
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 02:41:52</t>
+          <t>2026-05-23 17:41:52</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
@@ -39085,7 +39165,7 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 23:19:04</t>
+          <t>2026-05-23 14:19:04</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
@@ -39147,7 +39227,7 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 22:43:20</t>
+          <t>2026-05-23 13:43:20</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
@@ -39209,7 +39289,7 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 15:54:19</t>
+          <t>2026-05-23 06:54:19</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
@@ -39271,7 +39351,7 @@
     <row r="107">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 02:25:24</t>
+          <t>2026-05-22 17:25:24</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
@@ -39333,7 +39413,7 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 01:29:23</t>
+          <t>2026-05-21 16:29:23</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
@@ -39395,7 +39475,7 @@
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 00:48:49</t>
+          <t>2026-05-21 15:48:49</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
@@ -39457,7 +39537,7 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:45</t>
+          <t>2026-05-21 15:00:45</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
@@ -39519,7 +39599,7 @@
     <row r="111">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 23:22:44</t>
+          <t>2026-05-21 14:22:44</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
@@ -39581,7 +39661,7 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 00:05:15</t>
+          <t>2026-05-20 15:05:15</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
@@ -39643,7 +39723,7 @@
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 23:43:50</t>
+          <t>2026-05-20 14:43:50</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
@@ -39705,7 +39785,7 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 22:57:45</t>
+          <t>2026-05-20 13:57:45</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
@@ -39767,7 +39847,7 @@
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 01:25:45</t>
+          <t>2026-05-19 16:25:45</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
@@ -39829,7 +39909,7 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 00:46:42</t>
+          <t>2026-05-19 15:46:42</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
@@ -39891,7 +39971,7 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>2026-05-18 22:56:39</t>
+          <t>2026-05-18 13:56:39</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
@@ -39953,7 +40033,7 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 01:35:56</t>
+          <t>2026-05-14 16:35:56</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
@@ -40015,7 +40095,7 @@
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 01:17:05</t>
+          <t>2026-05-14 16:17:05</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
@@ -40077,7 +40157,7 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 00:05:48</t>
+          <t>2026-05-14 15:05:48</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
@@ -40139,7 +40219,7 @@
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>2026-05-14 01:25:38</t>
+          <t>2026-05-13 16:25:38</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
@@ -40201,7 +40281,7 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>2026-05-12 00:19:57</t>
+          <t>2026-05-11 15:19:57</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
@@ -40263,7 +40343,7 @@
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 23:54:15</t>
+          <t>2026-05-11 14:54:15</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
@@ -40325,7 +40405,7 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 23:14:30</t>
+          <t>2026-05-11 14:14:30</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
@@ -40387,7 +40467,7 @@
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 22:37:05</t>
+          <t>2026-05-11 13:37:05</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
@@ -40449,7 +40529,7 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 21:53:13</t>
+          <t>2026-05-11 12:53:13</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
@@ -40511,7 +40591,7 @@
     <row r="127">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 00:04:01</t>
+          <t>2026-05-10 15:04:01</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
@@ -40573,7 +40653,7 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:54:24</t>
+          <t>2026-05-09 16:54:24</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
@@ -40635,7 +40715,7 @@
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:22:50</t>
+          <t>2026-05-09 16:22:50</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
@@ -40697,7 +40777,7 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 00:26:16</t>
+          <t>2026-05-09 15:26:16</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
@@ -40759,7 +40839,7 @@
     <row r="131">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 23:38:30</t>
+          <t>2026-05-09 14:38:30</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
@@ -40821,7 +40901,7 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 22:50:20</t>
+          <t>2026-05-09 13:50:20</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
@@ -40883,7 +40963,7 @@
     <row r="133">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 22:13:25</t>
+          <t>2026-05-09 13:13:25</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
@@ -40945,7 +41025,7 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 20:00:11</t>
+          <t>2026-05-09 11:00:11</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
@@ -41007,7 +41087,7 @@
     <row r="135">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 19:10:28</t>
+          <t>2026-05-09 10:10:28</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
@@ -41069,7 +41149,7 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 02:17:27</t>
+          <t>2026-05-08 17:17:27</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
@@ -41131,7 +41211,7 @@
     <row r="137">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 01:38:25</t>
+          <t>2026-05-08 16:38:25</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
@@ -41193,7 +41273,7 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 00:58:58</t>
+          <t>2026-05-08 15:58:58</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
@@ -41255,7 +41335,7 @@
     <row r="139">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 00:37:55</t>
+          <t>2026-05-08 15:37:55</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
@@ -41317,7 +41397,7 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 01:48:31</t>
+          <t>2026-05-07 16:48:31</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
@@ -41379,7 +41459,7 @@
     <row r="141">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 01:02:52</t>
+          <t>2026-05-07 16:02:52</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
@@ -41441,7 +41521,7 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 00:23:29</t>
+          <t>2026-05-07 15:23:29</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
@@ -41503,7 +41583,7 @@
     <row r="143">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 01:30:56</t>
+          <t>2026-05-06 16:30:56</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
@@ -41565,7 +41645,7 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 00:42:16</t>
+          <t>2026-05-06 15:42:16</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
@@ -41627,7 +41707,7 @@
     <row r="145">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 23:44:04</t>
+          <t>2026-05-06 14:44:04</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
@@ -41689,7 +41769,7 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:13:52</t>
+          <t>2026-05-06 09:13:52</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
@@ -41751,7 +41831,7 @@
     <row r="147">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:05:08</t>
+          <t>2026-05-06 09:05:08</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
@@ -41813,7 +41893,7 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 17:22:30</t>
+          <t>2026-05-06 08:22:30</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
@@ -41875,7 +41955,7 @@
     <row r="149">
       <c r="A149" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 16:28:42</t>
+          <t>2026-05-06 07:28:42</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
@@ -41937,7 +42017,7 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 03:16:57</t>
+          <t>2026-05-05 18:16:57</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
@@ -41999,7 +42079,7 @@
     <row r="151">
       <c r="A151" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:32:40</t>
+          <t>2026-05-05 17:32:40</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
@@ -42061,7 +42141,7 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:23:28</t>
+          <t>2026-05-05 17:23:28</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
@@ -42123,7 +42203,7 @@
     <row r="153">
       <c r="A153" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 01:48:28</t>
+          <t>2026-05-05 16:48:28</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
@@ -42185,7 +42265,7 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 00:52:33</t>
+          <t>2026-05-05 15:52:33</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
@@ -42247,7 +42327,7 @@
     <row r="155">
       <c r="A155" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 17:43:06</t>
+          <t>2026-05-05 08:43:06</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
@@ -42309,7 +42389,7 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>2026-05-03 00:36:42</t>
+          <t>2026-05-02 15:36:42</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
@@ -42371,7 +42451,7 @@
     <row r="157">
       <c r="A157" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 23:51:09</t>
+          <t>2026-05-02 14:51:09</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
@@ -42433,7 +42513,7 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 22:15:10</t>
+          <t>2026-05-02 13:15:10</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
@@ -42495,7 +42575,7 @@
     <row r="159">
       <c r="A159" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 21:29:49</t>
+          <t>2026-05-02 12:29:49</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
@@ -42557,7 +42637,7 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 01:39:42</t>
+          <t>2026-04-30 16:39:42</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
@@ -42619,7 +42699,7 @@
     <row r="161">
       <c r="A161" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 01:01:34</t>
+          <t>2026-04-30 16:01:34</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
@@ -42681,7 +42761,7 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 00:24:48</t>
+          <t>2026-04-30 15:24:48</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
@@ -42743,7 +42823,7 @@
     <row r="163">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 23:37:10</t>
+          <t>2026-04-30 14:37:10</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
@@ -42805,7 +42885,7 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 22:58:06</t>
+          <t>2026-04-30 13:58:06</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
@@ -42867,7 +42947,7 @@
     <row r="165">
       <c r="A165" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 03:29:33</t>
+          <t>2026-04-29 18:29:33</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
@@ -42929,7 +43009,7 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 02:54:07</t>
+          <t>2026-04-29 17:54:07</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
@@ -42991,7 +43071,7 @@
     <row r="167">
       <c r="A167" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 02:20:58</t>
+          <t>2026-04-29 17:20:58</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
@@ -43053,7 +43133,7 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 01:42:01</t>
+          <t>2026-04-29 16:42:01</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
@@ -43115,7 +43195,7 @@
     <row r="169">
       <c r="A169" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 01:03:17</t>
+          <t>2026-04-29 16:03:17</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
@@ -43177,7 +43257,7 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 00:19:47</t>
+          <t>2026-04-29 15:19:47</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
@@ -43239,7 +43319,7 @@
     <row r="171">
       <c r="A171" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 23:29:53</t>
+          <t>2026-04-29 14:29:53</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
@@ -43301,7 +43381,7 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:59:49</t>
+          <t>2026-04-29 13:59:49</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
@@ -43363,7 +43443,7 @@
     <row r="173">
       <c r="A173" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:38:22</t>
+          <t>2026-04-29 13:38:22</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
@@ -43425,7 +43505,7 @@
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:44</t>
+          <t>2026-04-29 13:17:44</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
@@ -43487,7 +43567,7 @@
     <row r="175">
       <c r="A175" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 03:28:56</t>
+          <t>2026-04-28 18:28:56</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
@@ -43549,7 +43629,7 @@
     <row r="176">
       <c r="A176" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:58:50</t>
+          <t>2026-04-28 17:58:50</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
@@ -43611,7 +43691,7 @@
     <row r="177">
       <c r="A177" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:29:43</t>
+          <t>2026-04-28 17:29:43</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
@@ -43673,7 +43753,7 @@
     <row r="178">
       <c r="A178" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 01:38:43</t>
+          <t>2026-04-28 16:38:43</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
@@ -43735,7 +43815,7 @@
     <row r="179">
       <c r="A179" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:54</t>
+          <t>2026-04-28 15:58:54</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
@@ -43797,7 +43877,7 @@
     <row r="180">
       <c r="A180" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:31:32</t>
+          <t>2026-04-28 15:31:32</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
@@ -43859,7 +43939,7 @@
     <row r="181">
       <c r="A181" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:04:20</t>
+          <t>2026-04-28 15:04:20</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
@@ -43921,7 +44001,7 @@
     <row r="182">
       <c r="A182" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 23:37:27</t>
+          <t>2026-04-28 14:37:27</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
@@ -43983,7 +44063,7 @@
     <row r="183">
       <c r="A183" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 23:09:10</t>
+          <t>2026-04-28 14:09:10</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
@@ -44045,7 +44125,7 @@
     <row r="184">
       <c r="A184" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:59:25</t>
+          <t>2026-04-27 14:59:25</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
@@ -44107,7 +44187,7 @@
     <row r="185">
       <c r="A185" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:49:35</t>
+          <t>2026-04-27 14:49:35</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
@@ -44169,7 +44249,7 @@
     <row r="186">
       <c r="A186" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 22:55:34</t>
+          <t>2026-04-27 13:55:34</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
@@ -44231,7 +44311,7 @@
     <row r="187">
       <c r="A187" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 22:04:13</t>
+          <t>2026-04-27 13:04:13</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
@@ -44293,7 +44373,7 @@
     <row r="188">
       <c r="A188" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 02:49:02</t>
+          <t>2026-04-24 17:49:02</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
@@ -44355,7 +44435,7 @@
     <row r="189">
       <c r="A189" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 02:03:56</t>
+          <t>2026-04-24 17:03:56</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
@@ -44417,7 +44497,7 @@
     <row r="190">
       <c r="A190" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 01:37:00</t>
+          <t>2026-04-24 16:37:00</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
@@ -44479,7 +44559,7 @@
     <row r="191">
       <c r="A191" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:33:59</t>
+          <t>2026-04-23 15:33:59</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
@@ -44541,7 +44621,7 @@
     <row r="192">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:22:46</t>
+          <t>2026-04-23 15:22:46</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
@@ -44603,7 +44683,7 @@
     <row r="193">
       <c r="A193" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:12:54</t>
+          <t>2026-04-23 15:12:54</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
@@ -44665,7 +44745,7 @@
     <row r="194">
       <c r="A194" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 22:36:03</t>
+          <t>2026-04-23 13:36:03</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
@@ -44727,7 +44807,7 @@
     <row r="195">
       <c r="A195" s="13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:58:57</t>
+          <t>2026-04-13 15:58:57</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
@@ -44789,7 +44869,7 @@
     <row r="196">
       <c r="A196" s="13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:09:08</t>
+          <t>2026-04-13 15:09:08</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
@@ -44851,7 +44931,7 @@
     <row r="197">
       <c r="A197" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 01:48:02</t>
+          <t>2026-04-12 16:48:02</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
@@ -44913,7 +44993,7 @@
     <row r="198">
       <c r="A198" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 01:17:58</t>
+          <t>2026-04-12 16:17:58</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
@@ -44975,7 +45055,7 @@
     <row r="199">
       <c r="A199" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 00:41:20</t>
+          <t>2026-04-12 15:41:20</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
@@ -45037,7 +45117,7 @@
     <row r="200">
       <c r="A200" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 23:18:06</t>
+          <t>2026-04-09 14:18:06</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
@@ -45099,7 +45179,7 @@
     <row r="201">
       <c r="A201" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 22:52:44</t>
+          <t>2026-04-09 13:52:44</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
@@ -45161,7 +45241,7 @@
     <row r="202">
       <c r="A202" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 22:27:45</t>
+          <t>2026-04-09 13:27:45</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
@@ -45223,7 +45303,7 @@
     <row r="203">
       <c r="A203" s="13" t="inlineStr">
         <is>
-          <t>2026-04-08 01:10:31</t>
+          <t>2026-04-07 16:10:31</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
@@ -45285,7 +45365,7 @@
     <row r="204">
       <c r="A204" s="13" t="inlineStr">
         <is>
-          <t>2026-04-08 00:29:19</t>
+          <t>2026-04-07 15:29:19</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
@@ -45347,7 +45427,7 @@
     <row r="205">
       <c r="A205" s="13" t="inlineStr">
         <is>
-          <t>2026-04-04 04:36:31</t>
+          <t>2026-04-03 19:36:31</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
@@ -45409,7 +45489,7 @@
     <row r="206">
       <c r="A206" s="13" t="inlineStr">
         <is>
-          <t>2026-04-04 04:16:32</t>
+          <t>2026-04-03 19:16:32</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
@@ -45471,7 +45551,7 @@
     <row r="207">
       <c r="A207" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 04:24:43</t>
+          <t>2026-03-27 19:24:43</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
@@ -45533,7 +45613,7 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:38:31</t>
+          <t>2026-03-27 18:38:31</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
@@ -45595,7 +45675,7 @@
     <row r="209">
       <c r="A209" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:17:50</t>
+          <t>2026-03-27 18:17:50</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
@@ -45657,7 +45737,7 @@
     <row r="210">
       <c r="A210" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 02:43:19</t>
+          <t>2026-03-27 17:43:19</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
@@ -45719,7 +45799,7 @@
     <row r="211">
       <c r="A211" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 02:15:18</t>
+          <t>2026-03-27 17:15:18</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
@@ -45781,7 +45861,7 @@
     <row r="212">
       <c r="A212" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 23:18:12</t>
+          <t>2026-03-25 14:18:12</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
@@ -45843,7 +45923,7 @@
     <row r="213">
       <c r="A213" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 00:01:49</t>
+          <t>2026-03-24 15:01:49</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
@@ -45905,7 +45985,7 @@
     <row r="214">
       <c r="A214" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 23:25:16</t>
+          <t>2026-03-24 14:25:16</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
@@ -45967,7 +46047,7 @@
     <row r="215">
       <c r="A215" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 23:02:52</t>
+          <t>2026-03-24 14:02:52</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
@@ -46029,7 +46109,7 @@
     <row r="216">
       <c r="A216" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 22:26:26</t>
+          <t>2026-03-24 13:26:26</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
@@ -46091,7 +46171,7 @@
     <row r="217">
       <c r="A217" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 00:56:18</t>
+          <t>2026-03-23 15:56:18</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
@@ -46153,7 +46233,7 @@
     <row r="218">
       <c r="A218" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 00:29:29</t>
+          <t>2026-03-23 15:29:29</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
@@ -46215,7 +46295,7 @@
     <row r="219">
       <c r="A219" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 23:51:11</t>
+          <t>2026-03-22 14:51:11</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
@@ -46277,7 +46357,7 @@
     <row r="220">
       <c r="A220" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 01:04:36</t>
+          <t>2026-03-21 16:04:36</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
@@ -46339,7 +46419,7 @@
     <row r="221">
       <c r="A221" s="13" t="inlineStr">
         <is>
-          <t>2026-03-21 02:55:49</t>
+          <t>2026-03-20 17:55:49</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
@@ -46401,7 +46481,7 @@
     <row r="222">
       <c r="A222" s="13" t="inlineStr">
         <is>
-          <t>2026-03-18 00:07:07</t>
+          <t>2026-03-17 15:07:07</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
@@ -46463,7 +46543,7 @@
     <row r="223">
       <c r="A223" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 23:24:05</t>
+          <t>2026-03-17 14:24:05</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
@@ -46525,7 +46605,7 @@
     <row r="224">
       <c r="A224" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 02:00:50</t>
+          <t>2026-03-16 17:00:50</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
@@ -46587,7 +46667,7 @@
     <row r="225">
       <c r="A225" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 01:33:08</t>
+          <t>2026-03-16 16:33:08</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
@@ -46649,7 +46729,7 @@
     <row r="226">
       <c r="A226" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 23:28:09</t>
+          <t>2026-03-16 14:28:09</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
@@ -46711,7 +46791,7 @@
     <row r="227">
       <c r="A227" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 01:32:22</t>
+          <t>2026-03-15 16:32:22</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
@@ -46773,7 +46853,7 @@
     <row r="228">
       <c r="A228" s="13" t="inlineStr">
         <is>
-          <t>2026-03-14 01:43:49</t>
+          <t>2026-03-13 16:43:49</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
@@ -46835,7 +46915,7 @@
     <row r="229">
       <c r="A229" s="13" t="inlineStr">
         <is>
-          <t>2026-03-14 01:19:35</t>
+          <t>2026-03-13 16:19:35</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
@@ -46897,7 +46977,7 @@
     <row r="230">
       <c r="A230" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 23:45:27</t>
+          <t>2026-03-12 14:45:27</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
@@ -46959,7 +47039,7 @@
     <row r="231">
       <c r="A231" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 23:02:09</t>
+          <t>2026-03-12 14:02:09</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
@@ -47021,7 +47101,7 @@
     <row r="232">
       <c r="A232" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 22:42:59</t>
+          <t>2026-03-12 13:42:59</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
@@ -47083,7 +47163,7 @@
     <row r="233">
       <c r="A233" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 01:39:10</t>
+          <t>2026-03-11 16:39:10</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
@@ -47145,7 +47225,7 @@
     <row r="234">
       <c r="A234" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:43:21</t>
+          <t>2026-03-11 15:43:21</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
@@ -47207,7 +47287,7 @@
     <row r="235">
       <c r="A235" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:04:25</t>
+          <t>2026-03-11 15:04:25</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
@@ -47269,7 +47349,7 @@
     <row r="236">
       <c r="A236" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 22:54:02</t>
+          <t>2026-03-11 13:54:02</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
@@ -47331,7 +47411,7 @@
     <row r="237">
       <c r="A237" s="13" t="inlineStr">
         <is>
-          <t>2026-03-08 02:01:53</t>
+          <t>2026-03-07 17:01:53</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
@@ -47393,7 +47473,7 @@
     <row r="238">
       <c r="A238" s="13" t="inlineStr">
         <is>
-          <t>2026-03-02 02:18:59</t>
+          <t>2026-03-01 17:18:59</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
@@ -47455,7 +47535,7 @@
     <row r="239">
       <c r="A239" s="13" t="inlineStr">
         <is>
-          <t>2026-02-24 01:40:38</t>
+          <t>2026-02-23 16:40:38</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
@@ -47517,7 +47597,7 @@
     <row r="240">
       <c r="A240" s="13" t="inlineStr">
         <is>
-          <t>2026-02-24 00:10:31</t>
+          <t>2026-02-23 15:10:31</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
@@ -47579,7 +47659,7 @@
     <row r="241">
       <c r="A241" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 23:33:47</t>
+          <t>2026-02-23 14:33:47</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
@@ -47641,7 +47721,7 @@
     <row r="242">
       <c r="A242" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 22:40:54</t>
+          <t>2026-02-23 13:40:54</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
@@ -47703,7 +47783,7 @@
     <row r="243">
       <c r="A243" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 21:58:56</t>
+          <t>2026-02-23 12:58:56</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
@@ -47765,7 +47845,7 @@
     <row r="244">
       <c r="A244" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 19:21:48</t>
+          <t>2026-02-23 10:21:48</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
@@ -47827,7 +47907,7 @@
     <row r="245">
       <c r="A245" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 17:17:13</t>
+          <t>2026-02-23 08:17:13</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
@@ -47889,7 +47969,7 @@
     <row r="246">
       <c r="A246" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 04:22:01</t>
+          <t>2026-02-22 19:22:01</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
@@ -47951,7 +48031,7 @@
     <row r="247">
       <c r="A247" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 03:23:51</t>
+          <t>2026-02-22 18:23:51</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
@@ -48013,7 +48093,7 @@
     <row r="248">
       <c r="A248" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 02:58:18</t>
+          <t>2026-02-22 17:58:18</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
@@ -48075,7 +48155,7 @@
     <row r="249">
       <c r="A249" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 02:29:21</t>
+          <t>2026-02-22 17:29:21</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
@@ -48137,7 +48217,7 @@
     <row r="250">
       <c r="A250" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 01:59:09</t>
+          <t>2026-02-22 16:59:09</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
@@ -48199,7 +48279,7 @@
     <row r="251">
       <c r="A251" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 01:32:08</t>
+          <t>2026-02-22 16:32:08</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
@@ -48261,7 +48341,7 @@
     <row r="252">
       <c r="A252" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 03:34:36</t>
+          <t>2026-02-20 18:34:36</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
@@ -48323,7 +48403,7 @@
     <row r="253">
       <c r="A253" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 02:57:13</t>
+          <t>2026-02-20 17:57:13</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
@@ -48385,7 +48465,7 @@
     <row r="254">
       <c r="A254" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 02:19:01</t>
+          <t>2026-02-20 17:19:01</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
@@ -48447,7 +48527,7 @@
     <row r="255">
       <c r="A255" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 01:41:10</t>
+          <t>2026-02-20 16:41:10</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
@@ -48509,7 +48589,7 @@
     <row r="256">
       <c r="A256" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 00:57:47</t>
+          <t>2026-02-20 15:57:47</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
@@ -48571,7 +48651,7 @@
     <row r="257">
       <c r="A257" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 00:39:52</t>
+          <t>2026-02-20 15:39:52</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
@@ -48633,7 +48713,7 @@
     <row r="258">
       <c r="A258" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 01:21:13</t>
+          <t>2026-02-19 16:21:13</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
@@ -48695,7 +48775,7 @@
     <row r="259">
       <c r="A259" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 00:33:10</t>
+          <t>2026-02-19 15:33:10</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
@@ -48757,7 +48837,7 @@
     <row r="260">
       <c r="A260" s="13" t="inlineStr">
         <is>
-          <t>2026-02-18 00:37:38</t>
+          <t>2026-02-17 15:37:38</t>
         </is>
       </c>
       <c r="B260" s="13" t="inlineStr">
@@ -48819,7 +48899,7 @@
     <row r="261">
       <c r="A261" s="13" t="inlineStr">
         <is>
-          <t>2026-02-17 23:58:39</t>
+          <t>2026-02-17 14:58:39</t>
         </is>
       </c>
       <c r="B261" s="13" t="inlineStr">
@@ -48881,7 +48961,7 @@
     <row r="262">
       <c r="A262" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 02:24:16</t>
+          <t>2026-02-15 17:24:16</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
@@ -48943,7 +49023,7 @@
     <row r="263">
       <c r="A263" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 01:47:19</t>
+          <t>2026-02-15 16:47:19</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
@@ -49005,7 +49085,7 @@
     <row r="264">
       <c r="A264" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 00:56:43</t>
+          <t>2026-02-15 15:56:43</t>
         </is>
       </c>
       <c r="B264" s="13" t="inlineStr">
@@ -49067,7 +49147,7 @@
     <row r="265">
       <c r="A265" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 00:26:20</t>
+          <t>2026-02-15 15:26:20</t>
         </is>
       </c>
       <c r="B265" s="13" t="inlineStr">
@@ -49129,7 +49209,7 @@
     <row r="266">
       <c r="A266" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 23:48:44</t>
+          <t>2026-02-15 14:48:44</t>
         </is>
       </c>
       <c r="B266" s="13" t="inlineStr">
@@ -49191,7 +49271,7 @@
     <row r="267">
       <c r="A267" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 04:17:17</t>
+          <t>2026-02-14 19:17:17</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
@@ -49253,7 +49333,7 @@
     <row r="268">
       <c r="A268" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 03:53:01</t>
+          <t>2026-02-14 18:53:01</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
@@ -49315,7 +49395,7 @@
     <row r="269">
       <c r="A269" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:59:46</t>
+          <t>2026-02-14 17:59:46</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
@@ -49377,7 +49457,7 @@
     <row r="270">
       <c r="A270" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:26:42</t>
+          <t>2026-02-14 17:26:42</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
@@ -49439,7 +49519,7 @@
     <row r="271">
       <c r="A271" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:00:09</t>
+          <t>2026-02-14 17:00:09</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
@@ -49501,7 +49581,7 @@
     <row r="272">
       <c r="A272" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 01:39:16</t>
+          <t>2026-02-14 16:39:16</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
@@ -49563,7 +49643,7 @@
     <row r="273">
       <c r="A273" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 00:56:51</t>
+          <t>2026-02-14 15:56:51</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
@@ -49625,7 +49705,7 @@
     <row r="274">
       <c r="A274" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 23:52:26</t>
+          <t>2026-02-14 14:52:26</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
@@ -49687,7 +49767,7 @@
     <row r="275">
       <c r="A275" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 23:14:55</t>
+          <t>2026-02-14 14:14:55</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
@@ -49749,7 +49829,7 @@
     <row r="276">
       <c r="A276" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 04:19:58</t>
+          <t>2026-02-13 19:19:58</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
@@ -49811,7 +49891,7 @@
     <row r="277">
       <c r="A277" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 03:37:53</t>
+          <t>2026-02-13 18:37:53</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
@@ -49873,7 +49953,7 @@
     <row r="278">
       <c r="A278" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 03:03:31</t>
+          <t>2026-02-13 18:03:31</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
@@ -49935,7 +50015,7 @@
     <row r="279">
       <c r="A279" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 02:08:36</t>
+          <t>2026-02-13 17:08:36</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
@@ -49997,7 +50077,7 @@
     <row r="280">
       <c r="A280" s="13" t="inlineStr">
         <is>
-          <t>2026-02-12 00:20:03</t>
+          <t>2026-02-11 15:20:03</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
@@ -50059,7 +50139,7 @@
     <row r="281">
       <c r="A281" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 03:05:03</t>
+          <t>2026-02-10 18:05:03</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
@@ -50121,7 +50201,7 @@
     <row r="282">
       <c r="A282" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 02:14:02</t>
+          <t>2026-02-10 17:14:02</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
@@ -50183,7 +50263,7 @@
     <row r="283">
       <c r="A283" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 01:33:21</t>
+          <t>2026-02-10 16:33:21</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
@@ -50245,7 +50325,7 @@
     <row r="284">
       <c r="A284" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 01:01:41</t>
+          <t>2026-02-10 16:01:41</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
@@ -50307,7 +50387,7 @@
     <row r="285">
       <c r="A285" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 01:49:32</t>
+          <t>2026-02-09 16:49:32</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
@@ -50369,7 +50449,7 @@
     <row r="286">
       <c r="A286" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 01:42:29</t>
+          <t>2026-02-09 16:42:29</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
@@ -50431,7 +50511,7 @@
     <row r="287">
       <c r="A287" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 23:44:10</t>
+          <t>2026-02-09 14:44:10</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
@@ -50493,7 +50573,7 @@
     <row r="288">
       <c r="A288" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 23:00:28</t>
+          <t>2026-02-09 14:00:28</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
@@ -50555,7 +50635,7 @@
     <row r="289">
       <c r="A289" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 00:27:49</t>
+          <t>2026-02-08 15:27:49</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
@@ -50617,7 +50697,7 @@
     <row r="290">
       <c r="A290" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 00:16:42</t>
+          <t>2026-02-08 15:16:42</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
@@ -50679,7 +50759,7 @@
     <row r="291">
       <c r="A291" s="13" t="inlineStr">
         <is>
-          <t>2026-02-08 04:04:43</t>
+          <t>2026-02-07 19:04:43</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
@@ -50741,7 +50821,7 @@
     <row r="292">
       <c r="A292" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 03:13:11</t>
+          <t>2026-02-06 18:13:11</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
@@ -50803,7 +50883,7 @@
     <row r="293">
       <c r="A293" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 02:19:42</t>
+          <t>2026-02-06 17:19:42</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
@@ -50865,7 +50945,7 @@
     <row r="294">
       <c r="A294" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 01:37:36</t>
+          <t>2026-02-06 16:37:36</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
@@ -50927,7 +51007,7 @@
     <row r="295">
       <c r="A295" s="13" t="inlineStr">
         <is>
-          <t>2026-02-03 23:04:49</t>
+          <t>2026-02-03 14:04:49</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
@@ -50989,7 +51069,7 @@
     <row r="296">
       <c r="A296" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 23:21:38</t>
+          <t>2026-02-02 14:21:38</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
@@ -51051,7 +51131,7 @@
     <row r="297">
       <c r="A297" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 03:08:17</t>
+          <t>2026-02-01 18:08:17</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
@@ -51113,7 +51193,7 @@
     <row r="298">
       <c r="A298" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 02:41:55</t>
+          <t>2026-02-01 17:41:55</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
@@ -51175,7 +51255,7 @@
     <row r="299">
       <c r="A299" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 02:09:57</t>
+          <t>2026-02-01 17:09:57</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
@@ -51237,7 +51317,7 @@
     <row r="300">
       <c r="A300" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 01:41:49</t>
+          <t>2026-02-01 16:41:49</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
@@ -51299,7 +51379,7 @@
     <row r="301">
       <c r="A301" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 02:22:13</t>
+          <t>2026-01-31 17:22:13</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
@@ -51361,7 +51441,7 @@
     <row r="302">
       <c r="A302" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 01:20:54</t>
+          <t>2026-01-31 16:20:54</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
@@ -51423,7 +51503,7 @@
     <row r="303">
       <c r="A303" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 01:09:32</t>
+          <t>2026-01-31 16:09:32</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
@@ -51485,7 +51565,7 @@
     <row r="304">
       <c r="A304" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 00:29:37</t>
+          <t>2026-01-31 15:29:37</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
@@ -51547,7 +51627,7 @@
     <row r="305">
       <c r="A305" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 00:03:50</t>
+          <t>2026-01-31 15:03:50</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
@@ -51609,7 +51689,7 @@
     <row r="306">
       <c r="A306" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 23:15:28</t>
+          <t>2026-01-31 14:15:28</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
@@ -51671,7 +51751,7 @@
     <row r="307">
       <c r="A307" s="13" t="inlineStr">
         <is>
-          <t>2026-01-29 00:36:39</t>
+          <t>2026-01-28 15:36:39</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
@@ -51733,7 +51813,7 @@
     <row r="308">
       <c r="A308" s="13" t="inlineStr">
         <is>
-          <t>2026-01-29 00:02:45</t>
+          <t>2026-01-28 15:02:45</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
@@ -51795,7 +51875,7 @@
     <row r="309">
       <c r="A309" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 23:26:47</t>
+          <t>2026-01-28 14:26:47</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
@@ -51857,7 +51937,7 @@
     <row r="310">
       <c r="A310" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 23:04:33</t>
+          <t>2026-01-28 14:04:33</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
@@ -51919,7 +51999,7 @@
     <row r="311">
       <c r="A311" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 00:33:31</t>
+          <t>2026-01-27 15:33:31</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
@@ -51981,7 +52061,7 @@
     <row r="312">
       <c r="A312" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 23:59:21</t>
+          <t>2026-01-27 14:59:21</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
@@ -52043,7 +52123,7 @@
     <row r="313">
       <c r="A313" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 23:08:33</t>
+          <t>2026-01-27 14:08:33</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
@@ -52105,7 +52185,7 @@
     <row r="314">
       <c r="A314" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 23:28:17</t>
+          <t>2026-01-25 14:28:17</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
@@ -52167,7 +52247,7 @@
     <row r="315">
       <c r="A315" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 22:56:22</t>
+          <t>2026-01-25 13:56:22</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
@@ -52229,7 +52309,7 @@
     <row r="316">
       <c r="A316" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 22:28:25</t>
+          <t>2026-01-25 13:28:25</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
@@ -52291,7 +52371,7 @@
     <row r="317">
       <c r="A317" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 21:42:03</t>
+          <t>2026-01-25 12:42:03</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
@@ -52353,7 +52433,7 @@
     <row r="318">
       <c r="A318" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 19:38:23</t>
+          <t>2026-01-25 10:38:23</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
@@ -52415,7 +52495,7 @@
     <row r="319">
       <c r="A319" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 18:56:35</t>
+          <t>2026-01-25 09:56:35</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
@@ -52477,7 +52557,7 @@
     <row r="320">
       <c r="A320" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 18:29:19</t>
+          <t>2026-01-25 09:29:19</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
@@ -52539,7 +52619,7 @@
     <row r="321">
       <c r="A321" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 17:14:05</t>
+          <t>2026-01-25 08:14:05</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
@@ -52601,7 +52681,7 @@
     <row r="322">
       <c r="A322" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 02:47:24</t>
+          <t>2026-01-23 17:47:24</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
@@ -52663,7 +52743,7 @@
     <row r="323">
       <c r="A323" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 02:12:26</t>
+          <t>2026-01-23 17:12:26</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
@@ -52725,7 +52805,7 @@
     <row r="324">
       <c r="A324" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 01:33:34</t>
+          <t>2026-01-23 16:33:34</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
@@ -52787,7 +52867,7 @@
     <row r="325">
       <c r="A325" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 01:00:39</t>
+          <t>2026-01-23 16:00:39</t>
         </is>
       </c>
       <c r="B325" s="13" t="inlineStr">
@@ -52849,7 +52929,7 @@
     <row r="326">
       <c r="A326" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 00:19:07</t>
+          <t>2026-01-23 15:19:07</t>
         </is>
       </c>
       <c r="B326" s="13" t="inlineStr">
@@ -52911,7 +52991,7 @@
     <row r="327">
       <c r="A327" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 23:52:33</t>
+          <t>2026-01-23 14:52:33</t>
         </is>
       </c>
       <c r="B327" s="13" t="inlineStr">
@@ -52973,7 +53053,7 @@
     <row r="328">
       <c r="A328" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 23:19:19</t>
+          <t>2026-01-23 14:19:19</t>
         </is>
       </c>
       <c r="B328" s="13" t="inlineStr">
@@ -53035,7 +53115,7 @@
     <row r="329">
       <c r="A329" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36:59</t>
+          <t>2026-01-23 13:36:59</t>
         </is>
       </c>
       <c r="B329" s="13" t="inlineStr">
@@ -53097,7 +53177,7 @@
     <row r="330">
       <c r="A330" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 03:01:58</t>
+          <t>2026-01-22 18:01:58</t>
         </is>
       </c>
       <c r="B330" s="13" t="inlineStr">
@@ -53159,7 +53239,7 @@
     <row r="331">
       <c r="A331" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 02:25:41</t>
+          <t>2026-01-22 17:25:41</t>
         </is>
       </c>
       <c r="B331" s="13" t="inlineStr">
@@ -53221,7 +53301,7 @@
     <row r="332">
       <c r="A332" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 00:32:45</t>
+          <t>2026-01-22 15:32:45</t>
         </is>
       </c>
       <c r="B332" s="13" t="inlineStr">
@@ -53283,7 +53363,7 @@
     <row r="333">
       <c r="A333" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 23:54:46</t>
+          <t>2026-01-22 14:54:46</t>
         </is>
       </c>
       <c r="B333" s="13" t="inlineStr">
@@ -53345,7 +53425,7 @@
     <row r="334">
       <c r="A334" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 23:17:42</t>
+          <t>2026-01-22 14:17:42</t>
         </is>
       </c>
       <c r="B334" s="13" t="inlineStr">
@@ -53407,7 +53487,7 @@
     <row r="335">
       <c r="A335" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 01:10:08</t>
+          <t>2026-01-21 16:10:08</t>
         </is>
       </c>
       <c r="B335" s="13" t="inlineStr">
@@ -53469,7 +53549,7 @@
     <row r="336">
       <c r="A336" s="13" t="inlineStr">
         <is>
-          <t>2026-01-21 00:27:51</t>
+          <t>2026-01-20 15:27:51</t>
         </is>
       </c>
       <c r="B336" s="13" t="inlineStr">
@@ -53531,7 +53611,7 @@
     <row r="337">
       <c r="A337" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 23:25:34</t>
+          <t>2026-01-20 14:25:34</t>
         </is>
       </c>
       <c r="B337" s="13" t="inlineStr">
@@ -53593,7 +53673,7 @@
     <row r="338">
       <c r="A338" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 22:56:13</t>
+          <t>2026-01-20 13:56:13</t>
         </is>
       </c>
       <c r="B338" s="13" t="inlineStr">
@@ -53655,7 +53735,7 @@
     <row r="339">
       <c r="A339" s="13" t="inlineStr">
         <is>
-          <t>2026-01-19 01:59:11</t>
+          <t>2026-01-18 16:59:11</t>
         </is>
       </c>
       <c r="B339" s="13" t="inlineStr">
@@ -53717,7 +53797,7 @@
     <row r="340">
       <c r="A340" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 03:05:32</t>
+          <t>2026-01-17 18:05:32</t>
         </is>
       </c>
       <c r="B340" s="13" t="inlineStr">
@@ -53779,7 +53859,7 @@
     <row r="341">
       <c r="A341" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 02:19:17</t>
+          <t>2026-01-17 17:19:17</t>
         </is>
       </c>
       <c r="B341" s="13" t="inlineStr">
@@ -53841,7 +53921,7 @@
     <row r="342">
       <c r="A342" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 01:58:17</t>
+          <t>2026-01-17 16:58:17</t>
         </is>
       </c>
       <c r="B342" s="13" t="inlineStr">
@@ -53903,7 +53983,7 @@
     <row r="343">
       <c r="A343" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 01:18:29</t>
+          <t>2026-01-17 16:18:29</t>
         </is>
       </c>
       <c r="B343" s="13" t="inlineStr">
@@ -53965,7 +54045,7 @@
     <row r="344">
       <c r="A344" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 00:38:58</t>
+          <t>2026-01-17 15:38:58</t>
         </is>
       </c>
       <c r="B344" s="13" t="inlineStr">
@@ -54027,7 +54107,7 @@
     <row r="345">
       <c r="A345" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 18:46:30</t>
+          <t>2026-01-17 09:46:30</t>
         </is>
       </c>
       <c r="B345" s="13" t="inlineStr">
@@ -54089,7 +54169,7 @@
     <row r="346">
       <c r="A346" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 02:21:36</t>
+          <t>2026-01-16 17:21:36</t>
         </is>
       </c>
       <c r="B346" s="13" t="inlineStr">
@@ -54151,7 +54231,7 @@
     <row r="347">
       <c r="A347" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 01:51:05</t>
+          <t>2026-01-16 16:51:05</t>
         </is>
       </c>
       <c r="B347" s="13" t="inlineStr">
@@ -54213,7 +54293,7 @@
     <row r="348">
       <c r="A348" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 01:18:22</t>
+          <t>2026-01-16 16:18:22</t>
         </is>
       </c>
       <c r="B348" s="13" t="inlineStr">
@@ -54275,7 +54355,7 @@
     <row r="349">
       <c r="A349" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 01:41:15</t>
+          <t>2026-01-15 16:41:15</t>
         </is>
       </c>
       <c r="B349" s="13" t="inlineStr">
@@ -54337,7 +54417,7 @@
     <row r="350">
       <c r="A350" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 01:05:38</t>
+          <t>2026-01-15 16:05:38</t>
         </is>
       </c>
       <c r="B350" s="13" t="inlineStr">
@@ -54399,7 +54479,7 @@
     <row r="351">
       <c r="A351" s="13" t="inlineStr">
         <is>
-          <t>2026-01-14 00:57:21</t>
+          <t>2026-01-13 15:57:21</t>
         </is>
       </c>
       <c r="B351" s="13" t="inlineStr">
@@ -54461,7 +54541,7 @@
     <row r="352">
       <c r="A352" s="13" t="inlineStr">
         <is>
-          <t>2026-01-14 00:19:49</t>
+          <t>2026-01-13 15:19:49</t>
         </is>
       </c>
       <c r="B352" s="13" t="inlineStr">
@@ -54523,7 +54603,7 @@
     <row r="353">
       <c r="A353" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 23:53:29</t>
+          <t>2026-01-13 14:53:29</t>
         </is>
       </c>
       <c r="B353" s="13" t="inlineStr">
@@ -54585,7 +54665,7 @@
     <row r="354">
       <c r="A354" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 02:23:29</t>
+          <t>2026-01-12 17:23:29</t>
         </is>
       </c>
       <c r="B354" s="13" t="inlineStr">
@@ -54647,7 +54727,7 @@
     <row r="355">
       <c r="A355" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 01:42:12</t>
+          <t>2026-01-12 16:42:12</t>
         </is>
       </c>
       <c r="B355" s="13" t="inlineStr">
@@ -54709,7 +54789,7 @@
     <row r="356">
       <c r="A356" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 01:17:01</t>
+          <t>2026-01-12 16:17:01</t>
         </is>
       </c>
       <c r="B356" s="13" t="inlineStr">
@@ -54771,7 +54851,7 @@
     <row r="357">
       <c r="A357" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 00:43:11</t>
+          <t>2026-01-12 15:43:11</t>
         </is>
       </c>
       <c r="B357" s="13" t="inlineStr">
@@ -54833,7 +54913,7 @@
     <row r="358">
       <c r="A358" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 17:24:44</t>
+          <t>2026-01-12 08:24:44</t>
         </is>
       </c>
       <c r="B358" s="13" t="inlineStr">
@@ -54895,7 +54975,7 @@
     <row r="359">
       <c r="A359" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 03:12:16</t>
+          <t>2026-01-11 18:12:16</t>
         </is>
       </c>
       <c r="B359" s="13" t="inlineStr">
@@ -54957,7 +55037,7 @@
     <row r="360">
       <c r="A360" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 02:54:03</t>
+          <t>2026-01-10 17:54:03</t>
         </is>
       </c>
       <c r="B360" s="13" t="inlineStr">
@@ -55019,7 +55099,7 @@
     <row r="361">
       <c r="A361" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 02:14:56</t>
+          <t>2026-01-10 17:14:56</t>
         </is>
       </c>
       <c r="B361" s="13" t="inlineStr">
@@ -55081,7 +55161,7 @@
     <row r="362">
       <c r="A362" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 01:17:21</t>
+          <t>2026-01-10 16:17:21</t>
         </is>
       </c>
       <c r="B362" s="13" t="inlineStr">
@@ -55143,7 +55223,7 @@
     <row r="363">
       <c r="A363" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 00:22:11</t>
+          <t>2026-01-10 15:22:11</t>
         </is>
       </c>
       <c r="B363" s="13" t="inlineStr">
@@ -55205,7 +55285,7 @@
     <row r="364">
       <c r="A364" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 23:38:24</t>
+          <t>2026-01-10 14:38:24</t>
         </is>
       </c>
       <c r="B364" s="13" t="inlineStr">
@@ -55267,7 +55347,7 @@
     <row r="365">
       <c r="A365" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 02:54:19</t>
+          <t>2026-01-09 17:54:19</t>
         </is>
       </c>
       <c r="B365" s="13" t="inlineStr">
@@ -55329,7 +55409,7 @@
     <row r="366">
       <c r="A366" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 02:00:16</t>
+          <t>2026-01-09 17:00:16</t>
         </is>
       </c>
       <c r="B366" s="13" t="inlineStr">
@@ -55391,7 +55471,7 @@
     <row r="367">
       <c r="A367" s="13" t="inlineStr">
         <is>
-          <t>2026-01-09 23:36:27</t>
+          <t>2026-01-09 14:36:27</t>
         </is>
       </c>
       <c r="B367" s="13" t="inlineStr">
@@ -55450,8 +55530,70 @@
         </is>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-05 14:21:47</t>
+        </is>
+      </c>
+      <c r="B368" s="13" t="inlineStr">
+        <is>
+          <t>ランク</t>
+        </is>
+      </c>
+      <c r="C368" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D368" s="13" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E368" s="13" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F368" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G368" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H368" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I368" s="13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J368" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K368" s="14" t="inlineStr"/>
+      <c r="L368" s="14" t="inlineStr"/>
+      <c r="M368" s="14" t="inlineStr"/>
+      <c r="N368" s="14" t="inlineStr"/>
+      <c r="O368" s="14" t="inlineStr"/>
+      <c r="P368" s="13" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P367"/>
+  <autoFilter ref="A1:P368"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-07-30 10:04:01</t>
+          <t>出力日時：2026-07-31 11:06:10</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'キュー別'!$A$1:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'チャンピオン別'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SUPチャンピオン別'!$A$1:$L$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$375</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$375</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$376</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$376</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,14 +532,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>対象期間：2026-01-09 23:36:27 ～ 2026-08-01 04:00:11</t>
+          <t>対象期間：2026-01-05 14:21:47 ～ 2026-07-31 19:00:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-01 04:35:56</t>
+          <t>出力日時：2026-08-01 08:58:22</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.4786096256684492</v>
+        <v>0.4773333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.671122994652406</v>
+        <v>1.666666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5.328877005347594</v>
+        <v>5.328</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>8.909090909090908</v>
+        <v>8.909333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.98</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>60.24331550802139</v>
+        <v>60.176</v>
       </c>
     </row>
     <row r="15">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2.055427807486631</v>
+        <v>2.053040000000001</v>
       </c>
     </row>
     <row r="16">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>56.44385026737968</v>
+        <v>56.41333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1.82283422459893</v>
+        <v>1.821973333333332</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.5102739726027398</v>
+        <v>0.5085324232081911</v>
       </c>
     </row>
     <row r="24">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>1.445205479452055</v>
+        <v>1.440273037542662</v>
       </c>
     </row>
     <row r="25">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.157534246575342</v>
+        <v>5.156996587030717</v>
       </c>
     </row>
     <row r="26">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>9.808219178082192</v>
+        <v>9.805460750853243</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>36.19520547945206</v>
+        <v>36.19112627986348</v>
       </c>
     </row>
     <row r="29">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1.251369863013698</v>
+        <v>1.251058020477816</v>
       </c>
     </row>
     <row r="30">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>63.82191780821918</v>
+        <v>63.75767918088737</v>
       </c>
     </row>
     <row r="31">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>2.060034246575342</v>
+        <v>2.058122866894197</v>
       </c>
     </row>
   </sheetData>
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>149</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.5102739726027398</v>
+        <v>0.5085324232081911</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.445205479452055</v>
+        <v>1.440273037542662</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5.157534246575342</v>
+        <v>5.156996587030717</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9.808219178082192</v>
+        <v>9.805460750853243</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.251369863013698</v>
+        <v>1.251058020477816</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>63.82191780821918</v>
+        <v>63.75767918088737</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>2.060034246575342</v>
+        <v>2.058122866894197</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.933833333333333</v>
+        <v>4.933833333333332</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>31.96666666666667</v>
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>2.242894736842105</v>
+        <v>2.242894736842106</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>53.4078947368421</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>1.735427631578948</v>
+        <v>1.735427631578947</v>
       </c>
     </row>
     <row r="3">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>31</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.4428571428571428</v>
+        <v>0.4366197183098591</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.128571428571429</v>
+        <v>1.112676056338028</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>5.757142857142857</v>
+        <v>5.746478873239437</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>9.942857142857143</v>
+        <v>9.929577464788732</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.241285714285714</v>
+        <v>1.240140845070422</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>69.62857142857143</v>
+        <v>69.28169014084507</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.202428571428571</v>
+        <v>2.192535211267606</v>
       </c>
     </row>
   </sheetData>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1.797111111111111</v>
+        <v>1.797111111111112</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>68.51111111111111</v>
@@ -1516,25 +1516,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.775</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.153846153846154</v>
+        <v>5.15</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.17948717948718</v>
+        <v>7.225</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.232820512820513</v>
+        <v>1.231</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.97435897435897</v>
+        <v>53.75</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.871025641025641</v>
+        <v>1.86175</v>
       </c>
     </row>
     <row r="6">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5.148285714285715</v>
+        <v>5.148285714285714</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>34.6</v>
@@ -1800,7 +1800,7 @@
         <v>25.625</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.85625</v>
+        <v>0.8562500000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1842,7 +1842,7 @@
         <v>21.83333333333333</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.8633333333333333</v>
+        <v>0.8633333333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5.050000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>16.25</v>
@@ -2833,25 +2833,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.775</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.153846153846154</v>
+        <v>5.15</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.17948717948718</v>
+        <v>7.225</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.232820512820513</v>
+        <v>1.231</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.97435897435897</v>
+        <v>53.75</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.871025641025641</v>
+        <v>1.86175</v>
       </c>
     </row>
     <row r="6">
@@ -3224,7 +3224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V375"/>
+  <dimension ref="A1:V376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3366,7 +3366,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 04:00:11</t>
+          <t>2026-07-31 19:00:11</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 03:30:26</t>
+          <t>2026-07-31 18:30:26</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 02:52:16</t>
+          <t>2026-07-31 17:52:16</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 01:50:20</t>
+          <t>2026-07-31 16:50:20</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 01:16:45</t>
+          <t>2026-07-31 16:16:45</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 22:56:19</t>
+          <t>2026-07-31 13:56:19</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 22:22:46</t>
+          <t>2026-07-31 13:22:46</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 21:49:35</t>
+          <t>2026-07-31 12:49:35</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 23:51:39</t>
+          <t>2026-07-28 14:51:39</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 23:05:20</t>
+          <t>2026-07-28 14:05:20</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -4166,7 +4166,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27 01:21:51</t>
+          <t>2026-07-26 16:21:51</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27 00:43:02</t>
+          <t>2026-07-26 15:43:02</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -4326,7 +4326,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 23:12:09</t>
+          <t>2026-07-25 14:12:09</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 22:30:57</t>
+          <t>2026-07-25 13:30:57</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -4486,7 +4486,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 00:11:55</t>
+          <t>2026-07-24 15:11:55</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -4566,7 +4566,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24 23:25:38</t>
+          <t>2026-07-24 14:25:38</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -4646,7 +4646,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22 00:17:56</t>
+          <t>2026-07-21 15:17:56</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22 00:04:35</t>
+          <t>2026-07-21 15:04:35</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 23:25:56</t>
+          <t>2026-07-21 14:25:56</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -4886,7 +4886,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 22:44:36</t>
+          <t>2026-07-21 13:44:36</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -4966,7 +4966,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 22:18:59</t>
+          <t>2026-07-21 13:18:59</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20 03:20:20</t>
+          <t>2026-07-19 18:20:20</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -5126,7 +5126,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20 02:39:51</t>
+          <t>2026-07-19 17:39:51</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:59:14</t>
+          <t>2026-07-18 09:59:14</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -5286,7 +5286,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:21:14</t>
+          <t>2026-07-18 09:21:14</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -5366,7 +5366,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 23:06:28</t>
+          <t>2026-07-16 14:06:28</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 22:32:42</t>
+          <t>2026-07-16 13:32:42</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -5526,7 +5526,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 00:40:48</t>
+          <t>2026-07-15 15:40:48</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -5606,7 +5606,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 23:41:56</t>
+          <t>2026-07-15 14:41:56</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 22:58:44</t>
+          <t>2026-07-15 13:58:44</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -5766,7 +5766,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 22:34:16</t>
+          <t>2026-07-15 13:34:16</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -5846,7 +5846,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 23:36:35</t>
+          <t>2026-07-14 14:36:35</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -5926,7 +5926,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 22:49:50</t>
+          <t>2026-07-14 13:49:50</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -6006,7 +6006,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 01:02:29</t>
+          <t>2026-07-13 16:02:29</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 00:22:46</t>
+          <t>2026-07-13 15:22:46</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 23:51:38</t>
+          <t>2026-07-13 14:51:38</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 02:05:19</t>
+          <t>2026-07-12 17:05:19</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -6326,7 +6326,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 01:29:17</t>
+          <t>2026-07-12 16:29:17</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -6406,7 +6406,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 03:11:38</t>
+          <t>2026-07-11 18:11:38</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -6486,7 +6486,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 02:46:15</t>
+          <t>2026-07-11 17:46:15</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -6566,7 +6566,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 03:42:29</t>
+          <t>2026-07-10 18:42:29</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -6646,7 +6646,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 03:06:21</t>
+          <t>2026-07-10 18:06:21</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -6726,7 +6726,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:55:25</t>
+          <t>2026-07-08 17:55:25</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -6806,7 +6806,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:17:09</t>
+          <t>2026-07-08 17:17:09</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -6886,7 +6886,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 02:03:51</t>
+          <t>2026-07-05 17:03:51</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -6966,7 +6966,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 01:07:17</t>
+          <t>2026-07-05 16:07:17</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 00:23:00</t>
+          <t>2026-07-05 15:23:00</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -7126,7 +7126,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05 03:21:23</t>
+          <t>2026-07-04 18:21:23</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-07-04 03:01:40</t>
+          <t>2026-07-03 18:01:40</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -7286,7 +7286,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03 01:48:19</t>
+          <t>2026-07-02 16:48:19</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -7366,7 +7366,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01 00:21:19</t>
+          <t>2026-06-30 15:21:19</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -7446,7 +7446,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 23:38:16</t>
+          <t>2026-06-30 14:38:16</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -7526,7 +7526,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 01:16:28</t>
+          <t>2026-06-29 16:16:28</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 00:34:32</t>
+          <t>2026-06-29 15:34:32</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -7686,7 +7686,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26 00:50:56</t>
+          <t>2026-06-25 15:50:56</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -7766,7 +7766,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26 00:06:40</t>
+          <t>2026-06-25 15:06:40</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -7846,7 +7846,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07:56</t>
+          <t>2026-06-24 17:07:56</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -7926,7 +7926,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 01:33:19</t>
+          <t>2026-06-24 16:33:19</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -8006,7 +8006,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:47:59</t>
+          <t>2026-06-24 15:47:59</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -8086,7 +8086,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:08:31</t>
+          <t>2026-06-24 15:08:31</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 23:33:15</t>
+          <t>2026-06-24 14:33:15</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -8246,7 +8246,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 22:39:11</t>
+          <t>2026-06-24 13:39:11</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -8326,7 +8326,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 01:16:06</t>
+          <t>2026-06-22 16:16:06</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -8406,7 +8406,7 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 00:38:08</t>
+          <t>2026-06-22 15:38:08</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -8486,7 +8486,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 00:29:33</t>
+          <t>2026-06-22 15:29:33</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -8566,7 +8566,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 01:54:04</t>
+          <t>2026-06-18 16:54:04</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 01:14:50</t>
+          <t>2026-06-18 16:14:50</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 00:35:17</t>
+          <t>2026-06-18 15:35:17</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -8806,7 +8806,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 23:55:50</t>
+          <t>2026-06-18 14:55:50</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -8886,7 +8886,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 00:44:42</t>
+          <t>2026-06-17 15:44:42</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -8966,7 +8966,7 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 23:57:38</t>
+          <t>2026-06-17 14:57:38</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -9046,7 +9046,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 01:58:55</t>
+          <t>2026-06-16 16:58:55</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -9126,7 +9126,7 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 01:30:07</t>
+          <t>2026-06-16 16:30:07</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -9206,7 +9206,7 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 03:10:28</t>
+          <t>2026-06-14 18:10:28</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
@@ -9286,7 +9286,7 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 02:27:52</t>
+          <t>2026-06-14 17:27:52</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -9366,7 +9366,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 01:57:23</t>
+          <t>2026-06-14 16:57:23</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -9446,7 +9446,7 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 01:27:22</t>
+          <t>2026-06-14 16:27:22</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -9526,7 +9526,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 00:24:35</t>
+          <t>2026-06-14 15:24:35</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -9606,7 +9606,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 23:46:55</t>
+          <t>2026-06-14 14:46:55</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -9686,7 +9686,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 01:41:53</t>
+          <t>2026-06-13 16:41:53</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -9766,7 +9766,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 00:52:58</t>
+          <t>2026-06-13 15:52:58</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -9846,7 +9846,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 00:14:23</t>
+          <t>2026-06-13 15:14:23</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -9926,7 +9926,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 23:45:21</t>
+          <t>2026-06-13 14:45:21</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -10006,7 +10006,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 23:05:32</t>
+          <t>2026-06-13 14:05:32</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -10086,7 +10086,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 01:08:14</t>
+          <t>2026-06-10 16:08:14</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -10166,7 +10166,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:34:35</t>
+          <t>2026-06-10 15:34:35</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:09:17</t>
+          <t>2026-06-10 15:09:17</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -10326,7 +10326,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 23:27:53</t>
+          <t>2026-06-10 14:27:53</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 00:49:00</t>
+          <t>2026-06-09 15:49:00</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -10486,7 +10486,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06 02:58:51</t>
+          <t>2026-06-05 17:58:51</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -10566,7 +10566,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06 02:15:04</t>
+          <t>2026-06-05 17:15:04</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -10646,7 +10646,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 23:49:14</t>
+          <t>2026-06-04 14:49:14</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -10726,7 +10726,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 21:40:04</t>
+          <t>2026-06-04 12:40:04</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -10806,7 +10806,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 21:17:24</t>
+          <t>2026-06-04 12:17:24</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -10886,7 +10886,7 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 01:06:27</t>
+          <t>2026-06-03 16:06:27</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -10966,7 +10966,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 00:31:09</t>
+          <t>2026-06-03 15:31:09</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -11046,7 +11046,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 23:53:57</t>
+          <t>2026-06-03 14:53:57</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -11126,7 +11126,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 22:44:02</t>
+          <t>2026-06-03 13:44:02</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02 22:49:11</t>
+          <t>2026-06-02 13:49:11</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -11286,7 +11286,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:56:06</t>
+          <t>2026-06-01 14:56:06</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -11366,7 +11366,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:20:26</t>
+          <t>2026-06-01 14:20:26</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -11446,7 +11446,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:01:06</t>
+          <t>2026-06-01 14:01:06</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -11526,7 +11526,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31 03:01:04</t>
+          <t>2026-05-30 18:01:04</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31 02:13:41</t>
+          <t>2026-05-30 17:13:41</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -11686,7 +11686,7 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 23:00:40</t>
+          <t>2026-05-25 14:00:40</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -11766,7 +11766,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 01:55:47</t>
+          <t>2026-05-24 16:55:47</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -11846,7 +11846,7 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 01:24:22</t>
+          <t>2026-05-24 16:24:22</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -11926,7 +11926,7 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 23:49:25</t>
+          <t>2026-05-24 14:49:25</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -12006,7 +12006,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 03:13:39</t>
+          <t>2026-05-23 18:13:39</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 02:41:52</t>
+          <t>2026-05-23 17:41:52</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -12166,7 +12166,7 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 23:19:04</t>
+          <t>2026-05-23 14:19:04</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -12246,7 +12246,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 22:43:20</t>
+          <t>2026-05-23 13:43:20</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -12326,7 +12326,7 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 15:54:19</t>
+          <t>2026-05-23 06:54:19</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -12406,7 +12406,7 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 02:25:24</t>
+          <t>2026-05-22 17:25:24</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -12486,7 +12486,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 01:29:23</t>
+          <t>2026-05-21 16:29:23</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -12566,7 +12566,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 00:48:49</t>
+          <t>2026-05-21 15:48:49</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -12646,7 +12646,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:45</t>
+          <t>2026-05-21 15:00:45</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -12726,7 +12726,7 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 23:22:44</t>
+          <t>2026-05-21 14:22:44</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -12806,7 +12806,7 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 00:05:15</t>
+          <t>2026-05-20 15:05:15</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -12886,7 +12886,7 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 23:43:50</t>
+          <t>2026-05-20 14:43:50</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -12966,7 +12966,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 22:57:45</t>
+          <t>2026-05-20 13:57:45</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -13046,7 +13046,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 01:25:45</t>
+          <t>2026-05-19 16:25:45</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -13126,7 +13126,7 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 00:46:42</t>
+          <t>2026-05-19 15:46:42</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -13206,7 +13206,7 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>2026-05-18 22:56:39</t>
+          <t>2026-05-18 13:56:39</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -13286,7 +13286,7 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 01:35:56</t>
+          <t>2026-05-14 16:35:56</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -13366,7 +13366,7 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 01:17:05</t>
+          <t>2026-05-14 16:17:05</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -13446,7 +13446,7 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 00:05:48</t>
+          <t>2026-05-14 15:05:48</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -13526,7 +13526,7 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14 01:25:38</t>
+          <t>2026-05-13 16:25:38</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -13606,7 +13606,7 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>2026-05-12 00:19:57</t>
+          <t>2026-05-11 15:19:57</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -13686,7 +13686,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 23:54:15</t>
+          <t>2026-05-11 14:54:15</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 23:14:30</t>
+          <t>2026-05-11 14:14:30</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -13846,7 +13846,7 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 22:37:05</t>
+          <t>2026-05-11 13:37:05</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -13926,7 +13926,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 21:53:13</t>
+          <t>2026-05-11 12:53:13</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -14006,7 +14006,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 00:04:01</t>
+          <t>2026-05-10 15:04:01</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -14086,7 +14086,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:54:24</t>
+          <t>2026-05-09 16:54:24</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -14166,7 +14166,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:22:50</t>
+          <t>2026-05-09 16:22:50</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -14246,7 +14246,7 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 00:26:16</t>
+          <t>2026-05-09 15:26:16</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -14326,7 +14326,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 23:38:30</t>
+          <t>2026-05-09 14:38:30</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -14406,7 +14406,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 22:50:20</t>
+          <t>2026-05-09 13:50:20</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -14486,7 +14486,7 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 22:13:25</t>
+          <t>2026-05-09 13:13:25</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -14566,7 +14566,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 20:00:11</t>
+          <t>2026-05-09 11:00:11</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -14646,7 +14646,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 19:10:28</t>
+          <t>2026-05-09 10:10:28</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -14726,7 +14726,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 02:17:27</t>
+          <t>2026-05-08 17:17:27</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -14806,7 +14806,7 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 01:38:25</t>
+          <t>2026-05-08 16:38:25</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -14886,7 +14886,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 00:58:58</t>
+          <t>2026-05-08 15:58:58</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -14966,7 +14966,7 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 00:37:55</t>
+          <t>2026-05-08 15:37:55</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -15046,7 +15046,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 01:48:31</t>
+          <t>2026-05-07 16:48:31</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -15126,7 +15126,7 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 01:02:52</t>
+          <t>2026-05-07 16:02:52</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -15206,7 +15206,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 00:23:29</t>
+          <t>2026-05-07 15:23:29</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -15286,7 +15286,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 01:30:56</t>
+          <t>2026-05-06 16:30:56</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -15366,7 +15366,7 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 00:42:16</t>
+          <t>2026-05-06 15:42:16</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 23:44:04</t>
+          <t>2026-05-06 14:44:04</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -15526,7 +15526,7 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:13:52</t>
+          <t>2026-05-06 09:13:52</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -15606,7 +15606,7 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:05:08</t>
+          <t>2026-05-06 09:05:08</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -15686,7 +15686,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 17:22:30</t>
+          <t>2026-05-06 08:22:30</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -15766,7 +15766,7 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 16:28:42</t>
+          <t>2026-05-06 07:28:42</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -15846,7 +15846,7 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 03:16:57</t>
+          <t>2026-05-05 18:16:57</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -15926,7 +15926,7 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:32:40</t>
+          <t>2026-05-05 17:32:40</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:23:28</t>
+          <t>2026-05-05 17:23:28</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -16086,7 +16086,7 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 01:48:28</t>
+          <t>2026-05-05 16:48:28</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -16166,7 +16166,7 @@
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 00:52:33</t>
+          <t>2026-05-05 15:52:33</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -16246,7 +16246,7 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 17:43:06</t>
+          <t>2026-05-05 08:43:06</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -16326,7 +16326,7 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>2026-05-03 00:36:42</t>
+          <t>2026-05-02 15:36:42</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -16406,7 +16406,7 @@
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 23:51:09</t>
+          <t>2026-05-02 14:51:09</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -16486,7 +16486,7 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 22:15:10</t>
+          <t>2026-05-02 13:15:10</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -16566,7 +16566,7 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 21:29:49</t>
+          <t>2026-05-02 12:29:49</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -16646,7 +16646,7 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 01:39:42</t>
+          <t>2026-04-30 16:39:42</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -16726,7 +16726,7 @@
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 01:01:34</t>
+          <t>2026-04-30 16:01:34</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -16806,7 +16806,7 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 00:24:48</t>
+          <t>2026-04-30 15:24:48</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -16886,7 +16886,7 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 23:37:10</t>
+          <t>2026-04-30 14:37:10</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
@@ -16966,7 +16966,7 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 22:58:06</t>
+          <t>2026-04-30 13:58:06</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -17046,7 +17046,7 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 03:29:33</t>
+          <t>2026-04-29 18:29:33</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 02:54:07</t>
+          <t>2026-04-29 17:54:07</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
@@ -17206,7 +17206,7 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 02:20:58</t>
+          <t>2026-04-29 17:20:58</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -17286,7 +17286,7 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 01:42:01</t>
+          <t>2026-04-29 16:42:01</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
@@ -17366,7 +17366,7 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 01:03:17</t>
+          <t>2026-04-29 16:03:17</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -17446,7 +17446,7 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 00:19:47</t>
+          <t>2026-04-29 15:19:47</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -17526,7 +17526,7 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 23:29:53</t>
+          <t>2026-04-29 14:29:53</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
@@ -17606,7 +17606,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:59:49</t>
+          <t>2026-04-29 13:59:49</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -17686,7 +17686,7 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:38:22</t>
+          <t>2026-04-29 13:38:22</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
@@ -17766,7 +17766,7 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:44</t>
+          <t>2026-04-29 13:17:44</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
@@ -17846,7 +17846,7 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 03:28:56</t>
+          <t>2026-04-28 18:28:56</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
@@ -17926,7 +17926,7 @@
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:58:50</t>
+          <t>2026-04-28 17:58:50</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
@@ -18006,7 +18006,7 @@
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:29:43</t>
+          <t>2026-04-28 17:29:43</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
@@ -18086,7 +18086,7 @@
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 01:38:43</t>
+          <t>2026-04-28 16:38:43</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
@@ -18166,7 +18166,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:54</t>
+          <t>2026-04-28 15:58:54</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
@@ -18246,7 +18246,7 @@
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:31:32</t>
+          <t>2026-04-28 15:31:32</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
@@ -18326,7 +18326,7 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:04:20</t>
+          <t>2026-04-28 15:04:20</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
@@ -18406,7 +18406,7 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 23:37:27</t>
+          <t>2026-04-28 14:37:27</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
@@ -18486,7 +18486,7 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 23:09:10</t>
+          <t>2026-04-28 14:09:10</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
@@ -18566,7 +18566,7 @@
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:59:25</t>
+          <t>2026-04-27 14:59:25</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -18646,7 +18646,7 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:49:35</t>
+          <t>2026-04-27 14:49:35</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
@@ -18726,7 +18726,7 @@
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 22:55:34</t>
+          <t>2026-04-27 13:55:34</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 22:04:13</t>
+          <t>2026-04-27 13:04:13</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
@@ -18886,7 +18886,7 @@
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 02:49:02</t>
+          <t>2026-04-24 17:49:02</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -18966,7 +18966,7 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 02:03:56</t>
+          <t>2026-04-24 17:03:56</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
@@ -19046,7 +19046,7 @@
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 01:37:00</t>
+          <t>2026-04-24 16:37:00</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -19126,7 +19126,7 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:33:59</t>
+          <t>2026-04-23 15:33:59</t>
         </is>
       </c>
       <c r="B199" s="7" t="inlineStr">
@@ -19206,7 +19206,7 @@
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:22:46</t>
+          <t>2026-04-23 15:22:46</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -19286,7 +19286,7 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:12:54</t>
+          <t>2026-04-23 15:12:54</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
@@ -19366,7 +19366,7 @@
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 22:36:03</t>
+          <t>2026-04-23 13:36:03</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -19446,7 +19446,7 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:58:57</t>
+          <t>2026-04-13 15:58:57</t>
         </is>
       </c>
       <c r="B203" s="7" t="inlineStr">
@@ -19526,7 +19526,7 @@
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:09:08</t>
+          <t>2026-04-13 15:09:08</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
@@ -19606,7 +19606,7 @@
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 01:48:02</t>
+          <t>2026-04-12 16:48:02</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
@@ -19686,7 +19686,7 @@
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 01:17:58</t>
+          <t>2026-04-12 16:17:58</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
@@ -19766,7 +19766,7 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 00:41:20</t>
+          <t>2026-04-12 15:41:20</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
@@ -19846,7 +19846,7 @@
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 23:18:06</t>
+          <t>2026-04-09 14:18:06</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -19926,7 +19926,7 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 22:52:44</t>
+          <t>2026-04-09 13:52:44</t>
         </is>
       </c>
       <c r="B209" s="7" t="inlineStr">
@@ -20006,7 +20006,7 @@
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 22:27:45</t>
+          <t>2026-04-09 13:27:45</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -20086,7 +20086,7 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>2026-04-08 01:10:31</t>
+          <t>2026-04-07 16:10:31</t>
         </is>
       </c>
       <c r="B211" s="7" t="inlineStr">
@@ -20166,7 +20166,7 @@
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>2026-04-08 00:29:19</t>
+          <t>2026-04-07 15:29:19</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
@@ -20246,7 +20246,7 @@
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>2026-04-04 04:36:31</t>
+          <t>2026-04-03 19:36:31</t>
         </is>
       </c>
       <c r="B213" s="7" t="inlineStr">
@@ -20326,7 +20326,7 @@
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>2026-04-04 04:16:32</t>
+          <t>2026-04-03 19:16:32</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
@@ -20406,7 +20406,7 @@
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 04:24:43</t>
+          <t>2026-03-27 19:24:43</t>
         </is>
       </c>
       <c r="B215" s="7" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 03:38:31</t>
+          <t>2026-03-27 18:38:31</t>
         </is>
       </c>
       <c r="B216" s="7" t="inlineStr">
@@ -20566,7 +20566,7 @@
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 03:17:50</t>
+          <t>2026-03-27 18:17:50</t>
         </is>
       </c>
       <c r="B217" s="7" t="inlineStr">
@@ -20646,7 +20646,7 @@
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 02:43:19</t>
+          <t>2026-03-27 17:43:19</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
@@ -20726,7 +20726,7 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 02:15:18</t>
+          <t>2026-03-27 17:15:18</t>
         </is>
       </c>
       <c r="B219" s="7" t="inlineStr">
@@ -20806,7 +20806,7 @@
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 23:18:12</t>
+          <t>2026-03-25 14:18:12</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
@@ -20886,7 +20886,7 @@
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 00:01:49</t>
+          <t>2026-03-24 15:01:49</t>
         </is>
       </c>
       <c r="B221" s="7" t="inlineStr">
@@ -20966,7 +20966,7 @@
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 23:25:16</t>
+          <t>2026-03-24 14:25:16</t>
         </is>
       </c>
       <c r="B222" s="7" t="inlineStr">
@@ -21046,7 +21046,7 @@
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 23:02:52</t>
+          <t>2026-03-24 14:02:52</t>
         </is>
       </c>
       <c r="B223" s="7" t="inlineStr">
@@ -21126,7 +21126,7 @@
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 22:26:26</t>
+          <t>2026-03-24 13:26:26</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -21206,7 +21206,7 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 00:56:18</t>
+          <t>2026-03-23 15:56:18</t>
         </is>
       </c>
       <c r="B225" s="7" t="inlineStr">
@@ -21286,7 +21286,7 @@
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 00:29:29</t>
+          <t>2026-03-23 15:29:29</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
@@ -21366,7 +21366,7 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 23:51:11</t>
+          <t>2026-03-22 14:51:11</t>
         </is>
       </c>
       <c r="B227" s="7" t="inlineStr">
@@ -21446,7 +21446,7 @@
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 01:04:36</t>
+          <t>2026-03-21 16:04:36</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
@@ -21526,7 +21526,7 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>2026-03-21 02:55:49</t>
+          <t>2026-03-20 17:55:49</t>
         </is>
       </c>
       <c r="B229" s="7" t="inlineStr">
@@ -21606,7 +21606,7 @@
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
         <is>
-          <t>2026-03-18 00:07:07</t>
+          <t>2026-03-17 15:07:07</t>
         </is>
       </c>
       <c r="B230" s="7" t="inlineStr">
@@ -21686,7 +21686,7 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 23:24:05</t>
+          <t>2026-03-17 14:24:05</t>
         </is>
       </c>
       <c r="B231" s="7" t="inlineStr">
@@ -21766,7 +21766,7 @@
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 02:00:50</t>
+          <t>2026-03-16 17:00:50</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
@@ -21846,7 +21846,7 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 01:33:08</t>
+          <t>2026-03-16 16:33:08</t>
         </is>
       </c>
       <c r="B233" s="7" t="inlineStr">
@@ -21926,7 +21926,7 @@
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 23:28:09</t>
+          <t>2026-03-16 14:28:09</t>
         </is>
       </c>
       <c r="B234" s="7" t="inlineStr">
@@ -22006,7 +22006,7 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 01:32:22</t>
+          <t>2026-03-15 16:32:22</t>
         </is>
       </c>
       <c r="B235" s="7" t="inlineStr">
@@ -22086,7 +22086,7 @@
     <row r="236">
       <c r="A236" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14 01:43:49</t>
+          <t>2026-03-13 16:43:49</t>
         </is>
       </c>
       <c r="B236" s="7" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14 01:19:35</t>
+          <t>2026-03-13 16:19:35</t>
         </is>
       </c>
       <c r="B237" s="7" t="inlineStr">
@@ -22246,7 +22246,7 @@
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 23:45:27</t>
+          <t>2026-03-12 14:45:27</t>
         </is>
       </c>
       <c r="B238" s="7" t="inlineStr">
@@ -22326,7 +22326,7 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 23:02:09</t>
+          <t>2026-03-12 14:02:09</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
@@ -22406,7 +22406,7 @@
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 22:42:59</t>
+          <t>2026-03-12 13:42:59</t>
         </is>
       </c>
       <c r="B240" s="7" t="inlineStr">
@@ -22486,7 +22486,7 @@
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 01:39:10</t>
+          <t>2026-03-11 16:39:10</t>
         </is>
       </c>
       <c r="B241" s="7" t="inlineStr">
@@ -22566,7 +22566,7 @@
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:43:21</t>
+          <t>2026-03-11 15:43:21</t>
         </is>
       </c>
       <c r="B242" s="7" t="inlineStr">
@@ -22646,7 +22646,7 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:04:25</t>
+          <t>2026-03-11 15:04:25</t>
         </is>
       </c>
       <c r="B243" s="7" t="inlineStr">
@@ -22726,7 +22726,7 @@
     <row r="244">
       <c r="A244" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 22:54:02</t>
+          <t>2026-03-11 13:54:02</t>
         </is>
       </c>
       <c r="B244" s="7" t="inlineStr">
@@ -22806,7 +22806,7 @@
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>2026-03-08 02:01:53</t>
+          <t>2026-03-07 17:01:53</t>
         </is>
       </c>
       <c r="B245" s="7" t="inlineStr">
@@ -22886,7 +22886,7 @@
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>2026-03-02 02:18:59</t>
+          <t>2026-03-01 17:18:59</t>
         </is>
       </c>
       <c r="B246" s="7" t="inlineStr">
@@ -22966,7 +22966,7 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>2026-02-24 01:40:38</t>
+          <t>2026-02-23 16:40:38</t>
         </is>
       </c>
       <c r="B247" s="7" t="inlineStr">
@@ -23046,7 +23046,7 @@
     <row r="248">
       <c r="A248" s="7" t="inlineStr">
         <is>
-          <t>2026-02-24 00:10:31</t>
+          <t>2026-02-23 15:10:31</t>
         </is>
       </c>
       <c r="B248" s="7" t="inlineStr">
@@ -23126,7 +23126,7 @@
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 23:33:47</t>
+          <t>2026-02-23 14:33:47</t>
         </is>
       </c>
       <c r="B249" s="7" t="inlineStr">
@@ -23206,7 +23206,7 @@
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 22:40:54</t>
+          <t>2026-02-23 13:40:54</t>
         </is>
       </c>
       <c r="B250" s="7" t="inlineStr">
@@ -23286,7 +23286,7 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 21:58:56</t>
+          <t>2026-02-23 12:58:56</t>
         </is>
       </c>
       <c r="B251" s="7" t="inlineStr">
@@ -23366,7 +23366,7 @@
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 19:21:48</t>
+          <t>2026-02-23 10:21:48</t>
         </is>
       </c>
       <c r="B252" s="7" t="inlineStr">
@@ -23446,7 +23446,7 @@
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 17:17:13</t>
+          <t>2026-02-23 08:17:13</t>
         </is>
       </c>
       <c r="B253" s="7" t="inlineStr">
@@ -23526,7 +23526,7 @@
     <row r="254">
       <c r="A254" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 04:22:01</t>
+          <t>2026-02-22 19:22:01</t>
         </is>
       </c>
       <c r="B254" s="7" t="inlineStr">
@@ -23606,7 +23606,7 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 03:23:51</t>
+          <t>2026-02-22 18:23:51</t>
         </is>
       </c>
       <c r="B255" s="7" t="inlineStr">
@@ -23686,7 +23686,7 @@
     <row r="256">
       <c r="A256" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 02:58:18</t>
+          <t>2026-02-22 17:58:18</t>
         </is>
       </c>
       <c r="B256" s="7" t="inlineStr">
@@ -23766,7 +23766,7 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 02:29:21</t>
+          <t>2026-02-22 17:29:21</t>
         </is>
       </c>
       <c r="B257" s="7" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="258">
       <c r="A258" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 01:59:09</t>
+          <t>2026-02-22 16:59:09</t>
         </is>
       </c>
       <c r="B258" s="7" t="inlineStr">
@@ -23926,7 +23926,7 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 01:32:08</t>
+          <t>2026-02-22 16:32:08</t>
         </is>
       </c>
       <c r="B259" s="7" t="inlineStr">
@@ -24006,7 +24006,7 @@
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 03:34:36</t>
+          <t>2026-02-20 18:34:36</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
@@ -24086,7 +24086,7 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 02:57:13</t>
+          <t>2026-02-20 17:57:13</t>
         </is>
       </c>
       <c r="B261" s="7" t="inlineStr">
@@ -24166,7 +24166,7 @@
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 02:19:01</t>
+          <t>2026-02-20 17:19:01</t>
         </is>
       </c>
       <c r="B262" s="7" t="inlineStr">
@@ -24246,7 +24246,7 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 01:41:10</t>
+          <t>2026-02-20 16:41:10</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
@@ -24326,7 +24326,7 @@
     <row r="264">
       <c r="A264" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:57:47</t>
+          <t>2026-02-20 15:57:47</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -24406,7 +24406,7 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:39:52</t>
+          <t>2026-02-20 15:39:52</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
@@ -24486,7 +24486,7 @@
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 01:21:13</t>
+          <t>2026-02-19 16:21:13</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -24566,7 +24566,7 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 00:33:10</t>
+          <t>2026-02-19 15:33:10</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -24646,7 +24646,7 @@
     <row r="268">
       <c r="A268" s="7" t="inlineStr">
         <is>
-          <t>2026-02-18 00:37:38</t>
+          <t>2026-02-17 15:37:38</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
@@ -24726,7 +24726,7 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>2026-02-17 23:58:39</t>
+          <t>2026-02-17 14:58:39</t>
         </is>
       </c>
       <c r="B269" s="7" t="inlineStr">
@@ -24806,7 +24806,7 @@
     <row r="270">
       <c r="A270" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 02:24:16</t>
+          <t>2026-02-15 17:24:16</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
@@ -24886,7 +24886,7 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 01:47:19</t>
+          <t>2026-02-15 16:47:19</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
@@ -24966,7 +24966,7 @@
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 00:56:43</t>
+          <t>2026-02-15 15:56:43</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -25046,7 +25046,7 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 00:26:20</t>
+          <t>2026-02-15 15:26:20</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
@@ -25126,7 +25126,7 @@
     <row r="274">
       <c r="A274" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 23:48:44</t>
+          <t>2026-02-15 14:48:44</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -25206,7 +25206,7 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 04:17:17</t>
+          <t>2026-02-14 19:17:17</t>
         </is>
       </c>
       <c r="B275" s="7" t="inlineStr">
@@ -25286,7 +25286,7 @@
     <row r="276">
       <c r="A276" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 03:53:01</t>
+          <t>2026-02-14 18:53:01</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
@@ -25366,7 +25366,7 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:59:46</t>
+          <t>2026-02-14 17:59:46</t>
         </is>
       </c>
       <c r="B277" s="7" t="inlineStr">
@@ -25446,7 +25446,7 @@
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:26:42</t>
+          <t>2026-02-14 17:26:42</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:00:09</t>
+          <t>2026-02-14 17:00:09</t>
         </is>
       </c>
       <c r="B279" s="7" t="inlineStr">
@@ -25606,7 +25606,7 @@
     <row r="280">
       <c r="A280" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 01:39:16</t>
+          <t>2026-02-14 16:39:16</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -25686,7 +25686,7 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 00:56:51</t>
+          <t>2026-02-14 15:56:51</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
@@ -25766,7 +25766,7 @@
     <row r="282">
       <c r="A282" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 23:52:26</t>
+          <t>2026-02-14 14:52:26</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -25846,7 +25846,7 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 23:14:55</t>
+          <t>2026-02-14 14:14:55</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
@@ -25926,7 +25926,7 @@
     <row r="284">
       <c r="A284" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 04:19:58</t>
+          <t>2026-02-13 19:19:58</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -26006,7 +26006,7 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 03:37:53</t>
+          <t>2026-02-13 18:37:53</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
@@ -26086,7 +26086,7 @@
     <row r="286">
       <c r="A286" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 03:03:31</t>
+          <t>2026-02-13 18:03:31</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -26166,7 +26166,7 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 02:08:36</t>
+          <t>2026-02-13 17:08:36</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -26246,7 +26246,7 @@
     <row r="288">
       <c r="A288" s="7" t="inlineStr">
         <is>
-          <t>2026-02-12 00:20:03</t>
+          <t>2026-02-11 15:20:03</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -26326,7 +26326,7 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 03:05:03</t>
+          <t>2026-02-10 18:05:03</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -26406,7 +26406,7 @@
     <row r="290">
       <c r="A290" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 02:14:02</t>
+          <t>2026-02-10 17:14:02</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -26486,7 +26486,7 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 01:33:21</t>
+          <t>2026-02-10 16:33:21</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
@@ -26566,7 +26566,7 @@
     <row r="292">
       <c r="A292" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 01:01:41</t>
+          <t>2026-02-10 16:01:41</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -26646,7 +26646,7 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 01:49:32</t>
+          <t>2026-02-09 16:49:32</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
@@ -26726,7 +26726,7 @@
     <row r="294">
       <c r="A294" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 01:42:29</t>
+          <t>2026-02-09 16:42:29</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -26806,7 +26806,7 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 23:44:10</t>
+          <t>2026-02-09 14:44:10</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
@@ -26886,7 +26886,7 @@
     <row r="296">
       <c r="A296" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 23:00:28</t>
+          <t>2026-02-09 14:00:28</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -26966,7 +26966,7 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 00:27:49</t>
+          <t>2026-02-08 15:27:49</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -27046,7 +27046,7 @@
     <row r="298">
       <c r="A298" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 00:16:42</t>
+          <t>2026-02-08 15:16:42</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -27126,7 +27126,7 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08 04:04:43</t>
+          <t>2026-02-07 19:04:43</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="300">
       <c r="A300" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 03:13:11</t>
+          <t>2026-02-06 18:13:11</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
@@ -27286,7 +27286,7 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 02:19:42</t>
+          <t>2026-02-06 17:19:42</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -27366,7 +27366,7 @@
     <row r="302">
       <c r="A302" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 01:37:36</t>
+          <t>2026-02-06 16:37:36</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
@@ -27446,7 +27446,7 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>2026-02-03 23:04:49</t>
+          <t>2026-02-03 14:04:49</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
@@ -27526,7 +27526,7 @@
     <row r="304">
       <c r="A304" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 23:21:38</t>
+          <t>2026-02-02 14:21:38</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -27606,7 +27606,7 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 03:08:17</t>
+          <t>2026-02-01 18:08:17</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -27686,7 +27686,7 @@
     <row r="306">
       <c r="A306" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 02:41:55</t>
+          <t>2026-02-01 17:41:55</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -27766,7 +27766,7 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 02:09:57</t>
+          <t>2026-02-01 17:09:57</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
@@ -27846,7 +27846,7 @@
     <row r="308">
       <c r="A308" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 01:41:49</t>
+          <t>2026-02-01 16:41:49</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
@@ -27926,7 +27926,7 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 02:22:13</t>
+          <t>2026-01-31 17:22:13</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
@@ -28006,7 +28006,7 @@
     <row r="310">
       <c r="A310" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 01:20:54</t>
+          <t>2026-01-31 16:20:54</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -28086,7 +28086,7 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 01:09:32</t>
+          <t>2026-01-31 16:09:32</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -28166,7 +28166,7 @@
     <row r="312">
       <c r="A312" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 00:29:37</t>
+          <t>2026-01-31 15:29:37</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -28246,7 +28246,7 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 00:03:50</t>
+          <t>2026-01-31 15:03:50</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -28326,7 +28326,7 @@
     <row r="314">
       <c r="A314" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 23:15:28</t>
+          <t>2026-01-31 14:15:28</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -28406,7 +28406,7 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>2026-01-29 00:36:39</t>
+          <t>2026-01-28 15:36:39</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -28486,7 +28486,7 @@
     <row r="316">
       <c r="A316" s="7" t="inlineStr">
         <is>
-          <t>2026-01-29 00:02:45</t>
+          <t>2026-01-28 15:02:45</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -28566,7 +28566,7 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 23:26:47</t>
+          <t>2026-01-28 14:26:47</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -28646,7 +28646,7 @@
     <row r="318">
       <c r="A318" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 23:04:33</t>
+          <t>2026-01-28 14:04:33</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -28726,7 +28726,7 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 00:33:31</t>
+          <t>2026-01-27 15:33:31</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -28806,7 +28806,7 @@
     <row r="320">
       <c r="A320" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 23:59:21</t>
+          <t>2026-01-27 14:59:21</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 23:08:33</t>
+          <t>2026-01-27 14:08:33</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -28966,7 +28966,7 @@
     <row r="322">
       <c r="A322" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 23:28:17</t>
+          <t>2026-01-25 14:28:17</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -29046,7 +29046,7 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 22:56:22</t>
+          <t>2026-01-25 13:56:22</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -29126,7 +29126,7 @@
     <row r="324">
       <c r="A324" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 22:28:25</t>
+          <t>2026-01-25 13:28:25</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -29206,7 +29206,7 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 21:42:03</t>
+          <t>2026-01-25 12:42:03</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -29286,7 +29286,7 @@
     <row r="326">
       <c r="A326" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 19:38:23</t>
+          <t>2026-01-25 10:38:23</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -29366,7 +29366,7 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 18:56:35</t>
+          <t>2026-01-25 09:56:35</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -29446,7 +29446,7 @@
     <row r="328">
       <c r="A328" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 18:29:19</t>
+          <t>2026-01-25 09:29:19</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -29526,7 +29526,7 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 17:14:05</t>
+          <t>2026-01-25 08:14:05</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -29606,7 +29606,7 @@
     <row r="330">
       <c r="A330" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 02:47:24</t>
+          <t>2026-01-23 17:47:24</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -29686,7 +29686,7 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 02:12:26</t>
+          <t>2026-01-23 17:12:26</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -29766,7 +29766,7 @@
     <row r="332">
       <c r="A332" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 01:33:34</t>
+          <t>2026-01-23 16:33:34</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -29846,7 +29846,7 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 01:00:39</t>
+          <t>2026-01-23 16:00:39</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -29926,7 +29926,7 @@
     <row r="334">
       <c r="A334" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 00:19:07</t>
+          <t>2026-01-23 15:19:07</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -30006,7 +30006,7 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 23:52:33</t>
+          <t>2026-01-23 14:52:33</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -30086,7 +30086,7 @@
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 23:19:19</t>
+          <t>2026-01-23 14:19:19</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -30166,7 +30166,7 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36:59</t>
+          <t>2026-01-23 13:36:59</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -30246,7 +30246,7 @@
     <row r="338">
       <c r="A338" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 03:01:58</t>
+          <t>2026-01-22 18:01:58</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -30326,7 +30326,7 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 02:25:41</t>
+          <t>2026-01-22 17:25:41</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -30406,7 +30406,7 @@
     <row r="340">
       <c r="A340" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 00:32:45</t>
+          <t>2026-01-22 15:32:45</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -30486,7 +30486,7 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 23:54:46</t>
+          <t>2026-01-22 14:54:46</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="342">
       <c r="A342" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 23:17:42</t>
+          <t>2026-01-22 14:17:42</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -30646,7 +30646,7 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 01:10:08</t>
+          <t>2026-01-21 16:10:08</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -30726,7 +30726,7 @@
     <row r="344">
       <c r="A344" s="7" t="inlineStr">
         <is>
-          <t>2026-01-21 00:27:51</t>
+          <t>2026-01-20 15:27:51</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -30806,7 +30806,7 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 23:25:34</t>
+          <t>2026-01-20 14:25:34</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -30886,7 +30886,7 @@
     <row r="346">
       <c r="A346" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 22:56:13</t>
+          <t>2026-01-20 13:56:13</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -30966,7 +30966,7 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>2026-01-19 01:59:11</t>
+          <t>2026-01-18 16:59:11</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -31046,7 +31046,7 @@
     <row r="348">
       <c r="A348" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 03:05:32</t>
+          <t>2026-01-17 18:05:32</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -31126,7 +31126,7 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 02:19:17</t>
+          <t>2026-01-17 17:19:17</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -31206,7 +31206,7 @@
     <row r="350">
       <c r="A350" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 01:58:17</t>
+          <t>2026-01-17 16:58:17</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -31286,7 +31286,7 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 01:18:29</t>
+          <t>2026-01-17 16:18:29</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -31366,7 +31366,7 @@
     <row r="352">
       <c r="A352" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 00:38:58</t>
+          <t>2026-01-17 15:38:58</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -31446,7 +31446,7 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 18:46:30</t>
+          <t>2026-01-17 09:46:30</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -31526,7 +31526,7 @@
     <row r="354">
       <c r="A354" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 02:21:36</t>
+          <t>2026-01-16 17:21:36</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -31606,7 +31606,7 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 01:51:05</t>
+          <t>2026-01-16 16:51:05</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -31686,7 +31686,7 @@
     <row r="356">
       <c r="A356" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 01:18:22</t>
+          <t>2026-01-16 16:18:22</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -31766,7 +31766,7 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 01:41:15</t>
+          <t>2026-01-15 16:41:15</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -31846,7 +31846,7 @@
     <row r="358">
       <c r="A358" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 01:05:38</t>
+          <t>2026-01-15 16:05:38</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -31926,7 +31926,7 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14 00:57:21</t>
+          <t>2026-01-13 15:57:21</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -32006,7 +32006,7 @@
     <row r="360">
       <c r="A360" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14 00:19:49</t>
+          <t>2026-01-13 15:19:49</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -32086,7 +32086,7 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 23:53:29</t>
+          <t>2026-01-13 14:53:29</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -32166,7 +32166,7 @@
     <row r="362">
       <c r="A362" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 02:23:29</t>
+          <t>2026-01-12 17:23:29</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 01:42:12</t>
+          <t>2026-01-12 16:42:12</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -32326,7 +32326,7 @@
     <row r="364">
       <c r="A364" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 01:17:01</t>
+          <t>2026-01-12 16:17:01</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -32406,7 +32406,7 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 00:43:11</t>
+          <t>2026-01-12 15:43:11</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -32486,7 +32486,7 @@
     <row r="366">
       <c r="A366" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 17:24:44</t>
+          <t>2026-01-12 08:24:44</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -32566,7 +32566,7 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 03:12:16</t>
+          <t>2026-01-11 18:12:16</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -32646,7 +32646,7 @@
     <row r="368">
       <c r="A368" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 02:54:03</t>
+          <t>2026-01-10 17:54:03</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -32726,7 +32726,7 @@
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 02:14:56</t>
+          <t>2026-01-10 17:14:56</t>
         </is>
       </c>
       <c r="B369" s="7" t="inlineStr">
@@ -32806,7 +32806,7 @@
     <row r="370">
       <c r="A370" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 01:17:21</t>
+          <t>2026-01-10 16:17:21</t>
         </is>
       </c>
       <c r="B370" s="7" t="inlineStr">
@@ -32886,7 +32886,7 @@
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 00:22:11</t>
+          <t>2026-01-10 15:22:11</t>
         </is>
       </c>
       <c r="B371" s="7" t="inlineStr">
@@ -32966,7 +32966,7 @@
     <row r="372">
       <c r="A372" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 23:38:24</t>
+          <t>2026-01-10 14:38:24</t>
         </is>
       </c>
       <c r="B372" s="7" t="inlineStr">
@@ -33046,7 +33046,7 @@
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 02:54:19</t>
+          <t>2026-01-09 17:54:19</t>
         </is>
       </c>
       <c r="B373" s="7" t="inlineStr">
@@ -33126,7 +33126,7 @@
     <row r="374">
       <c r="A374" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 02:00:16</t>
+          <t>2026-01-09 17:00:16</t>
         </is>
       </c>
       <c r="B374" s="7" t="inlineStr">
@@ -33206,7 +33206,7 @@
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>2026-01-09 23:36:27</t>
+          <t>2026-01-09 14:36:27</t>
         </is>
       </c>
       <c r="B375" s="7" t="inlineStr">
@@ -33283,8 +33283,88 @@
         </is>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-05 14:21:47</t>
+        </is>
+      </c>
+      <c r="B376" s="7" t="inlineStr">
+        <is>
+          <t>ランク(ソロ/デュオ)</t>
+        </is>
+      </c>
+      <c r="C376" s="10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D376" s="7" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E376" s="7" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F376" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H376" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I376" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J376" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K376" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="L376" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M376" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N376" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="O376" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P376" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q376" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R376" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S376" s="11" t="n">
+        <v>6751</v>
+      </c>
+      <c r="T376" s="11" t="n">
+        <v>2219</v>
+      </c>
+      <c r="U376" s="6" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V376" s="7" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V375"/>
+  <autoFilter ref="A1:V376"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33295,7 +33375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P375"/>
+  <dimension ref="A1:P376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -33401,7 +33481,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 04:00:11</t>
+          <t>2026-07-31 19:00:11</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
@@ -33463,7 +33543,7 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 03:30:26</t>
+          <t>2026-07-31 18:30:26</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
@@ -33525,7 +33605,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 02:52:16</t>
+          <t>2026-07-31 17:52:16</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -33587,7 +33667,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 01:50:20</t>
+          <t>2026-07-31 16:50:20</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -33649,7 +33729,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 01:16:45</t>
+          <t>2026-07-31 16:16:45</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -33711,7 +33791,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 22:56:19</t>
+          <t>2026-07-31 13:56:19</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -33773,7 +33853,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 22:22:46</t>
+          <t>2026-07-31 13:22:46</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -33835,7 +33915,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 21:49:35</t>
+          <t>2026-07-31 12:49:35</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -33897,7 +33977,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 23:51:39</t>
+          <t>2026-07-28 14:51:39</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -33959,7 +34039,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 23:05:20</t>
+          <t>2026-07-28 14:05:20</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -34021,7 +34101,7 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>2026-07-27 01:21:51</t>
+          <t>2026-07-26 16:21:51</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -34083,7 +34163,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>2026-07-27 00:43:02</t>
+          <t>2026-07-26 15:43:02</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -34145,7 +34225,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 23:12:09</t>
+          <t>2026-07-25 14:12:09</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
@@ -34207,7 +34287,7 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 22:30:57</t>
+          <t>2026-07-25 13:30:57</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -34269,7 +34349,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 00:11:55</t>
+          <t>2026-07-24 15:11:55</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -34331,7 +34411,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>2026-07-24 23:25:38</t>
+          <t>2026-07-24 14:25:38</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -34393,7 +34473,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>2026-07-22 00:17:56</t>
+          <t>2026-07-21 15:17:56</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -34455,7 +34535,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>2026-07-22 00:04:35</t>
+          <t>2026-07-21 15:04:35</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -34517,7 +34597,7 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 23:25:56</t>
+          <t>2026-07-21 14:25:56</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -34579,7 +34659,7 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 22:44:36</t>
+          <t>2026-07-21 13:44:36</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -34641,7 +34721,7 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 22:18:59</t>
+          <t>2026-07-21 13:18:59</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -34703,7 +34783,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>2026-07-20 03:20:20</t>
+          <t>2026-07-19 18:20:20</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -34765,7 +34845,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>2026-07-20 02:39:51</t>
+          <t>2026-07-19 17:39:51</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -34827,7 +34907,7 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:59:14</t>
+          <t>2026-07-18 09:59:14</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -34889,7 +34969,7 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:21:14</t>
+          <t>2026-07-18 09:21:14</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
@@ -34951,7 +35031,7 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 23:06:28</t>
+          <t>2026-07-16 14:06:28</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -35013,7 +35093,7 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 22:32:42</t>
+          <t>2026-07-16 13:32:42</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
@@ -35075,7 +35155,7 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 00:40:48</t>
+          <t>2026-07-15 15:40:48</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -35137,7 +35217,7 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 23:41:56</t>
+          <t>2026-07-15 14:41:56</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
@@ -35199,7 +35279,7 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 22:58:44</t>
+          <t>2026-07-15 13:58:44</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
@@ -35261,7 +35341,7 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 22:34:16</t>
+          <t>2026-07-15 13:34:16</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
@@ -35323,7 +35403,7 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 23:36:35</t>
+          <t>2026-07-14 14:36:35</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -35385,7 +35465,7 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 22:49:50</t>
+          <t>2026-07-14 13:49:50</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
@@ -35447,7 +35527,7 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 01:02:29</t>
+          <t>2026-07-13 16:02:29</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
@@ -35509,7 +35589,7 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 00:22:46</t>
+          <t>2026-07-13 15:22:46</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
@@ -35571,7 +35651,7 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 23:51:38</t>
+          <t>2026-07-13 14:51:38</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -35633,7 +35713,7 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 02:05:19</t>
+          <t>2026-07-12 17:05:19</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
@@ -35695,7 +35775,7 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 01:29:17</t>
+          <t>2026-07-12 16:29:17</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -35757,7 +35837,7 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 03:11:38</t>
+          <t>2026-07-11 18:11:38</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
@@ -35819,7 +35899,7 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 02:46:15</t>
+          <t>2026-07-11 17:46:15</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
@@ -35881,7 +35961,7 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 03:42:29</t>
+          <t>2026-07-10 18:42:29</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
@@ -35943,7 +36023,7 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 03:06:21</t>
+          <t>2026-07-10 18:06:21</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
@@ -36005,7 +36085,7 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:55:25</t>
+          <t>2026-07-08 17:55:25</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
@@ -36067,7 +36147,7 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:17:09</t>
+          <t>2026-07-08 17:17:09</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
@@ -36129,7 +36209,7 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 02:03:51</t>
+          <t>2026-07-05 17:03:51</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
@@ -36191,7 +36271,7 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 01:07:17</t>
+          <t>2026-07-05 16:07:17</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
@@ -36253,7 +36333,7 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 00:23:00</t>
+          <t>2026-07-05 15:23:00</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
@@ -36315,7 +36395,7 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>2026-07-05 03:21:23</t>
+          <t>2026-07-04 18:21:23</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
@@ -36377,7 +36457,7 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>2026-07-04 03:01:40</t>
+          <t>2026-07-03 18:01:40</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
@@ -36439,7 +36519,7 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>2026-07-03 01:48:19</t>
+          <t>2026-07-02 16:48:19</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
@@ -36501,7 +36581,7 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>2026-07-01 00:21:19</t>
+          <t>2026-06-30 15:21:19</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
@@ -36563,7 +36643,7 @@
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 23:38:16</t>
+          <t>2026-06-30 14:38:16</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
@@ -36625,7 +36705,7 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 01:16:28</t>
+          <t>2026-06-29 16:16:28</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
@@ -36687,7 +36767,7 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 00:34:32</t>
+          <t>2026-06-29 15:34:32</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
@@ -36749,7 +36829,7 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>2026-06-26 00:50:56</t>
+          <t>2026-06-25 15:50:56</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
@@ -36811,7 +36891,7 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>2026-06-26 00:06:40</t>
+          <t>2026-06-25 15:06:40</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
@@ -36873,7 +36953,7 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07:56</t>
+          <t>2026-06-24 17:07:56</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
@@ -36935,7 +37015,7 @@
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 01:33:19</t>
+          <t>2026-06-24 16:33:19</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
@@ -36997,7 +37077,7 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:47:59</t>
+          <t>2026-06-24 15:47:59</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
@@ -37059,7 +37139,7 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:08:31</t>
+          <t>2026-06-24 15:08:31</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
@@ -37121,7 +37201,7 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 23:33:15</t>
+          <t>2026-06-24 14:33:15</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
@@ -37183,7 +37263,7 @@
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 22:39:11</t>
+          <t>2026-06-24 13:39:11</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
@@ -37245,7 +37325,7 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 01:16:06</t>
+          <t>2026-06-22 16:16:06</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
@@ -37307,7 +37387,7 @@
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 00:38:08</t>
+          <t>2026-06-22 15:38:08</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
@@ -37369,7 +37449,7 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 00:29:33</t>
+          <t>2026-06-22 15:29:33</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
@@ -37431,7 +37511,7 @@
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 01:54:04</t>
+          <t>2026-06-18 16:54:04</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
@@ -37493,7 +37573,7 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 01:14:50</t>
+          <t>2026-06-18 16:14:50</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
@@ -37555,7 +37635,7 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 00:35:17</t>
+          <t>2026-06-18 15:35:17</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
@@ -37617,7 +37697,7 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 23:55:50</t>
+          <t>2026-06-18 14:55:50</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
@@ -37679,7 +37759,7 @@
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 00:44:42</t>
+          <t>2026-06-17 15:44:42</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
@@ -37741,7 +37821,7 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 23:57:38</t>
+          <t>2026-06-17 14:57:38</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
@@ -37803,7 +37883,7 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 01:58:55</t>
+          <t>2026-06-16 16:58:55</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
@@ -37865,7 +37945,7 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 01:30:07</t>
+          <t>2026-06-16 16:30:07</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
@@ -37927,7 +38007,7 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 03:10:28</t>
+          <t>2026-06-14 18:10:28</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
@@ -37989,7 +38069,7 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 02:27:52</t>
+          <t>2026-06-14 17:27:52</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
@@ -38051,7 +38131,7 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 01:57:23</t>
+          <t>2026-06-14 16:57:23</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
@@ -38113,7 +38193,7 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 01:27:22</t>
+          <t>2026-06-14 16:27:22</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
@@ -38175,7 +38255,7 @@
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 00:24:35</t>
+          <t>2026-06-14 15:24:35</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
@@ -38237,7 +38317,7 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 23:46:55</t>
+          <t>2026-06-14 14:46:55</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
@@ -38299,7 +38379,7 @@
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 01:41:53</t>
+          <t>2026-06-13 16:41:53</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
@@ -38361,7 +38441,7 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 00:52:58</t>
+          <t>2026-06-13 15:52:58</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
@@ -38423,7 +38503,7 @@
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 00:14:23</t>
+          <t>2026-06-13 15:14:23</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
@@ -38485,7 +38565,7 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 23:45:21</t>
+          <t>2026-06-13 14:45:21</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
@@ -38547,7 +38627,7 @@
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 23:05:32</t>
+          <t>2026-06-13 14:05:32</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
@@ -38609,7 +38689,7 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 01:08:14</t>
+          <t>2026-06-10 16:08:14</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
@@ -38671,7 +38751,7 @@
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:34:35</t>
+          <t>2026-06-10 15:34:35</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
@@ -38733,7 +38813,7 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:09:17</t>
+          <t>2026-06-10 15:09:17</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
@@ -38795,7 +38875,7 @@
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 23:27:53</t>
+          <t>2026-06-10 14:27:53</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
@@ -38857,7 +38937,7 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 00:49:00</t>
+          <t>2026-06-09 15:49:00</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
@@ -38919,7 +38999,7 @@
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>2026-06-06 02:58:51</t>
+          <t>2026-06-05 17:58:51</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
@@ -38981,7 +39061,7 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>2026-06-06 02:15:04</t>
+          <t>2026-06-05 17:15:04</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
@@ -39043,7 +39123,7 @@
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 23:49:14</t>
+          <t>2026-06-04 14:49:14</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
@@ -39105,7 +39185,7 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 21:40:04</t>
+          <t>2026-06-04 12:40:04</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
@@ -39167,7 +39247,7 @@
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 21:17:24</t>
+          <t>2026-06-04 12:17:24</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
@@ -39229,7 +39309,7 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 01:06:27</t>
+          <t>2026-06-03 16:06:27</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
@@ -39291,7 +39371,7 @@
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 00:31:09</t>
+          <t>2026-06-03 15:31:09</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
@@ -39353,7 +39433,7 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 23:53:57</t>
+          <t>2026-06-03 14:53:57</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
@@ -39415,7 +39495,7 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 22:44:02</t>
+          <t>2026-06-03 13:44:02</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
@@ -39477,7 +39557,7 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>2026-06-02 22:49:11</t>
+          <t>2026-06-02 13:49:11</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
@@ -39539,7 +39619,7 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:56:06</t>
+          <t>2026-06-01 14:56:06</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
@@ -39601,7 +39681,7 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:20:26</t>
+          <t>2026-06-01 14:20:26</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
@@ -39663,7 +39743,7 @@
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:01:06</t>
+          <t>2026-06-01 14:01:06</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
@@ -39725,7 +39805,7 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>2026-05-31 03:01:04</t>
+          <t>2026-05-30 18:01:04</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
@@ -39787,7 +39867,7 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>2026-05-31 02:13:41</t>
+          <t>2026-05-30 17:13:41</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
@@ -39849,7 +39929,7 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 23:00:40</t>
+          <t>2026-05-25 14:00:40</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
@@ -39911,7 +39991,7 @@
     <row r="107">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 01:55:47</t>
+          <t>2026-05-24 16:55:47</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
@@ -39973,7 +40053,7 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 01:24:22</t>
+          <t>2026-05-24 16:24:22</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
@@ -40035,7 +40115,7 @@
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 23:49:25</t>
+          <t>2026-05-24 14:49:25</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
@@ -40097,7 +40177,7 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 03:13:39</t>
+          <t>2026-05-23 18:13:39</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
@@ -40159,7 +40239,7 @@
     <row r="111">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 02:41:52</t>
+          <t>2026-05-23 17:41:52</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
@@ -40221,7 +40301,7 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 23:19:04</t>
+          <t>2026-05-23 14:19:04</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
@@ -40283,7 +40363,7 @@
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 22:43:20</t>
+          <t>2026-05-23 13:43:20</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
@@ -40345,7 +40425,7 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 15:54:19</t>
+          <t>2026-05-23 06:54:19</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
@@ -40407,7 +40487,7 @@
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 02:25:24</t>
+          <t>2026-05-22 17:25:24</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
@@ -40469,7 +40549,7 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 01:29:23</t>
+          <t>2026-05-21 16:29:23</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
@@ -40531,7 +40611,7 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 00:48:49</t>
+          <t>2026-05-21 15:48:49</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
@@ -40593,7 +40673,7 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:45</t>
+          <t>2026-05-21 15:00:45</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
@@ -40655,7 +40735,7 @@
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 23:22:44</t>
+          <t>2026-05-21 14:22:44</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
@@ -40717,7 +40797,7 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 00:05:15</t>
+          <t>2026-05-20 15:05:15</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
@@ -40779,7 +40859,7 @@
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 23:43:50</t>
+          <t>2026-05-20 14:43:50</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
@@ -40841,7 +40921,7 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 22:57:45</t>
+          <t>2026-05-20 13:57:45</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
@@ -40903,7 +40983,7 @@
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 01:25:45</t>
+          <t>2026-05-19 16:25:45</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
@@ -40965,7 +41045,7 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 00:46:42</t>
+          <t>2026-05-19 15:46:42</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
@@ -41027,7 +41107,7 @@
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>2026-05-18 22:56:39</t>
+          <t>2026-05-18 13:56:39</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
@@ -41089,7 +41169,7 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 01:35:56</t>
+          <t>2026-05-14 16:35:56</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
@@ -41151,7 +41231,7 @@
     <row r="127">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 01:17:05</t>
+          <t>2026-05-14 16:17:05</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
@@ -41213,7 +41293,7 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 00:05:48</t>
+          <t>2026-05-14 15:05:48</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
@@ -41275,7 +41355,7 @@
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>2026-05-14 01:25:38</t>
+          <t>2026-05-13 16:25:38</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
@@ -41337,7 +41417,7 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>2026-05-12 00:19:57</t>
+          <t>2026-05-11 15:19:57</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
@@ -41399,7 +41479,7 @@
     <row r="131">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 23:54:15</t>
+          <t>2026-05-11 14:54:15</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
@@ -41461,7 +41541,7 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 23:14:30</t>
+          <t>2026-05-11 14:14:30</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
@@ -41523,7 +41603,7 @@
     <row r="133">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 22:37:05</t>
+          <t>2026-05-11 13:37:05</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
@@ -41585,7 +41665,7 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 21:53:13</t>
+          <t>2026-05-11 12:53:13</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
@@ -41647,7 +41727,7 @@
     <row r="135">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 00:04:01</t>
+          <t>2026-05-10 15:04:01</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
@@ -41709,7 +41789,7 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:54:24</t>
+          <t>2026-05-09 16:54:24</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
@@ -41771,7 +41851,7 @@
     <row r="137">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:22:50</t>
+          <t>2026-05-09 16:22:50</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
@@ -41833,7 +41913,7 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 00:26:16</t>
+          <t>2026-05-09 15:26:16</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
@@ -41895,7 +41975,7 @@
     <row r="139">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 23:38:30</t>
+          <t>2026-05-09 14:38:30</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
@@ -41957,7 +42037,7 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 22:50:20</t>
+          <t>2026-05-09 13:50:20</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
@@ -42019,7 +42099,7 @@
     <row r="141">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 22:13:25</t>
+          <t>2026-05-09 13:13:25</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
@@ -42081,7 +42161,7 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 20:00:11</t>
+          <t>2026-05-09 11:00:11</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
@@ -42143,7 +42223,7 @@
     <row r="143">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 19:10:28</t>
+          <t>2026-05-09 10:10:28</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
@@ -42205,7 +42285,7 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 02:17:27</t>
+          <t>2026-05-08 17:17:27</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
@@ -42267,7 +42347,7 @@
     <row r="145">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 01:38:25</t>
+          <t>2026-05-08 16:38:25</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
@@ -42329,7 +42409,7 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 00:58:58</t>
+          <t>2026-05-08 15:58:58</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
@@ -42391,7 +42471,7 @@
     <row r="147">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 00:37:55</t>
+          <t>2026-05-08 15:37:55</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
@@ -42453,7 +42533,7 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 01:48:31</t>
+          <t>2026-05-07 16:48:31</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
@@ -42515,7 +42595,7 @@
     <row r="149">
       <c r="A149" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 01:02:52</t>
+          <t>2026-05-07 16:02:52</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
@@ -42577,7 +42657,7 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 00:23:29</t>
+          <t>2026-05-07 15:23:29</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
@@ -42639,7 +42719,7 @@
     <row r="151">
       <c r="A151" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 01:30:56</t>
+          <t>2026-05-06 16:30:56</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
@@ -42701,7 +42781,7 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 00:42:16</t>
+          <t>2026-05-06 15:42:16</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
@@ -42763,7 +42843,7 @@
     <row r="153">
       <c r="A153" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 23:44:04</t>
+          <t>2026-05-06 14:44:04</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
@@ -42825,7 +42905,7 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:13:52</t>
+          <t>2026-05-06 09:13:52</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
@@ -42887,7 +42967,7 @@
     <row r="155">
       <c r="A155" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:05:08</t>
+          <t>2026-05-06 09:05:08</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
@@ -42949,7 +43029,7 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 17:22:30</t>
+          <t>2026-05-06 08:22:30</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
@@ -43011,7 +43091,7 @@
     <row r="157">
       <c r="A157" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 16:28:42</t>
+          <t>2026-05-06 07:28:42</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
@@ -43073,7 +43153,7 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 03:16:57</t>
+          <t>2026-05-05 18:16:57</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
@@ -43135,7 +43215,7 @@
     <row r="159">
       <c r="A159" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:32:40</t>
+          <t>2026-05-05 17:32:40</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
@@ -43197,7 +43277,7 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:23:28</t>
+          <t>2026-05-05 17:23:28</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
@@ -43259,7 +43339,7 @@
     <row r="161">
       <c r="A161" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 01:48:28</t>
+          <t>2026-05-05 16:48:28</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
@@ -43321,7 +43401,7 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 00:52:33</t>
+          <t>2026-05-05 15:52:33</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
@@ -43383,7 +43463,7 @@
     <row r="163">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 17:43:06</t>
+          <t>2026-05-05 08:43:06</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
@@ -43445,7 +43525,7 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>2026-05-03 00:36:42</t>
+          <t>2026-05-02 15:36:42</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
@@ -43507,7 +43587,7 @@
     <row r="165">
       <c r="A165" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 23:51:09</t>
+          <t>2026-05-02 14:51:09</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
@@ -43569,7 +43649,7 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 22:15:10</t>
+          <t>2026-05-02 13:15:10</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
@@ -43631,7 +43711,7 @@
     <row r="167">
       <c r="A167" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 21:29:49</t>
+          <t>2026-05-02 12:29:49</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
@@ -43693,7 +43773,7 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 01:39:42</t>
+          <t>2026-04-30 16:39:42</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
@@ -43755,7 +43835,7 @@
     <row r="169">
       <c r="A169" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 01:01:34</t>
+          <t>2026-04-30 16:01:34</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
@@ -43817,7 +43897,7 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 00:24:48</t>
+          <t>2026-04-30 15:24:48</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
@@ -43879,7 +43959,7 @@
     <row r="171">
       <c r="A171" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 23:37:10</t>
+          <t>2026-04-30 14:37:10</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
@@ -43941,7 +44021,7 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 22:58:06</t>
+          <t>2026-04-30 13:58:06</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
@@ -44003,7 +44083,7 @@
     <row r="173">
       <c r="A173" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 03:29:33</t>
+          <t>2026-04-29 18:29:33</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
@@ -44065,7 +44145,7 @@
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 02:54:07</t>
+          <t>2026-04-29 17:54:07</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
@@ -44127,7 +44207,7 @@
     <row r="175">
       <c r="A175" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 02:20:58</t>
+          <t>2026-04-29 17:20:58</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
@@ -44189,7 +44269,7 @@
     <row r="176">
       <c r="A176" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 01:42:01</t>
+          <t>2026-04-29 16:42:01</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
@@ -44251,7 +44331,7 @@
     <row r="177">
       <c r="A177" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 01:03:17</t>
+          <t>2026-04-29 16:03:17</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
@@ -44313,7 +44393,7 @@
     <row r="178">
       <c r="A178" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 00:19:47</t>
+          <t>2026-04-29 15:19:47</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
@@ -44375,7 +44455,7 @@
     <row r="179">
       <c r="A179" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 23:29:53</t>
+          <t>2026-04-29 14:29:53</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
@@ -44437,7 +44517,7 @@
     <row r="180">
       <c r="A180" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:59:49</t>
+          <t>2026-04-29 13:59:49</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
@@ -44499,7 +44579,7 @@
     <row r="181">
       <c r="A181" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:38:22</t>
+          <t>2026-04-29 13:38:22</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
@@ -44561,7 +44641,7 @@
     <row r="182">
       <c r="A182" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:44</t>
+          <t>2026-04-29 13:17:44</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
@@ -44623,7 +44703,7 @@
     <row r="183">
       <c r="A183" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 03:28:56</t>
+          <t>2026-04-28 18:28:56</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
@@ -44685,7 +44765,7 @@
     <row r="184">
       <c r="A184" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:58:50</t>
+          <t>2026-04-28 17:58:50</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
@@ -44747,7 +44827,7 @@
     <row r="185">
       <c r="A185" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:29:43</t>
+          <t>2026-04-28 17:29:43</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
@@ -44809,7 +44889,7 @@
     <row r="186">
       <c r="A186" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 01:38:43</t>
+          <t>2026-04-28 16:38:43</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
@@ -44871,7 +44951,7 @@
     <row r="187">
       <c r="A187" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:54</t>
+          <t>2026-04-28 15:58:54</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
@@ -44933,7 +45013,7 @@
     <row r="188">
       <c r="A188" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:31:32</t>
+          <t>2026-04-28 15:31:32</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
@@ -44995,7 +45075,7 @@
     <row r="189">
       <c r="A189" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:04:20</t>
+          <t>2026-04-28 15:04:20</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
@@ -45057,7 +45137,7 @@
     <row r="190">
       <c r="A190" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 23:37:27</t>
+          <t>2026-04-28 14:37:27</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
@@ -45119,7 +45199,7 @@
     <row r="191">
       <c r="A191" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 23:09:10</t>
+          <t>2026-04-28 14:09:10</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
@@ -45181,7 +45261,7 @@
     <row r="192">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:59:25</t>
+          <t>2026-04-27 14:59:25</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
@@ -45243,7 +45323,7 @@
     <row r="193">
       <c r="A193" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:49:35</t>
+          <t>2026-04-27 14:49:35</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
@@ -45305,7 +45385,7 @@
     <row r="194">
       <c r="A194" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 22:55:34</t>
+          <t>2026-04-27 13:55:34</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
@@ -45367,7 +45447,7 @@
     <row r="195">
       <c r="A195" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 22:04:13</t>
+          <t>2026-04-27 13:04:13</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
@@ -45429,7 +45509,7 @@
     <row r="196">
       <c r="A196" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 02:49:02</t>
+          <t>2026-04-24 17:49:02</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
@@ -45491,7 +45571,7 @@
     <row r="197">
       <c r="A197" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 02:03:56</t>
+          <t>2026-04-24 17:03:56</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
@@ -45553,7 +45633,7 @@
     <row r="198">
       <c r="A198" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 01:37:00</t>
+          <t>2026-04-24 16:37:00</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
@@ -45615,7 +45695,7 @@
     <row r="199">
       <c r="A199" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:33:59</t>
+          <t>2026-04-23 15:33:59</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
@@ -45677,7 +45757,7 @@
     <row r="200">
       <c r="A200" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:22:46</t>
+          <t>2026-04-23 15:22:46</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
@@ -45739,7 +45819,7 @@
     <row r="201">
       <c r="A201" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:12:54</t>
+          <t>2026-04-23 15:12:54</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
@@ -45801,7 +45881,7 @@
     <row r="202">
       <c r="A202" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 22:36:03</t>
+          <t>2026-04-23 13:36:03</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
@@ -45863,7 +45943,7 @@
     <row r="203">
       <c r="A203" s="13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:58:57</t>
+          <t>2026-04-13 15:58:57</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
@@ -45925,7 +46005,7 @@
     <row r="204">
       <c r="A204" s="13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:09:08</t>
+          <t>2026-04-13 15:09:08</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
@@ -45987,7 +46067,7 @@
     <row r="205">
       <c r="A205" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 01:48:02</t>
+          <t>2026-04-12 16:48:02</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
@@ -46049,7 +46129,7 @@
     <row r="206">
       <c r="A206" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 01:17:58</t>
+          <t>2026-04-12 16:17:58</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
@@ -46111,7 +46191,7 @@
     <row r="207">
       <c r="A207" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 00:41:20</t>
+          <t>2026-04-12 15:41:20</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
@@ -46173,7 +46253,7 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 23:18:06</t>
+          <t>2026-04-09 14:18:06</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
@@ -46235,7 +46315,7 @@
     <row r="209">
       <c r="A209" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 22:52:44</t>
+          <t>2026-04-09 13:52:44</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
@@ -46297,7 +46377,7 @@
     <row r="210">
       <c r="A210" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 22:27:45</t>
+          <t>2026-04-09 13:27:45</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
@@ -46359,7 +46439,7 @@
     <row r="211">
       <c r="A211" s="13" t="inlineStr">
         <is>
-          <t>2026-04-08 01:10:31</t>
+          <t>2026-04-07 16:10:31</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
@@ -46421,7 +46501,7 @@
     <row r="212">
       <c r="A212" s="13" t="inlineStr">
         <is>
-          <t>2026-04-08 00:29:19</t>
+          <t>2026-04-07 15:29:19</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
@@ -46483,7 +46563,7 @@
     <row r="213">
       <c r="A213" s="13" t="inlineStr">
         <is>
-          <t>2026-04-04 04:36:31</t>
+          <t>2026-04-03 19:36:31</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
@@ -46545,7 +46625,7 @@
     <row r="214">
       <c r="A214" s="13" t="inlineStr">
         <is>
-          <t>2026-04-04 04:16:32</t>
+          <t>2026-04-03 19:16:32</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
@@ -46607,7 +46687,7 @@
     <row r="215">
       <c r="A215" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 04:24:43</t>
+          <t>2026-03-27 19:24:43</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
@@ -46669,7 +46749,7 @@
     <row r="216">
       <c r="A216" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:38:31</t>
+          <t>2026-03-27 18:38:31</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
@@ -46731,7 +46811,7 @@
     <row r="217">
       <c r="A217" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:17:50</t>
+          <t>2026-03-27 18:17:50</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
@@ -46793,7 +46873,7 @@
     <row r="218">
       <c r="A218" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 02:43:19</t>
+          <t>2026-03-27 17:43:19</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
@@ -46855,7 +46935,7 @@
     <row r="219">
       <c r="A219" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 02:15:18</t>
+          <t>2026-03-27 17:15:18</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
@@ -46917,7 +46997,7 @@
     <row r="220">
       <c r="A220" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 23:18:12</t>
+          <t>2026-03-25 14:18:12</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
@@ -46979,7 +47059,7 @@
     <row r="221">
       <c r="A221" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 00:01:49</t>
+          <t>2026-03-24 15:01:49</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
@@ -47041,7 +47121,7 @@
     <row r="222">
       <c r="A222" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 23:25:16</t>
+          <t>2026-03-24 14:25:16</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
@@ -47103,7 +47183,7 @@
     <row r="223">
       <c r="A223" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 23:02:52</t>
+          <t>2026-03-24 14:02:52</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
@@ -47165,7 +47245,7 @@
     <row r="224">
       <c r="A224" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 22:26:26</t>
+          <t>2026-03-24 13:26:26</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
@@ -47227,7 +47307,7 @@
     <row r="225">
       <c r="A225" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 00:56:18</t>
+          <t>2026-03-23 15:56:18</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
@@ -47289,7 +47369,7 @@
     <row r="226">
       <c r="A226" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 00:29:29</t>
+          <t>2026-03-23 15:29:29</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
@@ -47351,7 +47431,7 @@
     <row r="227">
       <c r="A227" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 23:51:11</t>
+          <t>2026-03-22 14:51:11</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
@@ -47413,7 +47493,7 @@
     <row r="228">
       <c r="A228" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 01:04:36</t>
+          <t>2026-03-21 16:04:36</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
@@ -47475,7 +47555,7 @@
     <row r="229">
       <c r="A229" s="13" t="inlineStr">
         <is>
-          <t>2026-03-21 02:55:49</t>
+          <t>2026-03-20 17:55:49</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
@@ -47537,7 +47617,7 @@
     <row r="230">
       <c r="A230" s="13" t="inlineStr">
         <is>
-          <t>2026-03-18 00:07:07</t>
+          <t>2026-03-17 15:07:07</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
@@ -47599,7 +47679,7 @@
     <row r="231">
       <c r="A231" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 23:24:05</t>
+          <t>2026-03-17 14:24:05</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
@@ -47661,7 +47741,7 @@
     <row r="232">
       <c r="A232" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 02:00:50</t>
+          <t>2026-03-16 17:00:50</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
@@ -47723,7 +47803,7 @@
     <row r="233">
       <c r="A233" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 01:33:08</t>
+          <t>2026-03-16 16:33:08</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
@@ -47785,7 +47865,7 @@
     <row r="234">
       <c r="A234" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 23:28:09</t>
+          <t>2026-03-16 14:28:09</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
@@ -47847,7 +47927,7 @@
     <row r="235">
       <c r="A235" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 01:32:22</t>
+          <t>2026-03-15 16:32:22</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
@@ -47909,7 +47989,7 @@
     <row r="236">
       <c r="A236" s="13" t="inlineStr">
         <is>
-          <t>2026-03-14 01:43:49</t>
+          <t>2026-03-13 16:43:49</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
@@ -47971,7 +48051,7 @@
     <row r="237">
       <c r="A237" s="13" t="inlineStr">
         <is>
-          <t>2026-03-14 01:19:35</t>
+          <t>2026-03-13 16:19:35</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
@@ -48033,7 +48113,7 @@
     <row r="238">
       <c r="A238" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 23:45:27</t>
+          <t>2026-03-12 14:45:27</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
@@ -48095,7 +48175,7 @@
     <row r="239">
       <c r="A239" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 23:02:09</t>
+          <t>2026-03-12 14:02:09</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
@@ -48157,7 +48237,7 @@
     <row r="240">
       <c r="A240" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 22:42:59</t>
+          <t>2026-03-12 13:42:59</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
@@ -48219,7 +48299,7 @@
     <row r="241">
       <c r="A241" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 01:39:10</t>
+          <t>2026-03-11 16:39:10</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
@@ -48281,7 +48361,7 @@
     <row r="242">
       <c r="A242" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:43:21</t>
+          <t>2026-03-11 15:43:21</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
@@ -48343,7 +48423,7 @@
     <row r="243">
       <c r="A243" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:04:25</t>
+          <t>2026-03-11 15:04:25</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
@@ -48405,7 +48485,7 @@
     <row r="244">
       <c r="A244" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 22:54:02</t>
+          <t>2026-03-11 13:54:02</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
@@ -48467,7 +48547,7 @@
     <row r="245">
       <c r="A245" s="13" t="inlineStr">
         <is>
-          <t>2026-03-08 02:01:53</t>
+          <t>2026-03-07 17:01:53</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
@@ -48529,7 +48609,7 @@
     <row r="246">
       <c r="A246" s="13" t="inlineStr">
         <is>
-          <t>2026-03-02 02:18:59</t>
+          <t>2026-03-01 17:18:59</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
@@ -48591,7 +48671,7 @@
     <row r="247">
       <c r="A247" s="13" t="inlineStr">
         <is>
-          <t>2026-02-24 01:40:38</t>
+          <t>2026-02-23 16:40:38</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
@@ -48653,7 +48733,7 @@
     <row r="248">
       <c r="A248" s="13" t="inlineStr">
         <is>
-          <t>2026-02-24 00:10:31</t>
+          <t>2026-02-23 15:10:31</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
@@ -48715,7 +48795,7 @@
     <row r="249">
       <c r="A249" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 23:33:47</t>
+          <t>2026-02-23 14:33:47</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
@@ -48777,7 +48857,7 @@
     <row r="250">
       <c r="A250" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 22:40:54</t>
+          <t>2026-02-23 13:40:54</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
@@ -48839,7 +48919,7 @@
     <row r="251">
       <c r="A251" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 21:58:56</t>
+          <t>2026-02-23 12:58:56</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
@@ -48901,7 +48981,7 @@
     <row r="252">
       <c r="A252" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 19:21:48</t>
+          <t>2026-02-23 10:21:48</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
@@ -48963,7 +49043,7 @@
     <row r="253">
       <c r="A253" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 17:17:13</t>
+          <t>2026-02-23 08:17:13</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
@@ -49025,7 +49105,7 @@
     <row r="254">
       <c r="A254" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 04:22:01</t>
+          <t>2026-02-22 19:22:01</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
@@ -49087,7 +49167,7 @@
     <row r="255">
       <c r="A255" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 03:23:51</t>
+          <t>2026-02-22 18:23:51</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
@@ -49149,7 +49229,7 @@
     <row r="256">
       <c r="A256" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 02:58:18</t>
+          <t>2026-02-22 17:58:18</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
@@ -49211,7 +49291,7 @@
     <row r="257">
       <c r="A257" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 02:29:21</t>
+          <t>2026-02-22 17:29:21</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
@@ -49273,7 +49353,7 @@
     <row r="258">
       <c r="A258" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 01:59:09</t>
+          <t>2026-02-22 16:59:09</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
@@ -49335,7 +49415,7 @@
     <row r="259">
       <c r="A259" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 01:32:08</t>
+          <t>2026-02-22 16:32:08</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
@@ -49397,7 +49477,7 @@
     <row r="260">
       <c r="A260" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 03:34:36</t>
+          <t>2026-02-20 18:34:36</t>
         </is>
       </c>
       <c r="B260" s="13" t="inlineStr">
@@ -49459,7 +49539,7 @@
     <row r="261">
       <c r="A261" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 02:57:13</t>
+          <t>2026-02-20 17:57:13</t>
         </is>
       </c>
       <c r="B261" s="13" t="inlineStr">
@@ -49521,7 +49601,7 @@
     <row r="262">
       <c r="A262" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 02:19:01</t>
+          <t>2026-02-20 17:19:01</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
@@ -49583,7 +49663,7 @@
     <row r="263">
       <c r="A263" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 01:41:10</t>
+          <t>2026-02-20 16:41:10</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
@@ -49645,7 +49725,7 @@
     <row r="264">
       <c r="A264" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 00:57:47</t>
+          <t>2026-02-20 15:57:47</t>
         </is>
       </c>
       <c r="B264" s="13" t="inlineStr">
@@ -49707,7 +49787,7 @@
     <row r="265">
       <c r="A265" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 00:39:52</t>
+          <t>2026-02-20 15:39:52</t>
         </is>
       </c>
       <c r="B265" s="13" t="inlineStr">
@@ -49769,7 +49849,7 @@
     <row r="266">
       <c r="A266" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 01:21:13</t>
+          <t>2026-02-19 16:21:13</t>
         </is>
       </c>
       <c r="B266" s="13" t="inlineStr">
@@ -49831,7 +49911,7 @@
     <row r="267">
       <c r="A267" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 00:33:10</t>
+          <t>2026-02-19 15:33:10</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
@@ -49893,7 +49973,7 @@
     <row r="268">
       <c r="A268" s="13" t="inlineStr">
         <is>
-          <t>2026-02-18 00:37:38</t>
+          <t>2026-02-17 15:37:38</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
@@ -49955,7 +50035,7 @@
     <row r="269">
       <c r="A269" s="13" t="inlineStr">
         <is>
-          <t>2026-02-17 23:58:39</t>
+          <t>2026-02-17 14:58:39</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
@@ -50017,7 +50097,7 @@
     <row r="270">
       <c r="A270" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 02:24:16</t>
+          <t>2026-02-15 17:24:16</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
@@ -50079,7 +50159,7 @@
     <row r="271">
       <c r="A271" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 01:47:19</t>
+          <t>2026-02-15 16:47:19</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
@@ -50141,7 +50221,7 @@
     <row r="272">
       <c r="A272" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 00:56:43</t>
+          <t>2026-02-15 15:56:43</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
@@ -50203,7 +50283,7 @@
     <row r="273">
       <c r="A273" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 00:26:20</t>
+          <t>2026-02-15 15:26:20</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
@@ -50265,7 +50345,7 @@
     <row r="274">
       <c r="A274" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 23:48:44</t>
+          <t>2026-02-15 14:48:44</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
@@ -50327,7 +50407,7 @@
     <row r="275">
       <c r="A275" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 04:17:17</t>
+          <t>2026-02-14 19:17:17</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
@@ -50389,7 +50469,7 @@
     <row r="276">
       <c r="A276" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 03:53:01</t>
+          <t>2026-02-14 18:53:01</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
@@ -50451,7 +50531,7 @@
     <row r="277">
       <c r="A277" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:59:46</t>
+          <t>2026-02-14 17:59:46</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
@@ -50513,7 +50593,7 @@
     <row r="278">
       <c r="A278" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:26:42</t>
+          <t>2026-02-14 17:26:42</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
@@ -50575,7 +50655,7 @@
     <row r="279">
       <c r="A279" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:00:09</t>
+          <t>2026-02-14 17:00:09</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
@@ -50637,7 +50717,7 @@
     <row r="280">
       <c r="A280" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 01:39:16</t>
+          <t>2026-02-14 16:39:16</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
@@ -50699,7 +50779,7 @@
     <row r="281">
       <c r="A281" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 00:56:51</t>
+          <t>2026-02-14 15:56:51</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
@@ -50761,7 +50841,7 @@
     <row r="282">
       <c r="A282" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 23:52:26</t>
+          <t>2026-02-14 14:52:26</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
@@ -50823,7 +50903,7 @@
     <row r="283">
       <c r="A283" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 23:14:55</t>
+          <t>2026-02-14 14:14:55</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
@@ -50885,7 +50965,7 @@
     <row r="284">
       <c r="A284" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 04:19:58</t>
+          <t>2026-02-13 19:19:58</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
@@ -50947,7 +51027,7 @@
     <row r="285">
       <c r="A285" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 03:37:53</t>
+          <t>2026-02-13 18:37:53</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
@@ -51009,7 +51089,7 @@
     <row r="286">
       <c r="A286" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 03:03:31</t>
+          <t>2026-02-13 18:03:31</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
@@ -51071,7 +51151,7 @@
     <row r="287">
       <c r="A287" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 02:08:36</t>
+          <t>2026-02-13 17:08:36</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
@@ -51133,7 +51213,7 @@
     <row r="288">
       <c r="A288" s="13" t="inlineStr">
         <is>
-          <t>2026-02-12 00:20:03</t>
+          <t>2026-02-11 15:20:03</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
@@ -51195,7 +51275,7 @@
     <row r="289">
       <c r="A289" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 03:05:03</t>
+          <t>2026-02-10 18:05:03</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
@@ -51257,7 +51337,7 @@
     <row r="290">
       <c r="A290" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 02:14:02</t>
+          <t>2026-02-10 17:14:02</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
@@ -51319,7 +51399,7 @@
     <row r="291">
       <c r="A291" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 01:33:21</t>
+          <t>2026-02-10 16:33:21</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
@@ -51381,7 +51461,7 @@
     <row r="292">
       <c r="A292" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 01:01:41</t>
+          <t>2026-02-10 16:01:41</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
@@ -51443,7 +51523,7 @@
     <row r="293">
       <c r="A293" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 01:49:32</t>
+          <t>2026-02-09 16:49:32</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
@@ -51505,7 +51585,7 @@
     <row r="294">
       <c r="A294" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 01:42:29</t>
+          <t>2026-02-09 16:42:29</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
@@ -51567,7 +51647,7 @@
     <row r="295">
       <c r="A295" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 23:44:10</t>
+          <t>2026-02-09 14:44:10</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
@@ -51629,7 +51709,7 @@
     <row r="296">
       <c r="A296" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 23:00:28</t>
+          <t>2026-02-09 14:00:28</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
@@ -51691,7 +51771,7 @@
     <row r="297">
       <c r="A297" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 00:27:49</t>
+          <t>2026-02-08 15:27:49</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
@@ -51753,7 +51833,7 @@
     <row r="298">
       <c r="A298" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 00:16:42</t>
+          <t>2026-02-08 15:16:42</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
@@ -51815,7 +51895,7 @@
     <row r="299">
       <c r="A299" s="13" t="inlineStr">
         <is>
-          <t>2026-02-08 04:04:43</t>
+          <t>2026-02-07 19:04:43</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
@@ -51877,7 +51957,7 @@
     <row r="300">
       <c r="A300" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 03:13:11</t>
+          <t>2026-02-06 18:13:11</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
@@ -51939,7 +52019,7 @@
     <row r="301">
       <c r="A301" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 02:19:42</t>
+          <t>2026-02-06 17:19:42</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
@@ -52001,7 +52081,7 @@
     <row r="302">
       <c r="A302" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 01:37:36</t>
+          <t>2026-02-06 16:37:36</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
@@ -52063,7 +52143,7 @@
     <row r="303">
       <c r="A303" s="13" t="inlineStr">
         <is>
-          <t>2026-02-03 23:04:49</t>
+          <t>2026-02-03 14:04:49</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
@@ -52125,7 +52205,7 @@
     <row r="304">
       <c r="A304" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 23:21:38</t>
+          <t>2026-02-02 14:21:38</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
@@ -52187,7 +52267,7 @@
     <row r="305">
       <c r="A305" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 03:08:17</t>
+          <t>2026-02-01 18:08:17</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
@@ -52249,7 +52329,7 @@
     <row r="306">
       <c r="A306" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 02:41:55</t>
+          <t>2026-02-01 17:41:55</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
@@ -52311,7 +52391,7 @@
     <row r="307">
       <c r="A307" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 02:09:57</t>
+          <t>2026-02-01 17:09:57</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
@@ -52373,7 +52453,7 @@
     <row r="308">
       <c r="A308" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 01:41:49</t>
+          <t>2026-02-01 16:41:49</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
@@ -52435,7 +52515,7 @@
     <row r="309">
       <c r="A309" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 02:22:13</t>
+          <t>2026-01-31 17:22:13</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
@@ -52497,7 +52577,7 @@
     <row r="310">
       <c r="A310" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 01:20:54</t>
+          <t>2026-01-31 16:20:54</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
@@ -52559,7 +52639,7 @@
     <row r="311">
       <c r="A311" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 01:09:32</t>
+          <t>2026-01-31 16:09:32</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
@@ -52621,7 +52701,7 @@
     <row r="312">
       <c r="A312" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 00:29:37</t>
+          <t>2026-01-31 15:29:37</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
@@ -52683,7 +52763,7 @@
     <row r="313">
       <c r="A313" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 00:03:50</t>
+          <t>2026-01-31 15:03:50</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
@@ -52745,7 +52825,7 @@
     <row r="314">
       <c r="A314" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 23:15:28</t>
+          <t>2026-01-31 14:15:28</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
@@ -52807,7 +52887,7 @@
     <row r="315">
       <c r="A315" s="13" t="inlineStr">
         <is>
-          <t>2026-01-29 00:36:39</t>
+          <t>2026-01-28 15:36:39</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
@@ -52869,7 +52949,7 @@
     <row r="316">
       <c r="A316" s="13" t="inlineStr">
         <is>
-          <t>2026-01-29 00:02:45</t>
+          <t>2026-01-28 15:02:45</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
@@ -52931,7 +53011,7 @@
     <row r="317">
       <c r="A317" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 23:26:47</t>
+          <t>2026-01-28 14:26:47</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
@@ -52993,7 +53073,7 @@
     <row r="318">
       <c r="A318" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 23:04:33</t>
+          <t>2026-01-28 14:04:33</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
@@ -53055,7 +53135,7 @@
     <row r="319">
       <c r="A319" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 00:33:31</t>
+          <t>2026-01-27 15:33:31</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
@@ -53117,7 +53197,7 @@
     <row r="320">
       <c r="A320" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 23:59:21</t>
+          <t>2026-01-27 14:59:21</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
@@ -53179,7 +53259,7 @@
     <row r="321">
       <c r="A321" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 23:08:33</t>
+          <t>2026-01-27 14:08:33</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
@@ -53241,7 +53321,7 @@
     <row r="322">
       <c r="A322" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 23:28:17</t>
+          <t>2026-01-25 14:28:17</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
@@ -53303,7 +53383,7 @@
     <row r="323">
       <c r="A323" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 22:56:22</t>
+          <t>2026-01-25 13:56:22</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
@@ -53365,7 +53445,7 @@
     <row r="324">
       <c r="A324" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 22:28:25</t>
+          <t>2026-01-25 13:28:25</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
@@ -53427,7 +53507,7 @@
     <row r="325">
       <c r="A325" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 21:42:03</t>
+          <t>2026-01-25 12:42:03</t>
         </is>
       </c>
       <c r="B325" s="13" t="inlineStr">
@@ -53489,7 +53569,7 @@
     <row r="326">
       <c r="A326" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 19:38:23</t>
+          <t>2026-01-25 10:38:23</t>
         </is>
       </c>
       <c r="B326" s="13" t="inlineStr">
@@ -53551,7 +53631,7 @@
     <row r="327">
       <c r="A327" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 18:56:35</t>
+          <t>2026-01-25 09:56:35</t>
         </is>
       </c>
       <c r="B327" s="13" t="inlineStr">
@@ -53613,7 +53693,7 @@
     <row r="328">
       <c r="A328" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 18:29:19</t>
+          <t>2026-01-25 09:29:19</t>
         </is>
       </c>
       <c r="B328" s="13" t="inlineStr">
@@ -53675,7 +53755,7 @@
     <row r="329">
       <c r="A329" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 17:14:05</t>
+          <t>2026-01-25 08:14:05</t>
         </is>
       </c>
       <c r="B329" s="13" t="inlineStr">
@@ -53737,7 +53817,7 @@
     <row r="330">
       <c r="A330" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 02:47:24</t>
+          <t>2026-01-23 17:47:24</t>
         </is>
       </c>
       <c r="B330" s="13" t="inlineStr">
@@ -53799,7 +53879,7 @@
     <row r="331">
       <c r="A331" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 02:12:26</t>
+          <t>2026-01-23 17:12:26</t>
         </is>
       </c>
       <c r="B331" s="13" t="inlineStr">
@@ -53861,7 +53941,7 @@
     <row r="332">
       <c r="A332" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 01:33:34</t>
+          <t>2026-01-23 16:33:34</t>
         </is>
       </c>
       <c r="B332" s="13" t="inlineStr">
@@ -53923,7 +54003,7 @@
     <row r="333">
       <c r="A333" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 01:00:39</t>
+          <t>2026-01-23 16:00:39</t>
         </is>
       </c>
       <c r="B333" s="13" t="inlineStr">
@@ -53985,7 +54065,7 @@
     <row r="334">
       <c r="A334" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 00:19:07</t>
+          <t>2026-01-23 15:19:07</t>
         </is>
       </c>
       <c r="B334" s="13" t="inlineStr">
@@ -54047,7 +54127,7 @@
     <row r="335">
       <c r="A335" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 23:52:33</t>
+          <t>2026-01-23 14:52:33</t>
         </is>
       </c>
       <c r="B335" s="13" t="inlineStr">
@@ -54109,7 +54189,7 @@
     <row r="336">
       <c r="A336" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 23:19:19</t>
+          <t>2026-01-23 14:19:19</t>
         </is>
       </c>
       <c r="B336" s="13" t="inlineStr">
@@ -54171,7 +54251,7 @@
     <row r="337">
       <c r="A337" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36:59</t>
+          <t>2026-01-23 13:36:59</t>
         </is>
       </c>
       <c r="B337" s="13" t="inlineStr">
@@ -54233,7 +54313,7 @@
     <row r="338">
       <c r="A338" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 03:01:58</t>
+          <t>2026-01-22 18:01:58</t>
         </is>
       </c>
       <c r="B338" s="13" t="inlineStr">
@@ -54295,7 +54375,7 @@
     <row r="339">
       <c r="A339" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 02:25:41</t>
+          <t>2026-01-22 17:25:41</t>
         </is>
       </c>
       <c r="B339" s="13" t="inlineStr">
@@ -54357,7 +54437,7 @@
     <row r="340">
       <c r="A340" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 00:32:45</t>
+          <t>2026-01-22 15:32:45</t>
         </is>
       </c>
       <c r="B340" s="13" t="inlineStr">
@@ -54419,7 +54499,7 @@
     <row r="341">
       <c r="A341" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 23:54:46</t>
+          <t>2026-01-22 14:54:46</t>
         </is>
       </c>
       <c r="B341" s="13" t="inlineStr">
@@ -54481,7 +54561,7 @@
     <row r="342">
       <c r="A342" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 23:17:42</t>
+          <t>2026-01-22 14:17:42</t>
         </is>
       </c>
       <c r="B342" s="13" t="inlineStr">
@@ -54543,7 +54623,7 @@
     <row r="343">
       <c r="A343" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 01:10:08</t>
+          <t>2026-01-21 16:10:08</t>
         </is>
       </c>
       <c r="B343" s="13" t="inlineStr">
@@ -54605,7 +54685,7 @@
     <row r="344">
       <c r="A344" s="13" t="inlineStr">
         <is>
-          <t>2026-01-21 00:27:51</t>
+          <t>2026-01-20 15:27:51</t>
         </is>
       </c>
       <c r="B344" s="13" t="inlineStr">
@@ -54667,7 +54747,7 @@
     <row r="345">
       <c r="A345" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 23:25:34</t>
+          <t>2026-01-20 14:25:34</t>
         </is>
       </c>
       <c r="B345" s="13" t="inlineStr">
@@ -54729,7 +54809,7 @@
     <row r="346">
       <c r="A346" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 22:56:13</t>
+          <t>2026-01-20 13:56:13</t>
         </is>
       </c>
       <c r="B346" s="13" t="inlineStr">
@@ -54791,7 +54871,7 @@
     <row r="347">
       <c r="A347" s="13" t="inlineStr">
         <is>
-          <t>2026-01-19 01:59:11</t>
+          <t>2026-01-18 16:59:11</t>
         </is>
       </c>
       <c r="B347" s="13" t="inlineStr">
@@ -54853,7 +54933,7 @@
     <row r="348">
       <c r="A348" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 03:05:32</t>
+          <t>2026-01-17 18:05:32</t>
         </is>
       </c>
       <c r="B348" s="13" t="inlineStr">
@@ -54915,7 +54995,7 @@
     <row r="349">
       <c r="A349" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 02:19:17</t>
+          <t>2026-01-17 17:19:17</t>
         </is>
       </c>
       <c r="B349" s="13" t="inlineStr">
@@ -54977,7 +55057,7 @@
     <row r="350">
       <c r="A350" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 01:58:17</t>
+          <t>2026-01-17 16:58:17</t>
         </is>
       </c>
       <c r="B350" s="13" t="inlineStr">
@@ -55039,7 +55119,7 @@
     <row r="351">
       <c r="A351" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 01:18:29</t>
+          <t>2026-01-17 16:18:29</t>
         </is>
       </c>
       <c r="B351" s="13" t="inlineStr">
@@ -55101,7 +55181,7 @@
     <row r="352">
       <c r="A352" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 00:38:58</t>
+          <t>2026-01-17 15:38:58</t>
         </is>
       </c>
       <c r="B352" s="13" t="inlineStr">
@@ -55163,7 +55243,7 @@
     <row r="353">
       <c r="A353" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 18:46:30</t>
+          <t>2026-01-17 09:46:30</t>
         </is>
       </c>
       <c r="B353" s="13" t="inlineStr">
@@ -55225,7 +55305,7 @@
     <row r="354">
       <c r="A354" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 02:21:36</t>
+          <t>2026-01-16 17:21:36</t>
         </is>
       </c>
       <c r="B354" s="13" t="inlineStr">
@@ -55287,7 +55367,7 @@
     <row r="355">
       <c r="A355" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 01:51:05</t>
+          <t>2026-01-16 16:51:05</t>
         </is>
       </c>
       <c r="B355" s="13" t="inlineStr">
@@ -55349,7 +55429,7 @@
     <row r="356">
       <c r="A356" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 01:18:22</t>
+          <t>2026-01-16 16:18:22</t>
         </is>
       </c>
       <c r="B356" s="13" t="inlineStr">
@@ -55411,7 +55491,7 @@
     <row r="357">
       <c r="A357" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 01:41:15</t>
+          <t>2026-01-15 16:41:15</t>
         </is>
       </c>
       <c r="B357" s="13" t="inlineStr">
@@ -55473,7 +55553,7 @@
     <row r="358">
       <c r="A358" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 01:05:38</t>
+          <t>2026-01-15 16:05:38</t>
         </is>
       </c>
       <c r="B358" s="13" t="inlineStr">
@@ -55535,7 +55615,7 @@
     <row r="359">
       <c r="A359" s="13" t="inlineStr">
         <is>
-          <t>2026-01-14 00:57:21</t>
+          <t>2026-01-13 15:57:21</t>
         </is>
       </c>
       <c r="B359" s="13" t="inlineStr">
@@ -55597,7 +55677,7 @@
     <row r="360">
       <c r="A360" s="13" t="inlineStr">
         <is>
-          <t>2026-01-14 00:19:49</t>
+          <t>2026-01-13 15:19:49</t>
         </is>
       </c>
       <c r="B360" s="13" t="inlineStr">
@@ -55659,7 +55739,7 @@
     <row r="361">
       <c r="A361" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 23:53:29</t>
+          <t>2026-01-13 14:53:29</t>
         </is>
       </c>
       <c r="B361" s="13" t="inlineStr">
@@ -55721,7 +55801,7 @@
     <row r="362">
       <c r="A362" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 02:23:29</t>
+          <t>2026-01-12 17:23:29</t>
         </is>
       </c>
       <c r="B362" s="13" t="inlineStr">
@@ -55783,7 +55863,7 @@
     <row r="363">
       <c r="A363" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 01:42:12</t>
+          <t>2026-01-12 16:42:12</t>
         </is>
       </c>
       <c r="B363" s="13" t="inlineStr">
@@ -55845,7 +55925,7 @@
     <row r="364">
       <c r="A364" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 01:17:01</t>
+          <t>2026-01-12 16:17:01</t>
         </is>
       </c>
       <c r="B364" s="13" t="inlineStr">
@@ -55907,7 +55987,7 @@
     <row r="365">
       <c r="A365" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 00:43:11</t>
+          <t>2026-01-12 15:43:11</t>
         </is>
       </c>
       <c r="B365" s="13" t="inlineStr">
@@ -55969,7 +56049,7 @@
     <row r="366">
       <c r="A366" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 17:24:44</t>
+          <t>2026-01-12 08:24:44</t>
         </is>
       </c>
       <c r="B366" s="13" t="inlineStr">
@@ -56031,7 +56111,7 @@
     <row r="367">
       <c r="A367" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 03:12:16</t>
+          <t>2026-01-11 18:12:16</t>
         </is>
       </c>
       <c r="B367" s="13" t="inlineStr">
@@ -56093,7 +56173,7 @@
     <row r="368">
       <c r="A368" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 02:54:03</t>
+          <t>2026-01-10 17:54:03</t>
         </is>
       </c>
       <c r="B368" s="13" t="inlineStr">
@@ -56155,7 +56235,7 @@
     <row r="369">
       <c r="A369" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 02:14:56</t>
+          <t>2026-01-10 17:14:56</t>
         </is>
       </c>
       <c r="B369" s="13" t="inlineStr">
@@ -56217,7 +56297,7 @@
     <row r="370">
       <c r="A370" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 01:17:21</t>
+          <t>2026-01-10 16:17:21</t>
         </is>
       </c>
       <c r="B370" s="13" t="inlineStr">
@@ -56279,7 +56359,7 @@
     <row r="371">
       <c r="A371" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 00:22:11</t>
+          <t>2026-01-10 15:22:11</t>
         </is>
       </c>
       <c r="B371" s="13" t="inlineStr">
@@ -56341,7 +56421,7 @@
     <row r="372">
       <c r="A372" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 23:38:24</t>
+          <t>2026-01-10 14:38:24</t>
         </is>
       </c>
       <c r="B372" s="13" t="inlineStr">
@@ -56403,7 +56483,7 @@
     <row r="373">
       <c r="A373" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 02:54:19</t>
+          <t>2026-01-09 17:54:19</t>
         </is>
       </c>
       <c r="B373" s="13" t="inlineStr">
@@ -56465,7 +56545,7 @@
     <row r="374">
       <c r="A374" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 02:00:16</t>
+          <t>2026-01-09 17:00:16</t>
         </is>
       </c>
       <c r="B374" s="13" t="inlineStr">
@@ -56527,7 +56607,7 @@
     <row r="375">
       <c r="A375" s="13" t="inlineStr">
         <is>
-          <t>2026-01-09 23:36:27</t>
+          <t>2026-01-09 14:36:27</t>
         </is>
       </c>
       <c r="B375" s="13" t="inlineStr">
@@ -56586,8 +56666,70 @@
         </is>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-05 14:21:47</t>
+        </is>
+      </c>
+      <c r="B376" s="13" t="inlineStr">
+        <is>
+          <t>ランク</t>
+        </is>
+      </c>
+      <c r="C376" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D376" s="13" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E376" s="13" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F376" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G376" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H376" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I376" s="13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J376" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K376" s="14" t="inlineStr"/>
+      <c r="L376" s="14" t="inlineStr"/>
+      <c r="M376" s="14" t="inlineStr"/>
+      <c r="N376" s="14" t="inlineStr"/>
+      <c r="O376" s="14" t="inlineStr"/>
+      <c r="P376" s="13" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P375"/>
+  <autoFilter ref="A1:P376"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'キュー別'!$A$1:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'チャンピオン別'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SUPチャンピオン別'!$A$1:$L$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$376</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$376</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$375</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$375</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,14 +532,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>対象期間：2026-01-05 14:21:47 ～ 2026-07-31 19:00:11</t>
+          <t>対象期間：2026-01-09 23:36:27 ～ 2026-08-01 04:00:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-01 08:58:22</t>
+          <t>出力日時：2026-08-01 23:46:58</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.4773333333333333</v>
+        <v>0.4786096256684492</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.666666666666667</v>
+        <v>1.671122994652406</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5.328</v>
+        <v>5.328877005347594</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>8.909333333333333</v>
+        <v>8.909090909090908</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.99</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>60.176</v>
+        <v>60.24331550802139</v>
       </c>
     </row>
     <row r="15">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2.053040000000001</v>
+        <v>2.055427807486631</v>
       </c>
     </row>
     <row r="16">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>56.41333333333333</v>
+        <v>56.44385026737968</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1.821973333333332</v>
+        <v>1.82283422459893</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.5085324232081911</v>
+        <v>0.5102739726027398</v>
       </c>
     </row>
     <row r="24">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>1.440273037542662</v>
+        <v>1.445205479452055</v>
       </c>
     </row>
     <row r="25">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.156996587030717</v>
+        <v>5.157534246575342</v>
       </c>
     </row>
     <row r="26">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>9.805460750853243</v>
+        <v>9.808219178082192</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>36.19112627986348</v>
+        <v>36.19520547945206</v>
       </c>
     </row>
     <row r="29">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1.251058020477816</v>
+        <v>1.251369863013698</v>
       </c>
     </row>
     <row r="30">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>63.75767918088737</v>
+        <v>63.82191780821918</v>
       </c>
     </row>
     <row r="31">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>2.058122866894197</v>
+        <v>2.060034246575342</v>
       </c>
     </row>
   </sheetData>
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>149</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.5085324232081911</v>
+        <v>0.5102739726027398</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.440273037542662</v>
+        <v>1.445205479452055</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5.156996587030717</v>
+        <v>5.157534246575342</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9.805460750853243</v>
+        <v>9.808219178082192</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.251058020477816</v>
+        <v>1.251369863013698</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>63.75767918088737</v>
+        <v>63.82191780821918</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>2.058122866894197</v>
+        <v>2.060034246575342</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.933833333333332</v>
+        <v>4.933833333333333</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>31.96666666666667</v>
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>2.242894736842106</v>
+        <v>2.242894736842105</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>53.4078947368421</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>1.735427631578947</v>
+        <v>1.735427631578948</v>
       </c>
     </row>
     <row r="3">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>31</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.4366197183098591</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.112676056338028</v>
+        <v>1.128571428571429</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>5.746478873239437</v>
+        <v>5.757142857142857</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>9.929577464788732</v>
+        <v>9.942857142857143</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.240140845070422</v>
+        <v>1.241285714285714</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>69.28169014084507</v>
+        <v>69.62857142857143</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.192535211267606</v>
+        <v>2.202428571428571</v>
       </c>
     </row>
   </sheetData>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1.797111111111112</v>
+        <v>1.797111111111111</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>68.51111111111111</v>
@@ -1516,25 +1516,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.775</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.15</v>
+        <v>5.153846153846154</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.225</v>
+        <v>7.17948717948718</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.231</v>
+        <v>1.232820512820513</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.75</v>
+        <v>53.97435897435897</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.86175</v>
+        <v>1.871025641025641</v>
       </c>
     </row>
     <row r="6">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5.148285714285714</v>
+        <v>5.148285714285715</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>34.6</v>
@@ -1800,7 +1800,7 @@
         <v>25.625</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.8562500000000001</v>
+        <v>0.85625</v>
       </c>
     </row>
     <row r="12">
@@ -1842,7 +1842,7 @@
         <v>21.83333333333333</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.8633333333333334</v>
+        <v>0.8633333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5.05</v>
+        <v>5.050000000000001</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>16.25</v>
@@ -2833,25 +2833,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.775</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.15</v>
+        <v>5.153846153846154</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.225</v>
+        <v>7.17948717948718</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.231</v>
+        <v>1.232820512820513</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.75</v>
+        <v>53.97435897435897</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.86175</v>
+        <v>1.871025641025641</v>
       </c>
     </row>
     <row r="6">
@@ -3224,7 +3224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V376"/>
+  <dimension ref="A1:V375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3366,7 +3366,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00:11</t>
+          <t>2026-08-01 04:00:11</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 18:30:26</t>
+          <t>2026-08-01 03:30:26</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 17:52:16</t>
+          <t>2026-08-01 02:52:16</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 16:50:20</t>
+          <t>2026-08-01 01:50:20</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 16:16:45</t>
+          <t>2026-08-01 01:16:45</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 13:56:19</t>
+          <t>2026-07-31 22:56:19</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 13:22:46</t>
+          <t>2026-07-31 22:22:46</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 12:49:35</t>
+          <t>2026-07-31 21:49:35</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 14:51:39</t>
+          <t>2026-07-28 23:51:39</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 14:05:20</t>
+          <t>2026-07-28 23:05:20</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -4166,7 +4166,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 16:21:51</t>
+          <t>2026-07-27 01:21:51</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 15:43:02</t>
+          <t>2026-07-27 00:43:02</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -4326,7 +4326,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 14:12:09</t>
+          <t>2026-07-25 23:12:09</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 13:30:57</t>
+          <t>2026-07-25 22:30:57</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -4486,7 +4486,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24 15:11:55</t>
+          <t>2026-07-25 00:11:55</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -4566,7 +4566,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24 14:25:38</t>
+          <t>2026-07-24 23:25:38</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -4646,7 +4646,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 15:17:56</t>
+          <t>2026-07-22 00:17:56</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 15:04:35</t>
+          <t>2026-07-22 00:04:35</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 14:25:56</t>
+          <t>2026-07-21 23:25:56</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -4886,7 +4886,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 13:44:36</t>
+          <t>2026-07-21 22:44:36</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -4966,7 +4966,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 13:18:59</t>
+          <t>2026-07-21 22:18:59</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-19 18:20:20</t>
+          <t>2026-07-20 03:20:20</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -5126,7 +5126,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-19 17:39:51</t>
+          <t>2026-07-20 02:39:51</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 09:59:14</t>
+          <t>2026-07-18 18:59:14</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -5286,7 +5286,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 09:21:14</t>
+          <t>2026-07-18 18:21:14</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -5366,7 +5366,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 14:06:28</t>
+          <t>2026-07-16 23:06:28</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 13:32:42</t>
+          <t>2026-07-16 22:32:42</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -5526,7 +5526,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 15:40:48</t>
+          <t>2026-07-16 00:40:48</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -5606,7 +5606,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 14:41:56</t>
+          <t>2026-07-15 23:41:56</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 13:58:44</t>
+          <t>2026-07-15 22:58:44</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -5766,7 +5766,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 13:34:16</t>
+          <t>2026-07-15 22:34:16</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -5846,7 +5846,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 14:36:35</t>
+          <t>2026-07-14 23:36:35</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -5926,7 +5926,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 13:49:50</t>
+          <t>2026-07-14 22:49:50</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -6006,7 +6006,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 16:02:29</t>
+          <t>2026-07-14 01:02:29</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 15:22:46</t>
+          <t>2026-07-14 00:22:46</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 14:51:38</t>
+          <t>2026-07-13 23:51:38</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 17:05:19</t>
+          <t>2026-07-13 02:05:19</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -6326,7 +6326,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 16:29:17</t>
+          <t>2026-07-13 01:29:17</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -6406,7 +6406,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 18:11:38</t>
+          <t>2026-07-12 03:11:38</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -6486,7 +6486,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 17:46:15</t>
+          <t>2026-07-12 02:46:15</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -6566,7 +6566,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10 18:42:29</t>
+          <t>2026-07-11 03:42:29</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -6646,7 +6646,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10 18:06:21</t>
+          <t>2026-07-11 03:06:21</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -6726,7 +6726,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08 17:55:25</t>
+          <t>2026-07-09 02:55:25</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -6806,7 +6806,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08 17:17:09</t>
+          <t>2026-07-09 02:17:09</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -6886,7 +6886,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05 17:03:51</t>
+          <t>2026-07-06 02:03:51</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -6966,7 +6966,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05 16:07:17</t>
+          <t>2026-07-06 01:07:17</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05 15:23:00</t>
+          <t>2026-07-06 00:23:00</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -7126,7 +7126,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>2026-07-04 18:21:23</t>
+          <t>2026-07-05 03:21:23</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03 18:01:40</t>
+          <t>2026-07-04 03:01:40</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -7286,7 +7286,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02 16:48:19</t>
+          <t>2026-07-03 01:48:19</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -7366,7 +7366,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 15:21:19</t>
+          <t>2026-07-01 00:21:19</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -7446,7 +7446,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 14:38:16</t>
+          <t>2026-06-30 23:38:16</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -7526,7 +7526,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-06-29 16:16:28</t>
+          <t>2026-06-30 01:16:28</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-29 15:34:32</t>
+          <t>2026-06-30 00:34:32</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -7686,7 +7686,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 15:50:56</t>
+          <t>2026-06-26 00:50:56</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -7766,7 +7766,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 15:06:40</t>
+          <t>2026-06-26 00:06:40</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -7846,7 +7846,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 17:07:56</t>
+          <t>2026-06-25 02:07:56</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -7926,7 +7926,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 16:33:19</t>
+          <t>2026-06-25 01:33:19</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -8006,7 +8006,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 15:47:59</t>
+          <t>2026-06-25 00:47:59</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -8086,7 +8086,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 15:08:31</t>
+          <t>2026-06-25 00:08:31</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 14:33:15</t>
+          <t>2026-06-24 23:33:15</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -8246,7 +8246,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 13:39:11</t>
+          <t>2026-06-24 22:39:11</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -8326,7 +8326,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22 16:16:06</t>
+          <t>2026-06-23 01:16:06</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -8406,7 +8406,7 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22 15:38:08</t>
+          <t>2026-06-23 00:38:08</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -8486,7 +8486,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22 15:29:33</t>
+          <t>2026-06-23 00:29:33</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -8566,7 +8566,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 16:54:04</t>
+          <t>2026-06-19 01:54:04</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 16:14:50</t>
+          <t>2026-06-19 01:14:50</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 15:35:17</t>
+          <t>2026-06-19 00:35:17</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -8806,7 +8806,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 14:55:50</t>
+          <t>2026-06-18 23:55:50</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -8886,7 +8886,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 15:44:42</t>
+          <t>2026-06-18 00:44:42</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -8966,7 +8966,7 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 14:57:38</t>
+          <t>2026-06-17 23:57:38</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -9046,7 +9046,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16 16:58:55</t>
+          <t>2026-06-17 01:58:55</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -9126,7 +9126,7 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16 16:30:07</t>
+          <t>2026-06-17 01:30:07</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -9206,7 +9206,7 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 18:10:28</t>
+          <t>2026-06-15 03:10:28</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
@@ -9286,7 +9286,7 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 17:27:52</t>
+          <t>2026-06-15 02:27:52</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -9366,7 +9366,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 16:57:23</t>
+          <t>2026-06-15 01:57:23</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -9446,7 +9446,7 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 16:27:22</t>
+          <t>2026-06-15 01:27:22</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -9526,7 +9526,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 15:24:35</t>
+          <t>2026-06-15 00:24:35</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -9606,7 +9606,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 14:46:55</t>
+          <t>2026-06-14 23:46:55</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -9686,7 +9686,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 16:41:53</t>
+          <t>2026-06-14 01:41:53</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -9766,7 +9766,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 15:52:58</t>
+          <t>2026-06-14 00:52:58</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -9846,7 +9846,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 15:14:23</t>
+          <t>2026-06-14 00:14:23</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -9926,7 +9926,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 14:45:21</t>
+          <t>2026-06-13 23:45:21</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -10006,7 +10006,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 14:05:32</t>
+          <t>2026-06-13 23:05:32</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -10086,7 +10086,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 16:08:14</t>
+          <t>2026-06-11 01:08:14</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -10166,7 +10166,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 15:34:35</t>
+          <t>2026-06-11 00:34:35</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 15:09:17</t>
+          <t>2026-06-11 00:09:17</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -10326,7 +10326,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 14:27:53</t>
+          <t>2026-06-10 23:27:53</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09 15:49:00</t>
+          <t>2026-06-10 00:49:00</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -10486,7 +10486,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05 17:58:51</t>
+          <t>2026-06-06 02:58:51</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -10566,7 +10566,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>2026-06-05 17:15:04</t>
+          <t>2026-06-06 02:15:04</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -10646,7 +10646,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 14:49:14</t>
+          <t>2026-06-04 23:49:14</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -10726,7 +10726,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 12:40:04</t>
+          <t>2026-06-04 21:40:04</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -10806,7 +10806,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 12:17:24</t>
+          <t>2026-06-04 21:17:24</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -10886,7 +10886,7 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 16:06:27</t>
+          <t>2026-06-04 01:06:27</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -10966,7 +10966,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 15:31:09</t>
+          <t>2026-06-04 00:31:09</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -11046,7 +11046,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 14:53:57</t>
+          <t>2026-06-03 23:53:57</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -11126,7 +11126,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 13:44:02</t>
+          <t>2026-06-03 22:44:02</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02 13:49:11</t>
+          <t>2026-06-02 22:49:11</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -11286,7 +11286,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 14:56:06</t>
+          <t>2026-06-01 23:56:06</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -11366,7 +11366,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 14:20:26</t>
+          <t>2026-06-01 23:20:26</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -11446,7 +11446,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 14:01:06</t>
+          <t>2026-06-01 23:01:06</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -11526,7 +11526,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>2026-05-30 18:01:04</t>
+          <t>2026-05-31 03:01:04</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>2026-05-30 17:13:41</t>
+          <t>2026-05-31 02:13:41</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -11686,7 +11686,7 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:00:40</t>
+          <t>2026-05-25 23:00:40</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -11766,7 +11766,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 16:55:47</t>
+          <t>2026-05-25 01:55:47</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -11846,7 +11846,7 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 16:24:22</t>
+          <t>2026-05-25 01:24:22</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -11926,7 +11926,7 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 14:49:25</t>
+          <t>2026-05-24 23:49:25</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -12006,7 +12006,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 18:13:39</t>
+          <t>2026-05-24 03:13:39</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 17:41:52</t>
+          <t>2026-05-24 02:41:52</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -12166,7 +12166,7 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 14:19:04</t>
+          <t>2026-05-23 23:19:04</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -12246,7 +12246,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 13:43:20</t>
+          <t>2026-05-23 22:43:20</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -12326,7 +12326,7 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 06:54:19</t>
+          <t>2026-05-23 15:54:19</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -12406,7 +12406,7 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 17:25:24</t>
+          <t>2026-05-23 02:25:24</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -12486,7 +12486,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 16:29:23</t>
+          <t>2026-05-22 01:29:23</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -12566,7 +12566,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 15:48:49</t>
+          <t>2026-05-22 00:48:49</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -12646,7 +12646,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 15:00:45</t>
+          <t>2026-05-22 00:00:45</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -12726,7 +12726,7 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 14:22:44</t>
+          <t>2026-05-21 23:22:44</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -12806,7 +12806,7 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 15:05:15</t>
+          <t>2026-05-21 00:05:15</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -12886,7 +12886,7 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 14:43:50</t>
+          <t>2026-05-20 23:43:50</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -12966,7 +12966,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 13:57:45</t>
+          <t>2026-05-20 22:57:45</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -13046,7 +13046,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>2026-05-19 16:25:45</t>
+          <t>2026-05-20 01:25:45</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -13126,7 +13126,7 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>2026-05-19 15:46:42</t>
+          <t>2026-05-20 00:46:42</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -13206,7 +13206,7 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>2026-05-18 13:56:39</t>
+          <t>2026-05-18 22:56:39</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -13286,7 +13286,7 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14 16:35:56</t>
+          <t>2026-05-15 01:35:56</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -13366,7 +13366,7 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14 16:17:05</t>
+          <t>2026-05-15 01:17:05</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -13446,7 +13446,7 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14 15:05:48</t>
+          <t>2026-05-15 00:05:48</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -13526,7 +13526,7 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>2026-05-13 16:25:38</t>
+          <t>2026-05-14 01:25:38</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -13606,7 +13606,7 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 15:19:57</t>
+          <t>2026-05-12 00:19:57</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -13686,7 +13686,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 14:54:15</t>
+          <t>2026-05-11 23:54:15</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 14:14:30</t>
+          <t>2026-05-11 23:14:30</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -13846,7 +13846,7 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 13:37:05</t>
+          <t>2026-05-11 22:37:05</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -13926,7 +13926,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 12:53:13</t>
+          <t>2026-05-11 21:53:13</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -14006,7 +14006,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 15:04:01</t>
+          <t>2026-05-11 00:04:01</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -14086,7 +14086,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 16:54:24</t>
+          <t>2026-05-10 01:54:24</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -14166,7 +14166,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 16:22:50</t>
+          <t>2026-05-10 01:22:50</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -14246,7 +14246,7 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 15:26:16</t>
+          <t>2026-05-10 00:26:16</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -14326,7 +14326,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 14:38:30</t>
+          <t>2026-05-09 23:38:30</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -14406,7 +14406,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 13:50:20</t>
+          <t>2026-05-09 22:50:20</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -14486,7 +14486,7 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 13:13:25</t>
+          <t>2026-05-09 22:13:25</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -14566,7 +14566,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 11:00:11</t>
+          <t>2026-05-09 20:00:11</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -14646,7 +14646,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 10:10:28</t>
+          <t>2026-05-09 19:10:28</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -14726,7 +14726,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 17:17:27</t>
+          <t>2026-05-09 02:17:27</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -14806,7 +14806,7 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 16:38:25</t>
+          <t>2026-05-09 01:38:25</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -14886,7 +14886,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 15:58:58</t>
+          <t>2026-05-09 00:58:58</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -14966,7 +14966,7 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 15:37:55</t>
+          <t>2026-05-09 00:37:55</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -15046,7 +15046,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 16:48:31</t>
+          <t>2026-05-08 01:48:31</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -15126,7 +15126,7 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 16:02:52</t>
+          <t>2026-05-08 01:02:52</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -15206,7 +15206,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 15:23:29</t>
+          <t>2026-05-08 00:23:29</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -15286,7 +15286,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 16:30:56</t>
+          <t>2026-05-07 01:30:56</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -15366,7 +15366,7 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 15:42:16</t>
+          <t>2026-05-07 00:42:16</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 14:44:04</t>
+          <t>2026-05-06 23:44:04</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -15526,7 +15526,7 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 09:13:52</t>
+          <t>2026-05-06 18:13:52</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -15606,7 +15606,7 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 09:05:08</t>
+          <t>2026-05-06 18:05:08</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -15686,7 +15686,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 08:22:30</t>
+          <t>2026-05-06 17:22:30</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -15766,7 +15766,7 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 07:28:42</t>
+          <t>2026-05-06 16:28:42</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -15846,7 +15846,7 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 18:16:57</t>
+          <t>2026-05-06 03:16:57</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -15926,7 +15926,7 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 17:32:40</t>
+          <t>2026-05-06 02:32:40</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 17:23:28</t>
+          <t>2026-05-06 02:23:28</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -16086,7 +16086,7 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 16:48:28</t>
+          <t>2026-05-06 01:48:28</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -16166,7 +16166,7 @@
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 15:52:33</t>
+          <t>2026-05-06 00:52:33</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -16246,7 +16246,7 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 08:43:06</t>
+          <t>2026-05-05 17:43:06</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -16326,7 +16326,7 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 15:36:42</t>
+          <t>2026-05-03 00:36:42</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -16406,7 +16406,7 @@
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 14:51:09</t>
+          <t>2026-05-02 23:51:09</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -16486,7 +16486,7 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 13:15:10</t>
+          <t>2026-05-02 22:15:10</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -16566,7 +16566,7 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 12:29:49</t>
+          <t>2026-05-02 21:29:49</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -16646,7 +16646,7 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 16:39:42</t>
+          <t>2026-05-01 01:39:42</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -16726,7 +16726,7 @@
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 16:01:34</t>
+          <t>2026-05-01 01:01:34</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -16806,7 +16806,7 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 15:24:48</t>
+          <t>2026-05-01 00:24:48</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -16886,7 +16886,7 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 14:37:10</t>
+          <t>2026-04-30 23:37:10</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
@@ -16966,7 +16966,7 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 13:58:06</t>
+          <t>2026-04-30 22:58:06</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -17046,7 +17046,7 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 18:29:33</t>
+          <t>2026-04-30 03:29:33</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 17:54:07</t>
+          <t>2026-04-30 02:54:07</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
@@ -17206,7 +17206,7 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 17:20:58</t>
+          <t>2026-04-30 02:20:58</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -17286,7 +17286,7 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 16:42:01</t>
+          <t>2026-04-30 01:42:01</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
@@ -17366,7 +17366,7 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 16:03:17</t>
+          <t>2026-04-30 01:03:17</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -17446,7 +17446,7 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 15:19:47</t>
+          <t>2026-04-30 00:19:47</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -17526,7 +17526,7 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 14:29:53</t>
+          <t>2026-04-29 23:29:53</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
@@ -17606,7 +17606,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 13:59:49</t>
+          <t>2026-04-29 22:59:49</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -17686,7 +17686,7 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 13:38:22</t>
+          <t>2026-04-29 22:38:22</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
@@ -17766,7 +17766,7 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 13:17:44</t>
+          <t>2026-04-29 22:17:44</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
@@ -17846,7 +17846,7 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 18:28:56</t>
+          <t>2026-04-29 03:28:56</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
@@ -17926,7 +17926,7 @@
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 17:58:50</t>
+          <t>2026-04-29 02:58:50</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
@@ -18006,7 +18006,7 @@
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 17:29:43</t>
+          <t>2026-04-29 02:29:43</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
@@ -18086,7 +18086,7 @@
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 16:38:43</t>
+          <t>2026-04-29 01:38:43</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
@@ -18166,7 +18166,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 15:58:54</t>
+          <t>2026-04-29 00:58:54</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
@@ -18246,7 +18246,7 @@
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 15:31:32</t>
+          <t>2026-04-29 00:31:32</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
@@ -18326,7 +18326,7 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 15:04:20</t>
+          <t>2026-04-29 00:04:20</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
@@ -18406,7 +18406,7 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 14:37:27</t>
+          <t>2026-04-28 23:37:27</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
@@ -18486,7 +18486,7 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 14:09:10</t>
+          <t>2026-04-28 23:09:10</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
@@ -18566,7 +18566,7 @@
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 14:59:25</t>
+          <t>2026-04-27 23:59:25</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -18646,7 +18646,7 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 14:49:35</t>
+          <t>2026-04-27 23:49:35</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
@@ -18726,7 +18726,7 @@
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 13:55:34</t>
+          <t>2026-04-27 22:55:34</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 13:04:13</t>
+          <t>2026-04-27 22:04:13</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
@@ -18886,7 +18886,7 @@
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 17:49:02</t>
+          <t>2026-04-25 02:49:02</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -18966,7 +18966,7 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 17:03:56</t>
+          <t>2026-04-25 02:03:56</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
@@ -19046,7 +19046,7 @@
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 16:37:00</t>
+          <t>2026-04-25 01:37:00</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -19126,7 +19126,7 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 15:33:59</t>
+          <t>2026-04-24 00:33:59</t>
         </is>
       </c>
       <c r="B199" s="7" t="inlineStr">
@@ -19206,7 +19206,7 @@
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 15:22:46</t>
+          <t>2026-04-24 00:22:46</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -19286,7 +19286,7 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 15:12:54</t>
+          <t>2026-04-24 00:12:54</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
@@ -19366,7 +19366,7 @@
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 13:36:03</t>
+          <t>2026-04-23 22:36:03</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -19446,7 +19446,7 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 15:58:57</t>
+          <t>2026-04-14 00:58:57</t>
         </is>
       </c>
       <c r="B203" s="7" t="inlineStr">
@@ -19526,7 +19526,7 @@
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 15:09:08</t>
+          <t>2026-04-14 00:09:08</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
@@ -19606,7 +19606,7 @@
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>2026-04-12 16:48:02</t>
+          <t>2026-04-13 01:48:02</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
@@ -19686,7 +19686,7 @@
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>2026-04-12 16:17:58</t>
+          <t>2026-04-13 01:17:58</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
@@ -19766,7 +19766,7 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>2026-04-12 15:41:20</t>
+          <t>2026-04-13 00:41:20</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
@@ -19846,7 +19846,7 @@
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 14:18:06</t>
+          <t>2026-04-09 23:18:06</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -19926,7 +19926,7 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 13:52:44</t>
+          <t>2026-04-09 22:52:44</t>
         </is>
       </c>
       <c r="B209" s="7" t="inlineStr">
@@ -20006,7 +20006,7 @@
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 13:27:45</t>
+          <t>2026-04-09 22:27:45</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -20086,7 +20086,7 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>2026-04-07 16:10:31</t>
+          <t>2026-04-08 01:10:31</t>
         </is>
       </c>
       <c r="B211" s="7" t="inlineStr">
@@ -20166,7 +20166,7 @@
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>2026-04-07 15:29:19</t>
+          <t>2026-04-08 00:29:19</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
@@ -20246,7 +20246,7 @@
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>2026-04-03 19:36:31</t>
+          <t>2026-04-04 04:36:31</t>
         </is>
       </c>
       <c r="B213" s="7" t="inlineStr">
@@ -20326,7 +20326,7 @@
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>2026-04-03 19:16:32</t>
+          <t>2026-04-04 04:16:32</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
@@ -20406,7 +20406,7 @@
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>2026-03-27 19:24:43</t>
+          <t>2026-03-28 04:24:43</t>
         </is>
       </c>
       <c r="B215" s="7" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>2026-03-27 18:38:31</t>
+          <t>2026-03-28 03:38:31</t>
         </is>
       </c>
       <c r="B216" s="7" t="inlineStr">
@@ -20566,7 +20566,7 @@
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>2026-03-27 18:17:50</t>
+          <t>2026-03-28 03:17:50</t>
         </is>
       </c>
       <c r="B217" s="7" t="inlineStr">
@@ -20646,7 +20646,7 @@
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>2026-03-27 17:43:19</t>
+          <t>2026-03-28 02:43:19</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
@@ -20726,7 +20726,7 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>2026-03-27 17:15:18</t>
+          <t>2026-03-28 02:15:18</t>
         </is>
       </c>
       <c r="B219" s="7" t="inlineStr">
@@ -20806,7 +20806,7 @@
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 14:18:12</t>
+          <t>2026-03-25 23:18:12</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
@@ -20886,7 +20886,7 @@
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 15:01:49</t>
+          <t>2026-03-25 00:01:49</t>
         </is>
       </c>
       <c r="B221" s="7" t="inlineStr">
@@ -20966,7 +20966,7 @@
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 14:25:16</t>
+          <t>2026-03-24 23:25:16</t>
         </is>
       </c>
       <c r="B222" s="7" t="inlineStr">
@@ -21046,7 +21046,7 @@
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 14:02:52</t>
+          <t>2026-03-24 23:02:52</t>
         </is>
       </c>
       <c r="B223" s="7" t="inlineStr">
@@ -21126,7 +21126,7 @@
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 13:26:26</t>
+          <t>2026-03-24 22:26:26</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -21206,7 +21206,7 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>2026-03-23 15:56:18</t>
+          <t>2026-03-24 00:56:18</t>
         </is>
       </c>
       <c r="B225" s="7" t="inlineStr">
@@ -21286,7 +21286,7 @@
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>2026-03-23 15:29:29</t>
+          <t>2026-03-24 00:29:29</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
@@ -21366,7 +21366,7 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 14:51:11</t>
+          <t>2026-03-22 23:51:11</t>
         </is>
       </c>
       <c r="B227" s="7" t="inlineStr">
@@ -21446,7 +21446,7 @@
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
-          <t>2026-03-21 16:04:36</t>
+          <t>2026-03-22 01:04:36</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
@@ -21526,7 +21526,7 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>2026-03-20 17:55:49</t>
+          <t>2026-03-21 02:55:49</t>
         </is>
       </c>
       <c r="B229" s="7" t="inlineStr">
@@ -21606,7 +21606,7 @@
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 15:07:07</t>
+          <t>2026-03-18 00:07:07</t>
         </is>
       </c>
       <c r="B230" s="7" t="inlineStr">
@@ -21686,7 +21686,7 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 14:24:05</t>
+          <t>2026-03-17 23:24:05</t>
         </is>
       </c>
       <c r="B231" s="7" t="inlineStr">
@@ -21766,7 +21766,7 @@
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 17:00:50</t>
+          <t>2026-03-17 02:00:50</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
@@ -21846,7 +21846,7 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 16:33:08</t>
+          <t>2026-03-17 01:33:08</t>
         </is>
       </c>
       <c r="B233" s="7" t="inlineStr">
@@ -21926,7 +21926,7 @@
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 14:28:09</t>
+          <t>2026-03-16 23:28:09</t>
         </is>
       </c>
       <c r="B234" s="7" t="inlineStr">
@@ -22006,7 +22006,7 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>2026-03-15 16:32:22</t>
+          <t>2026-03-16 01:32:22</t>
         </is>
       </c>
       <c r="B235" s="7" t="inlineStr">
@@ -22086,7 +22086,7 @@
     <row r="236">
       <c r="A236" s="7" t="inlineStr">
         <is>
-          <t>2026-03-13 16:43:49</t>
+          <t>2026-03-14 01:43:49</t>
         </is>
       </c>
       <c r="B236" s="7" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>2026-03-13 16:19:35</t>
+          <t>2026-03-14 01:19:35</t>
         </is>
       </c>
       <c r="B237" s="7" t="inlineStr">
@@ -22246,7 +22246,7 @@
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 14:45:27</t>
+          <t>2026-03-12 23:45:27</t>
         </is>
       </c>
       <c r="B238" s="7" t="inlineStr">
@@ -22326,7 +22326,7 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 14:02:09</t>
+          <t>2026-03-12 23:02:09</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
@@ -22406,7 +22406,7 @@
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 13:42:59</t>
+          <t>2026-03-12 22:42:59</t>
         </is>
       </c>
       <c r="B240" s="7" t="inlineStr">
@@ -22486,7 +22486,7 @@
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 16:39:10</t>
+          <t>2026-03-12 01:39:10</t>
         </is>
       </c>
       <c r="B241" s="7" t="inlineStr">
@@ -22566,7 +22566,7 @@
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 15:43:21</t>
+          <t>2026-03-12 00:43:21</t>
         </is>
       </c>
       <c r="B242" s="7" t="inlineStr">
@@ -22646,7 +22646,7 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:25</t>
+          <t>2026-03-12 00:04:25</t>
         </is>
       </c>
       <c r="B243" s="7" t="inlineStr">
@@ -22726,7 +22726,7 @@
     <row r="244">
       <c r="A244" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 13:54:02</t>
+          <t>2026-03-11 22:54:02</t>
         </is>
       </c>
       <c r="B244" s="7" t="inlineStr">
@@ -22806,7 +22806,7 @@
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>2026-03-07 17:01:53</t>
+          <t>2026-03-08 02:01:53</t>
         </is>
       </c>
       <c r="B245" s="7" t="inlineStr">
@@ -22886,7 +22886,7 @@
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>2026-03-01 17:18:59</t>
+          <t>2026-03-02 02:18:59</t>
         </is>
       </c>
       <c r="B246" s="7" t="inlineStr">
@@ -22966,7 +22966,7 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 16:40:38</t>
+          <t>2026-02-24 01:40:38</t>
         </is>
       </c>
       <c r="B247" s="7" t="inlineStr">
@@ -23046,7 +23046,7 @@
     <row r="248">
       <c r="A248" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 15:10:31</t>
+          <t>2026-02-24 00:10:31</t>
         </is>
       </c>
       <c r="B248" s="7" t="inlineStr">
@@ -23126,7 +23126,7 @@
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 14:33:47</t>
+          <t>2026-02-23 23:33:47</t>
         </is>
       </c>
       <c r="B249" s="7" t="inlineStr">
@@ -23206,7 +23206,7 @@
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 13:40:54</t>
+          <t>2026-02-23 22:40:54</t>
         </is>
       </c>
       <c r="B250" s="7" t="inlineStr">
@@ -23286,7 +23286,7 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 12:58:56</t>
+          <t>2026-02-23 21:58:56</t>
         </is>
       </c>
       <c r="B251" s="7" t="inlineStr">
@@ -23366,7 +23366,7 @@
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 10:21:48</t>
+          <t>2026-02-23 19:21:48</t>
         </is>
       </c>
       <c r="B252" s="7" t="inlineStr">
@@ -23446,7 +23446,7 @@
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 08:17:13</t>
+          <t>2026-02-23 17:17:13</t>
         </is>
       </c>
       <c r="B253" s="7" t="inlineStr">
@@ -23526,7 +23526,7 @@
     <row r="254">
       <c r="A254" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22 19:22:01</t>
+          <t>2026-02-23 04:22:01</t>
         </is>
       </c>
       <c r="B254" s="7" t="inlineStr">
@@ -23606,7 +23606,7 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22 18:23:51</t>
+          <t>2026-02-23 03:23:51</t>
         </is>
       </c>
       <c r="B255" s="7" t="inlineStr">
@@ -23686,7 +23686,7 @@
     <row r="256">
       <c r="A256" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22 17:58:18</t>
+          <t>2026-02-23 02:58:18</t>
         </is>
       </c>
       <c r="B256" s="7" t="inlineStr">
@@ -23766,7 +23766,7 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22 17:29:21</t>
+          <t>2026-02-23 02:29:21</t>
         </is>
       </c>
       <c r="B257" s="7" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="258">
       <c r="A258" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22 16:59:09</t>
+          <t>2026-02-23 01:59:09</t>
         </is>
       </c>
       <c r="B258" s="7" t="inlineStr">
@@ -23926,7 +23926,7 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22 16:32:08</t>
+          <t>2026-02-23 01:32:08</t>
         </is>
       </c>
       <c r="B259" s="7" t="inlineStr">
@@ -24006,7 +24006,7 @@
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 18:34:36</t>
+          <t>2026-02-21 03:34:36</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
@@ -24086,7 +24086,7 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 17:57:13</t>
+          <t>2026-02-21 02:57:13</t>
         </is>
       </c>
       <c r="B261" s="7" t="inlineStr">
@@ -24166,7 +24166,7 @@
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 17:19:01</t>
+          <t>2026-02-21 02:19:01</t>
         </is>
       </c>
       <c r="B262" s="7" t="inlineStr">
@@ -24246,7 +24246,7 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 16:41:10</t>
+          <t>2026-02-21 01:41:10</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
@@ -24326,7 +24326,7 @@
     <row r="264">
       <c r="A264" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 15:57:47</t>
+          <t>2026-02-21 00:57:47</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -24406,7 +24406,7 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 15:39:52</t>
+          <t>2026-02-21 00:39:52</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
@@ -24486,7 +24486,7 @@
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
         <is>
-          <t>2026-02-19 16:21:13</t>
+          <t>2026-02-20 01:21:13</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -24566,7 +24566,7 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>2026-02-19 15:33:10</t>
+          <t>2026-02-20 00:33:10</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -24646,7 +24646,7 @@
     <row r="268">
       <c r="A268" s="7" t="inlineStr">
         <is>
-          <t>2026-02-17 15:37:38</t>
+          <t>2026-02-18 00:37:38</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
@@ -24726,7 +24726,7 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>2026-02-17 14:58:39</t>
+          <t>2026-02-17 23:58:39</t>
         </is>
       </c>
       <c r="B269" s="7" t="inlineStr">
@@ -24806,7 +24806,7 @@
     <row r="270">
       <c r="A270" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 17:24:16</t>
+          <t>2026-02-16 02:24:16</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
@@ -24886,7 +24886,7 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 16:47:19</t>
+          <t>2026-02-16 01:47:19</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
@@ -24966,7 +24966,7 @@
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 15:56:43</t>
+          <t>2026-02-16 00:56:43</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -25046,7 +25046,7 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 15:26:20</t>
+          <t>2026-02-16 00:26:20</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
@@ -25126,7 +25126,7 @@
     <row r="274">
       <c r="A274" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 14:48:44</t>
+          <t>2026-02-15 23:48:44</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -25206,7 +25206,7 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 19:17:17</t>
+          <t>2026-02-15 04:17:17</t>
         </is>
       </c>
       <c r="B275" s="7" t="inlineStr">
@@ -25286,7 +25286,7 @@
     <row r="276">
       <c r="A276" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 18:53:01</t>
+          <t>2026-02-15 03:53:01</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
@@ -25366,7 +25366,7 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 17:59:46</t>
+          <t>2026-02-15 02:59:46</t>
         </is>
       </c>
       <c r="B277" s="7" t="inlineStr">
@@ -25446,7 +25446,7 @@
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 17:26:42</t>
+          <t>2026-02-15 02:26:42</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 17:00:09</t>
+          <t>2026-02-15 02:00:09</t>
         </is>
       </c>
       <c r="B279" s="7" t="inlineStr">
@@ -25606,7 +25606,7 @@
     <row r="280">
       <c r="A280" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 16:39:16</t>
+          <t>2026-02-15 01:39:16</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -25686,7 +25686,7 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 15:56:51</t>
+          <t>2026-02-15 00:56:51</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
@@ -25766,7 +25766,7 @@
     <row r="282">
       <c r="A282" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 14:52:26</t>
+          <t>2026-02-14 23:52:26</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -25846,7 +25846,7 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 14:14:55</t>
+          <t>2026-02-14 23:14:55</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
@@ -25926,7 +25926,7 @@
     <row r="284">
       <c r="A284" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13 19:19:58</t>
+          <t>2026-02-14 04:19:58</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -26006,7 +26006,7 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13 18:37:53</t>
+          <t>2026-02-14 03:37:53</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
@@ -26086,7 +26086,7 @@
     <row r="286">
       <c r="A286" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13 18:03:31</t>
+          <t>2026-02-14 03:03:31</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -26166,7 +26166,7 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13 17:08:36</t>
+          <t>2026-02-14 02:08:36</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -26246,7 +26246,7 @@
     <row r="288">
       <c r="A288" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 15:20:03</t>
+          <t>2026-02-12 00:20:03</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -26326,7 +26326,7 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 18:05:03</t>
+          <t>2026-02-11 03:05:03</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -26406,7 +26406,7 @@
     <row r="290">
       <c r="A290" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 17:14:02</t>
+          <t>2026-02-11 02:14:02</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -26486,7 +26486,7 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 16:33:21</t>
+          <t>2026-02-11 01:33:21</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
@@ -26566,7 +26566,7 @@
     <row r="292">
       <c r="A292" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 16:01:41</t>
+          <t>2026-02-11 01:01:41</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -26646,7 +26646,7 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 16:49:32</t>
+          <t>2026-02-10 01:49:32</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
@@ -26726,7 +26726,7 @@
     <row r="294">
       <c r="A294" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 16:42:29</t>
+          <t>2026-02-10 01:42:29</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -26806,7 +26806,7 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 14:44:10</t>
+          <t>2026-02-09 23:44:10</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
@@ -26886,7 +26886,7 @@
     <row r="296">
       <c r="A296" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 14:00:28</t>
+          <t>2026-02-09 23:00:28</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -26966,7 +26966,7 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08 15:27:49</t>
+          <t>2026-02-09 00:27:49</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -27046,7 +27046,7 @@
     <row r="298">
       <c r="A298" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08 15:16:42</t>
+          <t>2026-02-09 00:16:42</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -27126,7 +27126,7 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 19:04:43</t>
+          <t>2026-02-08 04:04:43</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="300">
       <c r="A300" s="7" t="inlineStr">
         <is>
-          <t>2026-02-06 18:13:11</t>
+          <t>2026-02-07 03:13:11</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
@@ -27286,7 +27286,7 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>2026-02-06 17:19:42</t>
+          <t>2026-02-07 02:19:42</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -27366,7 +27366,7 @@
     <row r="302">
       <c r="A302" s="7" t="inlineStr">
         <is>
-          <t>2026-02-06 16:37:36</t>
+          <t>2026-02-07 01:37:36</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
@@ -27446,7 +27446,7 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>2026-02-03 14:04:49</t>
+          <t>2026-02-03 23:04:49</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
@@ -27526,7 +27526,7 @@
     <row r="304">
       <c r="A304" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 14:21:38</t>
+          <t>2026-02-02 23:21:38</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -27606,7 +27606,7 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 18:08:17</t>
+          <t>2026-02-02 03:08:17</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -27686,7 +27686,7 @@
     <row r="306">
       <c r="A306" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 17:41:55</t>
+          <t>2026-02-02 02:41:55</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -27766,7 +27766,7 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 17:09:57</t>
+          <t>2026-02-02 02:09:57</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
@@ -27846,7 +27846,7 @@
     <row r="308">
       <c r="A308" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 16:41:49</t>
+          <t>2026-02-02 01:41:49</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
@@ -27926,7 +27926,7 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 17:22:13</t>
+          <t>2026-02-01 02:22:13</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
@@ -28006,7 +28006,7 @@
     <row r="310">
       <c r="A310" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 16:20:54</t>
+          <t>2026-02-01 01:20:54</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -28086,7 +28086,7 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 16:09:32</t>
+          <t>2026-02-01 01:09:32</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -28166,7 +28166,7 @@
     <row r="312">
       <c r="A312" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 15:29:37</t>
+          <t>2026-02-01 00:29:37</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -28246,7 +28246,7 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 15:03:50</t>
+          <t>2026-02-01 00:03:50</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -28326,7 +28326,7 @@
     <row r="314">
       <c r="A314" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 14:15:28</t>
+          <t>2026-01-31 23:15:28</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -28406,7 +28406,7 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 15:36:39</t>
+          <t>2026-01-29 00:36:39</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -28486,7 +28486,7 @@
     <row r="316">
       <c r="A316" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 15:02:45</t>
+          <t>2026-01-29 00:02:45</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -28566,7 +28566,7 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 14:26:47</t>
+          <t>2026-01-28 23:26:47</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -28646,7 +28646,7 @@
     <row r="318">
       <c r="A318" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 14:04:33</t>
+          <t>2026-01-28 23:04:33</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -28726,7 +28726,7 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 15:33:31</t>
+          <t>2026-01-28 00:33:31</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -28806,7 +28806,7 @@
     <row r="320">
       <c r="A320" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 14:59:21</t>
+          <t>2026-01-27 23:59:21</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 14:08:33</t>
+          <t>2026-01-27 23:08:33</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -28966,7 +28966,7 @@
     <row r="322">
       <c r="A322" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 14:28:17</t>
+          <t>2026-01-25 23:28:17</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -29046,7 +29046,7 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 13:56:22</t>
+          <t>2026-01-25 22:56:22</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -29126,7 +29126,7 @@
     <row r="324">
       <c r="A324" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 13:28:25</t>
+          <t>2026-01-25 22:28:25</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -29206,7 +29206,7 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 12:42:03</t>
+          <t>2026-01-25 21:42:03</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -29286,7 +29286,7 @@
     <row r="326">
       <c r="A326" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 10:38:23</t>
+          <t>2026-01-25 19:38:23</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -29366,7 +29366,7 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 09:56:35</t>
+          <t>2026-01-25 18:56:35</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -29446,7 +29446,7 @@
     <row r="328">
       <c r="A328" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 09:29:19</t>
+          <t>2026-01-25 18:29:19</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -29526,7 +29526,7 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 08:14:05</t>
+          <t>2026-01-25 17:14:05</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -29606,7 +29606,7 @@
     <row r="330">
       <c r="A330" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 17:47:24</t>
+          <t>2026-01-24 02:47:24</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -29686,7 +29686,7 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 17:12:26</t>
+          <t>2026-01-24 02:12:26</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -29766,7 +29766,7 @@
     <row r="332">
       <c r="A332" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 16:33:34</t>
+          <t>2026-01-24 01:33:34</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -29846,7 +29846,7 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 16:00:39</t>
+          <t>2026-01-24 01:00:39</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -29926,7 +29926,7 @@
     <row r="334">
       <c r="A334" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 15:19:07</t>
+          <t>2026-01-24 00:19:07</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -30006,7 +30006,7 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 14:52:33</t>
+          <t>2026-01-23 23:52:33</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -30086,7 +30086,7 @@
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 14:19:19</t>
+          <t>2026-01-23 23:19:19</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -30166,7 +30166,7 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 13:36:59</t>
+          <t>2026-01-23 22:36:59</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -30246,7 +30246,7 @@
     <row r="338">
       <c r="A338" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 18:01:58</t>
+          <t>2026-01-23 03:01:58</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -30326,7 +30326,7 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 17:25:41</t>
+          <t>2026-01-23 02:25:41</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -30406,7 +30406,7 @@
     <row r="340">
       <c r="A340" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 15:32:45</t>
+          <t>2026-01-23 00:32:45</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -30486,7 +30486,7 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 14:54:46</t>
+          <t>2026-01-22 23:54:46</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="342">
       <c r="A342" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 14:17:42</t>
+          <t>2026-01-22 23:17:42</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -30646,7 +30646,7 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>2026-01-21 16:10:08</t>
+          <t>2026-01-22 01:10:08</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -30726,7 +30726,7 @@
     <row r="344">
       <c r="A344" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 15:27:51</t>
+          <t>2026-01-21 00:27:51</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -30806,7 +30806,7 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 14:25:34</t>
+          <t>2026-01-20 23:25:34</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -30886,7 +30886,7 @@
     <row r="346">
       <c r="A346" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 13:56:13</t>
+          <t>2026-01-20 22:56:13</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -30966,7 +30966,7 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 16:59:11</t>
+          <t>2026-01-19 01:59:11</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -31046,7 +31046,7 @@
     <row r="348">
       <c r="A348" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 18:05:32</t>
+          <t>2026-01-18 03:05:32</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -31126,7 +31126,7 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 17:19:17</t>
+          <t>2026-01-18 02:19:17</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -31206,7 +31206,7 @@
     <row r="350">
       <c r="A350" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 16:58:17</t>
+          <t>2026-01-18 01:58:17</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -31286,7 +31286,7 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 16:18:29</t>
+          <t>2026-01-18 01:18:29</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -31366,7 +31366,7 @@
     <row r="352">
       <c r="A352" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 15:38:58</t>
+          <t>2026-01-18 00:38:58</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -31446,7 +31446,7 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 09:46:30</t>
+          <t>2026-01-17 18:46:30</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -31526,7 +31526,7 @@
     <row r="354">
       <c r="A354" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 17:21:36</t>
+          <t>2026-01-17 02:21:36</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -31606,7 +31606,7 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 16:51:05</t>
+          <t>2026-01-17 01:51:05</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -31686,7 +31686,7 @@
     <row r="356">
       <c r="A356" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 16:18:22</t>
+          <t>2026-01-17 01:18:22</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -31766,7 +31766,7 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>2026-01-15 16:41:15</t>
+          <t>2026-01-16 01:41:15</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -31846,7 +31846,7 @@
     <row r="358">
       <c r="A358" s="7" t="inlineStr">
         <is>
-          <t>2026-01-15 16:05:38</t>
+          <t>2026-01-16 01:05:38</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -31926,7 +31926,7 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 15:57:21</t>
+          <t>2026-01-14 00:57:21</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -32006,7 +32006,7 @@
     <row r="360">
       <c r="A360" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 15:19:49</t>
+          <t>2026-01-14 00:19:49</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -32086,7 +32086,7 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 14:53:29</t>
+          <t>2026-01-13 23:53:29</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -32166,7 +32166,7 @@
     <row r="362">
       <c r="A362" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 17:23:29</t>
+          <t>2026-01-13 02:23:29</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 16:42:12</t>
+          <t>2026-01-13 01:42:12</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -32326,7 +32326,7 @@
     <row r="364">
       <c r="A364" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 16:17:01</t>
+          <t>2026-01-13 01:17:01</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -32406,7 +32406,7 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 15:43:11</t>
+          <t>2026-01-13 00:43:11</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -32486,7 +32486,7 @@
     <row r="366">
       <c r="A366" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 08:24:44</t>
+          <t>2026-01-12 17:24:44</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -32566,7 +32566,7 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 18:12:16</t>
+          <t>2026-01-12 03:12:16</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -32646,7 +32646,7 @@
     <row r="368">
       <c r="A368" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 17:54:03</t>
+          <t>2026-01-11 02:54:03</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -32726,7 +32726,7 @@
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 17:14:56</t>
+          <t>2026-01-11 02:14:56</t>
         </is>
       </c>
       <c r="B369" s="7" t="inlineStr">
@@ -32806,7 +32806,7 @@
     <row r="370">
       <c r="A370" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 16:17:21</t>
+          <t>2026-01-11 01:17:21</t>
         </is>
       </c>
       <c r="B370" s="7" t="inlineStr">
@@ -32886,7 +32886,7 @@
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 15:22:11</t>
+          <t>2026-01-11 00:22:11</t>
         </is>
       </c>
       <c r="B371" s="7" t="inlineStr">
@@ -32966,7 +32966,7 @@
     <row r="372">
       <c r="A372" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 14:38:24</t>
+          <t>2026-01-10 23:38:24</t>
         </is>
       </c>
       <c r="B372" s="7" t="inlineStr">
@@ -33046,7 +33046,7 @@
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>2026-01-09 17:54:19</t>
+          <t>2026-01-10 02:54:19</t>
         </is>
       </c>
       <c r="B373" s="7" t="inlineStr">
@@ -33126,7 +33126,7 @@
     <row r="374">
       <c r="A374" s="7" t="inlineStr">
         <is>
-          <t>2026-01-09 17:00:16</t>
+          <t>2026-01-10 02:00:16</t>
         </is>
       </c>
       <c r="B374" s="7" t="inlineStr">
@@ -33206,7 +33206,7 @@
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>2026-01-09 14:36:27</t>
+          <t>2026-01-09 23:36:27</t>
         </is>
       </c>
       <c r="B375" s="7" t="inlineStr">
@@ -33283,88 +33283,8 @@
         </is>
       </c>
     </row>
-    <row r="376">
-      <c r="A376" s="7" t="inlineStr">
-        <is>
-          <t>2026-01-05 14:21:47</t>
-        </is>
-      </c>
-      <c r="B376" s="7" t="inlineStr">
-        <is>
-          <t>ランク(ソロ/デュオ)</t>
-        </is>
-      </c>
-      <c r="C376" s="10" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D376" s="7" t="inlineStr">
-        <is>
-          <t>SUP</t>
-        </is>
-      </c>
-      <c r="E376" s="7" t="inlineStr">
-        <is>
-          <t>ジャンナ</t>
-        </is>
-      </c>
-      <c r="F376" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G376" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H376" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I376" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J376" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="K376" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="L376" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="M376" s="6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N376" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="O376" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P376" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q376" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R376" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S376" s="11" t="n">
-        <v>6751</v>
-      </c>
-      <c r="T376" s="11" t="n">
-        <v>2219</v>
-      </c>
-      <c r="U376" s="6" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="V376" s="7" t="inlineStr">
-        <is>
-          <t>JP1_556572228</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V376"/>
+  <autoFilter ref="A1:V375"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33375,7 +33295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P376"/>
+  <dimension ref="A1:P375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -33481,7 +33401,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00:11</t>
+          <t>2026-08-01 04:00:11</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
@@ -33543,7 +33463,7 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 18:30:26</t>
+          <t>2026-08-01 03:30:26</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
@@ -33605,7 +33525,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 17:52:16</t>
+          <t>2026-08-01 02:52:16</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -33667,7 +33587,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 16:50:20</t>
+          <t>2026-08-01 01:50:20</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -33729,7 +33649,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 16:16:45</t>
+          <t>2026-08-01 01:16:45</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -33791,7 +33711,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 13:56:19</t>
+          <t>2026-07-31 22:56:19</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -33853,7 +33773,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 13:22:46</t>
+          <t>2026-07-31 22:22:46</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -33915,7 +33835,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 12:49:35</t>
+          <t>2026-07-31 21:49:35</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -33977,7 +33897,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 14:51:39</t>
+          <t>2026-07-28 23:51:39</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -34039,7 +33959,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 14:05:20</t>
+          <t>2026-07-28 23:05:20</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -34101,7 +34021,7 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>2026-07-26 16:21:51</t>
+          <t>2026-07-27 01:21:51</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -34163,7 +34083,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>2026-07-26 15:43:02</t>
+          <t>2026-07-27 00:43:02</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -34225,7 +34145,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 14:12:09</t>
+          <t>2026-07-25 23:12:09</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
@@ -34287,7 +34207,7 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 13:30:57</t>
+          <t>2026-07-25 22:30:57</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -34349,7 +34269,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>2026-07-24 15:11:55</t>
+          <t>2026-07-25 00:11:55</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -34411,7 +34331,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>2026-07-24 14:25:38</t>
+          <t>2026-07-24 23:25:38</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -34473,7 +34393,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 15:17:56</t>
+          <t>2026-07-22 00:17:56</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -34535,7 +34455,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 15:04:35</t>
+          <t>2026-07-22 00:04:35</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -34597,7 +34517,7 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 14:25:56</t>
+          <t>2026-07-21 23:25:56</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -34659,7 +34579,7 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 13:44:36</t>
+          <t>2026-07-21 22:44:36</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -34721,7 +34641,7 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 13:18:59</t>
+          <t>2026-07-21 22:18:59</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -34783,7 +34703,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>2026-07-19 18:20:20</t>
+          <t>2026-07-20 03:20:20</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -34845,7 +34765,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>2026-07-19 17:39:51</t>
+          <t>2026-07-20 02:39:51</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -34907,7 +34827,7 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 09:59:14</t>
+          <t>2026-07-18 18:59:14</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -34969,7 +34889,7 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 09:21:14</t>
+          <t>2026-07-18 18:21:14</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
@@ -35031,7 +34951,7 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 14:06:28</t>
+          <t>2026-07-16 23:06:28</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -35093,7 +35013,7 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 13:32:42</t>
+          <t>2026-07-16 22:32:42</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
@@ -35155,7 +35075,7 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 15:40:48</t>
+          <t>2026-07-16 00:40:48</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -35217,7 +35137,7 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 14:41:56</t>
+          <t>2026-07-15 23:41:56</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
@@ -35279,7 +35199,7 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 13:58:44</t>
+          <t>2026-07-15 22:58:44</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
@@ -35341,7 +35261,7 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 13:34:16</t>
+          <t>2026-07-15 22:34:16</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
@@ -35403,7 +35323,7 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 14:36:35</t>
+          <t>2026-07-14 23:36:35</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -35465,7 +35385,7 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 13:49:50</t>
+          <t>2026-07-14 22:49:50</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
@@ -35527,7 +35447,7 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 16:02:29</t>
+          <t>2026-07-14 01:02:29</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
@@ -35589,7 +35509,7 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 15:22:46</t>
+          <t>2026-07-14 00:22:46</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
@@ -35651,7 +35571,7 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 14:51:38</t>
+          <t>2026-07-13 23:51:38</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -35713,7 +35633,7 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 17:05:19</t>
+          <t>2026-07-13 02:05:19</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
@@ -35775,7 +35695,7 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 16:29:17</t>
+          <t>2026-07-13 01:29:17</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -35837,7 +35757,7 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 18:11:38</t>
+          <t>2026-07-12 03:11:38</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
@@ -35899,7 +35819,7 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 17:46:15</t>
+          <t>2026-07-12 02:46:15</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
@@ -35961,7 +35881,7 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>2026-07-10 18:42:29</t>
+          <t>2026-07-11 03:42:29</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
@@ -36023,7 +35943,7 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>2026-07-10 18:06:21</t>
+          <t>2026-07-11 03:06:21</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
@@ -36085,7 +36005,7 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>2026-07-08 17:55:25</t>
+          <t>2026-07-09 02:55:25</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
@@ -36147,7 +36067,7 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>2026-07-08 17:17:09</t>
+          <t>2026-07-09 02:17:09</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
@@ -36209,7 +36129,7 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>2026-07-05 17:03:51</t>
+          <t>2026-07-06 02:03:51</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
@@ -36271,7 +36191,7 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>2026-07-05 16:07:17</t>
+          <t>2026-07-06 01:07:17</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
@@ -36333,7 +36253,7 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>2026-07-05 15:23:00</t>
+          <t>2026-07-06 00:23:00</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
@@ -36395,7 +36315,7 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>2026-07-04 18:21:23</t>
+          <t>2026-07-05 03:21:23</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
@@ -36457,7 +36377,7 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>2026-07-03 18:01:40</t>
+          <t>2026-07-04 03:01:40</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
@@ -36519,7 +36439,7 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>2026-07-02 16:48:19</t>
+          <t>2026-07-03 01:48:19</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
@@ -36581,7 +36501,7 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 15:21:19</t>
+          <t>2026-07-01 00:21:19</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
@@ -36643,7 +36563,7 @@
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 14:38:16</t>
+          <t>2026-06-30 23:38:16</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
@@ -36705,7 +36625,7 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>2026-06-29 16:16:28</t>
+          <t>2026-06-30 01:16:28</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
@@ -36767,7 +36687,7 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>2026-06-29 15:34:32</t>
+          <t>2026-06-30 00:34:32</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
@@ -36829,7 +36749,7 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 15:50:56</t>
+          <t>2026-06-26 00:50:56</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
@@ -36891,7 +36811,7 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 15:06:40</t>
+          <t>2026-06-26 00:06:40</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
@@ -36953,7 +36873,7 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 17:07:56</t>
+          <t>2026-06-25 02:07:56</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
@@ -37015,7 +36935,7 @@
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 16:33:19</t>
+          <t>2026-06-25 01:33:19</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
@@ -37077,7 +36997,7 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 15:47:59</t>
+          <t>2026-06-25 00:47:59</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
@@ -37139,7 +37059,7 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 15:08:31</t>
+          <t>2026-06-25 00:08:31</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
@@ -37201,7 +37121,7 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 14:33:15</t>
+          <t>2026-06-24 23:33:15</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
@@ -37263,7 +37183,7 @@
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 13:39:11</t>
+          <t>2026-06-24 22:39:11</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
@@ -37325,7 +37245,7 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>2026-06-22 16:16:06</t>
+          <t>2026-06-23 01:16:06</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
@@ -37387,7 +37307,7 @@
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>2026-06-22 15:38:08</t>
+          <t>2026-06-23 00:38:08</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
@@ -37449,7 +37369,7 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>2026-06-22 15:29:33</t>
+          <t>2026-06-23 00:29:33</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
@@ -37511,7 +37431,7 @@
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 16:54:04</t>
+          <t>2026-06-19 01:54:04</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
@@ -37573,7 +37493,7 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 16:14:50</t>
+          <t>2026-06-19 01:14:50</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
@@ -37635,7 +37555,7 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 15:35:17</t>
+          <t>2026-06-19 00:35:17</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
@@ -37697,7 +37617,7 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 14:55:50</t>
+          <t>2026-06-18 23:55:50</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
@@ -37759,7 +37679,7 @@
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 15:44:42</t>
+          <t>2026-06-18 00:44:42</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
@@ -37821,7 +37741,7 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 14:57:38</t>
+          <t>2026-06-17 23:57:38</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
@@ -37883,7 +37803,7 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>2026-06-16 16:58:55</t>
+          <t>2026-06-17 01:58:55</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
@@ -37945,7 +37865,7 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>2026-06-16 16:30:07</t>
+          <t>2026-06-17 01:30:07</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
@@ -38007,7 +37927,7 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 18:10:28</t>
+          <t>2026-06-15 03:10:28</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
@@ -38069,7 +37989,7 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 17:27:52</t>
+          <t>2026-06-15 02:27:52</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
@@ -38131,7 +38051,7 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 16:57:23</t>
+          <t>2026-06-15 01:57:23</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
@@ -38193,7 +38113,7 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 16:27:22</t>
+          <t>2026-06-15 01:27:22</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
@@ -38255,7 +38175,7 @@
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 15:24:35</t>
+          <t>2026-06-15 00:24:35</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
@@ -38317,7 +38237,7 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 14:46:55</t>
+          <t>2026-06-14 23:46:55</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
@@ -38379,7 +38299,7 @@
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 16:41:53</t>
+          <t>2026-06-14 01:41:53</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
@@ -38441,7 +38361,7 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 15:52:58</t>
+          <t>2026-06-14 00:52:58</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
@@ -38503,7 +38423,7 @@
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 15:14:23</t>
+          <t>2026-06-14 00:14:23</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
@@ -38565,7 +38485,7 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 14:45:21</t>
+          <t>2026-06-13 23:45:21</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
@@ -38627,7 +38547,7 @@
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 14:05:32</t>
+          <t>2026-06-13 23:05:32</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
@@ -38689,7 +38609,7 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 16:08:14</t>
+          <t>2026-06-11 01:08:14</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
@@ -38751,7 +38671,7 @@
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 15:34:35</t>
+          <t>2026-06-11 00:34:35</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
@@ -38813,7 +38733,7 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 15:09:17</t>
+          <t>2026-06-11 00:09:17</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
@@ -38875,7 +38795,7 @@
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 14:27:53</t>
+          <t>2026-06-10 23:27:53</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
@@ -38937,7 +38857,7 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>2026-06-09 15:49:00</t>
+          <t>2026-06-10 00:49:00</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
@@ -38999,7 +38919,7 @@
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>2026-06-05 17:58:51</t>
+          <t>2026-06-06 02:58:51</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
@@ -39061,7 +38981,7 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>2026-06-05 17:15:04</t>
+          <t>2026-06-06 02:15:04</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
@@ -39123,7 +39043,7 @@
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 14:49:14</t>
+          <t>2026-06-04 23:49:14</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
@@ -39185,7 +39105,7 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 12:40:04</t>
+          <t>2026-06-04 21:40:04</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
@@ -39247,7 +39167,7 @@
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 12:17:24</t>
+          <t>2026-06-04 21:17:24</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
@@ -39309,7 +39229,7 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 16:06:27</t>
+          <t>2026-06-04 01:06:27</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
@@ -39371,7 +39291,7 @@
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 15:31:09</t>
+          <t>2026-06-04 00:31:09</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
@@ -39433,7 +39353,7 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 14:53:57</t>
+          <t>2026-06-03 23:53:57</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
@@ -39495,7 +39415,7 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 13:44:02</t>
+          <t>2026-06-03 22:44:02</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
@@ -39557,7 +39477,7 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>2026-06-02 13:49:11</t>
+          <t>2026-06-02 22:49:11</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
@@ -39619,7 +39539,7 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 14:56:06</t>
+          <t>2026-06-01 23:56:06</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
@@ -39681,7 +39601,7 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 14:20:26</t>
+          <t>2026-06-01 23:20:26</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
@@ -39743,7 +39663,7 @@
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 14:01:06</t>
+          <t>2026-06-01 23:01:06</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
@@ -39805,7 +39725,7 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>2026-05-30 18:01:04</t>
+          <t>2026-05-31 03:01:04</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
@@ -39867,7 +39787,7 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>2026-05-30 17:13:41</t>
+          <t>2026-05-31 02:13:41</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
@@ -39929,7 +39849,7 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 14:00:40</t>
+          <t>2026-05-25 23:00:40</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
@@ -39991,7 +39911,7 @@
     <row r="107">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 16:55:47</t>
+          <t>2026-05-25 01:55:47</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
@@ -40053,7 +39973,7 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 16:24:22</t>
+          <t>2026-05-25 01:24:22</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
@@ -40115,7 +40035,7 @@
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 14:49:25</t>
+          <t>2026-05-24 23:49:25</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
@@ -40177,7 +40097,7 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 18:13:39</t>
+          <t>2026-05-24 03:13:39</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
@@ -40239,7 +40159,7 @@
     <row r="111">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 17:41:52</t>
+          <t>2026-05-24 02:41:52</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
@@ -40301,7 +40221,7 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 14:19:04</t>
+          <t>2026-05-23 23:19:04</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
@@ -40363,7 +40283,7 @@
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 13:43:20</t>
+          <t>2026-05-23 22:43:20</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
@@ -40425,7 +40345,7 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 06:54:19</t>
+          <t>2026-05-23 15:54:19</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
@@ -40487,7 +40407,7 @@
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 17:25:24</t>
+          <t>2026-05-23 02:25:24</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
@@ -40549,7 +40469,7 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 16:29:23</t>
+          <t>2026-05-22 01:29:23</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
@@ -40611,7 +40531,7 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 15:48:49</t>
+          <t>2026-05-22 00:48:49</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
@@ -40673,7 +40593,7 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 15:00:45</t>
+          <t>2026-05-22 00:00:45</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
@@ -40735,7 +40655,7 @@
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 14:22:44</t>
+          <t>2026-05-21 23:22:44</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
@@ -40797,7 +40717,7 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 15:05:15</t>
+          <t>2026-05-21 00:05:15</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
@@ -40859,7 +40779,7 @@
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 14:43:50</t>
+          <t>2026-05-20 23:43:50</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
@@ -40921,7 +40841,7 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 13:57:45</t>
+          <t>2026-05-20 22:57:45</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
@@ -40983,7 +40903,7 @@
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>2026-05-19 16:25:45</t>
+          <t>2026-05-20 01:25:45</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
@@ -41045,7 +40965,7 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>2026-05-19 15:46:42</t>
+          <t>2026-05-20 00:46:42</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
@@ -41107,7 +41027,7 @@
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>2026-05-18 13:56:39</t>
+          <t>2026-05-18 22:56:39</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
@@ -41169,7 +41089,7 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>2026-05-14 16:35:56</t>
+          <t>2026-05-15 01:35:56</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
@@ -41231,7 +41151,7 @@
     <row r="127">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>2026-05-14 16:17:05</t>
+          <t>2026-05-15 01:17:05</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
@@ -41293,7 +41213,7 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>2026-05-14 15:05:48</t>
+          <t>2026-05-15 00:05:48</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
@@ -41355,7 +41275,7 @@
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>2026-05-13 16:25:38</t>
+          <t>2026-05-14 01:25:38</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
@@ -41417,7 +41337,7 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 15:19:57</t>
+          <t>2026-05-12 00:19:57</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
@@ -41479,7 +41399,7 @@
     <row r="131">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 14:54:15</t>
+          <t>2026-05-11 23:54:15</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
@@ -41541,7 +41461,7 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 14:14:30</t>
+          <t>2026-05-11 23:14:30</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
@@ -41603,7 +41523,7 @@
     <row r="133">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 13:37:05</t>
+          <t>2026-05-11 22:37:05</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
@@ -41665,7 +41585,7 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 12:53:13</t>
+          <t>2026-05-11 21:53:13</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
@@ -41727,7 +41647,7 @@
     <row r="135">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 15:04:01</t>
+          <t>2026-05-11 00:04:01</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
@@ -41789,7 +41709,7 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 16:54:24</t>
+          <t>2026-05-10 01:54:24</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
@@ -41851,7 +41771,7 @@
     <row r="137">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 16:22:50</t>
+          <t>2026-05-10 01:22:50</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
@@ -41913,7 +41833,7 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 15:26:16</t>
+          <t>2026-05-10 00:26:16</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
@@ -41975,7 +41895,7 @@
     <row r="139">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 14:38:30</t>
+          <t>2026-05-09 23:38:30</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
@@ -42037,7 +41957,7 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 13:50:20</t>
+          <t>2026-05-09 22:50:20</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
@@ -42099,7 +42019,7 @@
     <row r="141">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 13:13:25</t>
+          <t>2026-05-09 22:13:25</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
@@ -42161,7 +42081,7 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 11:00:11</t>
+          <t>2026-05-09 20:00:11</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
@@ -42223,7 +42143,7 @@
     <row r="143">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 10:10:28</t>
+          <t>2026-05-09 19:10:28</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
@@ -42285,7 +42205,7 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 17:17:27</t>
+          <t>2026-05-09 02:17:27</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
@@ -42347,7 +42267,7 @@
     <row r="145">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 16:38:25</t>
+          <t>2026-05-09 01:38:25</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
@@ -42409,7 +42329,7 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 15:58:58</t>
+          <t>2026-05-09 00:58:58</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
@@ -42471,7 +42391,7 @@
     <row r="147">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 15:37:55</t>
+          <t>2026-05-09 00:37:55</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
@@ -42533,7 +42453,7 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 16:48:31</t>
+          <t>2026-05-08 01:48:31</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
@@ -42595,7 +42515,7 @@
     <row r="149">
       <c r="A149" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 16:02:52</t>
+          <t>2026-05-08 01:02:52</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
@@ -42657,7 +42577,7 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 15:23:29</t>
+          <t>2026-05-08 00:23:29</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
@@ -42719,7 +42639,7 @@
     <row r="151">
       <c r="A151" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 16:30:56</t>
+          <t>2026-05-07 01:30:56</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
@@ -42781,7 +42701,7 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 15:42:16</t>
+          <t>2026-05-07 00:42:16</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
@@ -42843,7 +42763,7 @@
     <row r="153">
       <c r="A153" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 14:44:04</t>
+          <t>2026-05-06 23:44:04</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
@@ -42905,7 +42825,7 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 09:13:52</t>
+          <t>2026-05-06 18:13:52</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
@@ -42967,7 +42887,7 @@
     <row r="155">
       <c r="A155" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 09:05:08</t>
+          <t>2026-05-06 18:05:08</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
@@ -43029,7 +42949,7 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 08:22:30</t>
+          <t>2026-05-06 17:22:30</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
@@ -43091,7 +43011,7 @@
     <row r="157">
       <c r="A157" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 07:28:42</t>
+          <t>2026-05-06 16:28:42</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
@@ -43153,7 +43073,7 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 18:16:57</t>
+          <t>2026-05-06 03:16:57</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
@@ -43215,7 +43135,7 @@
     <row r="159">
       <c r="A159" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 17:32:40</t>
+          <t>2026-05-06 02:32:40</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
@@ -43277,7 +43197,7 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 17:23:28</t>
+          <t>2026-05-06 02:23:28</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
@@ -43339,7 +43259,7 @@
     <row r="161">
       <c r="A161" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 16:48:28</t>
+          <t>2026-05-06 01:48:28</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
@@ -43401,7 +43321,7 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 15:52:33</t>
+          <t>2026-05-06 00:52:33</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
@@ -43463,7 +43383,7 @@
     <row r="163">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 08:43:06</t>
+          <t>2026-05-05 17:43:06</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
@@ -43525,7 +43445,7 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 15:36:42</t>
+          <t>2026-05-03 00:36:42</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
@@ -43587,7 +43507,7 @@
     <row r="165">
       <c r="A165" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 14:51:09</t>
+          <t>2026-05-02 23:51:09</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
@@ -43649,7 +43569,7 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 13:15:10</t>
+          <t>2026-05-02 22:15:10</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
@@ -43711,7 +43631,7 @@
     <row r="167">
       <c r="A167" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 12:29:49</t>
+          <t>2026-05-02 21:29:49</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
@@ -43773,7 +43693,7 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 16:39:42</t>
+          <t>2026-05-01 01:39:42</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
@@ -43835,7 +43755,7 @@
     <row r="169">
       <c r="A169" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 16:01:34</t>
+          <t>2026-05-01 01:01:34</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
@@ -43897,7 +43817,7 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 15:24:48</t>
+          <t>2026-05-01 00:24:48</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
@@ -43959,7 +43879,7 @@
     <row r="171">
       <c r="A171" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 14:37:10</t>
+          <t>2026-04-30 23:37:10</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
@@ -44021,7 +43941,7 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 13:58:06</t>
+          <t>2026-04-30 22:58:06</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
@@ -44083,7 +44003,7 @@
     <row r="173">
       <c r="A173" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 18:29:33</t>
+          <t>2026-04-30 03:29:33</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
@@ -44145,7 +44065,7 @@
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 17:54:07</t>
+          <t>2026-04-30 02:54:07</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
@@ -44207,7 +44127,7 @@
     <row r="175">
       <c r="A175" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 17:20:58</t>
+          <t>2026-04-30 02:20:58</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
@@ -44269,7 +44189,7 @@
     <row r="176">
       <c r="A176" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 16:42:01</t>
+          <t>2026-04-30 01:42:01</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
@@ -44331,7 +44251,7 @@
     <row r="177">
       <c r="A177" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 16:03:17</t>
+          <t>2026-04-30 01:03:17</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
@@ -44393,7 +44313,7 @@
     <row r="178">
       <c r="A178" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 15:19:47</t>
+          <t>2026-04-30 00:19:47</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
@@ -44455,7 +44375,7 @@
     <row r="179">
       <c r="A179" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 14:29:53</t>
+          <t>2026-04-29 23:29:53</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
@@ -44517,7 +44437,7 @@
     <row r="180">
       <c r="A180" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 13:59:49</t>
+          <t>2026-04-29 22:59:49</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
@@ -44579,7 +44499,7 @@
     <row r="181">
       <c r="A181" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 13:38:22</t>
+          <t>2026-04-29 22:38:22</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
@@ -44641,7 +44561,7 @@
     <row r="182">
       <c r="A182" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 13:17:44</t>
+          <t>2026-04-29 22:17:44</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
@@ -44703,7 +44623,7 @@
     <row r="183">
       <c r="A183" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 18:28:56</t>
+          <t>2026-04-29 03:28:56</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
@@ -44765,7 +44685,7 @@
     <row r="184">
       <c r="A184" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 17:58:50</t>
+          <t>2026-04-29 02:58:50</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
@@ -44827,7 +44747,7 @@
     <row r="185">
       <c r="A185" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 17:29:43</t>
+          <t>2026-04-29 02:29:43</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
@@ -44889,7 +44809,7 @@
     <row r="186">
       <c r="A186" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 16:38:43</t>
+          <t>2026-04-29 01:38:43</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
@@ -44951,7 +44871,7 @@
     <row r="187">
       <c r="A187" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 15:58:54</t>
+          <t>2026-04-29 00:58:54</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
@@ -45013,7 +44933,7 @@
     <row r="188">
       <c r="A188" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 15:31:32</t>
+          <t>2026-04-29 00:31:32</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
@@ -45075,7 +44995,7 @@
     <row r="189">
       <c r="A189" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 15:04:20</t>
+          <t>2026-04-29 00:04:20</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
@@ -45137,7 +45057,7 @@
     <row r="190">
       <c r="A190" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 14:37:27</t>
+          <t>2026-04-28 23:37:27</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
@@ -45199,7 +45119,7 @@
     <row r="191">
       <c r="A191" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 14:09:10</t>
+          <t>2026-04-28 23:09:10</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
@@ -45261,7 +45181,7 @@
     <row r="192">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 14:59:25</t>
+          <t>2026-04-27 23:59:25</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
@@ -45323,7 +45243,7 @@
     <row r="193">
       <c r="A193" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 14:49:35</t>
+          <t>2026-04-27 23:49:35</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
@@ -45385,7 +45305,7 @@
     <row r="194">
       <c r="A194" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 13:55:34</t>
+          <t>2026-04-27 22:55:34</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
@@ -45447,7 +45367,7 @@
     <row r="195">
       <c r="A195" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 13:04:13</t>
+          <t>2026-04-27 22:04:13</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
@@ -45509,7 +45429,7 @@
     <row r="196">
       <c r="A196" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 17:49:02</t>
+          <t>2026-04-25 02:49:02</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
@@ -45571,7 +45491,7 @@
     <row r="197">
       <c r="A197" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 17:03:56</t>
+          <t>2026-04-25 02:03:56</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
@@ -45633,7 +45553,7 @@
     <row r="198">
       <c r="A198" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 16:37:00</t>
+          <t>2026-04-25 01:37:00</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
@@ -45695,7 +45615,7 @@
     <row r="199">
       <c r="A199" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 15:33:59</t>
+          <t>2026-04-24 00:33:59</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
@@ -45757,7 +45677,7 @@
     <row r="200">
       <c r="A200" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 15:22:46</t>
+          <t>2026-04-24 00:22:46</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
@@ -45819,7 +45739,7 @@
     <row r="201">
       <c r="A201" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 15:12:54</t>
+          <t>2026-04-24 00:12:54</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
@@ -45881,7 +45801,7 @@
     <row r="202">
       <c r="A202" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 13:36:03</t>
+          <t>2026-04-23 22:36:03</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
@@ -45943,7 +45863,7 @@
     <row r="203">
       <c r="A203" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 15:58:57</t>
+          <t>2026-04-14 00:58:57</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
@@ -46005,7 +45925,7 @@
     <row r="204">
       <c r="A204" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 15:09:08</t>
+          <t>2026-04-14 00:09:08</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
@@ -46067,7 +45987,7 @@
     <row r="205">
       <c r="A205" s="13" t="inlineStr">
         <is>
-          <t>2026-04-12 16:48:02</t>
+          <t>2026-04-13 01:48:02</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
@@ -46129,7 +46049,7 @@
     <row r="206">
       <c r="A206" s="13" t="inlineStr">
         <is>
-          <t>2026-04-12 16:17:58</t>
+          <t>2026-04-13 01:17:58</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
@@ -46191,7 +46111,7 @@
     <row r="207">
       <c r="A207" s="13" t="inlineStr">
         <is>
-          <t>2026-04-12 15:41:20</t>
+          <t>2026-04-13 00:41:20</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
@@ -46253,7 +46173,7 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 14:18:06</t>
+          <t>2026-04-09 23:18:06</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
@@ -46315,7 +46235,7 @@
     <row r="209">
       <c r="A209" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 13:52:44</t>
+          <t>2026-04-09 22:52:44</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
@@ -46377,7 +46297,7 @@
     <row r="210">
       <c r="A210" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 13:27:45</t>
+          <t>2026-04-09 22:27:45</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
@@ -46439,7 +46359,7 @@
     <row r="211">
       <c r="A211" s="13" t="inlineStr">
         <is>
-          <t>2026-04-07 16:10:31</t>
+          <t>2026-04-08 01:10:31</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
@@ -46501,7 +46421,7 @@
     <row r="212">
       <c r="A212" s="13" t="inlineStr">
         <is>
-          <t>2026-04-07 15:29:19</t>
+          <t>2026-04-08 00:29:19</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
@@ -46563,7 +46483,7 @@
     <row r="213">
       <c r="A213" s="13" t="inlineStr">
         <is>
-          <t>2026-04-03 19:36:31</t>
+          <t>2026-04-04 04:36:31</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
@@ -46625,7 +46545,7 @@
     <row r="214">
       <c r="A214" s="13" t="inlineStr">
         <is>
-          <t>2026-04-03 19:16:32</t>
+          <t>2026-04-04 04:16:32</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
@@ -46687,7 +46607,7 @@
     <row r="215">
       <c r="A215" s="13" t="inlineStr">
         <is>
-          <t>2026-03-27 19:24:43</t>
+          <t>2026-03-28 04:24:43</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
@@ -46749,7 +46669,7 @@
     <row r="216">
       <c r="A216" s="13" t="inlineStr">
         <is>
-          <t>2026-03-27 18:38:31</t>
+          <t>2026-03-28 03:38:31</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
@@ -46811,7 +46731,7 @@
     <row r="217">
       <c r="A217" s="13" t="inlineStr">
         <is>
-          <t>2026-03-27 18:17:50</t>
+          <t>2026-03-28 03:17:50</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
@@ -46873,7 +46793,7 @@
     <row r="218">
       <c r="A218" s="13" t="inlineStr">
         <is>
-          <t>2026-03-27 17:43:19</t>
+          <t>2026-03-28 02:43:19</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
@@ -46935,7 +46855,7 @@
     <row r="219">
       <c r="A219" s="13" t="inlineStr">
         <is>
-          <t>2026-03-27 17:15:18</t>
+          <t>2026-03-28 02:15:18</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
@@ -46997,7 +46917,7 @@
     <row r="220">
       <c r="A220" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 14:18:12</t>
+          <t>2026-03-25 23:18:12</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
@@ -47059,7 +46979,7 @@
     <row r="221">
       <c r="A221" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 15:01:49</t>
+          <t>2026-03-25 00:01:49</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
@@ -47121,7 +47041,7 @@
     <row r="222">
       <c r="A222" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 14:25:16</t>
+          <t>2026-03-24 23:25:16</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
@@ -47183,7 +47103,7 @@
     <row r="223">
       <c r="A223" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 14:02:52</t>
+          <t>2026-03-24 23:02:52</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
@@ -47245,7 +47165,7 @@
     <row r="224">
       <c r="A224" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 13:26:26</t>
+          <t>2026-03-24 22:26:26</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
@@ -47307,7 +47227,7 @@
     <row r="225">
       <c r="A225" s="13" t="inlineStr">
         <is>
-          <t>2026-03-23 15:56:18</t>
+          <t>2026-03-24 00:56:18</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
@@ -47369,7 +47289,7 @@
     <row r="226">
       <c r="A226" s="13" t="inlineStr">
         <is>
-          <t>2026-03-23 15:29:29</t>
+          <t>2026-03-24 00:29:29</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
@@ -47431,7 +47351,7 @@
     <row r="227">
       <c r="A227" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 14:51:11</t>
+          <t>2026-03-22 23:51:11</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
@@ -47493,7 +47413,7 @@
     <row r="228">
       <c r="A228" s="13" t="inlineStr">
         <is>
-          <t>2026-03-21 16:04:36</t>
+          <t>2026-03-22 01:04:36</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
@@ -47555,7 +47475,7 @@
     <row r="229">
       <c r="A229" s="13" t="inlineStr">
         <is>
-          <t>2026-03-20 17:55:49</t>
+          <t>2026-03-21 02:55:49</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
@@ -47617,7 +47537,7 @@
     <row r="230">
       <c r="A230" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 15:07:07</t>
+          <t>2026-03-18 00:07:07</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
@@ -47679,7 +47599,7 @@
     <row r="231">
       <c r="A231" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 14:24:05</t>
+          <t>2026-03-17 23:24:05</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
@@ -47741,7 +47661,7 @@
     <row r="232">
       <c r="A232" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 17:00:50</t>
+          <t>2026-03-17 02:00:50</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
@@ -47803,7 +47723,7 @@
     <row r="233">
       <c r="A233" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 16:33:08</t>
+          <t>2026-03-17 01:33:08</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
@@ -47865,7 +47785,7 @@
     <row r="234">
       <c r="A234" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 14:28:09</t>
+          <t>2026-03-16 23:28:09</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
@@ -47927,7 +47847,7 @@
     <row r="235">
       <c r="A235" s="13" t="inlineStr">
         <is>
-          <t>2026-03-15 16:32:22</t>
+          <t>2026-03-16 01:32:22</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
@@ -47989,7 +47909,7 @@
     <row r="236">
       <c r="A236" s="13" t="inlineStr">
         <is>
-          <t>2026-03-13 16:43:49</t>
+          <t>2026-03-14 01:43:49</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
@@ -48051,7 +47971,7 @@
     <row r="237">
       <c r="A237" s="13" t="inlineStr">
         <is>
-          <t>2026-03-13 16:19:35</t>
+          <t>2026-03-14 01:19:35</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
@@ -48113,7 +48033,7 @@
     <row r="238">
       <c r="A238" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 14:45:27</t>
+          <t>2026-03-12 23:45:27</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
@@ -48175,7 +48095,7 @@
     <row r="239">
       <c r="A239" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 14:02:09</t>
+          <t>2026-03-12 23:02:09</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
@@ -48237,7 +48157,7 @@
     <row r="240">
       <c r="A240" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 13:42:59</t>
+          <t>2026-03-12 22:42:59</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
@@ -48299,7 +48219,7 @@
     <row r="241">
       <c r="A241" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 16:39:10</t>
+          <t>2026-03-12 01:39:10</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
@@ -48361,7 +48281,7 @@
     <row r="242">
       <c r="A242" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 15:43:21</t>
+          <t>2026-03-12 00:43:21</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
@@ -48423,7 +48343,7 @@
     <row r="243">
       <c r="A243" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:25</t>
+          <t>2026-03-12 00:04:25</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
@@ -48485,7 +48405,7 @@
     <row r="244">
       <c r="A244" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 13:54:02</t>
+          <t>2026-03-11 22:54:02</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
@@ -48547,7 +48467,7 @@
     <row r="245">
       <c r="A245" s="13" t="inlineStr">
         <is>
-          <t>2026-03-07 17:01:53</t>
+          <t>2026-03-08 02:01:53</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
@@ -48609,7 +48529,7 @@
     <row r="246">
       <c r="A246" s="13" t="inlineStr">
         <is>
-          <t>2026-03-01 17:18:59</t>
+          <t>2026-03-02 02:18:59</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
@@ -48671,7 +48591,7 @@
     <row r="247">
       <c r="A247" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 16:40:38</t>
+          <t>2026-02-24 01:40:38</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
@@ -48733,7 +48653,7 @@
     <row r="248">
       <c r="A248" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 15:10:31</t>
+          <t>2026-02-24 00:10:31</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
@@ -48795,7 +48715,7 @@
     <row r="249">
       <c r="A249" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 14:33:47</t>
+          <t>2026-02-23 23:33:47</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
@@ -48857,7 +48777,7 @@
     <row r="250">
       <c r="A250" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 13:40:54</t>
+          <t>2026-02-23 22:40:54</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
@@ -48919,7 +48839,7 @@
     <row r="251">
       <c r="A251" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 12:58:56</t>
+          <t>2026-02-23 21:58:56</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
@@ -48981,7 +48901,7 @@
     <row r="252">
       <c r="A252" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 10:21:48</t>
+          <t>2026-02-23 19:21:48</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
@@ -49043,7 +48963,7 @@
     <row r="253">
       <c r="A253" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 08:17:13</t>
+          <t>2026-02-23 17:17:13</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
@@ -49105,7 +49025,7 @@
     <row r="254">
       <c r="A254" s="13" t="inlineStr">
         <is>
-          <t>2026-02-22 19:22:01</t>
+          <t>2026-02-23 04:22:01</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
@@ -49167,7 +49087,7 @@
     <row r="255">
       <c r="A255" s="13" t="inlineStr">
         <is>
-          <t>2026-02-22 18:23:51</t>
+          <t>2026-02-23 03:23:51</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
@@ -49229,7 +49149,7 @@
     <row r="256">
       <c r="A256" s="13" t="inlineStr">
         <is>
-          <t>2026-02-22 17:58:18</t>
+          <t>2026-02-23 02:58:18</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
@@ -49291,7 +49211,7 @@
     <row r="257">
       <c r="A257" s="13" t="inlineStr">
         <is>
-          <t>2026-02-22 17:29:21</t>
+          <t>2026-02-23 02:29:21</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
@@ -49353,7 +49273,7 @@
     <row r="258">
       <c r="A258" s="13" t="inlineStr">
         <is>
-          <t>2026-02-22 16:59:09</t>
+          <t>2026-02-23 01:59:09</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
@@ -49415,7 +49335,7 @@
     <row r="259">
       <c r="A259" s="13" t="inlineStr">
         <is>
-          <t>2026-02-22 16:32:08</t>
+          <t>2026-02-23 01:32:08</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
@@ -49477,7 +49397,7 @@
     <row r="260">
       <c r="A260" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 18:34:36</t>
+          <t>2026-02-21 03:34:36</t>
         </is>
       </c>
       <c r="B260" s="13" t="inlineStr">
@@ -49539,7 +49459,7 @@
     <row r="261">
       <c r="A261" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 17:57:13</t>
+          <t>2026-02-21 02:57:13</t>
         </is>
       </c>
       <c r="B261" s="13" t="inlineStr">
@@ -49601,7 +49521,7 @@
     <row r="262">
       <c r="A262" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 17:19:01</t>
+          <t>2026-02-21 02:19:01</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
@@ -49663,7 +49583,7 @@
     <row r="263">
       <c r="A263" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 16:41:10</t>
+          <t>2026-02-21 01:41:10</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
@@ -49725,7 +49645,7 @@
     <row r="264">
       <c r="A264" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 15:57:47</t>
+          <t>2026-02-21 00:57:47</t>
         </is>
       </c>
       <c r="B264" s="13" t="inlineStr">
@@ -49787,7 +49707,7 @@
     <row r="265">
       <c r="A265" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 15:39:52</t>
+          <t>2026-02-21 00:39:52</t>
         </is>
       </c>
       <c r="B265" s="13" t="inlineStr">
@@ -49849,7 +49769,7 @@
     <row r="266">
       <c r="A266" s="13" t="inlineStr">
         <is>
-          <t>2026-02-19 16:21:13</t>
+          <t>2026-02-20 01:21:13</t>
         </is>
       </c>
       <c r="B266" s="13" t="inlineStr">
@@ -49911,7 +49831,7 @@
     <row r="267">
       <c r="A267" s="13" t="inlineStr">
         <is>
-          <t>2026-02-19 15:33:10</t>
+          <t>2026-02-20 00:33:10</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
@@ -49973,7 +49893,7 @@
     <row r="268">
       <c r="A268" s="13" t="inlineStr">
         <is>
-          <t>2026-02-17 15:37:38</t>
+          <t>2026-02-18 00:37:38</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
@@ -50035,7 +49955,7 @@
     <row r="269">
       <c r="A269" s="13" t="inlineStr">
         <is>
-          <t>2026-02-17 14:58:39</t>
+          <t>2026-02-17 23:58:39</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
@@ -50097,7 +50017,7 @@
     <row r="270">
       <c r="A270" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 17:24:16</t>
+          <t>2026-02-16 02:24:16</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
@@ -50159,7 +50079,7 @@
     <row r="271">
       <c r="A271" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 16:47:19</t>
+          <t>2026-02-16 01:47:19</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
@@ -50221,7 +50141,7 @@
     <row r="272">
       <c r="A272" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 15:56:43</t>
+          <t>2026-02-16 00:56:43</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
@@ -50283,7 +50203,7 @@
     <row r="273">
       <c r="A273" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 15:26:20</t>
+          <t>2026-02-16 00:26:20</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
@@ -50345,7 +50265,7 @@
     <row r="274">
       <c r="A274" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 14:48:44</t>
+          <t>2026-02-15 23:48:44</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
@@ -50407,7 +50327,7 @@
     <row r="275">
       <c r="A275" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 19:17:17</t>
+          <t>2026-02-15 04:17:17</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
@@ -50469,7 +50389,7 @@
     <row r="276">
       <c r="A276" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 18:53:01</t>
+          <t>2026-02-15 03:53:01</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
@@ -50531,7 +50451,7 @@
     <row r="277">
       <c r="A277" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 17:59:46</t>
+          <t>2026-02-15 02:59:46</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
@@ -50593,7 +50513,7 @@
     <row r="278">
       <c r="A278" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 17:26:42</t>
+          <t>2026-02-15 02:26:42</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
@@ -50655,7 +50575,7 @@
     <row r="279">
       <c r="A279" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 17:00:09</t>
+          <t>2026-02-15 02:00:09</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
@@ -50717,7 +50637,7 @@
     <row r="280">
       <c r="A280" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 16:39:16</t>
+          <t>2026-02-15 01:39:16</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
@@ -50779,7 +50699,7 @@
     <row r="281">
       <c r="A281" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 15:56:51</t>
+          <t>2026-02-15 00:56:51</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
@@ -50841,7 +50761,7 @@
     <row r="282">
       <c r="A282" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 14:52:26</t>
+          <t>2026-02-14 23:52:26</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
@@ -50903,7 +50823,7 @@
     <row r="283">
       <c r="A283" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 14:14:55</t>
+          <t>2026-02-14 23:14:55</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
@@ -50965,7 +50885,7 @@
     <row r="284">
       <c r="A284" s="13" t="inlineStr">
         <is>
-          <t>2026-02-13 19:19:58</t>
+          <t>2026-02-14 04:19:58</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
@@ -51027,7 +50947,7 @@
     <row r="285">
       <c r="A285" s="13" t="inlineStr">
         <is>
-          <t>2026-02-13 18:37:53</t>
+          <t>2026-02-14 03:37:53</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
@@ -51089,7 +51009,7 @@
     <row r="286">
       <c r="A286" s="13" t="inlineStr">
         <is>
-          <t>2026-02-13 18:03:31</t>
+          <t>2026-02-14 03:03:31</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
@@ -51151,7 +51071,7 @@
     <row r="287">
       <c r="A287" s="13" t="inlineStr">
         <is>
-          <t>2026-02-13 17:08:36</t>
+          <t>2026-02-14 02:08:36</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
@@ -51213,7 +51133,7 @@
     <row r="288">
       <c r="A288" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 15:20:03</t>
+          <t>2026-02-12 00:20:03</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
@@ -51275,7 +51195,7 @@
     <row r="289">
       <c r="A289" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 18:05:03</t>
+          <t>2026-02-11 03:05:03</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
@@ -51337,7 +51257,7 @@
     <row r="290">
       <c r="A290" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 17:14:02</t>
+          <t>2026-02-11 02:14:02</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
@@ -51399,7 +51319,7 @@
     <row r="291">
       <c r="A291" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 16:33:21</t>
+          <t>2026-02-11 01:33:21</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
@@ -51461,7 +51381,7 @@
     <row r="292">
       <c r="A292" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 16:01:41</t>
+          <t>2026-02-11 01:01:41</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
@@ -51523,7 +51443,7 @@
     <row r="293">
       <c r="A293" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 16:49:32</t>
+          <t>2026-02-10 01:49:32</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
@@ -51585,7 +51505,7 @@
     <row r="294">
       <c r="A294" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 16:42:29</t>
+          <t>2026-02-10 01:42:29</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
@@ -51647,7 +51567,7 @@
     <row r="295">
       <c r="A295" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 14:44:10</t>
+          <t>2026-02-09 23:44:10</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
@@ -51709,7 +51629,7 @@
     <row r="296">
       <c r="A296" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 14:00:28</t>
+          <t>2026-02-09 23:00:28</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
@@ -51771,7 +51691,7 @@
     <row r="297">
       <c r="A297" s="13" t="inlineStr">
         <is>
-          <t>2026-02-08 15:27:49</t>
+          <t>2026-02-09 00:27:49</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
@@ -51833,7 +51753,7 @@
     <row r="298">
       <c r="A298" s="13" t="inlineStr">
         <is>
-          <t>2026-02-08 15:16:42</t>
+          <t>2026-02-09 00:16:42</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
@@ -51895,7 +51815,7 @@
     <row r="299">
       <c r="A299" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 19:04:43</t>
+          <t>2026-02-08 04:04:43</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
@@ -51957,7 +51877,7 @@
     <row r="300">
       <c r="A300" s="13" t="inlineStr">
         <is>
-          <t>2026-02-06 18:13:11</t>
+          <t>2026-02-07 03:13:11</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
@@ -52019,7 +51939,7 @@
     <row r="301">
       <c r="A301" s="13" t="inlineStr">
         <is>
-          <t>2026-02-06 17:19:42</t>
+          <t>2026-02-07 02:19:42</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
@@ -52081,7 +52001,7 @@
     <row r="302">
       <c r="A302" s="13" t="inlineStr">
         <is>
-          <t>2026-02-06 16:37:36</t>
+          <t>2026-02-07 01:37:36</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
@@ -52143,7 +52063,7 @@
     <row r="303">
       <c r="A303" s="13" t="inlineStr">
         <is>
-          <t>2026-02-03 14:04:49</t>
+          <t>2026-02-03 23:04:49</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
@@ -52205,7 +52125,7 @@
     <row r="304">
       <c r="A304" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 14:21:38</t>
+          <t>2026-02-02 23:21:38</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
@@ -52267,7 +52187,7 @@
     <row r="305">
       <c r="A305" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 18:08:17</t>
+          <t>2026-02-02 03:08:17</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
@@ -52329,7 +52249,7 @@
     <row r="306">
       <c r="A306" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 17:41:55</t>
+          <t>2026-02-02 02:41:55</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
@@ -52391,7 +52311,7 @@
     <row r="307">
       <c r="A307" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 17:09:57</t>
+          <t>2026-02-02 02:09:57</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
@@ -52453,7 +52373,7 @@
     <row r="308">
       <c r="A308" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 16:41:49</t>
+          <t>2026-02-02 01:41:49</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
@@ -52515,7 +52435,7 @@
     <row r="309">
       <c r="A309" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 17:22:13</t>
+          <t>2026-02-01 02:22:13</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
@@ -52577,7 +52497,7 @@
     <row r="310">
       <c r="A310" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 16:20:54</t>
+          <t>2026-02-01 01:20:54</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
@@ -52639,7 +52559,7 @@
     <row r="311">
       <c r="A311" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 16:09:32</t>
+          <t>2026-02-01 01:09:32</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
@@ -52701,7 +52621,7 @@
     <row r="312">
       <c r="A312" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 15:29:37</t>
+          <t>2026-02-01 00:29:37</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
@@ -52763,7 +52683,7 @@
     <row r="313">
       <c r="A313" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 15:03:50</t>
+          <t>2026-02-01 00:03:50</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
@@ -52825,7 +52745,7 @@
     <row r="314">
       <c r="A314" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 14:15:28</t>
+          <t>2026-01-31 23:15:28</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
@@ -52887,7 +52807,7 @@
     <row r="315">
       <c r="A315" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 15:36:39</t>
+          <t>2026-01-29 00:36:39</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
@@ -52949,7 +52869,7 @@
     <row r="316">
       <c r="A316" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 15:02:45</t>
+          <t>2026-01-29 00:02:45</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
@@ -53011,7 +52931,7 @@
     <row r="317">
       <c r="A317" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 14:26:47</t>
+          <t>2026-01-28 23:26:47</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
@@ -53073,7 +52993,7 @@
     <row r="318">
       <c r="A318" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 14:04:33</t>
+          <t>2026-01-28 23:04:33</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
@@ -53135,7 +53055,7 @@
     <row r="319">
       <c r="A319" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 15:33:31</t>
+          <t>2026-01-28 00:33:31</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
@@ -53197,7 +53117,7 @@
     <row r="320">
       <c r="A320" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 14:59:21</t>
+          <t>2026-01-27 23:59:21</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
@@ -53259,7 +53179,7 @@
     <row r="321">
       <c r="A321" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 14:08:33</t>
+          <t>2026-01-27 23:08:33</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
@@ -53321,7 +53241,7 @@
     <row r="322">
       <c r="A322" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 14:28:17</t>
+          <t>2026-01-25 23:28:17</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
@@ -53383,7 +53303,7 @@
     <row r="323">
       <c r="A323" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 13:56:22</t>
+          <t>2026-01-25 22:56:22</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
@@ -53445,7 +53365,7 @@
     <row r="324">
       <c r="A324" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 13:28:25</t>
+          <t>2026-01-25 22:28:25</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
@@ -53507,7 +53427,7 @@
     <row r="325">
       <c r="A325" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 12:42:03</t>
+          <t>2026-01-25 21:42:03</t>
         </is>
       </c>
       <c r="B325" s="13" t="inlineStr">
@@ -53569,7 +53489,7 @@
     <row r="326">
       <c r="A326" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 10:38:23</t>
+          <t>2026-01-25 19:38:23</t>
         </is>
       </c>
       <c r="B326" s="13" t="inlineStr">
@@ -53631,7 +53551,7 @@
     <row r="327">
       <c r="A327" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 09:56:35</t>
+          <t>2026-01-25 18:56:35</t>
         </is>
       </c>
       <c r="B327" s="13" t="inlineStr">
@@ -53693,7 +53613,7 @@
     <row r="328">
       <c r="A328" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 09:29:19</t>
+          <t>2026-01-25 18:29:19</t>
         </is>
       </c>
       <c r="B328" s="13" t="inlineStr">
@@ -53755,7 +53675,7 @@
     <row r="329">
       <c r="A329" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 08:14:05</t>
+          <t>2026-01-25 17:14:05</t>
         </is>
       </c>
       <c r="B329" s="13" t="inlineStr">
@@ -53817,7 +53737,7 @@
     <row r="330">
       <c r="A330" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 17:47:24</t>
+          <t>2026-01-24 02:47:24</t>
         </is>
       </c>
       <c r="B330" s="13" t="inlineStr">
@@ -53879,7 +53799,7 @@
     <row r="331">
       <c r="A331" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 17:12:26</t>
+          <t>2026-01-24 02:12:26</t>
         </is>
       </c>
       <c r="B331" s="13" t="inlineStr">
@@ -53941,7 +53861,7 @@
     <row r="332">
       <c r="A332" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 16:33:34</t>
+          <t>2026-01-24 01:33:34</t>
         </is>
       </c>
       <c r="B332" s="13" t="inlineStr">
@@ -54003,7 +53923,7 @@
     <row r="333">
       <c r="A333" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 16:00:39</t>
+          <t>2026-01-24 01:00:39</t>
         </is>
       </c>
       <c r="B333" s="13" t="inlineStr">
@@ -54065,7 +53985,7 @@
     <row r="334">
       <c r="A334" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 15:19:07</t>
+          <t>2026-01-24 00:19:07</t>
         </is>
       </c>
       <c r="B334" s="13" t="inlineStr">
@@ -54127,7 +54047,7 @@
     <row r="335">
       <c r="A335" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 14:52:33</t>
+          <t>2026-01-23 23:52:33</t>
         </is>
       </c>
       <c r="B335" s="13" t="inlineStr">
@@ -54189,7 +54109,7 @@
     <row r="336">
       <c r="A336" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 14:19:19</t>
+          <t>2026-01-23 23:19:19</t>
         </is>
       </c>
       <c r="B336" s="13" t="inlineStr">
@@ -54251,7 +54171,7 @@
     <row r="337">
       <c r="A337" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 13:36:59</t>
+          <t>2026-01-23 22:36:59</t>
         </is>
       </c>
       <c r="B337" s="13" t="inlineStr">
@@ -54313,7 +54233,7 @@
     <row r="338">
       <c r="A338" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 18:01:58</t>
+          <t>2026-01-23 03:01:58</t>
         </is>
       </c>
       <c r="B338" s="13" t="inlineStr">
@@ -54375,7 +54295,7 @@
     <row r="339">
       <c r="A339" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 17:25:41</t>
+          <t>2026-01-23 02:25:41</t>
         </is>
       </c>
       <c r="B339" s="13" t="inlineStr">
@@ -54437,7 +54357,7 @@
     <row r="340">
       <c r="A340" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 15:32:45</t>
+          <t>2026-01-23 00:32:45</t>
         </is>
       </c>
       <c r="B340" s="13" t="inlineStr">
@@ -54499,7 +54419,7 @@
     <row r="341">
       <c r="A341" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 14:54:46</t>
+          <t>2026-01-22 23:54:46</t>
         </is>
       </c>
       <c r="B341" s="13" t="inlineStr">
@@ -54561,7 +54481,7 @@
     <row r="342">
       <c r="A342" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 14:17:42</t>
+          <t>2026-01-22 23:17:42</t>
         </is>
       </c>
       <c r="B342" s="13" t="inlineStr">
@@ -54623,7 +54543,7 @@
     <row r="343">
       <c r="A343" s="13" t="inlineStr">
         <is>
-          <t>2026-01-21 16:10:08</t>
+          <t>2026-01-22 01:10:08</t>
         </is>
       </c>
       <c r="B343" s="13" t="inlineStr">
@@ -54685,7 +54605,7 @@
     <row r="344">
       <c r="A344" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 15:27:51</t>
+          <t>2026-01-21 00:27:51</t>
         </is>
       </c>
       <c r="B344" s="13" t="inlineStr">
@@ -54747,7 +54667,7 @@
     <row r="345">
       <c r="A345" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 14:25:34</t>
+          <t>2026-01-20 23:25:34</t>
         </is>
       </c>
       <c r="B345" s="13" t="inlineStr">
@@ -54809,7 +54729,7 @@
     <row r="346">
       <c r="A346" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 13:56:13</t>
+          <t>2026-01-20 22:56:13</t>
         </is>
       </c>
       <c r="B346" s="13" t="inlineStr">
@@ -54871,7 +54791,7 @@
     <row r="347">
       <c r="A347" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 16:59:11</t>
+          <t>2026-01-19 01:59:11</t>
         </is>
       </c>
       <c r="B347" s="13" t="inlineStr">
@@ -54933,7 +54853,7 @@
     <row r="348">
       <c r="A348" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 18:05:32</t>
+          <t>2026-01-18 03:05:32</t>
         </is>
       </c>
       <c r="B348" s="13" t="inlineStr">
@@ -54995,7 +54915,7 @@
     <row r="349">
       <c r="A349" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 17:19:17</t>
+          <t>2026-01-18 02:19:17</t>
         </is>
       </c>
       <c r="B349" s="13" t="inlineStr">
@@ -55057,7 +54977,7 @@
     <row r="350">
       <c r="A350" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 16:58:17</t>
+          <t>2026-01-18 01:58:17</t>
         </is>
       </c>
       <c r="B350" s="13" t="inlineStr">
@@ -55119,7 +55039,7 @@
     <row r="351">
       <c r="A351" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 16:18:29</t>
+          <t>2026-01-18 01:18:29</t>
         </is>
       </c>
       <c r="B351" s="13" t="inlineStr">
@@ -55181,7 +55101,7 @@
     <row r="352">
       <c r="A352" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 15:38:58</t>
+          <t>2026-01-18 00:38:58</t>
         </is>
       </c>
       <c r="B352" s="13" t="inlineStr">
@@ -55243,7 +55163,7 @@
     <row r="353">
       <c r="A353" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 09:46:30</t>
+          <t>2026-01-17 18:46:30</t>
         </is>
       </c>
       <c r="B353" s="13" t="inlineStr">
@@ -55305,7 +55225,7 @@
     <row r="354">
       <c r="A354" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 17:21:36</t>
+          <t>2026-01-17 02:21:36</t>
         </is>
       </c>
       <c r="B354" s="13" t="inlineStr">
@@ -55367,7 +55287,7 @@
     <row r="355">
       <c r="A355" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 16:51:05</t>
+          <t>2026-01-17 01:51:05</t>
         </is>
       </c>
       <c r="B355" s="13" t="inlineStr">
@@ -55429,7 +55349,7 @@
     <row r="356">
       <c r="A356" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 16:18:22</t>
+          <t>2026-01-17 01:18:22</t>
         </is>
       </c>
       <c r="B356" s="13" t="inlineStr">
@@ -55491,7 +55411,7 @@
     <row r="357">
       <c r="A357" s="13" t="inlineStr">
         <is>
-          <t>2026-01-15 16:41:15</t>
+          <t>2026-01-16 01:41:15</t>
         </is>
       </c>
       <c r="B357" s="13" t="inlineStr">
@@ -55553,7 +55473,7 @@
     <row r="358">
       <c r="A358" s="13" t="inlineStr">
         <is>
-          <t>2026-01-15 16:05:38</t>
+          <t>2026-01-16 01:05:38</t>
         </is>
       </c>
       <c r="B358" s="13" t="inlineStr">
@@ -55615,7 +55535,7 @@
     <row r="359">
       <c r="A359" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 15:57:21</t>
+          <t>2026-01-14 00:57:21</t>
         </is>
       </c>
       <c r="B359" s="13" t="inlineStr">
@@ -55677,7 +55597,7 @@
     <row r="360">
       <c r="A360" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 15:19:49</t>
+          <t>2026-01-14 00:19:49</t>
         </is>
       </c>
       <c r="B360" s="13" t="inlineStr">
@@ -55739,7 +55659,7 @@
     <row r="361">
       <c r="A361" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 14:53:29</t>
+          <t>2026-01-13 23:53:29</t>
         </is>
       </c>
       <c r="B361" s="13" t="inlineStr">
@@ -55801,7 +55721,7 @@
     <row r="362">
       <c r="A362" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 17:23:29</t>
+          <t>2026-01-13 02:23:29</t>
         </is>
       </c>
       <c r="B362" s="13" t="inlineStr">
@@ -55863,7 +55783,7 @@
     <row r="363">
       <c r="A363" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 16:42:12</t>
+          <t>2026-01-13 01:42:12</t>
         </is>
       </c>
       <c r="B363" s="13" t="inlineStr">
@@ -55925,7 +55845,7 @@
     <row r="364">
       <c r="A364" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 16:17:01</t>
+          <t>2026-01-13 01:17:01</t>
         </is>
       </c>
       <c r="B364" s="13" t="inlineStr">
@@ -55987,7 +55907,7 @@
     <row r="365">
       <c r="A365" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 15:43:11</t>
+          <t>2026-01-13 00:43:11</t>
         </is>
       </c>
       <c r="B365" s="13" t="inlineStr">
@@ -56049,7 +55969,7 @@
     <row r="366">
       <c r="A366" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 08:24:44</t>
+          <t>2026-01-12 17:24:44</t>
         </is>
       </c>
       <c r="B366" s="13" t="inlineStr">
@@ -56111,7 +56031,7 @@
     <row r="367">
       <c r="A367" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 18:12:16</t>
+          <t>2026-01-12 03:12:16</t>
         </is>
       </c>
       <c r="B367" s="13" t="inlineStr">
@@ -56173,7 +56093,7 @@
     <row r="368">
       <c r="A368" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 17:54:03</t>
+          <t>2026-01-11 02:54:03</t>
         </is>
       </c>
       <c r="B368" s="13" t="inlineStr">
@@ -56235,7 +56155,7 @@
     <row r="369">
       <c r="A369" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 17:14:56</t>
+          <t>2026-01-11 02:14:56</t>
         </is>
       </c>
       <c r="B369" s="13" t="inlineStr">
@@ -56297,7 +56217,7 @@
     <row r="370">
       <c r="A370" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 16:17:21</t>
+          <t>2026-01-11 01:17:21</t>
         </is>
       </c>
       <c r="B370" s="13" t="inlineStr">
@@ -56359,7 +56279,7 @@
     <row r="371">
       <c r="A371" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 15:22:11</t>
+          <t>2026-01-11 00:22:11</t>
         </is>
       </c>
       <c r="B371" s="13" t="inlineStr">
@@ -56421,7 +56341,7 @@
     <row r="372">
       <c r="A372" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 14:38:24</t>
+          <t>2026-01-10 23:38:24</t>
         </is>
       </c>
       <c r="B372" s="13" t="inlineStr">
@@ -56483,7 +56403,7 @@
     <row r="373">
       <c r="A373" s="13" t="inlineStr">
         <is>
-          <t>2026-01-09 17:54:19</t>
+          <t>2026-01-10 02:54:19</t>
         </is>
       </c>
       <c r="B373" s="13" t="inlineStr">
@@ -56545,7 +56465,7 @@
     <row r="374">
       <c r="A374" s="13" t="inlineStr">
         <is>
-          <t>2026-01-09 17:00:16</t>
+          <t>2026-01-10 02:00:16</t>
         </is>
       </c>
       <c r="B374" s="13" t="inlineStr">
@@ -56607,7 +56527,7 @@
     <row r="375">
       <c r="A375" s="13" t="inlineStr">
         <is>
-          <t>2026-01-09 14:36:27</t>
+          <t>2026-01-09 23:36:27</t>
         </is>
       </c>
       <c r="B375" s="13" t="inlineStr">
@@ -56666,70 +56586,8 @@
         </is>
       </c>
     </row>
-    <row r="376">
-      <c r="A376" s="13" t="inlineStr">
-        <is>
-          <t>2026-01-05 14:21:47</t>
-        </is>
-      </c>
-      <c r="B376" s="13" t="inlineStr">
-        <is>
-          <t>ランク</t>
-        </is>
-      </c>
-      <c r="C376" s="13" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D376" s="13" t="inlineStr">
-        <is>
-          <t>SUP</t>
-        </is>
-      </c>
-      <c r="E376" s="13" t="inlineStr">
-        <is>
-          <t>ジャンナ</t>
-        </is>
-      </c>
-      <c r="F376" s="13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G376" s="13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H376" s="13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I376" s="13" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J376" s="13" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K376" s="14" t="inlineStr"/>
-      <c r="L376" s="14" t="inlineStr"/>
-      <c r="M376" s="14" t="inlineStr"/>
-      <c r="N376" s="14" t="inlineStr"/>
-      <c r="O376" s="14" t="inlineStr"/>
-      <c r="P376" s="13" t="inlineStr">
-        <is>
-          <t>JP1_556572228</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P376"/>
+  <autoFilter ref="A1:P375"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-03 02:37:36</t>
+          <t>出力日時：2026-08-03 02:40:16</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'キュー別'!$A$1:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'チャンピオン別'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SUPチャンピオン別'!$A$1:$L$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$383</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$383</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$384</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$384</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,14 +532,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>対象期間：2026-01-09 23:36:27 ～ 2026-08-03 02:00:01</t>
+          <t>対象期間：2026-01-05 14:21:47 ～ 2026-08-02 17:00:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-03 02:40:16</t>
+          <t>出力日時：2026-08-03 05:29:08</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.4738219895287958</v>
+        <v>0.4725848563968668</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.670157068062827</v>
+        <v>1.66579634464752</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5.342931937172775</v>
+        <v>5.342036553524804</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>8.921465968586388</v>
+        <v>8.921671018276763</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>59.91884816753927</v>
+        <v>59.85378590078329</v>
       </c>
     </row>
     <row r="15">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2.040497382198953</v>
+        <v>2.038198433420366</v>
       </c>
     </row>
     <row r="16">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>56.95549738219896</v>
+        <v>56.9242819843342</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1.836492146596858</v>
+        <v>1.835613577023498</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.5033333333333333</v>
+        <v>0.5016611295681063</v>
       </c>
     </row>
     <row r="24">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>1.45</v>
+        <v>1.445182724252492</v>
       </c>
     </row>
     <row r="25">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.18</v>
+        <v>5.179401993355482</v>
       </c>
     </row>
     <row r="26">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.79734219269103</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>36.42333333333333</v>
+        <v>36.41860465116279</v>
       </c>
     </row>
     <row r="29">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1.2538</v>
+        <v>1.253488372093023</v>
       </c>
     </row>
     <row r="30">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>64.27666666666667</v>
+        <v>64.2126245847176</v>
       </c>
     </row>
     <row r="31">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>2.0711</v>
+        <v>2.069202657807307</v>
       </c>
     </row>
   </sheetData>
@@ -820,7 +820,7 @@
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>151</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.5033333333333333</v>
+        <v>0.5016611295681063</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.45</v>
+        <v>1.445182724252492</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5.18</v>
+        <v>5.179401993355482</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.79734219269103</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.2538</v>
+        <v>1.253488372093023</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>64.27666666666667</v>
+        <v>64.2126245847176</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>2.0711</v>
+        <v>2.069202657807307</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.933833333333333</v>
+        <v>4.933833333333332</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>31.96666666666667</v>
@@ -1128,12 +1128,12 @@
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1239,7 +1239,7 @@
         <v>53.35294117647059</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>1.738398692810458</v>
+        <v>1.738398692810457</v>
       </c>
     </row>
     <row r="3">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>32</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4155844155844156</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.157894736842105</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>5.828947368421052</v>
+        <v>5.818181818181818</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>10.07894736842105</v>
+        <v>10.06493506493507</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.253421052631579</v>
+        <v>1.252207792207792</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>71.46052631578948</v>
+        <v>71.11688311688312</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.231447368421053</v>
+        <v>2.221948051948053</v>
       </c>
     </row>
   </sheetData>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1.797111111111111</v>
+        <v>1.797111111111112</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>68.51111111111111</v>
@@ -1516,25 +1516,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.775</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.153846153846154</v>
+        <v>5.15</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.17948717948718</v>
+        <v>7.225</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.232820512820513</v>
+        <v>1.231</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.97435897435897</v>
+        <v>53.75</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.871025641025641</v>
+        <v>1.86175</v>
       </c>
     </row>
     <row r="6">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5.148285714285715</v>
+        <v>5.148285714285714</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>34.6</v>
@@ -1800,7 +1800,7 @@
         <v>25.625</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.85625</v>
+        <v>0.8562500000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1842,7 +1842,7 @@
         <v>21.83333333333333</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.8633333333333333</v>
+        <v>0.8633333333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5.050000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>16.25</v>
@@ -2833,25 +2833,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.775</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.153846153846154</v>
+        <v>5.15</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.17948717948718</v>
+        <v>7.225</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.232820512820513</v>
+        <v>1.231</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.97435897435897</v>
+        <v>53.75</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.871025641025641</v>
+        <v>1.86175</v>
       </c>
     </row>
     <row r="6">
@@ -3224,7 +3224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V383"/>
+  <dimension ref="A1:V384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3366,7 +3366,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03 02:00:01</t>
+          <t>2026-08-02 17:00:01</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03 00:22:22</t>
+          <t>2026-08-02 15:22:22</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 23:45:22</t>
+          <t>2026-08-02 14:45:22</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 18:45:07</t>
+          <t>2026-08-02 09:45:07</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 18:20:05</t>
+          <t>2026-08-02 09:20:05</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:32</t>
+          <t>2026-08-02 08:49:32</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 03:33:03</t>
+          <t>2026-08-01 18:33:03</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 02:39:30</t>
+          <t>2026-08-01 17:39:30</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 04:00:11</t>
+          <t>2026-07-31 19:00:11</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 03:30:26</t>
+          <t>2026-07-31 18:30:26</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -4166,7 +4166,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 02:52:16</t>
+          <t>2026-07-31 17:52:16</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 01:50:20</t>
+          <t>2026-07-31 16:50:20</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -4326,7 +4326,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 01:16:45</t>
+          <t>2026-07-31 16:16:45</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 22:56:19</t>
+          <t>2026-07-31 13:56:19</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -4486,7 +4486,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 22:22:46</t>
+          <t>2026-07-31 13:22:46</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -4566,7 +4566,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 21:49:35</t>
+          <t>2026-07-31 12:49:35</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -4646,7 +4646,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 23:51:39</t>
+          <t>2026-07-28 14:51:39</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 23:05:20</t>
+          <t>2026-07-28 14:05:20</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27 01:21:51</t>
+          <t>2026-07-26 16:21:51</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -4886,7 +4886,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27 00:43:02</t>
+          <t>2026-07-26 15:43:02</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -4966,7 +4966,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 23:12:09</t>
+          <t>2026-07-25 14:12:09</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 22:30:57</t>
+          <t>2026-07-25 13:30:57</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -5126,7 +5126,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 00:11:55</t>
+          <t>2026-07-24 15:11:55</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24 23:25:38</t>
+          <t>2026-07-24 14:25:38</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -5286,7 +5286,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22 00:17:56</t>
+          <t>2026-07-21 15:17:56</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -5366,7 +5366,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22 00:04:35</t>
+          <t>2026-07-21 15:04:35</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 23:25:56</t>
+          <t>2026-07-21 14:25:56</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -5526,7 +5526,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 22:44:36</t>
+          <t>2026-07-21 13:44:36</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -5606,7 +5606,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 22:18:59</t>
+          <t>2026-07-21 13:18:59</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20 03:20:20</t>
+          <t>2026-07-19 18:20:20</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -5766,7 +5766,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20 02:39:51</t>
+          <t>2026-07-19 17:39:51</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -5846,7 +5846,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:59:14</t>
+          <t>2026-07-18 09:59:14</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -5926,7 +5926,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:21:14</t>
+          <t>2026-07-18 09:21:14</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -6006,7 +6006,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 23:06:28</t>
+          <t>2026-07-16 14:06:28</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 22:32:42</t>
+          <t>2026-07-16 13:32:42</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 00:40:48</t>
+          <t>2026-07-15 15:40:48</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 23:41:56</t>
+          <t>2026-07-15 14:41:56</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -6326,7 +6326,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 22:58:44</t>
+          <t>2026-07-15 13:58:44</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -6406,7 +6406,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 22:34:16</t>
+          <t>2026-07-15 13:34:16</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -6486,7 +6486,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 23:36:35</t>
+          <t>2026-07-14 14:36:35</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -6566,7 +6566,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 22:49:50</t>
+          <t>2026-07-14 13:49:50</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -6646,7 +6646,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 01:02:29</t>
+          <t>2026-07-13 16:02:29</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -6726,7 +6726,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 00:22:46</t>
+          <t>2026-07-13 15:22:46</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -6806,7 +6806,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 23:51:38</t>
+          <t>2026-07-13 14:51:38</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -6886,7 +6886,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 02:05:19</t>
+          <t>2026-07-12 17:05:19</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -6966,7 +6966,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 01:29:17</t>
+          <t>2026-07-12 16:29:17</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 03:11:38</t>
+          <t>2026-07-11 18:11:38</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -7126,7 +7126,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 02:46:15</t>
+          <t>2026-07-11 17:46:15</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 03:42:29</t>
+          <t>2026-07-10 18:42:29</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -7286,7 +7286,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 03:06:21</t>
+          <t>2026-07-10 18:06:21</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -7366,7 +7366,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:55:25</t>
+          <t>2026-07-08 17:55:25</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -7446,7 +7446,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:17:09</t>
+          <t>2026-07-08 17:17:09</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -7526,7 +7526,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 02:03:51</t>
+          <t>2026-07-05 17:03:51</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 01:07:17</t>
+          <t>2026-07-05 16:07:17</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -7686,7 +7686,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 00:23:00</t>
+          <t>2026-07-05 15:23:00</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -7766,7 +7766,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05 03:21:23</t>
+          <t>2026-07-04 18:21:23</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -7846,7 +7846,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>2026-07-04 03:01:40</t>
+          <t>2026-07-03 18:01:40</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -7926,7 +7926,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03 01:48:19</t>
+          <t>2026-07-02 16:48:19</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -8006,7 +8006,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01 00:21:19</t>
+          <t>2026-06-30 15:21:19</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -8086,7 +8086,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 23:38:16</t>
+          <t>2026-06-30 14:38:16</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 01:16:28</t>
+          <t>2026-06-29 16:16:28</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -8246,7 +8246,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 00:34:32</t>
+          <t>2026-06-29 15:34:32</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -8326,7 +8326,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26 00:50:56</t>
+          <t>2026-06-25 15:50:56</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -8406,7 +8406,7 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26 00:06:40</t>
+          <t>2026-06-25 15:06:40</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -8486,7 +8486,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07:56</t>
+          <t>2026-06-24 17:07:56</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -8566,7 +8566,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 01:33:19</t>
+          <t>2026-06-24 16:33:19</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:47:59</t>
+          <t>2026-06-24 15:47:59</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:08:31</t>
+          <t>2026-06-24 15:08:31</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -8806,7 +8806,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 23:33:15</t>
+          <t>2026-06-24 14:33:15</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -8886,7 +8886,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 22:39:11</t>
+          <t>2026-06-24 13:39:11</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -8966,7 +8966,7 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 01:16:06</t>
+          <t>2026-06-22 16:16:06</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -9046,7 +9046,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 00:38:08</t>
+          <t>2026-06-22 15:38:08</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -9126,7 +9126,7 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 00:29:33</t>
+          <t>2026-06-22 15:29:33</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -9206,7 +9206,7 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 01:54:04</t>
+          <t>2026-06-18 16:54:04</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
@@ -9286,7 +9286,7 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 01:14:50</t>
+          <t>2026-06-18 16:14:50</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -9366,7 +9366,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 00:35:17</t>
+          <t>2026-06-18 15:35:17</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -9446,7 +9446,7 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 23:55:50</t>
+          <t>2026-06-18 14:55:50</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -9526,7 +9526,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 00:44:42</t>
+          <t>2026-06-17 15:44:42</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -9606,7 +9606,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 23:57:38</t>
+          <t>2026-06-17 14:57:38</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -9686,7 +9686,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 01:58:55</t>
+          <t>2026-06-16 16:58:55</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -9766,7 +9766,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 01:30:07</t>
+          <t>2026-06-16 16:30:07</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -9846,7 +9846,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 03:10:28</t>
+          <t>2026-06-14 18:10:28</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -9926,7 +9926,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 02:27:52</t>
+          <t>2026-06-14 17:27:52</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -10006,7 +10006,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 01:57:23</t>
+          <t>2026-06-14 16:57:23</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -10086,7 +10086,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 01:27:22</t>
+          <t>2026-06-14 16:27:22</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -10166,7 +10166,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 00:24:35</t>
+          <t>2026-06-14 15:24:35</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 23:46:55</t>
+          <t>2026-06-14 14:46:55</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -10326,7 +10326,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 01:41:53</t>
+          <t>2026-06-13 16:41:53</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 00:52:58</t>
+          <t>2026-06-13 15:52:58</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -10486,7 +10486,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 00:14:23</t>
+          <t>2026-06-13 15:14:23</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -10566,7 +10566,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 23:45:21</t>
+          <t>2026-06-13 14:45:21</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -10646,7 +10646,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 23:05:32</t>
+          <t>2026-06-13 14:05:32</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -10726,7 +10726,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 01:08:14</t>
+          <t>2026-06-10 16:08:14</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -10806,7 +10806,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:34:35</t>
+          <t>2026-06-10 15:34:35</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -10886,7 +10886,7 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:09:17</t>
+          <t>2026-06-10 15:09:17</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -10966,7 +10966,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 23:27:53</t>
+          <t>2026-06-10 14:27:53</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -11046,7 +11046,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 00:49:00</t>
+          <t>2026-06-09 15:49:00</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -11126,7 +11126,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06 02:58:51</t>
+          <t>2026-06-05 17:58:51</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06 02:15:04</t>
+          <t>2026-06-05 17:15:04</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -11286,7 +11286,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 23:49:14</t>
+          <t>2026-06-04 14:49:14</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -11366,7 +11366,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 21:40:04</t>
+          <t>2026-06-04 12:40:04</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -11446,7 +11446,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 21:17:24</t>
+          <t>2026-06-04 12:17:24</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -11526,7 +11526,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 01:06:27</t>
+          <t>2026-06-03 16:06:27</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 00:31:09</t>
+          <t>2026-06-03 15:31:09</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -11686,7 +11686,7 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 23:53:57</t>
+          <t>2026-06-03 14:53:57</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -11766,7 +11766,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 22:44:02</t>
+          <t>2026-06-03 13:44:02</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -11846,7 +11846,7 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02 22:49:11</t>
+          <t>2026-06-02 13:49:11</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -11926,7 +11926,7 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:56:06</t>
+          <t>2026-06-01 14:56:06</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -12006,7 +12006,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:20:26</t>
+          <t>2026-06-01 14:20:26</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:01:06</t>
+          <t>2026-06-01 14:01:06</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -12166,7 +12166,7 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31 03:01:04</t>
+          <t>2026-05-30 18:01:04</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -12246,7 +12246,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31 02:13:41</t>
+          <t>2026-05-30 17:13:41</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -12326,7 +12326,7 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 23:00:40</t>
+          <t>2026-05-25 14:00:40</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -12406,7 +12406,7 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 01:55:47</t>
+          <t>2026-05-24 16:55:47</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -12486,7 +12486,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 01:24:22</t>
+          <t>2026-05-24 16:24:22</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -12566,7 +12566,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 23:49:25</t>
+          <t>2026-05-24 14:49:25</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -12646,7 +12646,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 03:13:39</t>
+          <t>2026-05-23 18:13:39</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -12726,7 +12726,7 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 02:41:52</t>
+          <t>2026-05-23 17:41:52</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -12806,7 +12806,7 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 23:19:04</t>
+          <t>2026-05-23 14:19:04</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -12886,7 +12886,7 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 22:43:20</t>
+          <t>2026-05-23 13:43:20</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -12966,7 +12966,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 15:54:19</t>
+          <t>2026-05-23 06:54:19</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -13046,7 +13046,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 02:25:24</t>
+          <t>2026-05-22 17:25:24</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -13126,7 +13126,7 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 01:29:23</t>
+          <t>2026-05-21 16:29:23</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -13206,7 +13206,7 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 00:48:49</t>
+          <t>2026-05-21 15:48:49</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -13286,7 +13286,7 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:45</t>
+          <t>2026-05-21 15:00:45</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -13366,7 +13366,7 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 23:22:44</t>
+          <t>2026-05-21 14:22:44</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -13446,7 +13446,7 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 00:05:15</t>
+          <t>2026-05-20 15:05:15</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -13526,7 +13526,7 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 23:43:50</t>
+          <t>2026-05-20 14:43:50</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -13606,7 +13606,7 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 22:57:45</t>
+          <t>2026-05-20 13:57:45</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -13686,7 +13686,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 01:25:45</t>
+          <t>2026-05-19 16:25:45</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 00:46:42</t>
+          <t>2026-05-19 15:46:42</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -13846,7 +13846,7 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>2026-05-18 22:56:39</t>
+          <t>2026-05-18 13:56:39</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -13926,7 +13926,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 01:35:56</t>
+          <t>2026-05-14 16:35:56</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -14006,7 +14006,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 01:17:05</t>
+          <t>2026-05-14 16:17:05</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -14086,7 +14086,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 00:05:48</t>
+          <t>2026-05-14 15:05:48</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -14166,7 +14166,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14 01:25:38</t>
+          <t>2026-05-13 16:25:38</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -14246,7 +14246,7 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>2026-05-12 00:19:57</t>
+          <t>2026-05-11 15:19:57</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -14326,7 +14326,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 23:54:15</t>
+          <t>2026-05-11 14:54:15</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -14406,7 +14406,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 23:14:30</t>
+          <t>2026-05-11 14:14:30</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -14486,7 +14486,7 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 22:37:05</t>
+          <t>2026-05-11 13:37:05</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -14566,7 +14566,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 21:53:13</t>
+          <t>2026-05-11 12:53:13</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -14646,7 +14646,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 00:04:01</t>
+          <t>2026-05-10 15:04:01</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -14726,7 +14726,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:54:24</t>
+          <t>2026-05-09 16:54:24</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -14806,7 +14806,7 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:22:50</t>
+          <t>2026-05-09 16:22:50</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -14886,7 +14886,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 00:26:16</t>
+          <t>2026-05-09 15:26:16</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -14966,7 +14966,7 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 23:38:30</t>
+          <t>2026-05-09 14:38:30</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -15046,7 +15046,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 22:50:20</t>
+          <t>2026-05-09 13:50:20</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -15126,7 +15126,7 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 22:13:25</t>
+          <t>2026-05-09 13:13:25</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -15206,7 +15206,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 20:00:11</t>
+          <t>2026-05-09 11:00:11</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -15286,7 +15286,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 19:10:28</t>
+          <t>2026-05-09 10:10:28</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -15366,7 +15366,7 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 02:17:27</t>
+          <t>2026-05-08 17:17:27</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 01:38:25</t>
+          <t>2026-05-08 16:38:25</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -15526,7 +15526,7 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 00:58:58</t>
+          <t>2026-05-08 15:58:58</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -15606,7 +15606,7 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 00:37:55</t>
+          <t>2026-05-08 15:37:55</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -15686,7 +15686,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 01:48:31</t>
+          <t>2026-05-07 16:48:31</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -15766,7 +15766,7 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 01:02:52</t>
+          <t>2026-05-07 16:02:52</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -15846,7 +15846,7 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 00:23:29</t>
+          <t>2026-05-07 15:23:29</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -15926,7 +15926,7 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 01:30:56</t>
+          <t>2026-05-06 16:30:56</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 00:42:16</t>
+          <t>2026-05-06 15:42:16</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -16086,7 +16086,7 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 23:44:04</t>
+          <t>2026-05-06 14:44:04</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -16166,7 +16166,7 @@
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:13:52</t>
+          <t>2026-05-06 09:13:52</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -16246,7 +16246,7 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:05:08</t>
+          <t>2026-05-06 09:05:08</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -16326,7 +16326,7 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 17:22:30</t>
+          <t>2026-05-06 08:22:30</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -16406,7 +16406,7 @@
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 16:28:42</t>
+          <t>2026-05-06 07:28:42</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -16486,7 +16486,7 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 03:16:57</t>
+          <t>2026-05-05 18:16:57</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -16566,7 +16566,7 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:32:40</t>
+          <t>2026-05-05 17:32:40</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -16646,7 +16646,7 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:23:28</t>
+          <t>2026-05-05 17:23:28</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -16726,7 +16726,7 @@
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 01:48:28</t>
+          <t>2026-05-05 16:48:28</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -16806,7 +16806,7 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 00:52:33</t>
+          <t>2026-05-05 15:52:33</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -16886,7 +16886,7 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 17:43:06</t>
+          <t>2026-05-05 08:43:06</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
@@ -16966,7 +16966,7 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>2026-05-03 00:36:42</t>
+          <t>2026-05-02 15:36:42</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -17046,7 +17046,7 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 23:51:09</t>
+          <t>2026-05-02 14:51:09</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 22:15:10</t>
+          <t>2026-05-02 13:15:10</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
@@ -17206,7 +17206,7 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 21:29:49</t>
+          <t>2026-05-02 12:29:49</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -17286,7 +17286,7 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 01:39:42</t>
+          <t>2026-04-30 16:39:42</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
@@ -17366,7 +17366,7 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 01:01:34</t>
+          <t>2026-04-30 16:01:34</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -17446,7 +17446,7 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 00:24:48</t>
+          <t>2026-04-30 15:24:48</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -17526,7 +17526,7 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 23:37:10</t>
+          <t>2026-04-30 14:37:10</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
@@ -17606,7 +17606,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 22:58:06</t>
+          <t>2026-04-30 13:58:06</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -17686,7 +17686,7 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 03:29:33</t>
+          <t>2026-04-29 18:29:33</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
@@ -17766,7 +17766,7 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 02:54:07</t>
+          <t>2026-04-29 17:54:07</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
@@ -17846,7 +17846,7 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 02:20:58</t>
+          <t>2026-04-29 17:20:58</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
@@ -17926,7 +17926,7 @@
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 01:42:01</t>
+          <t>2026-04-29 16:42:01</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
@@ -18006,7 +18006,7 @@
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 01:03:17</t>
+          <t>2026-04-29 16:03:17</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
@@ -18086,7 +18086,7 @@
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 00:19:47</t>
+          <t>2026-04-29 15:19:47</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
@@ -18166,7 +18166,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 23:29:53</t>
+          <t>2026-04-29 14:29:53</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
@@ -18246,7 +18246,7 @@
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:59:49</t>
+          <t>2026-04-29 13:59:49</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
@@ -18326,7 +18326,7 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:38:22</t>
+          <t>2026-04-29 13:38:22</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
@@ -18406,7 +18406,7 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:44</t>
+          <t>2026-04-29 13:17:44</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
@@ -18486,7 +18486,7 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 03:28:56</t>
+          <t>2026-04-28 18:28:56</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
@@ -18566,7 +18566,7 @@
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:58:50</t>
+          <t>2026-04-28 17:58:50</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -18646,7 +18646,7 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:29:43</t>
+          <t>2026-04-28 17:29:43</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
@@ -18726,7 +18726,7 @@
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 01:38:43</t>
+          <t>2026-04-28 16:38:43</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:54</t>
+          <t>2026-04-28 15:58:54</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
@@ -18886,7 +18886,7 @@
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:31:32</t>
+          <t>2026-04-28 15:31:32</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -18966,7 +18966,7 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:04:20</t>
+          <t>2026-04-28 15:04:20</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
@@ -19046,7 +19046,7 @@
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 23:37:27</t>
+          <t>2026-04-28 14:37:27</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -19126,7 +19126,7 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 23:09:10</t>
+          <t>2026-04-28 14:09:10</t>
         </is>
       </c>
       <c r="B199" s="7" t="inlineStr">
@@ -19206,7 +19206,7 @@
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:59:25</t>
+          <t>2026-04-27 14:59:25</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -19286,7 +19286,7 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:49:35</t>
+          <t>2026-04-27 14:49:35</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
@@ -19366,7 +19366,7 @@
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 22:55:34</t>
+          <t>2026-04-27 13:55:34</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -19446,7 +19446,7 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 22:04:13</t>
+          <t>2026-04-27 13:04:13</t>
         </is>
       </c>
       <c r="B203" s="7" t="inlineStr">
@@ -19526,7 +19526,7 @@
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 02:49:02</t>
+          <t>2026-04-24 17:49:02</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
@@ -19606,7 +19606,7 @@
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 02:03:56</t>
+          <t>2026-04-24 17:03:56</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
@@ -19686,7 +19686,7 @@
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 01:37:00</t>
+          <t>2026-04-24 16:37:00</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
@@ -19766,7 +19766,7 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:33:59</t>
+          <t>2026-04-23 15:33:59</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
@@ -19846,7 +19846,7 @@
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:22:46</t>
+          <t>2026-04-23 15:22:46</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -19926,7 +19926,7 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:12:54</t>
+          <t>2026-04-23 15:12:54</t>
         </is>
       </c>
       <c r="B209" s="7" t="inlineStr">
@@ -20006,7 +20006,7 @@
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 22:36:03</t>
+          <t>2026-04-23 13:36:03</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -20086,7 +20086,7 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:58:57</t>
+          <t>2026-04-13 15:58:57</t>
         </is>
       </c>
       <c r="B211" s="7" t="inlineStr">
@@ -20166,7 +20166,7 @@
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:09:08</t>
+          <t>2026-04-13 15:09:08</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
@@ -20246,7 +20246,7 @@
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 01:48:02</t>
+          <t>2026-04-12 16:48:02</t>
         </is>
       </c>
       <c r="B213" s="7" t="inlineStr">
@@ -20326,7 +20326,7 @@
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 01:17:58</t>
+          <t>2026-04-12 16:17:58</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
@@ -20406,7 +20406,7 @@
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 00:41:20</t>
+          <t>2026-04-12 15:41:20</t>
         </is>
       </c>
       <c r="B215" s="7" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 23:18:06</t>
+          <t>2026-04-09 14:18:06</t>
         </is>
       </c>
       <c r="B216" s="7" t="inlineStr">
@@ -20566,7 +20566,7 @@
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 22:52:44</t>
+          <t>2026-04-09 13:52:44</t>
         </is>
       </c>
       <c r="B217" s="7" t="inlineStr">
@@ -20646,7 +20646,7 @@
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 22:27:45</t>
+          <t>2026-04-09 13:27:45</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
@@ -20726,7 +20726,7 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>2026-04-08 01:10:31</t>
+          <t>2026-04-07 16:10:31</t>
         </is>
       </c>
       <c r="B219" s="7" t="inlineStr">
@@ -20806,7 +20806,7 @@
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>2026-04-08 00:29:19</t>
+          <t>2026-04-07 15:29:19</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
@@ -20886,7 +20886,7 @@
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>2026-04-04 04:36:31</t>
+          <t>2026-04-03 19:36:31</t>
         </is>
       </c>
       <c r="B221" s="7" t="inlineStr">
@@ -20966,7 +20966,7 @@
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>2026-04-04 04:16:32</t>
+          <t>2026-04-03 19:16:32</t>
         </is>
       </c>
       <c r="B222" s="7" t="inlineStr">
@@ -21046,7 +21046,7 @@
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 04:24:43</t>
+          <t>2026-03-27 19:24:43</t>
         </is>
       </c>
       <c r="B223" s="7" t="inlineStr">
@@ -21126,7 +21126,7 @@
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 03:38:31</t>
+          <t>2026-03-27 18:38:31</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -21206,7 +21206,7 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 03:17:50</t>
+          <t>2026-03-27 18:17:50</t>
         </is>
       </c>
       <c r="B225" s="7" t="inlineStr">
@@ -21286,7 +21286,7 @@
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 02:43:19</t>
+          <t>2026-03-27 17:43:19</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
@@ -21366,7 +21366,7 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 02:15:18</t>
+          <t>2026-03-27 17:15:18</t>
         </is>
       </c>
       <c r="B227" s="7" t="inlineStr">
@@ -21446,7 +21446,7 @@
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 23:18:12</t>
+          <t>2026-03-25 14:18:12</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
@@ -21526,7 +21526,7 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 00:01:49</t>
+          <t>2026-03-24 15:01:49</t>
         </is>
       </c>
       <c r="B229" s="7" t="inlineStr">
@@ -21606,7 +21606,7 @@
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 23:25:16</t>
+          <t>2026-03-24 14:25:16</t>
         </is>
       </c>
       <c r="B230" s="7" t="inlineStr">
@@ -21686,7 +21686,7 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 23:02:52</t>
+          <t>2026-03-24 14:02:52</t>
         </is>
       </c>
       <c r="B231" s="7" t="inlineStr">
@@ -21766,7 +21766,7 @@
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 22:26:26</t>
+          <t>2026-03-24 13:26:26</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
@@ -21846,7 +21846,7 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 00:56:18</t>
+          <t>2026-03-23 15:56:18</t>
         </is>
       </c>
       <c r="B233" s="7" t="inlineStr">
@@ -21926,7 +21926,7 @@
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 00:29:29</t>
+          <t>2026-03-23 15:29:29</t>
         </is>
       </c>
       <c r="B234" s="7" t="inlineStr">
@@ -22006,7 +22006,7 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 23:51:11</t>
+          <t>2026-03-22 14:51:11</t>
         </is>
       </c>
       <c r="B235" s="7" t="inlineStr">
@@ -22086,7 +22086,7 @@
     <row r="236">
       <c r="A236" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 01:04:36</t>
+          <t>2026-03-21 16:04:36</t>
         </is>
       </c>
       <c r="B236" s="7" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>2026-03-21 02:55:49</t>
+          <t>2026-03-20 17:55:49</t>
         </is>
       </c>
       <c r="B237" s="7" t="inlineStr">
@@ -22246,7 +22246,7 @@
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>2026-03-18 00:07:07</t>
+          <t>2026-03-17 15:07:07</t>
         </is>
       </c>
       <c r="B238" s="7" t="inlineStr">
@@ -22326,7 +22326,7 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 23:24:05</t>
+          <t>2026-03-17 14:24:05</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
@@ -22406,7 +22406,7 @@
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 02:00:50</t>
+          <t>2026-03-16 17:00:50</t>
         </is>
       </c>
       <c r="B240" s="7" t="inlineStr">
@@ -22486,7 +22486,7 @@
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 01:33:08</t>
+          <t>2026-03-16 16:33:08</t>
         </is>
       </c>
       <c r="B241" s="7" t="inlineStr">
@@ -22566,7 +22566,7 @@
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 23:28:09</t>
+          <t>2026-03-16 14:28:09</t>
         </is>
       </c>
       <c r="B242" s="7" t="inlineStr">
@@ -22646,7 +22646,7 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 01:32:22</t>
+          <t>2026-03-15 16:32:22</t>
         </is>
       </c>
       <c r="B243" s="7" t="inlineStr">
@@ -22726,7 +22726,7 @@
     <row r="244">
       <c r="A244" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14 01:43:49</t>
+          <t>2026-03-13 16:43:49</t>
         </is>
       </c>
       <c r="B244" s="7" t="inlineStr">
@@ -22806,7 +22806,7 @@
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14 01:19:35</t>
+          <t>2026-03-13 16:19:35</t>
         </is>
       </c>
       <c r="B245" s="7" t="inlineStr">
@@ -22886,7 +22886,7 @@
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 23:45:27</t>
+          <t>2026-03-12 14:45:27</t>
         </is>
       </c>
       <c r="B246" s="7" t="inlineStr">
@@ -22966,7 +22966,7 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 23:02:09</t>
+          <t>2026-03-12 14:02:09</t>
         </is>
       </c>
       <c r="B247" s="7" t="inlineStr">
@@ -23046,7 +23046,7 @@
     <row r="248">
       <c r="A248" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 22:42:59</t>
+          <t>2026-03-12 13:42:59</t>
         </is>
       </c>
       <c r="B248" s="7" t="inlineStr">
@@ -23126,7 +23126,7 @@
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 01:39:10</t>
+          <t>2026-03-11 16:39:10</t>
         </is>
       </c>
       <c r="B249" s="7" t="inlineStr">
@@ -23206,7 +23206,7 @@
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:43:21</t>
+          <t>2026-03-11 15:43:21</t>
         </is>
       </c>
       <c r="B250" s="7" t="inlineStr">
@@ -23286,7 +23286,7 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:04:25</t>
+          <t>2026-03-11 15:04:25</t>
         </is>
       </c>
       <c r="B251" s="7" t="inlineStr">
@@ -23366,7 +23366,7 @@
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 22:54:02</t>
+          <t>2026-03-11 13:54:02</t>
         </is>
       </c>
       <c r="B252" s="7" t="inlineStr">
@@ -23446,7 +23446,7 @@
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>2026-03-08 02:01:53</t>
+          <t>2026-03-07 17:01:53</t>
         </is>
       </c>
       <c r="B253" s="7" t="inlineStr">
@@ -23526,7 +23526,7 @@
     <row r="254">
       <c r="A254" s="7" t="inlineStr">
         <is>
-          <t>2026-03-02 02:18:59</t>
+          <t>2026-03-01 17:18:59</t>
         </is>
       </c>
       <c r="B254" s="7" t="inlineStr">
@@ -23606,7 +23606,7 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>2026-02-24 01:40:38</t>
+          <t>2026-02-23 16:40:38</t>
         </is>
       </c>
       <c r="B255" s="7" t="inlineStr">
@@ -23686,7 +23686,7 @@
     <row r="256">
       <c r="A256" s="7" t="inlineStr">
         <is>
-          <t>2026-02-24 00:10:31</t>
+          <t>2026-02-23 15:10:31</t>
         </is>
       </c>
       <c r="B256" s="7" t="inlineStr">
@@ -23766,7 +23766,7 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 23:33:47</t>
+          <t>2026-02-23 14:33:47</t>
         </is>
       </c>
       <c r="B257" s="7" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="258">
       <c r="A258" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 22:40:54</t>
+          <t>2026-02-23 13:40:54</t>
         </is>
       </c>
       <c r="B258" s="7" t="inlineStr">
@@ -23926,7 +23926,7 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 21:58:56</t>
+          <t>2026-02-23 12:58:56</t>
         </is>
       </c>
       <c r="B259" s="7" t="inlineStr">
@@ -24006,7 +24006,7 @@
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 19:21:48</t>
+          <t>2026-02-23 10:21:48</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
@@ -24086,7 +24086,7 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 17:17:13</t>
+          <t>2026-02-23 08:17:13</t>
         </is>
       </c>
       <c r="B261" s="7" t="inlineStr">
@@ -24166,7 +24166,7 @@
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 04:22:01</t>
+          <t>2026-02-22 19:22:01</t>
         </is>
       </c>
       <c r="B262" s="7" t="inlineStr">
@@ -24246,7 +24246,7 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 03:23:51</t>
+          <t>2026-02-22 18:23:51</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
@@ -24326,7 +24326,7 @@
     <row r="264">
       <c r="A264" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 02:58:18</t>
+          <t>2026-02-22 17:58:18</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -24406,7 +24406,7 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 02:29:21</t>
+          <t>2026-02-22 17:29:21</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
@@ -24486,7 +24486,7 @@
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 01:59:09</t>
+          <t>2026-02-22 16:59:09</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -24566,7 +24566,7 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 01:32:08</t>
+          <t>2026-02-22 16:32:08</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -24646,7 +24646,7 @@
     <row r="268">
       <c r="A268" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 03:34:36</t>
+          <t>2026-02-20 18:34:36</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
@@ -24726,7 +24726,7 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 02:57:13</t>
+          <t>2026-02-20 17:57:13</t>
         </is>
       </c>
       <c r="B269" s="7" t="inlineStr">
@@ -24806,7 +24806,7 @@
     <row r="270">
       <c r="A270" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 02:19:01</t>
+          <t>2026-02-20 17:19:01</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
@@ -24886,7 +24886,7 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 01:41:10</t>
+          <t>2026-02-20 16:41:10</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
@@ -24966,7 +24966,7 @@
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:57:47</t>
+          <t>2026-02-20 15:57:47</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -25046,7 +25046,7 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:39:52</t>
+          <t>2026-02-20 15:39:52</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
@@ -25126,7 +25126,7 @@
     <row r="274">
       <c r="A274" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 01:21:13</t>
+          <t>2026-02-19 16:21:13</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -25206,7 +25206,7 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 00:33:10</t>
+          <t>2026-02-19 15:33:10</t>
         </is>
       </c>
       <c r="B275" s="7" t="inlineStr">
@@ -25286,7 +25286,7 @@
     <row r="276">
       <c r="A276" s="7" t="inlineStr">
         <is>
-          <t>2026-02-18 00:37:38</t>
+          <t>2026-02-17 15:37:38</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
@@ -25366,7 +25366,7 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>2026-02-17 23:58:39</t>
+          <t>2026-02-17 14:58:39</t>
         </is>
       </c>
       <c r="B277" s="7" t="inlineStr">
@@ -25446,7 +25446,7 @@
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 02:24:16</t>
+          <t>2026-02-15 17:24:16</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 01:47:19</t>
+          <t>2026-02-15 16:47:19</t>
         </is>
       </c>
       <c r="B279" s="7" t="inlineStr">
@@ -25606,7 +25606,7 @@
     <row r="280">
       <c r="A280" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 00:56:43</t>
+          <t>2026-02-15 15:56:43</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -25686,7 +25686,7 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 00:26:20</t>
+          <t>2026-02-15 15:26:20</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
@@ -25766,7 +25766,7 @@
     <row r="282">
       <c r="A282" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 23:48:44</t>
+          <t>2026-02-15 14:48:44</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -25846,7 +25846,7 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 04:17:17</t>
+          <t>2026-02-14 19:17:17</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
@@ -25926,7 +25926,7 @@
     <row r="284">
       <c r="A284" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 03:53:01</t>
+          <t>2026-02-14 18:53:01</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -26006,7 +26006,7 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:59:46</t>
+          <t>2026-02-14 17:59:46</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
@@ -26086,7 +26086,7 @@
     <row r="286">
       <c r="A286" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:26:42</t>
+          <t>2026-02-14 17:26:42</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -26166,7 +26166,7 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:00:09</t>
+          <t>2026-02-14 17:00:09</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -26246,7 +26246,7 @@
     <row r="288">
       <c r="A288" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 01:39:16</t>
+          <t>2026-02-14 16:39:16</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -26326,7 +26326,7 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 00:56:51</t>
+          <t>2026-02-14 15:56:51</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -26406,7 +26406,7 @@
     <row r="290">
       <c r="A290" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 23:52:26</t>
+          <t>2026-02-14 14:52:26</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -26486,7 +26486,7 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 23:14:55</t>
+          <t>2026-02-14 14:14:55</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
@@ -26566,7 +26566,7 @@
     <row r="292">
       <c r="A292" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 04:19:58</t>
+          <t>2026-02-13 19:19:58</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -26646,7 +26646,7 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 03:37:53</t>
+          <t>2026-02-13 18:37:53</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
@@ -26726,7 +26726,7 @@
     <row r="294">
       <c r="A294" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 03:03:31</t>
+          <t>2026-02-13 18:03:31</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -26806,7 +26806,7 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 02:08:36</t>
+          <t>2026-02-13 17:08:36</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
@@ -26886,7 +26886,7 @@
     <row r="296">
       <c r="A296" s="7" t="inlineStr">
         <is>
-          <t>2026-02-12 00:20:03</t>
+          <t>2026-02-11 15:20:03</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -26966,7 +26966,7 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 03:05:03</t>
+          <t>2026-02-10 18:05:03</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -27046,7 +27046,7 @@
     <row r="298">
       <c r="A298" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 02:14:02</t>
+          <t>2026-02-10 17:14:02</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -27126,7 +27126,7 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 01:33:21</t>
+          <t>2026-02-10 16:33:21</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="300">
       <c r="A300" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 01:01:41</t>
+          <t>2026-02-10 16:01:41</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
@@ -27286,7 +27286,7 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 01:49:32</t>
+          <t>2026-02-09 16:49:32</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -27366,7 +27366,7 @@
     <row r="302">
       <c r="A302" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 01:42:29</t>
+          <t>2026-02-09 16:42:29</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
@@ -27446,7 +27446,7 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 23:44:10</t>
+          <t>2026-02-09 14:44:10</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
@@ -27526,7 +27526,7 @@
     <row r="304">
       <c r="A304" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 23:00:28</t>
+          <t>2026-02-09 14:00:28</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -27606,7 +27606,7 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 00:27:49</t>
+          <t>2026-02-08 15:27:49</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -27686,7 +27686,7 @@
     <row r="306">
       <c r="A306" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 00:16:42</t>
+          <t>2026-02-08 15:16:42</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -27766,7 +27766,7 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08 04:04:43</t>
+          <t>2026-02-07 19:04:43</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
@@ -27846,7 +27846,7 @@
     <row r="308">
       <c r="A308" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 03:13:11</t>
+          <t>2026-02-06 18:13:11</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
@@ -27926,7 +27926,7 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 02:19:42</t>
+          <t>2026-02-06 17:19:42</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
@@ -28006,7 +28006,7 @@
     <row r="310">
       <c r="A310" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 01:37:36</t>
+          <t>2026-02-06 16:37:36</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -28086,7 +28086,7 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>2026-02-03 23:04:49</t>
+          <t>2026-02-03 14:04:49</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -28166,7 +28166,7 @@
     <row r="312">
       <c r="A312" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 23:21:38</t>
+          <t>2026-02-02 14:21:38</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -28246,7 +28246,7 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 03:08:17</t>
+          <t>2026-02-01 18:08:17</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -28326,7 +28326,7 @@
     <row r="314">
       <c r="A314" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 02:41:55</t>
+          <t>2026-02-01 17:41:55</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -28406,7 +28406,7 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 02:09:57</t>
+          <t>2026-02-01 17:09:57</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -28486,7 +28486,7 @@
     <row r="316">
       <c r="A316" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 01:41:49</t>
+          <t>2026-02-01 16:41:49</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -28566,7 +28566,7 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 02:22:13</t>
+          <t>2026-01-31 17:22:13</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -28646,7 +28646,7 @@
     <row r="318">
       <c r="A318" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 01:20:54</t>
+          <t>2026-01-31 16:20:54</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -28726,7 +28726,7 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 01:09:32</t>
+          <t>2026-01-31 16:09:32</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -28806,7 +28806,7 @@
     <row r="320">
       <c r="A320" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 00:29:37</t>
+          <t>2026-01-31 15:29:37</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 00:03:50</t>
+          <t>2026-01-31 15:03:50</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -28966,7 +28966,7 @@
     <row r="322">
       <c r="A322" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 23:15:28</t>
+          <t>2026-01-31 14:15:28</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -29046,7 +29046,7 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>2026-01-29 00:36:39</t>
+          <t>2026-01-28 15:36:39</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -29126,7 +29126,7 @@
     <row r="324">
       <c r="A324" s="7" t="inlineStr">
         <is>
-          <t>2026-01-29 00:02:45</t>
+          <t>2026-01-28 15:02:45</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -29206,7 +29206,7 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 23:26:47</t>
+          <t>2026-01-28 14:26:47</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -29286,7 +29286,7 @@
     <row r="326">
       <c r="A326" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 23:04:33</t>
+          <t>2026-01-28 14:04:33</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -29366,7 +29366,7 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 00:33:31</t>
+          <t>2026-01-27 15:33:31</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -29446,7 +29446,7 @@
     <row r="328">
       <c r="A328" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 23:59:21</t>
+          <t>2026-01-27 14:59:21</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -29526,7 +29526,7 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 23:08:33</t>
+          <t>2026-01-27 14:08:33</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -29606,7 +29606,7 @@
     <row r="330">
       <c r="A330" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 23:28:17</t>
+          <t>2026-01-25 14:28:17</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -29686,7 +29686,7 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 22:56:22</t>
+          <t>2026-01-25 13:56:22</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -29766,7 +29766,7 @@
     <row r="332">
       <c r="A332" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 22:28:25</t>
+          <t>2026-01-25 13:28:25</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -29846,7 +29846,7 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 21:42:03</t>
+          <t>2026-01-25 12:42:03</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -29926,7 +29926,7 @@
     <row r="334">
       <c r="A334" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 19:38:23</t>
+          <t>2026-01-25 10:38:23</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -30006,7 +30006,7 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 18:56:35</t>
+          <t>2026-01-25 09:56:35</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -30086,7 +30086,7 @@
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 18:29:19</t>
+          <t>2026-01-25 09:29:19</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -30166,7 +30166,7 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 17:14:05</t>
+          <t>2026-01-25 08:14:05</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -30246,7 +30246,7 @@
     <row r="338">
       <c r="A338" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 02:47:24</t>
+          <t>2026-01-23 17:47:24</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -30326,7 +30326,7 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 02:12:26</t>
+          <t>2026-01-23 17:12:26</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -30406,7 +30406,7 @@
     <row r="340">
       <c r="A340" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 01:33:34</t>
+          <t>2026-01-23 16:33:34</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -30486,7 +30486,7 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 01:00:39</t>
+          <t>2026-01-23 16:00:39</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="342">
       <c r="A342" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 00:19:07</t>
+          <t>2026-01-23 15:19:07</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -30646,7 +30646,7 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 23:52:33</t>
+          <t>2026-01-23 14:52:33</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -30726,7 +30726,7 @@
     <row r="344">
       <c r="A344" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 23:19:19</t>
+          <t>2026-01-23 14:19:19</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -30806,7 +30806,7 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36:59</t>
+          <t>2026-01-23 13:36:59</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -30886,7 +30886,7 @@
     <row r="346">
       <c r="A346" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 03:01:58</t>
+          <t>2026-01-22 18:01:58</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -30966,7 +30966,7 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 02:25:41</t>
+          <t>2026-01-22 17:25:41</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -31046,7 +31046,7 @@
     <row r="348">
       <c r="A348" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 00:32:45</t>
+          <t>2026-01-22 15:32:45</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -31126,7 +31126,7 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 23:54:46</t>
+          <t>2026-01-22 14:54:46</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -31206,7 +31206,7 @@
     <row r="350">
       <c r="A350" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 23:17:42</t>
+          <t>2026-01-22 14:17:42</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -31286,7 +31286,7 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 01:10:08</t>
+          <t>2026-01-21 16:10:08</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -31366,7 +31366,7 @@
     <row r="352">
       <c r="A352" s="7" t="inlineStr">
         <is>
-          <t>2026-01-21 00:27:51</t>
+          <t>2026-01-20 15:27:51</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -31446,7 +31446,7 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 23:25:34</t>
+          <t>2026-01-20 14:25:34</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -31526,7 +31526,7 @@
     <row r="354">
       <c r="A354" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 22:56:13</t>
+          <t>2026-01-20 13:56:13</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -31606,7 +31606,7 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>2026-01-19 01:59:11</t>
+          <t>2026-01-18 16:59:11</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -31686,7 +31686,7 @@
     <row r="356">
       <c r="A356" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 03:05:32</t>
+          <t>2026-01-17 18:05:32</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -31766,7 +31766,7 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 02:19:17</t>
+          <t>2026-01-17 17:19:17</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -31846,7 +31846,7 @@
     <row r="358">
       <c r="A358" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 01:58:17</t>
+          <t>2026-01-17 16:58:17</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -31926,7 +31926,7 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 01:18:29</t>
+          <t>2026-01-17 16:18:29</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -32006,7 +32006,7 @@
     <row r="360">
       <c r="A360" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 00:38:58</t>
+          <t>2026-01-17 15:38:58</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -32086,7 +32086,7 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 18:46:30</t>
+          <t>2026-01-17 09:46:30</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -32166,7 +32166,7 @@
     <row r="362">
       <c r="A362" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 02:21:36</t>
+          <t>2026-01-16 17:21:36</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 01:51:05</t>
+          <t>2026-01-16 16:51:05</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -32326,7 +32326,7 @@
     <row r="364">
       <c r="A364" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 01:18:22</t>
+          <t>2026-01-16 16:18:22</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -32406,7 +32406,7 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 01:41:15</t>
+          <t>2026-01-15 16:41:15</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -32486,7 +32486,7 @@
     <row r="366">
       <c r="A366" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 01:05:38</t>
+          <t>2026-01-15 16:05:38</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -32566,7 +32566,7 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14 00:57:21</t>
+          <t>2026-01-13 15:57:21</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -32646,7 +32646,7 @@
     <row r="368">
       <c r="A368" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14 00:19:49</t>
+          <t>2026-01-13 15:19:49</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -32726,7 +32726,7 @@
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 23:53:29</t>
+          <t>2026-01-13 14:53:29</t>
         </is>
       </c>
       <c r="B369" s="7" t="inlineStr">
@@ -32806,7 +32806,7 @@
     <row r="370">
       <c r="A370" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 02:23:29</t>
+          <t>2026-01-12 17:23:29</t>
         </is>
       </c>
       <c r="B370" s="7" t="inlineStr">
@@ -32886,7 +32886,7 @@
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 01:42:12</t>
+          <t>2026-01-12 16:42:12</t>
         </is>
       </c>
       <c r="B371" s="7" t="inlineStr">
@@ -32966,7 +32966,7 @@
     <row r="372">
       <c r="A372" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 01:17:01</t>
+          <t>2026-01-12 16:17:01</t>
         </is>
       </c>
       <c r="B372" s="7" t="inlineStr">
@@ -33046,7 +33046,7 @@
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 00:43:11</t>
+          <t>2026-01-12 15:43:11</t>
         </is>
       </c>
       <c r="B373" s="7" t="inlineStr">
@@ -33126,7 +33126,7 @@
     <row r="374">
       <c r="A374" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 17:24:44</t>
+          <t>2026-01-12 08:24:44</t>
         </is>
       </c>
       <c r="B374" s="7" t="inlineStr">
@@ -33206,7 +33206,7 @@
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 03:12:16</t>
+          <t>2026-01-11 18:12:16</t>
         </is>
       </c>
       <c r="B375" s="7" t="inlineStr">
@@ -33286,7 +33286,7 @@
     <row r="376">
       <c r="A376" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 02:54:03</t>
+          <t>2026-01-10 17:54:03</t>
         </is>
       </c>
       <c r="B376" s="7" t="inlineStr">
@@ -33366,7 +33366,7 @@
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 02:14:56</t>
+          <t>2026-01-10 17:14:56</t>
         </is>
       </c>
       <c r="B377" s="7" t="inlineStr">
@@ -33446,7 +33446,7 @@
     <row r="378">
       <c r="A378" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 01:17:21</t>
+          <t>2026-01-10 16:17:21</t>
         </is>
       </c>
       <c r="B378" s="7" t="inlineStr">
@@ -33526,7 +33526,7 @@
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 00:22:11</t>
+          <t>2026-01-10 15:22:11</t>
         </is>
       </c>
       <c r="B379" s="7" t="inlineStr">
@@ -33606,7 +33606,7 @@
     <row r="380">
       <c r="A380" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 23:38:24</t>
+          <t>2026-01-10 14:38:24</t>
         </is>
       </c>
       <c r="B380" s="7" t="inlineStr">
@@ -33686,7 +33686,7 @@
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 02:54:19</t>
+          <t>2026-01-09 17:54:19</t>
         </is>
       </c>
       <c r="B381" s="7" t="inlineStr">
@@ -33766,7 +33766,7 @@
     <row r="382">
       <c r="A382" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 02:00:16</t>
+          <t>2026-01-09 17:00:16</t>
         </is>
       </c>
       <c r="B382" s="7" t="inlineStr">
@@ -33846,7 +33846,7 @@
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>2026-01-09 23:36:27</t>
+          <t>2026-01-09 14:36:27</t>
         </is>
       </c>
       <c r="B383" s="7" t="inlineStr">
@@ -33923,8 +33923,88 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-05 14:21:47</t>
+        </is>
+      </c>
+      <c r="B384" s="7" t="inlineStr">
+        <is>
+          <t>ランク(ソロ/デュオ)</t>
+        </is>
+      </c>
+      <c r="C384" s="10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D384" s="7" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E384" s="7" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F384" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G384" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H384" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I384" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J384" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K384" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="L384" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M384" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N384" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="O384" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P384" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q384" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R384" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S384" s="11" t="n">
+        <v>6751</v>
+      </c>
+      <c r="T384" s="11" t="n">
+        <v>2219</v>
+      </c>
+      <c r="U384" s="6" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V384" s="7" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V383"/>
+  <autoFilter ref="A1:V384"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33935,7 +34015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P383"/>
+  <dimension ref="A1:P384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -34041,7 +34121,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03 02:00:01</t>
+          <t>2026-08-02 17:00:01</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
@@ -34103,7 +34183,7 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03 00:22:22</t>
+          <t>2026-08-02 15:22:22</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
@@ -34165,7 +34245,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 23:45:22</t>
+          <t>2026-08-02 14:45:22</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -34227,7 +34307,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 18:45:07</t>
+          <t>2026-08-02 09:45:07</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -34289,7 +34369,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 18:20:05</t>
+          <t>2026-08-02 09:20:05</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -34351,7 +34431,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:32</t>
+          <t>2026-08-02 08:49:32</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -34413,7 +34493,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 03:33:03</t>
+          <t>2026-08-01 18:33:03</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -34475,7 +34555,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 02:39:30</t>
+          <t>2026-08-01 17:39:30</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -34537,7 +34617,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 04:00:11</t>
+          <t>2026-07-31 19:00:11</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -34599,7 +34679,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 03:30:26</t>
+          <t>2026-07-31 18:30:26</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -34661,7 +34741,7 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 02:52:16</t>
+          <t>2026-07-31 17:52:16</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -34723,7 +34803,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 01:50:20</t>
+          <t>2026-07-31 16:50:20</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -34785,7 +34865,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 01:16:45</t>
+          <t>2026-07-31 16:16:45</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
@@ -34847,7 +34927,7 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 22:56:19</t>
+          <t>2026-07-31 13:56:19</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -34909,7 +34989,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 22:22:46</t>
+          <t>2026-07-31 13:22:46</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -34971,7 +35051,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 21:49:35</t>
+          <t>2026-07-31 12:49:35</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -35033,7 +35113,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 23:51:39</t>
+          <t>2026-07-28 14:51:39</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -35095,7 +35175,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 23:05:20</t>
+          <t>2026-07-28 14:05:20</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -35157,7 +35237,7 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>2026-07-27 01:21:51</t>
+          <t>2026-07-26 16:21:51</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -35219,7 +35299,7 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>2026-07-27 00:43:02</t>
+          <t>2026-07-26 15:43:02</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -35281,7 +35361,7 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 23:12:09</t>
+          <t>2026-07-25 14:12:09</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -35343,7 +35423,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 22:30:57</t>
+          <t>2026-07-25 13:30:57</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -35405,7 +35485,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 00:11:55</t>
+          <t>2026-07-24 15:11:55</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -35467,7 +35547,7 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>2026-07-24 23:25:38</t>
+          <t>2026-07-24 14:25:38</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -35529,7 +35609,7 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>2026-07-22 00:17:56</t>
+          <t>2026-07-21 15:17:56</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
@@ -35591,7 +35671,7 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>2026-07-22 00:04:35</t>
+          <t>2026-07-21 15:04:35</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -35653,7 +35733,7 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 23:25:56</t>
+          <t>2026-07-21 14:25:56</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
@@ -35715,7 +35795,7 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 22:44:36</t>
+          <t>2026-07-21 13:44:36</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -35777,7 +35857,7 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 22:18:59</t>
+          <t>2026-07-21 13:18:59</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
@@ -35839,7 +35919,7 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>2026-07-20 03:20:20</t>
+          <t>2026-07-19 18:20:20</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
@@ -35901,7 +35981,7 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>2026-07-20 02:39:51</t>
+          <t>2026-07-19 17:39:51</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
@@ -35963,7 +36043,7 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:59:14</t>
+          <t>2026-07-18 09:59:14</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -36025,7 +36105,7 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:21:14</t>
+          <t>2026-07-18 09:21:14</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
@@ -36087,7 +36167,7 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 23:06:28</t>
+          <t>2026-07-16 14:06:28</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
@@ -36149,7 +36229,7 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 22:32:42</t>
+          <t>2026-07-16 13:32:42</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
@@ -36211,7 +36291,7 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 00:40:48</t>
+          <t>2026-07-15 15:40:48</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -36273,7 +36353,7 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 23:41:56</t>
+          <t>2026-07-15 14:41:56</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
@@ -36335,7 +36415,7 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 22:58:44</t>
+          <t>2026-07-15 13:58:44</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -36397,7 +36477,7 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 22:34:16</t>
+          <t>2026-07-15 13:34:16</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
@@ -36459,7 +36539,7 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 23:36:35</t>
+          <t>2026-07-14 14:36:35</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
@@ -36521,7 +36601,7 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 22:49:50</t>
+          <t>2026-07-14 13:49:50</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
@@ -36583,7 +36663,7 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 01:02:29</t>
+          <t>2026-07-13 16:02:29</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
@@ -36645,7 +36725,7 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 00:22:46</t>
+          <t>2026-07-13 15:22:46</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
@@ -36707,7 +36787,7 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 23:51:38</t>
+          <t>2026-07-13 14:51:38</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
@@ -36769,7 +36849,7 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 02:05:19</t>
+          <t>2026-07-12 17:05:19</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
@@ -36831,7 +36911,7 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 01:29:17</t>
+          <t>2026-07-12 16:29:17</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
@@ -36893,7 +36973,7 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 03:11:38</t>
+          <t>2026-07-11 18:11:38</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
@@ -36955,7 +37035,7 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 02:46:15</t>
+          <t>2026-07-11 17:46:15</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
@@ -37017,7 +37097,7 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 03:42:29</t>
+          <t>2026-07-10 18:42:29</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
@@ -37079,7 +37159,7 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 03:06:21</t>
+          <t>2026-07-10 18:06:21</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
@@ -37141,7 +37221,7 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:55:25</t>
+          <t>2026-07-08 17:55:25</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
@@ -37203,7 +37283,7 @@
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:17:09</t>
+          <t>2026-07-08 17:17:09</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
@@ -37265,7 +37345,7 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 02:03:51</t>
+          <t>2026-07-05 17:03:51</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
@@ -37327,7 +37407,7 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 01:07:17</t>
+          <t>2026-07-05 16:07:17</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
@@ -37389,7 +37469,7 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 00:23:00</t>
+          <t>2026-07-05 15:23:00</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
@@ -37451,7 +37531,7 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>2026-07-05 03:21:23</t>
+          <t>2026-07-04 18:21:23</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
@@ -37513,7 +37593,7 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>2026-07-04 03:01:40</t>
+          <t>2026-07-03 18:01:40</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
@@ -37575,7 +37655,7 @@
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>2026-07-03 01:48:19</t>
+          <t>2026-07-02 16:48:19</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
@@ -37637,7 +37717,7 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>2026-07-01 00:21:19</t>
+          <t>2026-06-30 15:21:19</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
@@ -37699,7 +37779,7 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 23:38:16</t>
+          <t>2026-06-30 14:38:16</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
@@ -37761,7 +37841,7 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 01:16:28</t>
+          <t>2026-06-29 16:16:28</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
@@ -37823,7 +37903,7 @@
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 00:34:32</t>
+          <t>2026-06-29 15:34:32</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
@@ -37885,7 +37965,7 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>2026-06-26 00:50:56</t>
+          <t>2026-06-25 15:50:56</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
@@ -37947,7 +38027,7 @@
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>2026-06-26 00:06:40</t>
+          <t>2026-06-25 15:06:40</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
@@ -38009,7 +38089,7 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07:56</t>
+          <t>2026-06-24 17:07:56</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
@@ -38071,7 +38151,7 @@
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 01:33:19</t>
+          <t>2026-06-24 16:33:19</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
@@ -38133,7 +38213,7 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:47:59</t>
+          <t>2026-06-24 15:47:59</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
@@ -38195,7 +38275,7 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:08:31</t>
+          <t>2026-06-24 15:08:31</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
@@ -38257,7 +38337,7 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 23:33:15</t>
+          <t>2026-06-24 14:33:15</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
@@ -38319,7 +38399,7 @@
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 22:39:11</t>
+          <t>2026-06-24 13:39:11</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
@@ -38381,7 +38461,7 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 01:16:06</t>
+          <t>2026-06-22 16:16:06</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
@@ -38443,7 +38523,7 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 00:38:08</t>
+          <t>2026-06-22 15:38:08</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
@@ -38505,7 +38585,7 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 00:29:33</t>
+          <t>2026-06-22 15:29:33</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
@@ -38567,7 +38647,7 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 01:54:04</t>
+          <t>2026-06-18 16:54:04</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
@@ -38629,7 +38709,7 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 01:14:50</t>
+          <t>2026-06-18 16:14:50</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
@@ -38691,7 +38771,7 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 00:35:17</t>
+          <t>2026-06-18 15:35:17</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
@@ -38753,7 +38833,7 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 23:55:50</t>
+          <t>2026-06-18 14:55:50</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
@@ -38815,7 +38895,7 @@
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 00:44:42</t>
+          <t>2026-06-17 15:44:42</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
@@ -38877,7 +38957,7 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 23:57:38</t>
+          <t>2026-06-17 14:57:38</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
@@ -38939,7 +39019,7 @@
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 01:58:55</t>
+          <t>2026-06-16 16:58:55</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
@@ -39001,7 +39081,7 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 01:30:07</t>
+          <t>2026-06-16 16:30:07</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
@@ -39063,7 +39143,7 @@
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 03:10:28</t>
+          <t>2026-06-14 18:10:28</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
@@ -39125,7 +39205,7 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 02:27:52</t>
+          <t>2026-06-14 17:27:52</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
@@ -39187,7 +39267,7 @@
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 01:57:23</t>
+          <t>2026-06-14 16:57:23</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
@@ -39249,7 +39329,7 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 01:27:22</t>
+          <t>2026-06-14 16:27:22</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
@@ -39311,7 +39391,7 @@
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 00:24:35</t>
+          <t>2026-06-14 15:24:35</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
@@ -39373,7 +39453,7 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 23:46:55</t>
+          <t>2026-06-14 14:46:55</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
@@ -39435,7 +39515,7 @@
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 01:41:53</t>
+          <t>2026-06-13 16:41:53</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
@@ -39497,7 +39577,7 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 00:52:58</t>
+          <t>2026-06-13 15:52:58</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
@@ -39559,7 +39639,7 @@
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 00:14:23</t>
+          <t>2026-06-13 15:14:23</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
@@ -39621,7 +39701,7 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 23:45:21</t>
+          <t>2026-06-13 14:45:21</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
@@ -39683,7 +39763,7 @@
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 23:05:32</t>
+          <t>2026-06-13 14:05:32</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
@@ -39745,7 +39825,7 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 01:08:14</t>
+          <t>2026-06-10 16:08:14</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
@@ -39807,7 +39887,7 @@
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:34:35</t>
+          <t>2026-06-10 15:34:35</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
@@ -39869,7 +39949,7 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:09:17</t>
+          <t>2026-06-10 15:09:17</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
@@ -39931,7 +40011,7 @@
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 23:27:53</t>
+          <t>2026-06-10 14:27:53</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
@@ -39993,7 +40073,7 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 00:49:00</t>
+          <t>2026-06-09 15:49:00</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
@@ -40055,7 +40135,7 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>2026-06-06 02:58:51</t>
+          <t>2026-06-05 17:58:51</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
@@ -40117,7 +40197,7 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>2026-06-06 02:15:04</t>
+          <t>2026-06-05 17:15:04</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
@@ -40179,7 +40259,7 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 23:49:14</t>
+          <t>2026-06-04 14:49:14</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
@@ -40241,7 +40321,7 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 21:40:04</t>
+          <t>2026-06-04 12:40:04</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
@@ -40303,7 +40383,7 @@
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 21:17:24</t>
+          <t>2026-06-04 12:17:24</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
@@ -40365,7 +40445,7 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 01:06:27</t>
+          <t>2026-06-03 16:06:27</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
@@ -40427,7 +40507,7 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 00:31:09</t>
+          <t>2026-06-03 15:31:09</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
@@ -40489,7 +40569,7 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 23:53:57</t>
+          <t>2026-06-03 14:53:57</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
@@ -40551,7 +40631,7 @@
     <row r="107">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 22:44:02</t>
+          <t>2026-06-03 13:44:02</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
@@ -40613,7 +40693,7 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>2026-06-02 22:49:11</t>
+          <t>2026-06-02 13:49:11</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
@@ -40675,7 +40755,7 @@
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:56:06</t>
+          <t>2026-06-01 14:56:06</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
@@ -40737,7 +40817,7 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:20:26</t>
+          <t>2026-06-01 14:20:26</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
@@ -40799,7 +40879,7 @@
     <row r="111">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:01:06</t>
+          <t>2026-06-01 14:01:06</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
@@ -40861,7 +40941,7 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>2026-05-31 03:01:04</t>
+          <t>2026-05-30 18:01:04</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
@@ -40923,7 +41003,7 @@
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>2026-05-31 02:13:41</t>
+          <t>2026-05-30 17:13:41</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
@@ -40985,7 +41065,7 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 23:00:40</t>
+          <t>2026-05-25 14:00:40</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
@@ -41047,7 +41127,7 @@
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 01:55:47</t>
+          <t>2026-05-24 16:55:47</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
@@ -41109,7 +41189,7 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 01:24:22</t>
+          <t>2026-05-24 16:24:22</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
@@ -41171,7 +41251,7 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 23:49:25</t>
+          <t>2026-05-24 14:49:25</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
@@ -41233,7 +41313,7 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 03:13:39</t>
+          <t>2026-05-23 18:13:39</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
@@ -41295,7 +41375,7 @@
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 02:41:52</t>
+          <t>2026-05-23 17:41:52</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
@@ -41357,7 +41437,7 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 23:19:04</t>
+          <t>2026-05-23 14:19:04</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
@@ -41419,7 +41499,7 @@
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 22:43:20</t>
+          <t>2026-05-23 13:43:20</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
@@ -41481,7 +41561,7 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 15:54:19</t>
+          <t>2026-05-23 06:54:19</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
@@ -41543,7 +41623,7 @@
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 02:25:24</t>
+          <t>2026-05-22 17:25:24</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
@@ -41605,7 +41685,7 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 01:29:23</t>
+          <t>2026-05-21 16:29:23</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
@@ -41667,7 +41747,7 @@
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 00:48:49</t>
+          <t>2026-05-21 15:48:49</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
@@ -41729,7 +41809,7 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:45</t>
+          <t>2026-05-21 15:00:45</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
@@ -41791,7 +41871,7 @@
     <row r="127">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 23:22:44</t>
+          <t>2026-05-21 14:22:44</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
@@ -41853,7 +41933,7 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 00:05:15</t>
+          <t>2026-05-20 15:05:15</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
@@ -41915,7 +41995,7 @@
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 23:43:50</t>
+          <t>2026-05-20 14:43:50</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
@@ -41977,7 +42057,7 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 22:57:45</t>
+          <t>2026-05-20 13:57:45</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
@@ -42039,7 +42119,7 @@
     <row r="131">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 01:25:45</t>
+          <t>2026-05-19 16:25:45</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
@@ -42101,7 +42181,7 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 00:46:42</t>
+          <t>2026-05-19 15:46:42</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
@@ -42163,7 +42243,7 @@
     <row r="133">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>2026-05-18 22:56:39</t>
+          <t>2026-05-18 13:56:39</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
@@ -42225,7 +42305,7 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 01:35:56</t>
+          <t>2026-05-14 16:35:56</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
@@ -42287,7 +42367,7 @@
     <row r="135">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 01:17:05</t>
+          <t>2026-05-14 16:17:05</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
@@ -42349,7 +42429,7 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 00:05:48</t>
+          <t>2026-05-14 15:05:48</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
@@ -42411,7 +42491,7 @@
     <row r="137">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>2026-05-14 01:25:38</t>
+          <t>2026-05-13 16:25:38</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
@@ -42473,7 +42553,7 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>2026-05-12 00:19:57</t>
+          <t>2026-05-11 15:19:57</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
@@ -42535,7 +42615,7 @@
     <row r="139">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 23:54:15</t>
+          <t>2026-05-11 14:54:15</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
@@ -42597,7 +42677,7 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 23:14:30</t>
+          <t>2026-05-11 14:14:30</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
@@ -42659,7 +42739,7 @@
     <row r="141">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 22:37:05</t>
+          <t>2026-05-11 13:37:05</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
@@ -42721,7 +42801,7 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 21:53:13</t>
+          <t>2026-05-11 12:53:13</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
@@ -42783,7 +42863,7 @@
     <row r="143">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 00:04:01</t>
+          <t>2026-05-10 15:04:01</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
@@ -42845,7 +42925,7 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:54:24</t>
+          <t>2026-05-09 16:54:24</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
@@ -42907,7 +42987,7 @@
     <row r="145">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:22:50</t>
+          <t>2026-05-09 16:22:50</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
@@ -42969,7 +43049,7 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 00:26:16</t>
+          <t>2026-05-09 15:26:16</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
@@ -43031,7 +43111,7 @@
     <row r="147">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 23:38:30</t>
+          <t>2026-05-09 14:38:30</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
@@ -43093,7 +43173,7 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 22:50:20</t>
+          <t>2026-05-09 13:50:20</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
@@ -43155,7 +43235,7 @@
     <row r="149">
       <c r="A149" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 22:13:25</t>
+          <t>2026-05-09 13:13:25</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
@@ -43217,7 +43297,7 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 20:00:11</t>
+          <t>2026-05-09 11:00:11</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
@@ -43279,7 +43359,7 @@
     <row r="151">
       <c r="A151" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 19:10:28</t>
+          <t>2026-05-09 10:10:28</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
@@ -43341,7 +43421,7 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 02:17:27</t>
+          <t>2026-05-08 17:17:27</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
@@ -43403,7 +43483,7 @@
     <row r="153">
       <c r="A153" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 01:38:25</t>
+          <t>2026-05-08 16:38:25</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
@@ -43465,7 +43545,7 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 00:58:58</t>
+          <t>2026-05-08 15:58:58</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
@@ -43527,7 +43607,7 @@
     <row r="155">
       <c r="A155" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 00:37:55</t>
+          <t>2026-05-08 15:37:55</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
@@ -43589,7 +43669,7 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 01:48:31</t>
+          <t>2026-05-07 16:48:31</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
@@ -43651,7 +43731,7 @@
     <row r="157">
       <c r="A157" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 01:02:52</t>
+          <t>2026-05-07 16:02:52</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
@@ -43713,7 +43793,7 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 00:23:29</t>
+          <t>2026-05-07 15:23:29</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
@@ -43775,7 +43855,7 @@
     <row r="159">
       <c r="A159" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 01:30:56</t>
+          <t>2026-05-06 16:30:56</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
@@ -43837,7 +43917,7 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 00:42:16</t>
+          <t>2026-05-06 15:42:16</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
@@ -43899,7 +43979,7 @@
     <row r="161">
       <c r="A161" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 23:44:04</t>
+          <t>2026-05-06 14:44:04</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
@@ -43961,7 +44041,7 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:13:52</t>
+          <t>2026-05-06 09:13:52</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
@@ -44023,7 +44103,7 @@
     <row r="163">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:05:08</t>
+          <t>2026-05-06 09:05:08</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
@@ -44085,7 +44165,7 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 17:22:30</t>
+          <t>2026-05-06 08:22:30</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
@@ -44147,7 +44227,7 @@
     <row r="165">
       <c r="A165" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 16:28:42</t>
+          <t>2026-05-06 07:28:42</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
@@ -44209,7 +44289,7 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 03:16:57</t>
+          <t>2026-05-05 18:16:57</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
@@ -44271,7 +44351,7 @@
     <row r="167">
       <c r="A167" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:32:40</t>
+          <t>2026-05-05 17:32:40</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
@@ -44333,7 +44413,7 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:23:28</t>
+          <t>2026-05-05 17:23:28</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
@@ -44395,7 +44475,7 @@
     <row r="169">
       <c r="A169" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 01:48:28</t>
+          <t>2026-05-05 16:48:28</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
@@ -44457,7 +44537,7 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 00:52:33</t>
+          <t>2026-05-05 15:52:33</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
@@ -44519,7 +44599,7 @@
     <row r="171">
       <c r="A171" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 17:43:06</t>
+          <t>2026-05-05 08:43:06</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
@@ -44581,7 +44661,7 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>2026-05-03 00:36:42</t>
+          <t>2026-05-02 15:36:42</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
@@ -44643,7 +44723,7 @@
     <row r="173">
       <c r="A173" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 23:51:09</t>
+          <t>2026-05-02 14:51:09</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
@@ -44705,7 +44785,7 @@
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 22:15:10</t>
+          <t>2026-05-02 13:15:10</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
@@ -44767,7 +44847,7 @@
     <row r="175">
       <c r="A175" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 21:29:49</t>
+          <t>2026-05-02 12:29:49</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
@@ -44829,7 +44909,7 @@
     <row r="176">
       <c r="A176" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 01:39:42</t>
+          <t>2026-04-30 16:39:42</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
@@ -44891,7 +44971,7 @@
     <row r="177">
       <c r="A177" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 01:01:34</t>
+          <t>2026-04-30 16:01:34</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
@@ -44953,7 +45033,7 @@
     <row r="178">
       <c r="A178" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 00:24:48</t>
+          <t>2026-04-30 15:24:48</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
@@ -45015,7 +45095,7 @@
     <row r="179">
       <c r="A179" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 23:37:10</t>
+          <t>2026-04-30 14:37:10</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
@@ -45077,7 +45157,7 @@
     <row r="180">
       <c r="A180" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 22:58:06</t>
+          <t>2026-04-30 13:58:06</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
@@ -45139,7 +45219,7 @@
     <row r="181">
       <c r="A181" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 03:29:33</t>
+          <t>2026-04-29 18:29:33</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
@@ -45201,7 +45281,7 @@
     <row r="182">
       <c r="A182" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 02:54:07</t>
+          <t>2026-04-29 17:54:07</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
@@ -45263,7 +45343,7 @@
     <row r="183">
       <c r="A183" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 02:20:58</t>
+          <t>2026-04-29 17:20:58</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
@@ -45325,7 +45405,7 @@
     <row r="184">
       <c r="A184" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 01:42:01</t>
+          <t>2026-04-29 16:42:01</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
@@ -45387,7 +45467,7 @@
     <row r="185">
       <c r="A185" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 01:03:17</t>
+          <t>2026-04-29 16:03:17</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
@@ -45449,7 +45529,7 @@
     <row r="186">
       <c r="A186" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 00:19:47</t>
+          <t>2026-04-29 15:19:47</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
@@ -45511,7 +45591,7 @@
     <row r="187">
       <c r="A187" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 23:29:53</t>
+          <t>2026-04-29 14:29:53</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
@@ -45573,7 +45653,7 @@
     <row r="188">
       <c r="A188" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:59:49</t>
+          <t>2026-04-29 13:59:49</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
@@ -45635,7 +45715,7 @@
     <row r="189">
       <c r="A189" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:38:22</t>
+          <t>2026-04-29 13:38:22</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
@@ -45697,7 +45777,7 @@
     <row r="190">
       <c r="A190" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:44</t>
+          <t>2026-04-29 13:17:44</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
@@ -45759,7 +45839,7 @@
     <row r="191">
       <c r="A191" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 03:28:56</t>
+          <t>2026-04-28 18:28:56</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
@@ -45821,7 +45901,7 @@
     <row r="192">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:58:50</t>
+          <t>2026-04-28 17:58:50</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
@@ -45883,7 +45963,7 @@
     <row r="193">
       <c r="A193" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:29:43</t>
+          <t>2026-04-28 17:29:43</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
@@ -45945,7 +46025,7 @@
     <row r="194">
       <c r="A194" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 01:38:43</t>
+          <t>2026-04-28 16:38:43</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
@@ -46007,7 +46087,7 @@
     <row r="195">
       <c r="A195" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:54</t>
+          <t>2026-04-28 15:58:54</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
@@ -46069,7 +46149,7 @@
     <row r="196">
       <c r="A196" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:31:32</t>
+          <t>2026-04-28 15:31:32</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
@@ -46131,7 +46211,7 @@
     <row r="197">
       <c r="A197" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:04:20</t>
+          <t>2026-04-28 15:04:20</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
@@ -46193,7 +46273,7 @@
     <row r="198">
       <c r="A198" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 23:37:27</t>
+          <t>2026-04-28 14:37:27</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
@@ -46255,7 +46335,7 @@
     <row r="199">
       <c r="A199" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 23:09:10</t>
+          <t>2026-04-28 14:09:10</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
@@ -46317,7 +46397,7 @@
     <row r="200">
       <c r="A200" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:59:25</t>
+          <t>2026-04-27 14:59:25</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
@@ -46379,7 +46459,7 @@
     <row r="201">
       <c r="A201" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:49:35</t>
+          <t>2026-04-27 14:49:35</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
@@ -46441,7 +46521,7 @@
     <row r="202">
       <c r="A202" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 22:55:34</t>
+          <t>2026-04-27 13:55:34</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
@@ -46503,7 +46583,7 @@
     <row r="203">
       <c r="A203" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 22:04:13</t>
+          <t>2026-04-27 13:04:13</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
@@ -46565,7 +46645,7 @@
     <row r="204">
       <c r="A204" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 02:49:02</t>
+          <t>2026-04-24 17:49:02</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
@@ -46627,7 +46707,7 @@
     <row r="205">
       <c r="A205" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 02:03:56</t>
+          <t>2026-04-24 17:03:56</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
@@ -46689,7 +46769,7 @@
     <row r="206">
       <c r="A206" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 01:37:00</t>
+          <t>2026-04-24 16:37:00</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
@@ -46751,7 +46831,7 @@
     <row r="207">
       <c r="A207" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:33:59</t>
+          <t>2026-04-23 15:33:59</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
@@ -46813,7 +46893,7 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:22:46</t>
+          <t>2026-04-23 15:22:46</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
@@ -46875,7 +46955,7 @@
     <row r="209">
       <c r="A209" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:12:54</t>
+          <t>2026-04-23 15:12:54</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
@@ -46937,7 +47017,7 @@
     <row r="210">
       <c r="A210" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 22:36:03</t>
+          <t>2026-04-23 13:36:03</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
@@ -46999,7 +47079,7 @@
     <row r="211">
       <c r="A211" s="13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:58:57</t>
+          <t>2026-04-13 15:58:57</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
@@ -47061,7 +47141,7 @@
     <row r="212">
       <c r="A212" s="13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:09:08</t>
+          <t>2026-04-13 15:09:08</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
@@ -47123,7 +47203,7 @@
     <row r="213">
       <c r="A213" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 01:48:02</t>
+          <t>2026-04-12 16:48:02</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
@@ -47185,7 +47265,7 @@
     <row r="214">
       <c r="A214" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 01:17:58</t>
+          <t>2026-04-12 16:17:58</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
@@ -47247,7 +47327,7 @@
     <row r="215">
       <c r="A215" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 00:41:20</t>
+          <t>2026-04-12 15:41:20</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
@@ -47309,7 +47389,7 @@
     <row r="216">
       <c r="A216" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 23:18:06</t>
+          <t>2026-04-09 14:18:06</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
@@ -47371,7 +47451,7 @@
     <row r="217">
       <c r="A217" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 22:52:44</t>
+          <t>2026-04-09 13:52:44</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
@@ -47433,7 +47513,7 @@
     <row r="218">
       <c r="A218" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 22:27:45</t>
+          <t>2026-04-09 13:27:45</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
@@ -47495,7 +47575,7 @@
     <row r="219">
       <c r="A219" s="13" t="inlineStr">
         <is>
-          <t>2026-04-08 01:10:31</t>
+          <t>2026-04-07 16:10:31</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
@@ -47557,7 +47637,7 @@
     <row r="220">
       <c r="A220" s="13" t="inlineStr">
         <is>
-          <t>2026-04-08 00:29:19</t>
+          <t>2026-04-07 15:29:19</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
@@ -47619,7 +47699,7 @@
     <row r="221">
       <c r="A221" s="13" t="inlineStr">
         <is>
-          <t>2026-04-04 04:36:31</t>
+          <t>2026-04-03 19:36:31</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
@@ -47681,7 +47761,7 @@
     <row r="222">
       <c r="A222" s="13" t="inlineStr">
         <is>
-          <t>2026-04-04 04:16:32</t>
+          <t>2026-04-03 19:16:32</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
@@ -47743,7 +47823,7 @@
     <row r="223">
       <c r="A223" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 04:24:43</t>
+          <t>2026-03-27 19:24:43</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
@@ -47805,7 +47885,7 @@
     <row r="224">
       <c r="A224" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:38:31</t>
+          <t>2026-03-27 18:38:31</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
@@ -47867,7 +47947,7 @@
     <row r="225">
       <c r="A225" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:17:50</t>
+          <t>2026-03-27 18:17:50</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
@@ -47929,7 +48009,7 @@
     <row r="226">
       <c r="A226" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 02:43:19</t>
+          <t>2026-03-27 17:43:19</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
@@ -47991,7 +48071,7 @@
     <row r="227">
       <c r="A227" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 02:15:18</t>
+          <t>2026-03-27 17:15:18</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
@@ -48053,7 +48133,7 @@
     <row r="228">
       <c r="A228" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 23:18:12</t>
+          <t>2026-03-25 14:18:12</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
@@ -48115,7 +48195,7 @@
     <row r="229">
       <c r="A229" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 00:01:49</t>
+          <t>2026-03-24 15:01:49</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
@@ -48177,7 +48257,7 @@
     <row r="230">
       <c r="A230" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 23:25:16</t>
+          <t>2026-03-24 14:25:16</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
@@ -48239,7 +48319,7 @@
     <row r="231">
       <c r="A231" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 23:02:52</t>
+          <t>2026-03-24 14:02:52</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
@@ -48301,7 +48381,7 @@
     <row r="232">
       <c r="A232" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 22:26:26</t>
+          <t>2026-03-24 13:26:26</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
@@ -48363,7 +48443,7 @@
     <row r="233">
       <c r="A233" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 00:56:18</t>
+          <t>2026-03-23 15:56:18</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
@@ -48425,7 +48505,7 @@
     <row r="234">
       <c r="A234" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 00:29:29</t>
+          <t>2026-03-23 15:29:29</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
@@ -48487,7 +48567,7 @@
     <row r="235">
       <c r="A235" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 23:51:11</t>
+          <t>2026-03-22 14:51:11</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
@@ -48549,7 +48629,7 @@
     <row r="236">
       <c r="A236" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 01:04:36</t>
+          <t>2026-03-21 16:04:36</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
@@ -48611,7 +48691,7 @@
     <row r="237">
       <c r="A237" s="13" t="inlineStr">
         <is>
-          <t>2026-03-21 02:55:49</t>
+          <t>2026-03-20 17:55:49</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
@@ -48673,7 +48753,7 @@
     <row r="238">
       <c r="A238" s="13" t="inlineStr">
         <is>
-          <t>2026-03-18 00:07:07</t>
+          <t>2026-03-17 15:07:07</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
@@ -48735,7 +48815,7 @@
     <row r="239">
       <c r="A239" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 23:24:05</t>
+          <t>2026-03-17 14:24:05</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
@@ -48797,7 +48877,7 @@
     <row r="240">
       <c r="A240" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 02:00:50</t>
+          <t>2026-03-16 17:00:50</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
@@ -48859,7 +48939,7 @@
     <row r="241">
       <c r="A241" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 01:33:08</t>
+          <t>2026-03-16 16:33:08</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
@@ -48921,7 +49001,7 @@
     <row r="242">
       <c r="A242" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 23:28:09</t>
+          <t>2026-03-16 14:28:09</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
@@ -48983,7 +49063,7 @@
     <row r="243">
       <c r="A243" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 01:32:22</t>
+          <t>2026-03-15 16:32:22</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
@@ -49045,7 +49125,7 @@
     <row r="244">
       <c r="A244" s="13" t="inlineStr">
         <is>
-          <t>2026-03-14 01:43:49</t>
+          <t>2026-03-13 16:43:49</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
@@ -49107,7 +49187,7 @@
     <row r="245">
       <c r="A245" s="13" t="inlineStr">
         <is>
-          <t>2026-03-14 01:19:35</t>
+          <t>2026-03-13 16:19:35</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
@@ -49169,7 +49249,7 @@
     <row r="246">
       <c r="A246" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 23:45:27</t>
+          <t>2026-03-12 14:45:27</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
@@ -49231,7 +49311,7 @@
     <row r="247">
       <c r="A247" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 23:02:09</t>
+          <t>2026-03-12 14:02:09</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
@@ -49293,7 +49373,7 @@
     <row r="248">
       <c r="A248" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 22:42:59</t>
+          <t>2026-03-12 13:42:59</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
@@ -49355,7 +49435,7 @@
     <row r="249">
       <c r="A249" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 01:39:10</t>
+          <t>2026-03-11 16:39:10</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
@@ -49417,7 +49497,7 @@
     <row r="250">
       <c r="A250" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:43:21</t>
+          <t>2026-03-11 15:43:21</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
@@ -49479,7 +49559,7 @@
     <row r="251">
       <c r="A251" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:04:25</t>
+          <t>2026-03-11 15:04:25</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
@@ -49541,7 +49621,7 @@
     <row r="252">
       <c r="A252" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 22:54:02</t>
+          <t>2026-03-11 13:54:02</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
@@ -49603,7 +49683,7 @@
     <row r="253">
       <c r="A253" s="13" t="inlineStr">
         <is>
-          <t>2026-03-08 02:01:53</t>
+          <t>2026-03-07 17:01:53</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
@@ -49665,7 +49745,7 @@
     <row r="254">
       <c r="A254" s="13" t="inlineStr">
         <is>
-          <t>2026-03-02 02:18:59</t>
+          <t>2026-03-01 17:18:59</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
@@ -49727,7 +49807,7 @@
     <row r="255">
       <c r="A255" s="13" t="inlineStr">
         <is>
-          <t>2026-02-24 01:40:38</t>
+          <t>2026-02-23 16:40:38</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
@@ -49789,7 +49869,7 @@
     <row r="256">
       <c r="A256" s="13" t="inlineStr">
         <is>
-          <t>2026-02-24 00:10:31</t>
+          <t>2026-02-23 15:10:31</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
@@ -49851,7 +49931,7 @@
     <row r="257">
       <c r="A257" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 23:33:47</t>
+          <t>2026-02-23 14:33:47</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
@@ -49913,7 +49993,7 @@
     <row r="258">
       <c r="A258" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 22:40:54</t>
+          <t>2026-02-23 13:40:54</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
@@ -49975,7 +50055,7 @@
     <row r="259">
       <c r="A259" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 21:58:56</t>
+          <t>2026-02-23 12:58:56</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
@@ -50037,7 +50117,7 @@
     <row r="260">
       <c r="A260" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 19:21:48</t>
+          <t>2026-02-23 10:21:48</t>
         </is>
       </c>
       <c r="B260" s="13" t="inlineStr">
@@ -50099,7 +50179,7 @@
     <row r="261">
       <c r="A261" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 17:17:13</t>
+          <t>2026-02-23 08:17:13</t>
         </is>
       </c>
       <c r="B261" s="13" t="inlineStr">
@@ -50161,7 +50241,7 @@
     <row r="262">
       <c r="A262" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 04:22:01</t>
+          <t>2026-02-22 19:22:01</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
@@ -50223,7 +50303,7 @@
     <row r="263">
       <c r="A263" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 03:23:51</t>
+          <t>2026-02-22 18:23:51</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
@@ -50285,7 +50365,7 @@
     <row r="264">
       <c r="A264" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 02:58:18</t>
+          <t>2026-02-22 17:58:18</t>
         </is>
       </c>
       <c r="B264" s="13" t="inlineStr">
@@ -50347,7 +50427,7 @@
     <row r="265">
       <c r="A265" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 02:29:21</t>
+          <t>2026-02-22 17:29:21</t>
         </is>
       </c>
       <c r="B265" s="13" t="inlineStr">
@@ -50409,7 +50489,7 @@
     <row r="266">
       <c r="A266" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 01:59:09</t>
+          <t>2026-02-22 16:59:09</t>
         </is>
       </c>
       <c r="B266" s="13" t="inlineStr">
@@ -50471,7 +50551,7 @@
     <row r="267">
       <c r="A267" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 01:32:08</t>
+          <t>2026-02-22 16:32:08</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
@@ -50533,7 +50613,7 @@
     <row r="268">
       <c r="A268" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 03:34:36</t>
+          <t>2026-02-20 18:34:36</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
@@ -50595,7 +50675,7 @@
     <row r="269">
       <c r="A269" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 02:57:13</t>
+          <t>2026-02-20 17:57:13</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
@@ -50657,7 +50737,7 @@
     <row r="270">
       <c r="A270" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 02:19:01</t>
+          <t>2026-02-20 17:19:01</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
@@ -50719,7 +50799,7 @@
     <row r="271">
       <c r="A271" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 01:41:10</t>
+          <t>2026-02-20 16:41:10</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
@@ -50781,7 +50861,7 @@
     <row r="272">
       <c r="A272" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 00:57:47</t>
+          <t>2026-02-20 15:57:47</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
@@ -50843,7 +50923,7 @@
     <row r="273">
       <c r="A273" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 00:39:52</t>
+          <t>2026-02-20 15:39:52</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
@@ -50905,7 +50985,7 @@
     <row r="274">
       <c r="A274" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 01:21:13</t>
+          <t>2026-02-19 16:21:13</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
@@ -50967,7 +51047,7 @@
     <row r="275">
       <c r="A275" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 00:33:10</t>
+          <t>2026-02-19 15:33:10</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
@@ -51029,7 +51109,7 @@
     <row r="276">
       <c r="A276" s="13" t="inlineStr">
         <is>
-          <t>2026-02-18 00:37:38</t>
+          <t>2026-02-17 15:37:38</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
@@ -51091,7 +51171,7 @@
     <row r="277">
       <c r="A277" s="13" t="inlineStr">
         <is>
-          <t>2026-02-17 23:58:39</t>
+          <t>2026-02-17 14:58:39</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
@@ -51153,7 +51233,7 @@
     <row r="278">
       <c r="A278" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 02:24:16</t>
+          <t>2026-02-15 17:24:16</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
@@ -51215,7 +51295,7 @@
     <row r="279">
       <c r="A279" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 01:47:19</t>
+          <t>2026-02-15 16:47:19</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
@@ -51277,7 +51357,7 @@
     <row r="280">
       <c r="A280" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 00:56:43</t>
+          <t>2026-02-15 15:56:43</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
@@ -51339,7 +51419,7 @@
     <row r="281">
       <c r="A281" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 00:26:20</t>
+          <t>2026-02-15 15:26:20</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
@@ -51401,7 +51481,7 @@
     <row r="282">
       <c r="A282" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 23:48:44</t>
+          <t>2026-02-15 14:48:44</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
@@ -51463,7 +51543,7 @@
     <row r="283">
       <c r="A283" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 04:17:17</t>
+          <t>2026-02-14 19:17:17</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
@@ -51525,7 +51605,7 @@
     <row r="284">
       <c r="A284" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 03:53:01</t>
+          <t>2026-02-14 18:53:01</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
@@ -51587,7 +51667,7 @@
     <row r="285">
       <c r="A285" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:59:46</t>
+          <t>2026-02-14 17:59:46</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
@@ -51649,7 +51729,7 @@
     <row r="286">
       <c r="A286" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:26:42</t>
+          <t>2026-02-14 17:26:42</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
@@ -51711,7 +51791,7 @@
     <row r="287">
       <c r="A287" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:00:09</t>
+          <t>2026-02-14 17:00:09</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
@@ -51773,7 +51853,7 @@
     <row r="288">
       <c r="A288" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 01:39:16</t>
+          <t>2026-02-14 16:39:16</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
@@ -51835,7 +51915,7 @@
     <row r="289">
       <c r="A289" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 00:56:51</t>
+          <t>2026-02-14 15:56:51</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
@@ -51897,7 +51977,7 @@
     <row r="290">
       <c r="A290" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 23:52:26</t>
+          <t>2026-02-14 14:52:26</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
@@ -51959,7 +52039,7 @@
     <row r="291">
       <c r="A291" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 23:14:55</t>
+          <t>2026-02-14 14:14:55</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
@@ -52021,7 +52101,7 @@
     <row r="292">
       <c r="A292" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 04:19:58</t>
+          <t>2026-02-13 19:19:58</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
@@ -52083,7 +52163,7 @@
     <row r="293">
       <c r="A293" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 03:37:53</t>
+          <t>2026-02-13 18:37:53</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
@@ -52145,7 +52225,7 @@
     <row r="294">
       <c r="A294" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 03:03:31</t>
+          <t>2026-02-13 18:03:31</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
@@ -52207,7 +52287,7 @@
     <row r="295">
       <c r="A295" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 02:08:36</t>
+          <t>2026-02-13 17:08:36</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
@@ -52269,7 +52349,7 @@
     <row r="296">
       <c r="A296" s="13" t="inlineStr">
         <is>
-          <t>2026-02-12 00:20:03</t>
+          <t>2026-02-11 15:20:03</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
@@ -52331,7 +52411,7 @@
     <row r="297">
       <c r="A297" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 03:05:03</t>
+          <t>2026-02-10 18:05:03</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
@@ -52393,7 +52473,7 @@
     <row r="298">
       <c r="A298" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 02:14:02</t>
+          <t>2026-02-10 17:14:02</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
@@ -52455,7 +52535,7 @@
     <row r="299">
       <c r="A299" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 01:33:21</t>
+          <t>2026-02-10 16:33:21</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
@@ -52517,7 +52597,7 @@
     <row r="300">
       <c r="A300" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 01:01:41</t>
+          <t>2026-02-10 16:01:41</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
@@ -52579,7 +52659,7 @@
     <row r="301">
       <c r="A301" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 01:49:32</t>
+          <t>2026-02-09 16:49:32</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
@@ -52641,7 +52721,7 @@
     <row r="302">
       <c r="A302" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 01:42:29</t>
+          <t>2026-02-09 16:42:29</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
@@ -52703,7 +52783,7 @@
     <row r="303">
       <c r="A303" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 23:44:10</t>
+          <t>2026-02-09 14:44:10</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
@@ -52765,7 +52845,7 @@
     <row r="304">
       <c r="A304" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 23:00:28</t>
+          <t>2026-02-09 14:00:28</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
@@ -52827,7 +52907,7 @@
     <row r="305">
       <c r="A305" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 00:27:49</t>
+          <t>2026-02-08 15:27:49</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
@@ -52889,7 +52969,7 @@
     <row r="306">
       <c r="A306" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 00:16:42</t>
+          <t>2026-02-08 15:16:42</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
@@ -52951,7 +53031,7 @@
     <row r="307">
       <c r="A307" s="13" t="inlineStr">
         <is>
-          <t>2026-02-08 04:04:43</t>
+          <t>2026-02-07 19:04:43</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
@@ -53013,7 +53093,7 @@
     <row r="308">
       <c r="A308" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 03:13:11</t>
+          <t>2026-02-06 18:13:11</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
@@ -53075,7 +53155,7 @@
     <row r="309">
       <c r="A309" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 02:19:42</t>
+          <t>2026-02-06 17:19:42</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
@@ -53137,7 +53217,7 @@
     <row r="310">
       <c r="A310" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 01:37:36</t>
+          <t>2026-02-06 16:37:36</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
@@ -53199,7 +53279,7 @@
     <row r="311">
       <c r="A311" s="13" t="inlineStr">
         <is>
-          <t>2026-02-03 23:04:49</t>
+          <t>2026-02-03 14:04:49</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
@@ -53261,7 +53341,7 @@
     <row r="312">
       <c r="A312" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 23:21:38</t>
+          <t>2026-02-02 14:21:38</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
@@ -53323,7 +53403,7 @@
     <row r="313">
       <c r="A313" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 03:08:17</t>
+          <t>2026-02-01 18:08:17</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
@@ -53385,7 +53465,7 @@
     <row r="314">
       <c r="A314" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 02:41:55</t>
+          <t>2026-02-01 17:41:55</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
@@ -53447,7 +53527,7 @@
     <row r="315">
       <c r="A315" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 02:09:57</t>
+          <t>2026-02-01 17:09:57</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
@@ -53509,7 +53589,7 @@
     <row r="316">
       <c r="A316" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 01:41:49</t>
+          <t>2026-02-01 16:41:49</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
@@ -53571,7 +53651,7 @@
     <row r="317">
       <c r="A317" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 02:22:13</t>
+          <t>2026-01-31 17:22:13</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
@@ -53633,7 +53713,7 @@
     <row r="318">
       <c r="A318" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 01:20:54</t>
+          <t>2026-01-31 16:20:54</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
@@ -53695,7 +53775,7 @@
     <row r="319">
       <c r="A319" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 01:09:32</t>
+          <t>2026-01-31 16:09:32</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
@@ -53757,7 +53837,7 @@
     <row r="320">
       <c r="A320" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 00:29:37</t>
+          <t>2026-01-31 15:29:37</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
@@ -53819,7 +53899,7 @@
     <row r="321">
       <c r="A321" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 00:03:50</t>
+          <t>2026-01-31 15:03:50</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
@@ -53881,7 +53961,7 @@
     <row r="322">
       <c r="A322" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 23:15:28</t>
+          <t>2026-01-31 14:15:28</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
@@ -53943,7 +54023,7 @@
     <row r="323">
       <c r="A323" s="13" t="inlineStr">
         <is>
-          <t>2026-01-29 00:36:39</t>
+          <t>2026-01-28 15:36:39</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
@@ -54005,7 +54085,7 @@
     <row r="324">
       <c r="A324" s="13" t="inlineStr">
         <is>
-          <t>2026-01-29 00:02:45</t>
+          <t>2026-01-28 15:02:45</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
@@ -54067,7 +54147,7 @@
     <row r="325">
       <c r="A325" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 23:26:47</t>
+          <t>2026-01-28 14:26:47</t>
         </is>
       </c>
       <c r="B325" s="13" t="inlineStr">
@@ -54129,7 +54209,7 @@
     <row r="326">
       <c r="A326" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 23:04:33</t>
+          <t>2026-01-28 14:04:33</t>
         </is>
       </c>
       <c r="B326" s="13" t="inlineStr">
@@ -54191,7 +54271,7 @@
     <row r="327">
       <c r="A327" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 00:33:31</t>
+          <t>2026-01-27 15:33:31</t>
         </is>
       </c>
       <c r="B327" s="13" t="inlineStr">
@@ -54253,7 +54333,7 @@
     <row r="328">
       <c r="A328" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 23:59:21</t>
+          <t>2026-01-27 14:59:21</t>
         </is>
       </c>
       <c r="B328" s="13" t="inlineStr">
@@ -54315,7 +54395,7 @@
     <row r="329">
       <c r="A329" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 23:08:33</t>
+          <t>2026-01-27 14:08:33</t>
         </is>
       </c>
       <c r="B329" s="13" t="inlineStr">
@@ -54377,7 +54457,7 @@
     <row r="330">
       <c r="A330" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 23:28:17</t>
+          <t>2026-01-25 14:28:17</t>
         </is>
       </c>
       <c r="B330" s="13" t="inlineStr">
@@ -54439,7 +54519,7 @@
     <row r="331">
       <c r="A331" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 22:56:22</t>
+          <t>2026-01-25 13:56:22</t>
         </is>
       </c>
       <c r="B331" s="13" t="inlineStr">
@@ -54501,7 +54581,7 @@
     <row r="332">
       <c r="A332" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 22:28:25</t>
+          <t>2026-01-25 13:28:25</t>
         </is>
       </c>
       <c r="B332" s="13" t="inlineStr">
@@ -54563,7 +54643,7 @@
     <row r="333">
       <c r="A333" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 21:42:03</t>
+          <t>2026-01-25 12:42:03</t>
         </is>
       </c>
       <c r="B333" s="13" t="inlineStr">
@@ -54625,7 +54705,7 @@
     <row r="334">
       <c r="A334" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 19:38:23</t>
+          <t>2026-01-25 10:38:23</t>
         </is>
       </c>
       <c r="B334" s="13" t="inlineStr">
@@ -54687,7 +54767,7 @@
     <row r="335">
       <c r="A335" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 18:56:35</t>
+          <t>2026-01-25 09:56:35</t>
         </is>
       </c>
       <c r="B335" s="13" t="inlineStr">
@@ -54749,7 +54829,7 @@
     <row r="336">
       <c r="A336" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 18:29:19</t>
+          <t>2026-01-25 09:29:19</t>
         </is>
       </c>
       <c r="B336" s="13" t="inlineStr">
@@ -54811,7 +54891,7 @@
     <row r="337">
       <c r="A337" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 17:14:05</t>
+          <t>2026-01-25 08:14:05</t>
         </is>
       </c>
       <c r="B337" s="13" t="inlineStr">
@@ -54873,7 +54953,7 @@
     <row r="338">
       <c r="A338" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 02:47:24</t>
+          <t>2026-01-23 17:47:24</t>
         </is>
       </c>
       <c r="B338" s="13" t="inlineStr">
@@ -54935,7 +55015,7 @@
     <row r="339">
       <c r="A339" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 02:12:26</t>
+          <t>2026-01-23 17:12:26</t>
         </is>
       </c>
       <c r="B339" s="13" t="inlineStr">
@@ -54997,7 +55077,7 @@
     <row r="340">
       <c r="A340" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 01:33:34</t>
+          <t>2026-01-23 16:33:34</t>
         </is>
       </c>
       <c r="B340" s="13" t="inlineStr">
@@ -55059,7 +55139,7 @@
     <row r="341">
       <c r="A341" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 01:00:39</t>
+          <t>2026-01-23 16:00:39</t>
         </is>
       </c>
       <c r="B341" s="13" t="inlineStr">
@@ -55121,7 +55201,7 @@
     <row r="342">
       <c r="A342" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 00:19:07</t>
+          <t>2026-01-23 15:19:07</t>
         </is>
       </c>
       <c r="B342" s="13" t="inlineStr">
@@ -55183,7 +55263,7 @@
     <row r="343">
       <c r="A343" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 23:52:33</t>
+          <t>2026-01-23 14:52:33</t>
         </is>
       </c>
       <c r="B343" s="13" t="inlineStr">
@@ -55245,7 +55325,7 @@
     <row r="344">
       <c r="A344" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 23:19:19</t>
+          <t>2026-01-23 14:19:19</t>
         </is>
       </c>
       <c r="B344" s="13" t="inlineStr">
@@ -55307,7 +55387,7 @@
     <row r="345">
       <c r="A345" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36:59</t>
+          <t>2026-01-23 13:36:59</t>
         </is>
       </c>
       <c r="B345" s="13" t="inlineStr">
@@ -55369,7 +55449,7 @@
     <row r="346">
       <c r="A346" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 03:01:58</t>
+          <t>2026-01-22 18:01:58</t>
         </is>
       </c>
       <c r="B346" s="13" t="inlineStr">
@@ -55431,7 +55511,7 @@
     <row r="347">
       <c r="A347" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 02:25:41</t>
+          <t>2026-01-22 17:25:41</t>
         </is>
       </c>
       <c r="B347" s="13" t="inlineStr">
@@ -55493,7 +55573,7 @@
     <row r="348">
       <c r="A348" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 00:32:45</t>
+          <t>2026-01-22 15:32:45</t>
         </is>
       </c>
       <c r="B348" s="13" t="inlineStr">
@@ -55555,7 +55635,7 @@
     <row r="349">
       <c r="A349" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 23:54:46</t>
+          <t>2026-01-22 14:54:46</t>
         </is>
       </c>
       <c r="B349" s="13" t="inlineStr">
@@ -55617,7 +55697,7 @@
     <row r="350">
       <c r="A350" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 23:17:42</t>
+          <t>2026-01-22 14:17:42</t>
         </is>
       </c>
       <c r="B350" s="13" t="inlineStr">
@@ -55679,7 +55759,7 @@
     <row r="351">
       <c r="A351" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 01:10:08</t>
+          <t>2026-01-21 16:10:08</t>
         </is>
       </c>
       <c r="B351" s="13" t="inlineStr">
@@ -55741,7 +55821,7 @@
     <row r="352">
       <c r="A352" s="13" t="inlineStr">
         <is>
-          <t>2026-01-21 00:27:51</t>
+          <t>2026-01-20 15:27:51</t>
         </is>
       </c>
       <c r="B352" s="13" t="inlineStr">
@@ -55803,7 +55883,7 @@
     <row r="353">
       <c r="A353" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 23:25:34</t>
+          <t>2026-01-20 14:25:34</t>
         </is>
       </c>
       <c r="B353" s="13" t="inlineStr">
@@ -55865,7 +55945,7 @@
     <row r="354">
       <c r="A354" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 22:56:13</t>
+          <t>2026-01-20 13:56:13</t>
         </is>
       </c>
       <c r="B354" s="13" t="inlineStr">
@@ -55927,7 +56007,7 @@
     <row r="355">
       <c r="A355" s="13" t="inlineStr">
         <is>
-          <t>2026-01-19 01:59:11</t>
+          <t>2026-01-18 16:59:11</t>
         </is>
       </c>
       <c r="B355" s="13" t="inlineStr">
@@ -55989,7 +56069,7 @@
     <row r="356">
       <c r="A356" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 03:05:32</t>
+          <t>2026-01-17 18:05:32</t>
         </is>
       </c>
       <c r="B356" s="13" t="inlineStr">
@@ -56051,7 +56131,7 @@
     <row r="357">
       <c r="A357" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 02:19:17</t>
+          <t>2026-01-17 17:19:17</t>
         </is>
       </c>
       <c r="B357" s="13" t="inlineStr">
@@ -56113,7 +56193,7 @@
     <row r="358">
       <c r="A358" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 01:58:17</t>
+          <t>2026-01-17 16:58:17</t>
         </is>
       </c>
       <c r="B358" s="13" t="inlineStr">
@@ -56175,7 +56255,7 @@
     <row r="359">
       <c r="A359" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 01:18:29</t>
+          <t>2026-01-17 16:18:29</t>
         </is>
       </c>
       <c r="B359" s="13" t="inlineStr">
@@ -56237,7 +56317,7 @@
     <row r="360">
       <c r="A360" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 00:38:58</t>
+          <t>2026-01-17 15:38:58</t>
         </is>
       </c>
       <c r="B360" s="13" t="inlineStr">
@@ -56299,7 +56379,7 @@
     <row r="361">
       <c r="A361" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 18:46:30</t>
+          <t>2026-01-17 09:46:30</t>
         </is>
       </c>
       <c r="B361" s="13" t="inlineStr">
@@ -56361,7 +56441,7 @@
     <row r="362">
       <c r="A362" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 02:21:36</t>
+          <t>2026-01-16 17:21:36</t>
         </is>
       </c>
       <c r="B362" s="13" t="inlineStr">
@@ -56423,7 +56503,7 @@
     <row r="363">
       <c r="A363" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 01:51:05</t>
+          <t>2026-01-16 16:51:05</t>
         </is>
       </c>
       <c r="B363" s="13" t="inlineStr">
@@ -56485,7 +56565,7 @@
     <row r="364">
       <c r="A364" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 01:18:22</t>
+          <t>2026-01-16 16:18:22</t>
         </is>
       </c>
       <c r="B364" s="13" t="inlineStr">
@@ -56547,7 +56627,7 @@
     <row r="365">
       <c r="A365" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 01:41:15</t>
+          <t>2026-01-15 16:41:15</t>
         </is>
       </c>
       <c r="B365" s="13" t="inlineStr">
@@ -56609,7 +56689,7 @@
     <row r="366">
       <c r="A366" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 01:05:38</t>
+          <t>2026-01-15 16:05:38</t>
         </is>
       </c>
       <c r="B366" s="13" t="inlineStr">
@@ -56671,7 +56751,7 @@
     <row r="367">
       <c r="A367" s="13" t="inlineStr">
         <is>
-          <t>2026-01-14 00:57:21</t>
+          <t>2026-01-13 15:57:21</t>
         </is>
       </c>
       <c r="B367" s="13" t="inlineStr">
@@ -56733,7 +56813,7 @@
     <row r="368">
       <c r="A368" s="13" t="inlineStr">
         <is>
-          <t>2026-01-14 00:19:49</t>
+          <t>2026-01-13 15:19:49</t>
         </is>
       </c>
       <c r="B368" s="13" t="inlineStr">
@@ -56795,7 +56875,7 @@
     <row r="369">
       <c r="A369" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 23:53:29</t>
+          <t>2026-01-13 14:53:29</t>
         </is>
       </c>
       <c r="B369" s="13" t="inlineStr">
@@ -56857,7 +56937,7 @@
     <row r="370">
       <c r="A370" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 02:23:29</t>
+          <t>2026-01-12 17:23:29</t>
         </is>
       </c>
       <c r="B370" s="13" t="inlineStr">
@@ -56919,7 +56999,7 @@
     <row r="371">
       <c r="A371" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 01:42:12</t>
+          <t>2026-01-12 16:42:12</t>
         </is>
       </c>
       <c r="B371" s="13" t="inlineStr">
@@ -56981,7 +57061,7 @@
     <row r="372">
       <c r="A372" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 01:17:01</t>
+          <t>2026-01-12 16:17:01</t>
         </is>
       </c>
       <c r="B372" s="13" t="inlineStr">
@@ -57043,7 +57123,7 @@
     <row r="373">
       <c r="A373" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 00:43:11</t>
+          <t>2026-01-12 15:43:11</t>
         </is>
       </c>
       <c r="B373" s="13" t="inlineStr">
@@ -57105,7 +57185,7 @@
     <row r="374">
       <c r="A374" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 17:24:44</t>
+          <t>2026-01-12 08:24:44</t>
         </is>
       </c>
       <c r="B374" s="13" t="inlineStr">
@@ -57167,7 +57247,7 @@
     <row r="375">
       <c r="A375" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 03:12:16</t>
+          <t>2026-01-11 18:12:16</t>
         </is>
       </c>
       <c r="B375" s="13" t="inlineStr">
@@ -57229,7 +57309,7 @@
     <row r="376">
       <c r="A376" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 02:54:03</t>
+          <t>2026-01-10 17:54:03</t>
         </is>
       </c>
       <c r="B376" s="13" t="inlineStr">
@@ -57291,7 +57371,7 @@
     <row r="377">
       <c r="A377" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 02:14:56</t>
+          <t>2026-01-10 17:14:56</t>
         </is>
       </c>
       <c r="B377" s="13" t="inlineStr">
@@ -57353,7 +57433,7 @@
     <row r="378">
       <c r="A378" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 01:17:21</t>
+          <t>2026-01-10 16:17:21</t>
         </is>
       </c>
       <c r="B378" s="13" t="inlineStr">
@@ -57415,7 +57495,7 @@
     <row r="379">
       <c r="A379" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 00:22:11</t>
+          <t>2026-01-10 15:22:11</t>
         </is>
       </c>
       <c r="B379" s="13" t="inlineStr">
@@ -57477,7 +57557,7 @@
     <row r="380">
       <c r="A380" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 23:38:24</t>
+          <t>2026-01-10 14:38:24</t>
         </is>
       </c>
       <c r="B380" s="13" t="inlineStr">
@@ -57539,7 +57619,7 @@
     <row r="381">
       <c r="A381" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 02:54:19</t>
+          <t>2026-01-09 17:54:19</t>
         </is>
       </c>
       <c r="B381" s="13" t="inlineStr">
@@ -57601,7 +57681,7 @@
     <row r="382">
       <c r="A382" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 02:00:16</t>
+          <t>2026-01-09 17:00:16</t>
         </is>
       </c>
       <c r="B382" s="13" t="inlineStr">
@@ -57663,7 +57743,7 @@
     <row r="383">
       <c r="A383" s="13" t="inlineStr">
         <is>
-          <t>2026-01-09 23:36:27</t>
+          <t>2026-01-09 14:36:27</t>
         </is>
       </c>
       <c r="B383" s="13" t="inlineStr">
@@ -57722,8 +57802,70 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-05 14:21:47</t>
+        </is>
+      </c>
+      <c r="B384" s="13" t="inlineStr">
+        <is>
+          <t>ランク</t>
+        </is>
+      </c>
+      <c r="C384" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D384" s="13" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E384" s="13" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F384" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G384" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H384" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I384" s="13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J384" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K384" s="14" t="inlineStr"/>
+      <c r="L384" s="14" t="inlineStr"/>
+      <c r="M384" s="14" t="inlineStr"/>
+      <c r="N384" s="14" t="inlineStr"/>
+      <c r="O384" s="14" t="inlineStr"/>
+      <c r="P384" s="13" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P383"/>
+  <autoFilter ref="A1:P384"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-03 05:29:08</t>
+          <t>出力日時：2026-08-03 12:45:17</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-03 12:45:17</t>
+          <t>出力日時：2026-08-04 11:00:36</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-04 11:00:36</t>
+          <t>出力日時：2026-08-05 10:18:29</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'キュー別'!$A$1:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'チャンピオン別'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SUPチャンピオン別'!$A$1:$L$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$385</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$385</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$386</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$386</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,14 +532,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>対象期間：2026-01-09 23:36:27 ～ 2026-08-05 23:53:01</t>
+          <t>対象期間：2026-01-05 14:21:47 ～ 2026-08-05 14:53:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-06 00:15:55</t>
+          <t>出力日時：2026-08-06 10:57:45</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.4713541666666667</v>
+        <v>0.4701298701298701</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.682291666666667</v>
+        <v>1.677922077922078</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5.3515625</v>
+        <v>5.35064935064935</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>8.895833333333334</v>
+        <v>8.896103896103897</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>60.08333333333334</v>
+        <v>60.01818181818182</v>
       </c>
     </row>
     <row r="15">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2.046458333333333</v>
+        <v>2.044155844155845</v>
       </c>
     </row>
     <row r="16">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>56.92708333333334</v>
+        <v>56.8961038961039</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1.837473958333333</v>
+        <v>1.836597402597402</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.5016611295681063</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>1.445182724252492</v>
+        <v>1.440397350993377</v>
       </c>
     </row>
     <row r="25">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.172757475083056</v>
+        <v>5.172185430463577</v>
       </c>
     </row>
     <row r="26">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>9.777408637873755</v>
+        <v>9.774834437086092</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>36.43853820598007</v>
+        <v>36.43377483443709</v>
       </c>
     </row>
     <row r="29">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1.256279069767442</v>
+        <v>1.255960264900662</v>
       </c>
     </row>
     <row r="30">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>64.22591362126246</v>
+        <v>64.16225165562913</v>
       </c>
     </row>
     <row r="31">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>2.072159468438538</v>
+        <v>2.07026490066225</v>
       </c>
     </row>
   </sheetData>
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>151</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.5016611295681063</v>
+        <v>0.5</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.445182724252492</v>
+        <v>1.440397350993377</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5.172757475083056</v>
+        <v>5.172185430463577</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9.777408637873755</v>
+        <v>9.774834437086092</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.256279069767442</v>
+        <v>1.255960264900662</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>64.22591362126246</v>
+        <v>64.16225165562913</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>2.072159468438538</v>
+        <v>2.07026490066225</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.924590163934426</v>
+        <v>4.924590163934425</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>32.32786885245902</v>
@@ -1128,7 +1128,7 @@
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>32</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4155844155844156</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.157894736842105</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>5.828947368421052</v>
+        <v>5.818181818181818</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>10.07894736842105</v>
+        <v>10.06493506493507</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.253421052631579</v>
+        <v>1.252207792207792</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>71.46052631578948</v>
+        <v>71.11688311688312</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.231447368421053</v>
+        <v>2.221948051948053</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.490185185185185</v>
+        <v>1.490185185185186</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>62.64814814814815</v>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1.797111111111111</v>
+        <v>1.797111111111112</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>68.51111111111111</v>
@@ -1516,25 +1516,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.775</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.153846153846154</v>
+        <v>5.15</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.17948717948718</v>
+        <v>7.225</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.232820512820513</v>
+        <v>1.231</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.97435897435897</v>
+        <v>53.75</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.871025641025641</v>
+        <v>1.86175</v>
       </c>
     </row>
     <row r="6">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5.148285714285715</v>
+        <v>5.148285714285714</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>34.6</v>
@@ -1800,7 +1800,7 @@
         <v>25.625</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.85625</v>
+        <v>0.8562500000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5.050000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>16.25</v>
@@ -2833,25 +2833,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.775</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.153846153846154</v>
+        <v>5.15</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.17948717948718</v>
+        <v>7.225</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.232820512820513</v>
+        <v>1.231</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.97435897435897</v>
+        <v>53.75</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.871025641025641</v>
+        <v>1.86175</v>
       </c>
     </row>
     <row r="6">
@@ -3224,7 +3224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V385"/>
+  <dimension ref="A1:V386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3366,7 +3366,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05 23:53:01</t>
+          <t>2026-08-05 14:53:01</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05 23:15:09</t>
+          <t>2026-08-05 14:15:09</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03 02:00:01</t>
+          <t>2026-08-02 17:00:01</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03 00:22:22</t>
+          <t>2026-08-02 15:22:22</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 23:45:22</t>
+          <t>2026-08-02 14:45:22</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 18:45:07</t>
+          <t>2026-08-02 09:45:07</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 18:20:05</t>
+          <t>2026-08-02 09:20:05</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:32</t>
+          <t>2026-08-02 08:49:32</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 03:33:03</t>
+          <t>2026-08-01 18:33:03</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 02:39:30</t>
+          <t>2026-08-01 17:39:30</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -4166,7 +4166,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 04:00:11</t>
+          <t>2026-07-31 19:00:11</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 03:30:26</t>
+          <t>2026-07-31 18:30:26</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -4326,7 +4326,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 02:52:16</t>
+          <t>2026-07-31 17:52:16</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 01:50:20</t>
+          <t>2026-07-31 16:50:20</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -4486,7 +4486,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 01:16:45</t>
+          <t>2026-07-31 16:16:45</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -4566,7 +4566,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 22:56:19</t>
+          <t>2026-07-31 13:56:19</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -4646,7 +4646,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 22:22:46</t>
+          <t>2026-07-31 13:22:46</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 21:49:35</t>
+          <t>2026-07-31 12:49:35</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 23:51:39</t>
+          <t>2026-07-28 14:51:39</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -4886,7 +4886,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 23:05:20</t>
+          <t>2026-07-28 14:05:20</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -4966,7 +4966,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27 01:21:51</t>
+          <t>2026-07-26 16:21:51</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27 00:43:02</t>
+          <t>2026-07-26 15:43:02</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -5126,7 +5126,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 23:12:09</t>
+          <t>2026-07-25 14:12:09</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 22:30:57</t>
+          <t>2026-07-25 13:30:57</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -5286,7 +5286,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 00:11:55</t>
+          <t>2026-07-24 15:11:55</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -5366,7 +5366,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24 23:25:38</t>
+          <t>2026-07-24 14:25:38</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22 00:17:56</t>
+          <t>2026-07-21 15:17:56</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -5526,7 +5526,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22 00:04:35</t>
+          <t>2026-07-21 15:04:35</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -5606,7 +5606,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 23:25:56</t>
+          <t>2026-07-21 14:25:56</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 22:44:36</t>
+          <t>2026-07-21 13:44:36</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -5766,7 +5766,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 22:18:59</t>
+          <t>2026-07-21 13:18:59</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -5846,7 +5846,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20 03:20:20</t>
+          <t>2026-07-19 18:20:20</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -5926,7 +5926,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20 02:39:51</t>
+          <t>2026-07-19 17:39:51</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -6006,7 +6006,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:59:14</t>
+          <t>2026-07-18 09:59:14</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:21:14</t>
+          <t>2026-07-18 09:21:14</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 23:06:28</t>
+          <t>2026-07-16 14:06:28</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 22:32:42</t>
+          <t>2026-07-16 13:32:42</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -6326,7 +6326,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 00:40:48</t>
+          <t>2026-07-15 15:40:48</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -6406,7 +6406,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 23:41:56</t>
+          <t>2026-07-15 14:41:56</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -6486,7 +6486,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 22:58:44</t>
+          <t>2026-07-15 13:58:44</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -6566,7 +6566,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 22:34:16</t>
+          <t>2026-07-15 13:34:16</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -6646,7 +6646,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 23:36:35</t>
+          <t>2026-07-14 14:36:35</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -6726,7 +6726,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 22:49:50</t>
+          <t>2026-07-14 13:49:50</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -6806,7 +6806,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 01:02:29</t>
+          <t>2026-07-13 16:02:29</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -6886,7 +6886,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 00:22:46</t>
+          <t>2026-07-13 15:22:46</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -6966,7 +6966,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 23:51:38</t>
+          <t>2026-07-13 14:51:38</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 02:05:19</t>
+          <t>2026-07-12 17:05:19</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -7126,7 +7126,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 01:29:17</t>
+          <t>2026-07-12 16:29:17</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 03:11:38</t>
+          <t>2026-07-11 18:11:38</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -7286,7 +7286,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 02:46:15</t>
+          <t>2026-07-11 17:46:15</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -7366,7 +7366,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 03:42:29</t>
+          <t>2026-07-10 18:42:29</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -7446,7 +7446,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 03:06:21</t>
+          <t>2026-07-10 18:06:21</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -7526,7 +7526,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:55:25</t>
+          <t>2026-07-08 17:55:25</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:17:09</t>
+          <t>2026-07-08 17:17:09</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -7686,7 +7686,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 02:03:51</t>
+          <t>2026-07-05 17:03:51</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -7766,7 +7766,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 01:07:17</t>
+          <t>2026-07-05 16:07:17</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -7846,7 +7846,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 00:23:00</t>
+          <t>2026-07-05 15:23:00</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -7926,7 +7926,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05 03:21:23</t>
+          <t>2026-07-04 18:21:23</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -8006,7 +8006,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-07-04 03:01:40</t>
+          <t>2026-07-03 18:01:40</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -8086,7 +8086,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03 01:48:19</t>
+          <t>2026-07-02 16:48:19</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01 00:21:19</t>
+          <t>2026-06-30 15:21:19</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -8246,7 +8246,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 23:38:16</t>
+          <t>2026-06-30 14:38:16</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -8326,7 +8326,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 01:16:28</t>
+          <t>2026-06-29 16:16:28</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -8406,7 +8406,7 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 00:34:32</t>
+          <t>2026-06-29 15:34:32</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -8486,7 +8486,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26 00:50:56</t>
+          <t>2026-06-25 15:50:56</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -8566,7 +8566,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26 00:06:40</t>
+          <t>2026-06-25 15:06:40</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07:56</t>
+          <t>2026-06-24 17:07:56</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 01:33:19</t>
+          <t>2026-06-24 16:33:19</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -8806,7 +8806,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:47:59</t>
+          <t>2026-06-24 15:47:59</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -8886,7 +8886,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:08:31</t>
+          <t>2026-06-24 15:08:31</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -8966,7 +8966,7 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 23:33:15</t>
+          <t>2026-06-24 14:33:15</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -9046,7 +9046,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 22:39:11</t>
+          <t>2026-06-24 13:39:11</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -9126,7 +9126,7 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 01:16:06</t>
+          <t>2026-06-22 16:16:06</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -9206,7 +9206,7 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 00:38:08</t>
+          <t>2026-06-22 15:38:08</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
@@ -9286,7 +9286,7 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 00:29:33</t>
+          <t>2026-06-22 15:29:33</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -9366,7 +9366,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 01:54:04</t>
+          <t>2026-06-18 16:54:04</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -9446,7 +9446,7 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 01:14:50</t>
+          <t>2026-06-18 16:14:50</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -9526,7 +9526,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 00:35:17</t>
+          <t>2026-06-18 15:35:17</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -9606,7 +9606,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 23:55:50</t>
+          <t>2026-06-18 14:55:50</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -9686,7 +9686,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 00:44:42</t>
+          <t>2026-06-17 15:44:42</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -9766,7 +9766,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 23:57:38</t>
+          <t>2026-06-17 14:57:38</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -9846,7 +9846,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 01:58:55</t>
+          <t>2026-06-16 16:58:55</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -9926,7 +9926,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 01:30:07</t>
+          <t>2026-06-16 16:30:07</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -10006,7 +10006,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 03:10:28</t>
+          <t>2026-06-14 18:10:28</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -10086,7 +10086,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 02:27:52</t>
+          <t>2026-06-14 17:27:52</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -10166,7 +10166,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 01:57:23</t>
+          <t>2026-06-14 16:57:23</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 01:27:22</t>
+          <t>2026-06-14 16:27:22</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -10326,7 +10326,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 00:24:35</t>
+          <t>2026-06-14 15:24:35</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 23:46:55</t>
+          <t>2026-06-14 14:46:55</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -10486,7 +10486,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 01:41:53</t>
+          <t>2026-06-13 16:41:53</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -10566,7 +10566,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 00:52:58</t>
+          <t>2026-06-13 15:52:58</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -10646,7 +10646,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 00:14:23</t>
+          <t>2026-06-13 15:14:23</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -10726,7 +10726,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 23:45:21</t>
+          <t>2026-06-13 14:45:21</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -10806,7 +10806,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 23:05:32</t>
+          <t>2026-06-13 14:05:32</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -10886,7 +10886,7 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 01:08:14</t>
+          <t>2026-06-10 16:08:14</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -10966,7 +10966,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:34:35</t>
+          <t>2026-06-10 15:34:35</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -11046,7 +11046,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:09:17</t>
+          <t>2026-06-10 15:09:17</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -11126,7 +11126,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 23:27:53</t>
+          <t>2026-06-10 14:27:53</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -11206,7 +11206,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 00:49:00</t>
+          <t>2026-06-09 15:49:00</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -11286,7 +11286,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06 02:58:51</t>
+          <t>2026-06-05 17:58:51</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -11366,7 +11366,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06 02:15:04</t>
+          <t>2026-06-05 17:15:04</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -11446,7 +11446,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 23:49:14</t>
+          <t>2026-06-04 14:49:14</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -11526,7 +11526,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 21:40:04</t>
+          <t>2026-06-04 12:40:04</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 21:17:24</t>
+          <t>2026-06-04 12:17:24</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -11686,7 +11686,7 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 01:06:27</t>
+          <t>2026-06-03 16:06:27</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -11766,7 +11766,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 00:31:09</t>
+          <t>2026-06-03 15:31:09</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -11846,7 +11846,7 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 23:53:57</t>
+          <t>2026-06-03 14:53:57</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -11926,7 +11926,7 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 22:44:02</t>
+          <t>2026-06-03 13:44:02</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -12006,7 +12006,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02 22:49:11</t>
+          <t>2026-06-02 13:49:11</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:56:06</t>
+          <t>2026-06-01 14:56:06</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -12166,7 +12166,7 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:20:26</t>
+          <t>2026-06-01 14:20:26</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -12246,7 +12246,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:01:06</t>
+          <t>2026-06-01 14:01:06</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -12326,7 +12326,7 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31 03:01:04</t>
+          <t>2026-05-30 18:01:04</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -12406,7 +12406,7 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31 02:13:41</t>
+          <t>2026-05-30 17:13:41</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -12486,7 +12486,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 23:00:40</t>
+          <t>2026-05-25 14:00:40</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -12566,7 +12566,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 01:55:47</t>
+          <t>2026-05-24 16:55:47</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -12646,7 +12646,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 01:24:22</t>
+          <t>2026-05-24 16:24:22</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -12726,7 +12726,7 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 23:49:25</t>
+          <t>2026-05-24 14:49:25</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -12806,7 +12806,7 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 03:13:39</t>
+          <t>2026-05-23 18:13:39</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -12886,7 +12886,7 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 02:41:52</t>
+          <t>2026-05-23 17:41:52</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -12966,7 +12966,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 23:19:04</t>
+          <t>2026-05-23 14:19:04</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -13046,7 +13046,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 22:43:20</t>
+          <t>2026-05-23 13:43:20</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -13126,7 +13126,7 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 15:54:19</t>
+          <t>2026-05-23 06:54:19</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -13206,7 +13206,7 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 02:25:24</t>
+          <t>2026-05-22 17:25:24</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -13286,7 +13286,7 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 01:29:23</t>
+          <t>2026-05-21 16:29:23</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -13366,7 +13366,7 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 00:48:49</t>
+          <t>2026-05-21 15:48:49</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -13446,7 +13446,7 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:45</t>
+          <t>2026-05-21 15:00:45</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -13526,7 +13526,7 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 23:22:44</t>
+          <t>2026-05-21 14:22:44</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -13606,7 +13606,7 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 00:05:15</t>
+          <t>2026-05-20 15:05:15</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -13686,7 +13686,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 23:43:50</t>
+          <t>2026-05-20 14:43:50</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 22:57:45</t>
+          <t>2026-05-20 13:57:45</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -13846,7 +13846,7 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 01:25:45</t>
+          <t>2026-05-19 16:25:45</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -13926,7 +13926,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 00:46:42</t>
+          <t>2026-05-19 15:46:42</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -14006,7 +14006,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>2026-05-18 22:56:39</t>
+          <t>2026-05-18 13:56:39</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -14086,7 +14086,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 01:35:56</t>
+          <t>2026-05-14 16:35:56</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -14166,7 +14166,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 01:17:05</t>
+          <t>2026-05-14 16:17:05</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -14246,7 +14246,7 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 00:05:48</t>
+          <t>2026-05-14 15:05:48</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -14326,7 +14326,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14 01:25:38</t>
+          <t>2026-05-13 16:25:38</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -14406,7 +14406,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>2026-05-12 00:19:57</t>
+          <t>2026-05-11 15:19:57</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -14486,7 +14486,7 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 23:54:15</t>
+          <t>2026-05-11 14:54:15</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -14566,7 +14566,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 23:14:30</t>
+          <t>2026-05-11 14:14:30</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -14646,7 +14646,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 22:37:05</t>
+          <t>2026-05-11 13:37:05</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -14726,7 +14726,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 21:53:13</t>
+          <t>2026-05-11 12:53:13</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -14806,7 +14806,7 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 00:04:01</t>
+          <t>2026-05-10 15:04:01</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -14886,7 +14886,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:54:24</t>
+          <t>2026-05-09 16:54:24</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -14966,7 +14966,7 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:22:50</t>
+          <t>2026-05-09 16:22:50</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -15046,7 +15046,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 00:26:16</t>
+          <t>2026-05-09 15:26:16</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -15126,7 +15126,7 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 23:38:30</t>
+          <t>2026-05-09 14:38:30</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -15206,7 +15206,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 22:50:20</t>
+          <t>2026-05-09 13:50:20</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -15286,7 +15286,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 22:13:25</t>
+          <t>2026-05-09 13:13:25</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -15366,7 +15366,7 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 20:00:11</t>
+          <t>2026-05-09 11:00:11</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 19:10:28</t>
+          <t>2026-05-09 10:10:28</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -15526,7 +15526,7 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 02:17:27</t>
+          <t>2026-05-08 17:17:27</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -15606,7 +15606,7 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 01:38:25</t>
+          <t>2026-05-08 16:38:25</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -15686,7 +15686,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 00:58:58</t>
+          <t>2026-05-08 15:58:58</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -15766,7 +15766,7 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 00:37:55</t>
+          <t>2026-05-08 15:37:55</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -15846,7 +15846,7 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 01:48:31</t>
+          <t>2026-05-07 16:48:31</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -15926,7 +15926,7 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 01:02:52</t>
+          <t>2026-05-07 16:02:52</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 00:23:29</t>
+          <t>2026-05-07 15:23:29</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -16086,7 +16086,7 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 01:30:56</t>
+          <t>2026-05-06 16:30:56</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -16166,7 +16166,7 @@
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 00:42:16</t>
+          <t>2026-05-06 15:42:16</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -16246,7 +16246,7 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 23:44:04</t>
+          <t>2026-05-06 14:44:04</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -16326,7 +16326,7 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:13:52</t>
+          <t>2026-05-06 09:13:52</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -16406,7 +16406,7 @@
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:05:08</t>
+          <t>2026-05-06 09:05:08</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -16486,7 +16486,7 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 17:22:30</t>
+          <t>2026-05-06 08:22:30</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -16566,7 +16566,7 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 16:28:42</t>
+          <t>2026-05-06 07:28:42</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -16646,7 +16646,7 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 03:16:57</t>
+          <t>2026-05-05 18:16:57</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -16726,7 +16726,7 @@
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:32:40</t>
+          <t>2026-05-05 17:32:40</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -16806,7 +16806,7 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:23:28</t>
+          <t>2026-05-05 17:23:28</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -16886,7 +16886,7 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 01:48:28</t>
+          <t>2026-05-05 16:48:28</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
@@ -16966,7 +16966,7 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 00:52:33</t>
+          <t>2026-05-05 15:52:33</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -17046,7 +17046,7 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 17:43:06</t>
+          <t>2026-05-05 08:43:06</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>2026-05-03 00:36:42</t>
+          <t>2026-05-02 15:36:42</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
@@ -17206,7 +17206,7 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 23:51:09</t>
+          <t>2026-05-02 14:51:09</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -17286,7 +17286,7 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 22:15:10</t>
+          <t>2026-05-02 13:15:10</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
@@ -17366,7 +17366,7 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 21:29:49</t>
+          <t>2026-05-02 12:29:49</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -17446,7 +17446,7 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 01:39:42</t>
+          <t>2026-04-30 16:39:42</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -17526,7 +17526,7 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 01:01:34</t>
+          <t>2026-04-30 16:01:34</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
@@ -17606,7 +17606,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 00:24:48</t>
+          <t>2026-04-30 15:24:48</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -17686,7 +17686,7 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 23:37:10</t>
+          <t>2026-04-30 14:37:10</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
@@ -17766,7 +17766,7 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 22:58:06</t>
+          <t>2026-04-30 13:58:06</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
@@ -17846,7 +17846,7 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 03:29:33</t>
+          <t>2026-04-29 18:29:33</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
@@ -17926,7 +17926,7 @@
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 02:54:07</t>
+          <t>2026-04-29 17:54:07</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
@@ -18006,7 +18006,7 @@
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 02:20:58</t>
+          <t>2026-04-29 17:20:58</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
@@ -18086,7 +18086,7 @@
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 01:42:01</t>
+          <t>2026-04-29 16:42:01</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
@@ -18166,7 +18166,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 01:03:17</t>
+          <t>2026-04-29 16:03:17</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
@@ -18246,7 +18246,7 @@
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 00:19:47</t>
+          <t>2026-04-29 15:19:47</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
@@ -18326,7 +18326,7 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 23:29:53</t>
+          <t>2026-04-29 14:29:53</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
@@ -18406,7 +18406,7 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:59:49</t>
+          <t>2026-04-29 13:59:49</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
@@ -18486,7 +18486,7 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:38:22</t>
+          <t>2026-04-29 13:38:22</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
@@ -18566,7 +18566,7 @@
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:44</t>
+          <t>2026-04-29 13:17:44</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -18646,7 +18646,7 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 03:28:56</t>
+          <t>2026-04-28 18:28:56</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
@@ -18726,7 +18726,7 @@
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:58:50</t>
+          <t>2026-04-28 17:58:50</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:29:43</t>
+          <t>2026-04-28 17:29:43</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
@@ -18886,7 +18886,7 @@
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 01:38:43</t>
+          <t>2026-04-28 16:38:43</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -18966,7 +18966,7 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:54</t>
+          <t>2026-04-28 15:58:54</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
@@ -19046,7 +19046,7 @@
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:31:32</t>
+          <t>2026-04-28 15:31:32</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -19126,7 +19126,7 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:04:20</t>
+          <t>2026-04-28 15:04:20</t>
         </is>
       </c>
       <c r="B199" s="7" t="inlineStr">
@@ -19206,7 +19206,7 @@
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 23:37:27</t>
+          <t>2026-04-28 14:37:27</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -19286,7 +19286,7 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 23:09:10</t>
+          <t>2026-04-28 14:09:10</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
@@ -19366,7 +19366,7 @@
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:59:25</t>
+          <t>2026-04-27 14:59:25</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -19446,7 +19446,7 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:49:35</t>
+          <t>2026-04-27 14:49:35</t>
         </is>
       </c>
       <c r="B203" s="7" t="inlineStr">
@@ -19526,7 +19526,7 @@
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 22:55:34</t>
+          <t>2026-04-27 13:55:34</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
@@ -19606,7 +19606,7 @@
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 22:04:13</t>
+          <t>2026-04-27 13:04:13</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
@@ -19686,7 +19686,7 @@
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 02:49:02</t>
+          <t>2026-04-24 17:49:02</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
@@ -19766,7 +19766,7 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 02:03:56</t>
+          <t>2026-04-24 17:03:56</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
@@ -19846,7 +19846,7 @@
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 01:37:00</t>
+          <t>2026-04-24 16:37:00</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -19926,7 +19926,7 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:33:59</t>
+          <t>2026-04-23 15:33:59</t>
         </is>
       </c>
       <c r="B209" s="7" t="inlineStr">
@@ -20006,7 +20006,7 @@
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:22:46</t>
+          <t>2026-04-23 15:22:46</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -20086,7 +20086,7 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:12:54</t>
+          <t>2026-04-23 15:12:54</t>
         </is>
       </c>
       <c r="B211" s="7" t="inlineStr">
@@ -20166,7 +20166,7 @@
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 22:36:03</t>
+          <t>2026-04-23 13:36:03</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
@@ -20246,7 +20246,7 @@
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:58:57</t>
+          <t>2026-04-13 15:58:57</t>
         </is>
       </c>
       <c r="B213" s="7" t="inlineStr">
@@ -20326,7 +20326,7 @@
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:09:08</t>
+          <t>2026-04-13 15:09:08</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
@@ -20406,7 +20406,7 @@
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 01:48:02</t>
+          <t>2026-04-12 16:48:02</t>
         </is>
       </c>
       <c r="B215" s="7" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 01:17:58</t>
+          <t>2026-04-12 16:17:58</t>
         </is>
       </c>
       <c r="B216" s="7" t="inlineStr">
@@ -20566,7 +20566,7 @@
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 00:41:20</t>
+          <t>2026-04-12 15:41:20</t>
         </is>
       </c>
       <c r="B217" s="7" t="inlineStr">
@@ -20646,7 +20646,7 @@
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 23:18:06</t>
+          <t>2026-04-09 14:18:06</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
@@ -20726,7 +20726,7 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 22:52:44</t>
+          <t>2026-04-09 13:52:44</t>
         </is>
       </c>
       <c r="B219" s="7" t="inlineStr">
@@ -20806,7 +20806,7 @@
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 22:27:45</t>
+          <t>2026-04-09 13:27:45</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
@@ -20886,7 +20886,7 @@
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>2026-04-08 01:10:31</t>
+          <t>2026-04-07 16:10:31</t>
         </is>
       </c>
       <c r="B221" s="7" t="inlineStr">
@@ -20966,7 +20966,7 @@
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>2026-04-08 00:29:19</t>
+          <t>2026-04-07 15:29:19</t>
         </is>
       </c>
       <c r="B222" s="7" t="inlineStr">
@@ -21046,7 +21046,7 @@
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>2026-04-04 04:36:31</t>
+          <t>2026-04-03 19:36:31</t>
         </is>
       </c>
       <c r="B223" s="7" t="inlineStr">
@@ -21126,7 +21126,7 @@
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>2026-04-04 04:16:32</t>
+          <t>2026-04-03 19:16:32</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -21206,7 +21206,7 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 04:24:43</t>
+          <t>2026-03-27 19:24:43</t>
         </is>
       </c>
       <c r="B225" s="7" t="inlineStr">
@@ -21286,7 +21286,7 @@
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 03:38:31</t>
+          <t>2026-03-27 18:38:31</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
@@ -21366,7 +21366,7 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 03:17:50</t>
+          <t>2026-03-27 18:17:50</t>
         </is>
       </c>
       <c r="B227" s="7" t="inlineStr">
@@ -21446,7 +21446,7 @@
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 02:43:19</t>
+          <t>2026-03-27 17:43:19</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
@@ -21526,7 +21526,7 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 02:15:18</t>
+          <t>2026-03-27 17:15:18</t>
         </is>
       </c>
       <c r="B229" s="7" t="inlineStr">
@@ -21606,7 +21606,7 @@
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 23:18:12</t>
+          <t>2026-03-25 14:18:12</t>
         </is>
       </c>
       <c r="B230" s="7" t="inlineStr">
@@ -21686,7 +21686,7 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 00:01:49</t>
+          <t>2026-03-24 15:01:49</t>
         </is>
       </c>
       <c r="B231" s="7" t="inlineStr">
@@ -21766,7 +21766,7 @@
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 23:25:16</t>
+          <t>2026-03-24 14:25:16</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
@@ -21846,7 +21846,7 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 23:02:52</t>
+          <t>2026-03-24 14:02:52</t>
         </is>
       </c>
       <c r="B233" s="7" t="inlineStr">
@@ -21926,7 +21926,7 @@
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 22:26:26</t>
+          <t>2026-03-24 13:26:26</t>
         </is>
       </c>
       <c r="B234" s="7" t="inlineStr">
@@ -22006,7 +22006,7 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 00:56:18</t>
+          <t>2026-03-23 15:56:18</t>
         </is>
       </c>
       <c r="B235" s="7" t="inlineStr">
@@ -22086,7 +22086,7 @@
     <row r="236">
       <c r="A236" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 00:29:29</t>
+          <t>2026-03-23 15:29:29</t>
         </is>
       </c>
       <c r="B236" s="7" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 23:51:11</t>
+          <t>2026-03-22 14:51:11</t>
         </is>
       </c>
       <c r="B237" s="7" t="inlineStr">
@@ -22246,7 +22246,7 @@
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 01:04:36</t>
+          <t>2026-03-21 16:04:36</t>
         </is>
       </c>
       <c r="B238" s="7" t="inlineStr">
@@ -22326,7 +22326,7 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>2026-03-21 02:55:49</t>
+          <t>2026-03-20 17:55:49</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
@@ -22406,7 +22406,7 @@
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>2026-03-18 00:07:07</t>
+          <t>2026-03-17 15:07:07</t>
         </is>
       </c>
       <c r="B240" s="7" t="inlineStr">
@@ -22486,7 +22486,7 @@
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 23:24:05</t>
+          <t>2026-03-17 14:24:05</t>
         </is>
       </c>
       <c r="B241" s="7" t="inlineStr">
@@ -22566,7 +22566,7 @@
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 02:00:50</t>
+          <t>2026-03-16 17:00:50</t>
         </is>
       </c>
       <c r="B242" s="7" t="inlineStr">
@@ -22646,7 +22646,7 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 01:33:08</t>
+          <t>2026-03-16 16:33:08</t>
         </is>
       </c>
       <c r="B243" s="7" t="inlineStr">
@@ -22726,7 +22726,7 @@
     <row r="244">
       <c r="A244" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 23:28:09</t>
+          <t>2026-03-16 14:28:09</t>
         </is>
       </c>
       <c r="B244" s="7" t="inlineStr">
@@ -22806,7 +22806,7 @@
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 01:32:22</t>
+          <t>2026-03-15 16:32:22</t>
         </is>
       </c>
       <c r="B245" s="7" t="inlineStr">
@@ -22886,7 +22886,7 @@
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14 01:43:49</t>
+          <t>2026-03-13 16:43:49</t>
         </is>
       </c>
       <c r="B246" s="7" t="inlineStr">
@@ -22966,7 +22966,7 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14 01:19:35</t>
+          <t>2026-03-13 16:19:35</t>
         </is>
       </c>
       <c r="B247" s="7" t="inlineStr">
@@ -23046,7 +23046,7 @@
     <row r="248">
       <c r="A248" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 23:45:27</t>
+          <t>2026-03-12 14:45:27</t>
         </is>
       </c>
       <c r="B248" s="7" t="inlineStr">
@@ -23126,7 +23126,7 @@
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 23:02:09</t>
+          <t>2026-03-12 14:02:09</t>
         </is>
       </c>
       <c r="B249" s="7" t="inlineStr">
@@ -23206,7 +23206,7 @@
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 22:42:59</t>
+          <t>2026-03-12 13:42:59</t>
         </is>
       </c>
       <c r="B250" s="7" t="inlineStr">
@@ -23286,7 +23286,7 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 01:39:10</t>
+          <t>2026-03-11 16:39:10</t>
         </is>
       </c>
       <c r="B251" s="7" t="inlineStr">
@@ -23366,7 +23366,7 @@
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:43:21</t>
+          <t>2026-03-11 15:43:21</t>
         </is>
       </c>
       <c r="B252" s="7" t="inlineStr">
@@ -23446,7 +23446,7 @@
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:04:25</t>
+          <t>2026-03-11 15:04:25</t>
         </is>
       </c>
       <c r="B253" s="7" t="inlineStr">
@@ -23526,7 +23526,7 @@
     <row r="254">
       <c r="A254" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 22:54:02</t>
+          <t>2026-03-11 13:54:02</t>
         </is>
       </c>
       <c r="B254" s="7" t="inlineStr">
@@ -23606,7 +23606,7 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>2026-03-08 02:01:53</t>
+          <t>2026-03-07 17:01:53</t>
         </is>
       </c>
       <c r="B255" s="7" t="inlineStr">
@@ -23686,7 +23686,7 @@
     <row r="256">
       <c r="A256" s="7" t="inlineStr">
         <is>
-          <t>2026-03-02 02:18:59</t>
+          <t>2026-03-01 17:18:59</t>
         </is>
       </c>
       <c r="B256" s="7" t="inlineStr">
@@ -23766,7 +23766,7 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>2026-02-24 01:40:38</t>
+          <t>2026-02-23 16:40:38</t>
         </is>
       </c>
       <c r="B257" s="7" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="258">
       <c r="A258" s="7" t="inlineStr">
         <is>
-          <t>2026-02-24 00:10:31</t>
+          <t>2026-02-23 15:10:31</t>
         </is>
       </c>
       <c r="B258" s="7" t="inlineStr">
@@ -23926,7 +23926,7 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 23:33:47</t>
+          <t>2026-02-23 14:33:47</t>
         </is>
       </c>
       <c r="B259" s="7" t="inlineStr">
@@ -24006,7 +24006,7 @@
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 22:40:54</t>
+          <t>2026-02-23 13:40:54</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
@@ -24086,7 +24086,7 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 21:58:56</t>
+          <t>2026-02-23 12:58:56</t>
         </is>
       </c>
       <c r="B261" s="7" t="inlineStr">
@@ -24166,7 +24166,7 @@
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 19:21:48</t>
+          <t>2026-02-23 10:21:48</t>
         </is>
       </c>
       <c r="B262" s="7" t="inlineStr">
@@ -24246,7 +24246,7 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 17:17:13</t>
+          <t>2026-02-23 08:17:13</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
@@ -24326,7 +24326,7 @@
     <row r="264">
       <c r="A264" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 04:22:01</t>
+          <t>2026-02-22 19:22:01</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -24406,7 +24406,7 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 03:23:51</t>
+          <t>2026-02-22 18:23:51</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
@@ -24486,7 +24486,7 @@
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 02:58:18</t>
+          <t>2026-02-22 17:58:18</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -24566,7 +24566,7 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 02:29:21</t>
+          <t>2026-02-22 17:29:21</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -24646,7 +24646,7 @@
     <row r="268">
       <c r="A268" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 01:59:09</t>
+          <t>2026-02-22 16:59:09</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
@@ -24726,7 +24726,7 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 01:32:08</t>
+          <t>2026-02-22 16:32:08</t>
         </is>
       </c>
       <c r="B269" s="7" t="inlineStr">
@@ -24806,7 +24806,7 @@
     <row r="270">
       <c r="A270" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 03:34:36</t>
+          <t>2026-02-20 18:34:36</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
@@ -24886,7 +24886,7 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 02:57:13</t>
+          <t>2026-02-20 17:57:13</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
@@ -24966,7 +24966,7 @@
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 02:19:01</t>
+          <t>2026-02-20 17:19:01</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -25046,7 +25046,7 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 01:41:10</t>
+          <t>2026-02-20 16:41:10</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
@@ -25126,7 +25126,7 @@
     <row r="274">
       <c r="A274" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:57:47</t>
+          <t>2026-02-20 15:57:47</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -25206,7 +25206,7 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:39:52</t>
+          <t>2026-02-20 15:39:52</t>
         </is>
       </c>
       <c r="B275" s="7" t="inlineStr">
@@ -25286,7 +25286,7 @@
     <row r="276">
       <c r="A276" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 01:21:13</t>
+          <t>2026-02-19 16:21:13</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
@@ -25366,7 +25366,7 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 00:33:10</t>
+          <t>2026-02-19 15:33:10</t>
         </is>
       </c>
       <c r="B277" s="7" t="inlineStr">
@@ -25446,7 +25446,7 @@
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>2026-02-18 00:37:38</t>
+          <t>2026-02-17 15:37:38</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>2026-02-17 23:58:39</t>
+          <t>2026-02-17 14:58:39</t>
         </is>
       </c>
       <c r="B279" s="7" t="inlineStr">
@@ -25606,7 +25606,7 @@
     <row r="280">
       <c r="A280" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 02:24:16</t>
+          <t>2026-02-15 17:24:16</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -25686,7 +25686,7 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 01:47:19</t>
+          <t>2026-02-15 16:47:19</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
@@ -25766,7 +25766,7 @@
     <row r="282">
       <c r="A282" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 00:56:43</t>
+          <t>2026-02-15 15:56:43</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -25846,7 +25846,7 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 00:26:20</t>
+          <t>2026-02-15 15:26:20</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
@@ -25926,7 +25926,7 @@
     <row r="284">
       <c r="A284" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 23:48:44</t>
+          <t>2026-02-15 14:48:44</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -26006,7 +26006,7 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 04:17:17</t>
+          <t>2026-02-14 19:17:17</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
@@ -26086,7 +26086,7 @@
     <row r="286">
       <c r="A286" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 03:53:01</t>
+          <t>2026-02-14 18:53:01</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -26166,7 +26166,7 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:59:46</t>
+          <t>2026-02-14 17:59:46</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -26246,7 +26246,7 @@
     <row r="288">
       <c r="A288" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:26:42</t>
+          <t>2026-02-14 17:26:42</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -26326,7 +26326,7 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:00:09</t>
+          <t>2026-02-14 17:00:09</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -26406,7 +26406,7 @@
     <row r="290">
       <c r="A290" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 01:39:16</t>
+          <t>2026-02-14 16:39:16</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -26486,7 +26486,7 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 00:56:51</t>
+          <t>2026-02-14 15:56:51</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
@@ -26566,7 +26566,7 @@
     <row r="292">
       <c r="A292" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 23:52:26</t>
+          <t>2026-02-14 14:52:26</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -26646,7 +26646,7 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 23:14:55</t>
+          <t>2026-02-14 14:14:55</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
@@ -26726,7 +26726,7 @@
     <row r="294">
       <c r="A294" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 04:19:58</t>
+          <t>2026-02-13 19:19:58</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -26806,7 +26806,7 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 03:37:53</t>
+          <t>2026-02-13 18:37:53</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
@@ -26886,7 +26886,7 @@
     <row r="296">
       <c r="A296" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 03:03:31</t>
+          <t>2026-02-13 18:03:31</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -26966,7 +26966,7 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 02:08:36</t>
+          <t>2026-02-13 17:08:36</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -27046,7 +27046,7 @@
     <row r="298">
       <c r="A298" s="7" t="inlineStr">
         <is>
-          <t>2026-02-12 00:20:03</t>
+          <t>2026-02-11 15:20:03</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -27126,7 +27126,7 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 03:05:03</t>
+          <t>2026-02-10 18:05:03</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="300">
       <c r="A300" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 02:14:02</t>
+          <t>2026-02-10 17:14:02</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
@@ -27286,7 +27286,7 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 01:33:21</t>
+          <t>2026-02-10 16:33:21</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -27366,7 +27366,7 @@
     <row r="302">
       <c r="A302" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 01:01:41</t>
+          <t>2026-02-10 16:01:41</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
@@ -27446,7 +27446,7 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 01:49:32</t>
+          <t>2026-02-09 16:49:32</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
@@ -27526,7 +27526,7 @@
     <row r="304">
       <c r="A304" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 01:42:29</t>
+          <t>2026-02-09 16:42:29</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -27606,7 +27606,7 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 23:44:10</t>
+          <t>2026-02-09 14:44:10</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -27686,7 +27686,7 @@
     <row r="306">
       <c r="A306" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 23:00:28</t>
+          <t>2026-02-09 14:00:28</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -27766,7 +27766,7 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 00:27:49</t>
+          <t>2026-02-08 15:27:49</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
@@ -27846,7 +27846,7 @@
     <row r="308">
       <c r="A308" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 00:16:42</t>
+          <t>2026-02-08 15:16:42</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
@@ -27926,7 +27926,7 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08 04:04:43</t>
+          <t>2026-02-07 19:04:43</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
@@ -28006,7 +28006,7 @@
     <row r="310">
       <c r="A310" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 03:13:11</t>
+          <t>2026-02-06 18:13:11</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -28086,7 +28086,7 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 02:19:42</t>
+          <t>2026-02-06 17:19:42</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -28166,7 +28166,7 @@
     <row r="312">
       <c r="A312" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 01:37:36</t>
+          <t>2026-02-06 16:37:36</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -28246,7 +28246,7 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>2026-02-03 23:04:49</t>
+          <t>2026-02-03 14:04:49</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -28326,7 +28326,7 @@
     <row r="314">
       <c r="A314" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 23:21:38</t>
+          <t>2026-02-02 14:21:38</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -28406,7 +28406,7 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 03:08:17</t>
+          <t>2026-02-01 18:08:17</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -28486,7 +28486,7 @@
     <row r="316">
       <c r="A316" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 02:41:55</t>
+          <t>2026-02-01 17:41:55</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -28566,7 +28566,7 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 02:09:57</t>
+          <t>2026-02-01 17:09:57</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -28646,7 +28646,7 @@
     <row r="318">
       <c r="A318" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 01:41:49</t>
+          <t>2026-02-01 16:41:49</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -28726,7 +28726,7 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 02:22:13</t>
+          <t>2026-01-31 17:22:13</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -28806,7 +28806,7 @@
     <row r="320">
       <c r="A320" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 01:20:54</t>
+          <t>2026-01-31 16:20:54</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 01:09:32</t>
+          <t>2026-01-31 16:09:32</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -28966,7 +28966,7 @@
     <row r="322">
       <c r="A322" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 00:29:37</t>
+          <t>2026-01-31 15:29:37</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -29046,7 +29046,7 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 00:03:50</t>
+          <t>2026-01-31 15:03:50</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -29126,7 +29126,7 @@
     <row r="324">
       <c r="A324" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 23:15:28</t>
+          <t>2026-01-31 14:15:28</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -29206,7 +29206,7 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>2026-01-29 00:36:39</t>
+          <t>2026-01-28 15:36:39</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -29286,7 +29286,7 @@
     <row r="326">
       <c r="A326" s="7" t="inlineStr">
         <is>
-          <t>2026-01-29 00:02:45</t>
+          <t>2026-01-28 15:02:45</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -29366,7 +29366,7 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 23:26:47</t>
+          <t>2026-01-28 14:26:47</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -29446,7 +29446,7 @@
     <row r="328">
       <c r="A328" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 23:04:33</t>
+          <t>2026-01-28 14:04:33</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -29526,7 +29526,7 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 00:33:31</t>
+          <t>2026-01-27 15:33:31</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -29606,7 +29606,7 @@
     <row r="330">
       <c r="A330" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 23:59:21</t>
+          <t>2026-01-27 14:59:21</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -29686,7 +29686,7 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 23:08:33</t>
+          <t>2026-01-27 14:08:33</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -29766,7 +29766,7 @@
     <row r="332">
       <c r="A332" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 23:28:17</t>
+          <t>2026-01-25 14:28:17</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -29846,7 +29846,7 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 22:56:22</t>
+          <t>2026-01-25 13:56:22</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -29926,7 +29926,7 @@
     <row r="334">
       <c r="A334" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 22:28:25</t>
+          <t>2026-01-25 13:28:25</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -30006,7 +30006,7 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 21:42:03</t>
+          <t>2026-01-25 12:42:03</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -30086,7 +30086,7 @@
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 19:38:23</t>
+          <t>2026-01-25 10:38:23</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -30166,7 +30166,7 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 18:56:35</t>
+          <t>2026-01-25 09:56:35</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -30246,7 +30246,7 @@
     <row r="338">
       <c r="A338" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 18:29:19</t>
+          <t>2026-01-25 09:29:19</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -30326,7 +30326,7 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 17:14:05</t>
+          <t>2026-01-25 08:14:05</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -30406,7 +30406,7 @@
     <row r="340">
       <c r="A340" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 02:47:24</t>
+          <t>2026-01-23 17:47:24</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -30486,7 +30486,7 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 02:12:26</t>
+          <t>2026-01-23 17:12:26</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="342">
       <c r="A342" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 01:33:34</t>
+          <t>2026-01-23 16:33:34</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -30646,7 +30646,7 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 01:00:39</t>
+          <t>2026-01-23 16:00:39</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -30726,7 +30726,7 @@
     <row r="344">
       <c r="A344" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 00:19:07</t>
+          <t>2026-01-23 15:19:07</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -30806,7 +30806,7 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 23:52:33</t>
+          <t>2026-01-23 14:52:33</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -30886,7 +30886,7 @@
     <row r="346">
       <c r="A346" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 23:19:19</t>
+          <t>2026-01-23 14:19:19</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -30966,7 +30966,7 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36:59</t>
+          <t>2026-01-23 13:36:59</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -31046,7 +31046,7 @@
     <row r="348">
       <c r="A348" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 03:01:58</t>
+          <t>2026-01-22 18:01:58</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -31126,7 +31126,7 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 02:25:41</t>
+          <t>2026-01-22 17:25:41</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -31206,7 +31206,7 @@
     <row r="350">
       <c r="A350" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 00:32:45</t>
+          <t>2026-01-22 15:32:45</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -31286,7 +31286,7 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 23:54:46</t>
+          <t>2026-01-22 14:54:46</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -31366,7 +31366,7 @@
     <row r="352">
       <c r="A352" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 23:17:42</t>
+          <t>2026-01-22 14:17:42</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -31446,7 +31446,7 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 01:10:08</t>
+          <t>2026-01-21 16:10:08</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -31526,7 +31526,7 @@
     <row r="354">
       <c r="A354" s="7" t="inlineStr">
         <is>
-          <t>2026-01-21 00:27:51</t>
+          <t>2026-01-20 15:27:51</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -31606,7 +31606,7 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 23:25:34</t>
+          <t>2026-01-20 14:25:34</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -31686,7 +31686,7 @@
     <row r="356">
       <c r="A356" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 22:56:13</t>
+          <t>2026-01-20 13:56:13</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -31766,7 +31766,7 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>2026-01-19 01:59:11</t>
+          <t>2026-01-18 16:59:11</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -31846,7 +31846,7 @@
     <row r="358">
       <c r="A358" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 03:05:32</t>
+          <t>2026-01-17 18:05:32</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -31926,7 +31926,7 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 02:19:17</t>
+          <t>2026-01-17 17:19:17</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -32006,7 +32006,7 @@
     <row r="360">
       <c r="A360" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 01:58:17</t>
+          <t>2026-01-17 16:58:17</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -32086,7 +32086,7 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 01:18:29</t>
+          <t>2026-01-17 16:18:29</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -32166,7 +32166,7 @@
     <row r="362">
       <c r="A362" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 00:38:58</t>
+          <t>2026-01-17 15:38:58</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 18:46:30</t>
+          <t>2026-01-17 09:46:30</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -32326,7 +32326,7 @@
     <row r="364">
       <c r="A364" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 02:21:36</t>
+          <t>2026-01-16 17:21:36</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -32406,7 +32406,7 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 01:51:05</t>
+          <t>2026-01-16 16:51:05</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -32486,7 +32486,7 @@
     <row r="366">
       <c r="A366" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 01:18:22</t>
+          <t>2026-01-16 16:18:22</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -32566,7 +32566,7 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 01:41:15</t>
+          <t>2026-01-15 16:41:15</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -32646,7 +32646,7 @@
     <row r="368">
       <c r="A368" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 01:05:38</t>
+          <t>2026-01-15 16:05:38</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -32726,7 +32726,7 @@
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14 00:57:21</t>
+          <t>2026-01-13 15:57:21</t>
         </is>
       </c>
       <c r="B369" s="7" t="inlineStr">
@@ -32806,7 +32806,7 @@
     <row r="370">
       <c r="A370" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14 00:19:49</t>
+          <t>2026-01-13 15:19:49</t>
         </is>
       </c>
       <c r="B370" s="7" t="inlineStr">
@@ -32886,7 +32886,7 @@
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 23:53:29</t>
+          <t>2026-01-13 14:53:29</t>
         </is>
       </c>
       <c r="B371" s="7" t="inlineStr">
@@ -32966,7 +32966,7 @@
     <row r="372">
       <c r="A372" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 02:23:29</t>
+          <t>2026-01-12 17:23:29</t>
         </is>
       </c>
       <c r="B372" s="7" t="inlineStr">
@@ -33046,7 +33046,7 @@
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 01:42:12</t>
+          <t>2026-01-12 16:42:12</t>
         </is>
       </c>
       <c r="B373" s="7" t="inlineStr">
@@ -33126,7 +33126,7 @@
     <row r="374">
       <c r="A374" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 01:17:01</t>
+          <t>2026-01-12 16:17:01</t>
         </is>
       </c>
       <c r="B374" s="7" t="inlineStr">
@@ -33206,7 +33206,7 @@
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 00:43:11</t>
+          <t>2026-01-12 15:43:11</t>
         </is>
       </c>
       <c r="B375" s="7" t="inlineStr">
@@ -33286,7 +33286,7 @@
     <row r="376">
       <c r="A376" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 17:24:44</t>
+          <t>2026-01-12 08:24:44</t>
         </is>
       </c>
       <c r="B376" s="7" t="inlineStr">
@@ -33366,7 +33366,7 @@
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 03:12:16</t>
+          <t>2026-01-11 18:12:16</t>
         </is>
       </c>
       <c r="B377" s="7" t="inlineStr">
@@ -33446,7 +33446,7 @@
     <row r="378">
       <c r="A378" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 02:54:03</t>
+          <t>2026-01-10 17:54:03</t>
         </is>
       </c>
       <c r="B378" s="7" t="inlineStr">
@@ -33526,7 +33526,7 @@
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 02:14:56</t>
+          <t>2026-01-10 17:14:56</t>
         </is>
       </c>
       <c r="B379" s="7" t="inlineStr">
@@ -33606,7 +33606,7 @@
     <row r="380">
       <c r="A380" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 01:17:21</t>
+          <t>2026-01-10 16:17:21</t>
         </is>
       </c>
       <c r="B380" s="7" t="inlineStr">
@@ -33686,7 +33686,7 @@
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 00:22:11</t>
+          <t>2026-01-10 15:22:11</t>
         </is>
       </c>
       <c r="B381" s="7" t="inlineStr">
@@ -33766,7 +33766,7 @@
     <row r="382">
       <c r="A382" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 23:38:24</t>
+          <t>2026-01-10 14:38:24</t>
         </is>
       </c>
       <c r="B382" s="7" t="inlineStr">
@@ -33846,7 +33846,7 @@
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 02:54:19</t>
+          <t>2026-01-09 17:54:19</t>
         </is>
       </c>
       <c r="B383" s="7" t="inlineStr">
@@ -33926,7 +33926,7 @@
     <row r="384">
       <c r="A384" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 02:00:16</t>
+          <t>2026-01-09 17:00:16</t>
         </is>
       </c>
       <c r="B384" s="7" t="inlineStr">
@@ -34006,7 +34006,7 @@
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
         <is>
-          <t>2026-01-09 23:36:27</t>
+          <t>2026-01-09 14:36:27</t>
         </is>
       </c>
       <c r="B385" s="7" t="inlineStr">
@@ -34083,8 +34083,88 @@
         </is>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-05 14:21:47</t>
+        </is>
+      </c>
+      <c r="B386" s="7" t="inlineStr">
+        <is>
+          <t>ランク(ソロ/デュオ)</t>
+        </is>
+      </c>
+      <c r="C386" s="10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D386" s="7" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E386" s="7" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F386" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G386" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H386" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I386" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J386" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K386" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="L386" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M386" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N386" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="O386" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P386" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q386" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R386" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S386" s="11" t="n">
+        <v>6751</v>
+      </c>
+      <c r="T386" s="11" t="n">
+        <v>2219</v>
+      </c>
+      <c r="U386" s="6" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V386" s="7" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V385"/>
+  <autoFilter ref="A1:V386"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34095,7 +34175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P385"/>
+  <dimension ref="A1:P386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -34201,7 +34281,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>2026-08-05 23:53:01</t>
+          <t>2026-08-05 14:53:01</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
@@ -34263,7 +34343,7 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>2026-08-05 23:15:09</t>
+          <t>2026-08-05 14:15:09</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
@@ -34325,7 +34405,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03 02:00:01</t>
+          <t>2026-08-02 17:00:01</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -34387,7 +34467,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03 00:22:22</t>
+          <t>2026-08-02 15:22:22</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -34449,7 +34529,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 23:45:22</t>
+          <t>2026-08-02 14:45:22</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -34511,7 +34591,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 18:45:07</t>
+          <t>2026-08-02 09:45:07</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -34573,7 +34653,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 18:20:05</t>
+          <t>2026-08-02 09:20:05</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -34635,7 +34715,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:32</t>
+          <t>2026-08-02 08:49:32</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -34697,7 +34777,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 03:33:03</t>
+          <t>2026-08-01 18:33:03</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -34759,7 +34839,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 02:39:30</t>
+          <t>2026-08-01 17:39:30</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -34821,7 +34901,7 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 04:00:11</t>
+          <t>2026-07-31 19:00:11</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -34883,7 +34963,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 03:30:26</t>
+          <t>2026-07-31 18:30:26</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -34945,7 +35025,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 02:52:16</t>
+          <t>2026-07-31 17:52:16</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
@@ -35007,7 +35087,7 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 01:50:20</t>
+          <t>2026-07-31 16:50:20</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -35069,7 +35149,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 01:16:45</t>
+          <t>2026-07-31 16:16:45</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -35131,7 +35211,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 22:56:19</t>
+          <t>2026-07-31 13:56:19</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -35193,7 +35273,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 22:22:46</t>
+          <t>2026-07-31 13:22:46</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -35255,7 +35335,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 21:49:35</t>
+          <t>2026-07-31 12:49:35</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -35317,7 +35397,7 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 23:51:39</t>
+          <t>2026-07-28 14:51:39</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -35379,7 +35459,7 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 23:05:20</t>
+          <t>2026-07-28 14:05:20</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -35441,7 +35521,7 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>2026-07-27 01:21:51</t>
+          <t>2026-07-26 16:21:51</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -35503,7 +35583,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>2026-07-27 00:43:02</t>
+          <t>2026-07-26 15:43:02</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -35565,7 +35645,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 23:12:09</t>
+          <t>2026-07-25 14:12:09</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -35627,7 +35707,7 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 22:30:57</t>
+          <t>2026-07-25 13:30:57</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -35689,7 +35769,7 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 00:11:55</t>
+          <t>2026-07-24 15:11:55</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
@@ -35751,7 +35831,7 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>2026-07-24 23:25:38</t>
+          <t>2026-07-24 14:25:38</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -35813,7 +35893,7 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>2026-07-22 00:17:56</t>
+          <t>2026-07-21 15:17:56</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
@@ -35875,7 +35955,7 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>2026-07-22 00:04:35</t>
+          <t>2026-07-21 15:04:35</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -35937,7 +36017,7 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 23:25:56</t>
+          <t>2026-07-21 14:25:56</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
@@ -35999,7 +36079,7 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 22:44:36</t>
+          <t>2026-07-21 13:44:36</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
@@ -36061,7 +36141,7 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 22:18:59</t>
+          <t>2026-07-21 13:18:59</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
@@ -36123,7 +36203,7 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>2026-07-20 03:20:20</t>
+          <t>2026-07-19 18:20:20</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -36185,7 +36265,7 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>2026-07-20 02:39:51</t>
+          <t>2026-07-19 17:39:51</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
@@ -36247,7 +36327,7 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:59:14</t>
+          <t>2026-07-18 09:59:14</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
@@ -36309,7 +36389,7 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:21:14</t>
+          <t>2026-07-18 09:21:14</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
@@ -36371,7 +36451,7 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 23:06:28</t>
+          <t>2026-07-16 14:06:28</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -36433,7 +36513,7 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 22:32:42</t>
+          <t>2026-07-16 13:32:42</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
@@ -36495,7 +36575,7 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 00:40:48</t>
+          <t>2026-07-15 15:40:48</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -36557,7 +36637,7 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 23:41:56</t>
+          <t>2026-07-15 14:41:56</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
@@ -36619,7 +36699,7 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 22:58:44</t>
+          <t>2026-07-15 13:58:44</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
@@ -36681,7 +36761,7 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 22:34:16</t>
+          <t>2026-07-15 13:34:16</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
@@ -36743,7 +36823,7 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 23:36:35</t>
+          <t>2026-07-14 14:36:35</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
@@ -36805,7 +36885,7 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 22:49:50</t>
+          <t>2026-07-14 13:49:50</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
@@ -36867,7 +36947,7 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 01:02:29</t>
+          <t>2026-07-13 16:02:29</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
@@ -36929,7 +37009,7 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 00:22:46</t>
+          <t>2026-07-13 15:22:46</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
@@ -36991,7 +37071,7 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 23:51:38</t>
+          <t>2026-07-13 14:51:38</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
@@ -37053,7 +37133,7 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 02:05:19</t>
+          <t>2026-07-12 17:05:19</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
@@ -37115,7 +37195,7 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 01:29:17</t>
+          <t>2026-07-12 16:29:17</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
@@ -37177,7 +37257,7 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 03:11:38</t>
+          <t>2026-07-11 18:11:38</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
@@ -37239,7 +37319,7 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 02:46:15</t>
+          <t>2026-07-11 17:46:15</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
@@ -37301,7 +37381,7 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 03:42:29</t>
+          <t>2026-07-10 18:42:29</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
@@ -37363,7 +37443,7 @@
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 03:06:21</t>
+          <t>2026-07-10 18:06:21</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
@@ -37425,7 +37505,7 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:55:25</t>
+          <t>2026-07-08 17:55:25</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
@@ -37487,7 +37567,7 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:17:09</t>
+          <t>2026-07-08 17:17:09</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
@@ -37549,7 +37629,7 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 02:03:51</t>
+          <t>2026-07-05 17:03:51</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
@@ -37611,7 +37691,7 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 01:07:17</t>
+          <t>2026-07-05 16:07:17</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
@@ -37673,7 +37753,7 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 00:23:00</t>
+          <t>2026-07-05 15:23:00</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
@@ -37735,7 +37815,7 @@
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>2026-07-05 03:21:23</t>
+          <t>2026-07-04 18:21:23</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
@@ -37797,7 +37877,7 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>2026-07-04 03:01:40</t>
+          <t>2026-07-03 18:01:40</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
@@ -37859,7 +37939,7 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>2026-07-03 01:48:19</t>
+          <t>2026-07-02 16:48:19</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
@@ -37921,7 +38001,7 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>2026-07-01 00:21:19</t>
+          <t>2026-06-30 15:21:19</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
@@ -37983,7 +38063,7 @@
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 23:38:16</t>
+          <t>2026-06-30 14:38:16</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
@@ -38045,7 +38125,7 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 01:16:28</t>
+          <t>2026-06-29 16:16:28</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
@@ -38107,7 +38187,7 @@
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 00:34:32</t>
+          <t>2026-06-29 15:34:32</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
@@ -38169,7 +38249,7 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>2026-06-26 00:50:56</t>
+          <t>2026-06-25 15:50:56</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
@@ -38231,7 +38311,7 @@
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>2026-06-26 00:06:40</t>
+          <t>2026-06-25 15:06:40</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
@@ -38293,7 +38373,7 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07:56</t>
+          <t>2026-06-24 17:07:56</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
@@ -38355,7 +38435,7 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 01:33:19</t>
+          <t>2026-06-24 16:33:19</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
@@ -38417,7 +38497,7 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:47:59</t>
+          <t>2026-06-24 15:47:59</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
@@ -38479,7 +38559,7 @@
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:08:31</t>
+          <t>2026-06-24 15:08:31</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
@@ -38541,7 +38621,7 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 23:33:15</t>
+          <t>2026-06-24 14:33:15</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
@@ -38603,7 +38683,7 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 22:39:11</t>
+          <t>2026-06-24 13:39:11</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
@@ -38665,7 +38745,7 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 01:16:06</t>
+          <t>2026-06-22 16:16:06</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
@@ -38727,7 +38807,7 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 00:38:08</t>
+          <t>2026-06-22 15:38:08</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
@@ -38789,7 +38869,7 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 00:29:33</t>
+          <t>2026-06-22 15:29:33</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
@@ -38851,7 +38931,7 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 01:54:04</t>
+          <t>2026-06-18 16:54:04</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
@@ -38913,7 +38993,7 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 01:14:50</t>
+          <t>2026-06-18 16:14:50</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
@@ -38975,7 +39055,7 @@
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 00:35:17</t>
+          <t>2026-06-18 15:35:17</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
@@ -39037,7 +39117,7 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 23:55:50</t>
+          <t>2026-06-18 14:55:50</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
@@ -39099,7 +39179,7 @@
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 00:44:42</t>
+          <t>2026-06-17 15:44:42</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
@@ -39161,7 +39241,7 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 23:57:38</t>
+          <t>2026-06-17 14:57:38</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
@@ -39223,7 +39303,7 @@
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 01:58:55</t>
+          <t>2026-06-16 16:58:55</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
@@ -39285,7 +39365,7 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 01:30:07</t>
+          <t>2026-06-16 16:30:07</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
@@ -39347,7 +39427,7 @@
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 03:10:28</t>
+          <t>2026-06-14 18:10:28</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
@@ -39409,7 +39489,7 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 02:27:52</t>
+          <t>2026-06-14 17:27:52</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
@@ -39471,7 +39551,7 @@
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 01:57:23</t>
+          <t>2026-06-14 16:57:23</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
@@ -39533,7 +39613,7 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 01:27:22</t>
+          <t>2026-06-14 16:27:22</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
@@ -39595,7 +39675,7 @@
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 00:24:35</t>
+          <t>2026-06-14 15:24:35</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
@@ -39657,7 +39737,7 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 23:46:55</t>
+          <t>2026-06-14 14:46:55</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
@@ -39719,7 +39799,7 @@
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 01:41:53</t>
+          <t>2026-06-13 16:41:53</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
@@ -39781,7 +39861,7 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 00:52:58</t>
+          <t>2026-06-13 15:52:58</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
@@ -39843,7 +39923,7 @@
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 00:14:23</t>
+          <t>2026-06-13 15:14:23</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
@@ -39905,7 +39985,7 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 23:45:21</t>
+          <t>2026-06-13 14:45:21</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
@@ -39967,7 +40047,7 @@
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 23:05:32</t>
+          <t>2026-06-13 14:05:32</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
@@ -40029,7 +40109,7 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 01:08:14</t>
+          <t>2026-06-10 16:08:14</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
@@ -40091,7 +40171,7 @@
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:34:35</t>
+          <t>2026-06-10 15:34:35</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
@@ -40153,7 +40233,7 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:09:17</t>
+          <t>2026-06-10 15:09:17</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
@@ -40215,7 +40295,7 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 23:27:53</t>
+          <t>2026-06-10 14:27:53</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
@@ -40277,7 +40357,7 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 00:49:00</t>
+          <t>2026-06-09 15:49:00</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
@@ -40339,7 +40419,7 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>2026-06-06 02:58:51</t>
+          <t>2026-06-05 17:58:51</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
@@ -40401,7 +40481,7 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>2026-06-06 02:15:04</t>
+          <t>2026-06-05 17:15:04</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
@@ -40463,7 +40543,7 @@
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 23:49:14</t>
+          <t>2026-06-04 14:49:14</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
@@ -40525,7 +40605,7 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 21:40:04</t>
+          <t>2026-06-04 12:40:04</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
@@ -40587,7 +40667,7 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 21:17:24</t>
+          <t>2026-06-04 12:17:24</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
@@ -40649,7 +40729,7 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 01:06:27</t>
+          <t>2026-06-03 16:06:27</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
@@ -40711,7 +40791,7 @@
     <row r="107">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 00:31:09</t>
+          <t>2026-06-03 15:31:09</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
@@ -40773,7 +40853,7 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 23:53:57</t>
+          <t>2026-06-03 14:53:57</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
@@ -40835,7 +40915,7 @@
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 22:44:02</t>
+          <t>2026-06-03 13:44:02</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
@@ -40897,7 +40977,7 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>2026-06-02 22:49:11</t>
+          <t>2026-06-02 13:49:11</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
@@ -40959,7 +41039,7 @@
     <row r="111">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:56:06</t>
+          <t>2026-06-01 14:56:06</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
@@ -41021,7 +41101,7 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:20:26</t>
+          <t>2026-06-01 14:20:26</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
@@ -41083,7 +41163,7 @@
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:01:06</t>
+          <t>2026-06-01 14:01:06</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
@@ -41145,7 +41225,7 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>2026-05-31 03:01:04</t>
+          <t>2026-05-30 18:01:04</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
@@ -41207,7 +41287,7 @@
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>2026-05-31 02:13:41</t>
+          <t>2026-05-30 17:13:41</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
@@ -41269,7 +41349,7 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 23:00:40</t>
+          <t>2026-05-25 14:00:40</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
@@ -41331,7 +41411,7 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 01:55:47</t>
+          <t>2026-05-24 16:55:47</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
@@ -41393,7 +41473,7 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 01:24:22</t>
+          <t>2026-05-24 16:24:22</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
@@ -41455,7 +41535,7 @@
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 23:49:25</t>
+          <t>2026-05-24 14:49:25</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
@@ -41517,7 +41597,7 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 03:13:39</t>
+          <t>2026-05-23 18:13:39</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
@@ -41579,7 +41659,7 @@
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 02:41:52</t>
+          <t>2026-05-23 17:41:52</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
@@ -41641,7 +41721,7 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 23:19:04</t>
+          <t>2026-05-23 14:19:04</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
@@ -41703,7 +41783,7 @@
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 22:43:20</t>
+          <t>2026-05-23 13:43:20</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
@@ -41765,7 +41845,7 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 15:54:19</t>
+          <t>2026-05-23 06:54:19</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
@@ -41827,7 +41907,7 @@
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 02:25:24</t>
+          <t>2026-05-22 17:25:24</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
@@ -41889,7 +41969,7 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 01:29:23</t>
+          <t>2026-05-21 16:29:23</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
@@ -41951,7 +42031,7 @@
     <row r="127">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 00:48:49</t>
+          <t>2026-05-21 15:48:49</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
@@ -42013,7 +42093,7 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:45</t>
+          <t>2026-05-21 15:00:45</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
@@ -42075,7 +42155,7 @@
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 23:22:44</t>
+          <t>2026-05-21 14:22:44</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
@@ -42137,7 +42217,7 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 00:05:15</t>
+          <t>2026-05-20 15:05:15</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
@@ -42199,7 +42279,7 @@
     <row r="131">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 23:43:50</t>
+          <t>2026-05-20 14:43:50</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
@@ -42261,7 +42341,7 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 22:57:45</t>
+          <t>2026-05-20 13:57:45</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
@@ -42323,7 +42403,7 @@
     <row r="133">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 01:25:45</t>
+          <t>2026-05-19 16:25:45</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
@@ -42385,7 +42465,7 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 00:46:42</t>
+          <t>2026-05-19 15:46:42</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
@@ -42447,7 +42527,7 @@
     <row r="135">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>2026-05-18 22:56:39</t>
+          <t>2026-05-18 13:56:39</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
@@ -42509,7 +42589,7 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 01:35:56</t>
+          <t>2026-05-14 16:35:56</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
@@ -42571,7 +42651,7 @@
     <row r="137">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 01:17:05</t>
+          <t>2026-05-14 16:17:05</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
@@ -42633,7 +42713,7 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 00:05:48</t>
+          <t>2026-05-14 15:05:48</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
@@ -42695,7 +42775,7 @@
     <row r="139">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>2026-05-14 01:25:38</t>
+          <t>2026-05-13 16:25:38</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
@@ -42757,7 +42837,7 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>2026-05-12 00:19:57</t>
+          <t>2026-05-11 15:19:57</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
@@ -42819,7 +42899,7 @@
     <row r="141">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 23:54:15</t>
+          <t>2026-05-11 14:54:15</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
@@ -42881,7 +42961,7 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 23:14:30</t>
+          <t>2026-05-11 14:14:30</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
@@ -42943,7 +43023,7 @@
     <row r="143">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 22:37:05</t>
+          <t>2026-05-11 13:37:05</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
@@ -43005,7 +43085,7 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 21:53:13</t>
+          <t>2026-05-11 12:53:13</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
@@ -43067,7 +43147,7 @@
     <row r="145">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 00:04:01</t>
+          <t>2026-05-10 15:04:01</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
@@ -43129,7 +43209,7 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:54:24</t>
+          <t>2026-05-09 16:54:24</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
@@ -43191,7 +43271,7 @@
     <row r="147">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:22:50</t>
+          <t>2026-05-09 16:22:50</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
@@ -43253,7 +43333,7 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 00:26:16</t>
+          <t>2026-05-09 15:26:16</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
@@ -43315,7 +43395,7 @@
     <row r="149">
       <c r="A149" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 23:38:30</t>
+          <t>2026-05-09 14:38:30</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
@@ -43377,7 +43457,7 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 22:50:20</t>
+          <t>2026-05-09 13:50:20</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
@@ -43439,7 +43519,7 @@
     <row r="151">
       <c r="A151" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 22:13:25</t>
+          <t>2026-05-09 13:13:25</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
@@ -43501,7 +43581,7 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 20:00:11</t>
+          <t>2026-05-09 11:00:11</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
@@ -43563,7 +43643,7 @@
     <row r="153">
       <c r="A153" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 19:10:28</t>
+          <t>2026-05-09 10:10:28</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
@@ -43625,7 +43705,7 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 02:17:27</t>
+          <t>2026-05-08 17:17:27</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
@@ -43687,7 +43767,7 @@
     <row r="155">
       <c r="A155" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 01:38:25</t>
+          <t>2026-05-08 16:38:25</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
@@ -43749,7 +43829,7 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 00:58:58</t>
+          <t>2026-05-08 15:58:58</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
@@ -43811,7 +43891,7 @@
     <row r="157">
       <c r="A157" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 00:37:55</t>
+          <t>2026-05-08 15:37:55</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
@@ -43873,7 +43953,7 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 01:48:31</t>
+          <t>2026-05-07 16:48:31</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
@@ -43935,7 +44015,7 @@
     <row r="159">
       <c r="A159" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 01:02:52</t>
+          <t>2026-05-07 16:02:52</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
@@ -43997,7 +44077,7 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 00:23:29</t>
+          <t>2026-05-07 15:23:29</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
@@ -44059,7 +44139,7 @@
     <row r="161">
       <c r="A161" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 01:30:56</t>
+          <t>2026-05-06 16:30:56</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
@@ -44121,7 +44201,7 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 00:42:16</t>
+          <t>2026-05-06 15:42:16</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
@@ -44183,7 +44263,7 @@
     <row r="163">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 23:44:04</t>
+          <t>2026-05-06 14:44:04</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
@@ -44245,7 +44325,7 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:13:52</t>
+          <t>2026-05-06 09:13:52</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
@@ -44307,7 +44387,7 @@
     <row r="165">
       <c r="A165" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:05:08</t>
+          <t>2026-05-06 09:05:08</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
@@ -44369,7 +44449,7 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 17:22:30</t>
+          <t>2026-05-06 08:22:30</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
@@ -44431,7 +44511,7 @@
     <row r="167">
       <c r="A167" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 16:28:42</t>
+          <t>2026-05-06 07:28:42</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
@@ -44493,7 +44573,7 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 03:16:57</t>
+          <t>2026-05-05 18:16:57</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
@@ -44555,7 +44635,7 @@
     <row r="169">
       <c r="A169" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:32:40</t>
+          <t>2026-05-05 17:32:40</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
@@ -44617,7 +44697,7 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:23:28</t>
+          <t>2026-05-05 17:23:28</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
@@ -44679,7 +44759,7 @@
     <row r="171">
       <c r="A171" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 01:48:28</t>
+          <t>2026-05-05 16:48:28</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
@@ -44741,7 +44821,7 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 00:52:33</t>
+          <t>2026-05-05 15:52:33</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
@@ -44803,7 +44883,7 @@
     <row r="173">
       <c r="A173" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 17:43:06</t>
+          <t>2026-05-05 08:43:06</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
@@ -44865,7 +44945,7 @@
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>2026-05-03 00:36:42</t>
+          <t>2026-05-02 15:36:42</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
@@ -44927,7 +45007,7 @@
     <row r="175">
       <c r="A175" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 23:51:09</t>
+          <t>2026-05-02 14:51:09</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
@@ -44989,7 +45069,7 @@
     <row r="176">
       <c r="A176" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 22:15:10</t>
+          <t>2026-05-02 13:15:10</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
@@ -45051,7 +45131,7 @@
     <row r="177">
       <c r="A177" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 21:29:49</t>
+          <t>2026-05-02 12:29:49</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
@@ -45113,7 +45193,7 @@
     <row r="178">
       <c r="A178" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 01:39:42</t>
+          <t>2026-04-30 16:39:42</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
@@ -45175,7 +45255,7 @@
     <row r="179">
       <c r="A179" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 01:01:34</t>
+          <t>2026-04-30 16:01:34</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
@@ -45237,7 +45317,7 @@
     <row r="180">
       <c r="A180" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 00:24:48</t>
+          <t>2026-04-30 15:24:48</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
@@ -45299,7 +45379,7 @@
     <row r="181">
       <c r="A181" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 23:37:10</t>
+          <t>2026-04-30 14:37:10</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
@@ -45361,7 +45441,7 @@
     <row r="182">
       <c r="A182" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 22:58:06</t>
+          <t>2026-04-30 13:58:06</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
@@ -45423,7 +45503,7 @@
     <row r="183">
       <c r="A183" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 03:29:33</t>
+          <t>2026-04-29 18:29:33</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
@@ -45485,7 +45565,7 @@
     <row r="184">
       <c r="A184" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 02:54:07</t>
+          <t>2026-04-29 17:54:07</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
@@ -45547,7 +45627,7 @@
     <row r="185">
       <c r="A185" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 02:20:58</t>
+          <t>2026-04-29 17:20:58</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
@@ -45609,7 +45689,7 @@
     <row r="186">
       <c r="A186" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 01:42:01</t>
+          <t>2026-04-29 16:42:01</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
@@ -45671,7 +45751,7 @@
     <row r="187">
       <c r="A187" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 01:03:17</t>
+          <t>2026-04-29 16:03:17</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
@@ -45733,7 +45813,7 @@
     <row r="188">
       <c r="A188" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 00:19:47</t>
+          <t>2026-04-29 15:19:47</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
@@ -45795,7 +45875,7 @@
     <row r="189">
       <c r="A189" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 23:29:53</t>
+          <t>2026-04-29 14:29:53</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
@@ -45857,7 +45937,7 @@
     <row r="190">
       <c r="A190" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:59:49</t>
+          <t>2026-04-29 13:59:49</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
@@ -45919,7 +45999,7 @@
     <row r="191">
       <c r="A191" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:38:22</t>
+          <t>2026-04-29 13:38:22</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
@@ -45981,7 +46061,7 @@
     <row r="192">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:44</t>
+          <t>2026-04-29 13:17:44</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
@@ -46043,7 +46123,7 @@
     <row r="193">
       <c r="A193" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 03:28:56</t>
+          <t>2026-04-28 18:28:56</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
@@ -46105,7 +46185,7 @@
     <row r="194">
       <c r="A194" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:58:50</t>
+          <t>2026-04-28 17:58:50</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
@@ -46167,7 +46247,7 @@
     <row r="195">
       <c r="A195" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:29:43</t>
+          <t>2026-04-28 17:29:43</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
@@ -46229,7 +46309,7 @@
     <row r="196">
       <c r="A196" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 01:38:43</t>
+          <t>2026-04-28 16:38:43</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
@@ -46291,7 +46371,7 @@
     <row r="197">
       <c r="A197" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:54</t>
+          <t>2026-04-28 15:58:54</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
@@ -46353,7 +46433,7 @@
     <row r="198">
       <c r="A198" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:31:32</t>
+          <t>2026-04-28 15:31:32</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
@@ -46415,7 +46495,7 @@
     <row r="199">
       <c r="A199" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:04:20</t>
+          <t>2026-04-28 15:04:20</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
@@ -46477,7 +46557,7 @@
     <row r="200">
       <c r="A200" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 23:37:27</t>
+          <t>2026-04-28 14:37:27</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
@@ -46539,7 +46619,7 @@
     <row r="201">
       <c r="A201" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 23:09:10</t>
+          <t>2026-04-28 14:09:10</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
@@ -46601,7 +46681,7 @@
     <row r="202">
       <c r="A202" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:59:25</t>
+          <t>2026-04-27 14:59:25</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
@@ -46663,7 +46743,7 @@
     <row r="203">
       <c r="A203" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:49:35</t>
+          <t>2026-04-27 14:49:35</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
@@ -46725,7 +46805,7 @@
     <row r="204">
       <c r="A204" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 22:55:34</t>
+          <t>2026-04-27 13:55:34</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
@@ -46787,7 +46867,7 @@
     <row r="205">
       <c r="A205" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 22:04:13</t>
+          <t>2026-04-27 13:04:13</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
@@ -46849,7 +46929,7 @@
     <row r="206">
       <c r="A206" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 02:49:02</t>
+          <t>2026-04-24 17:49:02</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
@@ -46911,7 +46991,7 @@
     <row r="207">
       <c r="A207" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 02:03:56</t>
+          <t>2026-04-24 17:03:56</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
@@ -46973,7 +47053,7 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 01:37:00</t>
+          <t>2026-04-24 16:37:00</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
@@ -47035,7 +47115,7 @@
     <row r="209">
       <c r="A209" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:33:59</t>
+          <t>2026-04-23 15:33:59</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
@@ -47097,7 +47177,7 @@
     <row r="210">
       <c r="A210" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:22:46</t>
+          <t>2026-04-23 15:22:46</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
@@ -47159,7 +47239,7 @@
     <row r="211">
       <c r="A211" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:12:54</t>
+          <t>2026-04-23 15:12:54</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
@@ -47221,7 +47301,7 @@
     <row r="212">
       <c r="A212" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 22:36:03</t>
+          <t>2026-04-23 13:36:03</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
@@ -47283,7 +47363,7 @@
     <row r="213">
       <c r="A213" s="13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:58:57</t>
+          <t>2026-04-13 15:58:57</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
@@ -47345,7 +47425,7 @@
     <row r="214">
       <c r="A214" s="13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:09:08</t>
+          <t>2026-04-13 15:09:08</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
@@ -47407,7 +47487,7 @@
     <row r="215">
       <c r="A215" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 01:48:02</t>
+          <t>2026-04-12 16:48:02</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
@@ -47469,7 +47549,7 @@
     <row r="216">
       <c r="A216" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 01:17:58</t>
+          <t>2026-04-12 16:17:58</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
@@ -47531,7 +47611,7 @@
     <row r="217">
       <c r="A217" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 00:41:20</t>
+          <t>2026-04-12 15:41:20</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
@@ -47593,7 +47673,7 @@
     <row r="218">
       <c r="A218" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 23:18:06</t>
+          <t>2026-04-09 14:18:06</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
@@ -47655,7 +47735,7 @@
     <row r="219">
       <c r="A219" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 22:52:44</t>
+          <t>2026-04-09 13:52:44</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
@@ -47717,7 +47797,7 @@
     <row r="220">
       <c r="A220" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 22:27:45</t>
+          <t>2026-04-09 13:27:45</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
@@ -47779,7 +47859,7 @@
     <row r="221">
       <c r="A221" s="13" t="inlineStr">
         <is>
-          <t>2026-04-08 01:10:31</t>
+          <t>2026-04-07 16:10:31</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
@@ -47841,7 +47921,7 @@
     <row r="222">
       <c r="A222" s="13" t="inlineStr">
         <is>
-          <t>2026-04-08 00:29:19</t>
+          <t>2026-04-07 15:29:19</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
@@ -47903,7 +47983,7 @@
     <row r="223">
       <c r="A223" s="13" t="inlineStr">
         <is>
-          <t>2026-04-04 04:36:31</t>
+          <t>2026-04-03 19:36:31</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
@@ -47965,7 +48045,7 @@
     <row r="224">
       <c r="A224" s="13" t="inlineStr">
         <is>
-          <t>2026-04-04 04:16:32</t>
+          <t>2026-04-03 19:16:32</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
@@ -48027,7 +48107,7 @@
     <row r="225">
       <c r="A225" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 04:24:43</t>
+          <t>2026-03-27 19:24:43</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
@@ -48089,7 +48169,7 @@
     <row r="226">
       <c r="A226" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:38:31</t>
+          <t>2026-03-27 18:38:31</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
@@ -48151,7 +48231,7 @@
     <row r="227">
       <c r="A227" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:17:50</t>
+          <t>2026-03-27 18:17:50</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
@@ -48213,7 +48293,7 @@
     <row r="228">
       <c r="A228" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 02:43:19</t>
+          <t>2026-03-27 17:43:19</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
@@ -48275,7 +48355,7 @@
     <row r="229">
       <c r="A229" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 02:15:18</t>
+          <t>2026-03-27 17:15:18</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
@@ -48337,7 +48417,7 @@
     <row r="230">
       <c r="A230" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 23:18:12</t>
+          <t>2026-03-25 14:18:12</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
@@ -48399,7 +48479,7 @@
     <row r="231">
       <c r="A231" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 00:01:49</t>
+          <t>2026-03-24 15:01:49</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
@@ -48461,7 +48541,7 @@
     <row r="232">
       <c r="A232" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 23:25:16</t>
+          <t>2026-03-24 14:25:16</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
@@ -48523,7 +48603,7 @@
     <row r="233">
       <c r="A233" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 23:02:52</t>
+          <t>2026-03-24 14:02:52</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
@@ -48585,7 +48665,7 @@
     <row r="234">
       <c r="A234" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 22:26:26</t>
+          <t>2026-03-24 13:26:26</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
@@ -48647,7 +48727,7 @@
     <row r="235">
       <c r="A235" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 00:56:18</t>
+          <t>2026-03-23 15:56:18</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
@@ -48709,7 +48789,7 @@
     <row r="236">
       <c r="A236" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 00:29:29</t>
+          <t>2026-03-23 15:29:29</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
@@ -48771,7 +48851,7 @@
     <row r="237">
       <c r="A237" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 23:51:11</t>
+          <t>2026-03-22 14:51:11</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
@@ -48833,7 +48913,7 @@
     <row r="238">
       <c r="A238" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 01:04:36</t>
+          <t>2026-03-21 16:04:36</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
@@ -48895,7 +48975,7 @@
     <row r="239">
       <c r="A239" s="13" t="inlineStr">
         <is>
-          <t>2026-03-21 02:55:49</t>
+          <t>2026-03-20 17:55:49</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
@@ -48957,7 +49037,7 @@
     <row r="240">
       <c r="A240" s="13" t="inlineStr">
         <is>
-          <t>2026-03-18 00:07:07</t>
+          <t>2026-03-17 15:07:07</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
@@ -49019,7 +49099,7 @@
     <row r="241">
       <c r="A241" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 23:24:05</t>
+          <t>2026-03-17 14:24:05</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
@@ -49081,7 +49161,7 @@
     <row r="242">
       <c r="A242" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 02:00:50</t>
+          <t>2026-03-16 17:00:50</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
@@ -49143,7 +49223,7 @@
     <row r="243">
       <c r="A243" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 01:33:08</t>
+          <t>2026-03-16 16:33:08</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
@@ -49205,7 +49285,7 @@
     <row r="244">
       <c r="A244" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 23:28:09</t>
+          <t>2026-03-16 14:28:09</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
@@ -49267,7 +49347,7 @@
     <row r="245">
       <c r="A245" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 01:32:22</t>
+          <t>2026-03-15 16:32:22</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
@@ -49329,7 +49409,7 @@
     <row r="246">
       <c r="A246" s="13" t="inlineStr">
         <is>
-          <t>2026-03-14 01:43:49</t>
+          <t>2026-03-13 16:43:49</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
@@ -49391,7 +49471,7 @@
     <row r="247">
       <c r="A247" s="13" t="inlineStr">
         <is>
-          <t>2026-03-14 01:19:35</t>
+          <t>2026-03-13 16:19:35</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
@@ -49453,7 +49533,7 @@
     <row r="248">
       <c r="A248" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 23:45:27</t>
+          <t>2026-03-12 14:45:27</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
@@ -49515,7 +49595,7 @@
     <row r="249">
       <c r="A249" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 23:02:09</t>
+          <t>2026-03-12 14:02:09</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
@@ -49577,7 +49657,7 @@
     <row r="250">
       <c r="A250" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 22:42:59</t>
+          <t>2026-03-12 13:42:59</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
@@ -49639,7 +49719,7 @@
     <row r="251">
       <c r="A251" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 01:39:10</t>
+          <t>2026-03-11 16:39:10</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
@@ -49701,7 +49781,7 @@
     <row r="252">
       <c r="A252" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:43:21</t>
+          <t>2026-03-11 15:43:21</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
@@ -49763,7 +49843,7 @@
     <row r="253">
       <c r="A253" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:04:25</t>
+          <t>2026-03-11 15:04:25</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
@@ -49825,7 +49905,7 @@
     <row r="254">
       <c r="A254" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 22:54:02</t>
+          <t>2026-03-11 13:54:02</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
@@ -49887,7 +49967,7 @@
     <row r="255">
       <c r="A255" s="13" t="inlineStr">
         <is>
-          <t>2026-03-08 02:01:53</t>
+          <t>2026-03-07 17:01:53</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
@@ -49949,7 +50029,7 @@
     <row r="256">
       <c r="A256" s="13" t="inlineStr">
         <is>
-          <t>2026-03-02 02:18:59</t>
+          <t>2026-03-01 17:18:59</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
@@ -50011,7 +50091,7 @@
     <row r="257">
       <c r="A257" s="13" t="inlineStr">
         <is>
-          <t>2026-02-24 01:40:38</t>
+          <t>2026-02-23 16:40:38</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
@@ -50073,7 +50153,7 @@
     <row r="258">
       <c r="A258" s="13" t="inlineStr">
         <is>
-          <t>2026-02-24 00:10:31</t>
+          <t>2026-02-23 15:10:31</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
@@ -50135,7 +50215,7 @@
     <row r="259">
       <c r="A259" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 23:33:47</t>
+          <t>2026-02-23 14:33:47</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
@@ -50197,7 +50277,7 @@
     <row r="260">
       <c r="A260" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 22:40:54</t>
+          <t>2026-02-23 13:40:54</t>
         </is>
       </c>
       <c r="B260" s="13" t="inlineStr">
@@ -50259,7 +50339,7 @@
     <row r="261">
       <c r="A261" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 21:58:56</t>
+          <t>2026-02-23 12:58:56</t>
         </is>
       </c>
       <c r="B261" s="13" t="inlineStr">
@@ -50321,7 +50401,7 @@
     <row r="262">
       <c r="A262" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 19:21:48</t>
+          <t>2026-02-23 10:21:48</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
@@ -50383,7 +50463,7 @@
     <row r="263">
       <c r="A263" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 17:17:13</t>
+          <t>2026-02-23 08:17:13</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
@@ -50445,7 +50525,7 @@
     <row r="264">
       <c r="A264" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 04:22:01</t>
+          <t>2026-02-22 19:22:01</t>
         </is>
       </c>
       <c r="B264" s="13" t="inlineStr">
@@ -50507,7 +50587,7 @@
     <row r="265">
       <c r="A265" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 03:23:51</t>
+          <t>2026-02-22 18:23:51</t>
         </is>
       </c>
       <c r="B265" s="13" t="inlineStr">
@@ -50569,7 +50649,7 @@
     <row r="266">
       <c r="A266" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 02:58:18</t>
+          <t>2026-02-22 17:58:18</t>
         </is>
       </c>
       <c r="B266" s="13" t="inlineStr">
@@ -50631,7 +50711,7 @@
     <row r="267">
       <c r="A267" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 02:29:21</t>
+          <t>2026-02-22 17:29:21</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
@@ -50693,7 +50773,7 @@
     <row r="268">
       <c r="A268" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 01:59:09</t>
+          <t>2026-02-22 16:59:09</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
@@ -50755,7 +50835,7 @@
     <row r="269">
       <c r="A269" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 01:32:08</t>
+          <t>2026-02-22 16:32:08</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
@@ -50817,7 +50897,7 @@
     <row r="270">
       <c r="A270" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 03:34:36</t>
+          <t>2026-02-20 18:34:36</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
@@ -50879,7 +50959,7 @@
     <row r="271">
       <c r="A271" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 02:57:13</t>
+          <t>2026-02-20 17:57:13</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
@@ -50941,7 +51021,7 @@
     <row r="272">
       <c r="A272" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 02:19:01</t>
+          <t>2026-02-20 17:19:01</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
@@ -51003,7 +51083,7 @@
     <row r="273">
       <c r="A273" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 01:41:10</t>
+          <t>2026-02-20 16:41:10</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
@@ -51065,7 +51145,7 @@
     <row r="274">
       <c r="A274" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 00:57:47</t>
+          <t>2026-02-20 15:57:47</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
@@ -51127,7 +51207,7 @@
     <row r="275">
       <c r="A275" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 00:39:52</t>
+          <t>2026-02-20 15:39:52</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
@@ -51189,7 +51269,7 @@
     <row r="276">
       <c r="A276" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 01:21:13</t>
+          <t>2026-02-19 16:21:13</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
@@ -51251,7 +51331,7 @@
     <row r="277">
       <c r="A277" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 00:33:10</t>
+          <t>2026-02-19 15:33:10</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
@@ -51313,7 +51393,7 @@
     <row r="278">
       <c r="A278" s="13" t="inlineStr">
         <is>
-          <t>2026-02-18 00:37:38</t>
+          <t>2026-02-17 15:37:38</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
@@ -51375,7 +51455,7 @@
     <row r="279">
       <c r="A279" s="13" t="inlineStr">
         <is>
-          <t>2026-02-17 23:58:39</t>
+          <t>2026-02-17 14:58:39</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
@@ -51437,7 +51517,7 @@
     <row r="280">
       <c r="A280" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 02:24:16</t>
+          <t>2026-02-15 17:24:16</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
@@ -51499,7 +51579,7 @@
     <row r="281">
       <c r="A281" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 01:47:19</t>
+          <t>2026-02-15 16:47:19</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
@@ -51561,7 +51641,7 @@
     <row r="282">
       <c r="A282" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 00:56:43</t>
+          <t>2026-02-15 15:56:43</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
@@ -51623,7 +51703,7 @@
     <row r="283">
       <c r="A283" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 00:26:20</t>
+          <t>2026-02-15 15:26:20</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
@@ -51685,7 +51765,7 @@
     <row r="284">
       <c r="A284" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 23:48:44</t>
+          <t>2026-02-15 14:48:44</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
@@ -51747,7 +51827,7 @@
     <row r="285">
       <c r="A285" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 04:17:17</t>
+          <t>2026-02-14 19:17:17</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
@@ -51809,7 +51889,7 @@
     <row r="286">
       <c r="A286" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 03:53:01</t>
+          <t>2026-02-14 18:53:01</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
@@ -51871,7 +51951,7 @@
     <row r="287">
       <c r="A287" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:59:46</t>
+          <t>2026-02-14 17:59:46</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
@@ -51933,7 +52013,7 @@
     <row r="288">
       <c r="A288" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:26:42</t>
+          <t>2026-02-14 17:26:42</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
@@ -51995,7 +52075,7 @@
     <row r="289">
       <c r="A289" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:00:09</t>
+          <t>2026-02-14 17:00:09</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
@@ -52057,7 +52137,7 @@
     <row r="290">
       <c r="A290" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 01:39:16</t>
+          <t>2026-02-14 16:39:16</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
@@ -52119,7 +52199,7 @@
     <row r="291">
       <c r="A291" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 00:56:51</t>
+          <t>2026-02-14 15:56:51</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
@@ -52181,7 +52261,7 @@
     <row r="292">
       <c r="A292" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 23:52:26</t>
+          <t>2026-02-14 14:52:26</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
@@ -52243,7 +52323,7 @@
     <row r="293">
       <c r="A293" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 23:14:55</t>
+          <t>2026-02-14 14:14:55</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
@@ -52305,7 +52385,7 @@
     <row r="294">
       <c r="A294" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 04:19:58</t>
+          <t>2026-02-13 19:19:58</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
@@ -52367,7 +52447,7 @@
     <row r="295">
       <c r="A295" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 03:37:53</t>
+          <t>2026-02-13 18:37:53</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
@@ -52429,7 +52509,7 @@
     <row r="296">
       <c r="A296" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 03:03:31</t>
+          <t>2026-02-13 18:03:31</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
@@ -52491,7 +52571,7 @@
     <row r="297">
       <c r="A297" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 02:08:36</t>
+          <t>2026-02-13 17:08:36</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
@@ -52553,7 +52633,7 @@
     <row r="298">
       <c r="A298" s="13" t="inlineStr">
         <is>
-          <t>2026-02-12 00:20:03</t>
+          <t>2026-02-11 15:20:03</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
@@ -52615,7 +52695,7 @@
     <row r="299">
       <c r="A299" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 03:05:03</t>
+          <t>2026-02-10 18:05:03</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
@@ -52677,7 +52757,7 @@
     <row r="300">
       <c r="A300" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 02:14:02</t>
+          <t>2026-02-10 17:14:02</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
@@ -52739,7 +52819,7 @@
     <row r="301">
       <c r="A301" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 01:33:21</t>
+          <t>2026-02-10 16:33:21</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
@@ -52801,7 +52881,7 @@
     <row r="302">
       <c r="A302" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 01:01:41</t>
+          <t>2026-02-10 16:01:41</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
@@ -52863,7 +52943,7 @@
     <row r="303">
       <c r="A303" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 01:49:32</t>
+          <t>2026-02-09 16:49:32</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
@@ -52925,7 +53005,7 @@
     <row r="304">
       <c r="A304" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 01:42:29</t>
+          <t>2026-02-09 16:42:29</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
@@ -52987,7 +53067,7 @@
     <row r="305">
       <c r="A305" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 23:44:10</t>
+          <t>2026-02-09 14:44:10</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
@@ -53049,7 +53129,7 @@
     <row r="306">
       <c r="A306" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 23:00:28</t>
+          <t>2026-02-09 14:00:28</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
@@ -53111,7 +53191,7 @@
     <row r="307">
       <c r="A307" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 00:27:49</t>
+          <t>2026-02-08 15:27:49</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
@@ -53173,7 +53253,7 @@
     <row r="308">
       <c r="A308" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 00:16:42</t>
+          <t>2026-02-08 15:16:42</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
@@ -53235,7 +53315,7 @@
     <row r="309">
       <c r="A309" s="13" t="inlineStr">
         <is>
-          <t>2026-02-08 04:04:43</t>
+          <t>2026-02-07 19:04:43</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
@@ -53297,7 +53377,7 @@
     <row r="310">
       <c r="A310" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 03:13:11</t>
+          <t>2026-02-06 18:13:11</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
@@ -53359,7 +53439,7 @@
     <row r="311">
       <c r="A311" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 02:19:42</t>
+          <t>2026-02-06 17:19:42</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
@@ -53421,7 +53501,7 @@
     <row r="312">
       <c r="A312" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 01:37:36</t>
+          <t>2026-02-06 16:37:36</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
@@ -53483,7 +53563,7 @@
     <row r="313">
       <c r="A313" s="13" t="inlineStr">
         <is>
-          <t>2026-02-03 23:04:49</t>
+          <t>2026-02-03 14:04:49</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
@@ -53545,7 +53625,7 @@
     <row r="314">
       <c r="A314" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 23:21:38</t>
+          <t>2026-02-02 14:21:38</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
@@ -53607,7 +53687,7 @@
     <row r="315">
       <c r="A315" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 03:08:17</t>
+          <t>2026-02-01 18:08:17</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
@@ -53669,7 +53749,7 @@
     <row r="316">
       <c r="A316" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 02:41:55</t>
+          <t>2026-02-01 17:41:55</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
@@ -53731,7 +53811,7 @@
     <row r="317">
       <c r="A317" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 02:09:57</t>
+          <t>2026-02-01 17:09:57</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
@@ -53793,7 +53873,7 @@
     <row r="318">
       <c r="A318" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 01:41:49</t>
+          <t>2026-02-01 16:41:49</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
@@ -53855,7 +53935,7 @@
     <row r="319">
       <c r="A319" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 02:22:13</t>
+          <t>2026-01-31 17:22:13</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
@@ -53917,7 +53997,7 @@
     <row r="320">
       <c r="A320" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 01:20:54</t>
+          <t>2026-01-31 16:20:54</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
@@ -53979,7 +54059,7 @@
     <row r="321">
       <c r="A321" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 01:09:32</t>
+          <t>2026-01-31 16:09:32</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
@@ -54041,7 +54121,7 @@
     <row r="322">
       <c r="A322" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 00:29:37</t>
+          <t>2026-01-31 15:29:37</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
@@ -54103,7 +54183,7 @@
     <row r="323">
       <c r="A323" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 00:03:50</t>
+          <t>2026-01-31 15:03:50</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
@@ -54165,7 +54245,7 @@
     <row r="324">
       <c r="A324" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 23:15:28</t>
+          <t>2026-01-31 14:15:28</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
@@ -54227,7 +54307,7 @@
     <row r="325">
       <c r="A325" s="13" t="inlineStr">
         <is>
-          <t>2026-01-29 00:36:39</t>
+          <t>2026-01-28 15:36:39</t>
         </is>
       </c>
       <c r="B325" s="13" t="inlineStr">
@@ -54289,7 +54369,7 @@
     <row r="326">
       <c r="A326" s="13" t="inlineStr">
         <is>
-          <t>2026-01-29 00:02:45</t>
+          <t>2026-01-28 15:02:45</t>
         </is>
       </c>
       <c r="B326" s="13" t="inlineStr">
@@ -54351,7 +54431,7 @@
     <row r="327">
       <c r="A327" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 23:26:47</t>
+          <t>2026-01-28 14:26:47</t>
         </is>
       </c>
       <c r="B327" s="13" t="inlineStr">
@@ -54413,7 +54493,7 @@
     <row r="328">
       <c r="A328" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 23:04:33</t>
+          <t>2026-01-28 14:04:33</t>
         </is>
       </c>
       <c r="B328" s="13" t="inlineStr">
@@ -54475,7 +54555,7 @@
     <row r="329">
       <c r="A329" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 00:33:31</t>
+          <t>2026-01-27 15:33:31</t>
         </is>
       </c>
       <c r="B329" s="13" t="inlineStr">
@@ -54537,7 +54617,7 @@
     <row r="330">
       <c r="A330" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 23:59:21</t>
+          <t>2026-01-27 14:59:21</t>
         </is>
       </c>
       <c r="B330" s="13" t="inlineStr">
@@ -54599,7 +54679,7 @@
     <row r="331">
       <c r="A331" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 23:08:33</t>
+          <t>2026-01-27 14:08:33</t>
         </is>
       </c>
       <c r="B331" s="13" t="inlineStr">
@@ -54661,7 +54741,7 @@
     <row r="332">
       <c r="A332" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 23:28:17</t>
+          <t>2026-01-25 14:28:17</t>
         </is>
       </c>
       <c r="B332" s="13" t="inlineStr">
@@ -54723,7 +54803,7 @@
     <row r="333">
       <c r="A333" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 22:56:22</t>
+          <t>2026-01-25 13:56:22</t>
         </is>
       </c>
       <c r="B333" s="13" t="inlineStr">
@@ -54785,7 +54865,7 @@
     <row r="334">
       <c r="A334" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 22:28:25</t>
+          <t>2026-01-25 13:28:25</t>
         </is>
       </c>
       <c r="B334" s="13" t="inlineStr">
@@ -54847,7 +54927,7 @@
     <row r="335">
       <c r="A335" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 21:42:03</t>
+          <t>2026-01-25 12:42:03</t>
         </is>
       </c>
       <c r="B335" s="13" t="inlineStr">
@@ -54909,7 +54989,7 @@
     <row r="336">
       <c r="A336" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 19:38:23</t>
+          <t>2026-01-25 10:38:23</t>
         </is>
       </c>
       <c r="B336" s="13" t="inlineStr">
@@ -54971,7 +55051,7 @@
     <row r="337">
       <c r="A337" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 18:56:35</t>
+          <t>2026-01-25 09:56:35</t>
         </is>
       </c>
       <c r="B337" s="13" t="inlineStr">
@@ -55033,7 +55113,7 @@
     <row r="338">
       <c r="A338" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 18:29:19</t>
+          <t>2026-01-25 09:29:19</t>
         </is>
       </c>
       <c r="B338" s="13" t="inlineStr">
@@ -55095,7 +55175,7 @@
     <row r="339">
       <c r="A339" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 17:14:05</t>
+          <t>2026-01-25 08:14:05</t>
         </is>
       </c>
       <c r="B339" s="13" t="inlineStr">
@@ -55157,7 +55237,7 @@
     <row r="340">
       <c r="A340" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 02:47:24</t>
+          <t>2026-01-23 17:47:24</t>
         </is>
       </c>
       <c r="B340" s="13" t="inlineStr">
@@ -55219,7 +55299,7 @@
     <row r="341">
       <c r="A341" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 02:12:26</t>
+          <t>2026-01-23 17:12:26</t>
         </is>
       </c>
       <c r="B341" s="13" t="inlineStr">
@@ -55281,7 +55361,7 @@
     <row r="342">
       <c r="A342" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 01:33:34</t>
+          <t>2026-01-23 16:33:34</t>
         </is>
       </c>
       <c r="B342" s="13" t="inlineStr">
@@ -55343,7 +55423,7 @@
     <row r="343">
       <c r="A343" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 01:00:39</t>
+          <t>2026-01-23 16:00:39</t>
         </is>
       </c>
       <c r="B343" s="13" t="inlineStr">
@@ -55405,7 +55485,7 @@
     <row r="344">
       <c r="A344" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 00:19:07</t>
+          <t>2026-01-23 15:19:07</t>
         </is>
       </c>
       <c r="B344" s="13" t="inlineStr">
@@ -55467,7 +55547,7 @@
     <row r="345">
       <c r="A345" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 23:52:33</t>
+          <t>2026-01-23 14:52:33</t>
         </is>
       </c>
       <c r="B345" s="13" t="inlineStr">
@@ -55529,7 +55609,7 @@
     <row r="346">
       <c r="A346" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 23:19:19</t>
+          <t>2026-01-23 14:19:19</t>
         </is>
       </c>
       <c r="B346" s="13" t="inlineStr">
@@ -55591,7 +55671,7 @@
     <row r="347">
       <c r="A347" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36:59</t>
+          <t>2026-01-23 13:36:59</t>
         </is>
       </c>
       <c r="B347" s="13" t="inlineStr">
@@ -55653,7 +55733,7 @@
     <row r="348">
       <c r="A348" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 03:01:58</t>
+          <t>2026-01-22 18:01:58</t>
         </is>
       </c>
       <c r="B348" s="13" t="inlineStr">
@@ -55715,7 +55795,7 @@
     <row r="349">
       <c r="A349" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 02:25:41</t>
+          <t>2026-01-22 17:25:41</t>
         </is>
       </c>
       <c r="B349" s="13" t="inlineStr">
@@ -55777,7 +55857,7 @@
     <row r="350">
       <c r="A350" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 00:32:45</t>
+          <t>2026-01-22 15:32:45</t>
         </is>
       </c>
       <c r="B350" s="13" t="inlineStr">
@@ -55839,7 +55919,7 @@
     <row r="351">
       <c r="A351" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 23:54:46</t>
+          <t>2026-01-22 14:54:46</t>
         </is>
       </c>
       <c r="B351" s="13" t="inlineStr">
@@ -55901,7 +55981,7 @@
     <row r="352">
       <c r="A352" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 23:17:42</t>
+          <t>2026-01-22 14:17:42</t>
         </is>
       </c>
       <c r="B352" s="13" t="inlineStr">
@@ -55963,7 +56043,7 @@
     <row r="353">
       <c r="A353" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 01:10:08</t>
+          <t>2026-01-21 16:10:08</t>
         </is>
       </c>
       <c r="B353" s="13" t="inlineStr">
@@ -56025,7 +56105,7 @@
     <row r="354">
       <c r="A354" s="13" t="inlineStr">
         <is>
-          <t>2026-01-21 00:27:51</t>
+          <t>2026-01-20 15:27:51</t>
         </is>
       </c>
       <c r="B354" s="13" t="inlineStr">
@@ -56087,7 +56167,7 @@
     <row r="355">
       <c r="A355" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 23:25:34</t>
+          <t>2026-01-20 14:25:34</t>
         </is>
       </c>
       <c r="B355" s="13" t="inlineStr">
@@ -56149,7 +56229,7 @@
     <row r="356">
       <c r="A356" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 22:56:13</t>
+          <t>2026-01-20 13:56:13</t>
         </is>
       </c>
       <c r="B356" s="13" t="inlineStr">
@@ -56211,7 +56291,7 @@
     <row r="357">
       <c r="A357" s="13" t="inlineStr">
         <is>
-          <t>2026-01-19 01:59:11</t>
+          <t>2026-01-18 16:59:11</t>
         </is>
       </c>
       <c r="B357" s="13" t="inlineStr">
@@ -56273,7 +56353,7 @@
     <row r="358">
       <c r="A358" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 03:05:32</t>
+          <t>2026-01-17 18:05:32</t>
         </is>
       </c>
       <c r="B358" s="13" t="inlineStr">
@@ -56335,7 +56415,7 @@
     <row r="359">
       <c r="A359" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 02:19:17</t>
+          <t>2026-01-17 17:19:17</t>
         </is>
       </c>
       <c r="B359" s="13" t="inlineStr">
@@ -56397,7 +56477,7 @@
     <row r="360">
       <c r="A360" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 01:58:17</t>
+          <t>2026-01-17 16:58:17</t>
         </is>
       </c>
       <c r="B360" s="13" t="inlineStr">
@@ -56459,7 +56539,7 @@
     <row r="361">
       <c r="A361" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 01:18:29</t>
+          <t>2026-01-17 16:18:29</t>
         </is>
       </c>
       <c r="B361" s="13" t="inlineStr">
@@ -56521,7 +56601,7 @@
     <row r="362">
       <c r="A362" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 00:38:58</t>
+          <t>2026-01-17 15:38:58</t>
         </is>
       </c>
       <c r="B362" s="13" t="inlineStr">
@@ -56583,7 +56663,7 @@
     <row r="363">
       <c r="A363" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 18:46:30</t>
+          <t>2026-01-17 09:46:30</t>
         </is>
       </c>
       <c r="B363" s="13" t="inlineStr">
@@ -56645,7 +56725,7 @@
     <row r="364">
       <c r="A364" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 02:21:36</t>
+          <t>2026-01-16 17:21:36</t>
         </is>
       </c>
       <c r="B364" s="13" t="inlineStr">
@@ -56707,7 +56787,7 @@
     <row r="365">
       <c r="A365" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 01:51:05</t>
+          <t>2026-01-16 16:51:05</t>
         </is>
       </c>
       <c r="B365" s="13" t="inlineStr">
@@ -56769,7 +56849,7 @@
     <row r="366">
       <c r="A366" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 01:18:22</t>
+          <t>2026-01-16 16:18:22</t>
         </is>
       </c>
       <c r="B366" s="13" t="inlineStr">
@@ -56831,7 +56911,7 @@
     <row r="367">
       <c r="A367" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 01:41:15</t>
+          <t>2026-01-15 16:41:15</t>
         </is>
       </c>
       <c r="B367" s="13" t="inlineStr">
@@ -56893,7 +56973,7 @@
     <row r="368">
       <c r="A368" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 01:05:38</t>
+          <t>2026-01-15 16:05:38</t>
         </is>
       </c>
       <c r="B368" s="13" t="inlineStr">
@@ -56955,7 +57035,7 @@
     <row r="369">
       <c r="A369" s="13" t="inlineStr">
         <is>
-          <t>2026-01-14 00:57:21</t>
+          <t>2026-01-13 15:57:21</t>
         </is>
       </c>
       <c r="B369" s="13" t="inlineStr">
@@ -57017,7 +57097,7 @@
     <row r="370">
       <c r="A370" s="13" t="inlineStr">
         <is>
-          <t>2026-01-14 00:19:49</t>
+          <t>2026-01-13 15:19:49</t>
         </is>
       </c>
       <c r="B370" s="13" t="inlineStr">
@@ -57079,7 +57159,7 @@
     <row r="371">
       <c r="A371" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 23:53:29</t>
+          <t>2026-01-13 14:53:29</t>
         </is>
       </c>
       <c r="B371" s="13" t="inlineStr">
@@ -57141,7 +57221,7 @@
     <row r="372">
       <c r="A372" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 02:23:29</t>
+          <t>2026-01-12 17:23:29</t>
         </is>
       </c>
       <c r="B372" s="13" t="inlineStr">
@@ -57203,7 +57283,7 @@
     <row r="373">
       <c r="A373" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 01:42:12</t>
+          <t>2026-01-12 16:42:12</t>
         </is>
       </c>
       <c r="B373" s="13" t="inlineStr">
@@ -57265,7 +57345,7 @@
     <row r="374">
       <c r="A374" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 01:17:01</t>
+          <t>2026-01-12 16:17:01</t>
         </is>
       </c>
       <c r="B374" s="13" t="inlineStr">
@@ -57327,7 +57407,7 @@
     <row r="375">
       <c r="A375" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 00:43:11</t>
+          <t>2026-01-12 15:43:11</t>
         </is>
       </c>
       <c r="B375" s="13" t="inlineStr">
@@ -57389,7 +57469,7 @@
     <row r="376">
       <c r="A376" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 17:24:44</t>
+          <t>2026-01-12 08:24:44</t>
         </is>
       </c>
       <c r="B376" s="13" t="inlineStr">
@@ -57451,7 +57531,7 @@
     <row r="377">
       <c r="A377" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 03:12:16</t>
+          <t>2026-01-11 18:12:16</t>
         </is>
       </c>
       <c r="B377" s="13" t="inlineStr">
@@ -57513,7 +57593,7 @@
     <row r="378">
       <c r="A378" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 02:54:03</t>
+          <t>2026-01-10 17:54:03</t>
         </is>
       </c>
       <c r="B378" s="13" t="inlineStr">
@@ -57575,7 +57655,7 @@
     <row r="379">
       <c r="A379" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 02:14:56</t>
+          <t>2026-01-10 17:14:56</t>
         </is>
       </c>
       <c r="B379" s="13" t="inlineStr">
@@ -57637,7 +57717,7 @@
     <row r="380">
       <c r="A380" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 01:17:21</t>
+          <t>2026-01-10 16:17:21</t>
         </is>
       </c>
       <c r="B380" s="13" t="inlineStr">
@@ -57699,7 +57779,7 @@
     <row r="381">
       <c r="A381" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 00:22:11</t>
+          <t>2026-01-10 15:22:11</t>
         </is>
       </c>
       <c r="B381" s="13" t="inlineStr">
@@ -57761,7 +57841,7 @@
     <row r="382">
       <c r="A382" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 23:38:24</t>
+          <t>2026-01-10 14:38:24</t>
         </is>
       </c>
       <c r="B382" s="13" t="inlineStr">
@@ -57823,7 +57903,7 @@
     <row r="383">
       <c r="A383" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 02:54:19</t>
+          <t>2026-01-09 17:54:19</t>
         </is>
       </c>
       <c r="B383" s="13" t="inlineStr">
@@ -57885,7 +57965,7 @@
     <row r="384">
       <c r="A384" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 02:00:16</t>
+          <t>2026-01-09 17:00:16</t>
         </is>
       </c>
       <c r="B384" s="13" t="inlineStr">
@@ -57947,7 +58027,7 @@
     <row r="385">
       <c r="A385" s="13" t="inlineStr">
         <is>
-          <t>2026-01-09 23:36:27</t>
+          <t>2026-01-09 14:36:27</t>
         </is>
       </c>
       <c r="B385" s="13" t="inlineStr">
@@ -58006,8 +58086,70 @@
         </is>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-05 14:21:47</t>
+        </is>
+      </c>
+      <c r="B386" s="13" t="inlineStr">
+        <is>
+          <t>ランク</t>
+        </is>
+      </c>
+      <c r="C386" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D386" s="13" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E386" s="13" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F386" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G386" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H386" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I386" s="13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J386" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K386" s="14" t="inlineStr"/>
+      <c r="L386" s="14" t="inlineStr"/>
+      <c r="M386" s="14" t="inlineStr"/>
+      <c r="N386" s="14" t="inlineStr"/>
+      <c r="O386" s="14" t="inlineStr"/>
+      <c r="P386" s="13" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P385"/>
+  <autoFilter ref="A1:P386"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'キュー別'!$A$1:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'チャンピオン別'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SUPチャンピオン別'!$A$1:$L$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$389</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$389</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$390</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$390</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,14 +532,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>対象期間：2026-01-09 23:36:27 ～ 2026-08-07 01:41:05</t>
+          <t>対象期間：2026-01-05 14:21:47 ～ 2026-08-06 16:41:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-07 02:03:47</t>
+          <t>出力日時：2026-08-07 01:47:34</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.4742268041237113</v>
+        <v>0.4730077120822622</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.695876288659794</v>
+        <v>1.691516709511568</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5.360824742268041</v>
+        <v>5.359897172236503</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>8.896907216494846</v>
+        <v>8.897172236503856</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>59.9639175257732</v>
+        <v>59.89974293059126</v>
       </c>
     </row>
     <row r="15">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2.039845360824742</v>
+        <v>2.037583547557841</v>
       </c>
     </row>
     <row r="16">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>57.23453608247423</v>
+        <v>57.20308483290489</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1.845283505154639</v>
+        <v>1.84439588688946</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.5049180327868853</v>
+        <v>0.5032679738562091</v>
       </c>
     </row>
     <row r="24">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>1.465573770491803</v>
+        <v>1.46078431372549</v>
       </c>
     </row>
     <row r="25">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.18688524590164</v>
+        <v>5.186274509803922</v>
       </c>
     </row>
     <row r="26">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>9.767213114754098</v>
+        <v>9.764705882352942</v>
       </c>
     </row>
     <row r="27">
@@ -757,7 +757,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>36.59672131147541</v>
+        <v>36.59150326797386</v>
       </c>
     </row>
     <row r="29">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1.258229508196721</v>
+        <v>1.257908496732026</v>
       </c>
     </row>
     <row r="30">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>64.52131147540983</v>
+        <v>64.45751633986929</v>
       </c>
     </row>
     <row r="31">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>2.079016393442623</v>
+        <v>2.077124183006534</v>
       </c>
     </row>
   </sheetData>
@@ -898,39 +898,39 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>154</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.5049180327868853</v>
+        <v>0.5032679738562091</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.465573770491803</v>
+        <v>1.46078431372549</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5.18688524590164</v>
+        <v>5.186274509803922</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9.767213114754098</v>
+        <v>9.764705882352942</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.258229508196721</v>
+        <v>1.257908496732026</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>64.52131147540983</v>
+        <v>64.45751633986929</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>2.079016393442623</v>
+        <v>2.077124183006534</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.924590163934426</v>
+        <v>4.924590163934425</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>32.32786885245902</v>
@@ -1135,7 +1135,7 @@
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>2.231410256410256</v>
+        <v>2.231410256410257</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>53.76923076923077</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>1.751217948717949</v>
+        <v>1.751217948717948</v>
       </c>
     </row>
     <row r="3">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>32</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4155844155844156</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.157894736842105</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>5.828947368421052</v>
+        <v>5.818181818181818</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>10.07894736842105</v>
+        <v>10.06493506493507</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.253421052631579</v>
+        <v>1.252207792207792</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>71.46052631578948</v>
+        <v>71.11688311688312</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.231447368421053</v>
+        <v>2.221948051948053</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.490185185185185</v>
+        <v>1.490185185185186</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>62.64814814814815</v>
@@ -1516,25 +1516,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.775</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.153846153846154</v>
+        <v>5.15</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.17948717948718</v>
+        <v>7.225</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.232820512820513</v>
+        <v>1.231</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.97435897435897</v>
+        <v>53.75</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.871025641025641</v>
+        <v>1.86175</v>
       </c>
     </row>
     <row r="6">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5.148285714285715</v>
+        <v>5.148285714285714</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>34.6</v>
@@ -1800,7 +1800,7 @@
         <v>25.625</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.85625</v>
+        <v>0.8562500000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5.050000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>16.25</v>
@@ -2833,25 +2833,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.775</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.153846153846154</v>
+        <v>5.15</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.17948717948718</v>
+        <v>7.225</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.232820512820513</v>
+        <v>1.231</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.97435897435897</v>
+        <v>53.75</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.871025641025641</v>
+        <v>1.86175</v>
       </c>
     </row>
     <row r="6">
@@ -3266,7 +3266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V389"/>
+  <dimension ref="A1:V390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3408,7 +3408,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07 01:41:05</t>
+          <t>2026-08-06 16:41:05</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -3488,7 +3488,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07 01:01:17</t>
+          <t>2026-08-06 16:01:17</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -3568,7 +3568,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06 23:23:16</t>
+          <t>2026-08-06 14:23:16</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -3648,7 +3648,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06 22:29:00</t>
+          <t>2026-08-06 13:29:00</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -3728,7 +3728,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05 23:53:01</t>
+          <t>2026-08-05 14:53:01</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3808,7 +3808,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05 23:15:09</t>
+          <t>2026-08-05 14:15:09</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03 02:00:01</t>
+          <t>2026-08-02 17:00:01</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3968,7 +3968,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03 00:22:22</t>
+          <t>2026-08-02 15:22:22</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -4048,7 +4048,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 23:45:22</t>
+          <t>2026-08-02 14:45:22</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -4128,7 +4128,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 18:45:07</t>
+          <t>2026-08-02 09:45:07</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -4208,7 +4208,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 18:20:05</t>
+          <t>2026-08-02 09:20:05</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -4288,7 +4288,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:32</t>
+          <t>2026-08-02 08:49:32</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 03:33:03</t>
+          <t>2026-08-01 18:33:03</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -4448,7 +4448,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02 02:39:30</t>
+          <t>2026-08-01 17:39:30</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -4528,7 +4528,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 04:00:11</t>
+          <t>2026-07-31 19:00:11</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -4608,7 +4608,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 03:30:26</t>
+          <t>2026-07-31 18:30:26</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -4688,7 +4688,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 02:52:16</t>
+          <t>2026-07-31 17:52:16</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 01:50:20</t>
+          <t>2026-07-31 16:50:20</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -4848,7 +4848,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01 01:16:45</t>
+          <t>2026-07-31 16:16:45</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -4928,7 +4928,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 22:56:19</t>
+          <t>2026-07-31 13:56:19</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -5008,7 +5008,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 22:22:46</t>
+          <t>2026-07-31 13:22:46</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -5088,7 +5088,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31 21:49:35</t>
+          <t>2026-07-31 12:49:35</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -5168,7 +5168,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 23:51:39</t>
+          <t>2026-07-28 14:51:39</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -5248,7 +5248,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28 23:05:20</t>
+          <t>2026-07-28 14:05:20</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -5328,7 +5328,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27 01:21:51</t>
+          <t>2026-07-26 16:21:51</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -5408,7 +5408,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27 00:43:02</t>
+          <t>2026-07-26 15:43:02</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -5488,7 +5488,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 23:12:09</t>
+          <t>2026-07-25 14:12:09</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -5568,7 +5568,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 22:30:57</t>
+          <t>2026-07-25 13:30:57</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -5648,7 +5648,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25 00:11:55</t>
+          <t>2026-07-24 15:11:55</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -5728,7 +5728,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24 23:25:38</t>
+          <t>2026-07-24 14:25:38</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22 00:17:56</t>
+          <t>2026-07-21 15:17:56</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -5888,7 +5888,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22 00:04:35</t>
+          <t>2026-07-21 15:04:35</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -5968,7 +5968,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 23:25:56</t>
+          <t>2026-07-21 14:25:56</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -6048,7 +6048,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 22:44:36</t>
+          <t>2026-07-21 13:44:36</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -6128,7 +6128,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21 22:18:59</t>
+          <t>2026-07-21 13:18:59</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -6208,7 +6208,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20 03:20:20</t>
+          <t>2026-07-19 18:20:20</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -6288,7 +6288,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20 02:39:51</t>
+          <t>2026-07-19 17:39:51</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -6368,7 +6368,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:59:14</t>
+          <t>2026-07-18 09:59:14</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -6448,7 +6448,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:21:14</t>
+          <t>2026-07-18 09:21:14</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -6528,7 +6528,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 23:06:28</t>
+          <t>2026-07-16 14:06:28</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -6608,7 +6608,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 22:32:42</t>
+          <t>2026-07-16 13:32:42</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -6688,7 +6688,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16 00:40:48</t>
+          <t>2026-07-15 15:40:48</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -6768,7 +6768,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 23:41:56</t>
+          <t>2026-07-15 14:41:56</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -6848,7 +6848,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 22:58:44</t>
+          <t>2026-07-15 13:58:44</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -6928,7 +6928,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15 22:34:16</t>
+          <t>2026-07-15 13:34:16</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -7008,7 +7008,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 23:36:35</t>
+          <t>2026-07-14 14:36:35</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -7088,7 +7088,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 22:49:50</t>
+          <t>2026-07-14 13:49:50</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -7168,7 +7168,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 01:02:29</t>
+          <t>2026-07-13 16:02:29</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -7248,7 +7248,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14 00:22:46</t>
+          <t>2026-07-13 15:22:46</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -7328,7 +7328,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 23:51:38</t>
+          <t>2026-07-13 14:51:38</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -7408,7 +7408,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 02:05:19</t>
+          <t>2026-07-12 17:05:19</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -7488,7 +7488,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13 01:29:17</t>
+          <t>2026-07-12 16:29:17</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -7568,7 +7568,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 03:11:38</t>
+          <t>2026-07-11 18:11:38</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -7648,7 +7648,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 02:46:15</t>
+          <t>2026-07-11 17:46:15</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 03:42:29</t>
+          <t>2026-07-10 18:42:29</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11 03:06:21</t>
+          <t>2026-07-10 18:06:21</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -7888,7 +7888,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:55:25</t>
+          <t>2026-07-08 17:55:25</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -7968,7 +7968,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:17:09</t>
+          <t>2026-07-08 17:17:09</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -8048,7 +8048,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 02:03:51</t>
+          <t>2026-07-05 17:03:51</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -8128,7 +8128,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 01:07:17</t>
+          <t>2026-07-05 16:07:17</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -8208,7 +8208,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06 00:23:00</t>
+          <t>2026-07-05 15:23:00</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -8288,7 +8288,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>2026-07-05 03:21:23</t>
+          <t>2026-07-04 18:21:23</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -8368,7 +8368,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>2026-07-04 03:01:40</t>
+          <t>2026-07-03 18:01:40</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -8448,7 +8448,7 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03 01:48:19</t>
+          <t>2026-07-02 16:48:19</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -8528,7 +8528,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01 00:21:19</t>
+          <t>2026-06-30 15:21:19</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -8608,7 +8608,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 23:38:16</t>
+          <t>2026-06-30 14:38:16</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -8688,7 +8688,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 01:16:28</t>
+          <t>2026-06-29 16:16:28</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -8768,7 +8768,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30 00:34:32</t>
+          <t>2026-06-29 15:34:32</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -8848,7 +8848,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26 00:50:56</t>
+          <t>2026-06-25 15:50:56</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -8928,7 +8928,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26 00:06:40</t>
+          <t>2026-06-25 15:06:40</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -9008,7 +9008,7 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07:56</t>
+          <t>2026-06-24 17:07:56</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -9088,7 +9088,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 01:33:19</t>
+          <t>2026-06-24 16:33:19</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -9168,7 +9168,7 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:47:59</t>
+          <t>2026-06-24 15:47:59</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -9248,7 +9248,7 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:08:31</t>
+          <t>2026-06-24 15:08:31</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
@@ -9328,7 +9328,7 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 23:33:15</t>
+          <t>2026-06-24 14:33:15</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -9408,7 +9408,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24 22:39:11</t>
+          <t>2026-06-24 13:39:11</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -9488,7 +9488,7 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 01:16:06</t>
+          <t>2026-06-22 16:16:06</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -9568,7 +9568,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 00:38:08</t>
+          <t>2026-06-22 15:38:08</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -9648,7 +9648,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23 00:29:33</t>
+          <t>2026-06-22 15:29:33</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -9728,7 +9728,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 01:54:04</t>
+          <t>2026-06-18 16:54:04</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -9808,7 +9808,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 01:14:50</t>
+          <t>2026-06-18 16:14:50</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -9888,7 +9888,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 00:35:17</t>
+          <t>2026-06-18 15:35:17</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -9968,7 +9968,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 23:55:50</t>
+          <t>2026-06-18 14:55:50</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -10048,7 +10048,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18 00:44:42</t>
+          <t>2026-06-17 15:44:42</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -10128,7 +10128,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 23:57:38</t>
+          <t>2026-06-17 14:57:38</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -10208,7 +10208,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 01:58:55</t>
+          <t>2026-06-16 16:58:55</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -10288,7 +10288,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17 01:30:07</t>
+          <t>2026-06-16 16:30:07</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -10368,7 +10368,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 03:10:28</t>
+          <t>2026-06-14 18:10:28</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -10448,7 +10448,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 02:27:52</t>
+          <t>2026-06-14 17:27:52</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -10528,7 +10528,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 01:57:23</t>
+          <t>2026-06-14 16:57:23</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -10608,7 +10608,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 01:27:22</t>
+          <t>2026-06-14 16:27:22</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -10688,7 +10688,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15 00:24:35</t>
+          <t>2026-06-14 15:24:35</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -10768,7 +10768,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 23:46:55</t>
+          <t>2026-06-14 14:46:55</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -10848,7 +10848,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 01:41:53</t>
+          <t>2026-06-13 16:41:53</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -10928,7 +10928,7 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 00:52:58</t>
+          <t>2026-06-13 15:52:58</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -11008,7 +11008,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 00:14:23</t>
+          <t>2026-06-13 15:14:23</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -11088,7 +11088,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 23:45:21</t>
+          <t>2026-06-13 14:45:21</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -11168,7 +11168,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 23:05:32</t>
+          <t>2026-06-13 14:05:32</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -11248,7 +11248,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 01:08:14</t>
+          <t>2026-06-10 16:08:14</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -11328,7 +11328,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:34:35</t>
+          <t>2026-06-10 15:34:35</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -11408,7 +11408,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:09:17</t>
+          <t>2026-06-10 15:09:17</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -11488,7 +11488,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 23:27:53</t>
+          <t>2026-06-10 14:27:53</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -11568,7 +11568,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10 00:49:00</t>
+          <t>2026-06-09 15:49:00</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -11648,7 +11648,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06 02:58:51</t>
+          <t>2026-06-05 17:58:51</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -11728,7 +11728,7 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06 02:15:04</t>
+          <t>2026-06-05 17:15:04</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -11808,7 +11808,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 23:49:14</t>
+          <t>2026-06-04 14:49:14</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -11888,7 +11888,7 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 21:40:04</t>
+          <t>2026-06-04 12:40:04</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -11968,7 +11968,7 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 21:17:24</t>
+          <t>2026-06-04 12:17:24</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -12048,7 +12048,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 01:06:27</t>
+          <t>2026-06-03 16:06:27</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -12128,7 +12128,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04 00:31:09</t>
+          <t>2026-06-03 15:31:09</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -12208,7 +12208,7 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 23:53:57</t>
+          <t>2026-06-03 14:53:57</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -12288,7 +12288,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03 22:44:02</t>
+          <t>2026-06-03 13:44:02</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -12368,7 +12368,7 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02 22:49:11</t>
+          <t>2026-06-02 13:49:11</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -12448,7 +12448,7 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:56:06</t>
+          <t>2026-06-01 14:56:06</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -12528,7 +12528,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:20:26</t>
+          <t>2026-06-01 14:20:26</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -12608,7 +12608,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01 23:01:06</t>
+          <t>2026-06-01 14:01:06</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -12688,7 +12688,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31 03:01:04</t>
+          <t>2026-05-30 18:01:04</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -12768,7 +12768,7 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31 02:13:41</t>
+          <t>2026-05-30 17:13:41</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -12848,7 +12848,7 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 23:00:40</t>
+          <t>2026-05-25 14:00:40</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -12928,7 +12928,7 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 01:55:47</t>
+          <t>2026-05-24 16:55:47</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -13008,7 +13008,7 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25 01:24:22</t>
+          <t>2026-05-24 16:24:22</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -13088,7 +13088,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 23:49:25</t>
+          <t>2026-05-24 14:49:25</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -13168,7 +13168,7 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 03:13:39</t>
+          <t>2026-05-23 18:13:39</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -13248,7 +13248,7 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24 02:41:52</t>
+          <t>2026-05-23 17:41:52</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -13328,7 +13328,7 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 23:19:04</t>
+          <t>2026-05-23 14:19:04</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -13408,7 +13408,7 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 22:43:20</t>
+          <t>2026-05-23 13:43:20</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -13488,7 +13488,7 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 15:54:19</t>
+          <t>2026-05-23 06:54:19</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -13568,7 +13568,7 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23 02:25:24</t>
+          <t>2026-05-22 17:25:24</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -13648,7 +13648,7 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 01:29:23</t>
+          <t>2026-05-21 16:29:23</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -13728,7 +13728,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 00:48:49</t>
+          <t>2026-05-21 15:48:49</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -13808,7 +13808,7 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:45</t>
+          <t>2026-05-21 15:00:45</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -13888,7 +13888,7 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 23:22:44</t>
+          <t>2026-05-21 14:22:44</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -13968,7 +13968,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21 00:05:15</t>
+          <t>2026-05-20 15:05:15</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -14048,7 +14048,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 23:43:50</t>
+          <t>2026-05-20 14:43:50</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -14128,7 +14128,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 22:57:45</t>
+          <t>2026-05-20 13:57:45</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -14208,7 +14208,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 01:25:45</t>
+          <t>2026-05-19 16:25:45</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -14288,7 +14288,7 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20 00:46:42</t>
+          <t>2026-05-19 15:46:42</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -14368,7 +14368,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>2026-05-18 22:56:39</t>
+          <t>2026-05-18 13:56:39</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -14448,7 +14448,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 01:35:56</t>
+          <t>2026-05-14 16:35:56</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -14528,7 +14528,7 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 01:17:05</t>
+          <t>2026-05-14 16:17:05</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -14608,7 +14608,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15 00:05:48</t>
+          <t>2026-05-14 15:05:48</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -14688,7 +14688,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14 01:25:38</t>
+          <t>2026-05-13 16:25:38</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -14768,7 +14768,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>2026-05-12 00:19:57</t>
+          <t>2026-05-11 15:19:57</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -14848,7 +14848,7 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 23:54:15</t>
+          <t>2026-05-11 14:54:15</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -14928,7 +14928,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 23:14:30</t>
+          <t>2026-05-11 14:14:30</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -15008,7 +15008,7 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 22:37:05</t>
+          <t>2026-05-11 13:37:05</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -15088,7 +15088,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 21:53:13</t>
+          <t>2026-05-11 12:53:13</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -15168,7 +15168,7 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11 00:04:01</t>
+          <t>2026-05-10 15:04:01</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -15248,7 +15248,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:54:24</t>
+          <t>2026-05-09 16:54:24</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -15328,7 +15328,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:22:50</t>
+          <t>2026-05-09 16:22:50</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -15408,7 +15408,7 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>2026-05-10 00:26:16</t>
+          <t>2026-05-09 15:26:16</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -15488,7 +15488,7 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 23:38:30</t>
+          <t>2026-05-09 14:38:30</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -15568,7 +15568,7 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 22:50:20</t>
+          <t>2026-05-09 13:50:20</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -15648,7 +15648,7 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 22:13:25</t>
+          <t>2026-05-09 13:13:25</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -15728,7 +15728,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 20:00:11</t>
+          <t>2026-05-09 11:00:11</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -15808,7 +15808,7 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 19:10:28</t>
+          <t>2026-05-09 10:10:28</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -15888,7 +15888,7 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 02:17:27</t>
+          <t>2026-05-08 17:17:27</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -15968,7 +15968,7 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 01:38:25</t>
+          <t>2026-05-08 16:38:25</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -16048,7 +16048,7 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 00:58:58</t>
+          <t>2026-05-08 15:58:58</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -16128,7 +16128,7 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09 00:37:55</t>
+          <t>2026-05-08 15:37:55</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -16208,7 +16208,7 @@
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 01:48:31</t>
+          <t>2026-05-07 16:48:31</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -16288,7 +16288,7 @@
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 01:02:52</t>
+          <t>2026-05-07 16:02:52</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -16368,7 +16368,7 @@
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>2026-05-08 00:23:29</t>
+          <t>2026-05-07 15:23:29</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -16448,7 +16448,7 @@
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 01:30:56</t>
+          <t>2026-05-06 16:30:56</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -16528,7 +16528,7 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07 00:42:16</t>
+          <t>2026-05-06 15:42:16</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -16608,7 +16608,7 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 23:44:04</t>
+          <t>2026-05-06 14:44:04</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -16688,7 +16688,7 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:13:52</t>
+          <t>2026-05-06 09:13:52</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -16768,7 +16768,7 @@
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:05:08</t>
+          <t>2026-05-06 09:05:08</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -16848,7 +16848,7 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 17:22:30</t>
+          <t>2026-05-06 08:22:30</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -16928,7 +16928,7 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 16:28:42</t>
+          <t>2026-05-06 07:28:42</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
@@ -17008,7 +17008,7 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 03:16:57</t>
+          <t>2026-05-05 18:16:57</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -17088,7 +17088,7 @@
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:32:40</t>
+          <t>2026-05-05 17:32:40</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -17168,7 +17168,7 @@
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:23:28</t>
+          <t>2026-05-05 17:23:28</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
@@ -17248,7 +17248,7 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 01:48:28</t>
+          <t>2026-05-05 16:48:28</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -17328,7 +17328,7 @@
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06 00:52:33</t>
+          <t>2026-05-05 15:52:33</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
@@ -17408,7 +17408,7 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05 17:43:06</t>
+          <t>2026-05-05 08:43:06</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -17488,7 +17488,7 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>2026-05-03 00:36:42</t>
+          <t>2026-05-02 15:36:42</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -17568,7 +17568,7 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 23:51:09</t>
+          <t>2026-05-02 14:51:09</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
@@ -17648,7 +17648,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 22:15:10</t>
+          <t>2026-05-02 13:15:10</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -17728,7 +17728,7 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02 21:29:49</t>
+          <t>2026-05-02 12:29:49</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
@@ -17808,7 +17808,7 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 01:39:42</t>
+          <t>2026-04-30 16:39:42</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
@@ -17888,7 +17888,7 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 01:01:34</t>
+          <t>2026-04-30 16:01:34</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
@@ -17968,7 +17968,7 @@
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01 00:24:48</t>
+          <t>2026-04-30 15:24:48</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
@@ -18048,7 +18048,7 @@
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 23:37:10</t>
+          <t>2026-04-30 14:37:10</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
@@ -18128,7 +18128,7 @@
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 22:58:06</t>
+          <t>2026-04-30 13:58:06</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
@@ -18208,7 +18208,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 03:29:33</t>
+          <t>2026-04-29 18:29:33</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
@@ -18288,7 +18288,7 @@
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 02:54:07</t>
+          <t>2026-04-29 17:54:07</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
@@ -18368,7 +18368,7 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 02:20:58</t>
+          <t>2026-04-29 17:20:58</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
@@ -18448,7 +18448,7 @@
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 01:42:01</t>
+          <t>2026-04-29 16:42:01</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
@@ -18528,7 +18528,7 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 01:03:17</t>
+          <t>2026-04-29 16:03:17</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
@@ -18608,7 +18608,7 @@
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>2026-04-30 00:19:47</t>
+          <t>2026-04-29 15:19:47</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -18688,7 +18688,7 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 23:29:53</t>
+          <t>2026-04-29 14:29:53</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
@@ -18768,7 +18768,7 @@
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:59:49</t>
+          <t>2026-04-29 13:59:49</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
@@ -18848,7 +18848,7 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:38:22</t>
+          <t>2026-04-29 13:38:22</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
@@ -18928,7 +18928,7 @@
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:44</t>
+          <t>2026-04-29 13:17:44</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -19008,7 +19008,7 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 03:28:56</t>
+          <t>2026-04-28 18:28:56</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
@@ -19088,7 +19088,7 @@
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:58:50</t>
+          <t>2026-04-28 17:58:50</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -19168,7 +19168,7 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:29:43</t>
+          <t>2026-04-28 17:29:43</t>
         </is>
       </c>
       <c r="B199" s="7" t="inlineStr">
@@ -19248,7 +19248,7 @@
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 01:38:43</t>
+          <t>2026-04-28 16:38:43</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -19328,7 +19328,7 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:54</t>
+          <t>2026-04-28 15:58:54</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
@@ -19408,7 +19408,7 @@
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:31:32</t>
+          <t>2026-04-28 15:31:32</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -19488,7 +19488,7 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:04:20</t>
+          <t>2026-04-28 15:04:20</t>
         </is>
       </c>
       <c r="B203" s="7" t="inlineStr">
@@ -19568,7 +19568,7 @@
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 23:37:27</t>
+          <t>2026-04-28 14:37:27</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
@@ -19648,7 +19648,7 @@
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28 23:09:10</t>
+          <t>2026-04-28 14:09:10</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
@@ -19728,7 +19728,7 @@
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:59:25</t>
+          <t>2026-04-27 14:59:25</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
@@ -19808,7 +19808,7 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:49:35</t>
+          <t>2026-04-27 14:49:35</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
@@ -19888,7 +19888,7 @@
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 22:55:34</t>
+          <t>2026-04-27 13:55:34</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -19968,7 +19968,7 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27 22:04:13</t>
+          <t>2026-04-27 13:04:13</t>
         </is>
       </c>
       <c r="B209" s="7" t="inlineStr">
@@ -20048,7 +20048,7 @@
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 02:49:02</t>
+          <t>2026-04-24 17:49:02</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -20128,7 +20128,7 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 02:03:56</t>
+          <t>2026-04-24 17:03:56</t>
         </is>
       </c>
       <c r="B211" s="7" t="inlineStr">
@@ -20208,7 +20208,7 @@
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25 01:37:00</t>
+          <t>2026-04-24 16:37:00</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
@@ -20288,7 +20288,7 @@
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:33:59</t>
+          <t>2026-04-23 15:33:59</t>
         </is>
       </c>
       <c r="B213" s="7" t="inlineStr">
@@ -20368,7 +20368,7 @@
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:22:46</t>
+          <t>2026-04-23 15:22:46</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
@@ -20448,7 +20448,7 @@
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24 00:12:54</t>
+          <t>2026-04-23 15:12:54</t>
         </is>
       </c>
       <c r="B215" s="7" t="inlineStr">
@@ -20528,7 +20528,7 @@
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23 22:36:03</t>
+          <t>2026-04-23 13:36:03</t>
         </is>
       </c>
       <c r="B216" s="7" t="inlineStr">
@@ -20608,7 +20608,7 @@
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:58:57</t>
+          <t>2026-04-13 15:58:57</t>
         </is>
       </c>
       <c r="B217" s="7" t="inlineStr">
@@ -20688,7 +20688,7 @@
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:09:08</t>
+          <t>2026-04-13 15:09:08</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
@@ -20768,7 +20768,7 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 01:48:02</t>
+          <t>2026-04-12 16:48:02</t>
         </is>
       </c>
       <c r="B219" s="7" t="inlineStr">
@@ -20848,7 +20848,7 @@
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 01:17:58</t>
+          <t>2026-04-12 16:17:58</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
@@ -20928,7 +20928,7 @@
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13 00:41:20</t>
+          <t>2026-04-12 15:41:20</t>
         </is>
       </c>
       <c r="B221" s="7" t="inlineStr">
@@ -21008,7 +21008,7 @@
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 23:18:06</t>
+          <t>2026-04-09 14:18:06</t>
         </is>
       </c>
       <c r="B222" s="7" t="inlineStr">
@@ -21088,7 +21088,7 @@
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 22:52:44</t>
+          <t>2026-04-09 13:52:44</t>
         </is>
       </c>
       <c r="B223" s="7" t="inlineStr">
@@ -21168,7 +21168,7 @@
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09 22:27:45</t>
+          <t>2026-04-09 13:27:45</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -21248,7 +21248,7 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>2026-04-08 01:10:31</t>
+          <t>2026-04-07 16:10:31</t>
         </is>
       </c>
       <c r="B225" s="7" t="inlineStr">
@@ -21328,7 +21328,7 @@
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>2026-04-08 00:29:19</t>
+          <t>2026-04-07 15:29:19</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
@@ -21408,7 +21408,7 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>2026-04-04 04:36:31</t>
+          <t>2026-04-03 19:36:31</t>
         </is>
       </c>
       <c r="B227" s="7" t="inlineStr">
@@ -21488,7 +21488,7 @@
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
-          <t>2026-04-04 04:16:32</t>
+          <t>2026-04-03 19:16:32</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
@@ -21568,7 +21568,7 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 04:24:43</t>
+          <t>2026-03-27 19:24:43</t>
         </is>
       </c>
       <c r="B229" s="7" t="inlineStr">
@@ -21648,7 +21648,7 @@
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 03:38:31</t>
+          <t>2026-03-27 18:38:31</t>
         </is>
       </c>
       <c r="B230" s="7" t="inlineStr">
@@ -21728,7 +21728,7 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 03:17:50</t>
+          <t>2026-03-27 18:17:50</t>
         </is>
       </c>
       <c r="B231" s="7" t="inlineStr">
@@ -21808,7 +21808,7 @@
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 02:43:19</t>
+          <t>2026-03-27 17:43:19</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
@@ -21888,7 +21888,7 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28 02:15:18</t>
+          <t>2026-03-27 17:15:18</t>
         </is>
       </c>
       <c r="B233" s="7" t="inlineStr">
@@ -21968,7 +21968,7 @@
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 23:18:12</t>
+          <t>2026-03-25 14:18:12</t>
         </is>
       </c>
       <c r="B234" s="7" t="inlineStr">
@@ -22048,7 +22048,7 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25 00:01:49</t>
+          <t>2026-03-24 15:01:49</t>
         </is>
       </c>
       <c r="B235" s="7" t="inlineStr">
@@ -22128,7 +22128,7 @@
     <row r="236">
       <c r="A236" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 23:25:16</t>
+          <t>2026-03-24 14:25:16</t>
         </is>
       </c>
       <c r="B236" s="7" t="inlineStr">
@@ -22208,7 +22208,7 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 23:02:52</t>
+          <t>2026-03-24 14:02:52</t>
         </is>
       </c>
       <c r="B237" s="7" t="inlineStr">
@@ -22288,7 +22288,7 @@
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 22:26:26</t>
+          <t>2026-03-24 13:26:26</t>
         </is>
       </c>
       <c r="B238" s="7" t="inlineStr">
@@ -22368,7 +22368,7 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 00:56:18</t>
+          <t>2026-03-23 15:56:18</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
@@ -22448,7 +22448,7 @@
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24 00:29:29</t>
+          <t>2026-03-23 15:29:29</t>
         </is>
       </c>
       <c r="B240" s="7" t="inlineStr">
@@ -22528,7 +22528,7 @@
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 23:51:11</t>
+          <t>2026-03-22 14:51:11</t>
         </is>
       </c>
       <c r="B241" s="7" t="inlineStr">
@@ -22608,7 +22608,7 @@
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22 01:04:36</t>
+          <t>2026-03-21 16:04:36</t>
         </is>
       </c>
       <c r="B242" s="7" t="inlineStr">
@@ -22688,7 +22688,7 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>2026-03-21 02:55:49</t>
+          <t>2026-03-20 17:55:49</t>
         </is>
       </c>
       <c r="B243" s="7" t="inlineStr">
@@ -22768,7 +22768,7 @@
     <row r="244">
       <c r="A244" s="7" t="inlineStr">
         <is>
-          <t>2026-03-18 00:07:07</t>
+          <t>2026-03-17 15:07:07</t>
         </is>
       </c>
       <c r="B244" s="7" t="inlineStr">
@@ -22848,7 +22848,7 @@
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 23:24:05</t>
+          <t>2026-03-17 14:24:05</t>
         </is>
       </c>
       <c r="B245" s="7" t="inlineStr">
@@ -22928,7 +22928,7 @@
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 02:00:50</t>
+          <t>2026-03-16 17:00:50</t>
         </is>
       </c>
       <c r="B246" s="7" t="inlineStr">
@@ -23008,7 +23008,7 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>2026-03-17 01:33:08</t>
+          <t>2026-03-16 16:33:08</t>
         </is>
       </c>
       <c r="B247" s="7" t="inlineStr">
@@ -23088,7 +23088,7 @@
     <row r="248">
       <c r="A248" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 23:28:09</t>
+          <t>2026-03-16 14:28:09</t>
         </is>
       </c>
       <c r="B248" s="7" t="inlineStr">
@@ -23168,7 +23168,7 @@
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16 01:32:22</t>
+          <t>2026-03-15 16:32:22</t>
         </is>
       </c>
       <c r="B249" s="7" t="inlineStr">
@@ -23248,7 +23248,7 @@
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14 01:43:49</t>
+          <t>2026-03-13 16:43:49</t>
         </is>
       </c>
       <c r="B250" s="7" t="inlineStr">
@@ -23328,7 +23328,7 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14 01:19:35</t>
+          <t>2026-03-13 16:19:35</t>
         </is>
       </c>
       <c r="B251" s="7" t="inlineStr">
@@ -23408,7 +23408,7 @@
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 23:45:27</t>
+          <t>2026-03-12 14:45:27</t>
         </is>
       </c>
       <c r="B252" s="7" t="inlineStr">
@@ -23488,7 +23488,7 @@
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 23:02:09</t>
+          <t>2026-03-12 14:02:09</t>
         </is>
       </c>
       <c r="B253" s="7" t="inlineStr">
@@ -23568,7 +23568,7 @@
     <row r="254">
       <c r="A254" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 22:42:59</t>
+          <t>2026-03-12 13:42:59</t>
         </is>
       </c>
       <c r="B254" s="7" t="inlineStr">
@@ -23648,7 +23648,7 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 01:39:10</t>
+          <t>2026-03-11 16:39:10</t>
         </is>
       </c>
       <c r="B255" s="7" t="inlineStr">
@@ -23728,7 +23728,7 @@
     <row r="256">
       <c r="A256" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:43:21</t>
+          <t>2026-03-11 15:43:21</t>
         </is>
       </c>
       <c r="B256" s="7" t="inlineStr">
@@ -23808,7 +23808,7 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:04:25</t>
+          <t>2026-03-11 15:04:25</t>
         </is>
       </c>
       <c r="B257" s="7" t="inlineStr">
@@ -23888,7 +23888,7 @@
     <row r="258">
       <c r="A258" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 22:54:02</t>
+          <t>2026-03-11 13:54:02</t>
         </is>
       </c>
       <c r="B258" s="7" t="inlineStr">
@@ -23968,7 +23968,7 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>2026-03-08 02:01:53</t>
+          <t>2026-03-07 17:01:53</t>
         </is>
       </c>
       <c r="B259" s="7" t="inlineStr">
@@ -24048,7 +24048,7 @@
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>2026-03-02 02:18:59</t>
+          <t>2026-03-01 17:18:59</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
@@ -24128,7 +24128,7 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>2026-02-24 01:40:38</t>
+          <t>2026-02-23 16:40:38</t>
         </is>
       </c>
       <c r="B261" s="7" t="inlineStr">
@@ -24208,7 +24208,7 @@
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>2026-02-24 00:10:31</t>
+          <t>2026-02-23 15:10:31</t>
         </is>
       </c>
       <c r="B262" s="7" t="inlineStr">
@@ -24288,7 +24288,7 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 23:33:47</t>
+          <t>2026-02-23 14:33:47</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
@@ -24368,7 +24368,7 @@
     <row r="264">
       <c r="A264" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 22:40:54</t>
+          <t>2026-02-23 13:40:54</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -24448,7 +24448,7 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 21:58:56</t>
+          <t>2026-02-23 12:58:56</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
@@ -24528,7 +24528,7 @@
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 19:21:48</t>
+          <t>2026-02-23 10:21:48</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -24608,7 +24608,7 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 17:17:13</t>
+          <t>2026-02-23 08:17:13</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -24688,7 +24688,7 @@
     <row r="268">
       <c r="A268" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 04:22:01</t>
+          <t>2026-02-22 19:22:01</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
@@ -24768,7 +24768,7 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 03:23:51</t>
+          <t>2026-02-22 18:23:51</t>
         </is>
       </c>
       <c r="B269" s="7" t="inlineStr">
@@ -24848,7 +24848,7 @@
     <row r="270">
       <c r="A270" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 02:58:18</t>
+          <t>2026-02-22 17:58:18</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
@@ -24928,7 +24928,7 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 02:29:21</t>
+          <t>2026-02-22 17:29:21</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
@@ -25008,7 +25008,7 @@
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 01:59:09</t>
+          <t>2026-02-22 16:59:09</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -25088,7 +25088,7 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23 01:32:08</t>
+          <t>2026-02-22 16:32:08</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
@@ -25168,7 +25168,7 @@
     <row r="274">
       <c r="A274" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 03:34:36</t>
+          <t>2026-02-20 18:34:36</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -25248,7 +25248,7 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 02:57:13</t>
+          <t>2026-02-20 17:57:13</t>
         </is>
       </c>
       <c r="B275" s="7" t="inlineStr">
@@ -25328,7 +25328,7 @@
     <row r="276">
       <c r="A276" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 02:19:01</t>
+          <t>2026-02-20 17:19:01</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
@@ -25408,7 +25408,7 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 01:41:10</t>
+          <t>2026-02-20 16:41:10</t>
         </is>
       </c>
       <c r="B277" s="7" t="inlineStr">
@@ -25488,7 +25488,7 @@
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:57:47</t>
+          <t>2026-02-20 15:57:47</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -25568,7 +25568,7 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:39:52</t>
+          <t>2026-02-20 15:39:52</t>
         </is>
       </c>
       <c r="B279" s="7" t="inlineStr">
@@ -25648,7 +25648,7 @@
     <row r="280">
       <c r="A280" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 01:21:13</t>
+          <t>2026-02-19 16:21:13</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -25728,7 +25728,7 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20 00:33:10</t>
+          <t>2026-02-19 15:33:10</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
@@ -25808,7 +25808,7 @@
     <row r="282">
       <c r="A282" s="7" t="inlineStr">
         <is>
-          <t>2026-02-18 00:37:38</t>
+          <t>2026-02-17 15:37:38</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -25888,7 +25888,7 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>2026-02-17 23:58:39</t>
+          <t>2026-02-17 14:58:39</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
@@ -25968,7 +25968,7 @@
     <row r="284">
       <c r="A284" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 02:24:16</t>
+          <t>2026-02-15 17:24:16</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -26048,7 +26048,7 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 01:47:19</t>
+          <t>2026-02-15 16:47:19</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
@@ -26128,7 +26128,7 @@
     <row r="286">
       <c r="A286" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 00:56:43</t>
+          <t>2026-02-15 15:56:43</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -26208,7 +26208,7 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16 00:26:20</t>
+          <t>2026-02-15 15:26:20</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -26288,7 +26288,7 @@
     <row r="288">
       <c r="A288" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 23:48:44</t>
+          <t>2026-02-15 14:48:44</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -26368,7 +26368,7 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 04:17:17</t>
+          <t>2026-02-14 19:17:17</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -26448,7 +26448,7 @@
     <row r="290">
       <c r="A290" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 03:53:01</t>
+          <t>2026-02-14 18:53:01</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -26528,7 +26528,7 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:59:46</t>
+          <t>2026-02-14 17:59:46</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
@@ -26608,7 +26608,7 @@
     <row r="292">
       <c r="A292" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:26:42</t>
+          <t>2026-02-14 17:26:42</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -26688,7 +26688,7 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 02:00:09</t>
+          <t>2026-02-14 17:00:09</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
@@ -26768,7 +26768,7 @@
     <row r="294">
       <c r="A294" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 01:39:16</t>
+          <t>2026-02-14 16:39:16</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -26848,7 +26848,7 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15 00:56:51</t>
+          <t>2026-02-14 15:56:51</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
@@ -26928,7 +26928,7 @@
     <row r="296">
       <c r="A296" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 23:52:26</t>
+          <t>2026-02-14 14:52:26</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -27008,7 +27008,7 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 23:14:55</t>
+          <t>2026-02-14 14:14:55</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -27088,7 +27088,7 @@
     <row r="298">
       <c r="A298" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 04:19:58</t>
+          <t>2026-02-13 19:19:58</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -27168,7 +27168,7 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 03:37:53</t>
+          <t>2026-02-13 18:37:53</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
@@ -27248,7 +27248,7 @@
     <row r="300">
       <c r="A300" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 03:03:31</t>
+          <t>2026-02-13 18:03:31</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
@@ -27328,7 +27328,7 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14 02:08:36</t>
+          <t>2026-02-13 17:08:36</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -27408,7 +27408,7 @@
     <row r="302">
       <c r="A302" s="7" t="inlineStr">
         <is>
-          <t>2026-02-12 00:20:03</t>
+          <t>2026-02-11 15:20:03</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
@@ -27488,7 +27488,7 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 03:05:03</t>
+          <t>2026-02-10 18:05:03</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
@@ -27568,7 +27568,7 @@
     <row r="304">
       <c r="A304" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 02:14:02</t>
+          <t>2026-02-10 17:14:02</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -27648,7 +27648,7 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 01:33:21</t>
+          <t>2026-02-10 16:33:21</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -27728,7 +27728,7 @@
     <row r="306">
       <c r="A306" s="7" t="inlineStr">
         <is>
-          <t>2026-02-11 01:01:41</t>
+          <t>2026-02-10 16:01:41</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -27808,7 +27808,7 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 01:49:32</t>
+          <t>2026-02-09 16:49:32</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
@@ -27888,7 +27888,7 @@
     <row r="308">
       <c r="A308" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10 01:42:29</t>
+          <t>2026-02-09 16:42:29</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
@@ -27968,7 +27968,7 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 23:44:10</t>
+          <t>2026-02-09 14:44:10</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
@@ -28048,7 +28048,7 @@
     <row r="310">
       <c r="A310" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 23:00:28</t>
+          <t>2026-02-09 14:00:28</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -28128,7 +28128,7 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 00:27:49</t>
+          <t>2026-02-08 15:27:49</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -28208,7 +28208,7 @@
     <row r="312">
       <c r="A312" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09 00:16:42</t>
+          <t>2026-02-08 15:16:42</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -28288,7 +28288,7 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08 04:04:43</t>
+          <t>2026-02-07 19:04:43</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -28368,7 +28368,7 @@
     <row r="314">
       <c r="A314" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 03:13:11</t>
+          <t>2026-02-06 18:13:11</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -28448,7 +28448,7 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 02:19:42</t>
+          <t>2026-02-06 17:19:42</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -28528,7 +28528,7 @@
     <row r="316">
       <c r="A316" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07 01:37:36</t>
+          <t>2026-02-06 16:37:36</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -28608,7 +28608,7 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>2026-02-03 23:04:49</t>
+          <t>2026-02-03 14:04:49</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -28688,7 +28688,7 @@
     <row r="318">
       <c r="A318" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 23:21:38</t>
+          <t>2026-02-02 14:21:38</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -28768,7 +28768,7 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 03:08:17</t>
+          <t>2026-02-01 18:08:17</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -28848,7 +28848,7 @@
     <row r="320">
       <c r="A320" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 02:41:55</t>
+          <t>2026-02-01 17:41:55</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -28928,7 +28928,7 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 02:09:57</t>
+          <t>2026-02-01 17:09:57</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -29008,7 +29008,7 @@
     <row r="322">
       <c r="A322" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02 01:41:49</t>
+          <t>2026-02-01 16:41:49</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -29088,7 +29088,7 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 02:22:13</t>
+          <t>2026-01-31 17:22:13</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -29168,7 +29168,7 @@
     <row r="324">
       <c r="A324" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 01:20:54</t>
+          <t>2026-01-31 16:20:54</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -29248,7 +29248,7 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 01:09:32</t>
+          <t>2026-01-31 16:09:32</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -29328,7 +29328,7 @@
     <row r="326">
       <c r="A326" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 00:29:37</t>
+          <t>2026-01-31 15:29:37</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -29408,7 +29408,7 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01 00:03:50</t>
+          <t>2026-01-31 15:03:50</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -29488,7 +29488,7 @@
     <row r="328">
       <c r="A328" s="7" t="inlineStr">
         <is>
-          <t>2026-01-31 23:15:28</t>
+          <t>2026-01-31 14:15:28</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -29568,7 +29568,7 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>2026-01-29 00:36:39</t>
+          <t>2026-01-28 15:36:39</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -29648,7 +29648,7 @@
     <row r="330">
       <c r="A330" s="7" t="inlineStr">
         <is>
-          <t>2026-01-29 00:02:45</t>
+          <t>2026-01-28 15:02:45</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -29728,7 +29728,7 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 23:26:47</t>
+          <t>2026-01-28 14:26:47</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -29808,7 +29808,7 @@
     <row r="332">
       <c r="A332" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 23:04:33</t>
+          <t>2026-01-28 14:04:33</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -29888,7 +29888,7 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28 00:33:31</t>
+          <t>2026-01-27 15:33:31</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -29968,7 +29968,7 @@
     <row r="334">
       <c r="A334" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 23:59:21</t>
+          <t>2026-01-27 14:59:21</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -30048,7 +30048,7 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27 23:08:33</t>
+          <t>2026-01-27 14:08:33</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -30128,7 +30128,7 @@
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 23:28:17</t>
+          <t>2026-01-25 14:28:17</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -30208,7 +30208,7 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 22:56:22</t>
+          <t>2026-01-25 13:56:22</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -30288,7 +30288,7 @@
     <row r="338">
       <c r="A338" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 22:28:25</t>
+          <t>2026-01-25 13:28:25</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -30368,7 +30368,7 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 21:42:03</t>
+          <t>2026-01-25 12:42:03</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -30448,7 +30448,7 @@
     <row r="340">
       <c r="A340" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 19:38:23</t>
+          <t>2026-01-25 10:38:23</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -30528,7 +30528,7 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 18:56:35</t>
+          <t>2026-01-25 09:56:35</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -30608,7 +30608,7 @@
     <row r="342">
       <c r="A342" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 18:29:19</t>
+          <t>2026-01-25 09:29:19</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -30688,7 +30688,7 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25 17:14:05</t>
+          <t>2026-01-25 08:14:05</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -30768,7 +30768,7 @@
     <row r="344">
       <c r="A344" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 02:47:24</t>
+          <t>2026-01-23 17:47:24</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -30848,7 +30848,7 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 02:12:26</t>
+          <t>2026-01-23 17:12:26</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -30928,7 +30928,7 @@
     <row r="346">
       <c r="A346" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 01:33:34</t>
+          <t>2026-01-23 16:33:34</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -31008,7 +31008,7 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 01:00:39</t>
+          <t>2026-01-23 16:00:39</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -31088,7 +31088,7 @@
     <row r="348">
       <c r="A348" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24 00:19:07</t>
+          <t>2026-01-23 15:19:07</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -31168,7 +31168,7 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 23:52:33</t>
+          <t>2026-01-23 14:52:33</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -31248,7 +31248,7 @@
     <row r="350">
       <c r="A350" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 23:19:19</t>
+          <t>2026-01-23 14:19:19</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -31328,7 +31328,7 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36:59</t>
+          <t>2026-01-23 13:36:59</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -31408,7 +31408,7 @@
     <row r="352">
       <c r="A352" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 03:01:58</t>
+          <t>2026-01-22 18:01:58</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -31488,7 +31488,7 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 02:25:41</t>
+          <t>2026-01-22 17:25:41</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -31568,7 +31568,7 @@
     <row r="354">
       <c r="A354" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23 00:32:45</t>
+          <t>2026-01-22 15:32:45</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -31648,7 +31648,7 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 23:54:46</t>
+          <t>2026-01-22 14:54:46</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -31728,7 +31728,7 @@
     <row r="356">
       <c r="A356" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 23:17:42</t>
+          <t>2026-01-22 14:17:42</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -31808,7 +31808,7 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22 01:10:08</t>
+          <t>2026-01-21 16:10:08</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -31888,7 +31888,7 @@
     <row r="358">
       <c r="A358" s="7" t="inlineStr">
         <is>
-          <t>2026-01-21 00:27:51</t>
+          <t>2026-01-20 15:27:51</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -31968,7 +31968,7 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 23:25:34</t>
+          <t>2026-01-20 14:25:34</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -32048,7 +32048,7 @@
     <row r="360">
       <c r="A360" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20 22:56:13</t>
+          <t>2026-01-20 13:56:13</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -32128,7 +32128,7 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>2026-01-19 01:59:11</t>
+          <t>2026-01-18 16:59:11</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -32208,7 +32208,7 @@
     <row r="362">
       <c r="A362" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 03:05:32</t>
+          <t>2026-01-17 18:05:32</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -32288,7 +32288,7 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 02:19:17</t>
+          <t>2026-01-17 17:19:17</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -32368,7 +32368,7 @@
     <row r="364">
       <c r="A364" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 01:58:17</t>
+          <t>2026-01-17 16:58:17</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -32448,7 +32448,7 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 01:18:29</t>
+          <t>2026-01-17 16:18:29</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -32528,7 +32528,7 @@
     <row r="366">
       <c r="A366" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18 00:38:58</t>
+          <t>2026-01-17 15:38:58</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -32608,7 +32608,7 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 18:46:30</t>
+          <t>2026-01-17 09:46:30</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -32688,7 +32688,7 @@
     <row r="368">
       <c r="A368" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 02:21:36</t>
+          <t>2026-01-16 17:21:36</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -32768,7 +32768,7 @@
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 01:51:05</t>
+          <t>2026-01-16 16:51:05</t>
         </is>
       </c>
       <c r="B369" s="7" t="inlineStr">
@@ -32848,7 +32848,7 @@
     <row r="370">
       <c r="A370" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17 01:18:22</t>
+          <t>2026-01-16 16:18:22</t>
         </is>
       </c>
       <c r="B370" s="7" t="inlineStr">
@@ -32928,7 +32928,7 @@
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 01:41:15</t>
+          <t>2026-01-15 16:41:15</t>
         </is>
       </c>
       <c r="B371" s="7" t="inlineStr">
@@ -33008,7 +33008,7 @@
     <row r="372">
       <c r="A372" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16 01:05:38</t>
+          <t>2026-01-15 16:05:38</t>
         </is>
       </c>
       <c r="B372" s="7" t="inlineStr">
@@ -33088,7 +33088,7 @@
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14 00:57:21</t>
+          <t>2026-01-13 15:57:21</t>
         </is>
       </c>
       <c r="B373" s="7" t="inlineStr">
@@ -33168,7 +33168,7 @@
     <row r="374">
       <c r="A374" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14 00:19:49</t>
+          <t>2026-01-13 15:19:49</t>
         </is>
       </c>
       <c r="B374" s="7" t="inlineStr">
@@ -33248,7 +33248,7 @@
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 23:53:29</t>
+          <t>2026-01-13 14:53:29</t>
         </is>
       </c>
       <c r="B375" s="7" t="inlineStr">
@@ -33328,7 +33328,7 @@
     <row r="376">
       <c r="A376" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 02:23:29</t>
+          <t>2026-01-12 17:23:29</t>
         </is>
       </c>
       <c r="B376" s="7" t="inlineStr">
@@ -33408,7 +33408,7 @@
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 01:42:12</t>
+          <t>2026-01-12 16:42:12</t>
         </is>
       </c>
       <c r="B377" s="7" t="inlineStr">
@@ -33488,7 +33488,7 @@
     <row r="378">
       <c r="A378" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 01:17:01</t>
+          <t>2026-01-12 16:17:01</t>
         </is>
       </c>
       <c r="B378" s="7" t="inlineStr">
@@ -33568,7 +33568,7 @@
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13 00:43:11</t>
+          <t>2026-01-12 15:43:11</t>
         </is>
       </c>
       <c r="B379" s="7" t="inlineStr">
@@ -33648,7 +33648,7 @@
     <row r="380">
       <c r="A380" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 17:24:44</t>
+          <t>2026-01-12 08:24:44</t>
         </is>
       </c>
       <c r="B380" s="7" t="inlineStr">
@@ -33728,7 +33728,7 @@
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12 03:12:16</t>
+          <t>2026-01-11 18:12:16</t>
         </is>
       </c>
       <c r="B381" s="7" t="inlineStr">
@@ -33808,7 +33808,7 @@
     <row r="382">
       <c r="A382" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 02:54:03</t>
+          <t>2026-01-10 17:54:03</t>
         </is>
       </c>
       <c r="B382" s="7" t="inlineStr">
@@ -33888,7 +33888,7 @@
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 02:14:56</t>
+          <t>2026-01-10 17:14:56</t>
         </is>
       </c>
       <c r="B383" s="7" t="inlineStr">
@@ -33968,7 +33968,7 @@
     <row r="384">
       <c r="A384" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 01:17:21</t>
+          <t>2026-01-10 16:17:21</t>
         </is>
       </c>
       <c r="B384" s="7" t="inlineStr">
@@ -34048,7 +34048,7 @@
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11 00:22:11</t>
+          <t>2026-01-10 15:22:11</t>
         </is>
       </c>
       <c r="B385" s="7" t="inlineStr">
@@ -34128,7 +34128,7 @@
     <row r="386">
       <c r="A386" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 23:38:24</t>
+          <t>2026-01-10 14:38:24</t>
         </is>
       </c>
       <c r="B386" s="7" t="inlineStr">
@@ -34208,7 +34208,7 @@
     <row r="387">
       <c r="A387" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 02:54:19</t>
+          <t>2026-01-09 17:54:19</t>
         </is>
       </c>
       <c r="B387" s="7" t="inlineStr">
@@ -34288,7 +34288,7 @@
     <row r="388">
       <c r="A388" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10 02:00:16</t>
+          <t>2026-01-09 17:00:16</t>
         </is>
       </c>
       <c r="B388" s="7" t="inlineStr">
@@ -34368,7 +34368,7 @@
     <row r="389">
       <c r="A389" s="7" t="inlineStr">
         <is>
-          <t>2026-01-09 23:36:27</t>
+          <t>2026-01-09 14:36:27</t>
         </is>
       </c>
       <c r="B389" s="7" t="inlineStr">
@@ -34445,8 +34445,88 @@
         </is>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-05 14:21:47</t>
+        </is>
+      </c>
+      <c r="B390" s="7" t="inlineStr">
+        <is>
+          <t>ランク(ソロ/デュオ)</t>
+        </is>
+      </c>
+      <c r="C390" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D390" s="7" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E390" s="7" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F390" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G390" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H390" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I390" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J390" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K390" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="L390" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M390" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N390" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="O390" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P390" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q390" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R390" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S390" s="11" t="n">
+        <v>6751</v>
+      </c>
+      <c r="T390" s="11" t="n">
+        <v>2219</v>
+      </c>
+      <c r="U390" s="6" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V390" s="7" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V389"/>
+  <autoFilter ref="A1:V390"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34457,7 +34537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P389"/>
+  <dimension ref="A1:P390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -34563,7 +34643,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07 01:41:05</t>
+          <t>2026-08-06 16:41:05</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
@@ -34625,7 +34705,7 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07 01:01:17</t>
+          <t>2026-08-06 16:01:17</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
@@ -34687,7 +34767,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06 23:23:16</t>
+          <t>2026-08-06 14:23:16</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -34749,7 +34829,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>2026-08-06 22:29:00</t>
+          <t>2026-08-06 13:29:00</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -34811,7 +34891,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>2026-08-05 23:53:01</t>
+          <t>2026-08-05 14:53:01</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -34873,7 +34953,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>2026-08-05 23:15:09</t>
+          <t>2026-08-05 14:15:09</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -34935,7 +35015,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03 02:00:01</t>
+          <t>2026-08-02 17:00:01</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -34997,7 +35077,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03 00:22:22</t>
+          <t>2026-08-02 15:22:22</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -35059,7 +35139,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 23:45:22</t>
+          <t>2026-08-02 14:45:22</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -35121,7 +35201,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 18:45:07</t>
+          <t>2026-08-02 09:45:07</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -35183,7 +35263,7 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 18:20:05</t>
+          <t>2026-08-02 09:20:05</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -35245,7 +35325,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:32</t>
+          <t>2026-08-02 08:49:32</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -35307,7 +35387,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 03:33:03</t>
+          <t>2026-08-01 18:33:03</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
@@ -35369,7 +35449,7 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>2026-08-02 02:39:30</t>
+          <t>2026-08-01 17:39:30</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -35431,7 +35511,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 04:00:11</t>
+          <t>2026-07-31 19:00:11</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -35493,7 +35573,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 03:30:26</t>
+          <t>2026-07-31 18:30:26</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -35555,7 +35635,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 02:52:16</t>
+          <t>2026-07-31 17:52:16</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -35617,7 +35697,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 01:50:20</t>
+          <t>2026-07-31 16:50:20</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -35679,7 +35759,7 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>2026-08-01 01:16:45</t>
+          <t>2026-07-31 16:16:45</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -35741,7 +35821,7 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 22:56:19</t>
+          <t>2026-07-31 13:56:19</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -35803,7 +35883,7 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 22:22:46</t>
+          <t>2026-07-31 13:22:46</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -35865,7 +35945,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>2026-07-31 21:49:35</t>
+          <t>2026-07-31 12:49:35</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -35927,7 +36007,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 23:51:39</t>
+          <t>2026-07-28 14:51:39</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -35989,7 +36069,7 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>2026-07-28 23:05:20</t>
+          <t>2026-07-28 14:05:20</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -36051,7 +36131,7 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>2026-07-27 01:21:51</t>
+          <t>2026-07-26 16:21:51</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
@@ -36113,7 +36193,7 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>2026-07-27 00:43:02</t>
+          <t>2026-07-26 15:43:02</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -36175,7 +36255,7 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 23:12:09</t>
+          <t>2026-07-25 14:12:09</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
@@ -36237,7 +36317,7 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 22:30:57</t>
+          <t>2026-07-25 13:30:57</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -36299,7 +36379,7 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>2026-07-25 00:11:55</t>
+          <t>2026-07-24 15:11:55</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
@@ -36361,7 +36441,7 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>2026-07-24 23:25:38</t>
+          <t>2026-07-24 14:25:38</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
@@ -36423,7 +36503,7 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>2026-07-22 00:17:56</t>
+          <t>2026-07-21 15:17:56</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
@@ -36485,7 +36565,7 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>2026-07-22 00:04:35</t>
+          <t>2026-07-21 15:04:35</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -36547,7 +36627,7 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 23:25:56</t>
+          <t>2026-07-21 14:25:56</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
@@ -36609,7 +36689,7 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 22:44:36</t>
+          <t>2026-07-21 13:44:36</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
@@ -36671,7 +36751,7 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>2026-07-21 22:18:59</t>
+          <t>2026-07-21 13:18:59</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
@@ -36733,7 +36813,7 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>2026-07-20 03:20:20</t>
+          <t>2026-07-19 18:20:20</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -36795,7 +36875,7 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>2026-07-20 02:39:51</t>
+          <t>2026-07-19 17:39:51</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
@@ -36857,7 +36937,7 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:59:14</t>
+          <t>2026-07-18 09:59:14</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -36919,7 +36999,7 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:21:14</t>
+          <t>2026-07-18 09:21:14</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
@@ -36981,7 +37061,7 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 23:06:28</t>
+          <t>2026-07-16 14:06:28</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
@@ -37043,7 +37123,7 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 22:32:42</t>
+          <t>2026-07-16 13:32:42</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
@@ -37105,7 +37185,7 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16 00:40:48</t>
+          <t>2026-07-15 15:40:48</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
@@ -37167,7 +37247,7 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 23:41:56</t>
+          <t>2026-07-15 14:41:56</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
@@ -37229,7 +37309,7 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 22:58:44</t>
+          <t>2026-07-15 13:58:44</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
@@ -37291,7 +37371,7 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15 22:34:16</t>
+          <t>2026-07-15 13:34:16</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
@@ -37353,7 +37433,7 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 23:36:35</t>
+          <t>2026-07-14 14:36:35</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
@@ -37415,7 +37495,7 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 22:49:50</t>
+          <t>2026-07-14 13:49:50</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
@@ -37477,7 +37557,7 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 01:02:29</t>
+          <t>2026-07-13 16:02:29</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
@@ -37539,7 +37619,7 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14 00:22:46</t>
+          <t>2026-07-13 15:22:46</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
@@ -37601,7 +37681,7 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 23:51:38</t>
+          <t>2026-07-13 14:51:38</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
@@ -37663,7 +37743,7 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 02:05:19</t>
+          <t>2026-07-12 17:05:19</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
@@ -37725,7 +37805,7 @@
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>2026-07-13 01:29:17</t>
+          <t>2026-07-12 16:29:17</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
@@ -37787,7 +37867,7 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 03:11:38</t>
+          <t>2026-07-11 18:11:38</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
@@ -37849,7 +37929,7 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12 02:46:15</t>
+          <t>2026-07-11 17:46:15</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
@@ -37911,7 +37991,7 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 03:42:29</t>
+          <t>2026-07-10 18:42:29</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
@@ -37973,7 +38053,7 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11 03:06:21</t>
+          <t>2026-07-10 18:06:21</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
@@ -38035,7 +38115,7 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:55:25</t>
+          <t>2026-07-08 17:55:25</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
@@ -38097,7 +38177,7 @@
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:17:09</t>
+          <t>2026-07-08 17:17:09</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
@@ -38159,7 +38239,7 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 02:03:51</t>
+          <t>2026-07-05 17:03:51</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
@@ -38221,7 +38301,7 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 01:07:17</t>
+          <t>2026-07-05 16:07:17</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
@@ -38283,7 +38363,7 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06 00:23:00</t>
+          <t>2026-07-05 15:23:00</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
@@ -38345,7 +38425,7 @@
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>2026-07-05 03:21:23</t>
+          <t>2026-07-04 18:21:23</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
@@ -38407,7 +38487,7 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>2026-07-04 03:01:40</t>
+          <t>2026-07-03 18:01:40</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
@@ -38469,7 +38549,7 @@
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>2026-07-03 01:48:19</t>
+          <t>2026-07-02 16:48:19</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
@@ -38531,7 +38611,7 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>2026-07-01 00:21:19</t>
+          <t>2026-06-30 15:21:19</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
@@ -38593,7 +38673,7 @@
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 23:38:16</t>
+          <t>2026-06-30 14:38:16</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
@@ -38655,7 +38735,7 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 01:16:28</t>
+          <t>2026-06-29 16:16:28</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
@@ -38717,7 +38797,7 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>2026-06-30 00:34:32</t>
+          <t>2026-06-29 15:34:32</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
@@ -38779,7 +38859,7 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>2026-06-26 00:50:56</t>
+          <t>2026-06-25 15:50:56</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
@@ -38841,7 +38921,7 @@
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>2026-06-26 00:06:40</t>
+          <t>2026-06-25 15:06:40</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
@@ -38903,7 +38983,7 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 02:07:56</t>
+          <t>2026-06-24 17:07:56</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
@@ -38965,7 +39045,7 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 01:33:19</t>
+          <t>2026-06-24 16:33:19</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
@@ -39027,7 +39107,7 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:47:59</t>
+          <t>2026-06-24 15:47:59</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
@@ -39089,7 +39169,7 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:08:31</t>
+          <t>2026-06-24 15:08:31</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
@@ -39151,7 +39231,7 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 23:33:15</t>
+          <t>2026-06-24 14:33:15</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
@@ -39213,7 +39293,7 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>2026-06-24 22:39:11</t>
+          <t>2026-06-24 13:39:11</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
@@ -39275,7 +39355,7 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 01:16:06</t>
+          <t>2026-06-22 16:16:06</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
@@ -39337,7 +39417,7 @@
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 00:38:08</t>
+          <t>2026-06-22 15:38:08</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
@@ -39399,7 +39479,7 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>2026-06-23 00:29:33</t>
+          <t>2026-06-22 15:29:33</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
@@ -39461,7 +39541,7 @@
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 01:54:04</t>
+          <t>2026-06-18 16:54:04</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
@@ -39523,7 +39603,7 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 01:14:50</t>
+          <t>2026-06-18 16:14:50</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
@@ -39585,7 +39665,7 @@
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19 00:35:17</t>
+          <t>2026-06-18 15:35:17</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
@@ -39647,7 +39727,7 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 23:55:50</t>
+          <t>2026-06-18 14:55:50</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
@@ -39709,7 +39789,7 @@
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18 00:44:42</t>
+          <t>2026-06-17 15:44:42</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
@@ -39771,7 +39851,7 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 23:57:38</t>
+          <t>2026-06-17 14:57:38</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
@@ -39833,7 +39913,7 @@
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 01:58:55</t>
+          <t>2026-06-16 16:58:55</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
@@ -39895,7 +39975,7 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17 01:30:07</t>
+          <t>2026-06-16 16:30:07</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
@@ -39957,7 +40037,7 @@
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 03:10:28</t>
+          <t>2026-06-14 18:10:28</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
@@ -40019,7 +40099,7 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 02:27:52</t>
+          <t>2026-06-14 17:27:52</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
@@ -40081,7 +40161,7 @@
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 01:57:23</t>
+          <t>2026-06-14 16:57:23</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
@@ -40143,7 +40223,7 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 01:27:22</t>
+          <t>2026-06-14 16:27:22</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
@@ -40205,7 +40285,7 @@
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>2026-06-15 00:24:35</t>
+          <t>2026-06-14 15:24:35</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
@@ -40267,7 +40347,7 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 23:46:55</t>
+          <t>2026-06-14 14:46:55</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
@@ -40329,7 +40409,7 @@
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 01:41:53</t>
+          <t>2026-06-13 16:41:53</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
@@ -40391,7 +40471,7 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 00:52:58</t>
+          <t>2026-06-13 15:52:58</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
@@ -40453,7 +40533,7 @@
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>2026-06-14 00:14:23</t>
+          <t>2026-06-13 15:14:23</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
@@ -40515,7 +40595,7 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 23:45:21</t>
+          <t>2026-06-13 14:45:21</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
@@ -40577,7 +40657,7 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>2026-06-13 23:05:32</t>
+          <t>2026-06-13 14:05:32</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
@@ -40639,7 +40719,7 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 01:08:14</t>
+          <t>2026-06-10 16:08:14</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
@@ -40701,7 +40781,7 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:34:35</t>
+          <t>2026-06-10 15:34:35</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
@@ -40763,7 +40843,7 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:09:17</t>
+          <t>2026-06-10 15:09:17</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
@@ -40825,7 +40905,7 @@
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 23:27:53</t>
+          <t>2026-06-10 14:27:53</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
@@ -40887,7 +40967,7 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 00:49:00</t>
+          <t>2026-06-09 15:49:00</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
@@ -40949,7 +41029,7 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>2026-06-06 02:58:51</t>
+          <t>2026-06-05 17:58:51</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
@@ -41011,7 +41091,7 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>2026-06-06 02:15:04</t>
+          <t>2026-06-05 17:15:04</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
@@ -41073,7 +41153,7 @@
     <row r="107">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 23:49:14</t>
+          <t>2026-06-04 14:49:14</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
@@ -41135,7 +41215,7 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 21:40:04</t>
+          <t>2026-06-04 12:40:04</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
@@ -41197,7 +41277,7 @@
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 21:17:24</t>
+          <t>2026-06-04 12:17:24</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
@@ -41259,7 +41339,7 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 01:06:27</t>
+          <t>2026-06-03 16:06:27</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
@@ -41321,7 +41401,7 @@
     <row r="111">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04 00:31:09</t>
+          <t>2026-06-03 15:31:09</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
@@ -41383,7 +41463,7 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 23:53:57</t>
+          <t>2026-06-03 14:53:57</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
@@ -41445,7 +41525,7 @@
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>2026-06-03 22:44:02</t>
+          <t>2026-06-03 13:44:02</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
@@ -41507,7 +41587,7 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>2026-06-02 22:49:11</t>
+          <t>2026-06-02 13:49:11</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
@@ -41569,7 +41649,7 @@
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:56:06</t>
+          <t>2026-06-01 14:56:06</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
@@ -41631,7 +41711,7 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:20:26</t>
+          <t>2026-06-01 14:20:26</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
@@ -41693,7 +41773,7 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01 23:01:06</t>
+          <t>2026-06-01 14:01:06</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
@@ -41755,7 +41835,7 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>2026-05-31 03:01:04</t>
+          <t>2026-05-30 18:01:04</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
@@ -41817,7 +41897,7 @@
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>2026-05-31 02:13:41</t>
+          <t>2026-05-30 17:13:41</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
@@ -41879,7 +41959,7 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 23:00:40</t>
+          <t>2026-05-25 14:00:40</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
@@ -41941,7 +42021,7 @@
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 01:55:47</t>
+          <t>2026-05-24 16:55:47</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
@@ -42003,7 +42083,7 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>2026-05-25 01:24:22</t>
+          <t>2026-05-24 16:24:22</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
@@ -42065,7 +42145,7 @@
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 23:49:25</t>
+          <t>2026-05-24 14:49:25</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
@@ -42127,7 +42207,7 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 03:13:39</t>
+          <t>2026-05-23 18:13:39</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr">
@@ -42189,7 +42269,7 @@
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>2026-05-24 02:41:52</t>
+          <t>2026-05-23 17:41:52</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr">
@@ -42251,7 +42331,7 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 23:19:04</t>
+          <t>2026-05-23 14:19:04</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr">
@@ -42313,7 +42393,7 @@
     <row r="127">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 22:43:20</t>
+          <t>2026-05-23 13:43:20</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
@@ -42375,7 +42455,7 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 15:54:19</t>
+          <t>2026-05-23 06:54:19</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
@@ -42437,7 +42517,7 @@
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>2026-05-23 02:25:24</t>
+          <t>2026-05-22 17:25:24</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
@@ -42499,7 +42579,7 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 01:29:23</t>
+          <t>2026-05-21 16:29:23</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
@@ -42561,7 +42641,7 @@
     <row r="131">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 00:48:49</t>
+          <t>2026-05-21 15:48:49</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
@@ -42623,7 +42703,7 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:45</t>
+          <t>2026-05-21 15:00:45</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
@@ -42685,7 +42765,7 @@
     <row r="133">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 23:22:44</t>
+          <t>2026-05-21 14:22:44</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
@@ -42747,7 +42827,7 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>2026-05-21 00:05:15</t>
+          <t>2026-05-20 15:05:15</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr">
@@ -42809,7 +42889,7 @@
     <row r="135">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 23:43:50</t>
+          <t>2026-05-20 14:43:50</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
@@ -42871,7 +42951,7 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 22:57:45</t>
+          <t>2026-05-20 13:57:45</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
@@ -42933,7 +43013,7 @@
     <row r="137">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 01:25:45</t>
+          <t>2026-05-19 16:25:45</t>
         </is>
       </c>
       <c r="B137" s="13" t="inlineStr">
@@ -42995,7 +43075,7 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>2026-05-20 00:46:42</t>
+          <t>2026-05-19 15:46:42</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
@@ -43057,7 +43137,7 @@
     <row r="139">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>2026-05-18 22:56:39</t>
+          <t>2026-05-18 13:56:39</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
@@ -43119,7 +43199,7 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 01:35:56</t>
+          <t>2026-05-14 16:35:56</t>
         </is>
       </c>
       <c r="B140" s="13" t="inlineStr">
@@ -43181,7 +43261,7 @@
     <row r="141">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 01:17:05</t>
+          <t>2026-05-14 16:17:05</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
@@ -43243,7 +43323,7 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 00:05:48</t>
+          <t>2026-05-14 15:05:48</t>
         </is>
       </c>
       <c r="B142" s="13" t="inlineStr">
@@ -43305,7 +43385,7 @@
     <row r="143">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>2026-05-14 01:25:38</t>
+          <t>2026-05-13 16:25:38</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
@@ -43367,7 +43447,7 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>2026-05-12 00:19:57</t>
+          <t>2026-05-11 15:19:57</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
@@ -43429,7 +43509,7 @@
     <row r="145">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 23:54:15</t>
+          <t>2026-05-11 14:54:15</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
@@ -43491,7 +43571,7 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 23:14:30</t>
+          <t>2026-05-11 14:14:30</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
@@ -43553,7 +43633,7 @@
     <row r="147">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 22:37:05</t>
+          <t>2026-05-11 13:37:05</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
@@ -43615,7 +43695,7 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 21:53:13</t>
+          <t>2026-05-11 12:53:13</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
@@ -43677,7 +43757,7 @@
     <row r="149">
       <c r="A149" s="13" t="inlineStr">
         <is>
-          <t>2026-05-11 00:04:01</t>
+          <t>2026-05-10 15:04:01</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
@@ -43739,7 +43819,7 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:54:24</t>
+          <t>2026-05-09 16:54:24</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
@@ -43801,7 +43881,7 @@
     <row r="151">
       <c r="A151" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:22:50</t>
+          <t>2026-05-09 16:22:50</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
@@ -43863,7 +43943,7 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>2026-05-10 00:26:16</t>
+          <t>2026-05-09 15:26:16</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
@@ -43925,7 +44005,7 @@
     <row r="153">
       <c r="A153" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 23:38:30</t>
+          <t>2026-05-09 14:38:30</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
@@ -43987,7 +44067,7 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 22:50:20</t>
+          <t>2026-05-09 13:50:20</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
@@ -44049,7 +44129,7 @@
     <row r="155">
       <c r="A155" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 22:13:25</t>
+          <t>2026-05-09 13:13:25</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
@@ -44111,7 +44191,7 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 20:00:11</t>
+          <t>2026-05-09 11:00:11</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
@@ -44173,7 +44253,7 @@
     <row r="157">
       <c r="A157" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 19:10:28</t>
+          <t>2026-05-09 10:10:28</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
@@ -44235,7 +44315,7 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 02:17:27</t>
+          <t>2026-05-08 17:17:27</t>
         </is>
       </c>
       <c r="B158" s="13" t="inlineStr">
@@ -44297,7 +44377,7 @@
     <row r="159">
       <c r="A159" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 01:38:25</t>
+          <t>2026-05-08 16:38:25</t>
         </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
@@ -44359,7 +44439,7 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 00:58:58</t>
+          <t>2026-05-08 15:58:58</t>
         </is>
       </c>
       <c r="B160" s="13" t="inlineStr">
@@ -44421,7 +44501,7 @@
     <row r="161">
       <c r="A161" s="13" t="inlineStr">
         <is>
-          <t>2026-05-09 00:37:55</t>
+          <t>2026-05-08 15:37:55</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
@@ -44483,7 +44563,7 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 01:48:31</t>
+          <t>2026-05-07 16:48:31</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
@@ -44545,7 +44625,7 @@
     <row r="163">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 01:02:52</t>
+          <t>2026-05-07 16:02:52</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
@@ -44607,7 +44687,7 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>2026-05-08 00:23:29</t>
+          <t>2026-05-07 15:23:29</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
@@ -44669,7 +44749,7 @@
     <row r="165">
       <c r="A165" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 01:30:56</t>
+          <t>2026-05-06 16:30:56</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
@@ -44731,7 +44811,7 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07 00:42:16</t>
+          <t>2026-05-06 15:42:16</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
@@ -44793,7 +44873,7 @@
     <row r="167">
       <c r="A167" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 23:44:04</t>
+          <t>2026-05-06 14:44:04</t>
         </is>
       </c>
       <c r="B167" s="13" t="inlineStr">
@@ -44855,7 +44935,7 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:13:52</t>
+          <t>2026-05-06 09:13:52</t>
         </is>
       </c>
       <c r="B168" s="13" t="inlineStr">
@@ -44917,7 +44997,7 @@
     <row r="169">
       <c r="A169" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:05:08</t>
+          <t>2026-05-06 09:05:08</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
@@ -44979,7 +45059,7 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 17:22:30</t>
+          <t>2026-05-06 08:22:30</t>
         </is>
       </c>
       <c r="B170" s="13" t="inlineStr">
@@ -45041,7 +45121,7 @@
     <row r="171">
       <c r="A171" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 16:28:42</t>
+          <t>2026-05-06 07:28:42</t>
         </is>
       </c>
       <c r="B171" s="13" t="inlineStr">
@@ -45103,7 +45183,7 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 03:16:57</t>
+          <t>2026-05-05 18:16:57</t>
         </is>
       </c>
       <c r="B172" s="13" t="inlineStr">
@@ -45165,7 +45245,7 @@
     <row r="173">
       <c r="A173" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:32:40</t>
+          <t>2026-05-05 17:32:40</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
@@ -45227,7 +45307,7 @@
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:23:28</t>
+          <t>2026-05-05 17:23:28</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
@@ -45289,7 +45369,7 @@
     <row r="175">
       <c r="A175" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 01:48:28</t>
+          <t>2026-05-05 16:48:28</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
@@ -45351,7 +45431,7 @@
     <row r="176">
       <c r="A176" s="13" t="inlineStr">
         <is>
-          <t>2026-05-06 00:52:33</t>
+          <t>2026-05-05 15:52:33</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
@@ -45413,7 +45493,7 @@
     <row r="177">
       <c r="A177" s="13" t="inlineStr">
         <is>
-          <t>2026-05-05 17:43:06</t>
+          <t>2026-05-05 08:43:06</t>
         </is>
       </c>
       <c r="B177" s="13" t="inlineStr">
@@ -45475,7 +45555,7 @@
     <row r="178">
       <c r="A178" s="13" t="inlineStr">
         <is>
-          <t>2026-05-03 00:36:42</t>
+          <t>2026-05-02 15:36:42</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
@@ -45537,7 +45617,7 @@
     <row r="179">
       <c r="A179" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 23:51:09</t>
+          <t>2026-05-02 14:51:09</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
@@ -45599,7 +45679,7 @@
     <row r="180">
       <c r="A180" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 22:15:10</t>
+          <t>2026-05-02 13:15:10</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
@@ -45661,7 +45741,7 @@
     <row r="181">
       <c r="A181" s="13" t="inlineStr">
         <is>
-          <t>2026-05-02 21:29:49</t>
+          <t>2026-05-02 12:29:49</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
@@ -45723,7 +45803,7 @@
     <row r="182">
       <c r="A182" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 01:39:42</t>
+          <t>2026-04-30 16:39:42</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
@@ -45785,7 +45865,7 @@
     <row r="183">
       <c r="A183" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 01:01:34</t>
+          <t>2026-04-30 16:01:34</t>
         </is>
       </c>
       <c r="B183" s="13" t="inlineStr">
@@ -45847,7 +45927,7 @@
     <row r="184">
       <c r="A184" s="13" t="inlineStr">
         <is>
-          <t>2026-05-01 00:24:48</t>
+          <t>2026-04-30 15:24:48</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
@@ -45909,7 +45989,7 @@
     <row r="185">
       <c r="A185" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 23:37:10</t>
+          <t>2026-04-30 14:37:10</t>
         </is>
       </c>
       <c r="B185" s="13" t="inlineStr">
@@ -45971,7 +46051,7 @@
     <row r="186">
       <c r="A186" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 22:58:06</t>
+          <t>2026-04-30 13:58:06</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
@@ -46033,7 +46113,7 @@
     <row r="187">
       <c r="A187" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 03:29:33</t>
+          <t>2026-04-29 18:29:33</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
@@ -46095,7 +46175,7 @@
     <row r="188">
       <c r="A188" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 02:54:07</t>
+          <t>2026-04-29 17:54:07</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
@@ -46157,7 +46237,7 @@
     <row r="189">
       <c r="A189" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 02:20:58</t>
+          <t>2026-04-29 17:20:58</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
@@ -46219,7 +46299,7 @@
     <row r="190">
       <c r="A190" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 01:42:01</t>
+          <t>2026-04-29 16:42:01</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
@@ -46281,7 +46361,7 @@
     <row r="191">
       <c r="A191" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 01:03:17</t>
+          <t>2026-04-29 16:03:17</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
@@ -46343,7 +46423,7 @@
     <row r="192">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>2026-04-30 00:19:47</t>
+          <t>2026-04-29 15:19:47</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
@@ -46405,7 +46485,7 @@
     <row r="193">
       <c r="A193" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 23:29:53</t>
+          <t>2026-04-29 14:29:53</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
@@ -46467,7 +46547,7 @@
     <row r="194">
       <c r="A194" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:59:49</t>
+          <t>2026-04-29 13:59:49</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
@@ -46529,7 +46609,7 @@
     <row r="195">
       <c r="A195" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:38:22</t>
+          <t>2026-04-29 13:38:22</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
@@ -46591,7 +46671,7 @@
     <row r="196">
       <c r="A196" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:44</t>
+          <t>2026-04-29 13:17:44</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
@@ -46653,7 +46733,7 @@
     <row r="197">
       <c r="A197" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 03:28:56</t>
+          <t>2026-04-28 18:28:56</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
@@ -46715,7 +46795,7 @@
     <row r="198">
       <c r="A198" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:58:50</t>
+          <t>2026-04-28 17:58:50</t>
         </is>
       </c>
       <c r="B198" s="13" t="inlineStr">
@@ -46777,7 +46857,7 @@
     <row r="199">
       <c r="A199" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:29:43</t>
+          <t>2026-04-28 17:29:43</t>
         </is>
       </c>
       <c r="B199" s="13" t="inlineStr">
@@ -46839,7 +46919,7 @@
     <row r="200">
       <c r="A200" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 01:38:43</t>
+          <t>2026-04-28 16:38:43</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
@@ -46901,7 +46981,7 @@
     <row r="201">
       <c r="A201" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:54</t>
+          <t>2026-04-28 15:58:54</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
@@ -46963,7 +47043,7 @@
     <row r="202">
       <c r="A202" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:31:32</t>
+          <t>2026-04-28 15:31:32</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
@@ -47025,7 +47105,7 @@
     <row r="203">
       <c r="A203" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:04:20</t>
+          <t>2026-04-28 15:04:20</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
@@ -47087,7 +47167,7 @@
     <row r="204">
       <c r="A204" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 23:37:27</t>
+          <t>2026-04-28 14:37:27</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
@@ -47149,7 +47229,7 @@
     <row r="205">
       <c r="A205" s="13" t="inlineStr">
         <is>
-          <t>2026-04-28 23:09:10</t>
+          <t>2026-04-28 14:09:10</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
@@ -47211,7 +47291,7 @@
     <row r="206">
       <c r="A206" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:59:25</t>
+          <t>2026-04-27 14:59:25</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
@@ -47273,7 +47353,7 @@
     <row r="207">
       <c r="A207" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:49:35</t>
+          <t>2026-04-27 14:49:35</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
@@ -47335,7 +47415,7 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 22:55:34</t>
+          <t>2026-04-27 13:55:34</t>
         </is>
       </c>
       <c r="B208" s="13" t="inlineStr">
@@ -47397,7 +47477,7 @@
     <row r="209">
       <c r="A209" s="13" t="inlineStr">
         <is>
-          <t>2026-04-27 22:04:13</t>
+          <t>2026-04-27 13:04:13</t>
         </is>
       </c>
       <c r="B209" s="13" t="inlineStr">
@@ -47459,7 +47539,7 @@
     <row r="210">
       <c r="A210" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 02:49:02</t>
+          <t>2026-04-24 17:49:02</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
@@ -47521,7 +47601,7 @@
     <row r="211">
       <c r="A211" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 02:03:56</t>
+          <t>2026-04-24 17:03:56</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
@@ -47583,7 +47663,7 @@
     <row r="212">
       <c r="A212" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25 01:37:00</t>
+          <t>2026-04-24 16:37:00</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
@@ -47645,7 +47725,7 @@
     <row r="213">
       <c r="A213" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:33:59</t>
+          <t>2026-04-23 15:33:59</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
@@ -47707,7 +47787,7 @@
     <row r="214">
       <c r="A214" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:22:46</t>
+          <t>2026-04-23 15:22:46</t>
         </is>
       </c>
       <c r="B214" s="13" t="inlineStr">
@@ -47769,7 +47849,7 @@
     <row r="215">
       <c r="A215" s="13" t="inlineStr">
         <is>
-          <t>2026-04-24 00:12:54</t>
+          <t>2026-04-23 15:12:54</t>
         </is>
       </c>
       <c r="B215" s="13" t="inlineStr">
@@ -47831,7 +47911,7 @@
     <row r="216">
       <c r="A216" s="13" t="inlineStr">
         <is>
-          <t>2026-04-23 22:36:03</t>
+          <t>2026-04-23 13:36:03</t>
         </is>
       </c>
       <c r="B216" s="13" t="inlineStr">
@@ -47893,7 +47973,7 @@
     <row r="217">
       <c r="A217" s="13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:58:57</t>
+          <t>2026-04-13 15:58:57</t>
         </is>
       </c>
       <c r="B217" s="13" t="inlineStr">
@@ -47955,7 +48035,7 @@
     <row r="218">
       <c r="A218" s="13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:09:08</t>
+          <t>2026-04-13 15:09:08</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
@@ -48017,7 +48097,7 @@
     <row r="219">
       <c r="A219" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 01:48:02</t>
+          <t>2026-04-12 16:48:02</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
@@ -48079,7 +48159,7 @@
     <row r="220">
       <c r="A220" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 01:17:58</t>
+          <t>2026-04-12 16:17:58</t>
         </is>
       </c>
       <c r="B220" s="13" t="inlineStr">
@@ -48141,7 +48221,7 @@
     <row r="221">
       <c r="A221" s="13" t="inlineStr">
         <is>
-          <t>2026-04-13 00:41:20</t>
+          <t>2026-04-12 15:41:20</t>
         </is>
       </c>
       <c r="B221" s="13" t="inlineStr">
@@ -48203,7 +48283,7 @@
     <row r="222">
       <c r="A222" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 23:18:06</t>
+          <t>2026-04-09 14:18:06</t>
         </is>
       </c>
       <c r="B222" s="13" t="inlineStr">
@@ -48265,7 +48345,7 @@
     <row r="223">
       <c r="A223" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 22:52:44</t>
+          <t>2026-04-09 13:52:44</t>
         </is>
       </c>
       <c r="B223" s="13" t="inlineStr">
@@ -48327,7 +48407,7 @@
     <row r="224">
       <c r="A224" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 22:27:45</t>
+          <t>2026-04-09 13:27:45</t>
         </is>
       </c>
       <c r="B224" s="13" t="inlineStr">
@@ -48389,7 +48469,7 @@
     <row r="225">
       <c r="A225" s="13" t="inlineStr">
         <is>
-          <t>2026-04-08 01:10:31</t>
+          <t>2026-04-07 16:10:31</t>
         </is>
       </c>
       <c r="B225" s="13" t="inlineStr">
@@ -48451,7 +48531,7 @@
     <row r="226">
       <c r="A226" s="13" t="inlineStr">
         <is>
-          <t>2026-04-08 00:29:19</t>
+          <t>2026-04-07 15:29:19</t>
         </is>
       </c>
       <c r="B226" s="13" t="inlineStr">
@@ -48513,7 +48593,7 @@
     <row r="227">
       <c r="A227" s="13" t="inlineStr">
         <is>
-          <t>2026-04-04 04:36:31</t>
+          <t>2026-04-03 19:36:31</t>
         </is>
       </c>
       <c r="B227" s="13" t="inlineStr">
@@ -48575,7 +48655,7 @@
     <row r="228">
       <c r="A228" s="13" t="inlineStr">
         <is>
-          <t>2026-04-04 04:16:32</t>
+          <t>2026-04-03 19:16:32</t>
         </is>
       </c>
       <c r="B228" s="13" t="inlineStr">
@@ -48637,7 +48717,7 @@
     <row r="229">
       <c r="A229" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 04:24:43</t>
+          <t>2026-03-27 19:24:43</t>
         </is>
       </c>
       <c r="B229" s="13" t="inlineStr">
@@ -48699,7 +48779,7 @@
     <row r="230">
       <c r="A230" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:38:31</t>
+          <t>2026-03-27 18:38:31</t>
         </is>
       </c>
       <c r="B230" s="13" t="inlineStr">
@@ -48761,7 +48841,7 @@
     <row r="231">
       <c r="A231" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 03:17:50</t>
+          <t>2026-03-27 18:17:50</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
@@ -48823,7 +48903,7 @@
     <row r="232">
       <c r="A232" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 02:43:19</t>
+          <t>2026-03-27 17:43:19</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
@@ -48885,7 +48965,7 @@
     <row r="233">
       <c r="A233" s="13" t="inlineStr">
         <is>
-          <t>2026-03-28 02:15:18</t>
+          <t>2026-03-27 17:15:18</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
@@ -48947,7 +49027,7 @@
     <row r="234">
       <c r="A234" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 23:18:12</t>
+          <t>2026-03-25 14:18:12</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
@@ -49009,7 +49089,7 @@
     <row r="235">
       <c r="A235" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25 00:01:49</t>
+          <t>2026-03-24 15:01:49</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
@@ -49071,7 +49151,7 @@
     <row r="236">
       <c r="A236" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 23:25:16</t>
+          <t>2026-03-24 14:25:16</t>
         </is>
       </c>
       <c r="B236" s="13" t="inlineStr">
@@ -49133,7 +49213,7 @@
     <row r="237">
       <c r="A237" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 23:02:52</t>
+          <t>2026-03-24 14:02:52</t>
         </is>
       </c>
       <c r="B237" s="13" t="inlineStr">
@@ -49195,7 +49275,7 @@
     <row r="238">
       <c r="A238" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 22:26:26</t>
+          <t>2026-03-24 13:26:26</t>
         </is>
       </c>
       <c r="B238" s="13" t="inlineStr">
@@ -49257,7 +49337,7 @@
     <row r="239">
       <c r="A239" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 00:56:18</t>
+          <t>2026-03-23 15:56:18</t>
         </is>
       </c>
       <c r="B239" s="13" t="inlineStr">
@@ -49319,7 +49399,7 @@
     <row r="240">
       <c r="A240" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24 00:29:29</t>
+          <t>2026-03-23 15:29:29</t>
         </is>
       </c>
       <c r="B240" s="13" t="inlineStr">
@@ -49381,7 +49461,7 @@
     <row r="241">
       <c r="A241" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 23:51:11</t>
+          <t>2026-03-22 14:51:11</t>
         </is>
       </c>
       <c r="B241" s="13" t="inlineStr">
@@ -49443,7 +49523,7 @@
     <row r="242">
       <c r="A242" s="13" t="inlineStr">
         <is>
-          <t>2026-03-22 01:04:36</t>
+          <t>2026-03-21 16:04:36</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
@@ -49505,7 +49585,7 @@
     <row r="243">
       <c r="A243" s="13" t="inlineStr">
         <is>
-          <t>2026-03-21 02:55:49</t>
+          <t>2026-03-20 17:55:49</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
@@ -49567,7 +49647,7 @@
     <row r="244">
       <c r="A244" s="13" t="inlineStr">
         <is>
-          <t>2026-03-18 00:07:07</t>
+          <t>2026-03-17 15:07:07</t>
         </is>
       </c>
       <c r="B244" s="13" t="inlineStr">
@@ -49629,7 +49709,7 @@
     <row r="245">
       <c r="A245" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 23:24:05</t>
+          <t>2026-03-17 14:24:05</t>
         </is>
       </c>
       <c r="B245" s="13" t="inlineStr">
@@ -49691,7 +49771,7 @@
     <row r="246">
       <c r="A246" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 02:00:50</t>
+          <t>2026-03-16 17:00:50</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
@@ -49753,7 +49833,7 @@
     <row r="247">
       <c r="A247" s="13" t="inlineStr">
         <is>
-          <t>2026-03-17 01:33:08</t>
+          <t>2026-03-16 16:33:08</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
@@ -49815,7 +49895,7 @@
     <row r="248">
       <c r="A248" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 23:28:09</t>
+          <t>2026-03-16 14:28:09</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
@@ -49877,7 +49957,7 @@
     <row r="249">
       <c r="A249" s="13" t="inlineStr">
         <is>
-          <t>2026-03-16 01:32:22</t>
+          <t>2026-03-15 16:32:22</t>
         </is>
       </c>
       <c r="B249" s="13" t="inlineStr">
@@ -49939,7 +50019,7 @@
     <row r="250">
       <c r="A250" s="13" t="inlineStr">
         <is>
-          <t>2026-03-14 01:43:49</t>
+          <t>2026-03-13 16:43:49</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
@@ -50001,7 +50081,7 @@
     <row r="251">
       <c r="A251" s="13" t="inlineStr">
         <is>
-          <t>2026-03-14 01:19:35</t>
+          <t>2026-03-13 16:19:35</t>
         </is>
       </c>
       <c r="B251" s="13" t="inlineStr">
@@ -50063,7 +50143,7 @@
     <row r="252">
       <c r="A252" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 23:45:27</t>
+          <t>2026-03-12 14:45:27</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
@@ -50125,7 +50205,7 @@
     <row r="253">
       <c r="A253" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 23:02:09</t>
+          <t>2026-03-12 14:02:09</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
@@ -50187,7 +50267,7 @@
     <row r="254">
       <c r="A254" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 22:42:59</t>
+          <t>2026-03-12 13:42:59</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
@@ -50249,7 +50329,7 @@
     <row r="255">
       <c r="A255" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 01:39:10</t>
+          <t>2026-03-11 16:39:10</t>
         </is>
       </c>
       <c r="B255" s="13" t="inlineStr">
@@ -50311,7 +50391,7 @@
     <row r="256">
       <c r="A256" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:43:21</t>
+          <t>2026-03-11 15:43:21</t>
         </is>
       </c>
       <c r="B256" s="13" t="inlineStr">
@@ -50373,7 +50453,7 @@
     <row r="257">
       <c r="A257" s="13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:04:25</t>
+          <t>2026-03-11 15:04:25</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
@@ -50435,7 +50515,7 @@
     <row r="258">
       <c r="A258" s="13" t="inlineStr">
         <is>
-          <t>2026-03-11 22:54:02</t>
+          <t>2026-03-11 13:54:02</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
@@ -50497,7 +50577,7 @@
     <row r="259">
       <c r="A259" s="13" t="inlineStr">
         <is>
-          <t>2026-03-08 02:01:53</t>
+          <t>2026-03-07 17:01:53</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
@@ -50559,7 +50639,7 @@
     <row r="260">
       <c r="A260" s="13" t="inlineStr">
         <is>
-          <t>2026-03-02 02:18:59</t>
+          <t>2026-03-01 17:18:59</t>
         </is>
       </c>
       <c r="B260" s="13" t="inlineStr">
@@ -50621,7 +50701,7 @@
     <row r="261">
       <c r="A261" s="13" t="inlineStr">
         <is>
-          <t>2026-02-24 01:40:38</t>
+          <t>2026-02-23 16:40:38</t>
         </is>
       </c>
       <c r="B261" s="13" t="inlineStr">
@@ -50683,7 +50763,7 @@
     <row r="262">
       <c r="A262" s="13" t="inlineStr">
         <is>
-          <t>2026-02-24 00:10:31</t>
+          <t>2026-02-23 15:10:31</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
@@ -50745,7 +50825,7 @@
     <row r="263">
       <c r="A263" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 23:33:47</t>
+          <t>2026-02-23 14:33:47</t>
         </is>
       </c>
       <c r="B263" s="13" t="inlineStr">
@@ -50807,7 +50887,7 @@
     <row r="264">
       <c r="A264" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 22:40:54</t>
+          <t>2026-02-23 13:40:54</t>
         </is>
       </c>
       <c r="B264" s="13" t="inlineStr">
@@ -50869,7 +50949,7 @@
     <row r="265">
       <c r="A265" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 21:58:56</t>
+          <t>2026-02-23 12:58:56</t>
         </is>
       </c>
       <c r="B265" s="13" t="inlineStr">
@@ -50931,7 +51011,7 @@
     <row r="266">
       <c r="A266" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 19:21:48</t>
+          <t>2026-02-23 10:21:48</t>
         </is>
       </c>
       <c r="B266" s="13" t="inlineStr">
@@ -50993,7 +51073,7 @@
     <row r="267">
       <c r="A267" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 17:17:13</t>
+          <t>2026-02-23 08:17:13</t>
         </is>
       </c>
       <c r="B267" s="13" t="inlineStr">
@@ -51055,7 +51135,7 @@
     <row r="268">
       <c r="A268" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 04:22:01</t>
+          <t>2026-02-22 19:22:01</t>
         </is>
       </c>
       <c r="B268" s="13" t="inlineStr">
@@ -51117,7 +51197,7 @@
     <row r="269">
       <c r="A269" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 03:23:51</t>
+          <t>2026-02-22 18:23:51</t>
         </is>
       </c>
       <c r="B269" s="13" t="inlineStr">
@@ -51179,7 +51259,7 @@
     <row r="270">
       <c r="A270" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 02:58:18</t>
+          <t>2026-02-22 17:58:18</t>
         </is>
       </c>
       <c r="B270" s="13" t="inlineStr">
@@ -51241,7 +51321,7 @@
     <row r="271">
       <c r="A271" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 02:29:21</t>
+          <t>2026-02-22 17:29:21</t>
         </is>
       </c>
       <c r="B271" s="13" t="inlineStr">
@@ -51303,7 +51383,7 @@
     <row r="272">
       <c r="A272" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 01:59:09</t>
+          <t>2026-02-22 16:59:09</t>
         </is>
       </c>
       <c r="B272" s="13" t="inlineStr">
@@ -51365,7 +51445,7 @@
     <row r="273">
       <c r="A273" s="13" t="inlineStr">
         <is>
-          <t>2026-02-23 01:32:08</t>
+          <t>2026-02-22 16:32:08</t>
         </is>
       </c>
       <c r="B273" s="13" t="inlineStr">
@@ -51427,7 +51507,7 @@
     <row r="274">
       <c r="A274" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 03:34:36</t>
+          <t>2026-02-20 18:34:36</t>
         </is>
       </c>
       <c r="B274" s="13" t="inlineStr">
@@ -51489,7 +51569,7 @@
     <row r="275">
       <c r="A275" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 02:57:13</t>
+          <t>2026-02-20 17:57:13</t>
         </is>
       </c>
       <c r="B275" s="13" t="inlineStr">
@@ -51551,7 +51631,7 @@
     <row r="276">
       <c r="A276" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 02:19:01</t>
+          <t>2026-02-20 17:19:01</t>
         </is>
       </c>
       <c r="B276" s="13" t="inlineStr">
@@ -51613,7 +51693,7 @@
     <row r="277">
       <c r="A277" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 01:41:10</t>
+          <t>2026-02-20 16:41:10</t>
         </is>
       </c>
       <c r="B277" s="13" t="inlineStr">
@@ -51675,7 +51755,7 @@
     <row r="278">
       <c r="A278" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 00:57:47</t>
+          <t>2026-02-20 15:57:47</t>
         </is>
       </c>
       <c r="B278" s="13" t="inlineStr">
@@ -51737,7 +51817,7 @@
     <row r="279">
       <c r="A279" s="13" t="inlineStr">
         <is>
-          <t>2026-02-21 00:39:52</t>
+          <t>2026-02-20 15:39:52</t>
         </is>
       </c>
       <c r="B279" s="13" t="inlineStr">
@@ -51799,7 +51879,7 @@
     <row r="280">
       <c r="A280" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 01:21:13</t>
+          <t>2026-02-19 16:21:13</t>
         </is>
       </c>
       <c r="B280" s="13" t="inlineStr">
@@ -51861,7 +51941,7 @@
     <row r="281">
       <c r="A281" s="13" t="inlineStr">
         <is>
-          <t>2026-02-20 00:33:10</t>
+          <t>2026-02-19 15:33:10</t>
         </is>
       </c>
       <c r="B281" s="13" t="inlineStr">
@@ -51923,7 +52003,7 @@
     <row r="282">
       <c r="A282" s="13" t="inlineStr">
         <is>
-          <t>2026-02-18 00:37:38</t>
+          <t>2026-02-17 15:37:38</t>
         </is>
       </c>
       <c r="B282" s="13" t="inlineStr">
@@ -51985,7 +52065,7 @@
     <row r="283">
       <c r="A283" s="13" t="inlineStr">
         <is>
-          <t>2026-02-17 23:58:39</t>
+          <t>2026-02-17 14:58:39</t>
         </is>
       </c>
       <c r="B283" s="13" t="inlineStr">
@@ -52047,7 +52127,7 @@
     <row r="284">
       <c r="A284" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 02:24:16</t>
+          <t>2026-02-15 17:24:16</t>
         </is>
       </c>
       <c r="B284" s="13" t="inlineStr">
@@ -52109,7 +52189,7 @@
     <row r="285">
       <c r="A285" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 01:47:19</t>
+          <t>2026-02-15 16:47:19</t>
         </is>
       </c>
       <c r="B285" s="13" t="inlineStr">
@@ -52171,7 +52251,7 @@
     <row r="286">
       <c r="A286" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 00:56:43</t>
+          <t>2026-02-15 15:56:43</t>
         </is>
       </c>
       <c r="B286" s="13" t="inlineStr">
@@ -52233,7 +52313,7 @@
     <row r="287">
       <c r="A287" s="13" t="inlineStr">
         <is>
-          <t>2026-02-16 00:26:20</t>
+          <t>2026-02-15 15:26:20</t>
         </is>
       </c>
       <c r="B287" s="13" t="inlineStr">
@@ -52295,7 +52375,7 @@
     <row r="288">
       <c r="A288" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 23:48:44</t>
+          <t>2026-02-15 14:48:44</t>
         </is>
       </c>
       <c r="B288" s="13" t="inlineStr">
@@ -52357,7 +52437,7 @@
     <row r="289">
       <c r="A289" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 04:17:17</t>
+          <t>2026-02-14 19:17:17</t>
         </is>
       </c>
       <c r="B289" s="13" t="inlineStr">
@@ -52419,7 +52499,7 @@
     <row r="290">
       <c r="A290" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 03:53:01</t>
+          <t>2026-02-14 18:53:01</t>
         </is>
       </c>
       <c r="B290" s="13" t="inlineStr">
@@ -52481,7 +52561,7 @@
     <row r="291">
       <c r="A291" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:59:46</t>
+          <t>2026-02-14 17:59:46</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
@@ -52543,7 +52623,7 @@
     <row r="292">
       <c r="A292" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:26:42</t>
+          <t>2026-02-14 17:26:42</t>
         </is>
       </c>
       <c r="B292" s="13" t="inlineStr">
@@ -52605,7 +52685,7 @@
     <row r="293">
       <c r="A293" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 02:00:09</t>
+          <t>2026-02-14 17:00:09</t>
         </is>
       </c>
       <c r="B293" s="13" t="inlineStr">
@@ -52667,7 +52747,7 @@
     <row r="294">
       <c r="A294" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 01:39:16</t>
+          <t>2026-02-14 16:39:16</t>
         </is>
       </c>
       <c r="B294" s="13" t="inlineStr">
@@ -52729,7 +52809,7 @@
     <row r="295">
       <c r="A295" s="13" t="inlineStr">
         <is>
-          <t>2026-02-15 00:56:51</t>
+          <t>2026-02-14 15:56:51</t>
         </is>
       </c>
       <c r="B295" s="13" t="inlineStr">
@@ -52791,7 +52871,7 @@
     <row r="296">
       <c r="A296" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 23:52:26</t>
+          <t>2026-02-14 14:52:26</t>
         </is>
       </c>
       <c r="B296" s="13" t="inlineStr">
@@ -52853,7 +52933,7 @@
     <row r="297">
       <c r="A297" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 23:14:55</t>
+          <t>2026-02-14 14:14:55</t>
         </is>
       </c>
       <c r="B297" s="13" t="inlineStr">
@@ -52915,7 +52995,7 @@
     <row r="298">
       <c r="A298" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 04:19:58</t>
+          <t>2026-02-13 19:19:58</t>
         </is>
       </c>
       <c r="B298" s="13" t="inlineStr">
@@ -52977,7 +53057,7 @@
     <row r="299">
       <c r="A299" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 03:37:53</t>
+          <t>2026-02-13 18:37:53</t>
         </is>
       </c>
       <c r="B299" s="13" t="inlineStr">
@@ -53039,7 +53119,7 @@
     <row r="300">
       <c r="A300" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 03:03:31</t>
+          <t>2026-02-13 18:03:31</t>
         </is>
       </c>
       <c r="B300" s="13" t="inlineStr">
@@ -53101,7 +53181,7 @@
     <row r="301">
       <c r="A301" s="13" t="inlineStr">
         <is>
-          <t>2026-02-14 02:08:36</t>
+          <t>2026-02-13 17:08:36</t>
         </is>
       </c>
       <c r="B301" s="13" t="inlineStr">
@@ -53163,7 +53243,7 @@
     <row r="302">
       <c r="A302" s="13" t="inlineStr">
         <is>
-          <t>2026-02-12 00:20:03</t>
+          <t>2026-02-11 15:20:03</t>
         </is>
       </c>
       <c r="B302" s="13" t="inlineStr">
@@ -53225,7 +53305,7 @@
     <row r="303">
       <c r="A303" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 03:05:03</t>
+          <t>2026-02-10 18:05:03</t>
         </is>
       </c>
       <c r="B303" s="13" t="inlineStr">
@@ -53287,7 +53367,7 @@
     <row r="304">
       <c r="A304" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 02:14:02</t>
+          <t>2026-02-10 17:14:02</t>
         </is>
       </c>
       <c r="B304" s="13" t="inlineStr">
@@ -53349,7 +53429,7 @@
     <row r="305">
       <c r="A305" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 01:33:21</t>
+          <t>2026-02-10 16:33:21</t>
         </is>
       </c>
       <c r="B305" s="13" t="inlineStr">
@@ -53411,7 +53491,7 @@
     <row r="306">
       <c r="A306" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11 01:01:41</t>
+          <t>2026-02-10 16:01:41</t>
         </is>
       </c>
       <c r="B306" s="13" t="inlineStr">
@@ -53473,7 +53553,7 @@
     <row r="307">
       <c r="A307" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 01:49:32</t>
+          <t>2026-02-09 16:49:32</t>
         </is>
       </c>
       <c r="B307" s="13" t="inlineStr">
@@ -53535,7 +53615,7 @@
     <row r="308">
       <c r="A308" s="13" t="inlineStr">
         <is>
-          <t>2026-02-10 01:42:29</t>
+          <t>2026-02-09 16:42:29</t>
         </is>
       </c>
       <c r="B308" s="13" t="inlineStr">
@@ -53597,7 +53677,7 @@
     <row r="309">
       <c r="A309" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 23:44:10</t>
+          <t>2026-02-09 14:44:10</t>
         </is>
       </c>
       <c r="B309" s="13" t="inlineStr">
@@ -53659,7 +53739,7 @@
     <row r="310">
       <c r="A310" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 23:00:28</t>
+          <t>2026-02-09 14:00:28</t>
         </is>
       </c>
       <c r="B310" s="13" t="inlineStr">
@@ -53721,7 +53801,7 @@
     <row r="311">
       <c r="A311" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 00:27:49</t>
+          <t>2026-02-08 15:27:49</t>
         </is>
       </c>
       <c r="B311" s="13" t="inlineStr">
@@ -53783,7 +53863,7 @@
     <row r="312">
       <c r="A312" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09 00:16:42</t>
+          <t>2026-02-08 15:16:42</t>
         </is>
       </c>
       <c r="B312" s="13" t="inlineStr">
@@ -53845,7 +53925,7 @@
     <row r="313">
       <c r="A313" s="13" t="inlineStr">
         <is>
-          <t>2026-02-08 04:04:43</t>
+          <t>2026-02-07 19:04:43</t>
         </is>
       </c>
       <c r="B313" s="13" t="inlineStr">
@@ -53907,7 +53987,7 @@
     <row r="314">
       <c r="A314" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 03:13:11</t>
+          <t>2026-02-06 18:13:11</t>
         </is>
       </c>
       <c r="B314" s="13" t="inlineStr">
@@ -53969,7 +54049,7 @@
     <row r="315">
       <c r="A315" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 02:19:42</t>
+          <t>2026-02-06 17:19:42</t>
         </is>
       </c>
       <c r="B315" s="13" t="inlineStr">
@@ -54031,7 +54111,7 @@
     <row r="316">
       <c r="A316" s="13" t="inlineStr">
         <is>
-          <t>2026-02-07 01:37:36</t>
+          <t>2026-02-06 16:37:36</t>
         </is>
       </c>
       <c r="B316" s="13" t="inlineStr">
@@ -54093,7 +54173,7 @@
     <row r="317">
       <c r="A317" s="13" t="inlineStr">
         <is>
-          <t>2026-02-03 23:04:49</t>
+          <t>2026-02-03 14:04:49</t>
         </is>
       </c>
       <c r="B317" s="13" t="inlineStr">
@@ -54155,7 +54235,7 @@
     <row r="318">
       <c r="A318" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 23:21:38</t>
+          <t>2026-02-02 14:21:38</t>
         </is>
       </c>
       <c r="B318" s="13" t="inlineStr">
@@ -54217,7 +54297,7 @@
     <row r="319">
       <c r="A319" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 03:08:17</t>
+          <t>2026-02-01 18:08:17</t>
         </is>
       </c>
       <c r="B319" s="13" t="inlineStr">
@@ -54279,7 +54359,7 @@
     <row r="320">
       <c r="A320" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 02:41:55</t>
+          <t>2026-02-01 17:41:55</t>
         </is>
       </c>
       <c r="B320" s="13" t="inlineStr">
@@ -54341,7 +54421,7 @@
     <row r="321">
       <c r="A321" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 02:09:57</t>
+          <t>2026-02-01 17:09:57</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr">
@@ -54403,7 +54483,7 @@
     <row r="322">
       <c r="A322" s="13" t="inlineStr">
         <is>
-          <t>2026-02-02 01:41:49</t>
+          <t>2026-02-01 16:41:49</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
@@ -54465,7 +54545,7 @@
     <row r="323">
       <c r="A323" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 02:22:13</t>
+          <t>2026-01-31 17:22:13</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
@@ -54527,7 +54607,7 @@
     <row r="324">
       <c r="A324" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 01:20:54</t>
+          <t>2026-01-31 16:20:54</t>
         </is>
       </c>
       <c r="B324" s="13" t="inlineStr">
@@ -54589,7 +54669,7 @@
     <row r="325">
       <c r="A325" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 01:09:32</t>
+          <t>2026-01-31 16:09:32</t>
         </is>
       </c>
       <c r="B325" s="13" t="inlineStr">
@@ -54651,7 +54731,7 @@
     <row r="326">
       <c r="A326" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 00:29:37</t>
+          <t>2026-01-31 15:29:37</t>
         </is>
       </c>
       <c r="B326" s="13" t="inlineStr">
@@ -54713,7 +54793,7 @@
     <row r="327">
       <c r="A327" s="13" t="inlineStr">
         <is>
-          <t>2026-02-01 00:03:50</t>
+          <t>2026-01-31 15:03:50</t>
         </is>
       </c>
       <c r="B327" s="13" t="inlineStr">
@@ -54775,7 +54855,7 @@
     <row r="328">
       <c r="A328" s="13" t="inlineStr">
         <is>
-          <t>2026-01-31 23:15:28</t>
+          <t>2026-01-31 14:15:28</t>
         </is>
       </c>
       <c r="B328" s="13" t="inlineStr">
@@ -54837,7 +54917,7 @@
     <row r="329">
       <c r="A329" s="13" t="inlineStr">
         <is>
-          <t>2026-01-29 00:36:39</t>
+          <t>2026-01-28 15:36:39</t>
         </is>
       </c>
       <c r="B329" s="13" t="inlineStr">
@@ -54899,7 +54979,7 @@
     <row r="330">
       <c r="A330" s="13" t="inlineStr">
         <is>
-          <t>2026-01-29 00:02:45</t>
+          <t>2026-01-28 15:02:45</t>
         </is>
       </c>
       <c r="B330" s="13" t="inlineStr">
@@ -54961,7 +55041,7 @@
     <row r="331">
       <c r="A331" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 23:26:47</t>
+          <t>2026-01-28 14:26:47</t>
         </is>
       </c>
       <c r="B331" s="13" t="inlineStr">
@@ -55023,7 +55103,7 @@
     <row r="332">
       <c r="A332" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 23:04:33</t>
+          <t>2026-01-28 14:04:33</t>
         </is>
       </c>
       <c r="B332" s="13" t="inlineStr">
@@ -55085,7 +55165,7 @@
     <row r="333">
       <c r="A333" s="13" t="inlineStr">
         <is>
-          <t>2026-01-28 00:33:31</t>
+          <t>2026-01-27 15:33:31</t>
         </is>
       </c>
       <c r="B333" s="13" t="inlineStr">
@@ -55147,7 +55227,7 @@
     <row r="334">
       <c r="A334" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 23:59:21</t>
+          <t>2026-01-27 14:59:21</t>
         </is>
       </c>
       <c r="B334" s="13" t="inlineStr">
@@ -55209,7 +55289,7 @@
     <row r="335">
       <c r="A335" s="13" t="inlineStr">
         <is>
-          <t>2026-01-27 23:08:33</t>
+          <t>2026-01-27 14:08:33</t>
         </is>
       </c>
       <c r="B335" s="13" t="inlineStr">
@@ -55271,7 +55351,7 @@
     <row r="336">
       <c r="A336" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 23:28:17</t>
+          <t>2026-01-25 14:28:17</t>
         </is>
       </c>
       <c r="B336" s="13" t="inlineStr">
@@ -55333,7 +55413,7 @@
     <row r="337">
       <c r="A337" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 22:56:22</t>
+          <t>2026-01-25 13:56:22</t>
         </is>
       </c>
       <c r="B337" s="13" t="inlineStr">
@@ -55395,7 +55475,7 @@
     <row r="338">
       <c r="A338" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 22:28:25</t>
+          <t>2026-01-25 13:28:25</t>
         </is>
       </c>
       <c r="B338" s="13" t="inlineStr">
@@ -55457,7 +55537,7 @@
     <row r="339">
       <c r="A339" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 21:42:03</t>
+          <t>2026-01-25 12:42:03</t>
         </is>
       </c>
       <c r="B339" s="13" t="inlineStr">
@@ -55519,7 +55599,7 @@
     <row r="340">
       <c r="A340" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 19:38:23</t>
+          <t>2026-01-25 10:38:23</t>
         </is>
       </c>
       <c r="B340" s="13" t="inlineStr">
@@ -55581,7 +55661,7 @@
     <row r="341">
       <c r="A341" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 18:56:35</t>
+          <t>2026-01-25 09:56:35</t>
         </is>
       </c>
       <c r="B341" s="13" t="inlineStr">
@@ -55643,7 +55723,7 @@
     <row r="342">
       <c r="A342" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 18:29:19</t>
+          <t>2026-01-25 09:29:19</t>
         </is>
       </c>
       <c r="B342" s="13" t="inlineStr">
@@ -55705,7 +55785,7 @@
     <row r="343">
       <c r="A343" s="13" t="inlineStr">
         <is>
-          <t>2026-01-25 17:14:05</t>
+          <t>2026-01-25 08:14:05</t>
         </is>
       </c>
       <c r="B343" s="13" t="inlineStr">
@@ -55767,7 +55847,7 @@
     <row r="344">
       <c r="A344" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 02:47:24</t>
+          <t>2026-01-23 17:47:24</t>
         </is>
       </c>
       <c r="B344" s="13" t="inlineStr">
@@ -55829,7 +55909,7 @@
     <row r="345">
       <c r="A345" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 02:12:26</t>
+          <t>2026-01-23 17:12:26</t>
         </is>
       </c>
       <c r="B345" s="13" t="inlineStr">
@@ -55891,7 +55971,7 @@
     <row r="346">
       <c r="A346" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 01:33:34</t>
+          <t>2026-01-23 16:33:34</t>
         </is>
       </c>
       <c r="B346" s="13" t="inlineStr">
@@ -55953,7 +56033,7 @@
     <row r="347">
       <c r="A347" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 01:00:39</t>
+          <t>2026-01-23 16:00:39</t>
         </is>
       </c>
       <c r="B347" s="13" t="inlineStr">
@@ -56015,7 +56095,7 @@
     <row r="348">
       <c r="A348" s="13" t="inlineStr">
         <is>
-          <t>2026-01-24 00:19:07</t>
+          <t>2026-01-23 15:19:07</t>
         </is>
       </c>
       <c r="B348" s="13" t="inlineStr">
@@ -56077,7 +56157,7 @@
     <row r="349">
       <c r="A349" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 23:52:33</t>
+          <t>2026-01-23 14:52:33</t>
         </is>
       </c>
       <c r="B349" s="13" t="inlineStr">
@@ -56139,7 +56219,7 @@
     <row r="350">
       <c r="A350" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 23:19:19</t>
+          <t>2026-01-23 14:19:19</t>
         </is>
       </c>
       <c r="B350" s="13" t="inlineStr">
@@ -56201,7 +56281,7 @@
     <row r="351">
       <c r="A351" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36:59</t>
+          <t>2026-01-23 13:36:59</t>
         </is>
       </c>
       <c r="B351" s="13" t="inlineStr">
@@ -56263,7 +56343,7 @@
     <row r="352">
       <c r="A352" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 03:01:58</t>
+          <t>2026-01-22 18:01:58</t>
         </is>
       </c>
       <c r="B352" s="13" t="inlineStr">
@@ -56325,7 +56405,7 @@
     <row r="353">
       <c r="A353" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 02:25:41</t>
+          <t>2026-01-22 17:25:41</t>
         </is>
       </c>
       <c r="B353" s="13" t="inlineStr">
@@ -56387,7 +56467,7 @@
     <row r="354">
       <c r="A354" s="13" t="inlineStr">
         <is>
-          <t>2026-01-23 00:32:45</t>
+          <t>2026-01-22 15:32:45</t>
         </is>
       </c>
       <c r="B354" s="13" t="inlineStr">
@@ -56449,7 +56529,7 @@
     <row r="355">
       <c r="A355" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 23:54:46</t>
+          <t>2026-01-22 14:54:46</t>
         </is>
       </c>
       <c r="B355" s="13" t="inlineStr">
@@ -56511,7 +56591,7 @@
     <row r="356">
       <c r="A356" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 23:17:42</t>
+          <t>2026-01-22 14:17:42</t>
         </is>
       </c>
       <c r="B356" s="13" t="inlineStr">
@@ -56573,7 +56653,7 @@
     <row r="357">
       <c r="A357" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22 01:10:08</t>
+          <t>2026-01-21 16:10:08</t>
         </is>
       </c>
       <c r="B357" s="13" t="inlineStr">
@@ -56635,7 +56715,7 @@
     <row r="358">
       <c r="A358" s="13" t="inlineStr">
         <is>
-          <t>2026-01-21 00:27:51</t>
+          <t>2026-01-20 15:27:51</t>
         </is>
       </c>
       <c r="B358" s="13" t="inlineStr">
@@ -56697,7 +56777,7 @@
     <row r="359">
       <c r="A359" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 23:25:34</t>
+          <t>2026-01-20 14:25:34</t>
         </is>
       </c>
       <c r="B359" s="13" t="inlineStr">
@@ -56759,7 +56839,7 @@
     <row r="360">
       <c r="A360" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20 22:56:13</t>
+          <t>2026-01-20 13:56:13</t>
         </is>
       </c>
       <c r="B360" s="13" t="inlineStr">
@@ -56821,7 +56901,7 @@
     <row r="361">
       <c r="A361" s="13" t="inlineStr">
         <is>
-          <t>2026-01-19 01:59:11</t>
+          <t>2026-01-18 16:59:11</t>
         </is>
       </c>
       <c r="B361" s="13" t="inlineStr">
@@ -56883,7 +56963,7 @@
     <row r="362">
       <c r="A362" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 03:05:32</t>
+          <t>2026-01-17 18:05:32</t>
         </is>
       </c>
       <c r="B362" s="13" t="inlineStr">
@@ -56945,7 +57025,7 @@
     <row r="363">
       <c r="A363" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 02:19:17</t>
+          <t>2026-01-17 17:19:17</t>
         </is>
       </c>
       <c r="B363" s="13" t="inlineStr">
@@ -57007,7 +57087,7 @@
     <row r="364">
       <c r="A364" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 01:58:17</t>
+          <t>2026-01-17 16:58:17</t>
         </is>
       </c>
       <c r="B364" s="13" t="inlineStr">
@@ -57069,7 +57149,7 @@
     <row r="365">
       <c r="A365" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 01:18:29</t>
+          <t>2026-01-17 16:18:29</t>
         </is>
       </c>
       <c r="B365" s="13" t="inlineStr">
@@ -57131,7 +57211,7 @@
     <row r="366">
       <c r="A366" s="13" t="inlineStr">
         <is>
-          <t>2026-01-18 00:38:58</t>
+          <t>2026-01-17 15:38:58</t>
         </is>
       </c>
       <c r="B366" s="13" t="inlineStr">
@@ -57193,7 +57273,7 @@
     <row r="367">
       <c r="A367" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 18:46:30</t>
+          <t>2026-01-17 09:46:30</t>
         </is>
       </c>
       <c r="B367" s="13" t="inlineStr">
@@ -57255,7 +57335,7 @@
     <row r="368">
       <c r="A368" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 02:21:36</t>
+          <t>2026-01-16 17:21:36</t>
         </is>
       </c>
       <c r="B368" s="13" t="inlineStr">
@@ -57317,7 +57397,7 @@
     <row r="369">
       <c r="A369" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 01:51:05</t>
+          <t>2026-01-16 16:51:05</t>
         </is>
       </c>
       <c r="B369" s="13" t="inlineStr">
@@ -57379,7 +57459,7 @@
     <row r="370">
       <c r="A370" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17 01:18:22</t>
+          <t>2026-01-16 16:18:22</t>
         </is>
       </c>
       <c r="B370" s="13" t="inlineStr">
@@ -57441,7 +57521,7 @@
     <row r="371">
       <c r="A371" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 01:41:15</t>
+          <t>2026-01-15 16:41:15</t>
         </is>
       </c>
       <c r="B371" s="13" t="inlineStr">
@@ -57503,7 +57583,7 @@
     <row r="372">
       <c r="A372" s="13" t="inlineStr">
         <is>
-          <t>2026-01-16 01:05:38</t>
+          <t>2026-01-15 16:05:38</t>
         </is>
       </c>
       <c r="B372" s="13" t="inlineStr">
@@ -57565,7 +57645,7 @@
     <row r="373">
       <c r="A373" s="13" t="inlineStr">
         <is>
-          <t>2026-01-14 00:57:21</t>
+          <t>2026-01-13 15:57:21</t>
         </is>
       </c>
       <c r="B373" s="13" t="inlineStr">
@@ -57627,7 +57707,7 @@
     <row r="374">
       <c r="A374" s="13" t="inlineStr">
         <is>
-          <t>2026-01-14 00:19:49</t>
+          <t>2026-01-13 15:19:49</t>
         </is>
       </c>
       <c r="B374" s="13" t="inlineStr">
@@ -57689,7 +57769,7 @@
     <row r="375">
       <c r="A375" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 23:53:29</t>
+          <t>2026-01-13 14:53:29</t>
         </is>
       </c>
       <c r="B375" s="13" t="inlineStr">
@@ -57751,7 +57831,7 @@
     <row r="376">
       <c r="A376" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 02:23:29</t>
+          <t>2026-01-12 17:23:29</t>
         </is>
       </c>
       <c r="B376" s="13" t="inlineStr">
@@ -57813,7 +57893,7 @@
     <row r="377">
       <c r="A377" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 01:42:12</t>
+          <t>2026-01-12 16:42:12</t>
         </is>
       </c>
       <c r="B377" s="13" t="inlineStr">
@@ -57875,7 +57955,7 @@
     <row r="378">
       <c r="A378" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 01:17:01</t>
+          <t>2026-01-12 16:17:01</t>
         </is>
       </c>
       <c r="B378" s="13" t="inlineStr">
@@ -57937,7 +58017,7 @@
     <row r="379">
       <c r="A379" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13 00:43:11</t>
+          <t>2026-01-12 15:43:11</t>
         </is>
       </c>
       <c r="B379" s="13" t="inlineStr">
@@ -57999,7 +58079,7 @@
     <row r="380">
       <c r="A380" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 17:24:44</t>
+          <t>2026-01-12 08:24:44</t>
         </is>
       </c>
       <c r="B380" s="13" t="inlineStr">
@@ -58061,7 +58141,7 @@
     <row r="381">
       <c r="A381" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12 03:12:16</t>
+          <t>2026-01-11 18:12:16</t>
         </is>
       </c>
       <c r="B381" s="13" t="inlineStr">
@@ -58123,7 +58203,7 @@
     <row r="382">
       <c r="A382" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 02:54:03</t>
+          <t>2026-01-10 17:54:03</t>
         </is>
       </c>
       <c r="B382" s="13" t="inlineStr">
@@ -58185,7 +58265,7 @@
     <row r="383">
       <c r="A383" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 02:14:56</t>
+          <t>2026-01-10 17:14:56</t>
         </is>
       </c>
       <c r="B383" s="13" t="inlineStr">
@@ -58247,7 +58327,7 @@
     <row r="384">
       <c r="A384" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 01:17:21</t>
+          <t>2026-01-10 16:17:21</t>
         </is>
       </c>
       <c r="B384" s="13" t="inlineStr">
@@ -58309,7 +58389,7 @@
     <row r="385">
       <c r="A385" s="13" t="inlineStr">
         <is>
-          <t>2026-01-11 00:22:11</t>
+          <t>2026-01-10 15:22:11</t>
         </is>
       </c>
       <c r="B385" s="13" t="inlineStr">
@@ -58371,7 +58451,7 @@
     <row r="386">
       <c r="A386" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 23:38:24</t>
+          <t>2026-01-10 14:38:24</t>
         </is>
       </c>
       <c r="B386" s="13" t="inlineStr">
@@ -58433,7 +58513,7 @@
     <row r="387">
       <c r="A387" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 02:54:19</t>
+          <t>2026-01-09 17:54:19</t>
         </is>
       </c>
       <c r="B387" s="13" t="inlineStr">
@@ -58495,7 +58575,7 @@
     <row r="388">
       <c r="A388" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10 02:00:16</t>
+          <t>2026-01-09 17:00:16</t>
         </is>
       </c>
       <c r="B388" s="13" t="inlineStr">
@@ -58557,7 +58637,7 @@
     <row r="389">
       <c r="A389" s="13" t="inlineStr">
         <is>
-          <t>2026-01-09 23:36:27</t>
+          <t>2026-01-09 14:36:27</t>
         </is>
       </c>
       <c r="B389" s="13" t="inlineStr">
@@ -58616,8 +58696,70 @@
         </is>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-05 14:21:47</t>
+        </is>
+      </c>
+      <c r="B390" s="13" t="inlineStr">
+        <is>
+          <t>ランク</t>
+        </is>
+      </c>
+      <c r="C390" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D390" s="13" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E390" s="13" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F390" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G390" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H390" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I390" s="13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J390" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K390" s="14" t="inlineStr"/>
+      <c r="L390" s="14" t="inlineStr"/>
+      <c r="M390" s="14" t="inlineStr"/>
+      <c r="N390" s="14" t="inlineStr"/>
+      <c r="O390" s="14" t="inlineStr"/>
+      <c r="P390" s="13" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P389"/>
+  <autoFilter ref="A1:P390"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-07 01:47:34</t>
+          <t>出力日時：2026-08-07 05:59:54</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-07 05:59:54</t>
+          <t>出力日時：2026-08-08 04:37:57</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-08 04:37:57</t>
+          <t>出力日時：2026-08-09 04:51:20</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-09 04:51:20</t>
+          <t>出力日時：2026-08-10 06:00:35</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'キュー別'!$A$1:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'チャンピオン別'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SUPチャンピオン別'!$A$1:$L$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$390</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$390</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$391</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$391</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,14 +532,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>対象期間：2026-01-09 23:36:27 ～ 2026-08-10 23:30:12</t>
+          <t>対象期間：2026-01-05 23:21:47 ～ 2026-08-10 23:30:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-11 00:38:07</t>
+          <t>出力日時：2026-08-11 12:05:15</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.4755784061696658</v>
+        <v>0.4743589743589743</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.704370179948586</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5.372750642673521</v>
+        <v>5.371794871794871</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>8.9280205655527</v>
+        <v>8.928205128205128</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>59.89717223650386</v>
+        <v>59.83333333333334</v>
       </c>
     </row>
     <row r="15">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2.036786632390745</v>
+        <v>2.034538461538463</v>
       </c>
     </row>
     <row r="16">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>57.43444730077121</v>
+        <v>57.4025641025641</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1.849177377892031</v>
+        <v>1.848282051282051</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.5065359477124183</v>
+        <v>0.504885993485342</v>
       </c>
     </row>
     <row r="24">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>1.477124183006536</v>
+        <v>1.472312703583062</v>
       </c>
     </row>
     <row r="25">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.202614379084967</v>
+        <v>5.201954397394137</v>
       </c>
     </row>
     <row r="26">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>9.803921568627452</v>
+        <v>9.801302931596091</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>36.58823529411764</v>
+        <v>36.58306188925081</v>
       </c>
     </row>
     <row r="29">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1.256895424836601</v>
+        <v>1.25657980456026</v>
       </c>
     </row>
     <row r="30">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>64.7516339869281</v>
+        <v>64.68729641693811</v>
       </c>
     </row>
     <row r="31">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>2.083202614379085</v>
+        <v>2.08130293159609</v>
       </c>
     </row>
   </sheetData>
@@ -821,7 +821,7 @@
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>155</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.5065359477124183</v>
+        <v>0.504885993485342</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.477124183006536</v>
+        <v>1.472312703583062</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5.202614379084967</v>
+        <v>5.201954397394137</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9.803921568627452</v>
+        <v>9.801302931596091</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.256895424836601</v>
+        <v>1.25657980456026</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>64.7516339869281</v>
+        <v>64.68729641693811</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>2.083202614379085</v>
+        <v>2.08130293159609</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.924590163934426</v>
+        <v>4.924590163934425</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>32.32786885245902</v>
@@ -1133,7 +1133,7 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>2.226996805111821</v>
+        <v>2.226996805111822</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>54.02875399361022</v>
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>32</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4155844155844156</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.157894736842105</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>5.828947368421052</v>
+        <v>5.818181818181818</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>10.07894736842105</v>
+        <v>10.06493506493507</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.253421052631579</v>
+        <v>1.252207792207792</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>71.46052631578948</v>
+        <v>71.11688311688312</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.231447368421053</v>
+        <v>2.221948051948053</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.490185185185185</v>
+        <v>1.490185185185186</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>62.64814814814815</v>
@@ -1516,25 +1516,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.775</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.153846153846154</v>
+        <v>5.15</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.17948717948718</v>
+        <v>7.225</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.232820512820513</v>
+        <v>1.231</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.97435897435897</v>
+        <v>53.75</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.871025641025641</v>
+        <v>1.86175</v>
       </c>
     </row>
     <row r="6">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5.148285714285715</v>
+        <v>5.148285714285714</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>34.6</v>
@@ -1800,7 +1800,7 @@
         <v>25.625</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.85625</v>
+        <v>0.8562500000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5.050000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>16.25</v>
@@ -2833,25 +2833,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.775</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.153846153846154</v>
+        <v>5.15</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.17948717948718</v>
+        <v>7.225</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.232820512820513</v>
+        <v>1.231</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.97435897435897</v>
+        <v>53.75</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.871025641025641</v>
+        <v>1.86175</v>
       </c>
     </row>
     <row r="6">
@@ -3266,7 +3266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V390"/>
+  <dimension ref="A1:V391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -34525,8 +34525,88 @@
         </is>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-05 23:21:47</t>
+        </is>
+      </c>
+      <c r="B391" s="7" t="inlineStr">
+        <is>
+          <t>ランク(ソロ/デュオ)</t>
+        </is>
+      </c>
+      <c r="C391" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D391" s="7" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E391" s="7" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F391" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G391" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H391" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I391" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J391" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K391" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="L391" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M391" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N391" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="O391" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P391" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q391" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R391" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S391" s="11" t="n">
+        <v>6751</v>
+      </c>
+      <c r="T391" s="11" t="n">
+        <v>2219</v>
+      </c>
+      <c r="U391" s="6" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V391" s="7" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V390"/>
+  <autoFilter ref="A1:V391"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34537,7 +34617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P390"/>
+  <dimension ref="A1:P391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -58758,8 +58838,70 @@
         </is>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-05 23:21:47</t>
+        </is>
+      </c>
+      <c r="B391" s="13" t="inlineStr">
+        <is>
+          <t>ランク</t>
+        </is>
+      </c>
+      <c r="C391" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D391" s="13" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E391" s="13" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F391" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G391" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H391" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I391" s="13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J391" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K391" s="14" t="inlineStr"/>
+      <c r="L391" s="14" t="inlineStr"/>
+      <c r="M391" s="14" t="inlineStr"/>
+      <c r="N391" s="14" t="inlineStr"/>
+      <c r="O391" s="14" t="inlineStr"/>
+      <c r="P391" s="13" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P390"/>
+  <autoFilter ref="A1:P391"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'キュー別'!$A$1:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'チャンピオン別'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SUPチャンピオン別'!$A$1:$L$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$391</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$391</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$390</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$390</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,14 +532,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>対象期間：2026-01-05 23:21:47 ～ 2026-08-10 23:30:12</t>
+          <t>対象期間：2026-01-09 23:36:27 ～ 2026-08-10 23:30:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-11 12:05:15</t>
+          <t>出力日時：2026-08-12 00:35:58</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.4743589743589743</v>
+        <v>0.4755784061696658</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.7</v>
+        <v>1.704370179948586</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5.371794871794871</v>
+        <v>5.372750642673521</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>8.928205128205128</v>
+        <v>8.9280205655527</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>59.83333333333334</v>
+        <v>59.89717223650386</v>
       </c>
     </row>
     <row r="15">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2.034538461538463</v>
+        <v>2.036786632390745</v>
       </c>
     </row>
     <row r="16">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>57.4025641025641</v>
+        <v>57.43444730077121</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1.848282051282051</v>
+        <v>1.849177377892031</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.504885993485342</v>
+        <v>0.5065359477124183</v>
       </c>
     </row>
     <row r="24">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>1.472312703583062</v>
+        <v>1.477124183006536</v>
       </c>
     </row>
     <row r="25">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.201954397394137</v>
+        <v>5.202614379084967</v>
       </c>
     </row>
     <row r="26">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>9.801302931596091</v>
+        <v>9.803921568627452</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>36.58306188925081</v>
+        <v>36.58823529411764</v>
       </c>
     </row>
     <row r="29">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1.25657980456026</v>
+        <v>1.256895424836601</v>
       </c>
     </row>
     <row r="30">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>64.68729641693811</v>
+        <v>64.7516339869281</v>
       </c>
     </row>
     <row r="31">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>2.08130293159609</v>
+        <v>2.083202614379085</v>
       </c>
     </row>
   </sheetData>
@@ -821,7 +821,7 @@
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>155</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.504885993485342</v>
+        <v>0.5065359477124183</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.472312703583062</v>
+        <v>1.477124183006536</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5.201954397394137</v>
+        <v>5.202614379084967</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9.801302931596091</v>
+        <v>9.803921568627452</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.25657980456026</v>
+        <v>1.256895424836601</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>64.68729641693811</v>
+        <v>64.7516339869281</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>2.08130293159609</v>
+        <v>2.083202614379085</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.924590163934425</v>
+        <v>4.924590163934426</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>32.32786885245902</v>
@@ -1133,7 +1133,7 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>2.226996805111822</v>
+        <v>2.226996805111821</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>54.02875399361022</v>
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>32</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.4155844155844156</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.142857142857143</v>
+        <v>1.157894736842105</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>5.818181818181818</v>
+        <v>5.828947368421052</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>10.06493506493507</v>
+        <v>10.07894736842105</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.252207792207792</v>
+        <v>1.253421052631579</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>71.11688311688312</v>
+        <v>71.46052631578948</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.221948051948053</v>
+        <v>2.231447368421053</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.490185185185186</v>
+        <v>1.490185185185185</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>62.64814814814815</v>
@@ -1516,25 +1516,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.775</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.15</v>
+        <v>5.153846153846154</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.225</v>
+        <v>7.17948717948718</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.231</v>
+        <v>1.232820512820513</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.75</v>
+        <v>53.97435897435897</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.86175</v>
+        <v>1.871025641025641</v>
       </c>
     </row>
     <row r="6">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5.148285714285714</v>
+        <v>5.148285714285715</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>34.6</v>
@@ -1800,7 +1800,7 @@
         <v>25.625</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.8562500000000001</v>
+        <v>0.85625</v>
       </c>
     </row>
     <row r="12">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5.05</v>
+        <v>5.050000000000001</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>16.25</v>
@@ -2833,25 +2833,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.775</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.15</v>
+        <v>5.153846153846154</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.225</v>
+        <v>7.17948717948718</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -2859,13 +2859,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.231</v>
+        <v>1.232820512820513</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>53.75</v>
+        <v>53.97435897435897</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.86175</v>
+        <v>1.871025641025641</v>
       </c>
     </row>
     <row r="6">
@@ -3266,7 +3266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V391"/>
+  <dimension ref="A1:V390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -34525,88 +34525,8 @@
         </is>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" s="7" t="inlineStr">
-        <is>
-          <t>2026-01-05 23:21:47</t>
-        </is>
-      </c>
-      <c r="B391" s="7" t="inlineStr">
-        <is>
-          <t>ランク(ソロ/デュオ)</t>
-        </is>
-      </c>
-      <c r="C391" s="12" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D391" s="7" t="inlineStr">
-        <is>
-          <t>SUP</t>
-        </is>
-      </c>
-      <c r="E391" s="7" t="inlineStr">
-        <is>
-          <t>ジャンナ</t>
-        </is>
-      </c>
-      <c r="F391" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G391" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H391" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I391" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J391" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="K391" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="L391" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="M391" s="6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N391" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="O391" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P391" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q391" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R391" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S391" s="11" t="n">
-        <v>6751</v>
-      </c>
-      <c r="T391" s="11" t="n">
-        <v>2219</v>
-      </c>
-      <c r="U391" s="6" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="V391" s="7" t="inlineStr">
-        <is>
-          <t>JP1_556572228</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V391"/>
+  <autoFilter ref="A1:V390"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34617,7 +34537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P391"/>
+  <dimension ref="A1:P390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -58838,70 +58758,8 @@
         </is>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" s="13" t="inlineStr">
-        <is>
-          <t>2026-01-05 23:21:47</t>
-        </is>
-      </c>
-      <c r="B391" s="13" t="inlineStr">
-        <is>
-          <t>ランク</t>
-        </is>
-      </c>
-      <c r="C391" s="13" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D391" s="13" t="inlineStr">
-        <is>
-          <t>SUP</t>
-        </is>
-      </c>
-      <c r="E391" s="13" t="inlineStr">
-        <is>
-          <t>ジャンナ</t>
-        </is>
-      </c>
-      <c r="F391" s="13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G391" s="13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H391" s="13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I391" s="13" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J391" s="13" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K391" s="14" t="inlineStr"/>
-      <c r="L391" s="14" t="inlineStr"/>
-      <c r="M391" s="14" t="inlineStr"/>
-      <c r="N391" s="14" t="inlineStr"/>
-      <c r="O391" s="14" t="inlineStr"/>
-      <c r="P391" s="13" t="inlineStr">
-        <is>
-          <t>JP1_556572228</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P391"/>
+  <autoFilter ref="A1:P390"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'キュー別'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'チャンピオン別'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SUPチャンピオン別'!$A$1:$L$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$401</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$402</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$402</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,14 +532,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>対象期間：2026-01-09 23:36:27 ～ 2026-08-18 03:23:21</t>
+          <t>対象期間：2026-01-05 23:21:47 ～ 2026-08-18 03:23:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-18 03:56:29</t>
+          <t>出力日時：2026-08-18 11:16:46</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.475</v>
+        <v>0.4738154613466334</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.685</v>
+        <v>1.680798004987531</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5.4275</v>
+        <v>5.42643391521197</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>8.967499999999999</v>
+        <v>8.967581047381547</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>59.1475</v>
+        <v>59.08728179551122</v>
       </c>
     </row>
     <row r="15">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2.00995</v>
+        <v>2.007830423940151</v>
       </c>
     </row>
     <row r="16">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>58.205</v>
+        <v>58.17206982543641</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1.8701</v>
+        <v>1.869177057356608</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.5047318611987381</v>
+        <v>0.5031446540880503</v>
       </c>
     </row>
     <row r="24">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>1.460567823343849</v>
+        <v>1.455974842767296</v>
       </c>
     </row>
     <row r="25">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.277602523659306</v>
+        <v>5.276729559748428</v>
       </c>
     </row>
     <row r="26">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>9.823343848580441</v>
+        <v>9.820754716981131</v>
       </c>
     </row>
     <row r="27">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>36.45110410094637</v>
+        <v>36.44654088050314</v>
       </c>
     </row>
     <row r="29">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1.250094637223975</v>
+        <v>1.249811320754717</v>
       </c>
     </row>
     <row r="30">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>65.47003154574132</v>
+        <v>65.40566037735849</v>
       </c>
     </row>
     <row r="31">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>2.101482649842271</v>
+        <v>2.099591194968554</v>
       </c>
     </row>
   </sheetData>
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>160</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.5047318611987381</v>
+        <v>0.5031446540880503</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.460567823343849</v>
+        <v>1.455974842767296</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5.277602523659306</v>
+        <v>5.276729559748428</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9.823343848580441</v>
+        <v>9.820754716981131</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.250094637223975</v>
+        <v>1.249811320754717</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>65.47003154574132</v>
+        <v>65.40566037735849</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>2.101482649842271</v>
+        <v>2.099591194968554</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.924590163934426</v>
+        <v>4.924590163934425</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>32.32786885245902</v>
@@ -1128,7 +1128,7 @@
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>34</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.4197530864197531</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.148148148148148</v>
+        <v>1.134146341463415</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>5.987654320987654</v>
+        <v>5.975609756097561</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>10.04938271604938</v>
+        <v>10.03658536585366</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.236296296296296</v>
+        <v>1.235365853658536</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>71.80246913580247</v>
+        <v>71.47560975609755</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.246666666666667</v>
+        <v>2.237560975609757</v>
       </c>
     </row>
     <row r="4">
@@ -1558,25 +1558,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.825</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.225</v>
+        <v>5.219512195121951</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.05</v>
+        <v>7.097560975609756</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.223</v>
+        <v>1.221463414634147</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>55.55</v>
+        <v>55.29268292682926</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.90925</v>
+        <v>1.899268292682927</v>
       </c>
     </row>
     <row r="6">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5.148285714285715</v>
+        <v>5.148285714285714</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>34.6</v>
@@ -1842,7 +1842,7 @@
         <v>25.625</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.85625</v>
+        <v>0.8562500000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5.050000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>16.25</v>
@@ -2875,25 +2875,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.825</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.225</v>
+        <v>5.219512195121951</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.05</v>
+        <v>7.097560975609756</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.223</v>
+        <v>1.221463414634147</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>55.55</v>
+        <v>55.29268292682926</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.90925</v>
+        <v>1.899268292682927</v>
       </c>
     </row>
     <row r="6">
@@ -3308,7 +3308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V401"/>
+  <dimension ref="A1:V402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -35447,8 +35447,88 @@
         </is>
       </c>
     </row>
+    <row r="402">
+      <c r="A402" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-05 23:21:47</t>
+        </is>
+      </c>
+      <c r="B402" s="7" t="inlineStr">
+        <is>
+          <t>ランク(ソロ/デュオ)</t>
+        </is>
+      </c>
+      <c r="C402" s="10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D402" s="7" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E402" s="7" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F402" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G402" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H402" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I402" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J402" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K402" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="L402" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M402" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N402" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="O402" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P402" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q402" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R402" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S402" s="11" t="n">
+        <v>6751</v>
+      </c>
+      <c r="T402" s="11" t="n">
+        <v>2219</v>
+      </c>
+      <c r="U402" s="6" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V402" s="7" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V401"/>
+  <autoFilter ref="A1:V402"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -35459,7 +35539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P401"/>
+  <dimension ref="A1:P402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -60362,8 +60442,70 @@
         </is>
       </c>
     </row>
+    <row r="402">
+      <c r="A402" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-05 23:21:47</t>
+        </is>
+      </c>
+      <c r="B402" s="13" t="inlineStr">
+        <is>
+          <t>ランク</t>
+        </is>
+      </c>
+      <c r="C402" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D402" s="13" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E402" s="13" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F402" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G402" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H402" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I402" s="13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J402" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K402" s="14" t="inlineStr"/>
+      <c r="L402" s="14" t="inlineStr"/>
+      <c r="M402" s="14" t="inlineStr"/>
+      <c r="N402" s="14" t="inlineStr"/>
+      <c r="O402" s="14" t="inlineStr"/>
+      <c r="P402" s="13" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P401"/>
+  <autoFilter ref="A1:P402"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'キュー別'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'チャンピオン別'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SUPチャンピオン別'!$A$1:$L$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$406</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$406</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'試合履歴'!$A$1:$V$407</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'レビュー'!$A$1:$P$407</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,14 +532,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>対象期間：2026-01-09 23:36:27 ～ 2026-08-19 00:20:03</t>
+          <t>対象期間：2026-01-05 23:21:47 ～ 2026-08-19 00:20:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-19 02:54:44</t>
+          <t>出力日時：2026-08-19 11:19:31</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.4740740740740741</v>
+        <v>0.4729064039408867</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.683950617283951</v>
+        <v>1.679802955665025</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5.432098765432099</v>
+        <v>5.431034482758621</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>8.980246913580247</v>
+        <v>8.980295566502463</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>58.84691358024691</v>
+        <v>58.78817733990148</v>
       </c>
     </row>
     <row r="15">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1.999802469135802</v>
+        <v>1.997733990147784</v>
       </c>
     </row>
     <row r="16">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>58.42962962962963</v>
+        <v>58.39655172413793</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1.87841975308642</v>
+        <v>1.877487684729064</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.5031055900621118</v>
+        <v>0.5015479876160991</v>
       </c>
     </row>
     <row r="24">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>1.462732919254658</v>
+        <v>1.458204334365325</v>
       </c>
     </row>
     <row r="25">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.285714285714286</v>
+        <v>5.284829721362229</v>
       </c>
     </row>
     <row r="26">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>9.826086956521738</v>
+        <v>9.823529411764707</v>
       </c>
     </row>
     <row r="27">
@@ -757,7 +757,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>36.42546583850932</v>
+        <v>36.42105263157895</v>
       </c>
     </row>
     <row r="29">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1.249130434782609</v>
+        <v>1.248854489164086</v>
       </c>
     </row>
     <row r="30">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>65.63975155279503</v>
+        <v>65.57585139318886</v>
       </c>
     </row>
     <row r="31">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>2.108354037267081</v>
+        <v>2.106470588235295</v>
       </c>
     </row>
   </sheetData>
@@ -898,39 +898,39 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>162</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.5031055900621118</v>
+        <v>0.5015479876160991</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.462732919254658</v>
+        <v>1.458204334365325</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5.285714285714286</v>
+        <v>5.284829721362229</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9.826086956521738</v>
+        <v>9.823529411764707</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1.249130434782609</v>
+        <v>1.248854489164086</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>65.63975155279503</v>
+        <v>65.57585139318886</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>2.108354037267081</v>
+        <v>2.106470588235295</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.924590163934426</v>
+        <v>4.924590163934425</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>32.32786885245902</v>
@@ -1128,14 +1128,14 @@
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>36</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.4186046511627907</v>
+        <v>0.4137931034482759</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.174418604651163</v>
+        <v>1.160919540229885</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>5.976744186046512</v>
+        <v>5.96551724137931</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>10.04651162790698</v>
+        <v>10.03448275862069</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1.233488372093023</v>
+        <v>1.23264367816092</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>72.06976744186046</v>
+        <v>71.75862068965517</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.263953488372093</v>
+        <v>2.255172413793104</v>
       </c>
     </row>
     <row r="4">
@@ -1506,7 +1506,7 @@
         <v>63.28571428571428</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.024821428571429</v>
+        <v>2.024821428571428</v>
       </c>
     </row>
     <row r="4">
@@ -1558,25 +1558,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.825</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.225</v>
+        <v>5.219512195121951</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.05</v>
+        <v>7.097560975609756</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.223</v>
+        <v>1.221463414634147</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>55.55</v>
+        <v>55.29268292682926</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.90925</v>
+        <v>1.899268292682927</v>
       </c>
     </row>
     <row r="6">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5.148285714285715</v>
+        <v>5.148285714285714</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>34.6</v>
@@ -1842,7 +1842,7 @@
         <v>25.625</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.85625</v>
+        <v>0.8562500000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5.050000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>16.25</v>
@@ -2823,7 +2823,7 @@
         <v>64.09090909090909</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>2.045636363636364</v>
+        <v>2.045636363636363</v>
       </c>
     </row>
     <row r="4">
@@ -2875,25 +2875,25 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.825</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5.225</v>
+        <v>5.219512195121951</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.05</v>
+        <v>7.097560975609756</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.223</v>
+        <v>1.221463414634147</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>55.55</v>
+        <v>55.29268292682926</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.90925</v>
+        <v>1.899268292682927</v>
       </c>
     </row>
     <row r="6">
@@ -3308,7 +3308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V406"/>
+  <dimension ref="A1:V407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -35847,8 +35847,88 @@
         </is>
       </c>
     </row>
+    <row r="407">
+      <c r="A407" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-05 23:21:47</t>
+        </is>
+      </c>
+      <c r="B407" s="7" t="inlineStr">
+        <is>
+          <t>ランク(ソロ/デュオ)</t>
+        </is>
+      </c>
+      <c r="C407" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D407" s="7" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E407" s="7" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F407" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G407" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H407" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I407" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J407" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K407" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="L407" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M407" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N407" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="O407" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P407" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q407" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R407" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S407" s="11" t="n">
+        <v>6751</v>
+      </c>
+      <c r="T407" s="11" t="n">
+        <v>2219</v>
+      </c>
+      <c r="U407" s="6" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V407" s="7" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V406"/>
+  <autoFilter ref="A1:V407"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -35859,7 +35939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P406"/>
+  <dimension ref="A1:P407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -61072,8 +61152,70 @@
         </is>
       </c>
     </row>
+    <row r="407">
+      <c r="A407" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-05 23:21:47</t>
+        </is>
+      </c>
+      <c r="B407" s="13" t="inlineStr">
+        <is>
+          <t>ランク</t>
+        </is>
+      </c>
+      <c r="C407" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D407" s="13" t="inlineStr">
+        <is>
+          <t>SUP</t>
+        </is>
+      </c>
+      <c r="E407" s="13" t="inlineStr">
+        <is>
+          <t>ジャンナ</t>
+        </is>
+      </c>
+      <c r="F407" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G407" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H407" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I407" s="13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J407" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K407" s="14" t="inlineStr"/>
+      <c r="L407" s="14" t="inlineStr"/>
+      <c r="M407" s="14" t="inlineStr"/>
+      <c r="N407" s="14" t="inlineStr"/>
+      <c r="O407" s="14" t="inlineStr"/>
+      <c r="P407" s="13" t="inlineStr">
+        <is>
+          <t>JP1_556572228</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P406"/>
+  <autoFilter ref="A1:P407"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-19 11:19:31</t>
+          <t>出力日時：2026-08-20 11:18:31</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-20 11:18:31</t>
+          <t>出力日時：2026-08-20 16:48:24</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-20 16:48:24</t>
+          <t>出力日時：2026-08-20 19:10:07</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-20 19:10:07</t>
+          <t>出力日時：2026-08-20 20:16:53</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-20 20:16:53</t>
+          <t>出力日時：2026-08-21 11:24:30</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-21 11:24:30</t>
+          <t>出力日時：2026-08-22 11:17:20</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-22 11:17:20</t>
+          <t>出力日時：2026-08-23 11:25:08</t>
         </is>
       </c>
     </row>

--- a/data/excel/lol_report.xlsx
+++ b/data/excel/lol_report.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>出力日時：2026-08-23 11:25:08</t>
+          <t>出力日時：2026-08-24 11:24:15</t>
         </is>
       </c>
     </row>
